--- a/data/calendario_promocional.xlsx
+++ b/data/calendario_promocional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anheuserbuschinbev-my.sharepoint.com/personal/99823517_ab-inbev_com/Documents/001. Projetos/Streamlit Calendario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="634" documentId="11_F25DC773A252ABDACC1048AAA9DA54025ADE5901" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FCB5B08-193D-479F-ACA4-429272790AE3}"/>
+  <xr:revisionPtr revIDLastSave="635" documentId="11_F25DC773A252ABDACC1048AAA9DA54025ADE5901" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9158674B-A876-442E-B1DB-69E5842D1692}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5350" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5351" uniqueCount="114">
   <si>
     <t>Data</t>
   </si>
@@ -385,6 +385,9 @@
   </si>
   <si>
     <t>FF LN</t>
+  </si>
+  <si>
+    <t>Imagem</t>
   </si>
 </sst>
 </file>
@@ -3320,8 +3323,8 @@
       <c r="H1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="1">
-        <v>0</v>
+      <c r="I1" s="1" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">

--- a/data/calendario_promocional.xlsx
+++ b/data/calendario_promocional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anheuserbuschinbev-my.sharepoint.com/personal/99823517_ab-inbev_com/Documents/001. Projetos/Streamlit Calendario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="635" documentId="11_F25DC773A252ABDACC1048AAA9DA54025ADE5901" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9158674B-A876-442E-B1DB-69E5842D1692}"/>
+  <xr:revisionPtr revIDLastSave="638" documentId="11_F25DC773A252ABDACC1048AAA9DA54025ADE5901" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{176B6E20-E60A-4402-877D-330CF4B55518}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32714,17 +32714,17 @@
         <v>1</v>
       </c>
       <c r="F981" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G981">
-        <v>5.19</v>
+        <v>6.29</v>
       </c>
       <c r="H981">
         <v>4.8900000000000006</v>
       </c>
       <c r="I981" s="2" t="str">
         <f>_xlfn.XLOOKUP(F981,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>FF350.png</v>
+        <v>FFLN.png</v>
       </c>
     </row>
     <row r="982" spans="1:9" x14ac:dyDescent="0.25">
@@ -32744,17 +32744,17 @@
         <v>1</v>
       </c>
       <c r="F982" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G982">
-        <v>6.29</v>
+        <v>5.19</v>
       </c>
       <c r="H982">
         <v>5.99</v>
       </c>
       <c r="I982" s="2" t="str">
         <f>_xlfn.XLOOKUP(F982,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>FFLN.png</v>
+        <v>FF350.png</v>
       </c>
     </row>
     <row r="983" spans="1:9" x14ac:dyDescent="0.25">
@@ -32834,17 +32834,17 @@
         <v>2</v>
       </c>
       <c r="F985" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G985">
-        <v>5.19</v>
+        <v>6.29</v>
       </c>
       <c r="H985">
         <v>4.8900000000000006</v>
       </c>
       <c r="I985" s="2" t="str">
         <f>_xlfn.XLOOKUP(F985,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>FF350.png</v>
+        <v>FFLN.png</v>
       </c>
     </row>
     <row r="986" spans="1:9" x14ac:dyDescent="0.25">
@@ -32864,17 +32864,17 @@
         <v>2</v>
       </c>
       <c r="F986" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G986">
-        <v>6.29</v>
+        <v>5.19</v>
       </c>
       <c r="H986">
         <v>5.99</v>
       </c>
       <c r="I986" s="2" t="str">
         <f>_xlfn.XLOOKUP(F986,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>FFLN.png</v>
+        <v>FF350.png</v>
       </c>
     </row>
     <row r="987" spans="1:9" x14ac:dyDescent="0.25">

--- a/data/calendario_promocional.xlsx
+++ b/data/calendario_promocional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anheuserbuschinbev-my.sharepoint.com/personal/99823517_ab-inbev_com/Documents/001. Projetos/Streamlit Calendario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="638" documentId="11_F25DC773A252ABDACC1048AAA9DA54025ADE5901" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{176B6E20-E60A-4402-877D-330CF4B55518}"/>
+  <xr:revisionPtr revIDLastSave="644" documentId="11_F25DC773A252ABDACC1048AAA9DA54025ADE5901" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77F540BD-EE21-4263-94A7-CEA6E2CC106F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32720,7 +32720,7 @@
         <v>6.29</v>
       </c>
       <c r="H981">
-        <v>4.8900000000000006</v>
+        <v>5.99</v>
       </c>
       <c r="I981" s="2" t="str">
         <f>_xlfn.XLOOKUP(F981,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -32750,7 +32750,7 @@
         <v>5.19</v>
       </c>
       <c r="H982">
-        <v>5.99</v>
+        <v>4.8900000000000006</v>
       </c>
       <c r="I982" s="2" t="str">
         <f>_xlfn.XLOOKUP(F982,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -32840,7 +32840,7 @@
         <v>6.29</v>
       </c>
       <c r="H985">
-        <v>4.8900000000000006</v>
+        <v>5.99</v>
       </c>
       <c r="I985" s="2" t="str">
         <f>_xlfn.XLOOKUP(F985,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -32870,7 +32870,7 @@
         <v>5.19</v>
       </c>
       <c r="H986">
-        <v>5.99</v>
+        <v>4.8900000000000006</v>
       </c>
       <c r="I986" s="2" t="str">
         <f>_xlfn.XLOOKUP(F986,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -32931,7 +32931,7 @@
         <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>10</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">

--- a/data/calendario_promocional.xlsx
+++ b/data/calendario_promocional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anheuserbuschinbev-my.sharepoint.com/personal/99823517_ab-inbev_com/Documents/001. Projetos/Streamlit Calendario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="745" documentId="11_F25DC773A252ABDACC1048AAA9DA54025ADE5901" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{29B2213F-8FF6-4FBA-A65A-4F0D67FA9F51}"/>
+  <xr:revisionPtr revIDLastSave="747" documentId="11_F25DC773A252ABDACC1048AAA9DA54025ADE5901" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A63E7851-6EA4-4116-A6A1-7C826A26DCD1}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -448,151 +448,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1560,7 +1416,7 @@
   </sheetData>
   <autoFilter ref="A1:D37" xr:uid="{C0BF5819-473C-445D-A53D-FC51ACB237C6}"/>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="15" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -3436,6 +3292,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34B2C8DF-4561-40B2-8E7C-6CD69559B9AE}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:I1037"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3471,7 +3328,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -3501,7 +3358,7 @@
         <v>GCAP1.png</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -3531,7 +3388,7 @@
         <v>GCAP1,5.png</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -3561,7 +3418,7 @@
         <v>GCAP1,5.png</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -3591,7 +3448,7 @@
         <v>GCAP1,5.png</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -3621,7 +3478,7 @@
         <v>GCAP1,5.png</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -3651,7 +3508,7 @@
         <v>PCP2.png</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -3681,7 +3538,7 @@
         <v>PCP2.png</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -3711,7 +3568,7 @@
         <v>PCP2.png</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
@@ -3741,7 +3598,7 @@
         <v>PCP2.png</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -3771,7 +3628,7 @@
         <v>PCP2.png</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
@@ -3801,7 +3658,7 @@
         <v>BAREP2.png</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>10</v>
       </c>
@@ -3831,7 +3688,7 @@
         <v>H2OHP500.png</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>10</v>
       </c>
@@ -3861,7 +3718,7 @@
         <v>H2OHP500.png</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>10</v>
       </c>
@@ -3891,7 +3748,7 @@
         <v>H2OHP500.png</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>10</v>
       </c>
@@ -3921,7 +3778,7 @@
         <v>H2OHP500.png</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>10</v>
       </c>
@@ -3951,7 +3808,7 @@
         <v>SUKP2.png</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>10</v>
       </c>
@@ -3981,7 +3838,7 @@
         <v>SUKP2.png</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>10</v>
       </c>
@@ -4011,7 +3868,7 @@
         <v>SUKP2.png</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>10</v>
       </c>
@@ -4041,7 +3898,7 @@
         <v>SUKP2.png</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>10</v>
       </c>
@@ -4071,7 +3928,7 @@
         <v>SUKP2.png</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>10</v>
       </c>
@@ -4101,7 +3958,7 @@
         <v>GCAP2.png</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>10</v>
       </c>
@@ -4131,7 +3988,7 @@
         <v>GCAP2.png</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>10</v>
       </c>
@@ -4161,7 +4018,7 @@
         <v>GCAP2.png</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>10</v>
       </c>
@@ -4191,7 +4048,7 @@
         <v>GCAP2.png</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>10</v>
       </c>
@@ -4221,7 +4078,7 @@
         <v>GCAP2.png</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>10</v>
       </c>
@@ -4251,7 +4108,7 @@
         <v>GCA350.png</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>10</v>
       </c>
@@ -4281,7 +4138,7 @@
         <v>GCA350.png</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>10</v>
       </c>
@@ -4311,7 +4168,7 @@
         <v>GCA350.png</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>10</v>
       </c>
@@ -4341,7 +4198,7 @@
         <v>GCA350.png</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>10</v>
       </c>
@@ -4371,7 +4228,7 @@
         <v>GCA350.png</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>10</v>
       </c>
@@ -4401,7 +4258,7 @@
         <v>BAREP2.png</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>10</v>
       </c>
@@ -4431,7 +4288,7 @@
         <v>H2OHP500.png</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>10</v>
       </c>
@@ -4461,7 +4318,7 @@
         <v>H2OHP500.png</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>10</v>
       </c>
@@ -4491,7 +4348,7 @@
         <v>H2OHP500.png</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>10</v>
       </c>
@@ -4521,7 +4378,7 @@
         <v>H2OHP500.png</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>10</v>
       </c>
@@ -4551,7 +4408,7 @@
         <v>PCB350.png</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>10</v>
       </c>
@@ -4581,7 +4438,7 @@
         <v>PCB350.png</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>10</v>
       </c>
@@ -4611,7 +4468,7 @@
         <v>PCB350.png</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>10</v>
       </c>
@@ -4641,7 +4498,7 @@
         <v>PCB350.png</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>10</v>
       </c>
@@ -4671,7 +4528,7 @@
         <v>PCB350.png</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>10</v>
       </c>
@@ -4701,7 +4558,7 @@
         <v>GCAP2.png</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>10</v>
       </c>
@@ -4731,7 +4588,7 @@
         <v>GCAP2.png</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>10</v>
       </c>
@@ -4761,7 +4618,7 @@
         <v>GCAP2.png</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>10</v>
       </c>
@@ -4791,7 +4648,7 @@
         <v>GCAP2.png</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>10</v>
       </c>
@@ -4821,7 +4678,7 @@
         <v>GCAP2.png</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>10</v>
       </c>
@@ -4851,7 +4708,7 @@
         <v>GCA269.png</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>10</v>
       </c>
@@ -4881,7 +4738,7 @@
         <v>GCA269.png</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>10</v>
       </c>
@@ -4911,7 +4768,7 @@
         <v>GCA269.png</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>10</v>
       </c>
@@ -4941,7 +4798,7 @@
         <v>GCA269.png</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>10</v>
       </c>
@@ -4971,7 +4828,7 @@
         <v>GCA269.png</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>10</v>
       </c>
@@ -5001,7 +4858,7 @@
         <v>PC269.png</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>10</v>
       </c>
@@ -5031,7 +4888,7 @@
         <v>PC269.png</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>10</v>
       </c>
@@ -5061,7 +4918,7 @@
         <v>PC269.png</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>10</v>
       </c>
@@ -5091,7 +4948,7 @@
         <v>PC269.png</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>10</v>
       </c>
@@ -5121,7 +4978,7 @@
         <v>PC269.png</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>10</v>
       </c>
@@ -5151,7 +5008,7 @@
         <v>GCAP1.png</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>10</v>
       </c>
@@ -5181,7 +5038,7 @@
         <v>GCAP1,5.png</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>10</v>
       </c>
@@ -5211,7 +5068,7 @@
         <v>GCAP1,5.png</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>10</v>
       </c>
@@ -5241,7 +5098,7 @@
         <v>GCAP1,5.png</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>10</v>
       </c>
@@ -5271,7 +5128,7 @@
         <v>GCAP1,5.png</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>10</v>
       </c>
@@ -5301,7 +5158,7 @@
         <v>PCP2.png</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>10</v>
       </c>
@@ -5331,7 +5188,7 @@
         <v>PCP2.png</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>10</v>
       </c>
@@ -5361,7 +5218,7 @@
         <v>PCP2.png</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>10</v>
       </c>
@@ -5391,7 +5248,7 @@
         <v>PCP2.png</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>10</v>
       </c>
@@ -5421,7 +5278,7 @@
         <v>PCP2.png</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>10</v>
       </c>
@@ -5451,7 +5308,7 @@
         <v>H2OHP1,5.png</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>10</v>
       </c>
@@ -5481,7 +5338,7 @@
         <v>H2OHP1,5.png</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>10</v>
       </c>
@@ -5511,7 +5368,7 @@
         <v>H2OHP1,5.png</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>10</v>
       </c>
@@ -5541,7 +5398,7 @@
         <v>H2OHP1,5.png</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>10</v>
       </c>
@@ -5571,7 +5428,7 @@
         <v>SUKP2.png</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>10</v>
       </c>
@@ -5601,7 +5458,7 @@
         <v>SUKP2.png</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>10</v>
       </c>
@@ -5631,7 +5488,7 @@
         <v>SUKP2.png</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>10</v>
       </c>
@@ -5661,7 +5518,7 @@
         <v>SUKP2.png</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>10</v>
       </c>
@@ -5691,7 +5548,7 @@
         <v>SUKP2.png</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>10</v>
       </c>
@@ -5721,7 +5578,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>10</v>
       </c>
@@ -5751,7 +5608,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>10</v>
       </c>
@@ -5781,7 +5638,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>10</v>
       </c>
@@ -5811,7 +5668,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>10</v>
       </c>
@@ -5841,7 +5698,7 @@
         <v>AP269.png</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>10</v>
       </c>
@@ -5871,7 +5728,7 @@
         <v>AP269.png</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>10</v>
       </c>
@@ -5901,7 +5758,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>10</v>
       </c>
@@ -5931,7 +5788,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>10</v>
       </c>
@@ -5961,7 +5818,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>10</v>
       </c>
@@ -5991,7 +5848,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>10</v>
       </c>
@@ -6021,7 +5878,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>10</v>
       </c>
@@ -6051,7 +5908,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>10</v>
       </c>
@@ -6081,7 +5938,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>10</v>
       </c>
@@ -6111,7 +5968,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>10</v>
       </c>
@@ -6141,7 +5998,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>10</v>
       </c>
@@ -6171,7 +6028,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>10</v>
       </c>
@@ -6201,7 +6058,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>10</v>
       </c>
@@ -6231,7 +6088,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>10</v>
       </c>
@@ -6261,7 +6118,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>10</v>
       </c>
@@ -6291,7 +6148,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>10</v>
       </c>
@@ -6321,7 +6178,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>10</v>
       </c>
@@ -6351,7 +6208,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>10</v>
       </c>
@@ -6381,7 +6238,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>10</v>
       </c>
@@ -6411,7 +6268,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>10</v>
       </c>
@@ -6441,7 +6298,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>10</v>
       </c>
@@ -6471,7 +6328,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>10</v>
       </c>
@@ -6501,7 +6358,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>10</v>
       </c>
@@ -6531,7 +6388,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>10</v>
       </c>
@@ -6561,7 +6418,7 @@
         <v>AP269.png</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>10</v>
       </c>
@@ -6591,7 +6448,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>10</v>
       </c>
@@ -6621,7 +6478,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>10</v>
       </c>
@@ -6651,7 +6508,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>10</v>
       </c>
@@ -6681,7 +6538,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>10</v>
       </c>
@@ -6711,7 +6568,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>10</v>
       </c>
@@ -6741,7 +6598,7 @@
         <v>AP269.png</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>10</v>
       </c>
@@ -6771,7 +6628,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>10</v>
       </c>
@@ -6801,7 +6658,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>10</v>
       </c>
@@ -6831,7 +6688,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>10</v>
       </c>
@@ -6861,7 +6718,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>10</v>
       </c>
@@ -6891,7 +6748,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>10</v>
       </c>
@@ -6921,7 +6778,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>10</v>
       </c>
@@ -6951,7 +6808,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>10</v>
       </c>
@@ -6981,7 +6838,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>10</v>
       </c>
@@ -7011,7 +6868,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>10</v>
       </c>
@@ -7041,7 +6898,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>10</v>
       </c>
@@ -7071,7 +6928,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>10</v>
       </c>
@@ -7101,7 +6958,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>10</v>
       </c>
@@ -7131,7 +6988,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>10</v>
       </c>
@@ -7161,7 +7018,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>10</v>
       </c>
@@ -7191,7 +7048,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>10</v>
       </c>
@@ -7221,7 +7078,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>10</v>
       </c>
@@ -7251,7 +7108,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>10</v>
       </c>
@@ -7281,7 +7138,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>10</v>
       </c>
@@ -7311,7 +7168,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>10</v>
       </c>
@@ -7341,7 +7198,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>10</v>
       </c>
@@ -7371,7 +7228,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>10</v>
       </c>
@@ -7401,7 +7258,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>10</v>
       </c>
@@ -7431,7 +7288,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>10</v>
       </c>
@@ -7461,7 +7318,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>10</v>
       </c>
@@ -7491,7 +7348,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>10</v>
       </c>
@@ -7521,7 +7378,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>10</v>
       </c>
@@ -7551,7 +7408,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>10</v>
       </c>
@@ -7581,7 +7438,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>10</v>
       </c>
@@ -7611,7 +7468,7 @@
         <v>BC350.png</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>10</v>
       </c>
@@ -7641,7 +7498,7 @@
         <v>BC350.png</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>10</v>
       </c>
@@ -7671,7 +7528,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>10</v>
       </c>
@@ -7701,7 +7558,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>10</v>
       </c>
@@ -7731,7 +7588,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>10</v>
       </c>
@@ -7761,7 +7618,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>10</v>
       </c>
@@ -7791,7 +7648,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>10</v>
       </c>
@@ -7821,7 +7678,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>10</v>
       </c>
@@ -7851,7 +7708,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>10</v>
       </c>
@@ -7881,7 +7738,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>10</v>
       </c>
@@ -7911,7 +7768,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>10</v>
       </c>
@@ -7941,7 +7798,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>10</v>
       </c>
@@ -7971,7 +7828,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>10</v>
       </c>
@@ -8001,7 +7858,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>10</v>
       </c>
@@ -8031,7 +7888,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>10</v>
       </c>
@@ -8061,7 +7918,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>10</v>
       </c>
@@ -8091,7 +7948,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>10</v>
       </c>
@@ -8121,7 +7978,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>10</v>
       </c>
@@ -8151,7 +8008,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>10</v>
       </c>
@@ -8181,7 +8038,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>10</v>
       </c>
@@ -8211,7 +8068,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>10</v>
       </c>
@@ -8241,7 +8098,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>10</v>
       </c>
@@ -8271,7 +8128,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>10</v>
       </c>
@@ -8301,7 +8158,7 @@
         <v>AP350.png</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>10</v>
       </c>
@@ -8331,7 +8188,7 @@
         <v>AP350.png</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>10</v>
       </c>
@@ -8361,7 +8218,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>10</v>
       </c>
@@ -8391,7 +8248,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>10</v>
       </c>
@@ -8421,7 +8278,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>10</v>
       </c>
@@ -8451,7 +8308,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>10</v>
       </c>
@@ -8481,7 +8338,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>10</v>
       </c>
@@ -8511,7 +8368,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>10</v>
       </c>
@@ -8541,7 +8398,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>10</v>
       </c>
@@ -8571,7 +8428,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>10</v>
       </c>
@@ -8601,7 +8458,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>10</v>
       </c>
@@ -8631,7 +8488,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>10</v>
       </c>
@@ -8661,7 +8518,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>10</v>
       </c>
@@ -8691,7 +8548,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>10</v>
       </c>
@@ -8721,7 +8578,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
         <v>10</v>
       </c>
@@ -8751,7 +8608,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
         <v>10</v>
       </c>
@@ -8781,7 +8638,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>10</v>
       </c>
@@ -8811,7 +8668,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>10</v>
       </c>
@@ -8841,7 +8698,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>10</v>
       </c>
@@ -8871,7 +8728,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
         <v>10</v>
       </c>
@@ -8901,7 +8758,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
         <v>10</v>
       </c>
@@ -8931,7 +8788,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
         <v>10</v>
       </c>
@@ -8961,7 +8818,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>10</v>
       </c>
@@ -8991,7 +8848,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
         <v>10</v>
       </c>
@@ -9021,7 +8878,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>10</v>
       </c>
@@ -9051,7 +8908,7 @@
         <v>STE269.png</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>10</v>
       </c>
@@ -9081,7 +8938,7 @@
         <v>STE269.png</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
         <v>10</v>
       </c>
@@ -9111,7 +8968,7 @@
         <v>STE269.png</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>10</v>
       </c>
@@ -9141,7 +8998,7 @@
         <v>STE269.png</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>10</v>
       </c>
@@ -9171,7 +9028,7 @@
         <v>STE269.png</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>10</v>
       </c>
@@ -9201,7 +9058,7 @@
         <v>STE269.png</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
         <v>10</v>
       </c>
@@ -9231,7 +9088,7 @@
         <v>STE269.png</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>10</v>
       </c>
@@ -9261,7 +9118,7 @@
         <v>STE269.png</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>10</v>
       </c>
@@ -9291,7 +9148,7 @@
         <v>BUD350.png</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>10</v>
       </c>
@@ -9321,7 +9178,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
         <v>10</v>
       </c>
@@ -9351,7 +9208,7 @@
         <v>BUD350.png</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
         <v>10</v>
       </c>
@@ -9381,7 +9238,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
         <v>10</v>
       </c>
@@ -9411,7 +9268,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
         <v>10</v>
       </c>
@@ -9441,7 +9298,7 @@
         <v>BUD350.png</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
         <v>10</v>
       </c>
@@ -9471,7 +9328,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
         <v>10</v>
       </c>
@@ -9501,7 +9358,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
         <v>10</v>
       </c>
@@ -9531,7 +9388,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
         <v>10</v>
       </c>
@@ -9561,7 +9418,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
         <v>10</v>
       </c>
@@ -9591,7 +9448,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
         <v>10</v>
       </c>
@@ -9621,7 +9478,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
         <v>10</v>
       </c>
@@ -9651,7 +9508,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
         <v>10</v>
       </c>
@@ -9681,7 +9538,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>10</v>
       </c>
@@ -9711,7 +9568,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>10</v>
       </c>
@@ -9741,7 +9598,7 @@
         <v>COR269.png</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>10</v>
       </c>
@@ -9771,7 +9628,7 @@
         <v>COR269.png</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>10</v>
       </c>
@@ -9801,7 +9658,7 @@
         <v>COR269.png</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>10</v>
       </c>
@@ -9831,7 +9688,7 @@
         <v>COR269.png</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>10</v>
       </c>
@@ -9861,7 +9718,7 @@
         <v>STE350.png</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>10</v>
       </c>
@@ -9891,7 +9748,7 @@
         <v>STE350.png</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
         <v>10</v>
       </c>
@@ -9921,7 +9778,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>10</v>
       </c>
@@ -9951,7 +9808,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>10</v>
       </c>
@@ -9981,7 +9838,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>10</v>
       </c>
@@ -10011,7 +9868,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>10</v>
       </c>
@@ -10041,7 +9898,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>10</v>
       </c>
@@ -10071,7 +9928,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
         <v>10</v>
       </c>
@@ -10101,7 +9958,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>10</v>
       </c>
@@ -10131,7 +9988,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
         <v>10</v>
       </c>
@@ -10161,7 +10018,7 @@
         <v>STE350.png</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
         <v>10</v>
       </c>
@@ -10191,7 +10048,7 @@
         <v>STE350.png</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
         <v>10</v>
       </c>
@@ -10221,7 +10078,7 @@
         <v>STE350.png</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
         <v>10</v>
       </c>
@@ -10251,7 +10108,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
         <v>10</v>
       </c>
@@ -10281,7 +10138,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
         <v>10</v>
       </c>
@@ -10311,7 +10168,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
         <v>10</v>
       </c>
@@ -10341,7 +10198,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
         <v>10</v>
       </c>
@@ -10371,7 +10228,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
         <v>10</v>
       </c>
@@ -10401,7 +10258,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
         <v>10</v>
       </c>
@@ -10431,7 +10288,7 @@
         <v>STE350.png</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
         <v>10</v>
       </c>
@@ -10461,7 +10318,7 @@
         <v>COR350.png</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
         <v>10</v>
       </c>
@@ -10491,7 +10348,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
         <v>10</v>
       </c>
@@ -10521,7 +10378,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
         <v>10</v>
       </c>
@@ -10551,7 +10408,7 @@
         <v>COR350.png</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
         <v>10</v>
       </c>
@@ -10581,7 +10438,7 @@
         <v>COR350.png</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
         <v>10</v>
       </c>
@@ -10611,7 +10468,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
         <v>10</v>
       </c>
@@ -10641,7 +10498,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
         <v>10</v>
       </c>
@@ -10671,7 +10528,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
         <v>10</v>
       </c>
@@ -10701,7 +10558,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
         <v>10</v>
       </c>
@@ -10731,7 +10588,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
         <v>10</v>
       </c>
@@ -10761,7 +10618,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
         <v>10</v>
       </c>
@@ -10791,7 +10648,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
         <v>10</v>
       </c>
@@ -10821,7 +10678,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
         <v>10</v>
       </c>
@@ -10851,7 +10708,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
         <v>10</v>
       </c>
@@ -10881,7 +10738,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
         <v>10</v>
       </c>
@@ -10911,7 +10768,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
         <v>10</v>
       </c>
@@ -10941,7 +10798,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
         <v>10</v>
       </c>
@@ -10971,7 +10828,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
         <v>10</v>
       </c>
@@ -11001,7 +10858,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
         <v>10</v>
       </c>
@@ -11031,7 +10888,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
         <v>10</v>
       </c>
@@ -11061,7 +10918,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
         <v>10</v>
       </c>
@@ -11091,7 +10948,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
         <v>10</v>
       </c>
@@ -11121,7 +10978,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
         <v>10</v>
       </c>
@@ -11151,7 +11008,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
         <v>10</v>
       </c>
@@ -11181,7 +11038,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
         <v>10</v>
       </c>
@@ -11211,7 +11068,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
         <v>10</v>
       </c>
@@ -11241,7 +11098,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
         <v>10</v>
       </c>
@@ -11271,7 +11128,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
         <v>10</v>
       </c>
@@ -11301,7 +11158,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
         <v>10</v>
       </c>
@@ -11331,7 +11188,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
         <v>10</v>
       </c>
@@ -11361,7 +11218,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
         <v>10</v>
       </c>
@@ -11391,7 +11248,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
         <v>10</v>
       </c>
@@ -11421,7 +11278,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
         <v>10</v>
       </c>
@@ -11451,7 +11308,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
         <v>10</v>
       </c>
@@ -11481,7 +11338,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
         <v>10</v>
       </c>
@@ -11511,7 +11368,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
         <v>10</v>
       </c>
@@ -11541,7 +11398,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
         <v>10</v>
       </c>
@@ -11571,7 +11428,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
         <v>10</v>
       </c>
@@ -11601,7 +11458,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
         <v>10</v>
       </c>
@@ -11631,7 +11488,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
         <v>10</v>
       </c>
@@ -11661,7 +11518,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
         <v>10</v>
       </c>
@@ -11691,7 +11548,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
         <v>10</v>
       </c>
@@ -11721,7 +11578,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
         <v>10</v>
       </c>
@@ -11751,7 +11608,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
         <v>10</v>
       </c>
@@ -11781,7 +11638,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
         <v>10</v>
       </c>
@@ -11811,7 +11668,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
         <v>10</v>
       </c>
@@ -11841,7 +11698,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
         <v>10</v>
       </c>
@@ -11871,7 +11728,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
         <v>10</v>
       </c>
@@ -11901,7 +11758,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
         <v>10</v>
       </c>
@@ -11931,7 +11788,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
         <v>10</v>
       </c>
@@ -11961,7 +11818,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
         <v>10</v>
       </c>
@@ -11991,7 +11848,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
         <v>10</v>
       </c>
@@ -12021,7 +11878,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
         <v>10</v>
       </c>
@@ -12051,7 +11908,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
         <v>10</v>
       </c>
@@ -12081,7 +11938,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
         <v>10</v>
       </c>
@@ -12111,7 +11968,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
         <v>10</v>
       </c>
@@ -12141,7 +11998,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
         <v>10</v>
       </c>
@@ -12171,7 +12028,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
         <v>10</v>
       </c>
@@ -12201,7 +12058,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
         <v>10</v>
       </c>
@@ -12231,7 +12088,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
         <v>10</v>
       </c>
@@ -12261,7 +12118,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
         <v>10</v>
       </c>
@@ -12291,7 +12148,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
         <v>10</v>
       </c>
@@ -12321,7 +12178,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
         <v>10</v>
       </c>
@@ -12351,7 +12208,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
         <v>10</v>
       </c>
@@ -12381,7 +12238,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
         <v>10</v>
       </c>
@@ -12411,7 +12268,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
         <v>10</v>
       </c>
@@ -12441,7 +12298,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
         <v>10</v>
       </c>
@@ -12471,7 +12328,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
         <v>10</v>
       </c>
@@ -12501,7 +12358,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
         <v>10</v>
       </c>
@@ -12531,7 +12388,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
         <v>10</v>
       </c>
@@ -12561,7 +12418,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
         <v>10</v>
       </c>
@@ -12591,7 +12448,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
         <v>10</v>
       </c>
@@ -12621,7 +12478,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
         <v>10</v>
       </c>
@@ -12651,7 +12508,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
         <v>10</v>
       </c>
@@ -12681,7 +12538,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
         <v>10</v>
       </c>
@@ -12711,7 +12568,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
         <v>10</v>
       </c>
@@ -12741,7 +12598,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
         <v>10</v>
       </c>
@@ -12771,7 +12628,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
         <v>10</v>
       </c>
@@ -12801,7 +12658,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" s="2" t="s">
         <v>10</v>
       </c>
@@ -12831,7 +12688,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
         <v>10</v>
       </c>
@@ -12861,7 +12718,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
         <v>10</v>
       </c>
@@ -12891,7 +12748,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
         <v>10</v>
       </c>
@@ -12921,7 +12778,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" s="2" t="s">
         <v>10</v>
       </c>
@@ -12951,7 +12808,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
         <v>10</v>
       </c>
@@ -12981,7 +12838,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
         <v>10</v>
       </c>
@@ -13011,7 +12868,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
         <v>10</v>
       </c>
@@ -13041,7 +12898,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
         <v>10</v>
       </c>
@@ -13071,7 +12928,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
         <v>10</v>
       </c>
@@ -13101,7 +12958,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
         <v>106</v>
       </c>
@@ -13131,7 +12988,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
         <v>106</v>
       </c>
@@ -13161,7 +13018,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
         <v>106</v>
       </c>
@@ -13191,7 +13048,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
         <v>106</v>
       </c>
@@ -13221,7 +13078,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
         <v>106</v>
       </c>
@@ -13251,7 +13108,7 @@
         <v>AP269.png</v>
       </c>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
         <v>106</v>
       </c>
@@ -13281,7 +13138,7 @@
         <v>AP269.png</v>
       </c>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
         <v>106</v>
       </c>
@@ -13311,7 +13168,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
         <v>106</v>
       </c>
@@ -13341,7 +13198,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
         <v>106</v>
       </c>
@@ -13371,7 +13228,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
         <v>106</v>
       </c>
@@ -13401,7 +13258,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333" s="2" t="s">
         <v>106</v>
       </c>
@@ -13431,7 +13288,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
         <v>106</v>
       </c>
@@ -13461,7 +13318,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
         <v>106</v>
       </c>
@@ -13491,7 +13348,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
         <v>106</v>
       </c>
@@ -13521,7 +13378,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
         <v>106</v>
       </c>
@@ -13551,7 +13408,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
         <v>106</v>
       </c>
@@ -13581,7 +13438,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
         <v>106</v>
       </c>
@@ -13611,7 +13468,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
         <v>106</v>
       </c>
@@ -13641,7 +13498,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
         <v>106</v>
       </c>
@@ -13671,7 +13528,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
         <v>106</v>
       </c>
@@ -13701,7 +13558,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
         <v>106</v>
       </c>
@@ -13731,7 +13588,7 @@
         <v>AP269.png</v>
       </c>
     </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
         <v>106</v>
       </c>
@@ -13761,7 +13618,7 @@
         <v>AP269.png</v>
       </c>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
         <v>106</v>
       </c>
@@ -13791,7 +13648,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
         <v>106</v>
       </c>
@@ -13821,7 +13678,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
         <v>106</v>
       </c>
@@ -13851,7 +13708,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
         <v>106</v>
       </c>
@@ -13881,7 +13738,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
         <v>106</v>
       </c>
@@ -13911,7 +13768,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
         <v>106</v>
       </c>
@@ -13941,7 +13798,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
         <v>106</v>
       </c>
@@ -13971,7 +13828,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
         <v>106</v>
       </c>
@@ -14001,7 +13858,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
         <v>106</v>
       </c>
@@ -14031,7 +13888,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
         <v>106</v>
       </c>
@@ -14061,7 +13918,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
         <v>106</v>
       </c>
@@ -14091,7 +13948,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
         <v>106</v>
       </c>
@@ -14121,7 +13978,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
         <v>106</v>
       </c>
@@ -14151,7 +14008,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358" s="2" t="s">
         <v>106</v>
       </c>
@@ -14181,7 +14038,7 @@
         <v>BC350.png</v>
       </c>
     </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359" s="2" t="s">
         <v>106</v>
       </c>
@@ -14211,7 +14068,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360" s="2" t="s">
         <v>106</v>
       </c>
@@ -14241,7 +14098,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
         <v>106</v>
       </c>
@@ -14271,7 +14128,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362" s="2" t="s">
         <v>106</v>
       </c>
@@ -14301,7 +14158,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363" s="2" t="s">
         <v>106</v>
       </c>
@@ -14331,7 +14188,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364" s="2" t="s">
         <v>106</v>
       </c>
@@ -14361,7 +14218,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
         <v>106</v>
       </c>
@@ -14391,7 +14248,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
         <v>106</v>
       </c>
@@ -14421,7 +14278,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367" s="2" t="s">
         <v>106</v>
       </c>
@@ -14451,7 +14308,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
         <v>106</v>
       </c>
@@ -14481,7 +14338,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" s="2" t="s">
         <v>106</v>
       </c>
@@ -14511,7 +14368,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370" s="2" t="s">
         <v>106</v>
       </c>
@@ -14541,7 +14398,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371" s="2" t="s">
         <v>106</v>
       </c>
@@ -14571,7 +14428,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372" s="2" t="s">
         <v>106</v>
       </c>
@@ -14601,7 +14458,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373" s="2" t="s">
         <v>106</v>
       </c>
@@ -14631,7 +14488,7 @@
         <v>BC350.png</v>
       </c>
     </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374" s="2" t="s">
         <v>106</v>
       </c>
@@ -14661,7 +14518,7 @@
         <v>AP350.png</v>
       </c>
     </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375" s="2" t="s">
         <v>106</v>
       </c>
@@ -14691,7 +14548,7 @@
         <v>AP350.png</v>
       </c>
     </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376" s="2" t="s">
         <v>106</v>
       </c>
@@ -14721,7 +14578,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377" s="2" t="s">
         <v>106</v>
       </c>
@@ -14751,7 +14608,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378" s="2" t="s">
         <v>106</v>
       </c>
@@ -14781,7 +14638,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379" s="2" t="s">
         <v>106</v>
       </c>
@@ -14811,7 +14668,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="380" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A380" s="2" t="s">
         <v>106</v>
       </c>
@@ -14841,7 +14698,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381" s="2" t="s">
         <v>106</v>
       </c>
@@ -14871,7 +14728,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A382" s="2" t="s">
         <v>106</v>
       </c>
@@ -14901,7 +14758,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383" s="2" t="s">
         <v>106</v>
       </c>
@@ -14931,7 +14788,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384" s="2" t="s">
         <v>106</v>
       </c>
@@ -14961,7 +14818,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="385" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385" s="2" t="s">
         <v>106</v>
       </c>
@@ -14991,7 +14848,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="386" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386" s="2" t="s">
         <v>106</v>
       </c>
@@ -15021,7 +14878,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="387" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387" s="2" t="s">
         <v>106</v>
       </c>
@@ -15051,7 +14908,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="388" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388" s="2" t="s">
         <v>106</v>
       </c>
@@ -15081,7 +14938,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="389" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389" s="2" t="s">
         <v>106</v>
       </c>
@@ -15111,7 +14968,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="390" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390" s="2" t="s">
         <v>106</v>
       </c>
@@ -15141,7 +14998,7 @@
         <v>SPT269.png</v>
       </c>
     </row>
-    <row r="391" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391" s="2" t="s">
         <v>106</v>
       </c>
@@ -15171,7 +15028,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="392" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392" s="2" t="s">
         <v>106</v>
       </c>
@@ -15201,7 +15058,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="393" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393" s="2" t="s">
         <v>106</v>
       </c>
@@ -15231,7 +15088,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="394" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394" s="2" t="s">
         <v>106</v>
       </c>
@@ -15261,7 +15118,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="395" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395" s="2" t="s">
         <v>106</v>
       </c>
@@ -15291,7 +15148,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="396" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396" s="2" t="s">
         <v>106</v>
       </c>
@@ -15321,7 +15178,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="397" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397" s="2" t="s">
         <v>106</v>
       </c>
@@ -15351,7 +15208,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="398" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398" s="2" t="s">
         <v>106</v>
       </c>
@@ -15381,7 +15238,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="399" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399" s="2" t="s">
         <v>106</v>
       </c>
@@ -15411,7 +15268,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="400" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400" s="2" t="s">
         <v>106</v>
       </c>
@@ -15441,7 +15298,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="401" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401" s="2" t="s">
         <v>106</v>
       </c>
@@ -15471,7 +15328,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="402" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402" s="2" t="s">
         <v>106</v>
       </c>
@@ -15501,7 +15358,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="403" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403" s="2" t="s">
         <v>106</v>
       </c>
@@ -15531,7 +15388,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="404" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404" s="2" t="s">
         <v>106</v>
       </c>
@@ -15561,7 +15418,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="405" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405" s="2" t="s">
         <v>106</v>
       </c>
@@ -15591,7 +15448,7 @@
         <v>SPT269.png</v>
       </c>
     </row>
-    <row r="406" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406" s="2" t="s">
         <v>106</v>
       </c>
@@ -15621,7 +15478,7 @@
         <v>SPT269.png</v>
       </c>
     </row>
-    <row r="407" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A407" s="2" t="s">
         <v>106</v>
       </c>
@@ -15651,7 +15508,7 @@
         <v>SPT269.png</v>
       </c>
     </row>
-    <row r="408" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408" s="2" t="s">
         <v>106</v>
       </c>
@@ -15681,7 +15538,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="409" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409" s="2" t="s">
         <v>106</v>
       </c>
@@ -15711,7 +15568,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="410" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410" s="2" t="s">
         <v>106</v>
       </c>
@@ -15741,7 +15598,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="411" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411" s="2" t="s">
         <v>106</v>
       </c>
@@ -15771,7 +15628,7 @@
         <v>BUD350.png</v>
       </c>
     </row>
-    <row r="412" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A412" s="2" t="s">
         <v>106</v>
       </c>
@@ -15801,7 +15658,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="413" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413" s="2" t="s">
         <v>106</v>
       </c>
@@ -15831,7 +15688,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="414" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414" s="2" t="s">
         <v>106</v>
       </c>
@@ -15861,7 +15718,7 @@
         <v>BUD350.png</v>
       </c>
     </row>
-    <row r="415" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415" s="2" t="s">
         <v>106</v>
       </c>
@@ -15891,7 +15748,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="416" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416" s="2" t="s">
         <v>106</v>
       </c>
@@ -15921,7 +15778,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="417" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417" s="2" t="s">
         <v>106</v>
       </c>
@@ -15951,7 +15808,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="418" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A418" s="2" t="s">
         <v>106</v>
       </c>
@@ -15981,7 +15838,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="419" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A419" s="2" t="s">
         <v>106</v>
       </c>
@@ -16011,7 +15868,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="420" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A420" s="2" t="s">
         <v>106</v>
       </c>
@@ -16041,7 +15898,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="421" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A421" s="2" t="s">
         <v>106</v>
       </c>
@@ -16071,7 +15928,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="422" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A422" s="2" t="s">
         <v>106</v>
       </c>
@@ -16101,7 +15958,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="423" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A423" s="2" t="s">
         <v>106</v>
       </c>
@@ -16131,7 +15988,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="424" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A424" s="2" t="s">
         <v>106</v>
       </c>
@@ -16161,7 +16018,7 @@
         <v>BUD350.png</v>
       </c>
     </row>
-    <row r="425" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A425" s="2" t="s">
         <v>106</v>
       </c>
@@ -16191,7 +16048,7 @@
         <v>COR269.png</v>
       </c>
     </row>
-    <row r="426" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A426" s="2" t="s">
         <v>106</v>
       </c>
@@ -16221,7 +16078,7 @@
         <v>COR269.png</v>
       </c>
     </row>
-    <row r="427" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A427" s="2" t="s">
         <v>106</v>
       </c>
@@ -16251,7 +16108,7 @@
         <v>COR269.png</v>
       </c>
     </row>
-    <row r="428" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A428" s="2" t="s">
         <v>106</v>
       </c>
@@ -16281,7 +16138,7 @@
         <v>COR269.png</v>
       </c>
     </row>
-    <row r="429" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A429" s="2" t="s">
         <v>106</v>
       </c>
@@ -16311,7 +16168,7 @@
         <v>SPT350.png</v>
       </c>
     </row>
-    <row r="430" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A430" s="2" t="s">
         <v>106</v>
       </c>
@@ -16341,7 +16198,7 @@
         <v>SPT350.png</v>
       </c>
     </row>
-    <row r="431" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A431" s="2" t="s">
         <v>106</v>
       </c>
@@ -16371,7 +16228,7 @@
         <v>SPT350.png</v>
       </c>
     </row>
-    <row r="432" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A432" s="2" t="s">
         <v>106</v>
       </c>
@@ -16401,7 +16258,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="433" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A433" s="2" t="s">
         <v>106</v>
       </c>
@@ -16431,7 +16288,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="434" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A434" s="2" t="s">
         <v>106</v>
       </c>
@@ -16461,7 +16318,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="435" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A435" s="2" t="s">
         <v>106</v>
       </c>
@@ -16491,7 +16348,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="436" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A436" s="2" t="s">
         <v>106</v>
       </c>
@@ -16521,7 +16378,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="437" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A437" s="2" t="s">
         <v>106</v>
       </c>
@@ -16551,7 +16408,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="438" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A438" s="2" t="s">
         <v>106</v>
       </c>
@@ -16581,7 +16438,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="439" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A439" s="2" t="s">
         <v>106</v>
       </c>
@@ -16611,7 +16468,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="440" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A440" s="2" t="s">
         <v>106</v>
       </c>
@@ -16641,7 +16498,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="441" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A441" s="2" t="s">
         <v>106</v>
       </c>
@@ -16671,7 +16528,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="442" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A442" s="2" t="s">
         <v>106</v>
       </c>
@@ -16701,7 +16558,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="443" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A443" s="2" t="s">
         <v>106</v>
       </c>
@@ -16731,7 +16588,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="444" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A444" s="2" t="s">
         <v>106</v>
       </c>
@@ -16761,7 +16618,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="445" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A445" s="2" t="s">
         <v>106</v>
       </c>
@@ -16791,7 +16648,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="446" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A446" s="2" t="s">
         <v>106</v>
       </c>
@@ -16821,7 +16678,7 @@
         <v>COR350.png</v>
       </c>
     </row>
-    <row r="447" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A447" s="2" t="s">
         <v>106</v>
       </c>
@@ -16851,7 +16708,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="448" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A448" s="2" t="s">
         <v>106</v>
       </c>
@@ -16881,7 +16738,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="449" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A449" s="2" t="s">
         <v>106</v>
       </c>
@@ -16911,7 +16768,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="450" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A450" s="2" t="s">
         <v>106</v>
       </c>
@@ -16941,7 +16798,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="451" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A451" s="2" t="s">
         <v>106</v>
       </c>
@@ -16971,7 +16828,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="452" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A452" s="2" t="s">
         <v>106</v>
       </c>
@@ -17001,7 +16858,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="453" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A453" s="2" t="s">
         <v>106</v>
       </c>
@@ -17031,7 +16888,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="454" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A454" s="2" t="s">
         <v>106</v>
       </c>
@@ -17061,7 +16918,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="455" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A455" s="2" t="s">
         <v>106</v>
       </c>
@@ -17091,7 +16948,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="456" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A456" s="2" t="s">
         <v>106</v>
       </c>
@@ -17121,7 +16978,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="457" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A457" s="2" t="s">
         <v>106</v>
       </c>
@@ -17151,7 +17008,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="458" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A458" s="2" t="s">
         <v>106</v>
       </c>
@@ -17181,7 +17038,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="459" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A459" s="2" t="s">
         <v>106</v>
       </c>
@@ -17211,7 +17068,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="460" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A460" s="2" t="s">
         <v>106</v>
       </c>
@@ -17241,7 +17098,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="461" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A461" s="2" t="s">
         <v>106</v>
       </c>
@@ -17271,7 +17128,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="462" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A462" s="2" t="s">
         <v>106</v>
       </c>
@@ -17301,7 +17158,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="463" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A463" s="2" t="s">
         <v>106</v>
       </c>
@@ -17331,7 +17188,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="464" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A464" s="2" t="s">
         <v>106</v>
       </c>
@@ -17361,7 +17218,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="465" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A465" s="2" t="s">
         <v>106</v>
       </c>
@@ -17391,7 +17248,7 @@
         <v>COR350.png</v>
       </c>
     </row>
-    <row r="466" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A466" s="2" t="s">
         <v>106</v>
       </c>
@@ -17421,7 +17278,7 @@
         <v>COR350.png</v>
       </c>
     </row>
-    <row r="467" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A467" s="2" t="s">
         <v>106</v>
       </c>
@@ -17451,7 +17308,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="468" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A468" s="2" t="s">
         <v>106</v>
       </c>
@@ -17481,7 +17338,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="469" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A469" s="2" t="s">
         <v>106</v>
       </c>
@@ -17511,7 +17368,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="470" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A470" s="2" t="s">
         <v>106</v>
       </c>
@@ -17541,7 +17398,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="471" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A471" s="2" t="s">
         <v>106</v>
       </c>
@@ -17571,7 +17428,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="472" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A472" s="2" t="s">
         <v>106</v>
       </c>
@@ -17601,7 +17458,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="473" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A473" s="2" t="s">
         <v>106</v>
       </c>
@@ -17631,7 +17488,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="474" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A474" s="2" t="s">
         <v>106</v>
       </c>
@@ -17661,7 +17518,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="475" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A475" s="2" t="s">
         <v>106</v>
       </c>
@@ -17691,7 +17548,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="476" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A476" s="2" t="s">
         <v>106</v>
       </c>
@@ -17721,7 +17578,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="477" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A477" s="2" t="s">
         <v>106</v>
       </c>
@@ -17751,7 +17608,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="478" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A478" s="2" t="s">
         <v>106</v>
       </c>
@@ -17781,7 +17638,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="479" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A479" s="2" t="s">
         <v>106</v>
       </c>
@@ -17811,7 +17668,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="480" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A480" s="2" t="s">
         <v>106</v>
       </c>
@@ -17841,7 +17698,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="481" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A481" s="2" t="s">
         <v>106</v>
       </c>
@@ -17871,7 +17728,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="482" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A482" s="2" t="s">
         <v>106</v>
       </c>
@@ -17901,7 +17758,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="483" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A483" s="2" t="s">
         <v>106</v>
       </c>
@@ -17931,7 +17788,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="484" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A484" s="2" t="s">
         <v>106</v>
       </c>
@@ -17961,7 +17818,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="485" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A485" s="2" t="s">
         <v>106</v>
       </c>
@@ -17991,7 +17848,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="486" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A486" s="2" t="s">
         <v>106</v>
       </c>
@@ -18021,7 +17878,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="487" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A487" s="2" t="s">
         <v>106</v>
       </c>
@@ -18051,7 +17908,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="488" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A488" s="2" t="s">
         <v>106</v>
       </c>
@@ -18081,7 +17938,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="489" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A489" s="2" t="s">
         <v>106</v>
       </c>
@@ -18111,7 +17968,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="490" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A490" s="2" t="s">
         <v>106</v>
       </c>
@@ -18141,7 +17998,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="491" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A491" s="2" t="s">
         <v>106</v>
       </c>
@@ -18171,7 +18028,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="492" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A492" s="2" t="s">
         <v>106</v>
       </c>
@@ -18201,7 +18058,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="493" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A493" s="2" t="s">
         <v>106</v>
       </c>
@@ -18231,7 +18088,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="494" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A494" s="2" t="s">
         <v>106</v>
       </c>
@@ -18261,7 +18118,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="495" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A495" s="2" t="s">
         <v>106</v>
       </c>
@@ -18291,7 +18148,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="496" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A496" s="2" t="s">
         <v>106</v>
       </c>
@@ -18321,7 +18178,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="497" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A497" s="2" t="s">
         <v>106</v>
       </c>
@@ -18351,7 +18208,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="498" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A498" s="2" t="s">
         <v>106</v>
       </c>
@@ -18381,7 +18238,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="499" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A499" s="2" t="s">
         <v>106</v>
       </c>
@@ -18411,7 +18268,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="500" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A500" s="2" t="s">
         <v>106</v>
       </c>
@@ -18441,7 +18298,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="501" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A501" s="2" t="s">
         <v>106</v>
       </c>
@@ -18471,7 +18328,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="502" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A502" s="2" t="s">
         <v>106</v>
       </c>
@@ -18501,7 +18358,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="503" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A503" s="2" t="s">
         <v>106</v>
       </c>
@@ -18531,7 +18388,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="504" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A504" s="2" t="s">
         <v>106</v>
       </c>
@@ -18561,7 +18418,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="505" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A505" s="2" t="s">
         <v>106</v>
       </c>
@@ -18591,7 +18448,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="506" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A506" s="2" t="s">
         <v>106</v>
       </c>
@@ -18621,7 +18478,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="507" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A507" s="2" t="s">
         <v>106</v>
       </c>
@@ -18651,7 +18508,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="508" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A508" s="2" t="s">
         <v>106</v>
       </c>
@@ -18681,7 +18538,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="509" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A509" s="2" t="s">
         <v>106</v>
       </c>
@@ -18711,7 +18568,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="510" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A510" s="2" t="s">
         <v>106</v>
       </c>
@@ -18741,7 +18598,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="511" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A511" s="2" t="s">
         <v>106</v>
       </c>
@@ -18771,7 +18628,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="512" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A512" s="2" t="s">
         <v>106</v>
       </c>
@@ -18801,7 +18658,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="513" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A513" s="2" t="s">
         <v>106</v>
       </c>
@@ -18831,7 +18688,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="514" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A514" s="2" t="s">
         <v>106</v>
       </c>
@@ -18861,7 +18718,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="515" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A515" s="2" t="s">
         <v>106</v>
       </c>
@@ -18891,7 +18748,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="516" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A516" s="2" t="s">
         <v>106</v>
       </c>
@@ -18921,7 +18778,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="517" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A517" s="2" t="s">
         <v>106</v>
       </c>
@@ -18951,7 +18808,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="518" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A518" s="2" t="s">
         <v>106</v>
       </c>
@@ -18981,7 +18838,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="519" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A519" s="2" t="s">
         <v>106</v>
       </c>
@@ -19011,7 +18868,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="520" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A520" s="2" t="s">
         <v>106</v>
       </c>
@@ -19041,7 +18898,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="521" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A521" s="2" t="s">
         <v>102</v>
       </c>
@@ -19071,7 +18928,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="522" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A522" s="2" t="s">
         <v>102</v>
       </c>
@@ -19101,7 +18958,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="523" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A523" s="2" t="s">
         <v>102</v>
       </c>
@@ -19131,7 +18988,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="524" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A524" s="2" t="s">
         <v>102</v>
       </c>
@@ -19161,7 +19018,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="525" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A525" s="2" t="s">
         <v>102</v>
       </c>
@@ -19191,7 +19048,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="526" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A526" s="2" t="s">
         <v>102</v>
       </c>
@@ -19221,7 +19078,7 @@
         <v>AP269.png</v>
       </c>
     </row>
-    <row r="527" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A527" s="2" t="s">
         <v>102</v>
       </c>
@@ -19251,7 +19108,7 @@
         <v>AP269.png</v>
       </c>
     </row>
-    <row r="528" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A528" s="2" t="s">
         <v>102</v>
       </c>
@@ -19281,7 +19138,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="529" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A529" s="2" t="s">
         <v>102</v>
       </c>
@@ -19311,7 +19168,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="530" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A530" s="2" t="s">
         <v>102</v>
       </c>
@@ -19341,7 +19198,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="531" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A531" s="2" t="s">
         <v>102</v>
       </c>
@@ -19371,7 +19228,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="532" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A532" s="2" t="s">
         <v>102</v>
       </c>
@@ -19401,7 +19258,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="533" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A533" s="2" t="s">
         <v>102</v>
       </c>
@@ -19431,7 +19288,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="534" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A534" s="2" t="s">
         <v>102</v>
       </c>
@@ -19461,7 +19318,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="535" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A535" s="2" t="s">
         <v>102</v>
       </c>
@@ -19491,7 +19348,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="536" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A536" s="2" t="s">
         <v>102</v>
       </c>
@@ -19521,7 +19378,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="537" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A537" s="2" t="s">
         <v>102</v>
       </c>
@@ -19551,7 +19408,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="538" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A538" s="2" t="s">
         <v>102</v>
       </c>
@@ -19581,7 +19438,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="539" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A539" s="2" t="s">
         <v>102</v>
       </c>
@@ -19611,7 +19468,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="540" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A540" s="2" t="s">
         <v>102</v>
       </c>
@@ -19641,7 +19498,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="541" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A541" s="2" t="s">
         <v>102</v>
       </c>
@@ -19671,7 +19528,7 @@
         <v>AP269.png</v>
       </c>
     </row>
-    <row r="542" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A542" s="2" t="s">
         <v>102</v>
       </c>
@@ -19701,7 +19558,7 @@
         <v>AP269.png</v>
       </c>
     </row>
-    <row r="543" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A543" s="2" t="s">
         <v>102</v>
       </c>
@@ -19731,7 +19588,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="544" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A544" s="2" t="s">
         <v>102</v>
       </c>
@@ -19761,7 +19618,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="545" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A545" s="2" t="s">
         <v>102</v>
       </c>
@@ -19791,7 +19648,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="546" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A546" s="2" t="s">
         <v>102</v>
       </c>
@@ -19821,7 +19678,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="547" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A547" s="2" t="s">
         <v>102</v>
       </c>
@@ -19851,7 +19708,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="548" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A548" s="2" t="s">
         <v>102</v>
       </c>
@@ -19881,7 +19738,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="549" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A549" s="2" t="s">
         <v>102</v>
       </c>
@@ -19911,7 +19768,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="550" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A550" s="2" t="s">
         <v>102</v>
       </c>
@@ -19941,7 +19798,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="551" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A551" s="2" t="s">
         <v>102</v>
       </c>
@@ -19971,7 +19828,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="552" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A552" s="2" t="s">
         <v>102</v>
       </c>
@@ -20001,7 +19858,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="553" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A553" s="2" t="s">
         <v>102</v>
       </c>
@@ -20031,7 +19888,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="554" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A554" s="2" t="s">
         <v>102</v>
       </c>
@@ -20061,7 +19918,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="555" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A555" s="2" t="s">
         <v>102</v>
       </c>
@@ -20091,7 +19948,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="556" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A556" s="2" t="s">
         <v>102</v>
       </c>
@@ -20121,7 +19978,7 @@
         <v>BC350.png</v>
       </c>
     </row>
-    <row r="557" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A557" s="2" t="s">
         <v>102</v>
       </c>
@@ -20151,7 +20008,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="558" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A558" s="2" t="s">
         <v>102</v>
       </c>
@@ -20181,7 +20038,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="559" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A559" s="2" t="s">
         <v>102</v>
       </c>
@@ -20211,7 +20068,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="560" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A560" s="2" t="s">
         <v>102</v>
       </c>
@@ -20241,7 +20098,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="561" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A561" s="2" t="s">
         <v>102</v>
       </c>
@@ -20271,7 +20128,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="562" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A562" s="2" t="s">
         <v>102</v>
       </c>
@@ -20301,7 +20158,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="563" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A563" s="2" t="s">
         <v>102</v>
       </c>
@@ -20331,7 +20188,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="564" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A564" s="2" t="s">
         <v>102</v>
       </c>
@@ -20361,7 +20218,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="565" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A565" s="2" t="s">
         <v>102</v>
       </c>
@@ -20391,7 +20248,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="566" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A566" s="2" t="s">
         <v>102</v>
       </c>
@@ -20421,7 +20278,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="567" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A567" s="2" t="s">
         <v>102</v>
       </c>
@@ -20451,7 +20308,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="568" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A568" s="2" t="s">
         <v>102</v>
       </c>
@@ -20481,7 +20338,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="569" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A569" s="2" t="s">
         <v>102</v>
       </c>
@@ -20511,7 +20368,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="570" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A570" s="2" t="s">
         <v>102</v>
       </c>
@@ -20541,7 +20398,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="571" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A571" s="2" t="s">
         <v>102</v>
       </c>
@@ -20571,7 +20428,7 @@
         <v>BC350.png</v>
       </c>
     </row>
-    <row r="572" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A572" s="2" t="s">
         <v>102</v>
       </c>
@@ -20601,7 +20458,7 @@
         <v>AP350.png</v>
       </c>
     </row>
-    <row r="573" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A573" s="2" t="s">
         <v>102</v>
       </c>
@@ -20631,7 +20488,7 @@
         <v>AP350.png</v>
       </c>
     </row>
-    <row r="574" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A574" s="2" t="s">
         <v>102</v>
       </c>
@@ -20661,7 +20518,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="575" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A575" s="2" t="s">
         <v>102</v>
       </c>
@@ -20691,7 +20548,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="576" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A576" s="2" t="s">
         <v>102</v>
       </c>
@@ -20721,7 +20578,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="577" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A577" s="2" t="s">
         <v>102</v>
       </c>
@@ -20751,7 +20608,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="578" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A578" s="2" t="s">
         <v>102</v>
       </c>
@@ -20781,7 +20638,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="579" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A579" s="2" t="s">
         <v>102</v>
       </c>
@@ -20811,7 +20668,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="580" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A580" s="2" t="s">
         <v>102</v>
       </c>
@@ -20841,7 +20698,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="581" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A581" s="2" t="s">
         <v>102</v>
       </c>
@@ -20871,7 +20728,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="582" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A582" s="2" t="s">
         <v>102</v>
       </c>
@@ -20901,7 +20758,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="583" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A583" s="2" t="s">
         <v>102</v>
       </c>
@@ -20931,7 +20788,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="584" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A584" s="2" t="s">
         <v>102</v>
       </c>
@@ -20961,7 +20818,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="585" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A585" s="2" t="s">
         <v>102</v>
       </c>
@@ -20991,7 +20848,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="586" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A586" s="2" t="s">
         <v>102</v>
       </c>
@@ -21021,7 +20878,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="587" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A587" s="2" t="s">
         <v>102</v>
       </c>
@@ -21051,7 +20908,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="588" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A588" s="2" t="s">
         <v>102</v>
       </c>
@@ -21081,7 +20938,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="589" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A589" s="2" t="s">
         <v>102</v>
       </c>
@@ -21111,7 +20968,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="590" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A590" s="2" t="s">
         <v>102</v>
       </c>
@@ -21141,7 +20998,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="591" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A591" s="2" t="s">
         <v>102</v>
       </c>
@@ -21171,7 +21028,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="592" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A592" s="2" t="s">
         <v>102</v>
       </c>
@@ -21201,7 +21058,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="593" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A593" s="2" t="s">
         <v>102</v>
       </c>
@@ -21231,7 +21088,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="594" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A594" s="2" t="s">
         <v>102</v>
       </c>
@@ -21261,7 +21118,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="595" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A595" s="2" t="s">
         <v>102</v>
       </c>
@@ -21291,7 +21148,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="596" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A596" s="2" t="s">
         <v>102</v>
       </c>
@@ -21321,7 +21178,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="597" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A597" s="2" t="s">
         <v>102</v>
       </c>
@@ -21351,7 +21208,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="598" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A598" s="2" t="s">
         <v>102</v>
       </c>
@@ -21381,7 +21238,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="599" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A599" s="2" t="s">
         <v>102</v>
       </c>
@@ -21411,7 +21268,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="600" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A600" s="2" t="s">
         <v>102</v>
       </c>
@@ -21441,7 +21298,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="601" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A601" s="2" t="s">
         <v>102</v>
       </c>
@@ -21471,7 +21328,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="602" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A602" s="2" t="s">
         <v>102</v>
       </c>
@@ -21501,7 +21358,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="603" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A603" s="2" t="s">
         <v>102</v>
       </c>
@@ -21531,7 +21388,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="604" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A604" s="2" t="s">
         <v>102</v>
       </c>
@@ -21561,7 +21418,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="605" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A605" s="2" t="s">
         <v>102</v>
       </c>
@@ -21591,7 +21448,7 @@
         <v>BUD350.png</v>
       </c>
     </row>
-    <row r="606" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A606" s="2" t="s">
         <v>102</v>
       </c>
@@ -21621,7 +21478,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="607" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A607" s="2" t="s">
         <v>102</v>
       </c>
@@ -21651,7 +21508,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="608" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A608" s="2" t="s">
         <v>102</v>
       </c>
@@ -21681,7 +21538,7 @@
         <v>BUD350.png</v>
       </c>
     </row>
-    <row r="609" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A609" s="2" t="s">
         <v>102</v>
       </c>
@@ -21711,7 +21568,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="610" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A610" s="2" t="s">
         <v>102</v>
       </c>
@@ -21741,7 +21598,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="611" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A611" s="2" t="s">
         <v>102</v>
       </c>
@@ -21771,7 +21628,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="612" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A612" s="2" t="s">
         <v>102</v>
       </c>
@@ -21801,7 +21658,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="613" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A613" s="2" t="s">
         <v>102</v>
       </c>
@@ -21831,7 +21688,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="614" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A614" s="2" t="s">
         <v>102</v>
       </c>
@@ -21861,7 +21718,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="615" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A615" s="2" t="s">
         <v>102</v>
       </c>
@@ -21891,7 +21748,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="616" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A616" s="2" t="s">
         <v>102</v>
       </c>
@@ -21921,7 +21778,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="617" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A617" s="2" t="s">
         <v>102</v>
       </c>
@@ -21951,7 +21808,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="618" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A618" s="2" t="s">
         <v>102</v>
       </c>
@@ -21981,7 +21838,7 @@
         <v>BUD350.png</v>
       </c>
     </row>
-    <row r="619" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A619" s="2" t="s">
         <v>102</v>
       </c>
@@ -22011,7 +21868,7 @@
         <v>SPT269.png</v>
       </c>
     </row>
-    <row r="620" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A620" s="2" t="s">
         <v>102</v>
       </c>
@@ -22041,7 +21898,7 @@
         <v>SPT269.png</v>
       </c>
     </row>
-    <row r="621" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A621" s="2" t="s">
         <v>102</v>
       </c>
@@ -22071,7 +21928,7 @@
         <v>SPT269.png</v>
       </c>
     </row>
-    <row r="622" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A622" s="2" t="s">
         <v>102</v>
       </c>
@@ -22101,7 +21958,7 @@
         <v>SPT269.png</v>
       </c>
     </row>
-    <row r="623" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A623" s="2" t="s">
         <v>102</v>
       </c>
@@ -22131,7 +21988,7 @@
         <v>COR269.png</v>
       </c>
     </row>
-    <row r="624" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A624" s="2" t="s">
         <v>102</v>
       </c>
@@ -22161,7 +22018,7 @@
         <v>COR269.png</v>
       </c>
     </row>
-    <row r="625" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A625" s="2" t="s">
         <v>102</v>
       </c>
@@ -22191,7 +22048,7 @@
         <v>COR269.png</v>
       </c>
     </row>
-    <row r="626" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A626" s="2" t="s">
         <v>102</v>
       </c>
@@ -22221,7 +22078,7 @@
         <v>COR269.png</v>
       </c>
     </row>
-    <row r="627" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A627" s="2" t="s">
         <v>102</v>
       </c>
@@ -22251,7 +22108,7 @@
         <v>SPT350.png</v>
       </c>
     </row>
-    <row r="628" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A628" s="2" t="s">
         <v>102</v>
       </c>
@@ -22281,7 +22138,7 @@
         <v>SPT350.png</v>
       </c>
     </row>
-    <row r="629" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A629" s="2" t="s">
         <v>102</v>
       </c>
@@ -22311,7 +22168,7 @@
         <v>SPT350.png</v>
       </c>
     </row>
-    <row r="630" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A630" s="2" t="s">
         <v>102</v>
       </c>
@@ -22341,7 +22198,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="631" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A631" s="2" t="s">
         <v>102</v>
       </c>
@@ -22371,7 +22228,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="632" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A632" s="2" t="s">
         <v>102</v>
       </c>
@@ -22401,7 +22258,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="633" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A633" s="2" t="s">
         <v>102</v>
       </c>
@@ -22431,7 +22288,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="634" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A634" s="2" t="s">
         <v>102</v>
       </c>
@@ -22461,7 +22318,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="635" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A635" s="2" t="s">
         <v>102</v>
       </c>
@@ -22491,7 +22348,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="636" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A636" s="2" t="s">
         <v>102</v>
       </c>
@@ -22521,7 +22378,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="637" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A637" s="2" t="s">
         <v>102</v>
       </c>
@@ -22551,7 +22408,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="638" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A638" s="2" t="s">
         <v>102</v>
       </c>
@@ -22581,7 +22438,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="639" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A639" s="2" t="s">
         <v>102</v>
       </c>
@@ -22611,7 +22468,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="640" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A640" s="2" t="s">
         <v>102</v>
       </c>
@@ -22641,7 +22498,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="641" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A641" s="2" t="s">
         <v>102</v>
       </c>
@@ -22671,7 +22528,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="642" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A642" s="2" t="s">
         <v>102</v>
       </c>
@@ -22701,7 +22558,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="643" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A643" s="2" t="s">
         <v>102</v>
       </c>
@@ -22731,7 +22588,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="644" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A644" s="2" t="s">
         <v>102</v>
       </c>
@@ -22761,7 +22618,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="645" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A645" s="2" t="s">
         <v>102</v>
       </c>
@@ -22791,7 +22648,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="646" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A646" s="2" t="s">
         <v>102</v>
       </c>
@@ -22821,7 +22678,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="647" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A647" s="2" t="s">
         <v>102</v>
       </c>
@@ -22851,7 +22708,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="648" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A648" s="2" t="s">
         <v>102</v>
       </c>
@@ -22881,7 +22738,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="649" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A649" s="2" t="s">
         <v>102</v>
       </c>
@@ -22911,7 +22768,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="650" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A650" s="2" t="s">
         <v>102</v>
       </c>
@@ -22941,7 +22798,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="651" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A651" s="2" t="s">
         <v>102</v>
       </c>
@@ -22971,7 +22828,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="652" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A652" s="2" t="s">
         <v>102</v>
       </c>
@@ -23001,7 +22858,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="653" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A653" s="2" t="s">
         <v>102</v>
       </c>
@@ -23031,7 +22888,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="654" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A654" s="2" t="s">
         <v>102</v>
       </c>
@@ -23061,7 +22918,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="655" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A655" s="2" t="s">
         <v>102</v>
       </c>
@@ -23091,7 +22948,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="656" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A656" s="2" t="s">
         <v>102</v>
       </c>
@@ -23121,7 +22978,7 @@
         <v>COR350.png</v>
       </c>
     </row>
-    <row r="657" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A657" s="2" t="s">
         <v>102</v>
       </c>
@@ -23151,7 +23008,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="658" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A658" s="2" t="s">
         <v>102</v>
       </c>
@@ -23181,7 +23038,7 @@
         <v>COR350.png</v>
       </c>
     </row>
-    <row r="659" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A659" s="2" t="s">
         <v>102</v>
       </c>
@@ -23211,7 +23068,7 @@
         <v>COR350.png</v>
       </c>
     </row>
-    <row r="660" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A660" s="2" t="s">
         <v>102</v>
       </c>
@@ -23241,7 +23098,7 @@
         <v>COR350.png</v>
       </c>
     </row>
-    <row r="661" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A661" s="2" t="s">
         <v>102</v>
       </c>
@@ -23271,7 +23128,7 @@
         <v>COR350.png</v>
       </c>
     </row>
-    <row r="662" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A662" s="2" t="s">
         <v>102</v>
       </c>
@@ -23301,7 +23158,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="663" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A663" s="2" t="s">
         <v>102</v>
       </c>
@@ -23331,7 +23188,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="664" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A664" s="2" t="s">
         <v>102</v>
       </c>
@@ -23361,7 +23218,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="665" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A665" s="2" t="s">
         <v>102</v>
       </c>
@@ -23391,7 +23248,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="666" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A666" s="2" t="s">
         <v>102</v>
       </c>
@@ -23421,7 +23278,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="667" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A667" s="2" t="s">
         <v>102</v>
       </c>
@@ -23451,7 +23308,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="668" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A668" s="2" t="s">
         <v>102</v>
       </c>
@@ -23481,7 +23338,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="669" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A669" s="2" t="s">
         <v>102</v>
       </c>
@@ -23511,7 +23368,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="670" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A670" s="2" t="s">
         <v>102</v>
       </c>
@@ -23541,7 +23398,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="671" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A671" s="2" t="s">
         <v>102</v>
       </c>
@@ -23571,7 +23428,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="672" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A672" s="2" t="s">
         <v>102</v>
       </c>
@@ -23601,7 +23458,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="673" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A673" s="2" t="s">
         <v>102</v>
       </c>
@@ -23631,7 +23488,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="674" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A674" s="2" t="s">
         <v>102</v>
       </c>
@@ -23661,7 +23518,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="675" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A675" s="2" t="s">
         <v>102</v>
       </c>
@@ -23691,7 +23548,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="676" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A676" s="2" t="s">
         <v>102</v>
       </c>
@@ -23721,7 +23578,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="677" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A677" s="2" t="s">
         <v>102</v>
       </c>
@@ -23751,7 +23608,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="678" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A678" s="2" t="s">
         <v>102</v>
       </c>
@@ -23781,7 +23638,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="679" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A679" s="2" t="s">
         <v>102</v>
       </c>
@@ -23811,7 +23668,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="680" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A680" s="2" t="s">
         <v>102</v>
       </c>
@@ -23841,7 +23698,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="681" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A681" s="2" t="s">
         <v>102</v>
       </c>
@@ -23871,7 +23728,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="682" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A682" s="2" t="s">
         <v>102</v>
       </c>
@@ -23901,7 +23758,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="683" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A683" s="2" t="s">
         <v>102</v>
       </c>
@@ -23931,7 +23788,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="684" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A684" s="2" t="s">
         <v>102</v>
       </c>
@@ -23961,7 +23818,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="685" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A685" s="2" t="s">
         <v>102</v>
       </c>
@@ -23991,7 +23848,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="686" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A686" s="2" t="s">
         <v>102</v>
       </c>
@@ -24021,7 +23878,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="687" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A687" s="2" t="s">
         <v>102</v>
       </c>
@@ -24051,7 +23908,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="688" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A688" s="2" t="s">
         <v>102</v>
       </c>
@@ -24081,7 +23938,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="689" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A689" s="2" t="s">
         <v>102</v>
       </c>
@@ -24111,7 +23968,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="690" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A690" s="2" t="s">
         <v>102</v>
       </c>
@@ -24141,7 +23998,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="691" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A691" s="2" t="s">
         <v>102</v>
       </c>
@@ -24171,7 +24028,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="692" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A692" s="2" t="s">
         <v>102</v>
       </c>
@@ -24201,7 +24058,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="693" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A693" s="2" t="s">
         <v>102</v>
       </c>
@@ -24231,7 +24088,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="694" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A694" s="2" t="s">
         <v>102</v>
       </c>
@@ -24261,7 +24118,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="695" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A695" s="2" t="s">
         <v>102</v>
       </c>
@@ -24291,7 +24148,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="696" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A696" s="2" t="s">
         <v>102</v>
       </c>
@@ -24321,7 +24178,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="697" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A697" s="2" t="s">
         <v>102</v>
       </c>
@@ -24351,7 +24208,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="698" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A698" s="2" t="s">
         <v>102</v>
       </c>
@@ -24381,7 +24238,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="699" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A699" s="2" t="s">
         <v>102</v>
       </c>
@@ -24411,7 +24268,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="700" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A700" s="2" t="s">
         <v>102</v>
       </c>
@@ -24441,7 +24298,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="701" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A701" s="2" t="s">
         <v>102</v>
       </c>
@@ -24471,7 +24328,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="702" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A702" s="2" t="s">
         <v>102</v>
       </c>
@@ -24501,7 +24358,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="703" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A703" s="2" t="s">
         <v>102</v>
       </c>
@@ -24531,7 +24388,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="704" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A704" s="2" t="s">
         <v>102</v>
       </c>
@@ -24561,7 +24418,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="705" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A705" s="2" t="s">
         <v>102</v>
       </c>
@@ -24591,7 +24448,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="706" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A706" s="2" t="s">
         <v>102</v>
       </c>
@@ -24621,7 +24478,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="707" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A707" s="2" t="s">
         <v>102</v>
       </c>
@@ -24651,7 +24508,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="708" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A708" s="2" t="s">
         <v>102</v>
       </c>
@@ -24681,7 +24538,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="709" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A709" s="2" t="s">
         <v>102</v>
       </c>
@@ -24711,7 +24568,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="710" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A710" s="2" t="s">
         <v>102</v>
       </c>
@@ -24741,7 +24598,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="711" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A711" s="2" t="s">
         <v>102</v>
       </c>
@@ -24771,7 +24628,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="712" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A712" s="2" t="s">
         <v>102</v>
       </c>
@@ -24801,7 +24658,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="713" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A713" s="2" t="s">
         <v>102</v>
       </c>
@@ -24831,7 +24688,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="714" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A714" s="2" t="s">
         <v>102</v>
       </c>
@@ -24861,7 +24718,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="715" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A715" s="2" t="s">
         <v>102</v>
       </c>
@@ -24891,7 +24748,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="716" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A716" s="2" t="s">
         <v>102</v>
       </c>
@@ -24921,7 +24778,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="717" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A717" s="2" t="s">
         <v>102</v>
       </c>
@@ -24951,7 +24808,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="718" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A718" s="2" t="s">
         <v>102</v>
       </c>
@@ -24981,7 +24838,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="719" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A719" s="2" t="s">
         <v>102</v>
       </c>
@@ -25011,7 +24868,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="720" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A720" s="2" t="s">
         <v>102</v>
       </c>
@@ -25041,7 +24898,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="721" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A721" s="2" t="s">
         <v>105</v>
       </c>
@@ -25071,7 +24928,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="722" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A722" s="2" t="s">
         <v>105</v>
       </c>
@@ -25101,7 +24958,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="723" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A723" s="2" t="s">
         <v>105</v>
       </c>
@@ -25131,7 +24988,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="724" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A724" s="2" t="s">
         <v>105</v>
       </c>
@@ -25161,7 +25018,7 @@
         <v>AP269.png</v>
       </c>
     </row>
-    <row r="725" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A725" s="2" t="s">
         <v>105</v>
       </c>
@@ -25191,7 +25048,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="726" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A726" s="2" t="s">
         <v>105</v>
       </c>
@@ -25221,7 +25078,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="727" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A727" s="2" t="s">
         <v>105</v>
       </c>
@@ -25251,7 +25108,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="728" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A728" s="2" t="s">
         <v>105</v>
       </c>
@@ -25281,7 +25138,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="729" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A729" s="2" t="s">
         <v>105</v>
       </c>
@@ -25311,7 +25168,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="730" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A730" s="2" t="s">
         <v>105</v>
       </c>
@@ -25341,7 +25198,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="731" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A731" s="2" t="s">
         <v>105</v>
       </c>
@@ -25371,7 +25228,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="732" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A732" s="2" t="s">
         <v>105</v>
       </c>
@@ -25401,7 +25258,7 @@
         <v>AP350.png</v>
       </c>
     </row>
-    <row r="733" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A733" s="2" t="s">
         <v>105</v>
       </c>
@@ -25431,7 +25288,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="734" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A734" s="2" t="s">
         <v>105</v>
       </c>
@@ -25461,7 +25318,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="735" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A735" s="2" t="s">
         <v>105</v>
       </c>
@@ -25491,7 +25348,7 @@
         <v>SPT350.png</v>
       </c>
     </row>
-    <row r="736" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A736" s="2" t="s">
         <v>105</v>
       </c>
@@ -25521,7 +25378,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="737" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A737" s="2" t="s">
         <v>105</v>
       </c>
@@ -25551,7 +25408,7 @@
         <v>BUD350.png</v>
       </c>
     </row>
-    <row r="738" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A738" s="2" t="s">
         <v>105</v>
       </c>
@@ -25581,7 +25438,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="739" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A739" s="2" t="s">
         <v>105</v>
       </c>
@@ -25611,7 +25468,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="740" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A740" s="2" t="s">
         <v>105</v>
       </c>
@@ -25641,7 +25498,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="741" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A741" s="2" t="s">
         <v>105</v>
       </c>
@@ -25671,7 +25528,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="742" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A742" s="2" t="s">
         <v>105</v>
       </c>
@@ -25701,7 +25558,7 @@
         <v>COR350.png</v>
       </c>
     </row>
-    <row r="743" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A743" s="2" t="s">
         <v>105</v>
       </c>
@@ -25731,7 +25588,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="744" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A744" s="2" t="s">
         <v>105</v>
       </c>
@@ -25761,7 +25618,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="745" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A745" s="2" t="s">
         <v>105</v>
       </c>
@@ -25791,7 +25648,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="746" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A746" s="2" t="s">
         <v>105</v>
       </c>
@@ -25821,7 +25678,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="747" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A747" s="2" t="s">
         <v>105</v>
       </c>
@@ -25851,7 +25708,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="748" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A748" s="2" t="s">
         <v>105</v>
       </c>
@@ -25881,7 +25738,7 @@
         <v>AP269.png</v>
       </c>
     </row>
-    <row r="749" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A749" s="2" t="s">
         <v>105</v>
       </c>
@@ -25911,7 +25768,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="750" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A750" s="2" t="s">
         <v>105</v>
       </c>
@@ -25941,7 +25798,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="751" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A751" s="2" t="s">
         <v>105</v>
       </c>
@@ -25971,7 +25828,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="752" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A752" s="2" t="s">
         <v>105</v>
       </c>
@@ -26001,7 +25858,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="753" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A753" s="2" t="s">
         <v>105</v>
       </c>
@@ -26031,7 +25888,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="754" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A754" s="2" t="s">
         <v>105</v>
       </c>
@@ -26061,7 +25918,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="755" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A755" s="2" t="s">
         <v>105</v>
       </c>
@@ -26091,7 +25948,7 @@
         <v>AP350.png</v>
       </c>
     </row>
-    <row r="756" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A756" s="2" t="s">
         <v>105</v>
       </c>
@@ -26121,7 +25978,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="757" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A757" s="2" t="s">
         <v>105</v>
       </c>
@@ -26151,7 +26008,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="758" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A758" s="2" t="s">
         <v>105</v>
       </c>
@@ -26181,7 +26038,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="759" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A759" s="2" t="s">
         <v>105</v>
       </c>
@@ -26211,7 +26068,7 @@
         <v>SPT350.png</v>
       </c>
     </row>
-    <row r="760" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A760" s="2" t="s">
         <v>105</v>
       </c>
@@ -26241,7 +26098,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="761" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A761" s="2" t="s">
         <v>105</v>
       </c>
@@ -26271,7 +26128,7 @@
         <v>BUD350.png</v>
       </c>
     </row>
-    <row r="762" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A762" s="2" t="s">
         <v>105</v>
       </c>
@@ -26301,7 +26158,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="763" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A763" s="2" t="s">
         <v>105</v>
       </c>
@@ -26331,7 +26188,7 @@
         <v>BC350.png</v>
       </c>
     </row>
-    <row r="764" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A764" s="2" t="s">
         <v>105</v>
       </c>
@@ -26361,7 +26218,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="765" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A765" s="2" t="s">
         <v>105</v>
       </c>
@@ -26391,7 +26248,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="766" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A766" s="2" t="s">
         <v>105</v>
       </c>
@@ -26421,7 +26278,7 @@
         <v>COR350.png</v>
       </c>
     </row>
-    <row r="767" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A767" s="2" t="s">
         <v>105</v>
       </c>
@@ -26451,7 +26308,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="768" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A768" s="2" t="s">
         <v>105</v>
       </c>
@@ -26481,7 +26338,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="769" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A769" s="2" t="s">
         <v>105</v>
       </c>
@@ -26511,7 +26368,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="770" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A770" s="2" t="s">
         <v>105</v>
       </c>
@@ -26541,7 +26398,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="771" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A771" s="2" t="s">
         <v>105</v>
       </c>
@@ -26571,7 +26428,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="772" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A772" s="2" t="s">
         <v>105</v>
       </c>
@@ -26601,7 +26458,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="773" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A773" s="2" t="s">
         <v>105</v>
       </c>
@@ -26631,7 +26488,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="774" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A774" s="2" t="s">
         <v>105</v>
       </c>
@@ -26661,7 +26518,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="775" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A775" s="2" t="s">
         <v>105</v>
       </c>
@@ -26691,7 +26548,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="776" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A776" s="2" t="s">
         <v>105</v>
       </c>
@@ -26721,7 +26578,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="777" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A777" s="2" t="s">
         <v>105</v>
       </c>
@@ -26751,7 +26608,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="778" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A778" s="2" t="s">
         <v>105</v>
       </c>
@@ -26781,7 +26638,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="779" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A779" s="2" t="s">
         <v>105</v>
       </c>
@@ -26811,7 +26668,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="780" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A780" s="2" t="s">
         <v>105</v>
       </c>
@@ -26841,7 +26698,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="781" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A781" s="2" t="s">
         <v>105</v>
       </c>
@@ -26871,7 +26728,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="782" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A782" s="2" t="s">
         <v>105</v>
       </c>
@@ -26901,7 +26758,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="783" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A783" s="2" t="s">
         <v>105</v>
       </c>
@@ -26931,7 +26788,7 @@
         <v>SPT269.png</v>
       </c>
     </row>
-    <row r="784" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A784" s="2" t="s">
         <v>105</v>
       </c>
@@ -26961,7 +26818,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="785" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A785" s="2" t="s">
         <v>105</v>
       </c>
@@ -26991,7 +26848,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="786" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A786" s="2" t="s">
         <v>105</v>
       </c>
@@ -27021,7 +26878,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="787" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A787" s="2" t="s">
         <v>105</v>
       </c>
@@ -27051,7 +26908,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="788" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A788" s="2" t="s">
         <v>105</v>
       </c>
@@ -27081,7 +26938,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="789" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A789" s="2" t="s">
         <v>105</v>
       </c>
@@ -27111,7 +26968,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="790" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A790" s="2" t="s">
         <v>105</v>
       </c>
@@ -27141,7 +26998,7 @@
         <v>COR269.png</v>
       </c>
     </row>
-    <row r="791" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A791" s="2" t="s">
         <v>105</v>
       </c>
@@ -27171,7 +27028,7 @@
         <v>COR350.png</v>
       </c>
     </row>
-    <row r="792" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A792" s="2" t="s">
         <v>105</v>
       </c>
@@ -27201,7 +27058,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="793" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A793" s="2" t="s">
         <v>105</v>
       </c>
@@ -27231,7 +27088,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="794" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A794" s="2" t="s">
         <v>105</v>
       </c>
@@ -27261,7 +27118,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="795" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A795" s="2" t="s">
         <v>105</v>
       </c>
@@ -27291,7 +27148,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="796" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A796" s="2" t="s">
         <v>105</v>
       </c>
@@ -27321,7 +27178,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="797" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A797" s="2" t="s">
         <v>105</v>
       </c>
@@ -27351,7 +27208,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="798" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A798" s="2" t="s">
         <v>105</v>
       </c>
@@ -27381,7 +27238,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="799" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A799" s="2" t="s">
         <v>105</v>
       </c>
@@ -27411,7 +27268,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="800" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A800" s="2" t="s">
         <v>105</v>
       </c>
@@ -27441,7 +27298,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="801" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A801" s="2" t="s">
         <v>105</v>
       </c>
@@ -27471,7 +27328,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="802" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A802" s="2" t="s">
         <v>105</v>
       </c>
@@ -27501,7 +27358,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="803" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A803" s="2" t="s">
         <v>105</v>
       </c>
@@ -27531,7 +27388,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="804" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A804" s="2" t="s">
         <v>105</v>
       </c>
@@ -27561,7 +27418,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="805" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A805" s="2" t="s">
         <v>105</v>
       </c>
@@ -27591,7 +27448,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="806" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A806" s="2" t="s">
         <v>105</v>
       </c>
@@ -27621,7 +27478,7 @@
         <v>SPT269.png</v>
       </c>
     </row>
-    <row r="807" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A807" s="2" t="s">
         <v>105</v>
       </c>
@@ -27651,7 +27508,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="808" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A808" s="2" t="s">
         <v>105</v>
       </c>
@@ -27681,7 +27538,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="809" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A809" s="2" t="s">
         <v>105</v>
       </c>
@@ -27711,7 +27568,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="810" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A810" s="2" t="s">
         <v>105</v>
       </c>
@@ -27741,7 +27598,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="811" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A811" s="2" t="s">
         <v>105</v>
       </c>
@@ -27771,7 +27628,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="812" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A812" s="2" t="s">
         <v>105</v>
       </c>
@@ -27801,7 +27658,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="813" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A813" s="2" t="s">
         <v>105</v>
       </c>
@@ -27831,7 +27688,7 @@
         <v>COR269.png</v>
       </c>
     </row>
-    <row r="814" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A814" s="2" t="s">
         <v>105</v>
       </c>
@@ -27861,7 +27718,7 @@
         <v>COR350.png</v>
       </c>
     </row>
-    <row r="815" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A815" s="2" t="s">
         <v>105</v>
       </c>
@@ -27891,7 +27748,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="816" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A816" s="2" t="s">
         <v>105</v>
       </c>
@@ -27921,7 +27778,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="817" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A817" s="2" t="s">
         <v>105</v>
       </c>
@@ -27951,7 +27808,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="818" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A818" s="2" t="s">
         <v>105</v>
       </c>
@@ -27981,7 +27838,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="819" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A819" s="2" t="s">
         <v>105</v>
       </c>
@@ -28011,7 +27868,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="820" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A820" s="2" t="s">
         <v>105</v>
       </c>
@@ -28041,7 +27898,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="821" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A821" s="2" t="s">
         <v>105</v>
       </c>
@@ -28071,7 +27928,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="822" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A822" s="2" t="s">
         <v>105</v>
       </c>
@@ -28101,7 +27958,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="823" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A823" s="2" t="s">
         <v>105</v>
       </c>
@@ -28131,7 +27988,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="824" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A824" s="2" t="s">
         <v>105</v>
       </c>
@@ -28161,7 +28018,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="825" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A825" s="2" t="s">
         <v>105</v>
       </c>
@@ -28191,7 +28048,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="826" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A826" s="2" t="s">
         <v>105</v>
       </c>
@@ -28221,7 +28078,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="827" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A827" s="2" t="s">
         <v>105</v>
       </c>
@@ -28251,7 +28108,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="828" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A828" s="2" t="s">
         <v>105</v>
       </c>
@@ -28281,7 +28138,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="829" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A829" s="2" t="s">
         <v>105</v>
       </c>
@@ -28311,7 +28168,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="830" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A830" s="2" t="s">
         <v>105</v>
       </c>
@@ -28341,7 +28198,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="831" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A831" s="2" t="s">
         <v>105</v>
       </c>
@@ -28371,7 +28228,7 @@
         <v>SPT350.png</v>
       </c>
     </row>
-    <row r="832" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A832" s="2" t="s">
         <v>105</v>
       </c>
@@ -28401,7 +28258,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="833" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A833" s="2" t="s">
         <v>105</v>
       </c>
@@ -28431,7 +28288,7 @@
         <v>BUD350.png</v>
       </c>
     </row>
-    <row r="834" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A834" s="2" t="s">
         <v>105</v>
       </c>
@@ -28461,7 +28318,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="835" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A835" s="2" t="s">
         <v>105</v>
       </c>
@@ -28491,7 +28348,7 @@
         <v>BC350.png</v>
       </c>
     </row>
-    <row r="836" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A836" s="2" t="s">
         <v>105</v>
       </c>
@@ -28521,7 +28378,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="837" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A837" s="2" t="s">
         <v>105</v>
       </c>
@@ -28551,7 +28408,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="838" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A838" s="2" t="s">
         <v>105</v>
       </c>
@@ -28581,7 +28438,7 @@
         <v>COR350.png</v>
       </c>
     </row>
-    <row r="839" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A839" s="2" t="s">
         <v>105</v>
       </c>
@@ -28611,7 +28468,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="840" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A840" s="2" t="s">
         <v>105</v>
       </c>
@@ -28641,7 +28498,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="841" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A841" s="2" t="s">
         <v>105</v>
       </c>
@@ -28671,7 +28528,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="842" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A842" s="2" t="s">
         <v>105</v>
       </c>
@@ -28701,7 +28558,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="843" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A843" s="2" t="s">
         <v>105</v>
       </c>
@@ -28731,7 +28588,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="844" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A844" s="2" t="s">
         <v>105</v>
       </c>
@@ -28761,7 +28618,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="845" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A845" s="2" t="s">
         <v>105</v>
       </c>
@@ -28791,7 +28648,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="846" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A846" s="2" t="s">
         <v>105</v>
       </c>
@@ -28821,7 +28678,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="847" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A847" s="2" t="s">
         <v>105</v>
       </c>
@@ -28851,7 +28708,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="848" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A848" s="2" t="s">
         <v>105</v>
       </c>
@@ -28881,7 +28738,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="849" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A849" s="2" t="s">
         <v>105</v>
       </c>
@@ -28911,7 +28768,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="850" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A850" s="2" t="s">
         <v>105</v>
       </c>
@@ -28941,7 +28798,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="851" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A851" s="2" t="s">
         <v>105</v>
       </c>
@@ -28971,7 +28828,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="852" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A852" s="2" t="s">
         <v>105</v>
       </c>
@@ -29001,7 +28858,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="853" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A853" s="2" t="s">
         <v>105</v>
       </c>
@@ -29031,7 +28888,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="854" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A854" s="2" t="s">
         <v>105</v>
       </c>
@@ -29061,7 +28918,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="855" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A855" s="2" t="s">
         <v>105</v>
       </c>
@@ -29091,7 +28948,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="856" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A856" s="2" t="s">
         <v>105</v>
       </c>
@@ -29121,7 +28978,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="857" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A857" s="2" t="s">
         <v>105</v>
       </c>
@@ -29151,7 +29008,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="858" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A858" s="2" t="s">
         <v>105</v>
       </c>
@@ -29181,7 +29038,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="859" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A859" s="2" t="s">
         <v>105</v>
       </c>
@@ -29211,7 +29068,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="860" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A860" s="2" t="s">
         <v>105</v>
       </c>
@@ -29241,7 +29098,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="861" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A861" s="2" t="s">
         <v>105</v>
       </c>
@@ -29271,7 +29128,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="862" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A862" s="2" t="s">
         <v>105</v>
       </c>
@@ -29301,7 +29158,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="863" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A863" s="2" t="s">
         <v>105</v>
       </c>
@@ -29331,7 +29188,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="864" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A864" s="2" t="s">
         <v>105</v>
       </c>
@@ -29361,7 +29218,7 @@
         <v>SPT269.png</v>
       </c>
     </row>
-    <row r="865" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A865" s="2" t="s">
         <v>105</v>
       </c>
@@ -29391,7 +29248,7 @@
         <v>SPT269.png</v>
       </c>
     </row>
-    <row r="866" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A866" s="2" t="s">
         <v>105</v>
       </c>
@@ -29421,7 +29278,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="867" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A867" s="2" t="s">
         <v>105</v>
       </c>
@@ -29451,7 +29308,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="868" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A868" s="2" t="s">
         <v>105</v>
       </c>
@@ -29481,7 +29338,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="869" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A869" s="2" t="s">
         <v>105</v>
       </c>
@@ -29511,7 +29368,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="870" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A870" s="2" t="s">
         <v>105</v>
       </c>
@@ -29541,7 +29398,7 @@
         <v>COR269.png</v>
       </c>
     </row>
-    <row r="871" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A871" s="2" t="s">
         <v>105</v>
       </c>
@@ -29571,7 +29428,7 @@
         <v>COR269.png</v>
       </c>
     </row>
-    <row r="872" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A872" s="2" t="s">
         <v>105</v>
       </c>
@@ -29601,7 +29458,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="873" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A873" s="2" t="s">
         <v>105</v>
       </c>
@@ -29631,7 +29488,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="874" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A874" s="2" t="s">
         <v>105</v>
       </c>
@@ -29661,7 +29518,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="875" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A875" s="2" t="s">
         <v>105</v>
       </c>
@@ -29691,7 +29548,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="876" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A876" s="2" t="s">
         <v>105</v>
       </c>
@@ -29721,7 +29578,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="877" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A877" s="2" t="s">
         <v>105</v>
       </c>
@@ -29751,7 +29608,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="878" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A878" s="2" t="s">
         <v>105</v>
       </c>
@@ -29781,7 +29638,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="879" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A879" s="2" t="s">
         <v>105</v>
       </c>
@@ -29811,7 +29668,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="880" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A880" s="2" t="s">
         <v>105</v>
       </c>
@@ -29841,7 +29698,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="881" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A881" s="2" t="s">
         <v>105</v>
       </c>
@@ -29871,7 +29728,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="882" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A882" s="2" t="s">
         <v>105</v>
       </c>
@@ -29901,7 +29758,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="883" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A883" s="2" t="s">
         <v>105</v>
       </c>
@@ -29931,7 +29788,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="884" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A884" s="2" t="s">
         <v>105</v>
       </c>
@@ -29961,7 +29818,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="885" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A885" s="2" t="s">
         <v>105</v>
       </c>
@@ -29991,7 +29848,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="886" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A886" s="2" t="s">
         <v>105</v>
       </c>
@@ -30021,7 +29878,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="887" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A887" s="2" t="s">
         <v>105</v>
       </c>
@@ -30051,7 +29908,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="888" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A888" s="2" t="s">
         <v>105</v>
       </c>
@@ -30081,7 +29938,7 @@
         <v>AP269.png</v>
       </c>
     </row>
-    <row r="889" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A889" s="2" t="s">
         <v>105</v>
       </c>
@@ -30111,7 +29968,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="890" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A890" s="2" t="s">
         <v>105</v>
       </c>
@@ -30141,7 +29998,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="891" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A891" s="2" t="s">
         <v>105</v>
       </c>
@@ -30171,7 +30028,7 @@
         <v>AP269.png</v>
       </c>
     </row>
-    <row r="892" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A892" s="2" t="s">
         <v>105</v>
       </c>
@@ -30201,7 +30058,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="893" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A893" s="2" t="s">
         <v>105</v>
       </c>
@@ -30231,7 +30088,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="894" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A894" s="2" t="s">
         <v>105</v>
       </c>
@@ -30261,7 +30118,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="895" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A895" s="2" t="s">
         <v>105</v>
       </c>
@@ -30291,7 +30148,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="896" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A896" s="2" t="s">
         <v>105</v>
       </c>
@@ -30321,7 +30178,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="897" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A897" s="2" t="s">
         <v>105</v>
       </c>
@@ -30351,7 +30208,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="898" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A898" s="2" t="s">
         <v>105</v>
       </c>
@@ -30381,7 +30238,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="899" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A899" s="2" t="s">
         <v>105</v>
       </c>
@@ -30411,7 +30268,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="900" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A900" s="2" t="s">
         <v>105</v>
       </c>
@@ -30441,7 +30298,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="901" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A901" s="2" t="s">
         <v>105</v>
       </c>
@@ -30471,7 +30328,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="902" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A902" s="2" t="s">
         <v>105</v>
       </c>
@@ -30501,7 +30358,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="903" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A903" s="2" t="s">
         <v>105</v>
       </c>
@@ -30531,7 +30388,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="904" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A904" s="2" t="s">
         <v>105</v>
       </c>
@@ -30561,7 +30418,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="905" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A905" s="2" t="s">
         <v>105</v>
       </c>
@@ -30591,7 +30448,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="906" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A906" s="2" t="s">
         <v>105</v>
       </c>
@@ -30621,7 +30478,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="907" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A907" s="2" t="s">
         <v>105</v>
       </c>
@@ -30651,7 +30508,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="908" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A908" s="2" t="s">
         <v>101</v>
       </c>
@@ -30681,7 +30538,7 @@
         <v>BEATSLT.png</v>
       </c>
     </row>
-    <row r="909" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A909" s="2" t="s">
         <v>101</v>
       </c>
@@ -30711,7 +30568,7 @@
         <v>BEATSLT.png</v>
       </c>
     </row>
-    <row r="910" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A910" s="2" t="s">
         <v>101</v>
       </c>
@@ -30741,7 +30598,7 @@
         <v>BEATSLN.png</v>
       </c>
     </row>
-    <row r="911" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A911" s="2" t="s">
         <v>101</v>
       </c>
@@ -30771,7 +30628,7 @@
         <v>BEATSLN.png</v>
       </c>
     </row>
-    <row r="912" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A912" s="2" t="s">
         <v>101</v>
       </c>
@@ -30801,7 +30658,7 @@
         <v>BEATSLT.png</v>
       </c>
     </row>
-    <row r="913" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A913" s="2" t="s">
         <v>101</v>
       </c>
@@ -30831,7 +30688,7 @@
         <v>BEATSLT.png</v>
       </c>
     </row>
-    <row r="914" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A914" s="2" t="s">
         <v>101</v>
       </c>
@@ -30861,7 +30718,7 @@
         <v>BEATSLN.png</v>
       </c>
     </row>
-    <row r="915" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A915" s="2" t="s">
         <v>101</v>
       </c>
@@ -30914,14 +30771,14 @@
         <v>5.19</v>
       </c>
       <c r="H916">
-        <v>4.8900000000000006</v>
+        <v>4.5</v>
       </c>
       <c r="I916" s="2" t="str">
         <f>_xlfn.XLOOKUP(F916,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
         <v>FF350.png</v>
       </c>
     </row>
-    <row r="917" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A917" s="2" t="s">
         <v>101</v>
       </c>
@@ -30981,7 +30838,7 @@
         <v>FF350.png</v>
       </c>
     </row>
-    <row r="919" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A919" s="2" t="s">
         <v>101</v>
       </c>
@@ -31041,7 +30898,7 @@
         <v>FF350.png</v>
       </c>
     </row>
-    <row r="921" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A921" s="2" t="s">
         <v>101</v>
       </c>
@@ -31101,7 +30958,7 @@
         <v>FF350.png</v>
       </c>
     </row>
-    <row r="923" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A923" s="2" t="s">
         <v>101</v>
       </c>
@@ -31131,7 +30988,7 @@
         <v>FFLN.png</v>
       </c>
     </row>
-    <row r="924" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A924" s="2" t="s">
         <v>101</v>
       </c>
@@ -31161,7 +31018,7 @@
         <v>GCAP1.png</v>
       </c>
     </row>
-    <row r="925" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A925" s="2" t="s">
         <v>101</v>
       </c>
@@ -31191,7 +31048,7 @@
         <v>GCAP1,5.png</v>
       </c>
     </row>
-    <row r="926" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A926" s="2" t="s">
         <v>101</v>
       </c>
@@ -31221,7 +31078,7 @@
         <v>GCAP1,5.png</v>
       </c>
     </row>
-    <row r="927" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A927" s="2" t="s">
         <v>101</v>
       </c>
@@ -31251,7 +31108,7 @@
         <v>GCAP1,5.png</v>
       </c>
     </row>
-    <row r="928" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A928" s="2" t="s">
         <v>101</v>
       </c>
@@ -31281,7 +31138,7 @@
         <v>PCP2.png</v>
       </c>
     </row>
-    <row r="929" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A929" s="2" t="s">
         <v>101</v>
       </c>
@@ -31311,7 +31168,7 @@
         <v>PCP2.png</v>
       </c>
     </row>
-    <row r="930" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A930" s="2" t="s">
         <v>101</v>
       </c>
@@ -31341,7 +31198,7 @@
         <v>PCP2.png</v>
       </c>
     </row>
-    <row r="931" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A931" s="2" t="s">
         <v>101</v>
       </c>
@@ -31371,7 +31228,7 @@
         <v>PCP2.png</v>
       </c>
     </row>
-    <row r="932" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="932" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A932" s="2" t="s">
         <v>101</v>
       </c>
@@ -31401,7 +31258,7 @@
         <v>BAREP2.png</v>
       </c>
     </row>
-    <row r="933" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A933" s="2" t="s">
         <v>101</v>
       </c>
@@ -31431,7 +31288,7 @@
         <v>H2OHP500.png</v>
       </c>
     </row>
-    <row r="934" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A934" s="2" t="s">
         <v>101</v>
       </c>
@@ -31461,7 +31318,7 @@
         <v>H2OHP500.png</v>
       </c>
     </row>
-    <row r="935" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="935" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A935" s="2" t="s">
         <v>101</v>
       </c>
@@ -31491,7 +31348,7 @@
         <v>H2OHP500.png</v>
       </c>
     </row>
-    <row r="936" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="936" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A936" s="2" t="s">
         <v>101</v>
       </c>
@@ -31521,7 +31378,7 @@
         <v>H2OHP500.png</v>
       </c>
     </row>
-    <row r="937" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="937" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A937" s="2" t="s">
         <v>101</v>
       </c>
@@ -31551,7 +31408,7 @@
         <v>GCAP2.png</v>
       </c>
     </row>
-    <row r="938" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="938" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A938" s="2" t="s">
         <v>101</v>
       </c>
@@ -31581,7 +31438,7 @@
         <v>GCAP2.png</v>
       </c>
     </row>
-    <row r="939" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="939" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A939" s="2" t="s">
         <v>101</v>
       </c>
@@ -31611,7 +31468,7 @@
         <v>GCAP2.png</v>
       </c>
     </row>
-    <row r="940" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="940" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A940" s="2" t="s">
         <v>101</v>
       </c>
@@ -31641,7 +31498,7 @@
         <v>GCAP2.png</v>
       </c>
     </row>
-    <row r="941" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="941" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A941" s="2" t="s">
         <v>101</v>
       </c>
@@ -31671,7 +31528,7 @@
         <v>GCA350.png</v>
       </c>
     </row>
-    <row r="942" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="942" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A942" s="2" t="s">
         <v>101</v>
       </c>
@@ -31701,7 +31558,7 @@
         <v>GCA350.png</v>
       </c>
     </row>
-    <row r="943" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="943" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A943" s="2" t="s">
         <v>101</v>
       </c>
@@ -31731,7 +31588,7 @@
         <v>GCA350.png</v>
       </c>
     </row>
-    <row r="944" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="944" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A944" s="2" t="s">
         <v>101</v>
       </c>
@@ -31761,7 +31618,7 @@
         <v>GCA350.png</v>
       </c>
     </row>
-    <row r="945" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="945" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A945" s="2" t="s">
         <v>101</v>
       </c>
@@ -31791,7 +31648,7 @@
         <v>GCA350.png</v>
       </c>
     </row>
-    <row r="946" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="946" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A946" s="2" t="s">
         <v>101</v>
       </c>
@@ -31821,7 +31678,7 @@
         <v>BAREP2.png</v>
       </c>
     </row>
-    <row r="947" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="947" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A947" s="2" t="s">
         <v>101</v>
       </c>
@@ -31851,7 +31708,7 @@
         <v>H2OHP500.png</v>
       </c>
     </row>
-    <row r="948" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="948" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A948" s="2" t="s">
         <v>101</v>
       </c>
@@ -31881,7 +31738,7 @@
         <v>H2OHP500.png</v>
       </c>
     </row>
-    <row r="949" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="949" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A949" s="2" t="s">
         <v>101</v>
       </c>
@@ -31911,7 +31768,7 @@
         <v>H2OHP500.png</v>
       </c>
     </row>
-    <row r="950" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="950" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A950" s="2" t="s">
         <v>101</v>
       </c>
@@ -31941,7 +31798,7 @@
         <v>H2OHP500.png</v>
       </c>
     </row>
-    <row r="951" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="951" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A951" s="2" t="s">
         <v>101</v>
       </c>
@@ -31971,7 +31828,7 @@
         <v>PCB350.png</v>
       </c>
     </row>
-    <row r="952" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="952" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A952" s="2" t="s">
         <v>101</v>
       </c>
@@ -32001,7 +31858,7 @@
         <v>PCB350.png</v>
       </c>
     </row>
-    <row r="953" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="953" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A953" s="2" t="s">
         <v>101</v>
       </c>
@@ -32031,7 +31888,7 @@
         <v>PCB350.png</v>
       </c>
     </row>
-    <row r="954" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="954" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A954" s="2" t="s">
         <v>101</v>
       </c>
@@ -32061,7 +31918,7 @@
         <v>PCB350.png</v>
       </c>
     </row>
-    <row r="955" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="955" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A955" s="2" t="s">
         <v>101</v>
       </c>
@@ -32091,7 +31948,7 @@
         <v>PCB350.png</v>
       </c>
     </row>
-    <row r="956" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="956" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A956" s="2" t="s">
         <v>101</v>
       </c>
@@ -32121,7 +31978,7 @@
         <v>GCAP2.png</v>
       </c>
     </row>
-    <row r="957" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="957" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A957" s="2" t="s">
         <v>101</v>
       </c>
@@ -32151,7 +32008,7 @@
         <v>GCAP2.png</v>
       </c>
     </row>
-    <row r="958" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="958" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A958" s="2" t="s">
         <v>101</v>
       </c>
@@ -32181,7 +32038,7 @@
         <v>GCAP2.png</v>
       </c>
     </row>
-    <row r="959" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="959" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A959" s="2" t="s">
         <v>101</v>
       </c>
@@ -32211,7 +32068,7 @@
         <v>GCAP2.png</v>
       </c>
     </row>
-    <row r="960" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="960" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A960" s="2" t="s">
         <v>101</v>
       </c>
@@ -32241,7 +32098,7 @@
         <v>GCA269.png</v>
       </c>
     </row>
-    <row r="961" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="961" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A961" s="2" t="s">
         <v>101</v>
       </c>
@@ -32271,7 +32128,7 @@
         <v>GCA269.png</v>
       </c>
     </row>
-    <row r="962" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="962" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A962" s="2" t="s">
         <v>101</v>
       </c>
@@ -32301,7 +32158,7 @@
         <v>GCA269.png</v>
       </c>
     </row>
-    <row r="963" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="963" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A963" s="2" t="s">
         <v>101</v>
       </c>
@@ -32331,7 +32188,7 @@
         <v>GCA269.png</v>
       </c>
     </row>
-    <row r="964" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="964" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A964" s="2" t="s">
         <v>101</v>
       </c>
@@ -32361,7 +32218,7 @@
         <v>GCA269.png</v>
       </c>
     </row>
-    <row r="965" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="965" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A965" s="2" t="s">
         <v>101</v>
       </c>
@@ -32391,7 +32248,7 @@
         <v>PC269.png</v>
       </c>
     </row>
-    <row r="966" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="966" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A966" s="2" t="s">
         <v>101</v>
       </c>
@@ -32421,7 +32278,7 @@
         <v>PC269.png</v>
       </c>
     </row>
-    <row r="967" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="967" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A967" s="2" t="s">
         <v>101</v>
       </c>
@@ -32451,7 +32308,7 @@
         <v>PC269.png</v>
       </c>
     </row>
-    <row r="968" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="968" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A968" s="2" t="s">
         <v>101</v>
       </c>
@@ -32481,7 +32338,7 @@
         <v>PC269.png</v>
       </c>
     </row>
-    <row r="969" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="969" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A969" s="2" t="s">
         <v>101</v>
       </c>
@@ -32511,7 +32368,7 @@
         <v>PC269.png</v>
       </c>
     </row>
-    <row r="970" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="970" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A970" s="2" t="s">
         <v>101</v>
       </c>
@@ -32541,7 +32398,7 @@
         <v>GCAP1.png</v>
       </c>
     </row>
-    <row r="971" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="971" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A971" s="2" t="s">
         <v>101</v>
       </c>
@@ -32571,7 +32428,7 @@
         <v>GCAP1,5.png</v>
       </c>
     </row>
-    <row r="972" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="972" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A972" s="2" t="s">
         <v>101</v>
       </c>
@@ -32601,7 +32458,7 @@
         <v>GCAP1,5.png</v>
       </c>
     </row>
-    <row r="973" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="973" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A973" s="2" t="s">
         <v>101</v>
       </c>
@@ -32631,7 +32488,7 @@
         <v>GCAP1,5.png</v>
       </c>
     </row>
-    <row r="974" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="974" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A974" s="2" t="s">
         <v>101</v>
       </c>
@@ -32661,7 +32518,7 @@
         <v>PCP2.png</v>
       </c>
     </row>
-    <row r="975" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="975" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A975" s="2" t="s">
         <v>101</v>
       </c>
@@ -32691,7 +32548,7 @@
         <v>PCP2.png</v>
       </c>
     </row>
-    <row r="976" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="976" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A976" s="2" t="s">
         <v>101</v>
       </c>
@@ -32721,7 +32578,7 @@
         <v>PCP2.png</v>
       </c>
     </row>
-    <row r="977" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="977" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A977" s="2" t="s">
         <v>101</v>
       </c>
@@ -32751,7 +32608,7 @@
         <v>PCP2.png</v>
       </c>
     </row>
-    <row r="978" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="978" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A978" s="2" t="s">
         <v>101</v>
       </c>
@@ -32781,7 +32638,7 @@
         <v>H2OHP1,5.png</v>
       </c>
     </row>
-    <row r="979" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="979" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A979" s="2" t="s">
         <v>101</v>
       </c>
@@ -32811,7 +32668,7 @@
         <v>H2OHP1,5.png</v>
       </c>
     </row>
-    <row r="980" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="980" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A980" s="2" t="s">
         <v>101</v>
       </c>
@@ -32841,7 +32698,7 @@
         <v>H2OHP1,5.png</v>
       </c>
     </row>
-    <row r="981" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="981" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A981" s="2" t="s">
         <v>101</v>
       </c>
@@ -32871,176 +32728,182 @@
         <v>H2OHP1,5.png</v>
       </c>
     </row>
-    <row r="982" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="982" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I982" s="2"/>
     </row>
-    <row r="983" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="983" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I983" s="2"/>
     </row>
-    <row r="984" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="984" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I984" s="2"/>
     </row>
-    <row r="985" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="985" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I985" s="2"/>
     </row>
-    <row r="986" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="986" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I986" s="2"/>
     </row>
-    <row r="987" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="987" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I987" s="2"/>
     </row>
-    <row r="988" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="988" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I988" s="2"/>
     </row>
-    <row r="989" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="989" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I989" s="2"/>
     </row>
-    <row r="990" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="990" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I990" s="2"/>
     </row>
-    <row r="991" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="991" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I991" s="2"/>
     </row>
-    <row r="992" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="992" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I992" s="2"/>
     </row>
-    <row r="993" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="993" spans="9:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I993" s="2"/>
     </row>
-    <row r="994" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="994" spans="9:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I994" s="2"/>
     </row>
-    <row r="995" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="995" spans="9:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I995" s="2"/>
     </row>
-    <row r="996" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="996" spans="9:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I996" s="2"/>
     </row>
-    <row r="997" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="997" spans="9:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I997" s="2"/>
     </row>
-    <row r="998" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="998" spans="9:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I998" s="2"/>
     </row>
-    <row r="999" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="999" spans="9:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I999" s="2"/>
     </row>
-    <row r="1000" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="1000" spans="9:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I1000" s="2"/>
     </row>
-    <row r="1001" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="1001" spans="9:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I1001" s="2"/>
     </row>
-    <row r="1002" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="1002" spans="9:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I1002" s="2"/>
     </row>
-    <row r="1003" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="1003" spans="9:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I1003" s="2"/>
     </row>
-    <row r="1004" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="1004" spans="9:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I1004" s="2"/>
     </row>
-    <row r="1005" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="1005" spans="9:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I1005" s="2"/>
     </row>
-    <row r="1006" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="1006" spans="9:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I1006" s="2"/>
     </row>
-    <row r="1007" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="1007" spans="9:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I1007" s="2"/>
     </row>
-    <row r="1008" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="1008" spans="9:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I1008" s="2"/>
     </row>
-    <row r="1009" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="1009" spans="9:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I1009" s="2"/>
     </row>
-    <row r="1010" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="1010" spans="9:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I1010" s="2"/>
     </row>
-    <row r="1011" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="1011" spans="9:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I1011" s="2"/>
     </row>
-    <row r="1012" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="1012" spans="9:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I1012" s="2"/>
     </row>
-    <row r="1013" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="1013" spans="9:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I1013" s="2"/>
     </row>
-    <row r="1014" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="1014" spans="9:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I1014" s="2"/>
     </row>
-    <row r="1015" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="1015" spans="9:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I1015" s="2"/>
     </row>
-    <row r="1016" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="1016" spans="9:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I1016" s="2"/>
     </row>
-    <row r="1017" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="1017" spans="9:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I1017" s="2"/>
     </row>
-    <row r="1018" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="1018" spans="9:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I1018" s="2"/>
     </row>
-    <row r="1019" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="1019" spans="9:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I1019" s="2"/>
     </row>
-    <row r="1020" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="1020" spans="9:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I1020" s="2"/>
     </row>
-    <row r="1021" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="1021" spans="9:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I1021" s="2"/>
     </row>
-    <row r="1022" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="1022" spans="9:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I1022" s="2"/>
     </row>
-    <row r="1023" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="1023" spans="9:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I1023" s="2"/>
     </row>
-    <row r="1024" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="1024" spans="9:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I1024" s="2"/>
     </row>
-    <row r="1025" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="1025" spans="9:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I1025" s="2"/>
     </row>
-    <row r="1026" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="1026" spans="9:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I1026" s="2"/>
     </row>
-    <row r="1027" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="1027" spans="9:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I1027" s="2"/>
     </row>
-    <row r="1028" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="1028" spans="9:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I1028" s="2"/>
     </row>
-    <row r="1029" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="1029" spans="9:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I1029" s="2"/>
     </row>
-    <row r="1030" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="1030" spans="9:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I1030" s="2"/>
     </row>
-    <row r="1031" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="1031" spans="9:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I1031" s="2"/>
     </row>
-    <row r="1032" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="1032" spans="9:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I1032" s="2"/>
     </row>
-    <row r="1033" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="1033" spans="9:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I1033" s="2"/>
     </row>
-    <row r="1034" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="1034" spans="9:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I1034" s="2"/>
     </row>
-    <row r="1035" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="1035" spans="9:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I1035" s="2"/>
     </row>
-    <row r="1036" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="1036" spans="9:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I1036" s="2"/>
     </row>
-    <row r="1037" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="1037" spans="9:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="I1037" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1037" xr:uid="{34B2C8DF-4561-40B2-8E7C-6CD69559B9AE}"/>
+  <autoFilter ref="A1:I1037" xr:uid="{34B2C8DF-4561-40B2-8E7C-6CD69559B9AE}">
+    <filterColumn colId="5">
+      <filters>
+        <filter val="FF 350"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>

--- a/data/calendario_promocional.xlsx
+++ b/data/calendario_promocional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anheuserbuschinbev-my.sharepoint.com/personal/99823517_ab-inbev_com/Documents/001. Projetos/Streamlit Calendario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="747" documentId="11_F25DC773A252ABDACC1048AAA9DA54025ADE5901" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A63E7851-6EA4-4116-A6A1-7C826A26DCD1}"/>
+  <xr:revisionPtr revIDLastSave="757" documentId="11_F25DC773A252ABDACC1048AAA9DA54025ADE5901" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3399A06-1443-4945-A5DE-4B0342F26A85}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">CALENDARIO!$A$1:$B$53</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DeparaIMG!$A$1:$D$37</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">MECANICA!$A$1:$D$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">MECANICA!$A$1:$D$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">PRODUTOS!$A$1:$I$1037</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5321" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5345" uniqueCount="114">
   <si>
     <t>Data</t>
   </si>
@@ -2726,7 +2726,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D40F4A5-E774-499A-A01D-1C21EEE25028}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="47.5703125" bestFit="1" customWidth="1"/>
@@ -3278,8 +3278,92 @@
         <v>98</v>
       </c>
     </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D21" xr:uid="{6D40F4A5-E774-499A-A01D-1C21EEE25028}">
+  <autoFilter ref="A1:D39" xr:uid="{6D40F4A5-E774-499A-A01D-1C21EEE25028}">
     <filterColumn colId="1">
       <filters>
         <filter val="CERV"/>
@@ -30771,7 +30855,7 @@
         <v>5.19</v>
       </c>
       <c r="H916">
-        <v>4.5</v>
+        <v>4.8900000000000006</v>
       </c>
       <c r="I916" s="2" t="str">
         <f>_xlfn.XLOOKUP(F916,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>

--- a/data/calendario_promocional.xlsx
+++ b/data/calendario_promocional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anheuserbuschinbev-my.sharepoint.com/personal/99823517_ab-inbev_com/Documents/001. Projetos/Streamlit Calendario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="757" documentId="11_F25DC773A252ABDACC1048AAA9DA54025ADE5901" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3399A06-1443-4945-A5DE-4B0342F26A85}"/>
+  <xr:revisionPtr revIDLastSave="759" documentId="11_F25DC773A252ABDACC1048AAA9DA54025ADE5901" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11093FE8-8FE3-40AD-9226-FE38E034C5BF}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DeparaIMG" sheetId="5" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5345" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5337" uniqueCount="115">
   <si>
     <t>Data</t>
   </si>
@@ -388,6 +388,9 @@
   </si>
   <si>
     <t>Imagem</t>
+  </si>
+  <si>
+    <t>MATCH: 50% Volume Mês</t>
   </si>
 </sst>
 </file>
@@ -2726,7 +2729,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D40F4A5-E774-499A-A01D-1C21EEE25028}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="47.5703125" bestFit="1" customWidth="1"/>
@@ -3303,7 +3306,7 @@
         <v>23</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -3314,10 +3317,10 @@
         <v>107</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>99</v>
+        <v>59</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -3328,37 +3331,9 @@
         <v>107</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D45" s="2" t="s">
         <v>98</v>
       </c>
     </row>

--- a/data/calendario_promocional.xlsx
+++ b/data/calendario_promocional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anheuserbuschinbev-my.sharepoint.com/personal/99823517_ab-inbev_com/Documents/001. Projetos/Streamlit Calendario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="801" documentId="11_F25DC773A252ABDACC1048AAA9DA54025ADE5901" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8AC1759C-310D-4646-AA1E-53A0A4493E3D}"/>
+  <xr:revisionPtr revIDLastSave="807" documentId="11_F25DC773A252ABDACC1048AAA9DA54025ADE5901" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A111913-64E9-45D8-B574-B519FB56D9BC}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6819" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6576" uniqueCount="117">
   <si>
     <t>Data</t>
   </si>
@@ -391,12 +391,6 @@
   </si>
   <si>
     <t>MATCH: 50% Volume Mês</t>
-  </si>
-  <si>
-    <t>Q2</t>
-  </si>
-  <si>
-    <t>Q1</t>
   </si>
   <si>
     <t>DF/TO</t>
@@ -5775,7 +5769,7 @@
         <v>63</v>
       </c>
       <c r="C78" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D78" t="s">
         <v>26</v>
@@ -5805,7 +5799,7 @@
         <v>63</v>
       </c>
       <c r="C79" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D79" t="s">
         <v>25</v>
@@ -5835,7 +5829,7 @@
         <v>63</v>
       </c>
       <c r="C80" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D80" t="s">
         <v>25</v>
@@ -6135,7 +6129,7 @@
         <v>63</v>
       </c>
       <c r="C90" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D90" t="s">
         <v>26</v>
@@ -6165,7 +6159,7 @@
         <v>63</v>
       </c>
       <c r="C91" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D91" t="s">
         <v>25</v>
@@ -6285,7 +6279,7 @@
         <v>63</v>
       </c>
       <c r="C95" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D95" t="s">
         <v>25</v>
@@ -6315,7 +6309,7 @@
         <v>63</v>
       </c>
       <c r="C96" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D96" t="s">
         <v>26</v>
@@ -6405,7 +6399,7 @@
         <v>63</v>
       </c>
       <c r="C99" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D99" t="s">
         <v>25</v>
@@ -6435,7 +6429,7 @@
         <v>63</v>
       </c>
       <c r="C100" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D100" t="s">
         <v>25</v>
@@ -6465,7 +6459,7 @@
         <v>63</v>
       </c>
       <c r="C101" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D101" t="s">
         <v>26</v>
@@ -6855,7 +6849,7 @@
         <v>63</v>
       </c>
       <c r="C114" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D114" t="s">
         <v>25</v>
@@ -7065,7 +7059,7 @@
         <v>63</v>
       </c>
       <c r="C121" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D121" t="s">
         <v>25</v>
@@ -7185,7 +7179,7 @@
         <v>63</v>
       </c>
       <c r="C125" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D125" t="s">
         <v>25</v>
@@ -7215,7 +7209,7 @@
         <v>63</v>
       </c>
       <c r="C126" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D126" t="s">
         <v>25</v>
@@ -7365,7 +7359,7 @@
         <v>63</v>
       </c>
       <c r="C131" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D131" t="s">
         <v>25</v>
@@ -7395,7 +7389,7 @@
         <v>63</v>
       </c>
       <c r="C132" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D132" t="s">
         <v>25</v>
@@ -7605,7 +7599,7 @@
         <v>63</v>
       </c>
       <c r="C139" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D139" t="s">
         <v>26</v>
@@ -7725,7 +7719,7 @@
         <v>63</v>
       </c>
       <c r="C143" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D143" t="s">
         <v>25</v>
@@ -7815,7 +7809,7 @@
         <v>63</v>
       </c>
       <c r="C146" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D146" t="s">
         <v>25</v>
@@ -8055,7 +8049,7 @@
         <v>63</v>
       </c>
       <c r="C154" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D154" t="s">
         <v>25</v>
@@ -8115,7 +8109,7 @@
         <v>63</v>
       </c>
       <c r="C156" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D156" t="s">
         <v>26</v>
@@ -8235,7 +8229,7 @@
         <v>63</v>
       </c>
       <c r="C160" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D160" t="s">
         <v>25</v>
@@ -8265,7 +8259,7 @@
         <v>63</v>
       </c>
       <c r="C161" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D161" t="s">
         <v>26</v>
@@ -8295,7 +8289,7 @@
         <v>63</v>
       </c>
       <c r="C162" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D162" t="s">
         <v>26</v>
@@ -8355,7 +8349,7 @@
         <v>63</v>
       </c>
       <c r="C164" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D164" t="s">
         <v>26</v>
@@ -8385,7 +8379,7 @@
         <v>63</v>
       </c>
       <c r="C165" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D165" t="s">
         <v>26</v>
@@ -8595,7 +8589,7 @@
         <v>63</v>
       </c>
       <c r="C172" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D172" t="s">
         <v>26</v>
@@ -8625,7 +8619,7 @@
         <v>63</v>
       </c>
       <c r="C173" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D173" t="s">
         <v>26</v>
@@ -8775,7 +8769,7 @@
         <v>63</v>
       </c>
       <c r="C178" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D178" t="s">
         <v>25</v>
@@ -8805,7 +8799,7 @@
         <v>63</v>
       </c>
       <c r="C179" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D179" t="s">
         <v>26</v>
@@ -8895,7 +8889,7 @@
         <v>63</v>
       </c>
       <c r="C182" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D182" t="s">
         <v>26</v>
@@ -8985,7 +8979,7 @@
         <v>63</v>
       </c>
       <c r="C185" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D185" t="s">
         <v>26</v>
@@ -9285,7 +9279,7 @@
         <v>63</v>
       </c>
       <c r="C195" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D195" t="s">
         <v>26</v>
@@ -9315,7 +9309,7 @@
         <v>63</v>
       </c>
       <c r="C196" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D196" t="s">
         <v>25</v>
@@ -9345,7 +9339,7 @@
         <v>63</v>
       </c>
       <c r="C197" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D197" t="s">
         <v>26</v>
@@ -9375,7 +9369,7 @@
         <v>63</v>
       </c>
       <c r="C198" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D198" t="s">
         <v>26</v>
@@ -9855,7 +9849,7 @@
         <v>63</v>
       </c>
       <c r="C214" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D214" t="s">
         <v>26</v>
@@ -9915,7 +9909,7 @@
         <v>63</v>
       </c>
       <c r="C216" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D216" t="s">
         <v>25</v>
@@ -9945,7 +9939,7 @@
         <v>63</v>
       </c>
       <c r="C217" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D217" t="s">
         <v>26</v>
@@ -10095,7 +10089,7 @@
         <v>63</v>
       </c>
       <c r="C222" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D222" t="s">
         <v>25</v>
@@ -10125,7 +10119,7 @@
         <v>63</v>
       </c>
       <c r="C223" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D223" t="s">
         <v>26</v>
@@ -10155,7 +10149,7 @@
         <v>63</v>
       </c>
       <c r="C224" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D224" t="s">
         <v>25</v>
@@ -10215,7 +10209,7 @@
         <v>63</v>
       </c>
       <c r="C226" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D226" t="s">
         <v>26</v>
@@ -10425,7 +10419,7 @@
         <v>63</v>
       </c>
       <c r="C233" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D233" t="s">
         <v>25</v>
@@ -10455,7 +10449,7 @@
         <v>63</v>
       </c>
       <c r="C234" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D234" t="s">
         <v>26</v>
@@ -10485,7 +10479,7 @@
         <v>63</v>
       </c>
       <c r="C235" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D235" t="s">
         <v>26</v>
@@ -10515,7 +10509,7 @@
         <v>63</v>
       </c>
       <c r="C236" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D236" t="s">
         <v>25</v>
@@ -10575,7 +10569,7 @@
         <v>63</v>
       </c>
       <c r="C238" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D238" t="s">
         <v>26</v>
@@ -10695,7 +10689,7 @@
         <v>63</v>
       </c>
       <c r="C242" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D242" t="s">
         <v>26</v>
@@ -10935,7 +10929,7 @@
         <v>63</v>
       </c>
       <c r="C250" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D250" t="s">
         <v>25</v>
@@ -10965,7 +10959,7 @@
         <v>63</v>
       </c>
       <c r="C251" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D251" t="s">
         <v>26</v>
@@ -11085,7 +11079,7 @@
         <v>63</v>
       </c>
       <c r="C255" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D255" t="s">
         <v>25</v>
@@ -11115,7 +11109,7 @@
         <v>63</v>
       </c>
       <c r="C256" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D256" t="s">
         <v>26</v>
@@ -11145,7 +11139,7 @@
         <v>63</v>
       </c>
       <c r="C257" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D257" t="s">
         <v>25</v>
@@ -11175,7 +11169,7 @@
         <v>63</v>
       </c>
       <c r="C258" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D258" t="s">
         <v>26</v>
@@ -11235,7 +11229,7 @@
         <v>63</v>
       </c>
       <c r="C260" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D260" t="s">
         <v>26</v>
@@ -11445,7 +11439,7 @@
         <v>63</v>
       </c>
       <c r="C267" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D267" t="s">
         <v>25</v>
@@ -11475,7 +11469,7 @@
         <v>63</v>
       </c>
       <c r="C268" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D268" t="s">
         <v>26</v>
@@ -11685,7 +11679,7 @@
         <v>63</v>
       </c>
       <c r="C275" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D275" t="s">
         <v>25</v>
@@ -11715,7 +11709,7 @@
         <v>63</v>
       </c>
       <c r="C276" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D276" t="s">
         <v>26</v>
@@ -11895,7 +11889,7 @@
         <v>63</v>
       </c>
       <c r="C282" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D282" t="s">
         <v>25</v>
@@ -11955,7 +11949,7 @@
         <v>63</v>
       </c>
       <c r="C284" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D284" t="s">
         <v>25</v>
@@ -12105,7 +12099,7 @@
         <v>63</v>
       </c>
       <c r="C289" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D289" t="s">
         <v>26</v>
@@ -12165,7 +12159,7 @@
         <v>63</v>
       </c>
       <c r="C291" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D291" t="s">
         <v>26</v>
@@ -12315,7 +12309,7 @@
         <v>63</v>
       </c>
       <c r="C296" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D296" t="s">
         <v>26</v>
@@ -12495,7 +12489,7 @@
         <v>63</v>
       </c>
       <c r="C302" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D302" t="s">
         <v>26</v>
@@ -12645,7 +12639,7 @@
         <v>63</v>
       </c>
       <c r="C307" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D307" t="s">
         <v>25</v>
@@ -12675,7 +12669,7 @@
         <v>63</v>
       </c>
       <c r="C308" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D308" t="s">
         <v>26</v>
@@ -12855,7 +12849,7 @@
         <v>63</v>
       </c>
       <c r="C314" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D314" t="s">
         <v>25</v>
@@ -12885,7 +12879,7 @@
         <v>63</v>
       </c>
       <c r="C315" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D315" t="s">
         <v>25</v>
@@ -12915,7 +12909,7 @@
         <v>63</v>
       </c>
       <c r="C316" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D316" t="s">
         <v>26</v>
@@ -13095,7 +13089,7 @@
         <v>63</v>
       </c>
       <c r="C322" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D322" t="s">
         <v>25</v>
@@ -13245,7 +13239,7 @@
         <v>63</v>
       </c>
       <c r="C327" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D327" t="s">
         <v>25</v>
@@ -13335,7 +13329,7 @@
         <v>63</v>
       </c>
       <c r="C330" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D330" t="s">
         <v>25</v>
@@ -13365,7 +13359,7 @@
         <v>63</v>
       </c>
       <c r="C331" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D331" t="s">
         <v>26</v>
@@ -13455,7 +13449,7 @@
         <v>63</v>
       </c>
       <c r="C334" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D334" t="s">
         <v>25</v>
@@ -13485,7 +13479,7 @@
         <v>63</v>
       </c>
       <c r="C335" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D335" t="s">
         <v>25</v>
@@ -13515,7 +13509,7 @@
         <v>63</v>
       </c>
       <c r="C336" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D336" t="s">
         <v>26</v>
@@ -13845,7 +13839,7 @@
         <v>63</v>
       </c>
       <c r="C347" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D347" t="s">
         <v>25</v>
@@ -13965,7 +13959,7 @@
         <v>63</v>
       </c>
       <c r="C351" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D351" t="s">
         <v>25</v>
@@ -14175,7 +14169,7 @@
         <v>63</v>
       </c>
       <c r="C358" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D358" t="s">
         <v>26</v>
@@ -14205,7 +14199,7 @@
         <v>63</v>
       </c>
       <c r="C359" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D359" t="s">
         <v>25</v>
@@ -14235,7 +14229,7 @@
         <v>63</v>
       </c>
       <c r="C360" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D360" t="s">
         <v>25</v>
@@ -14385,7 +14379,7 @@
         <v>63</v>
       </c>
       <c r="C365" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D365" t="s">
         <v>25</v>
@@ -14415,7 +14409,7 @@
         <v>63</v>
       </c>
       <c r="C366" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D366" t="s">
         <v>25</v>
@@ -14655,7 +14649,7 @@
         <v>63</v>
       </c>
       <c r="C374" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D374" t="s">
         <v>26</v>
@@ -14895,7 +14889,7 @@
         <v>63</v>
       </c>
       <c r="C382" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D382" t="s">
         <v>25</v>
@@ -14925,7 +14919,7 @@
         <v>63</v>
       </c>
       <c r="C383" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D383" t="s">
         <v>26</v>
@@ -15075,7 +15069,7 @@
         <v>63</v>
       </c>
       <c r="C388" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D388" t="s">
         <v>25</v>
@@ -15105,7 +15099,7 @@
         <v>63</v>
       </c>
       <c r="C389" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D389" t="s">
         <v>26</v>
@@ -15165,7 +15159,7 @@
         <v>63</v>
       </c>
       <c r="C391" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D391" t="s">
         <v>26</v>
@@ -15195,7 +15189,7 @@
         <v>63</v>
       </c>
       <c r="C392" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D392" t="s">
         <v>26</v>
@@ -15405,7 +15399,7 @@
         <v>63</v>
       </c>
       <c r="C399" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D399" t="s">
         <v>26</v>
@@ -15435,7 +15429,7 @@
         <v>63</v>
       </c>
       <c r="C400" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D400" t="s">
         <v>26</v>
@@ -15675,7 +15669,7 @@
         <v>63</v>
       </c>
       <c r="C408" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D408" t="s">
         <v>25</v>
@@ -15705,7 +15699,7 @@
         <v>63</v>
       </c>
       <c r="C409" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D409" t="s">
         <v>26</v>
@@ -15735,7 +15729,7 @@
         <v>63</v>
       </c>
       <c r="C410" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D410" t="s">
         <v>25</v>
@@ -15765,7 +15759,7 @@
         <v>63</v>
       </c>
       <c r="C411" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D411" t="s">
         <v>26</v>
@@ -15795,7 +15789,7 @@
         <v>63</v>
       </c>
       <c r="C412" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D412" t="s">
         <v>26</v>
@@ -16155,7 +16149,7 @@
         <v>63</v>
       </c>
       <c r="C424" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D424" t="s">
         <v>26</v>
@@ -16305,7 +16299,7 @@
         <v>63</v>
       </c>
       <c r="C429" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D429" t="s">
         <v>26</v>
@@ -16365,7 +16359,7 @@
         <v>63</v>
       </c>
       <c r="C431" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D431" t="s">
         <v>26</v>
@@ -16395,7 +16389,7 @@
         <v>63</v>
       </c>
       <c r="C432" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D432" t="s">
         <v>25</v>
@@ -16425,7 +16419,7 @@
         <v>63</v>
       </c>
       <c r="C433" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D433" t="s">
         <v>26</v>
@@ -16575,7 +16569,7 @@
         <v>63</v>
       </c>
       <c r="C438" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D438" t="s">
         <v>25</v>
@@ -16605,7 +16599,7 @@
         <v>63</v>
       </c>
       <c r="C439" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D439" t="s">
         <v>26</v>
@@ -16815,7 +16809,7 @@
         <v>63</v>
       </c>
       <c r="C446" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D446" t="s">
         <v>26</v>
@@ -16845,7 +16839,7 @@
         <v>63</v>
       </c>
       <c r="C447" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D447" t="s">
         <v>26</v>
@@ -16875,7 +16869,7 @@
         <v>63</v>
       </c>
       <c r="C448" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D448" t="s">
         <v>25</v>
@@ -16905,7 +16899,7 @@
         <v>63</v>
       </c>
       <c r="C449" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D449" t="s">
         <v>26</v>
@@ -16935,7 +16929,7 @@
         <v>63</v>
       </c>
       <c r="C450" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D450" t="s">
         <v>26</v>
@@ -17145,7 +17139,7 @@
         <v>63</v>
       </c>
       <c r="C457" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D457" t="s">
         <v>25</v>
@@ -17175,7 +17169,7 @@
         <v>63</v>
       </c>
       <c r="C458" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D458" t="s">
         <v>26</v>
@@ -17205,7 +17199,7 @@
         <v>63</v>
       </c>
       <c r="C459" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D459" t="s">
         <v>25</v>
@@ -17235,7 +17229,7 @@
         <v>63</v>
       </c>
       <c r="C460" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D460" t="s">
         <v>26</v>
@@ -17415,7 +17409,7 @@
         <v>63</v>
       </c>
       <c r="C466" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D466" t="s">
         <v>26</v>
@@ -17535,7 +17529,7 @@
         <v>63</v>
       </c>
       <c r="C470" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D470" t="s">
         <v>26</v>
@@ -17715,7 +17709,7 @@
         <v>63</v>
       </c>
       <c r="C476" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D476" t="s">
         <v>25</v>
@@ -17805,7 +17799,7 @@
         <v>63</v>
       </c>
       <c r="C479" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D479" t="s">
         <v>25</v>
@@ -17835,7 +17829,7 @@
         <v>63</v>
       </c>
       <c r="C480" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D480" t="s">
         <v>26</v>
@@ -18045,7 +18039,7 @@
         <v>63</v>
       </c>
       <c r="C487" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D487" t="s">
         <v>25</v>
@@ -18075,7 +18069,7 @@
         <v>63</v>
       </c>
       <c r="C488" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D488" t="s">
         <v>26</v>
@@ -18255,7 +18249,7 @@
         <v>63</v>
       </c>
       <c r="C494" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D494" t="s">
         <v>26</v>
@@ -18435,7 +18429,7 @@
         <v>63</v>
       </c>
       <c r="C500" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D500" t="s">
         <v>26</v>
@@ -18585,7 +18579,7 @@
         <v>63</v>
       </c>
       <c r="C505" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D505" t="s">
         <v>25</v>
@@ -18615,7 +18609,7 @@
         <v>63</v>
       </c>
       <c r="C506" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D506" t="s">
         <v>26</v>
@@ -18795,7 +18789,7 @@
         <v>63</v>
       </c>
       <c r="C512" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D512" t="s">
         <v>25</v>
@@ -18825,7 +18819,7 @@
         <v>63</v>
       </c>
       <c r="C513" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D513" t="s">
         <v>25</v>
@@ -18855,7 +18849,7 @@
         <v>63</v>
       </c>
       <c r="C514" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D514" t="s">
         <v>26</v>
@@ -19035,7 +19029,7 @@
         <v>63</v>
       </c>
       <c r="C520" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D520" t="s">
         <v>25</v>
@@ -19215,7 +19209,7 @@
         <v>63</v>
       </c>
       <c r="C526" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D526" t="s">
         <v>25</v>
@@ -19275,7 +19269,7 @@
         <v>63</v>
       </c>
       <c r="C528" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D528" t="s">
         <v>25</v>
@@ -19305,7 +19299,7 @@
         <v>63</v>
       </c>
       <c r="C529" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D529" t="s">
         <v>26</v>
@@ -19395,7 +19389,7 @@
         <v>63</v>
       </c>
       <c r="C532" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D532" t="s">
         <v>25</v>
@@ -19425,7 +19419,7 @@
         <v>63</v>
       </c>
       <c r="C533" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D533" t="s">
         <v>25</v>
@@ -19455,7 +19449,7 @@
         <v>63</v>
       </c>
       <c r="C534" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D534" t="s">
         <v>26</v>
@@ -19785,7 +19779,7 @@
         <v>63</v>
       </c>
       <c r="C545" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D545" t="s">
         <v>25</v>
@@ -19905,7 +19899,7 @@
         <v>63</v>
       </c>
       <c r="C549" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D549" t="s">
         <v>25</v>
@@ -20115,7 +20109,7 @@
         <v>63</v>
       </c>
       <c r="C556" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D556" t="s">
         <v>26</v>
@@ -20145,7 +20139,7 @@
         <v>63</v>
       </c>
       <c r="C557" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D557" t="s">
         <v>25</v>
@@ -20175,7 +20169,7 @@
         <v>63</v>
       </c>
       <c r="C558" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D558" t="s">
         <v>25</v>
@@ -20325,7 +20319,7 @@
         <v>63</v>
       </c>
       <c r="C563" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D563" t="s">
         <v>25</v>
@@ -20355,7 +20349,7 @@
         <v>63</v>
       </c>
       <c r="C564" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D564" t="s">
         <v>25</v>
@@ -20595,7 +20589,7 @@
         <v>63</v>
       </c>
       <c r="C572" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D572" t="s">
         <v>26</v>
@@ -20655,7 +20649,7 @@
         <v>63</v>
       </c>
       <c r="C574" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D574" t="s">
         <v>26</v>
@@ -20685,7 +20679,7 @@
         <v>63</v>
       </c>
       <c r="C575" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D575" t="s">
         <v>26</v>
@@ -20775,7 +20769,7 @@
         <v>63</v>
       </c>
       <c r="C578" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D578" t="s">
         <v>25</v>
@@ -20805,7 +20799,7 @@
         <v>63</v>
       </c>
       <c r="C579" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D579" t="s">
         <v>26</v>
@@ -21135,7 +21129,7 @@
         <v>63</v>
       </c>
       <c r="C590" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D590" t="s">
         <v>25</v>
@@ -21165,7 +21159,7 @@
         <v>63</v>
       </c>
       <c r="C591" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D591" t="s">
         <v>26</v>
@@ -21315,7 +21309,7 @@
         <v>63</v>
       </c>
       <c r="C596" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D596" t="s">
         <v>26</v>
@@ -21345,7 +21339,7 @@
         <v>63</v>
       </c>
       <c r="C597" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D597" t="s">
         <v>26</v>
@@ -21495,7 +21489,7 @@
         <v>63</v>
       </c>
       <c r="C602" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D602" t="s">
         <v>25</v>
@@ -21525,7 +21519,7 @@
         <v>63</v>
       </c>
       <c r="C603" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D603" t="s">
         <v>26</v>
@@ -21555,7 +21549,7 @@
         <v>63</v>
       </c>
       <c r="C604" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D604" t="s">
         <v>25</v>
@@ -21585,7 +21579,7 @@
         <v>63</v>
       </c>
       <c r="C605" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D605" t="s">
         <v>26</v>
@@ -21615,7 +21609,7 @@
         <v>63</v>
       </c>
       <c r="C606" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D606" t="s">
         <v>26</v>
@@ -21975,7 +21969,7 @@
         <v>63</v>
       </c>
       <c r="C618" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D618" t="s">
         <v>26</v>
@@ -22245,7 +22239,7 @@
         <v>63</v>
       </c>
       <c r="C627" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D627" t="s">
         <v>26</v>
@@ -22305,7 +22299,7 @@
         <v>63</v>
       </c>
       <c r="C629" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D629" t="s">
         <v>26</v>
@@ -22335,7 +22329,7 @@
         <v>63</v>
       </c>
       <c r="C630" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D630" t="s">
         <v>25</v>
@@ -22365,7 +22359,7 @@
         <v>63</v>
       </c>
       <c r="C631" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D631" t="s">
         <v>26</v>
@@ -22515,7 +22509,7 @@
         <v>63</v>
       </c>
       <c r="C636" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D636" t="s">
         <v>25</v>
@@ -22545,7 +22539,7 @@
         <v>63</v>
       </c>
       <c r="C637" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D637" t="s">
         <v>26</v>
@@ -22755,7 +22749,7 @@
         <v>63</v>
       </c>
       <c r="C644" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D644" t="s">
         <v>26</v>
@@ -22785,7 +22779,7 @@
         <v>63</v>
       </c>
       <c r="C645" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D645" t="s">
         <v>26</v>
@@ -22995,7 +22989,7 @@
         <v>63</v>
       </c>
       <c r="C652" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D652" t="s">
         <v>26</v>
@@ -23025,7 +23019,7 @@
         <v>63</v>
       </c>
       <c r="C653" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D653" t="s">
         <v>26</v>
@@ -23115,7 +23109,7 @@
         <v>63</v>
       </c>
       <c r="C656" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D656" t="s">
         <v>26</v>
@@ -23145,7 +23139,7 @@
         <v>63</v>
       </c>
       <c r="C657" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D657" t="s">
         <v>26</v>
@@ -23265,7 +23259,7 @@
         <v>63</v>
       </c>
       <c r="C661" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D661" t="s">
         <v>26</v>
@@ -23385,7 +23379,7 @@
         <v>63</v>
       </c>
       <c r="C665" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D665" t="s">
         <v>26</v>
@@ -23475,7 +23469,7 @@
         <v>63</v>
       </c>
       <c r="C668" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D668" t="s">
         <v>25</v>
@@ -23505,7 +23499,7 @@
         <v>63</v>
       </c>
       <c r="C669" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D669" t="s">
         <v>26</v>
@@ -23715,7 +23709,7 @@
         <v>63</v>
       </c>
       <c r="C676" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D676" t="s">
         <v>25</v>
@@ -23745,7 +23739,7 @@
         <v>63</v>
       </c>
       <c r="C677" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D677" t="s">
         <v>26</v>
@@ -23925,7 +23919,7 @@
         <v>63</v>
       </c>
       <c r="C683" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D683" t="s">
         <v>26</v>
@@ -24105,7 +24099,7 @@
         <v>63</v>
       </c>
       <c r="C689" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D689" t="s">
         <v>26</v>
@@ -24255,7 +24249,7 @@
         <v>63</v>
       </c>
       <c r="C694" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D694" t="s">
         <v>25</v>
@@ -24285,7 +24279,7 @@
         <v>63</v>
       </c>
       <c r="C695" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D695" t="s">
         <v>26</v>
@@ -24465,7 +24459,7 @@
         <v>63</v>
       </c>
       <c r="C701" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D701" t="s">
         <v>25</v>
@@ -24495,7 +24489,7 @@
         <v>63</v>
       </c>
       <c r="C702" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D702" t="s">
         <v>25</v>
@@ -24525,7 +24519,7 @@
         <v>63</v>
       </c>
       <c r="C703" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D703" t="s">
         <v>26</v>
@@ -24705,7 +24699,7 @@
         <v>63</v>
       </c>
       <c r="C709" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D709" t="s">
         <v>25</v>
@@ -24735,7 +24729,7 @@
         <v>63</v>
       </c>
       <c r="C710" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D710" t="s">
         <v>25</v>
@@ -24855,7 +24849,7 @@
         <v>63</v>
       </c>
       <c r="C714" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D714" t="s">
         <v>25</v>
@@ -25065,7 +25059,7 @@
         <v>63</v>
       </c>
       <c r="C721" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D721" t="s">
         <v>25</v>
@@ -25095,7 +25089,7 @@
         <v>63</v>
       </c>
       <c r="C722" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D722" t="s">
         <v>25</v>
@@ -25125,7 +25119,7 @@
         <v>63</v>
       </c>
       <c r="C723" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D723" t="s">
         <v>25</v>
@@ -25155,7 +25149,7 @@
         <v>63</v>
       </c>
       <c r="C724" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D724" t="s">
         <v>25</v>
@@ -25185,7 +25179,7 @@
         <v>63</v>
       </c>
       <c r="C725" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D725" t="s">
         <v>25</v>
@@ -25215,7 +25209,7 @@
         <v>63</v>
       </c>
       <c r="C726" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D726" t="s">
         <v>25</v>
@@ -25245,7 +25239,7 @@
         <v>63</v>
       </c>
       <c r="C727" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D727" t="s">
         <v>25</v>
@@ -25275,7 +25269,7 @@
         <v>63</v>
       </c>
       <c r="C728" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D728" t="s">
         <v>25</v>
@@ -25305,7 +25299,7 @@
         <v>63</v>
       </c>
       <c r="C729" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D729" t="s">
         <v>25</v>
@@ -25335,7 +25329,7 @@
         <v>63</v>
       </c>
       <c r="C730" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D730" t="s">
         <v>25</v>
@@ -25365,7 +25359,7 @@
         <v>63</v>
       </c>
       <c r="C731" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D731" t="s">
         <v>26</v>
@@ -25395,7 +25389,7 @@
         <v>63</v>
       </c>
       <c r="C732" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D732" t="s">
         <v>26</v>
@@ -25425,7 +25419,7 @@
         <v>63</v>
       </c>
       <c r="C733" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D733" t="s">
         <v>26</v>
@@ -25455,7 +25449,7 @@
         <v>63</v>
       </c>
       <c r="C734" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D734" t="s">
         <v>26</v>
@@ -25485,7 +25479,7 @@
         <v>63</v>
       </c>
       <c r="C735" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D735" t="s">
         <v>26</v>
@@ -25515,7 +25509,7 @@
         <v>63</v>
       </c>
       <c r="C736" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D736" t="s">
         <v>26</v>
@@ -25545,7 +25539,7 @@
         <v>63</v>
       </c>
       <c r="C737" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D737" t="s">
         <v>26</v>
@@ -25575,7 +25569,7 @@
         <v>63</v>
       </c>
       <c r="C738" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D738" t="s">
         <v>26</v>
@@ -25605,7 +25599,7 @@
         <v>63</v>
       </c>
       <c r="C739" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D739" t="s">
         <v>26</v>
@@ -25635,7 +25629,7 @@
         <v>63</v>
       </c>
       <c r="C740" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D740" t="s">
         <v>26</v>
@@ -25665,7 +25659,7 @@
         <v>63</v>
       </c>
       <c r="C741" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D741" t="s">
         <v>26</v>
@@ -25695,7 +25689,7 @@
         <v>63</v>
       </c>
       <c r="C742" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D742" t="s">
         <v>26</v>
@@ -25725,7 +25719,7 @@
         <v>63</v>
       </c>
       <c r="C743" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D743" t="s">
         <v>26</v>
@@ -25755,7 +25749,7 @@
         <v>63</v>
       </c>
       <c r="C744" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D744" t="s">
         <v>26</v>
@@ -27945,7 +27939,7 @@
         <v>63</v>
       </c>
       <c r="C817" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D817" t="s">
         <v>25</v>
@@ -27975,7 +27969,7 @@
         <v>63</v>
       </c>
       <c r="C818" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D818" t="s">
         <v>25</v>
@@ -28005,7 +27999,7 @@
         <v>63</v>
       </c>
       <c r="C819" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D819" t="s">
         <v>25</v>
@@ -28035,7 +28029,7 @@
         <v>63</v>
       </c>
       <c r="C820" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D820" t="s">
         <v>25</v>
@@ -28065,7 +28059,7 @@
         <v>63</v>
       </c>
       <c r="C821" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D821" t="s">
         <v>25</v>
@@ -28095,7 +28089,7 @@
         <v>63</v>
       </c>
       <c r="C822" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D822" t="s">
         <v>25</v>
@@ -28125,7 +28119,7 @@
         <v>63</v>
       </c>
       <c r="C823" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D823" t="s">
         <v>25</v>
@@ -28155,7 +28149,7 @@
         <v>63</v>
       </c>
       <c r="C824" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D824" t="s">
         <v>25</v>
@@ -28185,7 +28179,7 @@
         <v>63</v>
       </c>
       <c r="C825" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D825" t="s">
         <v>25</v>
@@ -28215,7 +28209,7 @@
         <v>63</v>
       </c>
       <c r="C826" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D826" t="s">
         <v>25</v>
@@ -28245,7 +28239,7 @@
         <v>63</v>
       </c>
       <c r="C827" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D827" t="s">
         <v>26</v>
@@ -28275,7 +28269,7 @@
         <v>63</v>
       </c>
       <c r="C828" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D828" t="s">
         <v>26</v>
@@ -28305,7 +28299,7 @@
         <v>63</v>
       </c>
       <c r="C829" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D829" t="s">
         <v>26</v>
@@ -28335,7 +28329,7 @@
         <v>63</v>
       </c>
       <c r="C830" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D830" t="s">
         <v>26</v>
@@ -28365,7 +28359,7 @@
         <v>63</v>
       </c>
       <c r="C831" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D831" t="s">
         <v>26</v>
@@ -28395,7 +28389,7 @@
         <v>63</v>
       </c>
       <c r="C832" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D832" t="s">
         <v>26</v>
@@ -28425,7 +28419,7 @@
         <v>63</v>
       </c>
       <c r="C833" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D833" t="s">
         <v>26</v>
@@ -28455,7 +28449,7 @@
         <v>63</v>
       </c>
       <c r="C834" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D834" t="s">
         <v>26</v>
@@ -28485,7 +28479,7 @@
         <v>63</v>
       </c>
       <c r="C835" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D835" t="s">
         <v>26</v>
@@ -28515,7 +28509,7 @@
         <v>63</v>
       </c>
       <c r="C836" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D836" t="s">
         <v>26</v>
@@ -28545,7 +28539,7 @@
         <v>63</v>
       </c>
       <c r="C837" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D837" t="s">
         <v>26</v>
@@ -28575,7 +28569,7 @@
         <v>63</v>
       </c>
       <c r="C838" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D838" t="s">
         <v>26</v>
@@ -28605,7 +28599,7 @@
         <v>63</v>
       </c>
       <c r="C839" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D839" t="s">
         <v>26</v>
@@ -28635,7 +28629,7 @@
         <v>63</v>
       </c>
       <c r="C840" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D840" t="s">
         <v>26</v>
@@ -28665,7 +28659,7 @@
         <v>63</v>
       </c>
       <c r="C841" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D841" t="s">
         <v>26</v>
@@ -28785,7 +28779,7 @@
         <v>63</v>
       </c>
       <c r="C845" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D845" t="s">
         <v>26</v>
@@ -30255,7 +30249,7 @@
         <v>63</v>
       </c>
       <c r="C894" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D894" t="s">
         <v>25</v>
@@ -30285,7 +30279,7 @@
         <v>63</v>
       </c>
       <c r="C895" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D895" t="s">
         <v>26</v>
@@ -30495,7 +30489,7 @@
         <v>63</v>
       </c>
       <c r="C902" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D902" t="s">
         <v>25</v>
@@ -30525,7 +30519,7 @@
         <v>63</v>
       </c>
       <c r="C903" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D903" t="s">
         <v>26</v>
@@ -31160,7 +31154,7 @@
       <c r="D924" t="s">
         <v>25</v>
       </c>
-      <c r="E924">
+      <c r="E924" s="2">
         <v>1</v>
       </c>
       <c r="F924" t="s">
@@ -31190,7 +31184,7 @@
       <c r="D925" t="s">
         <v>25</v>
       </c>
-      <c r="E925">
+      <c r="E925" s="2">
         <v>1</v>
       </c>
       <c r="F925" t="s">
@@ -31220,7 +31214,7 @@
       <c r="D926" t="s">
         <v>25</v>
       </c>
-      <c r="E926">
+      <c r="E926" s="2">
         <v>1</v>
       </c>
       <c r="F926" t="s">
@@ -31250,7 +31244,7 @@
       <c r="D927" t="s">
         <v>25</v>
       </c>
-      <c r="E927">
+      <c r="E927" s="2">
         <v>1</v>
       </c>
       <c r="F927" t="s">
@@ -31280,7 +31274,7 @@
       <c r="D928" t="s">
         <v>25</v>
       </c>
-      <c r="E928">
+      <c r="E928" s="2">
         <v>1</v>
       </c>
       <c r="F928" t="s">
@@ -31310,7 +31304,7 @@
       <c r="D929" t="s">
         <v>25</v>
       </c>
-      <c r="E929">
+      <c r="E929" s="2">
         <v>1</v>
       </c>
       <c r="F929" t="s">
@@ -31340,7 +31334,7 @@
       <c r="D930" t="s">
         <v>25</v>
       </c>
-      <c r="E930">
+      <c r="E930" s="2">
         <v>1</v>
       </c>
       <c r="F930" t="s">
@@ -31370,7 +31364,7 @@
       <c r="D931" t="s">
         <v>25</v>
       </c>
-      <c r="E931">
+      <c r="E931" s="2">
         <v>1</v>
       </c>
       <c r="F931" t="s">
@@ -31400,7 +31394,7 @@
       <c r="D932" t="s">
         <v>25</v>
       </c>
-      <c r="E932">
+      <c r="E932" s="2">
         <v>1</v>
       </c>
       <c r="F932" t="s">
@@ -31430,7 +31424,7 @@
       <c r="D933" t="s">
         <v>25</v>
       </c>
-      <c r="E933">
+      <c r="E933" s="2">
         <v>1</v>
       </c>
       <c r="F933" t="s">
@@ -31460,7 +31454,7 @@
       <c r="D934" t="s">
         <v>25</v>
       </c>
-      <c r="E934">
+      <c r="E934" s="2">
         <v>1</v>
       </c>
       <c r="F934" t="s">
@@ -31490,7 +31484,7 @@
       <c r="D935" t="s">
         <v>25</v>
       </c>
-      <c r="E935">
+      <c r="E935" s="2">
         <v>1</v>
       </c>
       <c r="F935" t="s">
@@ -31520,7 +31514,7 @@
       <c r="D936" t="s">
         <v>25</v>
       </c>
-      <c r="E936">
+      <c r="E936" s="2">
         <v>1</v>
       </c>
       <c r="F936" t="s">
@@ -31550,7 +31544,7 @@
       <c r="D937" t="s">
         <v>26</v>
       </c>
-      <c r="E937">
+      <c r="E937" s="2">
         <v>1</v>
       </c>
       <c r="F937" t="s">
@@ -31580,7 +31574,7 @@
       <c r="D938" t="s">
         <v>26</v>
       </c>
-      <c r="E938">
+      <c r="E938" s="2">
         <v>1</v>
       </c>
       <c r="F938" t="s">
@@ -31610,7 +31604,7 @@
       <c r="D939" t="s">
         <v>26</v>
       </c>
-      <c r="E939">
+      <c r="E939" s="2">
         <v>1</v>
       </c>
       <c r="F939" t="s">
@@ -31640,7 +31634,7 @@
       <c r="D940" t="s">
         <v>26</v>
       </c>
-      <c r="E940">
+      <c r="E940" s="2">
         <v>1</v>
       </c>
       <c r="F940" t="s">
@@ -31670,7 +31664,7 @@
       <c r="D941" t="s">
         <v>26</v>
       </c>
-      <c r="E941">
+      <c r="E941" s="2">
         <v>1</v>
       </c>
       <c r="F941" t="s">
@@ -31700,7 +31694,7 @@
       <c r="D942" t="s">
         <v>26</v>
       </c>
-      <c r="E942">
+      <c r="E942" s="2">
         <v>1</v>
       </c>
       <c r="F942" t="s">
@@ -31730,7 +31724,7 @@
       <c r="D943" t="s">
         <v>26</v>
       </c>
-      <c r="E943">
+      <c r="E943" s="2">
         <v>1</v>
       </c>
       <c r="F943" t="s">
@@ -31760,7 +31754,7 @@
       <c r="D944" t="s">
         <v>26</v>
       </c>
-      <c r="E944">
+      <c r="E944" s="2">
         <v>1</v>
       </c>
       <c r="F944" t="s">
@@ -31790,7 +31784,7 @@
       <c r="D945" t="s">
         <v>26</v>
       </c>
-      <c r="E945">
+      <c r="E945" s="2">
         <v>1</v>
       </c>
       <c r="F945" t="s">
@@ -31820,7 +31814,7 @@
       <c r="D946" t="s">
         <v>26</v>
       </c>
-      <c r="E946">
+      <c r="E946" s="2">
         <v>1</v>
       </c>
       <c r="F946" t="s">
@@ -31850,7 +31844,7 @@
       <c r="D947" t="s">
         <v>26</v>
       </c>
-      <c r="E947">
+      <c r="E947" s="2">
         <v>1</v>
       </c>
       <c r="F947" t="s">
@@ -31880,7 +31874,7 @@
       <c r="D948" t="s">
         <v>26</v>
       </c>
-      <c r="E948">
+      <c r="E948" s="2">
         <v>1</v>
       </c>
       <c r="F948" t="s">
@@ -31910,7 +31904,7 @@
       <c r="D949" t="s">
         <v>26</v>
       </c>
-      <c r="E949">
+      <c r="E949" s="2">
         <v>1</v>
       </c>
       <c r="F949" t="s">
@@ -31940,7 +31934,7 @@
       <c r="D950" t="s">
         <v>26</v>
       </c>
-      <c r="E950">
+      <c r="E950" s="2">
         <v>1</v>
       </c>
       <c r="F950" t="s">
@@ -31970,7 +31964,7 @@
       <c r="D951" t="s">
         <v>26</v>
       </c>
-      <c r="E951">
+      <c r="E951" s="2">
         <v>1</v>
       </c>
       <c r="F951" t="s">
@@ -32000,7 +31994,7 @@
       <c r="D952" t="s">
         <v>26</v>
       </c>
-      <c r="E952">
+      <c r="E952" s="2">
         <v>1</v>
       </c>
       <c r="F952" t="s">
@@ -32030,7 +32024,7 @@
       <c r="D953" t="s">
         <v>26</v>
       </c>
-      <c r="E953">
+      <c r="E953" s="2">
         <v>1</v>
       </c>
       <c r="F953" t="s">
@@ -32060,7 +32054,7 @@
       <c r="D954" t="s">
         <v>26</v>
       </c>
-      <c r="E954">
+      <c r="E954" s="2">
         <v>1</v>
       </c>
       <c r="F954" t="s">
@@ -32090,7 +32084,7 @@
       <c r="D955" t="s">
         <v>26</v>
       </c>
-      <c r="E955">
+      <c r="E955" s="2">
         <v>1</v>
       </c>
       <c r="F955" t="s">
@@ -32120,7 +32114,7 @@
       <c r="D956" t="s">
         <v>25</v>
       </c>
-      <c r="E956">
+      <c r="E956" s="2">
         <v>2</v>
       </c>
       <c r="F956" t="s">
@@ -32150,7 +32144,7 @@
       <c r="D957" t="s">
         <v>25</v>
       </c>
-      <c r="E957">
+      <c r="E957" s="2">
         <v>2</v>
       </c>
       <c r="F957" t="s">
@@ -32180,7 +32174,7 @@
       <c r="D958" t="s">
         <v>25</v>
       </c>
-      <c r="E958">
+      <c r="E958" s="2">
         <v>2</v>
       </c>
       <c r="F958" t="s">
@@ -32210,7 +32204,7 @@
       <c r="D959" t="s">
         <v>25</v>
       </c>
-      <c r="E959">
+      <c r="E959" s="2">
         <v>2</v>
       </c>
       <c r="F959" t="s">
@@ -32240,7 +32234,7 @@
       <c r="D960" t="s">
         <v>25</v>
       </c>
-      <c r="E960">
+      <c r="E960" s="2">
         <v>2</v>
       </c>
       <c r="F960" t="s">
@@ -32270,7 +32264,7 @@
       <c r="D961" t="s">
         <v>25</v>
       </c>
-      <c r="E961">
+      <c r="E961" s="2">
         <v>2</v>
       </c>
       <c r="F961" t="s">
@@ -32300,7 +32294,7 @@
       <c r="D962" t="s">
         <v>25</v>
       </c>
-      <c r="E962">
+      <c r="E962" s="2">
         <v>2</v>
       </c>
       <c r="F962" t="s">
@@ -32330,7 +32324,7 @@
       <c r="D963" t="s">
         <v>25</v>
       </c>
-      <c r="E963">
+      <c r="E963" s="2">
         <v>2</v>
       </c>
       <c r="F963" t="s">
@@ -32360,7 +32354,7 @@
       <c r="D964" t="s">
         <v>25</v>
       </c>
-      <c r="E964">
+      <c r="E964" s="2">
         <v>2</v>
       </c>
       <c r="F964" t="s">
@@ -32390,7 +32384,7 @@
       <c r="D965" t="s">
         <v>25</v>
       </c>
-      <c r="E965">
+      <c r="E965" s="2">
         <v>2</v>
       </c>
       <c r="F965" t="s">
@@ -32420,7 +32414,7 @@
       <c r="D966" t="s">
         <v>25</v>
       </c>
-      <c r="E966">
+      <c r="E966" s="2">
         <v>2</v>
       </c>
       <c r="F966" t="s">
@@ -32450,7 +32444,7 @@
       <c r="D967" t="s">
         <v>25</v>
       </c>
-      <c r="E967">
+      <c r="E967" s="2">
         <v>2</v>
       </c>
       <c r="F967" t="s">
@@ -32480,7 +32474,7 @@
       <c r="D968" t="s">
         <v>25</v>
       </c>
-      <c r="E968">
+      <c r="E968" s="2">
         <v>2</v>
       </c>
       <c r="F968" t="s">
@@ -32510,7 +32504,7 @@
       <c r="D969" t="s">
         <v>25</v>
       </c>
-      <c r="E969">
+      <c r="E969" s="2">
         <v>2</v>
       </c>
       <c r="F969" t="s">
@@ -32540,7 +32534,7 @@
       <c r="D970" t="s">
         <v>26</v>
       </c>
-      <c r="E970">
+      <c r="E970" s="2">
         <v>2</v>
       </c>
       <c r="F970" t="s">
@@ -32570,7 +32564,7 @@
       <c r="D971" t="s">
         <v>26</v>
       </c>
-      <c r="E971">
+      <c r="E971" s="2">
         <v>2</v>
       </c>
       <c r="F971" t="s">
@@ -32600,7 +32594,7 @@
       <c r="D972" t="s">
         <v>26</v>
       </c>
-      <c r="E972">
+      <c r="E972" s="2">
         <v>2</v>
       </c>
       <c r="F972" t="s">
@@ -32630,7 +32624,7 @@
       <c r="D973" t="s">
         <v>26</v>
       </c>
-      <c r="E973">
+      <c r="E973" s="2">
         <v>2</v>
       </c>
       <c r="F973" t="s">
@@ -32660,7 +32654,7 @@
       <c r="D974" t="s">
         <v>26</v>
       </c>
-      <c r="E974">
+      <c r="E974" s="2">
         <v>2</v>
       </c>
       <c r="F974" t="s">
@@ -32690,7 +32684,7 @@
       <c r="D975" t="s">
         <v>26</v>
       </c>
-      <c r="E975">
+      <c r="E975" s="2">
         <v>2</v>
       </c>
       <c r="F975" t="s">
@@ -32720,7 +32714,7 @@
       <c r="D976" t="s">
         <v>26</v>
       </c>
-      <c r="E976">
+      <c r="E976" s="2">
         <v>2</v>
       </c>
       <c r="F976" t="s">
@@ -32750,7 +32744,7 @@
       <c r="D977" t="s">
         <v>26</v>
       </c>
-      <c r="E977">
+      <c r="E977" s="2">
         <v>2</v>
       </c>
       <c r="F977" t="s">
@@ -32780,7 +32774,7 @@
       <c r="D978" t="s">
         <v>26</v>
       </c>
-      <c r="E978">
+      <c r="E978" s="2">
         <v>2</v>
       </c>
       <c r="F978" t="s">
@@ -32810,7 +32804,7 @@
       <c r="D979" t="s">
         <v>26</v>
       </c>
-      <c r="E979">
+      <c r="E979" s="2">
         <v>2</v>
       </c>
       <c r="F979" t="s">
@@ -32840,7 +32834,7 @@
       <c r="D980" t="s">
         <v>26</v>
       </c>
-      <c r="E980">
+      <c r="E980" s="2">
         <v>2</v>
       </c>
       <c r="F980" t="s">
@@ -32870,7 +32864,7 @@
       <c r="D981" t="s">
         <v>26</v>
       </c>
-      <c r="E981">
+      <c r="E981" s="2">
         <v>2</v>
       </c>
       <c r="F981" t="s">
@@ -32900,8 +32894,8 @@
       <c r="D982" t="s">
         <v>25</v>
       </c>
-      <c r="E982" t="s">
-        <v>115</v>
+      <c r="E982" s="2">
+        <v>2</v>
       </c>
       <c r="F982" t="s">
         <v>67</v>
@@ -32931,8 +32925,8 @@
       <c r="D983" t="s">
         <v>26</v>
       </c>
-      <c r="E983" t="s">
-        <v>115</v>
+      <c r="E983" s="2">
+        <v>2</v>
       </c>
       <c r="F983" t="s">
         <v>67</v>
@@ -32962,8 +32956,8 @@
       <c r="D984" t="s">
         <v>25</v>
       </c>
-      <c r="E984" t="s">
-        <v>116</v>
+      <c r="E984" s="2">
+        <v>1</v>
       </c>
       <c r="F984" t="s">
         <v>68</v>
@@ -32993,8 +32987,8 @@
       <c r="D985" t="s">
         <v>26</v>
       </c>
-      <c r="E985" t="s">
-        <v>116</v>
+      <c r="E985" s="2">
+        <v>1</v>
       </c>
       <c r="F985" t="s">
         <v>68</v>
@@ -33024,8 +33018,8 @@
       <c r="D986" t="s">
         <v>26</v>
       </c>
-      <c r="E986" t="s">
-        <v>116</v>
+      <c r="E986" s="2">
+        <v>1</v>
       </c>
       <c r="F986" t="s">
         <v>68</v>
@@ -33050,13 +33044,13 @@
         <v>63</v>
       </c>
       <c r="C987" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D987" t="s">
         <v>26</v>
       </c>
-      <c r="E987" t="s">
-        <v>115</v>
+      <c r="E987" s="2">
+        <v>2</v>
       </c>
       <c r="F987" t="s">
         <v>64</v>
@@ -33081,13 +33075,13 @@
         <v>63</v>
       </c>
       <c r="C988" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D988" t="s">
         <v>25</v>
       </c>
-      <c r="E988" t="s">
-        <v>115</v>
+      <c r="E988" s="2">
+        <v>2</v>
       </c>
       <c r="F988" t="s">
         <v>64</v>
@@ -33112,13 +33106,13 @@
         <v>63</v>
       </c>
       <c r="C989" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D989" t="s">
         <v>25</v>
       </c>
-      <c r="E989" t="s">
-        <v>115</v>
+      <c r="E989" s="2">
+        <v>2</v>
       </c>
       <c r="F989" t="s">
         <v>68</v>
@@ -33148,8 +33142,8 @@
       <c r="D990" t="s">
         <v>25</v>
       </c>
-      <c r="E990" t="s">
-        <v>115</v>
+      <c r="E990" s="2">
+        <v>2</v>
       </c>
       <c r="F990" t="s">
         <v>68</v>
@@ -33179,8 +33173,8 @@
       <c r="D991" t="s">
         <v>26</v>
       </c>
-      <c r="E991" t="s">
-        <v>115</v>
+      <c r="E991" s="2">
+        <v>2</v>
       </c>
       <c r="F991" t="s">
         <v>64</v>
@@ -33210,8 +33204,8 @@
       <c r="D992" t="s">
         <v>25</v>
       </c>
-      <c r="E992" t="s">
-        <v>115</v>
+      <c r="E992" s="2">
+        <v>2</v>
       </c>
       <c r="F992" t="s">
         <v>64</v>
@@ -33241,8 +33235,8 @@
       <c r="D993" t="s">
         <v>26</v>
       </c>
-      <c r="E993" t="s">
-        <v>115</v>
+      <c r="E993" s="2">
+        <v>2</v>
       </c>
       <c r="F993" t="s">
         <v>64</v>
@@ -33272,8 +33266,8 @@
       <c r="D994" t="s">
         <v>25</v>
       </c>
-      <c r="E994" t="s">
-        <v>115</v>
+      <c r="E994" s="2">
+        <v>2</v>
       </c>
       <c r="F994" t="s">
         <v>64</v>
@@ -33303,8 +33297,8 @@
       <c r="D995" t="s">
         <v>26</v>
       </c>
-      <c r="E995" t="s">
-        <v>115</v>
+      <c r="E995" s="2">
+        <v>2</v>
       </c>
       <c r="F995" t="s">
         <v>64</v>
@@ -33334,8 +33328,8 @@
       <c r="D996" t="s">
         <v>25</v>
       </c>
-      <c r="E996" t="s">
-        <v>115</v>
+      <c r="E996" s="2">
+        <v>2</v>
       </c>
       <c r="F996" t="s">
         <v>64</v>
@@ -33365,8 +33359,8 @@
       <c r="D997" t="s">
         <v>26</v>
       </c>
-      <c r="E997" t="s">
-        <v>115</v>
+      <c r="E997" s="2">
+        <v>2</v>
       </c>
       <c r="F997" t="s">
         <v>64</v>
@@ -33396,8 +33390,8 @@
       <c r="D998" t="s">
         <v>25</v>
       </c>
-      <c r="E998" t="s">
-        <v>115</v>
+      <c r="E998" s="2">
+        <v>2</v>
       </c>
       <c r="F998" t="s">
         <v>64</v>
@@ -33422,13 +33416,13 @@
         <v>63</v>
       </c>
       <c r="C999" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D999" t="s">
         <v>26</v>
       </c>
-      <c r="E999" t="s">
-        <v>115</v>
+      <c r="E999" s="2">
+        <v>2</v>
       </c>
       <c r="F999" t="s">
         <v>64</v>
@@ -33453,13 +33447,13 @@
         <v>63</v>
       </c>
       <c r="C1000" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D1000" t="s">
         <v>25</v>
       </c>
-      <c r="E1000" t="s">
-        <v>115</v>
+      <c r="E1000" s="2">
+        <v>2</v>
       </c>
       <c r="F1000" t="s">
         <v>64</v>
@@ -33489,8 +33483,8 @@
       <c r="D1001" t="s">
         <v>26</v>
       </c>
-      <c r="E1001" t="s">
-        <v>115</v>
+      <c r="E1001" s="2">
+        <v>2</v>
       </c>
       <c r="F1001" t="s">
         <v>64</v>
@@ -33520,8 +33514,8 @@
       <c r="D1002" t="s">
         <v>25</v>
       </c>
-      <c r="E1002" t="s">
-        <v>115</v>
+      <c r="E1002" s="2">
+        <v>2</v>
       </c>
       <c r="F1002" t="s">
         <v>64</v>
@@ -33551,8 +33545,8 @@
       <c r="D1003" t="s">
         <v>25</v>
       </c>
-      <c r="E1003" t="s">
-        <v>116</v>
+      <c r="E1003" s="2">
+        <v>1</v>
       </c>
       <c r="F1003" t="s">
         <v>69</v>
@@ -33577,13 +33571,13 @@
         <v>63</v>
       </c>
       <c r="C1004" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D1004" t="s">
         <v>25</v>
       </c>
-      <c r="E1004" t="s">
-        <v>116</v>
+      <c r="E1004" s="2">
+        <v>1</v>
       </c>
       <c r="F1004" t="s">
         <v>69</v>
@@ -33608,13 +33602,13 @@
         <v>63</v>
       </c>
       <c r="C1005" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D1005" t="s">
         <v>26</v>
       </c>
-      <c r="E1005" t="s">
-        <v>116</v>
+      <c r="E1005" s="2">
+        <v>1</v>
       </c>
       <c r="F1005" t="s">
         <v>69</v>
@@ -33644,8 +33638,8 @@
       <c r="D1006" t="s">
         <v>25</v>
       </c>
-      <c r="E1006" t="s">
-        <v>116</v>
+      <c r="E1006" s="2">
+        <v>1</v>
       </c>
       <c r="F1006" t="s">
         <v>69</v>
@@ -33675,8 +33669,8 @@
       <c r="D1007" t="s">
         <v>26</v>
       </c>
-      <c r="E1007" t="s">
-        <v>116</v>
+      <c r="E1007" s="2">
+        <v>1</v>
       </c>
       <c r="F1007" t="s">
         <v>69</v>
@@ -33701,13 +33695,13 @@
         <v>63</v>
       </c>
       <c r="C1008" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D1008" t="s">
         <v>25</v>
       </c>
-      <c r="E1008" t="s">
-        <v>116</v>
+      <c r="E1008" s="2">
+        <v>1</v>
       </c>
       <c r="F1008" t="s">
         <v>69</v>
@@ -33732,13 +33726,13 @@
         <v>63</v>
       </c>
       <c r="C1009" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D1009" t="s">
         <v>25</v>
       </c>
-      <c r="E1009" t="s">
-        <v>115</v>
+      <c r="E1009" s="2">
+        <v>2</v>
       </c>
       <c r="F1009" t="s">
         <v>67</v>
@@ -33763,13 +33757,13 @@
         <v>63</v>
       </c>
       <c r="C1010" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D1010" t="s">
         <v>26</v>
       </c>
-      <c r="E1010" t="s">
-        <v>115</v>
+      <c r="E1010" s="2">
+        <v>2</v>
       </c>
       <c r="F1010" t="s">
         <v>67</v>
@@ -33799,8 +33793,8 @@
       <c r="D1011" t="s">
         <v>25</v>
       </c>
-      <c r="E1011" t="s">
-        <v>115</v>
+      <c r="E1011" s="2">
+        <v>2</v>
       </c>
       <c r="F1011" t="s">
         <v>67</v>
@@ -33830,8 +33824,8 @@
       <c r="D1012" t="s">
         <v>25</v>
       </c>
-      <c r="E1012" t="s">
-        <v>115</v>
+      <c r="E1012" s="2">
+        <v>2</v>
       </c>
       <c r="F1012" t="s">
         <v>67</v>
@@ -33861,8 +33855,8 @@
       <c r="D1013" t="s">
         <v>25</v>
       </c>
-      <c r="E1013" t="s">
-        <v>115</v>
+      <c r="E1013" s="2">
+        <v>2</v>
       </c>
       <c r="F1013" t="s">
         <v>68</v>
@@ -33892,8 +33886,8 @@
       <c r="D1014" t="s">
         <v>25</v>
       </c>
-      <c r="E1014" t="s">
-        <v>116</v>
+      <c r="E1014" s="2">
+        <v>1</v>
       </c>
       <c r="F1014" t="s">
         <v>69</v>
@@ -33923,8 +33917,8 @@
       <c r="D1015" t="s">
         <v>26</v>
       </c>
-      <c r="E1015" t="s">
-        <v>116</v>
+      <c r="E1015" s="2">
+        <v>1</v>
       </c>
       <c r="F1015" t="s">
         <v>69</v>
@@ -33954,8 +33948,8 @@
       <c r="D1016" t="s">
         <v>25</v>
       </c>
-      <c r="E1016" t="s">
-        <v>116</v>
+      <c r="E1016" s="2">
+        <v>1</v>
       </c>
       <c r="F1016" t="s">
         <v>69</v>
@@ -33985,8 +33979,8 @@
       <c r="D1017" t="s">
         <v>26</v>
       </c>
-      <c r="E1017" t="s">
-        <v>116</v>
+      <c r="E1017" s="2">
+        <v>1</v>
       </c>
       <c r="F1017" t="s">
         <v>69</v>
@@ -34016,8 +34010,8 @@
       <c r="D1018" t="s">
         <v>25</v>
       </c>
-      <c r="E1018" t="s">
-        <v>116</v>
+      <c r="E1018" s="2">
+        <v>1</v>
       </c>
       <c r="F1018" t="s">
         <v>69</v>
@@ -34047,8 +34041,8 @@
       <c r="D1019" t="s">
         <v>26</v>
       </c>
-      <c r="E1019" t="s">
-        <v>115</v>
+      <c r="E1019" s="2">
+        <v>2</v>
       </c>
       <c r="F1019" t="s">
         <v>68</v>
@@ -34078,8 +34072,8 @@
       <c r="D1020" t="s">
         <v>26</v>
       </c>
-      <c r="E1020" t="s">
-        <v>116</v>
+      <c r="E1020" s="2">
+        <v>1</v>
       </c>
       <c r="F1020" t="s">
         <v>69</v>
@@ -34109,8 +34103,8 @@
       <c r="D1021" t="s">
         <v>26</v>
       </c>
-      <c r="E1021" t="s">
-        <v>115</v>
+      <c r="E1021" s="2">
+        <v>2</v>
       </c>
       <c r="F1021" t="s">
         <v>67</v>
@@ -34140,8 +34134,8 @@
       <c r="D1022" t="s">
         <v>26</v>
       </c>
-      <c r="E1022" t="s">
-        <v>115</v>
+      <c r="E1022" s="2">
+        <v>2</v>
       </c>
       <c r="F1022" t="s">
         <v>67</v>
@@ -34166,13 +34160,13 @@
         <v>63</v>
       </c>
       <c r="C1023" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D1023" t="s">
         <v>25</v>
       </c>
-      <c r="E1023" t="s">
-        <v>116</v>
+      <c r="E1023" s="2">
+        <v>1</v>
       </c>
       <c r="F1023" t="s">
         <v>70</v>
@@ -34202,8 +34196,8 @@
       <c r="D1024" t="s">
         <v>25</v>
       </c>
-      <c r="E1024" t="s">
-        <v>116</v>
+      <c r="E1024" s="2">
+        <v>1</v>
       </c>
       <c r="F1024" t="s">
         <v>70</v>
@@ -34233,8 +34227,8 @@
       <c r="D1025" t="s">
         <v>26</v>
       </c>
-      <c r="E1025" t="s">
-        <v>116</v>
+      <c r="E1025" s="2">
+        <v>1</v>
       </c>
       <c r="F1025" t="s">
         <v>70</v>
@@ -34264,8 +34258,8 @@
       <c r="D1026" t="s">
         <v>25</v>
       </c>
-      <c r="E1026" t="s">
-        <v>116</v>
+      <c r="E1026" s="2">
+        <v>1</v>
       </c>
       <c r="F1026" t="s">
         <v>70</v>
@@ -34295,8 +34289,8 @@
       <c r="D1027" t="s">
         <v>26</v>
       </c>
-      <c r="E1027" t="s">
-        <v>116</v>
+      <c r="E1027" s="2">
+        <v>1</v>
       </c>
       <c r="F1027" t="s">
         <v>70</v>
@@ -34326,8 +34320,8 @@
       <c r="D1028" t="s">
         <v>26</v>
       </c>
-      <c r="E1028" t="s">
-        <v>116</v>
+      <c r="E1028" s="2">
+        <v>1</v>
       </c>
       <c r="F1028" t="s">
         <v>70</v>
@@ -34357,8 +34351,8 @@
       <c r="D1029" t="s">
         <v>25</v>
       </c>
-      <c r="E1029" t="s">
-        <v>116</v>
+      <c r="E1029" s="2">
+        <v>1</v>
       </c>
       <c r="F1029" t="s">
         <v>70</v>
@@ -34383,13 +34377,13 @@
         <v>63</v>
       </c>
       <c r="C1030" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D1030" t="s">
         <v>25</v>
       </c>
-      <c r="E1030" t="s">
-        <v>116</v>
+      <c r="E1030" s="2">
+        <v>1</v>
       </c>
       <c r="F1030" t="s">
         <v>70</v>
@@ -34419,8 +34413,8 @@
       <c r="D1031" t="s">
         <v>25</v>
       </c>
-      <c r="E1031" t="s">
-        <v>116</v>
+      <c r="E1031" s="2">
+        <v>1</v>
       </c>
       <c r="F1031" t="s">
         <v>70</v>
@@ -34450,8 +34444,8 @@
       <c r="D1032" t="s">
         <v>25</v>
       </c>
-      <c r="E1032" t="s">
-        <v>116</v>
+      <c r="E1032" s="2">
+        <v>1</v>
       </c>
       <c r="F1032" t="s">
         <v>70</v>
@@ -34481,8 +34475,8 @@
       <c r="D1033" t="s">
         <v>26</v>
       </c>
-      <c r="E1033" t="s">
-        <v>116</v>
+      <c r="E1033" s="2">
+        <v>1</v>
       </c>
       <c r="F1033" t="s">
         <v>70</v>
@@ -34507,13 +34501,13 @@
         <v>63</v>
       </c>
       <c r="C1034" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D1034" t="s">
         <v>25</v>
       </c>
-      <c r="E1034" t="s">
-        <v>116</v>
+      <c r="E1034" s="2">
+        <v>1</v>
       </c>
       <c r="F1034" t="s">
         <v>71</v>
@@ -34538,13 +34532,13 @@
         <v>63</v>
       </c>
       <c r="C1035" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D1035" t="s">
         <v>25</v>
       </c>
-      <c r="E1035" t="s">
-        <v>115</v>
+      <c r="E1035" s="2">
+        <v>2</v>
       </c>
       <c r="F1035" t="s">
         <v>71</v>
@@ -34574,8 +34568,8 @@
       <c r="D1036" t="s">
         <v>25</v>
       </c>
-      <c r="E1036" t="s">
-        <v>116</v>
+      <c r="E1036" s="2">
+        <v>1</v>
       </c>
       <c r="F1036" t="s">
         <v>71</v>
@@ -34605,8 +34599,8 @@
       <c r="D1037" t="s">
         <v>25</v>
       </c>
-      <c r="E1037" t="s">
-        <v>115</v>
+      <c r="E1037" s="2">
+        <v>2</v>
       </c>
       <c r="F1037" t="s">
         <v>71</v>
@@ -34636,8 +34630,8 @@
       <c r="D1038" t="s">
         <v>25</v>
       </c>
-      <c r="E1038" t="s">
-        <v>116</v>
+      <c r="E1038" s="2">
+        <v>1</v>
       </c>
       <c r="F1038" t="s">
         <v>71</v>
@@ -34667,8 +34661,8 @@
       <c r="D1039" t="s">
         <v>25</v>
       </c>
-      <c r="E1039" t="s">
-        <v>115</v>
+      <c r="E1039" s="2">
+        <v>2</v>
       </c>
       <c r="F1039" t="s">
         <v>71</v>
@@ -34693,13 +34687,13 @@
         <v>63</v>
       </c>
       <c r="C1040" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D1040" t="s">
         <v>25</v>
       </c>
-      <c r="E1040" t="s">
-        <v>116</v>
+      <c r="E1040" s="2">
+        <v>1</v>
       </c>
       <c r="F1040" t="s">
         <v>71</v>
@@ -34724,13 +34718,13 @@
         <v>63</v>
       </c>
       <c r="C1041" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D1041" t="s">
         <v>25</v>
       </c>
-      <c r="E1041" t="s">
-        <v>115</v>
+      <c r="E1041" s="2">
+        <v>2</v>
       </c>
       <c r="F1041" t="s">
         <v>71</v>
@@ -34760,8 +34754,8 @@
       <c r="D1042" t="s">
         <v>25</v>
       </c>
-      <c r="E1042" t="s">
-        <v>116</v>
+      <c r="E1042" s="2">
+        <v>1</v>
       </c>
       <c r="F1042" t="s">
         <v>71</v>
@@ -34791,8 +34785,8 @@
       <c r="D1043" t="s">
         <v>25</v>
       </c>
-      <c r="E1043" t="s">
-        <v>115</v>
+      <c r="E1043" s="2">
+        <v>2</v>
       </c>
       <c r="F1043" t="s">
         <v>71</v>
@@ -34822,8 +34816,8 @@
       <c r="D1044" t="s">
         <v>25</v>
       </c>
-      <c r="E1044" t="s">
-        <v>116</v>
+      <c r="E1044" s="2">
+        <v>1</v>
       </c>
       <c r="F1044" t="s">
         <v>71</v>
@@ -34853,8 +34847,8 @@
       <c r="D1045" t="s">
         <v>25</v>
       </c>
-      <c r="E1045" t="s">
-        <v>115</v>
+      <c r="E1045" s="2">
+        <v>2</v>
       </c>
       <c r="F1045" t="s">
         <v>71</v>
@@ -34884,8 +34878,8 @@
       <c r="D1046" t="s">
         <v>25</v>
       </c>
-      <c r="E1046" t="s">
-        <v>116</v>
+      <c r="E1046" s="2">
+        <v>1</v>
       </c>
       <c r="F1046" t="s">
         <v>71</v>
@@ -34915,8 +34909,8 @@
       <c r="D1047" t="s">
         <v>25</v>
       </c>
-      <c r="E1047" t="s">
-        <v>115</v>
+      <c r="E1047" s="2">
+        <v>2</v>
       </c>
       <c r="F1047" t="s">
         <v>71</v>
@@ -34941,13 +34935,13 @@
         <v>63</v>
       </c>
       <c r="C1048" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D1048" t="s">
         <v>26</v>
       </c>
-      <c r="E1048" t="s">
-        <v>116</v>
+      <c r="E1048" s="2">
+        <v>1</v>
       </c>
       <c r="F1048" t="s">
         <v>72</v>
@@ -34977,8 +34971,8 @@
       <c r="D1049" t="s">
         <v>26</v>
       </c>
-      <c r="E1049" t="s">
-        <v>116</v>
+      <c r="E1049" s="2">
+        <v>1</v>
       </c>
       <c r="F1049" t="s">
         <v>72</v>
@@ -35008,8 +35002,8 @@
       <c r="D1050" t="s">
         <v>25</v>
       </c>
-      <c r="E1050" t="s">
-        <v>115</v>
+      <c r="E1050" s="2">
+        <v>2</v>
       </c>
       <c r="F1050" t="s">
         <v>65</v>
@@ -35039,8 +35033,8 @@
       <c r="D1051" t="s">
         <v>25</v>
       </c>
-      <c r="E1051" t="s">
-        <v>115</v>
+      <c r="E1051" s="2">
+        <v>2</v>
       </c>
       <c r="F1051" t="s">
         <v>65</v>
@@ -35065,13 +35059,13 @@
         <v>63</v>
       </c>
       <c r="C1052" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D1052" t="s">
         <v>25</v>
       </c>
-      <c r="E1052" t="s">
-        <v>115</v>
+      <c r="E1052" s="2">
+        <v>2</v>
       </c>
       <c r="F1052" t="s">
         <v>65</v>
@@ -35101,8 +35095,8 @@
       <c r="D1053" t="s">
         <v>25</v>
       </c>
-      <c r="E1053" t="s">
-        <v>115</v>
+      <c r="E1053" s="2">
+        <v>2</v>
       </c>
       <c r="F1053" t="s">
         <v>65</v>
@@ -35132,8 +35126,8 @@
       <c r="D1054" t="s">
         <v>25</v>
       </c>
-      <c r="E1054" t="s">
-        <v>115</v>
+      <c r="E1054" s="2">
+        <v>2</v>
       </c>
       <c r="F1054" t="s">
         <v>65</v>
@@ -35158,13 +35152,13 @@
         <v>63</v>
       </c>
       <c r="C1055" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D1055" t="s">
         <v>25</v>
       </c>
-      <c r="E1055" t="s">
-        <v>115</v>
+      <c r="E1055" s="2">
+        <v>2</v>
       </c>
       <c r="F1055" t="s">
         <v>65</v>
@@ -35194,8 +35188,8 @@
       <c r="D1056" t="s">
         <v>25</v>
       </c>
-      <c r="E1056" t="s">
-        <v>115</v>
+      <c r="E1056" s="2">
+        <v>2</v>
       </c>
       <c r="F1056" t="s">
         <v>65</v>
@@ -35225,8 +35219,8 @@
       <c r="D1057" t="s">
         <v>25</v>
       </c>
-      <c r="E1057" t="s">
-        <v>115</v>
+      <c r="E1057" s="2">
+        <v>2</v>
       </c>
       <c r="F1057" t="s">
         <v>73</v>
@@ -35256,8 +35250,8 @@
       <c r="D1058" t="s">
         <v>26</v>
       </c>
-      <c r="E1058" t="s">
-        <v>115</v>
+      <c r="E1058" s="2">
+        <v>2</v>
       </c>
       <c r="F1058" t="s">
         <v>73</v>
@@ -35287,8 +35281,8 @@
       <c r="D1059" t="s">
         <v>25</v>
       </c>
-      <c r="E1059" t="s">
-        <v>115</v>
+      <c r="E1059" s="2">
+        <v>2</v>
       </c>
       <c r="F1059" t="s">
         <v>73</v>
@@ -35318,8 +35312,8 @@
       <c r="D1060" t="s">
         <v>25</v>
       </c>
-      <c r="E1060" t="s">
-        <v>115</v>
+      <c r="E1060" s="2">
+        <v>2</v>
       </c>
       <c r="F1060" t="s">
         <v>73</v>
@@ -35349,8 +35343,8 @@
       <c r="D1061" t="s">
         <v>26</v>
       </c>
-      <c r="E1061" t="s">
-        <v>115</v>
+      <c r="E1061" s="2">
+        <v>2</v>
       </c>
       <c r="F1061" t="s">
         <v>73</v>
@@ -35380,8 +35374,8 @@
       <c r="D1062" t="s">
         <v>26</v>
       </c>
-      <c r="E1062" t="s">
-        <v>115</v>
+      <c r="E1062" s="2">
+        <v>2</v>
       </c>
       <c r="F1062" t="s">
         <v>73</v>
@@ -35406,13 +35400,13 @@
         <v>63</v>
       </c>
       <c r="C1063" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D1063" t="s">
         <v>25</v>
       </c>
-      <c r="E1063" t="s">
-        <v>115</v>
+      <c r="E1063" s="2">
+        <v>2</v>
       </c>
       <c r="F1063" t="s">
         <v>73</v>
@@ -35442,8 +35436,8 @@
       <c r="D1064" t="s">
         <v>25</v>
       </c>
-      <c r="E1064" t="s">
-        <v>115</v>
+      <c r="E1064" s="2">
+        <v>2</v>
       </c>
       <c r="F1064" t="s">
         <v>73</v>
@@ -35468,13 +35462,13 @@
         <v>63</v>
       </c>
       <c r="C1065" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D1065" t="s">
         <v>26</v>
       </c>
-      <c r="E1065" t="s">
-        <v>115</v>
+      <c r="E1065" s="2">
+        <v>2</v>
       </c>
       <c r="F1065" t="s">
         <v>73</v>
@@ -35504,8 +35498,8 @@
       <c r="D1066" t="s">
         <v>26</v>
       </c>
-      <c r="E1066" t="s">
-        <v>115</v>
+      <c r="E1066" s="2">
+        <v>2</v>
       </c>
       <c r="F1066" t="s">
         <v>73</v>
@@ -35535,8 +35529,8 @@
       <c r="D1067" t="s">
         <v>25</v>
       </c>
-      <c r="E1067" t="s">
-        <v>115</v>
+      <c r="E1067" s="2">
+        <v>2</v>
       </c>
       <c r="F1067" t="s">
         <v>73</v>
@@ -35566,8 +35560,8 @@
       <c r="D1068" t="s">
         <v>26</v>
       </c>
-      <c r="E1068" t="s">
-        <v>115</v>
+      <c r="E1068" s="2">
+        <v>2</v>
       </c>
       <c r="F1068" t="s">
         <v>73</v>
@@ -35592,13 +35586,13 @@
         <v>63</v>
       </c>
       <c r="C1069" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D1069" t="s">
         <v>25</v>
       </c>
-      <c r="E1069" t="s">
-        <v>115</v>
+      <c r="E1069" s="2">
+        <v>2</v>
       </c>
       <c r="F1069" t="s">
         <v>73</v>
@@ -35623,13 +35617,13 @@
         <v>63</v>
       </c>
       <c r="C1070" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D1070" t="s">
         <v>26</v>
       </c>
-      <c r="E1070" t="s">
-        <v>115</v>
+      <c r="E1070" s="2">
+        <v>2</v>
       </c>
       <c r="F1070" t="s">
         <v>73</v>
@@ -35654,13 +35648,13 @@
         <v>63</v>
       </c>
       <c r="C1071" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D1071" t="s">
         <v>26</v>
       </c>
-      <c r="E1071" t="s">
-        <v>115</v>
+      <c r="E1071" s="2">
+        <v>2</v>
       </c>
       <c r="F1071" t="s">
         <v>74</v>
@@ -35690,8 +35684,8 @@
       <c r="D1072" t="s">
         <v>26</v>
       </c>
-      <c r="E1072" t="s">
-        <v>115</v>
+      <c r="E1072" s="2">
+        <v>2</v>
       </c>
       <c r="F1072" t="s">
         <v>74</v>
@@ -35716,13 +35710,13 @@
         <v>63</v>
       </c>
       <c r="C1073" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D1073" t="s">
         <v>26</v>
       </c>
-      <c r="E1073" t="s">
-        <v>116</v>
+      <c r="E1073" s="2">
+        <v>1</v>
       </c>
       <c r="F1073" t="s">
         <v>71</v>
@@ -35747,13 +35741,13 @@
         <v>63</v>
       </c>
       <c r="C1074" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D1074" t="s">
         <v>26</v>
       </c>
-      <c r="E1074" t="s">
-        <v>115</v>
+      <c r="E1074" s="2">
+        <v>2</v>
       </c>
       <c r="F1074" t="s">
         <v>71</v>
@@ -35783,8 +35777,8 @@
       <c r="D1075" t="s">
         <v>26</v>
       </c>
-      <c r="E1075" t="s">
-        <v>116</v>
+      <c r="E1075" s="2">
+        <v>1</v>
       </c>
       <c r="F1075" t="s">
         <v>71</v>
@@ -35814,8 +35808,8 @@
       <c r="D1076" t="s">
         <v>26</v>
       </c>
-      <c r="E1076" t="s">
-        <v>115</v>
+      <c r="E1076" s="2">
+        <v>2</v>
       </c>
       <c r="F1076" t="s">
         <v>71</v>
@@ -35845,8 +35839,8 @@
       <c r="D1077" t="s">
         <v>26</v>
       </c>
-      <c r="E1077" t="s">
-        <v>116</v>
+      <c r="E1077" s="2">
+        <v>1</v>
       </c>
       <c r="F1077" t="s">
         <v>71</v>
@@ -35876,8 +35870,8 @@
       <c r="D1078" t="s">
         <v>26</v>
       </c>
-      <c r="E1078" t="s">
-        <v>115</v>
+      <c r="E1078" s="2">
+        <v>2</v>
       </c>
       <c r="F1078" t="s">
         <v>71</v>
@@ -35907,8 +35901,8 @@
       <c r="D1079" t="s">
         <v>26</v>
       </c>
-      <c r="E1079" t="s">
-        <v>116</v>
+      <c r="E1079" s="2">
+        <v>1</v>
       </c>
       <c r="F1079" t="s">
         <v>71</v>
@@ -35938,8 +35932,8 @@
       <c r="D1080" t="s">
         <v>26</v>
       </c>
-      <c r="E1080" t="s">
-        <v>115</v>
+      <c r="E1080" s="2">
+        <v>2</v>
       </c>
       <c r="F1080" t="s">
         <v>71</v>
@@ -35964,13 +35958,13 @@
         <v>63</v>
       </c>
       <c r="C1081" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D1081" t="s">
         <v>26</v>
       </c>
-      <c r="E1081" t="s">
-        <v>116</v>
+      <c r="E1081" s="2">
+        <v>1</v>
       </c>
       <c r="F1081" t="s">
         <v>71</v>
@@ -35995,13 +35989,13 @@
         <v>63</v>
       </c>
       <c r="C1082" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D1082" t="s">
         <v>26</v>
       </c>
-      <c r="E1082" t="s">
-        <v>115</v>
+      <c r="E1082" s="2">
+        <v>2</v>
       </c>
       <c r="F1082" t="s">
         <v>71</v>
@@ -36031,8 +36025,8 @@
       <c r="D1083" t="s">
         <v>26</v>
       </c>
-      <c r="E1083" t="s">
-        <v>116</v>
+      <c r="E1083" s="2">
+        <v>1</v>
       </c>
       <c r="F1083" t="s">
         <v>71</v>
@@ -36062,8 +36056,8 @@
       <c r="D1084" t="s">
         <v>26</v>
       </c>
-      <c r="E1084" t="s">
-        <v>115</v>
+      <c r="E1084" s="2">
+        <v>2</v>
       </c>
       <c r="F1084" t="s">
         <v>71</v>
@@ -36093,8 +36087,8 @@
       <c r="D1085" t="s">
         <v>26</v>
       </c>
-      <c r="E1085" t="s">
-        <v>116</v>
+      <c r="E1085" s="2">
+        <v>1</v>
       </c>
       <c r="F1085" t="s">
         <v>71</v>
@@ -36124,8 +36118,8 @@
       <c r="D1086" t="s">
         <v>26</v>
       </c>
-      <c r="E1086" t="s">
-        <v>115</v>
+      <c r="E1086" s="2">
+        <v>2</v>
       </c>
       <c r="F1086" t="s">
         <v>71</v>
@@ -36150,13 +36144,13 @@
         <v>63</v>
       </c>
       <c r="C1087" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D1087" t="s">
         <v>25</v>
       </c>
-      <c r="E1087" t="s">
-        <v>116</v>
+      <c r="E1087" s="2">
+        <v>1</v>
       </c>
       <c r="F1087" t="s">
         <v>75</v>
@@ -36181,13 +36175,13 @@
         <v>63</v>
       </c>
       <c r="C1088" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D1088" t="s">
         <v>26</v>
       </c>
-      <c r="E1088" t="s">
-        <v>116</v>
+      <c r="E1088" s="2">
+        <v>1</v>
       </c>
       <c r="F1088" t="s">
         <v>75</v>
@@ -36217,8 +36211,8 @@
       <c r="D1089" t="s">
         <v>26</v>
       </c>
-      <c r="E1089" t="s">
-        <v>115</v>
+      <c r="E1089" s="2">
+        <v>2</v>
       </c>
       <c r="F1089" t="s">
         <v>65</v>
@@ -36248,8 +36242,8 @@
       <c r="D1090" t="s">
         <v>26</v>
       </c>
-      <c r="E1090" t="s">
-        <v>115</v>
+      <c r="E1090" s="2">
+        <v>2</v>
       </c>
       <c r="F1090" t="s">
         <v>65</v>
@@ -36274,13 +36268,13 @@
         <v>63</v>
       </c>
       <c r="C1091" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D1091" t="s">
         <v>26</v>
       </c>
-      <c r="E1091" t="s">
-        <v>115</v>
+      <c r="E1091" s="2">
+        <v>2</v>
       </c>
       <c r="F1091" t="s">
         <v>65</v>
@@ -36310,8 +36304,8 @@
       <c r="D1092" t="s">
         <v>26</v>
       </c>
-      <c r="E1092" t="s">
-        <v>115</v>
+      <c r="E1092" s="2">
+        <v>2</v>
       </c>
       <c r="F1092" t="s">
         <v>65</v>
@@ -36341,8 +36335,8 @@
       <c r="D1093" t="s">
         <v>26</v>
       </c>
-      <c r="E1093" t="s">
-        <v>115</v>
+      <c r="E1093" s="2">
+        <v>2</v>
       </c>
       <c r="F1093" t="s">
         <v>65</v>
@@ -36367,13 +36361,13 @@
         <v>63</v>
       </c>
       <c r="C1094" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D1094" t="s">
         <v>26</v>
       </c>
-      <c r="E1094" t="s">
-        <v>115</v>
+      <c r="E1094" s="2">
+        <v>2</v>
       </c>
       <c r="F1094" t="s">
         <v>65</v>
@@ -36403,8 +36397,8 @@
       <c r="D1095" t="s">
         <v>26</v>
       </c>
-      <c r="E1095" t="s">
-        <v>115</v>
+      <c r="E1095" s="2">
+        <v>2</v>
       </c>
       <c r="F1095" t="s">
         <v>65</v>
@@ -36434,8 +36428,8 @@
       <c r="D1096" t="s">
         <v>26</v>
       </c>
-      <c r="E1096" t="s">
-        <v>115</v>
+      <c r="E1096" s="2">
+        <v>2</v>
       </c>
       <c r="F1096" t="s">
         <v>76</v>
@@ -36465,8 +36459,8 @@
       <c r="D1097" t="s">
         <v>25</v>
       </c>
-      <c r="E1097" t="s">
-        <v>115</v>
+      <c r="E1097" s="2">
+        <v>2</v>
       </c>
       <c r="F1097" t="s">
         <v>76</v>
@@ -36496,8 +36490,8 @@
       <c r="D1098" t="s">
         <v>25</v>
       </c>
-      <c r="E1098" t="s">
-        <v>115</v>
+      <c r="E1098" s="2">
+        <v>2</v>
       </c>
       <c r="F1098" t="s">
         <v>76</v>
@@ -36527,8 +36521,8 @@
       <c r="D1099" t="s">
         <v>25</v>
       </c>
-      <c r="E1099" t="s">
-        <v>115</v>
+      <c r="E1099" s="2">
+        <v>2</v>
       </c>
       <c r="F1099" t="s">
         <v>76</v>
@@ -36558,8 +36552,8 @@
       <c r="D1100" t="s">
         <v>25</v>
       </c>
-      <c r="E1100" t="s">
-        <v>115</v>
+      <c r="E1100" s="2">
+        <v>2</v>
       </c>
       <c r="F1100" t="s">
         <v>76</v>
@@ -36589,8 +36583,8 @@
       <c r="D1101" t="s">
         <v>26</v>
       </c>
-      <c r="E1101" t="s">
-        <v>115</v>
+      <c r="E1101" s="2">
+        <v>2</v>
       </c>
       <c r="F1101" t="s">
         <v>76</v>
@@ -36620,8 +36614,8 @@
       <c r="D1102" t="s">
         <v>26</v>
       </c>
-      <c r="E1102" t="s">
-        <v>115</v>
+      <c r="E1102" s="2">
+        <v>2</v>
       </c>
       <c r="F1102" t="s">
         <v>76</v>
@@ -36651,8 +36645,8 @@
       <c r="D1103" t="s">
         <v>26</v>
       </c>
-      <c r="E1103" t="s">
-        <v>115</v>
+      <c r="E1103" s="2">
+        <v>2</v>
       </c>
       <c r="F1103" t="s">
         <v>76</v>
@@ -36677,13 +36671,13 @@
         <v>63</v>
       </c>
       <c r="C1104" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D1104" t="s">
         <v>26</v>
       </c>
-      <c r="E1104" t="s">
-        <v>116</v>
+      <c r="E1104" s="2">
+        <v>1</v>
       </c>
       <c r="F1104" t="s">
         <v>77</v>
@@ -36708,13 +36702,13 @@
         <v>63</v>
       </c>
       <c r="C1105" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D1105" t="s">
         <v>25</v>
       </c>
-      <c r="E1105" t="s">
-        <v>116</v>
+      <c r="E1105" s="2">
+        <v>1</v>
       </c>
       <c r="F1105" t="s">
         <v>75</v>
@@ -36739,13 +36733,13 @@
         <v>63</v>
       </c>
       <c r="C1106" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D1106" t="s">
         <v>26</v>
       </c>
-      <c r="E1106" t="s">
-        <v>116</v>
+      <c r="E1106" s="2">
+        <v>1</v>
       </c>
       <c r="F1106" t="s">
         <v>77</v>
@@ -36770,13 +36764,13 @@
         <v>63</v>
       </c>
       <c r="C1107" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D1107" t="s">
         <v>26</v>
       </c>
-      <c r="E1107" t="s">
-        <v>116</v>
+      <c r="E1107" s="2">
+        <v>1</v>
       </c>
       <c r="F1107" t="s">
         <v>75</v>
@@ -36806,8 +36800,8 @@
       <c r="D1108" t="s">
         <v>25</v>
       </c>
-      <c r="E1108" t="s">
-        <v>116</v>
+      <c r="E1108" s="2">
+        <v>1</v>
       </c>
       <c r="F1108" t="s">
         <v>75</v>
@@ -36837,8 +36831,8 @@
       <c r="D1109" t="s">
         <v>26</v>
       </c>
-      <c r="E1109" t="s">
-        <v>116</v>
+      <c r="E1109" s="2">
+        <v>1</v>
       </c>
       <c r="F1109" t="s">
         <v>77</v>
@@ -36868,8 +36862,8 @@
       <c r="D1110" t="s">
         <v>26</v>
       </c>
-      <c r="E1110" t="s">
-        <v>116</v>
+      <c r="E1110" s="2">
+        <v>1</v>
       </c>
       <c r="F1110" t="s">
         <v>75</v>
@@ -36899,8 +36893,8 @@
       <c r="D1111" t="s">
         <v>25</v>
       </c>
-      <c r="E1111" t="s">
-        <v>116</v>
+      <c r="E1111" s="2">
+        <v>1</v>
       </c>
       <c r="F1111" t="s">
         <v>75</v>
@@ -36930,8 +36924,8 @@
       <c r="D1112" t="s">
         <v>26</v>
       </c>
-      <c r="E1112" t="s">
-        <v>116</v>
+      <c r="E1112" s="2">
+        <v>1</v>
       </c>
       <c r="F1112" t="s">
         <v>75</v>
@@ -36961,8 +36955,8 @@
       <c r="D1113" t="s">
         <v>25</v>
       </c>
-      <c r="E1113" t="s">
-        <v>116</v>
+      <c r="E1113" s="2">
+        <v>1</v>
       </c>
       <c r="F1113" t="s">
         <v>75</v>
@@ -36992,8 +36986,8 @@
       <c r="D1114" t="s">
         <v>26</v>
       </c>
-      <c r="E1114" t="s">
-        <v>116</v>
+      <c r="E1114" s="2">
+        <v>1</v>
       </c>
       <c r="F1114" t="s">
         <v>75</v>
@@ -37023,8 +37017,8 @@
       <c r="D1115" t="s">
         <v>26</v>
       </c>
-      <c r="E1115" t="s">
-        <v>116</v>
+      <c r="E1115" s="2">
+        <v>1</v>
       </c>
       <c r="F1115" t="s">
         <v>75</v>
@@ -37054,8 +37048,8 @@
       <c r="D1116" t="s">
         <v>25</v>
       </c>
-      <c r="E1116" t="s">
-        <v>116</v>
+      <c r="E1116" s="2">
+        <v>1</v>
       </c>
       <c r="F1116" t="s">
         <v>75</v>
@@ -37085,8 +37079,8 @@
       <c r="D1117" t="s">
         <v>25</v>
       </c>
-      <c r="E1117" t="s">
-        <v>116</v>
+      <c r="E1117" s="2">
+        <v>1</v>
       </c>
       <c r="F1117" t="s">
         <v>75</v>
@@ -37116,8 +37110,8 @@
       <c r="D1118" t="s">
         <v>26</v>
       </c>
-      <c r="E1118" t="s">
-        <v>116</v>
+      <c r="E1118" s="2">
+        <v>1</v>
       </c>
       <c r="F1118" t="s">
         <v>75</v>
@@ -37147,8 +37141,8 @@
       <c r="D1119" t="s">
         <v>26</v>
       </c>
-      <c r="E1119" t="s">
-        <v>115</v>
+      <c r="E1119" s="2">
+        <v>2</v>
       </c>
       <c r="F1119" t="s">
         <v>78</v>
@@ -37178,8 +37172,8 @@
       <c r="D1120" t="s">
         <v>26</v>
       </c>
-      <c r="E1120" t="s">
-        <v>115</v>
+      <c r="E1120" s="2">
+        <v>2</v>
       </c>
       <c r="F1120" t="s">
         <v>78</v>
@@ -37209,8 +37203,8 @@
       <c r="D1121" t="s">
         <v>26</v>
       </c>
-      <c r="E1121" t="s">
-        <v>115</v>
+      <c r="E1121" s="2">
+        <v>2</v>
       </c>
       <c r="F1121" t="s">
         <v>78</v>
@@ -37240,8 +37234,8 @@
       <c r="D1122" t="s">
         <v>26</v>
       </c>
-      <c r="E1122" t="s">
-        <v>115</v>
+      <c r="E1122" s="2">
+        <v>2</v>
       </c>
       <c r="F1122" t="s">
         <v>78</v>
@@ -37266,13 +37260,13 @@
         <v>63</v>
       </c>
       <c r="C1123" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D1123" t="s">
         <v>26</v>
       </c>
-      <c r="E1123" t="s">
-        <v>115</v>
+      <c r="E1123" s="2">
+        <v>2</v>
       </c>
       <c r="F1123" t="s">
         <v>66</v>
@@ -37302,8 +37296,8 @@
       <c r="D1124" t="s">
         <v>26</v>
       </c>
-      <c r="E1124" t="s">
-        <v>115</v>
+      <c r="E1124" s="2">
+        <v>2</v>
       </c>
       <c r="F1124" t="s">
         <v>66</v>
@@ -37328,13 +37322,13 @@
         <v>63</v>
       </c>
       <c r="C1125" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D1125" t="s">
         <v>25</v>
       </c>
-      <c r="E1125" t="s">
-        <v>116</v>
+      <c r="E1125" s="2">
+        <v>1</v>
       </c>
       <c r="F1125" t="s">
         <v>79</v>
@@ -37359,13 +37353,13 @@
         <v>63</v>
       </c>
       <c r="C1126" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D1126" t="s">
         <v>26</v>
       </c>
-      <c r="E1126" t="s">
-        <v>116</v>
+      <c r="E1126" s="2">
+        <v>1</v>
       </c>
       <c r="F1126" t="s">
         <v>79</v>
@@ -37395,8 +37389,8 @@
       <c r="D1127" t="s">
         <v>25</v>
       </c>
-      <c r="E1127" t="s">
-        <v>116</v>
+      <c r="E1127" s="2">
+        <v>1</v>
       </c>
       <c r="F1127" t="s">
         <v>79</v>
@@ -37426,8 +37420,8 @@
       <c r="D1128" t="s">
         <v>26</v>
       </c>
-      <c r="E1128" t="s">
-        <v>116</v>
+      <c r="E1128" s="2">
+        <v>1</v>
       </c>
       <c r="F1128" t="s">
         <v>79</v>
@@ -37457,8 +37451,8 @@
       <c r="D1129" t="s">
         <v>25</v>
       </c>
-      <c r="E1129" t="s">
-        <v>116</v>
+      <c r="E1129" s="2">
+        <v>1</v>
       </c>
       <c r="F1129" t="s">
         <v>79</v>
@@ -37488,8 +37482,8 @@
       <c r="D1130" t="s">
         <v>26</v>
       </c>
-      <c r="E1130" t="s">
-        <v>116</v>
+      <c r="E1130" s="2">
+        <v>1</v>
       </c>
       <c r="F1130" t="s">
         <v>79</v>
@@ -37514,13 +37508,13 @@
         <v>63</v>
       </c>
       <c r="C1131" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D1131" t="s">
         <v>25</v>
       </c>
-      <c r="E1131" t="s">
-        <v>116</v>
+      <c r="E1131" s="2">
+        <v>1</v>
       </c>
       <c r="F1131" t="s">
         <v>79</v>
@@ -37545,13 +37539,13 @@
         <v>63</v>
       </c>
       <c r="C1132" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D1132" t="s">
         <v>26</v>
       </c>
-      <c r="E1132" t="s">
-        <v>116</v>
+      <c r="E1132" s="2">
+        <v>1</v>
       </c>
       <c r="F1132" t="s">
         <v>79</v>
@@ -37576,13 +37570,13 @@
         <v>63</v>
       </c>
       <c r="C1133" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D1133" t="s">
         <v>25</v>
       </c>
-      <c r="E1133" t="s">
-        <v>115</v>
+      <c r="E1133" s="2">
+        <v>2</v>
       </c>
       <c r="F1133" t="s">
         <v>66</v>
@@ -37612,8 +37606,8 @@
       <c r="D1134" t="s">
         <v>25</v>
       </c>
-      <c r="E1134" t="s">
-        <v>115</v>
+      <c r="E1134" s="2">
+        <v>2</v>
       </c>
       <c r="F1134" t="s">
         <v>66</v>
@@ -37638,13 +37632,13 @@
         <v>63</v>
       </c>
       <c r="C1135" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D1135" t="s">
         <v>26</v>
       </c>
-      <c r="E1135" t="s">
-        <v>115</v>
+      <c r="E1135" s="2">
+        <v>2</v>
       </c>
       <c r="F1135" t="s">
         <v>66</v>
@@ -37674,8 +37668,8 @@
       <c r="D1136" t="s">
         <v>25</v>
       </c>
-      <c r="E1136" t="s">
-        <v>116</v>
+      <c r="E1136" s="2">
+        <v>1</v>
       </c>
       <c r="F1136" t="s">
         <v>79</v>
@@ -37705,8 +37699,8 @@
       <c r="D1137" t="s">
         <v>26</v>
       </c>
-      <c r="E1137" t="s">
-        <v>116</v>
+      <c r="E1137" s="2">
+        <v>1</v>
       </c>
       <c r="F1137" t="s">
         <v>79</v>
@@ -37736,8 +37730,8 @@
       <c r="D1138" t="s">
         <v>25</v>
       </c>
-      <c r="E1138" t="s">
-        <v>116</v>
+      <c r="E1138" s="2">
+        <v>1</v>
       </c>
       <c r="F1138" t="s">
         <v>79</v>
@@ -37767,8 +37761,8 @@
       <c r="D1139" t="s">
         <v>25</v>
       </c>
-      <c r="E1139" t="s">
-        <v>116</v>
+      <c r="E1139" s="2">
+        <v>1</v>
       </c>
       <c r="F1139" t="s">
         <v>79</v>
@@ -37798,8 +37792,8 @@
       <c r="D1140" t="s">
         <v>26</v>
       </c>
-      <c r="E1140" t="s">
-        <v>116</v>
+      <c r="E1140" s="2">
+        <v>1</v>
       </c>
       <c r="F1140" t="s">
         <v>79</v>
@@ -37829,8 +37823,8 @@
       <c r="D1141" t="s">
         <v>26</v>
       </c>
-      <c r="E1141" t="s">
-        <v>116</v>
+      <c r="E1141" s="2">
+        <v>1</v>
       </c>
       <c r="F1141" t="s">
         <v>79</v>
@@ -37855,13 +37849,13 @@
         <v>63</v>
       </c>
       <c r="C1142" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D1142" t="s">
         <v>25</v>
       </c>
-      <c r="E1142" t="s">
-        <v>115</v>
+      <c r="E1142" s="2">
+        <v>2</v>
       </c>
       <c r="F1142" t="s">
         <v>66</v>
@@ -37886,13 +37880,13 @@
         <v>63</v>
       </c>
       <c r="C1143" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D1143" t="s">
         <v>26</v>
       </c>
-      <c r="E1143" t="s">
-        <v>115</v>
+      <c r="E1143" s="2">
+        <v>2</v>
       </c>
       <c r="F1143" t="s">
         <v>80</v>
@@ -37917,13 +37911,13 @@
         <v>63</v>
       </c>
       <c r="C1144" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D1144" t="s">
         <v>26</v>
       </c>
-      <c r="E1144" t="s">
-        <v>115</v>
+      <c r="E1144" s="2">
+        <v>2</v>
       </c>
       <c r="F1144" t="s">
         <v>81</v>
@@ -37948,13 +37942,13 @@
         <v>63</v>
       </c>
       <c r="C1145" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D1145" t="s">
         <v>25</v>
       </c>
-      <c r="E1145" t="s">
-        <v>115</v>
+      <c r="E1145" s="2">
+        <v>2</v>
       </c>
       <c r="F1145" t="s">
         <v>81</v>
@@ -37984,8 +37978,8 @@
       <c r="D1146" t="s">
         <v>26</v>
       </c>
-      <c r="E1146" t="s">
-        <v>115</v>
+      <c r="E1146" s="2">
+        <v>2</v>
       </c>
       <c r="F1146" t="s">
         <v>80</v>
@@ -38010,13 +38004,13 @@
         <v>63</v>
       </c>
       <c r="C1147" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D1147" t="s">
         <v>26</v>
       </c>
-      <c r="E1147" t="s">
-        <v>115</v>
+      <c r="E1147" s="2">
+        <v>2</v>
       </c>
       <c r="F1147" t="s">
         <v>80</v>
@@ -38046,8 +38040,8 @@
       <c r="D1148" t="s">
         <v>26</v>
       </c>
-      <c r="E1148" t="s">
-        <v>115</v>
+      <c r="E1148" s="2">
+        <v>2</v>
       </c>
       <c r="F1148" t="s">
         <v>81</v>
@@ -38077,8 +38071,8 @@
       <c r="D1149" t="s">
         <v>26</v>
       </c>
-      <c r="E1149" t="s">
-        <v>115</v>
+      <c r="E1149" s="2">
+        <v>2</v>
       </c>
       <c r="F1149" t="s">
         <v>81</v>
@@ -38108,8 +38102,8 @@
       <c r="D1150" t="s">
         <v>26</v>
       </c>
-      <c r="E1150" t="s">
-        <v>115</v>
+      <c r="E1150" s="2">
+        <v>2</v>
       </c>
       <c r="F1150" t="s">
         <v>81</v>
@@ -38134,13 +38128,13 @@
         <v>63</v>
       </c>
       <c r="C1151" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D1151" t="s">
         <v>26</v>
       </c>
-      <c r="E1151" t="s">
-        <v>115</v>
+      <c r="E1151" s="2">
+        <v>2</v>
       </c>
       <c r="F1151" t="s">
         <v>81</v>
@@ -38170,8 +38164,8 @@
       <c r="D1152" t="s">
         <v>26</v>
       </c>
-      <c r="E1152" t="s">
-        <v>115</v>
+      <c r="E1152" s="2">
+        <v>2</v>
       </c>
       <c r="F1152" t="s">
         <v>81</v>
@@ -38201,8 +38195,8 @@
       <c r="D1153" t="s">
         <v>26</v>
       </c>
-      <c r="E1153" t="s">
-        <v>115</v>
+      <c r="E1153" s="2">
+        <v>2</v>
       </c>
       <c r="F1153" t="s">
         <v>81</v>
@@ -38232,8 +38226,8 @@
       <c r="D1154" t="s">
         <v>25</v>
       </c>
-      <c r="E1154" t="s">
-        <v>115</v>
+      <c r="E1154" s="2">
+        <v>2</v>
       </c>
       <c r="F1154" t="s">
         <v>81</v>
@@ -38263,8 +38257,8 @@
       <c r="D1155" t="s">
         <v>25</v>
       </c>
-      <c r="E1155" t="s">
-        <v>115</v>
+      <c r="E1155" s="2">
+        <v>2</v>
       </c>
       <c r="F1155" t="s">
         <v>81</v>
@@ -38294,8 +38288,8 @@
       <c r="D1156" t="s">
         <v>25</v>
       </c>
-      <c r="E1156" t="s">
-        <v>115</v>
+      <c r="E1156" s="2">
+        <v>2</v>
       </c>
       <c r="F1156" t="s">
         <v>81</v>
@@ -38325,8 +38319,8 @@
       <c r="D1157" t="s">
         <v>25</v>
       </c>
-      <c r="E1157" t="s">
-        <v>115</v>
+      <c r="E1157" s="2">
+        <v>2</v>
       </c>
       <c r="F1157" t="s">
         <v>81</v>
@@ -38356,8 +38350,8 @@
       <c r="D1158" t="s">
         <v>25</v>
       </c>
-      <c r="E1158" t="s">
-        <v>115</v>
+      <c r="E1158" s="2">
+        <v>2</v>
       </c>
       <c r="F1158" t="s">
         <v>81</v>
@@ -38382,13 +38376,13 @@
         <v>63</v>
       </c>
       <c r="C1159" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D1159" t="s">
         <v>25</v>
       </c>
-      <c r="E1159" t="s">
-        <v>115</v>
+      <c r="E1159" s="2">
+        <v>2</v>
       </c>
       <c r="F1159" t="s">
         <v>81</v>
@@ -38413,13 +38407,13 @@
         <v>63</v>
       </c>
       <c r="C1160" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D1160" t="s">
         <v>26</v>
       </c>
-      <c r="E1160" t="s">
-        <v>116</v>
+      <c r="E1160" s="2">
+        <v>1</v>
       </c>
       <c r="F1160" t="s">
         <v>82</v>
@@ -38449,8 +38443,8 @@
       <c r="D1161" t="s">
         <v>26</v>
       </c>
-      <c r="E1161" t="s">
-        <v>116</v>
+      <c r="E1161" s="2">
+        <v>1</v>
       </c>
       <c r="F1161" t="s">
         <v>82</v>
@@ -38480,8 +38474,8 @@
       <c r="D1162" t="s">
         <v>26</v>
       </c>
-      <c r="E1162" t="s">
-        <v>116</v>
+      <c r="E1162" s="2">
+        <v>1</v>
       </c>
       <c r="F1162" t="s">
         <v>82</v>
@@ -38511,8 +38505,8 @@
       <c r="D1163" t="s">
         <v>26</v>
       </c>
-      <c r="E1163" t="s">
-        <v>116</v>
+      <c r="E1163" s="2">
+        <v>1</v>
       </c>
       <c r="F1163" t="s">
         <v>82</v>
@@ -38537,13 +38531,13 @@
         <v>63</v>
       </c>
       <c r="C1164" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D1164" t="s">
         <v>25</v>
       </c>
-      <c r="E1164" t="s">
-        <v>116</v>
+      <c r="E1164" s="2">
+        <v>1</v>
       </c>
       <c r="F1164" t="s">
         <v>82</v>
@@ -38568,13 +38562,13 @@
         <v>63</v>
       </c>
       <c r="C1165" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D1165" t="s">
         <v>26</v>
       </c>
-      <c r="E1165" t="s">
-        <v>116</v>
+      <c r="E1165" s="2">
+        <v>1</v>
       </c>
       <c r="F1165" t="s">
         <v>82</v>
@@ -38604,8 +38598,8 @@
       <c r="D1166" t="s">
         <v>26</v>
       </c>
-      <c r="E1166" t="s">
-        <v>116</v>
+      <c r="E1166" s="2">
+        <v>1</v>
       </c>
       <c r="F1166" t="s">
         <v>82</v>
@@ -38635,8 +38629,8 @@
       <c r="D1167" t="s">
         <v>26</v>
       </c>
-      <c r="E1167" t="s">
-        <v>116</v>
+      <c r="E1167" s="2">
+        <v>1</v>
       </c>
       <c r="F1167" t="s">
         <v>82</v>
@@ -38666,8 +38660,8 @@
       <c r="D1168" t="s">
         <v>26</v>
       </c>
-      <c r="E1168" t="s">
-        <v>116</v>
+      <c r="E1168" s="2">
+        <v>1</v>
       </c>
       <c r="F1168" t="s">
         <v>82</v>
@@ -38692,13 +38686,13 @@
         <v>63</v>
       </c>
       <c r="C1169" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D1169" t="s">
         <v>25</v>
       </c>
-      <c r="E1169" t="s">
-        <v>115</v>
+      <c r="E1169" s="2">
+        <v>2</v>
       </c>
       <c r="F1169" t="s">
         <v>84</v>
@@ -38723,13 +38717,13 @@
         <v>63</v>
       </c>
       <c r="C1170" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D1170" t="s">
         <v>26</v>
       </c>
-      <c r="E1170" t="s">
-        <v>115</v>
+      <c r="E1170" s="2">
+        <v>2</v>
       </c>
       <c r="F1170" t="s">
         <v>84</v>
@@ -38759,8 +38753,8 @@
       <c r="D1171" t="s">
         <v>25</v>
       </c>
-      <c r="E1171" t="s">
-        <v>115</v>
+      <c r="E1171" s="2">
+        <v>2</v>
       </c>
       <c r="F1171" t="s">
         <v>84</v>
@@ -38790,8 +38784,8 @@
       <c r="D1172" t="s">
         <v>26</v>
       </c>
-      <c r="E1172" t="s">
-        <v>115</v>
+      <c r="E1172" s="2">
+        <v>2</v>
       </c>
       <c r="F1172" t="s">
         <v>84</v>
@@ -38821,8 +38815,8 @@
       <c r="D1173" t="s">
         <v>25</v>
       </c>
-      <c r="E1173" t="s">
-        <v>115</v>
+      <c r="E1173" s="2">
+        <v>2</v>
       </c>
       <c r="F1173" t="s">
         <v>84</v>
@@ -38852,8 +38846,8 @@
       <c r="D1174" t="s">
         <v>26</v>
       </c>
-      <c r="E1174" t="s">
-        <v>115</v>
+      <c r="E1174" s="2">
+        <v>2</v>
       </c>
       <c r="F1174" t="s">
         <v>84</v>
@@ -38883,8 +38877,8 @@
       <c r="D1175" t="s">
         <v>25</v>
       </c>
-      <c r="E1175" t="s">
-        <v>115</v>
+      <c r="E1175" s="2">
+        <v>2</v>
       </c>
       <c r="F1175" t="s">
         <v>84</v>
@@ -38914,8 +38908,8 @@
       <c r="D1176" t="s">
         <v>26</v>
       </c>
-      <c r="E1176" t="s">
-        <v>115</v>
+      <c r="E1176" s="2">
+        <v>2</v>
       </c>
       <c r="F1176" t="s">
         <v>84</v>
@@ -38940,13 +38934,13 @@
         <v>63</v>
       </c>
       <c r="C1177" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D1177" t="s">
         <v>25</v>
       </c>
-      <c r="E1177" t="s">
-        <v>115</v>
+      <c r="E1177" s="2">
+        <v>2</v>
       </c>
       <c r="F1177" t="s">
         <v>84</v>
@@ -38971,13 +38965,13 @@
         <v>63</v>
       </c>
       <c r="C1178" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D1178" t="s">
         <v>26</v>
       </c>
-      <c r="E1178" t="s">
-        <v>115</v>
+      <c r="E1178" s="2">
+        <v>2</v>
       </c>
       <c r="F1178" t="s">
         <v>84</v>
@@ -39007,8 +39001,8 @@
       <c r="D1179" t="s">
         <v>26</v>
       </c>
-      <c r="E1179" t="s">
-        <v>115</v>
+      <c r="E1179" s="2">
+        <v>2</v>
       </c>
       <c r="F1179" t="s">
         <v>84</v>
@@ -39038,8 +39032,8 @@
       <c r="D1180" t="s">
         <v>26</v>
       </c>
-      <c r="E1180" t="s">
-        <v>115</v>
+      <c r="E1180" s="2">
+        <v>2</v>
       </c>
       <c r="F1180" t="s">
         <v>84</v>
@@ -39069,8 +39063,8 @@
       <c r="D1181" t="s">
         <v>25</v>
       </c>
-      <c r="E1181" t="s">
-        <v>115</v>
+      <c r="E1181" s="2">
+        <v>2</v>
       </c>
       <c r="F1181" t="s">
         <v>84</v>
@@ -39100,8 +39094,8 @@
       <c r="D1182" t="s">
         <v>25</v>
       </c>
-      <c r="E1182" t="s">
-        <v>115</v>
+      <c r="E1182" s="2">
+        <v>2</v>
       </c>
       <c r="F1182" t="s">
         <v>84</v>
@@ -39126,13 +39120,13 @@
         <v>63</v>
       </c>
       <c r="C1183" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D1183" t="s">
         <v>25</v>
       </c>
-      <c r="E1183" t="s">
-        <v>116</v>
+      <c r="E1183" s="2">
+        <v>1</v>
       </c>
       <c r="F1183" t="s">
         <v>85</v>
@@ -39162,8 +39156,8 @@
       <c r="D1184" t="s">
         <v>25</v>
       </c>
-      <c r="E1184" t="s">
-        <v>116</v>
+      <c r="E1184" s="2">
+        <v>1</v>
       </c>
       <c r="F1184" t="s">
         <v>85</v>
@@ -39188,13 +39182,13 @@
         <v>63</v>
       </c>
       <c r="C1185" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D1185" t="s">
         <v>25</v>
       </c>
-      <c r="E1185" t="s">
-        <v>116</v>
+      <c r="E1185" s="2">
+        <v>1</v>
       </c>
       <c r="F1185" t="s">
         <v>85</v>
@@ -39224,8 +39218,8 @@
       <c r="D1186" t="s">
         <v>25</v>
       </c>
-      <c r="E1186" t="s">
-        <v>116</v>
+      <c r="E1186" s="2">
+        <v>1</v>
       </c>
       <c r="F1186" t="s">
         <v>85</v>
@@ -39255,8 +39249,8 @@
       <c r="D1187" t="s">
         <v>25</v>
       </c>
-      <c r="E1187" t="s">
-        <v>116</v>
+      <c r="E1187" s="2">
+        <v>1</v>
       </c>
       <c r="F1187" t="s">
         <v>85</v>
@@ -39286,8 +39280,8 @@
       <c r="D1188" t="s">
         <v>25</v>
       </c>
-      <c r="E1188" t="s">
-        <v>116</v>
+      <c r="E1188" s="2">
+        <v>1</v>
       </c>
       <c r="F1188" t="s">
         <v>85</v>
@@ -39317,8 +39311,8 @@
       <c r="D1189" t="s">
         <v>25</v>
       </c>
-      <c r="E1189" t="s">
-        <v>116</v>
+      <c r="E1189" s="2">
+        <v>1</v>
       </c>
       <c r="F1189" t="s">
         <v>85</v>
@@ -39343,13 +39337,13 @@
         <v>63</v>
       </c>
       <c r="C1190" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D1190" t="s">
         <v>26</v>
       </c>
-      <c r="E1190" t="s">
-        <v>116</v>
+      <c r="E1190" s="2">
+        <v>1</v>
       </c>
       <c r="F1190" t="s">
         <v>85</v>
@@ -39379,8 +39373,8 @@
       <c r="D1191" t="s">
         <v>26</v>
       </c>
-      <c r="E1191" t="s">
-        <v>116</v>
+      <c r="E1191" s="2">
+        <v>1</v>
       </c>
       <c r="F1191" t="s">
         <v>85</v>
@@ -39405,13 +39399,13 @@
         <v>63</v>
       </c>
       <c r="C1192" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D1192" t="s">
         <v>26</v>
       </c>
-      <c r="E1192" t="s">
-        <v>116</v>
+      <c r="E1192" s="2">
+        <v>1</v>
       </c>
       <c r="F1192" t="s">
         <v>85</v>
@@ -39441,8 +39435,8 @@
       <c r="D1193" t="s">
         <v>26</v>
       </c>
-      <c r="E1193" t="s">
-        <v>116</v>
+      <c r="E1193" s="2">
+        <v>1</v>
       </c>
       <c r="F1193" t="s">
         <v>85</v>
@@ -39472,8 +39466,8 @@
       <c r="D1194" t="s">
         <v>26</v>
       </c>
-      <c r="E1194" t="s">
-        <v>116</v>
+      <c r="E1194" s="2">
+        <v>1</v>
       </c>
       <c r="F1194" t="s">
         <v>85</v>
@@ -39503,8 +39497,8 @@
       <c r="D1195" t="s">
         <v>26</v>
       </c>
-      <c r="E1195" t="s">
-        <v>116</v>
+      <c r="E1195" s="2">
+        <v>1</v>
       </c>
       <c r="F1195" t="s">
         <v>85</v>
@@ -39534,8 +39528,8 @@
       <c r="D1196" t="s">
         <v>25</v>
       </c>
-      <c r="E1196" t="s">
-        <v>116</v>
+      <c r="E1196" s="2">
+        <v>1</v>
       </c>
       <c r="F1196" t="s">
         <v>86</v>
@@ -39560,13 +39554,13 @@
         <v>63</v>
       </c>
       <c r="C1197" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D1197" t="s">
         <v>26</v>
       </c>
-      <c r="E1197" t="s">
-        <v>116</v>
+      <c r="E1197" s="2">
+        <v>1</v>
       </c>
       <c r="F1197" t="s">
         <v>86</v>
@@ -39596,8 +39590,8 @@
       <c r="D1198" t="s">
         <v>26</v>
       </c>
-      <c r="E1198" t="s">
-        <v>116</v>
+      <c r="E1198" s="2">
+        <v>1</v>
       </c>
       <c r="F1198" t="s">
         <v>86</v>
@@ -39627,8 +39621,8 @@
       <c r="D1199" t="s">
         <v>26</v>
       </c>
-      <c r="E1199" t="s">
-        <v>116</v>
+      <c r="E1199" s="2">
+        <v>1</v>
       </c>
       <c r="F1199" t="s">
         <v>86</v>
@@ -39658,8 +39652,8 @@
       <c r="D1200" t="s">
         <v>25</v>
       </c>
-      <c r="E1200" t="s">
-        <v>116</v>
+      <c r="E1200" s="2">
+        <v>1</v>
       </c>
       <c r="F1200" t="s">
         <v>86</v>
@@ -39689,8 +39683,8 @@
       <c r="D1201" t="s">
         <v>25</v>
       </c>
-      <c r="E1201" t="s">
-        <v>116</v>
+      <c r="E1201" s="2">
+        <v>1</v>
       </c>
       <c r="F1201" t="s">
         <v>86</v>
@@ -39720,8 +39714,8 @@
       <c r="D1202" t="s">
         <v>25</v>
       </c>
-      <c r="E1202" t="s">
-        <v>116</v>
+      <c r="E1202" s="2">
+        <v>1</v>
       </c>
       <c r="F1202" t="s">
         <v>87</v>
@@ -39746,13 +39740,13 @@
         <v>63</v>
       </c>
       <c r="C1203" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D1203" t="s">
         <v>26</v>
       </c>
-      <c r="E1203" t="s">
-        <v>116</v>
+      <c r="E1203" s="2">
+        <v>1</v>
       </c>
       <c r="F1203" t="s">
         <v>87</v>
@@ -39782,8 +39776,8 @@
       <c r="D1204" t="s">
         <v>26</v>
       </c>
-      <c r="E1204" t="s">
-        <v>116</v>
+      <c r="E1204" s="2">
+        <v>1</v>
       </c>
       <c r="F1204" t="s">
         <v>87</v>
@@ -39813,8 +39807,8 @@
       <c r="D1205" t="s">
         <v>26</v>
       </c>
-      <c r="E1205" t="s">
-        <v>116</v>
+      <c r="E1205" s="2">
+        <v>1</v>
       </c>
       <c r="F1205" t="s">
         <v>87</v>
@@ -39844,8 +39838,8 @@
       <c r="D1206" t="s">
         <v>25</v>
       </c>
-      <c r="E1206" t="s">
-        <v>116</v>
+      <c r="E1206" s="2">
+        <v>1</v>
       </c>
       <c r="F1206" t="s">
         <v>87</v>
@@ -39875,8 +39869,8 @@
       <c r="D1207" t="s">
         <v>25</v>
       </c>
-      <c r="E1207" t="s">
-        <v>116</v>
+      <c r="E1207" s="2">
+        <v>1</v>
       </c>
       <c r="F1207" t="s">
         <v>87</v>
@@ -39901,13 +39895,13 @@
         <v>63</v>
       </c>
       <c r="C1208" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D1208" t="s">
         <v>25</v>
       </c>
-      <c r="E1208" t="s">
-        <v>116</v>
+      <c r="E1208" s="2">
+        <v>1</v>
       </c>
       <c r="F1208" t="s">
         <v>86</v>
@@ -39932,13 +39926,13 @@
         <v>63</v>
       </c>
       <c r="C1209" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D1209" t="s">
         <v>26</v>
       </c>
-      <c r="E1209" t="s">
-        <v>116</v>
+      <c r="E1209" s="2">
+        <v>1</v>
       </c>
       <c r="F1209" t="s">
         <v>86</v>
@@ -39968,8 +39962,8 @@
       <c r="D1210" t="s">
         <v>25</v>
       </c>
-      <c r="E1210" t="s">
-        <v>116</v>
+      <c r="E1210" s="2">
+        <v>1</v>
       </c>
       <c r="F1210" t="s">
         <v>86</v>
@@ -39999,8 +39993,8 @@
       <c r="D1211" t="s">
         <v>26</v>
       </c>
-      <c r="E1211" t="s">
-        <v>116</v>
+      <c r="E1211" s="2">
+        <v>1</v>
       </c>
       <c r="F1211" t="s">
         <v>86</v>
@@ -40030,8 +40024,8 @@
       <c r="D1212" t="s">
         <v>25</v>
       </c>
-      <c r="E1212" t="s">
-        <v>116</v>
+      <c r="E1212" s="2">
+        <v>1</v>
       </c>
       <c r="F1212" t="s">
         <v>86</v>
@@ -40061,8 +40055,8 @@
       <c r="D1213" t="s">
         <v>26</v>
       </c>
-      <c r="E1213" t="s">
-        <v>116</v>
+      <c r="E1213" s="2">
+        <v>1</v>
       </c>
       <c r="F1213" t="s">
         <v>86</v>
@@ -40092,8 +40086,8 @@
       <c r="D1214" t="s">
         <v>26</v>
       </c>
-      <c r="E1214" t="s">
-        <v>116</v>
+      <c r="E1214" s="2">
+        <v>1</v>
       </c>
       <c r="F1214" t="s">
         <v>86</v>
@@ -40118,13 +40112,13 @@
         <v>63</v>
       </c>
       <c r="C1215" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D1215" t="s">
         <v>25</v>
       </c>
-      <c r="E1215" t="s">
-        <v>116</v>
+      <c r="E1215" s="2">
+        <v>1</v>
       </c>
       <c r="F1215" t="s">
         <v>86</v>
@@ -40149,13 +40143,13 @@
         <v>63</v>
       </c>
       <c r="C1216" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D1216" t="s">
         <v>25</v>
       </c>
-      <c r="E1216" t="s">
-        <v>116</v>
+      <c r="E1216" s="2">
+        <v>1</v>
       </c>
       <c r="F1216" t="s">
         <v>87</v>
@@ -40180,13 +40174,13 @@
         <v>63</v>
       </c>
       <c r="C1217" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D1217" t="s">
         <v>26</v>
       </c>
-      <c r="E1217" t="s">
-        <v>116</v>
+      <c r="E1217" s="2">
+        <v>1</v>
       </c>
       <c r="F1217" t="s">
         <v>87</v>
@@ -40216,8 +40210,8 @@
       <c r="D1218" t="s">
         <v>25</v>
       </c>
-      <c r="E1218" t="s">
-        <v>116</v>
+      <c r="E1218" s="2">
+        <v>1</v>
       </c>
       <c r="F1218" t="s">
         <v>87</v>
@@ -40247,8 +40241,8 @@
       <c r="D1219" t="s">
         <v>26</v>
       </c>
-      <c r="E1219" t="s">
-        <v>116</v>
+      <c r="E1219" s="2">
+        <v>1</v>
       </c>
       <c r="F1219" t="s">
         <v>87</v>
@@ -40278,8 +40272,8 @@
       <c r="D1220" t="s">
         <v>25</v>
       </c>
-      <c r="E1220" t="s">
-        <v>116</v>
+      <c r="E1220" s="2">
+        <v>1</v>
       </c>
       <c r="F1220" t="s">
         <v>87</v>
@@ -40309,8 +40303,8 @@
       <c r="D1221" t="s">
         <v>26</v>
       </c>
-      <c r="E1221" t="s">
-        <v>116</v>
+      <c r="E1221" s="2">
+        <v>1</v>
       </c>
       <c r="F1221" t="s">
         <v>87</v>
@@ -40340,8 +40334,8 @@
       <c r="D1222" t="s">
         <v>26</v>
       </c>
-      <c r="E1222" t="s">
-        <v>116</v>
+      <c r="E1222" s="2">
+        <v>1</v>
       </c>
       <c r="F1222" t="s">
         <v>87</v>
@@ -40366,13 +40360,13 @@
         <v>63</v>
       </c>
       <c r="C1223" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D1223" t="s">
         <v>25</v>
       </c>
-      <c r="E1223" t="s">
-        <v>116</v>
+      <c r="E1223" s="2">
+        <v>1</v>
       </c>
       <c r="F1223" t="s">
         <v>87</v>
@@ -40402,8 +40396,8 @@
       <c r="D1224" t="s">
         <v>26</v>
       </c>
-      <c r="E1224" t="s">
-        <v>116</v>
+      <c r="E1224" s="2">
+        <v>1</v>
       </c>
       <c r="F1224" t="s">
         <v>85</v>

--- a/data/calendario_promocional.xlsx
+++ b/data/calendario_promocional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anheuserbuschinbev-my.sharepoint.com/personal/99823517_ab-inbev_com/Documents/001. Projetos/Streamlit Calendario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="829" documentId="11_F25DC773A252ABDACC1048AAA9DA54025ADE5901" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10A45569-93E2-45F1-9967-242CCC7A29C4}"/>
+  <xr:revisionPtr revIDLastSave="836" documentId="11_F25DC773A252ABDACC1048AAA9DA54025ADE5901" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1675FBE9-651A-47B2-A880-2A330F599CCE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3779,7 +3779,7 @@
         <v>PCP2.png</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
@@ -4379,7 +4379,7 @@
         <v>GCA350.png</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>10</v>
       </c>
@@ -31079,7 +31079,7 @@
         <v>PCP2.png</v>
       </c>
     </row>
-    <row r="922" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A922" s="2" t="s">
         <v>100</v>
       </c>
@@ -31499,7 +31499,7 @@
         <v>GCA350.png</v>
       </c>
     </row>
-    <row r="936" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="936" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A936" s="2" t="s">
         <v>100</v>
       </c>
@@ -33539,7 +33539,7 @@
         <v>AP269.png</v>
       </c>
     </row>
-    <row r="1004" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1004" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1004" s="2" t="s">
         <v>100</v>
       </c>
@@ -33559,17 +33559,17 @@
         <v>69</v>
       </c>
       <c r="G1004">
-        <v>3.09</v>
+        <v>3.19</v>
       </c>
       <c r="H1004">
-        <v>2.79</v>
+        <v>2.99</v>
       </c>
       <c r="I1004" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1004,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="1005" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1005" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1005" s="2" t="s">
         <v>100</v>
       </c>
@@ -33589,10 +33589,10 @@
         <v>69</v>
       </c>
       <c r="G1005">
-        <v>3.09</v>
+        <v>3.19</v>
       </c>
       <c r="H1005">
-        <v>2.79</v>
+        <v>2.99</v>
       </c>
       <c r="I1005" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1005,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -33659,7 +33659,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="1008" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1008" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1008" s="2" t="s">
         <v>100</v>
       </c>
@@ -33679,10 +33679,10 @@
         <v>69</v>
       </c>
       <c r="G1008">
-        <v>3.09</v>
+        <v>3.19</v>
       </c>
       <c r="H1008">
-        <v>2.79</v>
+        <v>2.99</v>
       </c>
       <c r="I1008" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1008,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -33719,7 +33719,7 @@
         <v>AP269.png</v>
       </c>
     </row>
-    <row r="1010" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1010" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1010" s="2" t="s">
         <v>100</v>
       </c>
@@ -33739,10 +33739,10 @@
         <v>69</v>
       </c>
       <c r="G1010">
-        <v>3.09</v>
+        <v>3.19</v>
       </c>
       <c r="H1010">
-        <v>2.79</v>
+        <v>2.99</v>
       </c>
       <c r="I1010" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1010,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -39601,9 +39601,20 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:I1205" xr:uid="{34B2C8DF-4561-40B2-8E7C-6CD69559B9AE}">
-    <filterColumn colId="8">
+    <filterColumn colId="0">
       <filters>
-        <filter val="BAREP2.png"/>
+        <filter val="Outubro"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="2">
+      <filters>
+        <filter val="AC"/>
+        <filter val="RO"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="5">
+      <filters>
+        <filter val="BC 269"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/data/calendario_promocional.xlsx
+++ b/data/calendario_promocional.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anheuserbuschinbev-my.sharepoint.com/personal/99823517_ab-inbev_com/Documents/001. Projetos/Streamlit Calendario/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\99852106\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="836" documentId="11_F25DC773A252ABDACC1048AAA9DA54025ADE5901" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1675FBE9-651A-47B2-A880-2A330F599CCE}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E48E30ED-22CC-4A8C-A749-92C6EADCFC0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DeparaIMG" sheetId="5" r:id="rId1"/>
@@ -33559,7 +33559,7 @@
         <v>69</v>
       </c>
       <c r="G1004">
-        <v>3.19</v>
+        <v>49.99</v>
       </c>
       <c r="H1004">
         <v>2.99</v>
@@ -33589,7 +33589,7 @@
         <v>69</v>
       </c>
       <c r="G1005">
-        <v>3.19</v>
+        <v>49.99</v>
       </c>
       <c r="H1005">
         <v>2.99</v>
@@ -33679,7 +33679,7 @@
         <v>69</v>
       </c>
       <c r="G1008">
-        <v>3.19</v>
+        <v>49.99</v>
       </c>
       <c r="H1008">
         <v>2.99</v>
@@ -33739,7 +33739,7 @@
         <v>69</v>
       </c>
       <c r="G1010">
-        <v>3.19</v>
+        <v>49.99</v>
       </c>
       <c r="H1010">
         <v>2.99</v>

--- a/data/calendario_promocional.xlsx
+++ b/data/calendario_promocional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\99852106\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E48E30ED-22CC-4A8C-A749-92C6EADCFC0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB2072ED-86CE-4DD7-8F90-044E4D8FB7F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DeparaIMG" sheetId="5" r:id="rId1"/>
@@ -33559,7 +33559,7 @@
         <v>69</v>
       </c>
       <c r="G1004">
-        <v>49.99</v>
+        <v>3.19</v>
       </c>
       <c r="H1004">
         <v>2.99</v>
@@ -33589,7 +33589,7 @@
         <v>69</v>
       </c>
       <c r="G1005">
-        <v>49.99</v>
+        <v>3.19</v>
       </c>
       <c r="H1005">
         <v>2.99</v>
@@ -33679,7 +33679,7 @@
         <v>69</v>
       </c>
       <c r="G1008">
-        <v>49.99</v>
+        <v>3.19</v>
       </c>
       <c r="H1008">
         <v>2.99</v>
@@ -33739,7 +33739,7 @@
         <v>69</v>
       </c>
       <c r="G1010">
-        <v>49.99</v>
+        <v>3.19</v>
       </c>
       <c r="H1010">
         <v>2.99</v>
@@ -39626,6 +39626,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C08B3827-EDAF-4453-9F0C-3166EEE86952}">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="8.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">

--- a/data/calendario_promocional.xlsx
+++ b/data/calendario_promocional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anheuserbuschinbev-my.sharepoint.com/personal/99854257_ab-inbev_com/Documents/Pasta H OneDrive/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="107" documentId="13_ncr:1_{A3E51377-40B1-46DE-BFCA-D767C6F94B35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53C7994D-B8F8-48A6-9E42-256214A2E6AD}"/>
+  <xr:revisionPtr revIDLastSave="137" documentId="13_ncr:1_{A3E51377-40B1-46DE-BFCA-D767C6F94B35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B88D479B-BA0F-46B8-B2C2-63EDB27B526C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">CALENDARIO!$A$1:$B$53</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DeparaIMG!$A$1:$D$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">MECANICA!$A$1:$D$49</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">PRODUTOS!$A$1:$I$1208</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">PRODUTOS!$A$1:$I$1209</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6506" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6526" uniqueCount="121">
   <si>
     <t>Data</t>
   </si>
@@ -3534,7 +3534,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34B2C8DF-4561-40B2-8E7C-6CD69559B9AE}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:I1208"/>
+  <dimension ref="A1:I1213"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="20.85546875" customWidth="1"/>
@@ -30450,7 +30450,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="898" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A898" s="2" t="s">
         <v>98</v>
       </c>
@@ -30480,7 +30480,7 @@
         <v>BEATSLT.png</v>
       </c>
     </row>
-    <row r="899" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A899" s="2" t="s">
         <v>98</v>
       </c>
@@ -30510,7 +30510,7 @@
         <v>BEATSLT.png</v>
       </c>
     </row>
-    <row r="900" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A900" s="2" t="s">
         <v>98</v>
       </c>
@@ -30540,7 +30540,7 @@
         <v>BEATSLN.png</v>
       </c>
     </row>
-    <row r="901" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A901" s="2" t="s">
         <v>98</v>
       </c>
@@ -30570,7 +30570,7 @@
         <v>BEATSLN.png</v>
       </c>
     </row>
-    <row r="902" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A902" s="2" t="s">
         <v>98</v>
       </c>
@@ -30600,7 +30600,7 @@
         <v>BEATSLT.png</v>
       </c>
     </row>
-    <row r="903" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A903" s="2" t="s">
         <v>98</v>
       </c>
@@ -30630,7 +30630,7 @@
         <v>BEATSLT.png</v>
       </c>
     </row>
-    <row r="904" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A904" s="2" t="s">
         <v>98</v>
       </c>
@@ -30660,7 +30660,7 @@
         <v>BEATSLN.png</v>
       </c>
     </row>
-    <row r="905" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A905" s="2" t="s">
         <v>98</v>
       </c>
@@ -30690,7 +30690,7 @@
         <v>BEATSLN.png</v>
       </c>
     </row>
-    <row r="906" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A906" s="2" t="s">
         <v>98</v>
       </c>
@@ -30720,7 +30720,7 @@
         <v>FF350.png</v>
       </c>
     </row>
-    <row r="907" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A907" s="2" t="s">
         <v>98</v>
       </c>
@@ -30750,7 +30750,7 @@
         <v>FFLN.png</v>
       </c>
     </row>
-    <row r="908" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A908" s="2" t="s">
         <v>98</v>
       </c>
@@ -30780,7 +30780,7 @@
         <v>FF350.png</v>
       </c>
     </row>
-    <row r="909" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A909" s="2" t="s">
         <v>98</v>
       </c>
@@ -30810,7 +30810,7 @@
         <v>FFLN.png</v>
       </c>
     </row>
-    <row r="910" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A910" s="2" t="s">
         <v>98</v>
       </c>
@@ -30840,7 +30840,7 @@
         <v>FF350.png</v>
       </c>
     </row>
-    <row r="911" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A911" s="2" t="s">
         <v>98</v>
       </c>
@@ -30870,7 +30870,7 @@
         <v>FFLN.png</v>
       </c>
     </row>
-    <row r="912" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A912" s="2" t="s">
         <v>98</v>
       </c>
@@ -30900,7 +30900,7 @@
         <v>FF350.png</v>
       </c>
     </row>
-    <row r="913" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A913" s="2" t="s">
         <v>98</v>
       </c>
@@ -30930,7 +30930,7 @@
         <v>FFLN.png</v>
       </c>
     </row>
-    <row r="914" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A914" s="2" t="s">
         <v>98</v>
       </c>
@@ -30960,7 +30960,7 @@
         <v>GCAP1.png</v>
       </c>
     </row>
-    <row r="915" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A915" s="2" t="s">
         <v>98</v>
       </c>
@@ -30990,7 +30990,7 @@
         <v>GCAP1,5.png</v>
       </c>
     </row>
-    <row r="916" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A916" s="2" t="s">
         <v>98</v>
       </c>
@@ -31020,7 +31020,7 @@
         <v>GCAP1,5.png</v>
       </c>
     </row>
-    <row r="917" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A917" s="2" t="s">
         <v>98</v>
       </c>
@@ -31050,7 +31050,7 @@
         <v>GCAP1,5.png</v>
       </c>
     </row>
-    <row r="918" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A918" s="2" t="s">
         <v>98</v>
       </c>
@@ -31080,7 +31080,7 @@
         <v>PCP2.png</v>
       </c>
     </row>
-    <row r="919" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A919" s="2" t="s">
         <v>98</v>
       </c>
@@ -31110,7 +31110,7 @@
         <v>PCP2.png</v>
       </c>
     </row>
-    <row r="920" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A920" s="2" t="s">
         <v>98</v>
       </c>
@@ -31140,7 +31140,7 @@
         <v>PCP2.png</v>
       </c>
     </row>
-    <row r="921" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A921" s="2" t="s">
         <v>98</v>
       </c>
@@ -31170,7 +31170,7 @@
         <v>PCP2.png</v>
       </c>
     </row>
-    <row r="922" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A922" s="2" t="s">
         <v>98</v>
       </c>
@@ -31200,7 +31200,7 @@
         <v>BAREP2.png</v>
       </c>
     </row>
-    <row r="923" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A923" s="2" t="s">
         <v>98</v>
       </c>
@@ -31230,7 +31230,7 @@
         <v>H2OHP500.png</v>
       </c>
     </row>
-    <row r="924" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A924" s="2" t="s">
         <v>98</v>
       </c>
@@ -31260,7 +31260,7 @@
         <v>H2OHP500.png</v>
       </c>
     </row>
-    <row r="925" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A925" s="2" t="s">
         <v>98</v>
       </c>
@@ -31290,7 +31290,7 @@
         <v>H2OHP500.png</v>
       </c>
     </row>
-    <row r="926" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A926" s="2" t="s">
         <v>98</v>
       </c>
@@ -31320,7 +31320,7 @@
         <v>H2OHP500.png</v>
       </c>
     </row>
-    <row r="927" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A927" s="2" t="s">
         <v>98</v>
       </c>
@@ -31350,7 +31350,7 @@
         <v>GCAP2.png</v>
       </c>
     </row>
-    <row r="928" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A928" s="2" t="s">
         <v>98</v>
       </c>
@@ -31380,7 +31380,7 @@
         <v>GCAP2.png</v>
       </c>
     </row>
-    <row r="929" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A929" s="2" t="s">
         <v>98</v>
       </c>
@@ -31410,7 +31410,7 @@
         <v>GCAP2.png</v>
       </c>
     </row>
-    <row r="930" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A930" s="2" t="s">
         <v>98</v>
       </c>
@@ -31440,7 +31440,7 @@
         <v>GCAP2.png</v>
       </c>
     </row>
-    <row r="931" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A931" s="2" t="s">
         <v>98</v>
       </c>
@@ -31470,7 +31470,7 @@
         <v>GCA350.png</v>
       </c>
     </row>
-    <row r="932" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="932" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A932" s="2" t="s">
         <v>98</v>
       </c>
@@ -31500,7 +31500,7 @@
         <v>GCA350.png</v>
       </c>
     </row>
-    <row r="933" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A933" s="2" t="s">
         <v>98</v>
       </c>
@@ -31530,7 +31530,7 @@
         <v>GCA350.png</v>
       </c>
     </row>
-    <row r="934" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A934" s="2" t="s">
         <v>98</v>
       </c>
@@ -31560,7 +31560,7 @@
         <v>GCA350.png</v>
       </c>
     </row>
-    <row r="935" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="935" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A935" s="2" t="s">
         <v>98</v>
       </c>
@@ -31590,7 +31590,7 @@
         <v>GCA350.png</v>
       </c>
     </row>
-    <row r="936" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="936" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A936" s="2" t="s">
         <v>98</v>
       </c>
@@ -31620,7 +31620,7 @@
         <v>BAREP2.png</v>
       </c>
     </row>
-    <row r="937" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="937" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A937" s="2" t="s">
         <v>98</v>
       </c>
@@ -31650,7 +31650,7 @@
         <v>H2OHP500.png</v>
       </c>
     </row>
-    <row r="938" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="938" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A938" s="2" t="s">
         <v>98</v>
       </c>
@@ -31680,7 +31680,7 @@
         <v>H2OHP500.png</v>
       </c>
     </row>
-    <row r="939" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="939" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A939" s="2" t="s">
         <v>98</v>
       </c>
@@ -31710,7 +31710,7 @@
         <v>H2OHP500.png</v>
       </c>
     </row>
-    <row r="940" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="940" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A940" s="2" t="s">
         <v>98</v>
       </c>
@@ -31740,7 +31740,7 @@
         <v>H2OHP500.png</v>
       </c>
     </row>
-    <row r="941" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="941" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A941" s="2" t="s">
         <v>98</v>
       </c>
@@ -31770,7 +31770,7 @@
         <v>PCB350.png</v>
       </c>
     </row>
-    <row r="942" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="942" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A942" s="2" t="s">
         <v>98</v>
       </c>
@@ -31800,7 +31800,7 @@
         <v>PCB350.png</v>
       </c>
     </row>
-    <row r="943" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="943" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A943" s="2" t="s">
         <v>98</v>
       </c>
@@ -31830,7 +31830,7 @@
         <v>PCB350.png</v>
       </c>
     </row>
-    <row r="944" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="944" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A944" s="2" t="s">
         <v>98</v>
       </c>
@@ -31860,7 +31860,7 @@
         <v>PCB350.png</v>
       </c>
     </row>
-    <row r="945" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="945" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A945" s="2" t="s">
         <v>98</v>
       </c>
@@ -31890,7 +31890,7 @@
         <v>PCB350.png</v>
       </c>
     </row>
-    <row r="946" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="946" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A946" s="2" t="s">
         <v>98</v>
       </c>
@@ -31920,7 +31920,7 @@
         <v>GCAP2.png</v>
       </c>
     </row>
-    <row r="947" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="947" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A947" s="2" t="s">
         <v>98</v>
       </c>
@@ -31950,7 +31950,7 @@
         <v>GCAP2.png</v>
       </c>
     </row>
-    <row r="948" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="948" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A948" s="2" t="s">
         <v>98</v>
       </c>
@@ -31980,7 +31980,7 @@
         <v>GCAP2.png</v>
       </c>
     </row>
-    <row r="949" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="949" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A949" s="2" t="s">
         <v>98</v>
       </c>
@@ -32010,7 +32010,7 @@
         <v>GCAP2.png</v>
       </c>
     </row>
-    <row r="950" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="950" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A950" s="2" t="s">
         <v>98</v>
       </c>
@@ -32040,7 +32040,7 @@
         <v>GCA269.png</v>
       </c>
     </row>
-    <row r="951" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="951" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A951" s="2" t="s">
         <v>98</v>
       </c>
@@ -32070,7 +32070,7 @@
         <v>GCA269.png</v>
       </c>
     </row>
-    <row r="952" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="952" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A952" s="2" t="s">
         <v>98</v>
       </c>
@@ -32100,7 +32100,7 @@
         <v>GCA269.png</v>
       </c>
     </row>
-    <row r="953" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="953" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A953" s="2" t="s">
         <v>98</v>
       </c>
@@ -32130,7 +32130,7 @@
         <v>GCA269.png</v>
       </c>
     </row>
-    <row r="954" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="954" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A954" s="2" t="s">
         <v>98</v>
       </c>
@@ -32160,7 +32160,7 @@
         <v>GCA269.png</v>
       </c>
     </row>
-    <row r="955" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="955" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A955" s="2" t="s">
         <v>98</v>
       </c>
@@ -32190,7 +32190,7 @@
         <v>PC269.png</v>
       </c>
     </row>
-    <row r="956" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="956" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A956" s="2" t="s">
         <v>98</v>
       </c>
@@ -32220,7 +32220,7 @@
         <v>PC269.png</v>
       </c>
     </row>
-    <row r="957" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="957" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A957" s="2" t="s">
         <v>98</v>
       </c>
@@ -32250,7 +32250,7 @@
         <v>PC269.png</v>
       </c>
     </row>
-    <row r="958" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="958" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A958" s="2" t="s">
         <v>98</v>
       </c>
@@ -32280,7 +32280,7 @@
         <v>PC269.png</v>
       </c>
     </row>
-    <row r="959" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="959" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A959" s="2" t="s">
         <v>98</v>
       </c>
@@ -32310,7 +32310,7 @@
         <v>PC269.png</v>
       </c>
     </row>
-    <row r="960" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="960" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A960" s="2" t="s">
         <v>98</v>
       </c>
@@ -32340,7 +32340,7 @@
         <v>GCAP1.png</v>
       </c>
     </row>
-    <row r="961" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="961" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A961" s="2" t="s">
         <v>98</v>
       </c>
@@ -32370,7 +32370,7 @@
         <v>GCAP1,5.png</v>
       </c>
     </row>
-    <row r="962" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="962" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A962" s="2" t="s">
         <v>98</v>
       </c>
@@ -32400,7 +32400,7 @@
         <v>GCAP1,5.png</v>
       </c>
     </row>
-    <row r="963" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="963" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A963" s="2" t="s">
         <v>98</v>
       </c>
@@ -32430,7 +32430,7 @@
         <v>GCAP1,5.png</v>
       </c>
     </row>
-    <row r="964" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="964" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A964" s="2" t="s">
         <v>98</v>
       </c>
@@ -32460,7 +32460,7 @@
         <v>PCP2.png</v>
       </c>
     </row>
-    <row r="965" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="965" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A965" s="2" t="s">
         <v>98</v>
       </c>
@@ -32490,7 +32490,7 @@
         <v>PCP2.png</v>
       </c>
     </row>
-    <row r="966" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="966" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A966" s="2" t="s">
         <v>98</v>
       </c>
@@ -32520,7 +32520,7 @@
         <v>PCP2.png</v>
       </c>
     </row>
-    <row r="967" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="967" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A967" s="2" t="s">
         <v>98</v>
       </c>
@@ -32550,7 +32550,7 @@
         <v>PCP2.png</v>
       </c>
     </row>
-    <row r="968" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="968" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A968" s="2" t="s">
         <v>98</v>
       </c>
@@ -32580,7 +32580,7 @@
         <v>H2OHP1,5.png</v>
       </c>
     </row>
-    <row r="969" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="969" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A969" s="2" t="s">
         <v>98</v>
       </c>
@@ -32610,7 +32610,7 @@
         <v>H2OHP1,5.png</v>
       </c>
     </row>
-    <row r="970" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="970" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A970" s="2" t="s">
         <v>98</v>
       </c>
@@ -32640,7 +32640,7 @@
         <v>H2OHP1,5.png</v>
       </c>
     </row>
-    <row r="971" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="971" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A971" s="2" t="s">
         <v>98</v>
       </c>
@@ -32670,7 +32670,7 @@
         <v>H2OHP1,5.png</v>
       </c>
     </row>
-    <row r="972" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="972" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A972" s="2" t="s">
         <v>98</v>
       </c>
@@ -32700,7 +32700,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="973" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="973" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A973" s="2" t="s">
         <v>98</v>
       </c>
@@ -32730,7 +32730,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="974" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="974" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A974" s="2" t="s">
         <v>98</v>
       </c>
@@ -32760,7 +32760,7 @@
         <v>AP269.png</v>
       </c>
     </row>
-    <row r="975" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="975" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A975" s="2" t="s">
         <v>98</v>
       </c>
@@ -32790,7 +32790,7 @@
         <v>AP269.png</v>
       </c>
     </row>
-    <row r="976" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="976" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A976" s="2" t="s">
         <v>98</v>
       </c>
@@ -32820,7 +32820,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="977" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="977" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A977" s="2" t="s">
         <v>98</v>
       </c>
@@ -32850,7 +32850,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="978" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="978" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A978" s="2" t="s">
         <v>98</v>
       </c>
@@ -32880,7 +32880,7 @@
         <v>AP269.png</v>
       </c>
     </row>
-    <row r="979" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="979" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A979" s="2" t="s">
         <v>98</v>
       </c>
@@ -32910,7 +32910,7 @@
         <v>AP269.png</v>
       </c>
     </row>
-    <row r="980" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="980" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A980" s="2" t="s">
         <v>98</v>
       </c>
@@ -32940,7 +32940,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="981" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="981" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A981" s="2" t="s">
         <v>98</v>
       </c>
@@ -32970,7 +32970,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="982" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="982" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A982" s="2" t="s">
         <v>98</v>
       </c>
@@ -33000,7 +33000,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="983" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="983" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A983" s="2" t="s">
         <v>98</v>
       </c>
@@ -33030,7 +33030,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="984" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="984" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A984" s="2" t="s">
         <v>98</v>
       </c>
@@ -33060,7 +33060,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="985" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="985" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A985" s="2" t="s">
         <v>98</v>
       </c>
@@ -33090,7 +33090,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="986" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="986" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A986" s="2" t="s">
         <v>98</v>
       </c>
@@ -33120,7 +33120,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="987" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="987" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A987" s="2" t="s">
         <v>98</v>
       </c>
@@ -33150,7 +33150,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="988" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="988" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A988" s="2" t="s">
         <v>98</v>
       </c>
@@ -33180,7 +33180,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="989" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="989" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A989" s="2" t="s">
         <v>98</v>
       </c>
@@ -33210,7 +33210,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="990" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="990" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A990" s="2" t="s">
         <v>98</v>
       </c>
@@ -33240,7 +33240,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="991" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="991" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A991" s="2" t="s">
         <v>98</v>
       </c>
@@ -33270,7 +33270,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="992" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="992" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A992" s="2" t="s">
         <v>98</v>
       </c>
@@ -33300,7 +33300,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="993" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="993" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A993" s="2" t="s">
         <v>98</v>
       </c>
@@ -33330,7 +33330,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="994" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="994" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A994" s="2" t="s">
         <v>98</v>
       </c>
@@ -33360,7 +33360,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="995" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="995" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A995" s="2" t="s">
         <v>98</v>
       </c>
@@ -33390,7 +33390,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="996" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="996" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A996" s="2" t="s">
         <v>98</v>
       </c>
@@ -33420,7 +33420,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="997" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="997" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A997" s="2" t="s">
         <v>98</v>
       </c>
@@ -33450,7 +33450,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="998" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="998" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A998" s="2" t="s">
         <v>98</v>
       </c>
@@ -33480,7 +33480,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="999" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="999" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A999" s="2" t="s">
         <v>98</v>
       </c>
@@ -33510,7 +33510,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="1000" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1000" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1000" s="2" t="s">
         <v>98</v>
       </c>
@@ -33533,14 +33533,14 @@
         <v>3.29</v>
       </c>
       <c r="H1000">
-        <v>3.09</v>
+        <v>2.99</v>
       </c>
       <c r="I1000" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1000,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="1001" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1001" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1001" s="2" t="s">
         <v>98</v>
       </c>
@@ -33570,7 +33570,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="1002" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1002" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1002" s="2" t="s">
         <v>98</v>
       </c>
@@ -33600,7 +33600,7 @@
         <v>AP269.png</v>
       </c>
     </row>
-    <row r="1003" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1003" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1003" s="2" t="s">
         <v>98</v>
       </c>
@@ -33630,7 +33630,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="1004" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1004" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1004" s="2" t="s">
         <v>98</v>
       </c>
@@ -33660,7 +33660,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="1005" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1005" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1005" s="2" t="s">
         <v>98</v>
       </c>
@@ -33690,7 +33690,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="1006" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1006" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1006" s="2" t="s">
         <v>98</v>
       </c>
@@ -33720,7 +33720,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="1007" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1007" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1007" s="2" t="s">
         <v>98</v>
       </c>
@@ -33750,7 +33750,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="1008" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1008" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1008" s="2" t="s">
         <v>98</v>
       </c>
@@ -33780,7 +33780,7 @@
         <v>AP269.png</v>
       </c>
     </row>
-    <row r="1009" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1009" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1009" s="2" t="s">
         <v>98</v>
       </c>
@@ -33810,7 +33810,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="1010" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1010" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1010" s="2" t="s">
         <v>98</v>
       </c>
@@ -33833,14 +33833,14 @@
         <v>3.29</v>
       </c>
       <c r="H1010">
-        <v>3.09</v>
+        <v>2.99</v>
       </c>
       <c r="I1010" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1010,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="1011" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1011" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1011" s="2" t="s">
         <v>98</v>
       </c>
@@ -34080,7 +34080,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="1019" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1019" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1019" s="2" t="s">
         <v>98</v>
       </c>
@@ -34110,7 +34110,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1020" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1020" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1020" s="2" t="s">
         <v>98</v>
       </c>
@@ -34140,7 +34140,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1021" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1021" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1021" s="2" t="s">
         <v>98</v>
       </c>
@@ -34170,7 +34170,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1022" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1022" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1022" s="2" t="s">
         <v>98</v>
       </c>
@@ -34200,7 +34200,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1023" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1023" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1023" s="2" t="s">
         <v>98</v>
       </c>
@@ -34230,7 +34230,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1024" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1024" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1024" s="2" t="s">
         <v>98</v>
       </c>
@@ -34260,7 +34260,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1025" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1025" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1025" s="2" t="s">
         <v>98</v>
       </c>
@@ -34290,7 +34290,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1026" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1026" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1026" s="2" t="s">
         <v>98</v>
       </c>
@@ -34320,7 +34320,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1027" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1027" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1027" s="2" t="s">
         <v>98</v>
       </c>
@@ -34350,7 +34350,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1028" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1028" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1028" s="2" t="s">
         <v>98</v>
       </c>
@@ -34380,7 +34380,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1029" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1029" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1029" s="2" t="s">
         <v>98</v>
       </c>
@@ -34410,7 +34410,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1030" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1030" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1030" s="2" t="s">
         <v>98</v>
       </c>
@@ -34440,7 +34440,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1031" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1031" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1031" s="2" t="s">
         <v>98</v>
       </c>
@@ -34470,7 +34470,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1032" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1032" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1032" s="2" t="s">
         <v>98</v>
       </c>
@@ -34500,7 +34500,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1033" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1033" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1033" s="2" t="s">
         <v>98</v>
       </c>
@@ -34530,7 +34530,7 @@
         <v>BC350.png</v>
       </c>
     </row>
-    <row r="1034" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1034" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1034" s="2" t="s">
         <v>98</v>
       </c>
@@ -34560,7 +34560,7 @@
         <v>BC350.png</v>
       </c>
     </row>
-    <row r="1035" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1035" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1035" s="2" t="s">
         <v>98</v>
       </c>
@@ -34590,7 +34590,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="1036" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1036" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1036" s="2" t="s">
         <v>98</v>
       </c>
@@ -34620,7 +34620,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="1037" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1037" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1037" s="2" t="s">
         <v>98</v>
       </c>
@@ -34650,7 +34650,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="1038" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1038" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1038" s="2" t="s">
         <v>98</v>
       </c>
@@ -34680,7 +34680,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="1039" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1039" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1039" s="2" t="s">
         <v>98</v>
       </c>
@@ -34710,7 +34710,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="1040" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1040" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1040" s="2" t="s">
         <v>98</v>
       </c>
@@ -34740,7 +34740,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="1041" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1041" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1041" s="2" t="s">
         <v>98</v>
       </c>
@@ -34770,7 +34770,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="1042" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1042" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1042" s="2" t="s">
         <v>98</v>
       </c>
@@ -34790,17 +34790,17 @@
         <v>72</v>
       </c>
       <c r="G1042">
-        <v>3.99</v>
+        <v>3.89</v>
       </c>
       <c r="H1042">
-        <v>3.69</v>
+        <v>3.59</v>
       </c>
       <c r="I1042" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1042,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="1043" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1043" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1043" s="2" t="s">
         <v>98</v>
       </c>
@@ -34820,17 +34820,17 @@
         <v>72</v>
       </c>
       <c r="G1043">
-        <v>3.99</v>
+        <v>3.89</v>
       </c>
       <c r="H1043">
-        <v>3.69</v>
+        <v>3.59</v>
       </c>
       <c r="I1043" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1043,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="1044" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1044" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1044" s="2" t="s">
         <v>98</v>
       </c>
@@ -34850,17 +34850,17 @@
         <v>72</v>
       </c>
       <c r="G1044">
-        <v>3.99</v>
+        <v>3.89</v>
       </c>
       <c r="H1044">
-        <v>3.69</v>
+        <v>3.59</v>
       </c>
       <c r="I1044" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1044,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="1045" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1045" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1045" s="2" t="s">
         <v>98</v>
       </c>
@@ -34880,17 +34880,17 @@
         <v>72</v>
       </c>
       <c r="G1045">
-        <v>3.99</v>
+        <v>3.89</v>
       </c>
       <c r="H1045">
-        <v>3.69</v>
+        <v>3.59</v>
       </c>
       <c r="I1045" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1045,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="1046" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1046" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1046" s="2" t="s">
         <v>98</v>
       </c>
@@ -34910,17 +34910,17 @@
         <v>72</v>
       </c>
       <c r="G1046">
-        <v>3.99</v>
+        <v>3.89</v>
       </c>
       <c r="H1046">
-        <v>3.69</v>
+        <v>3.59</v>
       </c>
       <c r="I1046" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1046,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="1047" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1047" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1047" s="2" t="s">
         <v>98</v>
       </c>
@@ -34940,17 +34940,17 @@
         <v>72</v>
       </c>
       <c r="G1047">
-        <v>3.99</v>
+        <v>3.89</v>
       </c>
       <c r="H1047">
-        <v>3.69</v>
+        <v>3.59</v>
       </c>
       <c r="I1047" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1047,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="1048" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1048" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1048" s="2" t="s">
         <v>98</v>
       </c>
@@ -34970,17 +34970,17 @@
         <v>72</v>
       </c>
       <c r="G1048">
-        <v>3.99</v>
+        <v>3.89</v>
       </c>
       <c r="H1048">
-        <v>3.69</v>
+        <v>3.59</v>
       </c>
       <c r="I1048" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1048,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="1049" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1049" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1049" s="2" t="s">
         <v>98</v>
       </c>
@@ -35000,17 +35000,17 @@
         <v>72</v>
       </c>
       <c r="G1049">
-        <v>3.99</v>
+        <v>3.89</v>
       </c>
       <c r="H1049">
-        <v>3.69</v>
+        <v>3.59</v>
       </c>
       <c r="I1049" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1049,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="1050" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1050" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1050" s="2" t="s">
         <v>98</v>
       </c>
@@ -35030,17 +35030,17 @@
         <v>72</v>
       </c>
       <c r="G1050">
-        <v>3.99</v>
+        <v>3.89</v>
       </c>
       <c r="H1050">
-        <v>3.69</v>
+        <v>3.59</v>
       </c>
       <c r="I1050" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1050,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="1051" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1051" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1051" s="2" t="s">
         <v>98</v>
       </c>
@@ -35060,17 +35060,17 @@
         <v>72</v>
       </c>
       <c r="G1051">
-        <v>3.99</v>
+        <v>3.89</v>
       </c>
       <c r="H1051">
-        <v>3.69</v>
+        <v>3.59</v>
       </c>
       <c r="I1051" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1051,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="1052" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1052" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1052" s="2" t="s">
         <v>98</v>
       </c>
@@ -35090,17 +35090,17 @@
         <v>72</v>
       </c>
       <c r="G1052">
-        <v>3.99</v>
+        <v>3.89</v>
       </c>
       <c r="H1052">
-        <v>3.69</v>
+        <v>3.59</v>
       </c>
       <c r="I1052" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1052,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="1053" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1053" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1053" s="2" t="s">
         <v>98</v>
       </c>
@@ -35120,17 +35120,17 @@
         <v>72</v>
       </c>
       <c r="G1053">
-        <v>3.99</v>
+        <v>3.89</v>
       </c>
       <c r="H1053">
-        <v>3.69</v>
+        <v>3.59</v>
       </c>
       <c r="I1053" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1053,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="1054" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1054" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1054" s="2" t="s">
         <v>98</v>
       </c>
@@ -35160,7 +35160,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="1055" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1055" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1055" s="2" t="s">
         <v>98</v>
       </c>
@@ -35190,7 +35190,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="1056" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1056" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1056" s="2" t="s">
         <v>98</v>
       </c>
@@ -35220,7 +35220,7 @@
         <v>AP350.png</v>
       </c>
     </row>
-    <row r="1057" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1057" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1057" s="2" t="s">
         <v>98</v>
       </c>
@@ -35250,7 +35250,7 @@
         <v>AP350.png</v>
       </c>
     </row>
-    <row r="1058" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1058" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1058" s="2" t="s">
         <v>98</v>
       </c>
@@ -35280,7 +35280,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1059" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1059" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1059" s="2" t="s">
         <v>98</v>
       </c>
@@ -35310,7 +35310,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1060" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1060" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1060" s="2" t="s">
         <v>98</v>
       </c>
@@ -35340,7 +35340,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1061" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1061" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1061" s="2" t="s">
         <v>98</v>
       </c>
@@ -35370,7 +35370,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1062" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1062" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1062" s="2" t="s">
         <v>98</v>
       </c>
@@ -35400,7 +35400,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1063" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1063" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1063" s="2" t="s">
         <v>98</v>
       </c>
@@ -35430,7 +35430,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1064" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1064" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1064" s="2" t="s">
         <v>98</v>
       </c>
@@ -35460,7 +35460,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1065" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1065" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1065" s="2" t="s">
         <v>98</v>
       </c>
@@ -35490,7 +35490,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1066" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1066" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1066" s="2" t="s">
         <v>98</v>
       </c>
@@ -35520,7 +35520,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1067" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1067" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1067" s="2" t="s">
         <v>98</v>
       </c>
@@ -35550,7 +35550,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1068" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1068" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1068" s="2" t="s">
         <v>98</v>
       </c>
@@ -35580,7 +35580,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1069" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1069" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1069" s="2" t="s">
         <v>98</v>
       </c>
@@ -35610,7 +35610,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1070" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1070" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1070" s="2" t="s">
         <v>98</v>
       </c>
@@ -35640,7 +35640,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1071" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1071" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1071" s="2" t="s">
         <v>98</v>
       </c>
@@ -35670,7 +35670,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1072" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1072" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1072" s="2" t="s">
         <v>98</v>
       </c>
@@ -35700,7 +35700,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="1073" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1073" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1073" s="2" t="s">
         <v>98</v>
       </c>
@@ -35730,7 +35730,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="1074" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1074" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1074" s="2" t="s">
         <v>98</v>
       </c>
@@ -35760,7 +35760,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="1075" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1075" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1075" s="2" t="s">
         <v>98</v>
       </c>
@@ -35790,7 +35790,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="1076" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1076" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1076" s="2" t="s">
         <v>98</v>
       </c>
@@ -35820,7 +35820,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="1077" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1077" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1077" s="2" t="s">
         <v>98</v>
       </c>
@@ -35850,7 +35850,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="1078" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1078" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1078" s="2" t="s">
         <v>98</v>
       </c>
@@ -35880,7 +35880,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="1079" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1079" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1079" s="2" t="s">
         <v>98</v>
       </c>
@@ -35910,7 +35910,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="1080" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1080" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1080" s="2" t="s">
         <v>98</v>
       </c>
@@ -35940,7 +35940,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="1081" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1081" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1081" s="2" t="s">
         <v>98</v>
       </c>
@@ -35970,7 +35970,7 @@
         <v>STE269.png</v>
       </c>
     </row>
-    <row r="1082" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1082" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1082" s="2" t="s">
         <v>98</v>
       </c>
@@ -36000,7 +36000,7 @@
         <v>STE269.png</v>
       </c>
     </row>
-    <row r="1083" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1083" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1083" s="2" t="s">
         <v>98</v>
       </c>
@@ -36030,7 +36030,7 @@
         <v>STE269.png</v>
       </c>
     </row>
-    <row r="1084" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1084" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1084" s="2" t="s">
         <v>98</v>
       </c>
@@ -36060,7 +36060,7 @@
         <v>STE269.png</v>
       </c>
     </row>
-    <row r="1085" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1085" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1085" s="2" t="s">
         <v>98</v>
       </c>
@@ -36090,7 +36090,7 @@
         <v>BUD350.png</v>
       </c>
     </row>
-    <row r="1086" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1086" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1086" s="2" t="s">
         <v>98</v>
       </c>
@@ -36120,7 +36120,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="1087" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1087" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1087" s="2" t="s">
         <v>98</v>
       </c>
@@ -36150,7 +36150,7 @@
         <v>BUD350.png</v>
       </c>
     </row>
-    <row r="1088" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1088" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1088" s="2" t="s">
         <v>98</v>
       </c>
@@ -36180,7 +36180,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="1089" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1089" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1089" s="2" t="s">
         <v>98</v>
       </c>
@@ -36210,7 +36210,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="1090" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1090" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1090" s="2" t="s">
         <v>98</v>
       </c>
@@ -36240,7 +36240,7 @@
         <v>BUD350.png</v>
       </c>
     </row>
-    <row r="1091" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1091" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1091" s="2" t="s">
         <v>98</v>
       </c>
@@ -36270,7 +36270,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="1092" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1092" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1092" s="2" t="s">
         <v>98</v>
       </c>
@@ -36300,7 +36300,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="1093" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1093" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1093" s="2" t="s">
         <v>98</v>
       </c>
@@ -36330,7 +36330,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="1094" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1094" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1094" s="2" t="s">
         <v>98</v>
       </c>
@@ -36360,7 +36360,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="1095" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1095" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1095" s="2" t="s">
         <v>98</v>
       </c>
@@ -36390,7 +36390,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="1096" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1096" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1096" s="2" t="s">
         <v>98</v>
       </c>
@@ -36420,7 +36420,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="1097" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1097" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1097" s="2" t="s">
         <v>98</v>
       </c>
@@ -36450,7 +36450,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="1098" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1098" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1098" s="2" t="s">
         <v>98</v>
       </c>
@@ -36480,7 +36480,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="1099" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1099" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1099" s="2" t="s">
         <v>98</v>
       </c>
@@ -36510,7 +36510,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="1100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1100" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1100" s="2" t="s">
         <v>98</v>
       </c>
@@ -36540,7 +36540,7 @@
         <v>COR269.png</v>
       </c>
     </row>
-    <row r="1101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1101" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1101" s="2" t="s">
         <v>98</v>
       </c>
@@ -36570,7 +36570,7 @@
         <v>COR269.png</v>
       </c>
     </row>
-    <row r="1102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1102" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1102" s="2" t="s">
         <v>98</v>
       </c>
@@ -36600,7 +36600,7 @@
         <v>COR269.png</v>
       </c>
     </row>
-    <row r="1103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1103" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1103" s="2" t="s">
         <v>98</v>
       </c>
@@ -36630,7 +36630,7 @@
         <v>COR269.png</v>
       </c>
     </row>
-    <row r="1104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1104" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1104" s="2" t="s">
         <v>98</v>
       </c>
@@ -36660,7 +36660,7 @@
         <v>STE350.png</v>
       </c>
     </row>
-    <row r="1105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1105" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1105" s="2" t="s">
         <v>98</v>
       </c>
@@ -36690,7 +36690,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="1106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1106" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1106" s="2" t="s">
         <v>98</v>
       </c>
@@ -36720,7 +36720,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="1107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1107" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1107" s="2" t="s">
         <v>98</v>
       </c>
@@ -36750,7 +36750,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="1108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1108" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1108" s="2" t="s">
         <v>98</v>
       </c>
@@ -36780,7 +36780,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="1109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1109" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1109" s="2" t="s">
         <v>98</v>
       </c>
@@ -36810,7 +36810,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="1110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1110" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1110" s="2" t="s">
         <v>98</v>
       </c>
@@ -36840,7 +36840,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="1111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1111" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1111" s="2" t="s">
         <v>98</v>
       </c>
@@ -36870,7 +36870,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="1112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1112" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1112" s="2" t="s">
         <v>98</v>
       </c>
@@ -36900,7 +36900,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="1113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1113" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1113" s="2" t="s">
         <v>98</v>
       </c>
@@ -36930,7 +36930,7 @@
         <v>STE350.png</v>
       </c>
     </row>
-    <row r="1114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1114" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1114" s="2" t="s">
         <v>98</v>
       </c>
@@ -36960,7 +36960,7 @@
         <v>STE350.png</v>
       </c>
     </row>
-    <row r="1115" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1115" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1115" s="2" t="s">
         <v>98</v>
       </c>
@@ -36990,7 +36990,7 @@
         <v>STE350.png</v>
       </c>
     </row>
-    <row r="1116" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1116" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1116" s="2" t="s">
         <v>98</v>
       </c>
@@ -37020,7 +37020,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="1117" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1117" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1117" s="2" t="s">
         <v>98</v>
       </c>
@@ -37050,7 +37050,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="1118" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1118" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1118" s="2" t="s">
         <v>98</v>
       </c>
@@ -37080,7 +37080,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="1119" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1119" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1119" s="2" t="s">
         <v>98</v>
       </c>
@@ -37110,7 +37110,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="1120" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1120" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1120" s="2" t="s">
         <v>98</v>
       </c>
@@ -37140,7 +37140,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="1121" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1121" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1121" s="2" t="s">
         <v>98</v>
       </c>
@@ -37170,7 +37170,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="1122" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1122" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1122" s="2" t="s">
         <v>98</v>
       </c>
@@ -37200,7 +37200,7 @@
         <v>STE350.png</v>
       </c>
     </row>
-    <row r="1123" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1123" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1123" s="2" t="s">
         <v>98</v>
       </c>
@@ -37230,7 +37230,7 @@
         <v>COR350.png</v>
       </c>
     </row>
-    <row r="1124" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1124" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1124" s="2" t="s">
         <v>98</v>
       </c>
@@ -37260,7 +37260,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="1125" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1125" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1125" s="2" t="s">
         <v>98</v>
       </c>
@@ -37290,7 +37290,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="1126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1126" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1126" s="2" t="s">
         <v>98</v>
       </c>
@@ -37320,7 +37320,7 @@
         <v>COR350.png</v>
       </c>
     </row>
-    <row r="1127" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1127" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1127" s="2" t="s">
         <v>98</v>
       </c>
@@ -37350,7 +37350,7 @@
         <v>COR350.png</v>
       </c>
     </row>
-    <row r="1128" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1128" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1128" s="2" t="s">
         <v>98</v>
       </c>
@@ -37380,7 +37380,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="1129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1129" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1129" s="2" t="s">
         <v>98</v>
       </c>
@@ -37410,7 +37410,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="1130" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1130" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1130" s="2" t="s">
         <v>98</v>
       </c>
@@ -37440,7 +37440,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="1131" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1131" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1131" s="2" t="s">
         <v>98</v>
       </c>
@@ -37470,7 +37470,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="1132" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1132" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1132" s="2" t="s">
         <v>98</v>
       </c>
@@ -37500,7 +37500,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="1133" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1133" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1133" s="2" t="s">
         <v>98</v>
       </c>
@@ -37530,7 +37530,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="1134" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1134" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1134" s="2" t="s">
         <v>98</v>
       </c>
@@ -37560,7 +37560,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="1135" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1135" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1135" s="2" t="s">
         <v>98</v>
       </c>
@@ -37590,7 +37590,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="1136" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1136" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1136" s="2" t="s">
         <v>98</v>
       </c>
@@ -37620,7 +37620,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="1137" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1137" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1137" s="2" t="s">
         <v>98</v>
       </c>
@@ -37650,7 +37650,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="1138" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1138" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1138" s="2" t="s">
         <v>98</v>
       </c>
@@ -37680,7 +37680,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="1139" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1139" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1139" s="2" t="s">
         <v>98</v>
       </c>
@@ -37710,7 +37710,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="1140" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1140" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1140" s="2" t="s">
         <v>98</v>
       </c>
@@ -37740,7 +37740,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="1141" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1141" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1141" s="2" t="s">
         <v>98</v>
       </c>
@@ -37770,7 +37770,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="1142" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1142" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1142" s="2" t="s">
         <v>98</v>
       </c>
@@ -37800,7 +37800,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="1143" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1143" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1143" s="2" t="s">
         <v>98</v>
       </c>
@@ -37830,7 +37830,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="1144" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1144" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1144" s="2" t="s">
         <v>98</v>
       </c>
@@ -37860,7 +37860,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="1145" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1145" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1145" s="2" t="s">
         <v>98</v>
       </c>
@@ -37890,7 +37890,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="1146" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1146" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1146" s="2" t="s">
         <v>98</v>
       </c>
@@ -37920,7 +37920,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="1147" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1147" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1147" s="2" t="s">
         <v>98</v>
       </c>
@@ -37950,37 +37950,13 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="1148" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1148" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B1148" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1148" t="s">
-        <v>90</v>
-      </c>
-      <c r="D1148" t="s">
-        <v>26</v>
-      </c>
-      <c r="E1148" s="2">
-        <v>1</v>
-      </c>
-      <c r="F1148" t="s">
-        <v>81</v>
-      </c>
-      <c r="G1148">
-        <v>6.39</v>
-      </c>
-      <c r="H1148">
-        <v>5.69</v>
-      </c>
-      <c r="I1148" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1148,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>BUDZEROLN.png</v>
-      </c>
-    </row>
-    <row r="1149" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1148" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A1148" s="2"/>
+      <c r="B1148" s="2"/>
+      <c r="E1148" s="2"/>
+      <c r="I1148" s="2"/>
+    </row>
+    <row r="1149" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1149" s="2" t="s">
         <v>98</v>
       </c>
@@ -38010,7 +37986,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="1150" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1150" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1150" s="2" t="s">
         <v>98</v>
       </c>
@@ -38040,7 +38016,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="1151" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1151" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1151" s="2" t="s">
         <v>98</v>
       </c>
@@ -38070,7 +38046,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="1152" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1152" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1152" s="2" t="s">
         <v>98</v>
       </c>
@@ -38100,7 +38076,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="1153" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1153" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1153" s="2" t="s">
         <v>98</v>
       </c>
@@ -38130,7 +38106,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="1154" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1154" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1154" s="2" t="s">
         <v>98</v>
       </c>
@@ -38160,7 +38136,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="1155" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1155" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1155" s="2" t="s">
         <v>98</v>
       </c>
@@ -38190,7 +38166,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="1156" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1156" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1156" s="2" t="s">
         <v>98</v>
       </c>
@@ -38220,7 +38196,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="1157" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1157" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1157" s="2" t="s">
         <v>98</v>
       </c>
@@ -38250,7 +38226,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="1158" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1158" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1158" s="2" t="s">
         <v>98</v>
       </c>
@@ -38280,7 +38256,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="1159" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1159" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1159" s="2" t="s">
         <v>98</v>
       </c>
@@ -38310,7 +38286,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="1160" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1160" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1160" s="2" t="s">
         <v>98</v>
       </c>
@@ -38340,7 +38316,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="1161" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1161" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1161" s="2" t="s">
         <v>98</v>
       </c>
@@ -38370,7 +38346,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="1162" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1162" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1162" s="2" t="s">
         <v>98</v>
       </c>
@@ -38400,7 +38376,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="1163" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1163" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1163" s="2" t="s">
         <v>98</v>
       </c>
@@ -38430,7 +38406,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="1164" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1164" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1164" s="2" t="s">
         <v>98</v>
       </c>
@@ -38460,7 +38436,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="1165" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1165" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1165" s="2" t="s">
         <v>98</v>
       </c>
@@ -38490,7 +38466,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="1166" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1166" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1166" s="2" t="s">
         <v>98</v>
       </c>
@@ -38520,7 +38496,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="1167" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1167" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1167" s="2" t="s">
         <v>98</v>
       </c>
@@ -38550,7 +38526,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="1168" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1168" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1168" s="2" t="s">
         <v>98</v>
       </c>
@@ -38580,7 +38556,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="1169" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1169" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1169" s="2" t="s">
         <v>98</v>
       </c>
@@ -38610,7 +38586,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="1170" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1170" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1170" s="2" t="s">
         <v>98</v>
       </c>
@@ -38640,7 +38616,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="1171" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1171" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1171" s="2" t="s">
         <v>98</v>
       </c>
@@ -38670,7 +38646,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="1172" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1172" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1172" s="2" t="s">
         <v>98</v>
       </c>
@@ -38700,7 +38676,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="1173" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1173" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1173" s="2" t="s">
         <v>98</v>
       </c>
@@ -38730,7 +38706,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="1174" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1174" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1174" s="2" t="s">
         <v>98</v>
       </c>
@@ -38760,7 +38736,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="1175" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1175" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1175" s="2" t="s">
         <v>98</v>
       </c>
@@ -38790,7 +38766,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="1176" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1176" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1176" s="2" t="s">
         <v>98</v>
       </c>
@@ -38820,7 +38796,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="1177" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1177" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1177" s="2" t="s">
         <v>98</v>
       </c>
@@ -38850,7 +38826,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="1178" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1178" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1178" s="2" t="s">
         <v>98</v>
       </c>
@@ -38880,7 +38856,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="1179" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1179" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1179" s="2" t="s">
         <v>98</v>
       </c>
@@ -38910,7 +38886,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="1180" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1180" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1180" s="2" t="s">
         <v>98</v>
       </c>
@@ -38940,7 +38916,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="1181" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1181" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1181" s="2" t="s">
         <v>98</v>
       </c>
@@ -38970,7 +38946,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="1182" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1182" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1182" s="2" t="s">
         <v>98</v>
       </c>
@@ -39000,7 +38976,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="1183" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1183" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1183" s="2" t="s">
         <v>98</v>
       </c>
@@ -39030,7 +39006,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="1184" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1184" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1184" s="2" t="s">
         <v>98</v>
       </c>
@@ -39060,7 +39036,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="1185" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1185" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1185" s="2" t="s">
         <v>98</v>
       </c>
@@ -39090,7 +39066,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="1186" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1186" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1186" s="2" t="s">
         <v>98</v>
       </c>
@@ -39120,7 +39096,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="1187" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1187" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1187" s="2" t="s">
         <v>98</v>
       </c>
@@ -39150,7 +39126,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="1188" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1188" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1188" s="2" t="s">
         <v>98</v>
       </c>
@@ -39180,7 +39156,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="1189" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1189" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1189" s="2" t="s">
         <v>98</v>
       </c>
@@ -39210,7 +39186,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="1190" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1190" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1190" s="2" t="s">
         <v>98</v>
       </c>
@@ -39240,7 +39216,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="1191" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1191" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1191" s="2" t="s">
         <v>98</v>
       </c>
@@ -39270,7 +39246,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="1192" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1192" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1192" s="2" t="s">
         <v>98</v>
       </c>
@@ -39300,7 +39276,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="1193" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1193" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1193" s="2" t="s">
         <v>98</v>
       </c>
@@ -39330,7 +39306,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="1194" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1194" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1194" s="2" t="s">
         <v>98</v>
       </c>
@@ -39360,7 +39336,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="1195" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1195" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1195" s="2" t="s">
         <v>98</v>
       </c>
@@ -39390,7 +39366,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="1196" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1196" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1196" s="2" t="s">
         <v>98</v>
       </c>
@@ -39420,7 +39396,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="1197" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1197" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1197" s="2" t="s">
         <v>98</v>
       </c>
@@ -39450,7 +39426,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="1198" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1198" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1198" s="2" t="s">
         <v>98</v>
       </c>
@@ -39480,7 +39456,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="1199" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1199" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1199" s="2" t="s">
         <v>98</v>
       </c>
@@ -39510,7 +39486,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="1200" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1200" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1200" s="2" t="s">
         <v>98</v>
       </c>
@@ -39540,7 +39516,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="1201" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1201" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1201" s="2" t="s">
         <v>98</v>
       </c>
@@ -39570,7 +39546,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="1202" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1202" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1202" s="2" t="s">
         <v>98</v>
       </c>
@@ -39600,7 +39576,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="1203" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1203" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1203" s="2" t="s">
         <v>98</v>
       </c>
@@ -39630,7 +39606,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="1204" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1204" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1204" s="2" t="s">
         <v>98</v>
       </c>
@@ -39660,7 +39636,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="1205" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1205" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1205" s="2" t="s">
         <v>98</v>
       </c>
@@ -39690,7 +39666,7 @@
         <v>BC269MP.png</v>
       </c>
     </row>
-    <row r="1206" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1206" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1206" s="2" t="s">
         <v>98</v>
       </c>
@@ -39720,7 +39696,7 @@
         <v>SK269MP.png</v>
       </c>
     </row>
-    <row r="1207" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1207" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1207" s="2" t="s">
         <v>98</v>
       </c>
@@ -39750,7 +39726,7 @@
         <v>BUD269MP.png</v>
       </c>
     </row>
-    <row r="1208" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1208" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1208" s="2" t="s">
         <v>98</v>
       </c>
@@ -39780,11 +39756,171 @@
         <v>ORI269MP.png</v>
       </c>
     </row>
+    <row r="1209" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A1209" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1209" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1209" t="s">
+        <v>112</v>
+      </c>
+      <c r="D1209" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1209" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1209" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1209">
+        <v>4.49</v>
+      </c>
+      <c r="H1209">
+        <v>4.49</v>
+      </c>
+      <c r="I1209" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1209,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>STE350.png</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1210" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1210" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1210" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1210" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1210" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1210" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1210">
+        <v>3.49</v>
+      </c>
+      <c r="H1210">
+        <v>3.09</v>
+      </c>
+      <c r="I1210" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1210,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BUD269.png</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1211" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1211" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1211" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1211" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1211" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1211" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1211">
+        <v>3.49</v>
+      </c>
+      <c r="H1211">
+        <v>3.09</v>
+      </c>
+      <c r="I1211" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1211,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BUD269.png</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1212" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1212" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1212" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1212" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1212" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1212" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1212">
+        <v>3.49</v>
+      </c>
+      <c r="H1212">
+        <v>3.09</v>
+      </c>
+      <c r="I1212" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1212,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BUD269.png</v>
+      </c>
+    </row>
+    <row r="1213" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1213" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1213" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1213" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1213" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1213" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1213" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1213">
+        <v>3.49</v>
+      </c>
+      <c r="H1213">
+        <v>3.09</v>
+      </c>
+      <c r="I1213" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1213,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BUD269.png</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I1208" xr:uid="{34B2C8DF-4561-40B2-8E7C-6CD69559B9AE}">
+  <autoFilter ref="A1:I1209" xr:uid="{34B2C8DF-4561-40B2-8E7C-6CD69559B9AE}">
     <filterColumn colId="0">
       <filters>
         <filter val="Outubro"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="1">
+      <filters>
+        <filter val="CERV"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="5">
+      <filters>
+        <filter val="BUD 269"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/data/calendario_promocional.xlsx
+++ b/data/calendario_promocional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\99845131\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A504FFC4-D474-457C-BE99-5AC18C9F26CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D272B97-12F9-4E75-B23A-C4B2A441F49C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DeparaIMG" sheetId="5" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6528" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6528" uniqueCount="123">
   <si>
     <t>Data</t>
   </si>
@@ -413,6 +413,9 @@
   <si>
     <t>MIC 269</t>
   </si>
+  <si>
+    <t>Core Cash: 45 R$/hl</t>
+  </si>
 </sst>
 </file>
 
@@ -2845,7 +2848,6 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D40F4A5-E774-499A-A01D-1C21EEE25028}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:D49"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -2964,7 +2966,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -2978,7 +2980,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
@@ -2992,7 +2994,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -3006,7 +3008,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="12" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
@@ -3020,7 +3022,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>10</v>
       </c>
@@ -3034,7 +3036,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="14" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>10</v>
       </c>
@@ -3146,7 +3148,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="22" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>103</v>
       </c>
@@ -3160,7 +3162,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>103</v>
       </c>
@@ -3174,7 +3176,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="24" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>103</v>
       </c>
@@ -3188,7 +3190,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="25" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>103</v>
       </c>
@@ -3202,7 +3204,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="26" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>103</v>
       </c>
@@ -3216,7 +3218,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="27" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>103</v>
       </c>
@@ -3230,7 +3232,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="28" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>99</v>
       </c>
@@ -3244,7 +3246,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="29" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>99</v>
       </c>
@@ -3258,7 +3260,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="30" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>99</v>
       </c>
@@ -3272,7 +3274,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="31" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>99</v>
       </c>
@@ -3286,7 +3288,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="32" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>99</v>
       </c>
@@ -3300,7 +3302,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="33" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>99</v>
       </c>
@@ -3314,7 +3316,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="34" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>102</v>
       </c>
@@ -3328,7 +3330,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="35" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>102</v>
       </c>
@@ -3342,7 +3344,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="36" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>102</v>
       </c>
@@ -3356,7 +3358,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="37" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
         <v>102</v>
       </c>
@@ -3370,7 +3372,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="38" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>102</v>
       </c>
@@ -3384,7 +3386,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="39" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
         <v>102</v>
       </c>
@@ -3398,7 +3400,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="40" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>98</v>
       </c>
@@ -3412,7 +3414,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="41" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>98</v>
       </c>
@@ -3426,7 +3428,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="42" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
         <v>98</v>
       </c>
@@ -3440,7 +3442,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="43" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
         <v>98</v>
       </c>
@@ -3454,7 +3456,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="44" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
         <v>98</v>
       </c>
@@ -3468,7 +3470,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="45" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
         <v>98</v>
       </c>
@@ -3482,7 +3484,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="46" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
         <v>98</v>
       </c>
@@ -3496,7 +3498,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="47" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
         <v>98</v>
       </c>
@@ -3507,10 +3509,10 @@
         <v>23</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
         <v>98</v>
       </c>
@@ -3524,7 +3526,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="49" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
         <v>98</v>
       </c>
@@ -3539,13 +3541,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D49" xr:uid="{6D40F4A5-E774-499A-A01D-1C21EEE25028}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="NAB"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:D49" xr:uid="{6D40F4A5-E774-499A-A01D-1C21EEE25028}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>

--- a/data/calendario_promocional.xlsx
+++ b/data/calendario_promocional.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\99845131\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\99836025\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D272B97-12F9-4E75-B23A-C4B2A441F49C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA036B4B-040A-4C83-985C-9D380DA738A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DeparaIMG" sheetId="5" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">MECANICA!$A$1:$D$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">PRODUTOS!$A$1:$I$1213</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentManualCount="12"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -3548,6 +3548,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34B2C8DF-4561-40B2-8E7C-6CD69559B9AE}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:I1213"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -5804,7 +5805,7 @@
         <v>SUKP2.png</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
         <v>10</v>
       </c>
@@ -5834,7 +5835,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
         <v>10</v>
       </c>
@@ -5864,7 +5865,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
         <v>10</v>
       </c>
@@ -5894,7 +5895,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
         <v>10</v>
       </c>
@@ -5924,7 +5925,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
         <v>10</v>
       </c>
@@ -5954,7 +5955,7 @@
         <v>AP269.png</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
         <v>10</v>
       </c>
@@ -5984,7 +5985,7 @@
         <v>AP269.png</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
         <v>10</v>
       </c>
@@ -6014,7 +6015,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
         <v>10</v>
       </c>
@@ -6044,7 +6045,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
         <v>10</v>
       </c>
@@ -6074,7 +6075,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
         <v>10</v>
       </c>
@@ -6104,7 +6105,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
         <v>10</v>
       </c>
@@ -6134,7 +6135,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
         <v>10</v>
       </c>
@@ -6164,7 +6165,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
         <v>10</v>
       </c>
@@ -6194,7 +6195,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
         <v>10</v>
       </c>
@@ -6224,7 +6225,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
         <v>10</v>
       </c>
@@ -6254,7 +6255,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
         <v>10</v>
       </c>
@@ -6284,7 +6285,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
         <v>10</v>
       </c>
@@ -6314,7 +6315,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
         <v>10</v>
       </c>
@@ -6344,7 +6345,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
         <v>10</v>
       </c>
@@ -6374,7 +6375,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
         <v>10</v>
       </c>
@@ -6404,7 +6405,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
         <v>10</v>
       </c>
@@ -6434,7 +6435,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
         <v>10</v>
       </c>
@@ -6464,7 +6465,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
         <v>10</v>
       </c>
@@ -6494,7 +6495,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
         <v>10</v>
       </c>
@@ -6524,7 +6525,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
         <v>10</v>
       </c>
@@ -6554,7 +6555,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
         <v>10</v>
       </c>
@@ -6584,7 +6585,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
         <v>10</v>
       </c>
@@ -6614,7 +6615,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
         <v>10</v>
       </c>
@@ -6644,7 +6645,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
         <v>10</v>
       </c>
@@ -6674,7 +6675,7 @@
         <v>AP269.png</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
         <v>10</v>
       </c>
@@ -6704,7 +6705,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
         <v>10</v>
       </c>
@@ -6734,7 +6735,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
         <v>10</v>
       </c>
@@ -6764,7 +6765,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
         <v>10</v>
       </c>
@@ -6794,7 +6795,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
         <v>10</v>
       </c>
@@ -6824,7 +6825,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
         <v>10</v>
       </c>
@@ -6854,7 +6855,7 @@
         <v>AP269.png</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
         <v>10</v>
       </c>
@@ -6884,7 +6885,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
         <v>10</v>
       </c>
@@ -6914,7 +6915,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
         <v>10</v>
       </c>
@@ -6944,7 +6945,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
         <v>10</v>
       </c>
@@ -6974,7 +6975,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
         <v>10</v>
       </c>
@@ -7004,7 +7005,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
         <v>10</v>
       </c>
@@ -7034,7 +7035,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
         <v>10</v>
       </c>
@@ -7064,7 +7065,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
         <v>10</v>
       </c>
@@ -7094,7 +7095,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
         <v>10</v>
       </c>
@@ -7124,7 +7125,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
         <v>10</v>
       </c>
@@ -7154,7 +7155,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" s="2" t="s">
         <v>10</v>
       </c>
@@ -7184,7 +7185,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
         <v>10</v>
       </c>
@@ -7214,7 +7215,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123" s="2" t="s">
         <v>10</v>
       </c>
@@ -7244,7 +7245,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
         <v>10</v>
       </c>
@@ -7274,7 +7275,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125" s="2" t="s">
         <v>10</v>
       </c>
@@ -7304,7 +7305,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126" s="2" t="s">
         <v>10</v>
       </c>
@@ -7334,7 +7335,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127" s="2" t="s">
         <v>10</v>
       </c>
@@ -7364,7 +7365,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128" s="2" t="s">
         <v>10</v>
       </c>
@@ -7394,7 +7395,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129" s="2" t="s">
         <v>10</v>
       </c>
@@ -7424,7 +7425,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A130" s="2" t="s">
         <v>10</v>
       </c>
@@ -7454,7 +7455,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A131" s="2" t="s">
         <v>10</v>
       </c>
@@ -7484,7 +7485,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A132" s="2" t="s">
         <v>10</v>
       </c>
@@ -7514,7 +7515,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A133" s="2" t="s">
         <v>10</v>
       </c>
@@ -7544,7 +7545,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A134" s="2" t="s">
         <v>10</v>
       </c>
@@ -7574,7 +7575,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135" s="2" t="s">
         <v>10</v>
       </c>
@@ -7604,7 +7605,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136" s="2" t="s">
         <v>10</v>
       </c>
@@ -7634,7 +7635,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A137" s="2" t="s">
         <v>10</v>
       </c>
@@ -7664,7 +7665,7 @@
         <v>BC350.png</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A138" s="2" t="s">
         <v>10</v>
       </c>
@@ -7694,7 +7695,7 @@
         <v>BC350.png</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A139" s="2" t="s">
         <v>10</v>
       </c>
@@ -7724,7 +7725,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A140" s="2" t="s">
         <v>10</v>
       </c>
@@ -7754,7 +7755,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A141" s="2" t="s">
         <v>10</v>
       </c>
@@ -7784,7 +7785,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A142" s="2" t="s">
         <v>10</v>
       </c>
@@ -7814,7 +7815,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A143" s="2" t="s">
         <v>10</v>
       </c>
@@ -7844,7 +7845,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
         <v>10</v>
       </c>
@@ -7874,7 +7875,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145" s="2" t="s">
         <v>10</v>
       </c>
@@ -7904,7 +7905,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A146" s="2" t="s">
         <v>10</v>
       </c>
@@ -7934,7 +7935,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A147" s="2" t="s">
         <v>10</v>
       </c>
@@ -7964,7 +7965,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148" s="2" t="s">
         <v>10</v>
       </c>
@@ -7994,7 +7995,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A149" s="2" t="s">
         <v>10</v>
       </c>
@@ -8024,7 +8025,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A150" s="2" t="s">
         <v>10</v>
       </c>
@@ -8054,7 +8055,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151" s="2" t="s">
         <v>10</v>
       </c>
@@ -8084,7 +8085,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152" s="2" t="s">
         <v>10</v>
       </c>
@@ -8114,7 +8115,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153" s="2" t="s">
         <v>10</v>
       </c>
@@ -8144,7 +8145,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A154" s="2" t="s">
         <v>10</v>
       </c>
@@ -8174,7 +8175,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A155" s="2" t="s">
         <v>10</v>
       </c>
@@ -8204,7 +8205,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A156" s="2" t="s">
         <v>10</v>
       </c>
@@ -8234,7 +8235,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A157" s="2" t="s">
         <v>10</v>
       </c>
@@ -8264,7 +8265,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A158" s="2" t="s">
         <v>10</v>
       </c>
@@ -8294,7 +8295,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159" s="2" t="s">
         <v>10</v>
       </c>
@@ -8324,7 +8325,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A160" s="2" t="s">
         <v>10</v>
       </c>
@@ -8354,7 +8355,7 @@
         <v>AP350.png</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A161" s="2" t="s">
         <v>10</v>
       </c>
@@ -8384,7 +8385,7 @@
         <v>AP350.png</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A162" s="2" t="s">
         <v>10</v>
       </c>
@@ -8414,7 +8415,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A163" s="2" t="s">
         <v>10</v>
       </c>
@@ -8444,7 +8445,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A164" s="2" t="s">
         <v>10</v>
       </c>
@@ -8474,7 +8475,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A165" s="2" t="s">
         <v>10</v>
       </c>
@@ -8504,7 +8505,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A166" s="2" t="s">
         <v>10</v>
       </c>
@@ -8534,7 +8535,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A167" s="2" t="s">
         <v>10</v>
       </c>
@@ -8564,7 +8565,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A168" s="2" t="s">
         <v>10</v>
       </c>
@@ -8594,7 +8595,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A169" s="2" t="s">
         <v>10</v>
       </c>
@@ -8624,7 +8625,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A170" s="2" t="s">
         <v>10</v>
       </c>
@@ -8654,7 +8655,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A171" s="2" t="s">
         <v>10</v>
       </c>
@@ -8684,7 +8685,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A172" s="2" t="s">
         <v>10</v>
       </c>
@@ -8714,7 +8715,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A173" s="2" t="s">
         <v>10</v>
       </c>
@@ -8744,7 +8745,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A174" s="2" t="s">
         <v>10</v>
       </c>
@@ -8774,7 +8775,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A175" s="2" t="s">
         <v>10</v>
       </c>
@@ -8804,7 +8805,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A176" s="2" t="s">
         <v>10</v>
       </c>
@@ -8834,7 +8835,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A177" s="2" t="s">
         <v>10</v>
       </c>
@@ -8864,7 +8865,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A178" s="2" t="s">
         <v>10</v>
       </c>
@@ -8894,7 +8895,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A179" s="2" t="s">
         <v>10</v>
       </c>
@@ -8924,7 +8925,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A180" s="2" t="s">
         <v>10</v>
       </c>
@@ -8954,7 +8955,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A181" s="2" t="s">
         <v>10</v>
       </c>
@@ -8984,7 +8985,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A182" s="2" t="s">
         <v>10</v>
       </c>
@@ -9014,7 +9015,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A183" s="2" t="s">
         <v>10</v>
       </c>
@@ -9044,7 +9045,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A184" s="2" t="s">
         <v>10</v>
       </c>
@@ -9074,7 +9075,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A185" s="2" t="s">
         <v>10</v>
       </c>
@@ -9104,7 +9105,7 @@
         <v>STE269.png</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A186" s="2" t="s">
         <v>10</v>
       </c>
@@ -9134,7 +9135,7 @@
         <v>STE269.png</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A187" s="2" t="s">
         <v>10</v>
       </c>
@@ -9164,7 +9165,7 @@
         <v>STE269.png</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A188" s="2" t="s">
         <v>10</v>
       </c>
@@ -9194,7 +9195,7 @@
         <v>STE269.png</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A189" s="2" t="s">
         <v>10</v>
       </c>
@@ -9224,7 +9225,7 @@
         <v>BUD350.png</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A190" s="2" t="s">
         <v>10</v>
       </c>
@@ -9254,7 +9255,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A191" s="2" t="s">
         <v>10</v>
       </c>
@@ -9284,7 +9285,7 @@
         <v>BUD350.png</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A192" s="2" t="s">
         <v>10</v>
       </c>
@@ -9314,7 +9315,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A193" s="2" t="s">
         <v>10</v>
       </c>
@@ -9344,7 +9345,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A194" s="2" t="s">
         <v>10</v>
       </c>
@@ -9374,7 +9375,7 @@
         <v>BUD350.png</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A195" s="2" t="s">
         <v>10</v>
       </c>
@@ -9404,7 +9405,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A196" s="2" t="s">
         <v>10</v>
       </c>
@@ -9434,7 +9435,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A197" s="2" t="s">
         <v>10</v>
       </c>
@@ -9464,7 +9465,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A198" s="2" t="s">
         <v>10</v>
       </c>
@@ -9494,7 +9495,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A199" s="2" t="s">
         <v>10</v>
       </c>
@@ -9524,7 +9525,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A200" s="2" t="s">
         <v>10</v>
       </c>
@@ -9554,7 +9555,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A201" s="2" t="s">
         <v>10</v>
       </c>
@@ -9584,7 +9585,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A202" s="2" t="s">
         <v>10</v>
       </c>
@@ -9614,7 +9615,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A203" s="2" t="s">
         <v>10</v>
       </c>
@@ -9644,7 +9645,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A204" s="2" t="s">
         <v>10</v>
       </c>
@@ -9674,7 +9675,7 @@
         <v>COR269.png</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A205" s="2" t="s">
         <v>10</v>
       </c>
@@ -9704,7 +9705,7 @@
         <v>COR269.png</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A206" s="2" t="s">
         <v>10</v>
       </c>
@@ -9734,7 +9735,7 @@
         <v>COR269.png</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A207" s="2" t="s">
         <v>10</v>
       </c>
@@ -9764,7 +9765,7 @@
         <v>COR269.png</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A208" s="2" t="s">
         <v>10</v>
       </c>
@@ -9794,7 +9795,7 @@
         <v>STE350.png</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A209" s="2" t="s">
         <v>10</v>
       </c>
@@ -9824,7 +9825,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A210" s="2" t="s">
         <v>10</v>
       </c>
@@ -9854,7 +9855,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A211" s="2" t="s">
         <v>10</v>
       </c>
@@ -9884,7 +9885,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A212" s="2" t="s">
         <v>10</v>
       </c>
@@ -9914,7 +9915,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A213" s="2" t="s">
         <v>10</v>
       </c>
@@ -9944,7 +9945,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A214" s="2" t="s">
         <v>10</v>
       </c>
@@ -9974,7 +9975,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A215" s="2" t="s">
         <v>10</v>
       </c>
@@ -10004,7 +10005,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A216" s="2" t="s">
         <v>10</v>
       </c>
@@ -10034,7 +10035,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A217" s="2" t="s">
         <v>10</v>
       </c>
@@ -10064,7 +10065,7 @@
         <v>STE350.png</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A218" s="2" t="s">
         <v>10</v>
       </c>
@@ -10094,7 +10095,7 @@
         <v>STE350.png</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A219" s="2" t="s">
         <v>10</v>
       </c>
@@ -10124,7 +10125,7 @@
         <v>STE350.png</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A220" s="2" t="s">
         <v>10</v>
       </c>
@@ -10154,7 +10155,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A221" s="2" t="s">
         <v>10</v>
       </c>
@@ -10184,7 +10185,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A222" s="2" t="s">
         <v>10</v>
       </c>
@@ -10214,7 +10215,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A223" s="2" t="s">
         <v>10</v>
       </c>
@@ -10244,7 +10245,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A224" s="2" t="s">
         <v>10</v>
       </c>
@@ -10274,7 +10275,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A225" s="2" t="s">
         <v>10</v>
       </c>
@@ -10304,7 +10305,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A226" s="2" t="s">
         <v>10</v>
       </c>
@@ -10334,7 +10335,7 @@
         <v>STE350.png</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A227" s="2" t="s">
         <v>10</v>
       </c>
@@ -10364,7 +10365,7 @@
         <v>COR350.png</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A228" s="2" t="s">
         <v>10</v>
       </c>
@@ -10394,7 +10395,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A229" s="2" t="s">
         <v>10</v>
       </c>
@@ -10424,7 +10425,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A230" s="2" t="s">
         <v>10</v>
       </c>
@@ -10454,7 +10455,7 @@
         <v>COR350.png</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A231" s="2" t="s">
         <v>10</v>
       </c>
@@ -10484,7 +10485,7 @@
         <v>COR350.png</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A232" s="2" t="s">
         <v>10</v>
       </c>
@@ -10514,7 +10515,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A233" s="2" t="s">
         <v>10</v>
       </c>
@@ -10544,7 +10545,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A234" s="2" t="s">
         <v>10</v>
       </c>
@@ -10574,7 +10575,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A235" s="2" t="s">
         <v>10</v>
       </c>
@@ -10604,7 +10605,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A236" s="2" t="s">
         <v>10</v>
       </c>
@@ -10634,7 +10635,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A237" s="2" t="s">
         <v>10</v>
       </c>
@@ -10664,7 +10665,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A238" s="2" t="s">
         <v>10</v>
       </c>
@@ -10694,7 +10695,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A239" s="2" t="s">
         <v>10</v>
       </c>
@@ -10724,7 +10725,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A240" s="2" t="s">
         <v>10</v>
       </c>
@@ -10754,7 +10755,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A241" s="2" t="s">
         <v>10</v>
       </c>
@@ -10784,7 +10785,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A242" s="2" t="s">
         <v>10</v>
       </c>
@@ -10814,7 +10815,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A243" s="2" t="s">
         <v>10</v>
       </c>
@@ -10844,7 +10845,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A244" s="2" t="s">
         <v>10</v>
       </c>
@@ -10874,7 +10875,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A245" s="2" t="s">
         <v>10</v>
       </c>
@@ -10904,7 +10905,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A246" s="2" t="s">
         <v>10</v>
       </c>
@@ -10934,7 +10935,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A247" s="2" t="s">
         <v>10</v>
       </c>
@@ -10964,7 +10965,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A248" s="2" t="s">
         <v>10</v>
       </c>
@@ -10994,7 +10995,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A249" s="2" t="s">
         <v>10</v>
       </c>
@@ -11024,7 +11025,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A250" s="2" t="s">
         <v>10</v>
       </c>
@@ -11054,7 +11055,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A251" s="2" t="s">
         <v>10</v>
       </c>
@@ -11084,7 +11085,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A252" s="2" t="s">
         <v>10</v>
       </c>
@@ -11114,7 +11115,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A253" s="2" t="s">
         <v>10</v>
       </c>
@@ -11144,7 +11145,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A254" s="2" t="s">
         <v>10</v>
       </c>
@@ -11174,7 +11175,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A255" s="2" t="s">
         <v>10</v>
       </c>
@@ -11204,7 +11205,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A256" s="2" t="s">
         <v>10</v>
       </c>
@@ -11234,7 +11235,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A257" s="2" t="s">
         <v>10</v>
       </c>
@@ -11264,7 +11265,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A258" s="2" t="s">
         <v>10</v>
       </c>
@@ -11294,7 +11295,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A259" s="2" t="s">
         <v>10</v>
       </c>
@@ -11324,7 +11325,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A260" s="2" t="s">
         <v>10</v>
       </c>
@@ -11354,7 +11355,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A261" s="2" t="s">
         <v>10</v>
       </c>
@@ -11384,7 +11385,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A262" s="2" t="s">
         <v>10</v>
       </c>
@@ -11414,7 +11415,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A263" s="2" t="s">
         <v>10</v>
       </c>
@@ -11444,7 +11445,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A264" s="2" t="s">
         <v>10</v>
       </c>
@@ -11474,7 +11475,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A265" s="2" t="s">
         <v>10</v>
       </c>
@@ -11504,7 +11505,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A266" s="2" t="s">
         <v>10</v>
       </c>
@@ -11534,7 +11535,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A267" s="2" t="s">
         <v>10</v>
       </c>
@@ -11564,7 +11565,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A268" s="2" t="s">
         <v>10</v>
       </c>
@@ -11594,7 +11595,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A269" s="2" t="s">
         <v>10</v>
       </c>
@@ -11624,7 +11625,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A270" s="2" t="s">
         <v>10</v>
       </c>
@@ -11654,7 +11655,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A271" s="2" t="s">
         <v>10</v>
       </c>
@@ -11684,7 +11685,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A272" s="2" t="s">
         <v>10</v>
       </c>
@@ -11714,7 +11715,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A273" s="2" t="s">
         <v>10</v>
       </c>
@@ -11744,7 +11745,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A274" s="2" t="s">
         <v>10</v>
       </c>
@@ -11774,7 +11775,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A275" s="2" t="s">
         <v>10</v>
       </c>
@@ -11804,7 +11805,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A276" s="2" t="s">
         <v>10</v>
       </c>
@@ -11834,7 +11835,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A277" s="2" t="s">
         <v>10</v>
       </c>
@@ -11864,7 +11865,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A278" s="2" t="s">
         <v>10</v>
       </c>
@@ -11894,7 +11895,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A279" s="2" t="s">
         <v>10</v>
       </c>
@@ -11924,7 +11925,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A280" s="2" t="s">
         <v>10</v>
       </c>
@@ -11954,7 +11955,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A281" s="2" t="s">
         <v>10</v>
       </c>
@@ -11984,7 +11985,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A282" s="2" t="s">
         <v>10</v>
       </c>
@@ -12014,7 +12015,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A283" s="2" t="s">
         <v>10</v>
       </c>
@@ -12044,7 +12045,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A284" s="2" t="s">
         <v>10</v>
       </c>
@@ -12074,7 +12075,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A285" s="2" t="s">
         <v>10</v>
       </c>
@@ -12104,7 +12105,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A286" s="2" t="s">
         <v>10</v>
       </c>
@@ -12134,7 +12135,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A287" s="2" t="s">
         <v>10</v>
       </c>
@@ -12164,7 +12165,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A288" s="2" t="s">
         <v>10</v>
       </c>
@@ -12194,7 +12195,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A289" s="2" t="s">
         <v>10</v>
       </c>
@@ -12224,7 +12225,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A290" s="2" t="s">
         <v>10</v>
       </c>
@@ -12254,7 +12255,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A291" s="2" t="s">
         <v>10</v>
       </c>
@@ -12284,7 +12285,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A292" s="2" t="s">
         <v>10</v>
       </c>
@@ -12314,7 +12315,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A293" s="2" t="s">
         <v>10</v>
       </c>
@@ -12344,7 +12345,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A294" s="2" t="s">
         <v>10</v>
       </c>
@@ -12374,7 +12375,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A295" s="2" t="s">
         <v>10</v>
       </c>
@@ -12404,7 +12405,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A296" s="2" t="s">
         <v>10</v>
       </c>
@@ -12434,7 +12435,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A297" s="2" t="s">
         <v>10</v>
       </c>
@@ -12464,7 +12465,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A298" s="2" t="s">
         <v>10</v>
       </c>
@@ -12494,7 +12495,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A299" s="2" t="s">
         <v>10</v>
       </c>
@@ -12524,7 +12525,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A300" s="2" t="s">
         <v>10</v>
       </c>
@@ -12554,7 +12555,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A301" s="2" t="s">
         <v>10</v>
       </c>
@@ -12584,7 +12585,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A302" s="2" t="s">
         <v>10</v>
       </c>
@@ -12614,7 +12615,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A303" s="2" t="s">
         <v>10</v>
       </c>
@@ -12644,7 +12645,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A304" s="2" t="s">
         <v>10</v>
       </c>
@@ -12674,7 +12675,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A305" s="2" t="s">
         <v>10</v>
       </c>
@@ -12704,7 +12705,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A306" s="2" t="s">
         <v>10</v>
       </c>
@@ -12734,7 +12735,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A307" s="2" t="s">
         <v>10</v>
       </c>
@@ -12764,7 +12765,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A308" s="2" t="s">
         <v>10</v>
       </c>
@@ -12794,7 +12795,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A309" s="2" t="s">
         <v>10</v>
       </c>
@@ -12824,7 +12825,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A310" s="2" t="s">
         <v>10</v>
       </c>
@@ -12854,7 +12855,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A311" s="2" t="s">
         <v>10</v>
       </c>
@@ -12884,7 +12885,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A312" s="2" t="s">
         <v>10</v>
       </c>
@@ -12914,7 +12915,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A313" s="2" t="s">
         <v>10</v>
       </c>
@@ -12944,7 +12945,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A314" s="2" t="s">
         <v>10</v>
       </c>
@@ -12974,7 +12975,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A315" s="2" t="s">
         <v>10</v>
       </c>
@@ -13004,7 +13005,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A316" s="2" t="s">
         <v>103</v>
       </c>
@@ -13034,7 +13035,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A317" s="2" t="s">
         <v>103</v>
       </c>
@@ -13064,7 +13065,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A318" s="2" t="s">
         <v>103</v>
       </c>
@@ -13094,7 +13095,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A319" s="2" t="s">
         <v>103</v>
       </c>
@@ -13124,7 +13125,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A320" s="2" t="s">
         <v>103</v>
       </c>
@@ -13154,7 +13155,7 @@
         <v>AP269.png</v>
       </c>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A321" s="2" t="s">
         <v>103</v>
       </c>
@@ -13184,7 +13185,7 @@
         <v>AP269.png</v>
       </c>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A322" s="2" t="s">
         <v>103</v>
       </c>
@@ -13214,7 +13215,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A323" s="2" t="s">
         <v>103</v>
       </c>
@@ -13244,7 +13245,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A324" s="2" t="s">
         <v>103</v>
       </c>
@@ -13274,7 +13275,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A325" s="2" t="s">
         <v>103</v>
       </c>
@@ -13304,7 +13305,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A326" s="2" t="s">
         <v>103</v>
       </c>
@@ -13334,7 +13335,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A327" s="2" t="s">
         <v>103</v>
       </c>
@@ -13364,7 +13365,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A328" s="2" t="s">
         <v>103</v>
       </c>
@@ -13394,7 +13395,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A329" s="2" t="s">
         <v>103</v>
       </c>
@@ -13424,7 +13425,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A330" s="2" t="s">
         <v>103</v>
       </c>
@@ -13454,7 +13455,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A331" s="2" t="s">
         <v>103</v>
       </c>
@@ -13484,7 +13485,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A332" s="2" t="s">
         <v>103</v>
       </c>
@@ -13514,7 +13515,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A333" s="2" t="s">
         <v>103</v>
       </c>
@@ -13544,7 +13545,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A334" s="2" t="s">
         <v>103</v>
       </c>
@@ -13574,7 +13575,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A335" s="2" t="s">
         <v>103</v>
       </c>
@@ -13604,7 +13605,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A336" s="2" t="s">
         <v>103</v>
       </c>
@@ -13634,7 +13635,7 @@
         <v>AP269.png</v>
       </c>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A337" s="2" t="s">
         <v>103</v>
       </c>
@@ -13664,7 +13665,7 @@
         <v>AP269.png</v>
       </c>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A338" s="2" t="s">
         <v>103</v>
       </c>
@@ -13694,7 +13695,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A339" s="2" t="s">
         <v>103</v>
       </c>
@@ -13724,7 +13725,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A340" s="2" t="s">
         <v>103</v>
       </c>
@@ -13754,7 +13755,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A341" s="2" t="s">
         <v>103</v>
       </c>
@@ -13784,7 +13785,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A342" s="2" t="s">
         <v>103</v>
       </c>
@@ -13814,7 +13815,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A343" s="2" t="s">
         <v>103</v>
       </c>
@@ -13844,7 +13845,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A344" s="2" t="s">
         <v>103</v>
       </c>
@@ -13874,7 +13875,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A345" s="2" t="s">
         <v>103</v>
       </c>
@@ -13904,7 +13905,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A346" s="2" t="s">
         <v>103</v>
       </c>
@@ -13934,7 +13935,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A347" s="2" t="s">
         <v>103</v>
       </c>
@@ -13964,7 +13965,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A348" s="2" t="s">
         <v>103</v>
       </c>
@@ -13994,7 +13995,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A349" s="2" t="s">
         <v>103</v>
       </c>
@@ -14024,7 +14025,7 @@
         <v>BC350.png</v>
       </c>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A350" s="2" t="s">
         <v>103</v>
       </c>
@@ -14054,7 +14055,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A351" s="2" t="s">
         <v>103</v>
       </c>
@@ -14084,7 +14085,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A352" s="2" t="s">
         <v>103</v>
       </c>
@@ -14114,7 +14115,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A353" s="2" t="s">
         <v>103</v>
       </c>
@@ -14144,7 +14145,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A354" s="2" t="s">
         <v>103</v>
       </c>
@@ -14174,7 +14175,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A355" s="2" t="s">
         <v>103</v>
       </c>
@@ -14204,7 +14205,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A356" s="2" t="s">
         <v>103</v>
       </c>
@@ -14234,7 +14235,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A357" s="2" t="s">
         <v>103</v>
       </c>
@@ -14264,7 +14265,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A358" s="2" t="s">
         <v>103</v>
       </c>
@@ -14294,7 +14295,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A359" s="2" t="s">
         <v>103</v>
       </c>
@@ -14324,7 +14325,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A360" s="2" t="s">
         <v>103</v>
       </c>
@@ -14354,7 +14355,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A361" s="2" t="s">
         <v>103</v>
       </c>
@@ -14384,7 +14385,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A362" s="2" t="s">
         <v>103</v>
       </c>
@@ -14414,7 +14415,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A363" s="2" t="s">
         <v>103</v>
       </c>
@@ -14444,7 +14445,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A364" s="2" t="s">
         <v>103</v>
       </c>
@@ -14474,7 +14475,7 @@
         <v>BC350.png</v>
       </c>
     </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A365" s="2" t="s">
         <v>103</v>
       </c>
@@ -14504,7 +14505,7 @@
         <v>AP350.png</v>
       </c>
     </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A366" s="2" t="s">
         <v>103</v>
       </c>
@@ -14534,7 +14535,7 @@
         <v>AP350.png</v>
       </c>
     </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A367" s="2" t="s">
         <v>103</v>
       </c>
@@ -14564,7 +14565,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A368" s="2" t="s">
         <v>103</v>
       </c>
@@ -14594,7 +14595,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A369" s="2" t="s">
         <v>103</v>
       </c>
@@ -14624,7 +14625,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A370" s="2" t="s">
         <v>103</v>
       </c>
@@ -14654,7 +14655,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A371" s="2" t="s">
         <v>103</v>
       </c>
@@ -14684,7 +14685,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A372" s="2" t="s">
         <v>103</v>
       </c>
@@ -14714,7 +14715,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A373" s="2" t="s">
         <v>103</v>
       </c>
@@ -14744,7 +14745,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A374" s="2" t="s">
         <v>103</v>
       </c>
@@ -14774,7 +14775,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A375" s="2" t="s">
         <v>103</v>
       </c>
@@ -14804,7 +14805,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A376" s="2" t="s">
         <v>103</v>
       </c>
@@ -14834,7 +14835,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A377" s="2" t="s">
         <v>103</v>
       </c>
@@ -14864,7 +14865,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A378" s="2" t="s">
         <v>103</v>
       </c>
@@ -14894,7 +14895,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A379" s="2" t="s">
         <v>103</v>
       </c>
@@ -14924,7 +14925,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="380" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A380" s="2" t="s">
         <v>103</v>
       </c>
@@ -14954,7 +14955,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A381" s="2" t="s">
         <v>103</v>
       </c>
@@ -14984,7 +14985,7 @@
         <v>SPT269.png</v>
       </c>
     </row>
-    <row r="382" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A382" s="2" t="s">
         <v>103</v>
       </c>
@@ -15014,7 +15015,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="383" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A383" s="2" t="s">
         <v>103</v>
       </c>
@@ -15044,7 +15045,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="384" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A384" s="2" t="s">
         <v>103</v>
       </c>
@@ -15074,7 +15075,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="385" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A385" s="2" t="s">
         <v>103</v>
       </c>
@@ -15104,7 +15105,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="386" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A386" s="2" t="s">
         <v>103</v>
       </c>
@@ -15134,7 +15135,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="387" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A387" s="2" t="s">
         <v>103</v>
       </c>
@@ -15164,7 +15165,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="388" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A388" s="2" t="s">
         <v>103</v>
       </c>
@@ -15194,7 +15195,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="389" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A389" s="2" t="s">
         <v>103</v>
       </c>
@@ -15224,7 +15225,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="390" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A390" s="2" t="s">
         <v>103</v>
       </c>
@@ -15254,7 +15255,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="391" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A391" s="2" t="s">
         <v>103</v>
       </c>
@@ -15284,7 +15285,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="392" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A392" s="2" t="s">
         <v>103</v>
       </c>
@@ -15314,7 +15315,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="393" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A393" s="2" t="s">
         <v>103</v>
       </c>
@@ -15344,7 +15345,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="394" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A394" s="2" t="s">
         <v>103</v>
       </c>
@@ -15374,7 +15375,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="395" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A395" s="2" t="s">
         <v>103</v>
       </c>
@@ -15404,7 +15405,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="396" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A396" s="2" t="s">
         <v>103</v>
       </c>
@@ -15434,7 +15435,7 @@
         <v>SPT269.png</v>
       </c>
     </row>
-    <row r="397" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A397" s="2" t="s">
         <v>103</v>
       </c>
@@ -15464,7 +15465,7 @@
         <v>SPT269.png</v>
       </c>
     </row>
-    <row r="398" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A398" s="2" t="s">
         <v>103</v>
       </c>
@@ -15494,7 +15495,7 @@
         <v>SPT269.png</v>
       </c>
     </row>
-    <row r="399" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A399" s="2" t="s">
         <v>103</v>
       </c>
@@ -15524,7 +15525,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="400" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A400" s="2" t="s">
         <v>103</v>
       </c>
@@ -15554,7 +15555,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="401" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A401" s="2" t="s">
         <v>103</v>
       </c>
@@ -15584,7 +15585,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="402" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A402" s="2" t="s">
         <v>103</v>
       </c>
@@ -15614,7 +15615,7 @@
         <v>BUD350.png</v>
       </c>
     </row>
-    <row r="403" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A403" s="2" t="s">
         <v>103</v>
       </c>
@@ -15644,7 +15645,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="404" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A404" s="2" t="s">
         <v>103</v>
       </c>
@@ -15674,7 +15675,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="405" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A405" s="2" t="s">
         <v>103</v>
       </c>
@@ -15704,7 +15705,7 @@
         <v>BUD350.png</v>
       </c>
     </row>
-    <row r="406" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A406" s="2" t="s">
         <v>103</v>
       </c>
@@ -15734,7 +15735,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="407" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A407" s="2" t="s">
         <v>103</v>
       </c>
@@ -15764,7 +15765,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="408" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A408" s="2" t="s">
         <v>103</v>
       </c>
@@ -15794,7 +15795,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="409" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A409" s="2" t="s">
         <v>103</v>
       </c>
@@ -15824,7 +15825,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="410" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A410" s="2" t="s">
         <v>103</v>
       </c>
@@ -15854,7 +15855,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="411" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A411" s="2" t="s">
         <v>103</v>
       </c>
@@ -15884,7 +15885,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="412" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A412" s="2" t="s">
         <v>103</v>
       </c>
@@ -15914,7 +15915,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="413" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A413" s="2" t="s">
         <v>103</v>
       </c>
@@ -15944,7 +15945,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="414" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A414" s="2" t="s">
         <v>103</v>
       </c>
@@ -15974,7 +15975,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="415" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A415" s="2" t="s">
         <v>103</v>
       </c>
@@ -16004,7 +16005,7 @@
         <v>BUD350.png</v>
       </c>
     </row>
-    <row r="416" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A416" s="2" t="s">
         <v>103</v>
       </c>
@@ -16034,7 +16035,7 @@
         <v>COR269.png</v>
       </c>
     </row>
-    <row r="417" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A417" s="2" t="s">
         <v>103</v>
       </c>
@@ -16064,7 +16065,7 @@
         <v>COR269.png</v>
       </c>
     </row>
-    <row r="418" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A418" s="2" t="s">
         <v>103</v>
       </c>
@@ -16094,7 +16095,7 @@
         <v>COR269.png</v>
       </c>
     </row>
-    <row r="419" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A419" s="2" t="s">
         <v>103</v>
       </c>
@@ -16124,7 +16125,7 @@
         <v>COR269.png</v>
       </c>
     </row>
-    <row r="420" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A420" s="2" t="s">
         <v>103</v>
       </c>
@@ -16154,7 +16155,7 @@
         <v>SPT350.png</v>
       </c>
     </row>
-    <row r="421" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A421" s="2" t="s">
         <v>103</v>
       </c>
@@ -16184,7 +16185,7 @@
         <v>SPT350.png</v>
       </c>
     </row>
-    <row r="422" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A422" s="2" t="s">
         <v>103</v>
       </c>
@@ -16214,7 +16215,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="423" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A423" s="2" t="s">
         <v>103</v>
       </c>
@@ -16244,7 +16245,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="424" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A424" s="2" t="s">
         <v>103</v>
       </c>
@@ -16274,7 +16275,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="425" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A425" s="2" t="s">
         <v>103</v>
       </c>
@@ -16304,7 +16305,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="426" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A426" s="2" t="s">
         <v>103</v>
       </c>
@@ -16334,7 +16335,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="427" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A427" s="2" t="s">
         <v>103</v>
       </c>
@@ -16364,7 +16365,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="428" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A428" s="2" t="s">
         <v>103</v>
       </c>
@@ -16394,7 +16395,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="429" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A429" s="2" t="s">
         <v>103</v>
       </c>
@@ -16424,7 +16425,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="430" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A430" s="2" t="s">
         <v>103</v>
       </c>
@@ -16454,7 +16455,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="431" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A431" s="2" t="s">
         <v>103</v>
       </c>
@@ -16484,7 +16485,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="432" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A432" s="2" t="s">
         <v>103</v>
       </c>
@@ -16514,7 +16515,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="433" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A433" s="2" t="s">
         <v>103</v>
       </c>
@@ -16544,7 +16545,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="434" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A434" s="2" t="s">
         <v>103</v>
       </c>
@@ -16574,7 +16575,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="435" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A435" s="2" t="s">
         <v>103</v>
       </c>
@@ -16604,7 +16605,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="436" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A436" s="2" t="s">
         <v>103</v>
       </c>
@@ -16634,7 +16635,7 @@
         <v>COR350.png</v>
       </c>
     </row>
-    <row r="437" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A437" s="2" t="s">
         <v>103</v>
       </c>
@@ -16664,7 +16665,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="438" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A438" s="2" t="s">
         <v>103</v>
       </c>
@@ -16694,7 +16695,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="439" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A439" s="2" t="s">
         <v>103</v>
       </c>
@@ -16724,7 +16725,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="440" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A440" s="2" t="s">
         <v>103</v>
       </c>
@@ -16754,7 +16755,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="441" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A441" s="2" t="s">
         <v>103</v>
       </c>
@@ -16784,7 +16785,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="442" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A442" s="2" t="s">
         <v>103</v>
       </c>
@@ -16814,7 +16815,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="443" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A443" s="2" t="s">
         <v>103</v>
       </c>
@@ -16844,7 +16845,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="444" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A444" s="2" t="s">
         <v>103</v>
       </c>
@@ -16874,7 +16875,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="445" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A445" s="2" t="s">
         <v>103</v>
       </c>
@@ -16904,7 +16905,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="446" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A446" s="2" t="s">
         <v>103</v>
       </c>
@@ -16934,7 +16935,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="447" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A447" s="2" t="s">
         <v>103</v>
       </c>
@@ -16964,7 +16965,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="448" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A448" s="2" t="s">
         <v>103</v>
       </c>
@@ -16994,7 +16995,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="449" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A449" s="2" t="s">
         <v>103</v>
       </c>
@@ -17024,7 +17025,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="450" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A450" s="2" t="s">
         <v>103</v>
       </c>
@@ -17054,7 +17055,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="451" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A451" s="2" t="s">
         <v>103</v>
       </c>
@@ -17084,7 +17085,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="452" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A452" s="2" t="s">
         <v>103</v>
       </c>
@@ -17114,7 +17115,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="453" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A453" s="2" t="s">
         <v>103</v>
       </c>
@@ -17144,7 +17145,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="454" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A454" s="2" t="s">
         <v>103</v>
       </c>
@@ -17174,7 +17175,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="455" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A455" s="2" t="s">
         <v>103</v>
       </c>
@@ -17204,7 +17205,7 @@
         <v>COR350.png</v>
       </c>
     </row>
-    <row r="456" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A456" s="2" t="s">
         <v>103</v>
       </c>
@@ -17234,7 +17235,7 @@
         <v>COR350.png</v>
       </c>
     </row>
-    <row r="457" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A457" s="2" t="s">
         <v>103</v>
       </c>
@@ -17264,7 +17265,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="458" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A458" s="2" t="s">
         <v>103</v>
       </c>
@@ -17294,7 +17295,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="459" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A459" s="2" t="s">
         <v>103</v>
       </c>
@@ -17324,7 +17325,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="460" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A460" s="2" t="s">
         <v>103</v>
       </c>
@@ -17354,7 +17355,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="461" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A461" s="2" t="s">
         <v>103</v>
       </c>
@@ -17384,7 +17385,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="462" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A462" s="2" t="s">
         <v>103</v>
       </c>
@@ -17414,7 +17415,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="463" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A463" s="2" t="s">
         <v>103</v>
       </c>
@@ -17444,7 +17445,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="464" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A464" s="2" t="s">
         <v>103</v>
       </c>
@@ -17474,7 +17475,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="465" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A465" s="2" t="s">
         <v>103</v>
       </c>
@@ -17504,7 +17505,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="466" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A466" s="2" t="s">
         <v>103</v>
       </c>
@@ -17534,7 +17535,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="467" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A467" s="2" t="s">
         <v>103</v>
       </c>
@@ -17564,7 +17565,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="468" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A468" s="2" t="s">
         <v>103</v>
       </c>
@@ -17594,7 +17595,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="469" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A469" s="2" t="s">
         <v>103</v>
       </c>
@@ -17624,7 +17625,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="470" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A470" s="2" t="s">
         <v>103</v>
       </c>
@@ -17654,7 +17655,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="471" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A471" s="2" t="s">
         <v>103</v>
       </c>
@@ -17684,7 +17685,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="472" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A472" s="2" t="s">
         <v>103</v>
       </c>
@@ -17714,7 +17715,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="473" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A473" s="2" t="s">
         <v>103</v>
       </c>
@@ -17744,7 +17745,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="474" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A474" s="2" t="s">
         <v>103</v>
       </c>
@@ -17774,7 +17775,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="475" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A475" s="2" t="s">
         <v>103</v>
       </c>
@@ -17804,7 +17805,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="476" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A476" s="2" t="s">
         <v>103</v>
       </c>
@@ -17834,7 +17835,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="477" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A477" s="2" t="s">
         <v>103</v>
       </c>
@@ -17864,7 +17865,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="478" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A478" s="2" t="s">
         <v>103</v>
       </c>
@@ -17894,7 +17895,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="479" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A479" s="2" t="s">
         <v>103</v>
       </c>
@@ -17924,7 +17925,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="480" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A480" s="2" t="s">
         <v>103</v>
       </c>
@@ -17954,7 +17955,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="481" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A481" s="2" t="s">
         <v>103</v>
       </c>
@@ -17984,7 +17985,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="482" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A482" s="2" t="s">
         <v>103</v>
       </c>
@@ -18014,7 +18015,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="483" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A483" s="2" t="s">
         <v>103</v>
       </c>
@@ -18044,7 +18045,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="484" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A484" s="2" t="s">
         <v>103</v>
       </c>
@@ -18074,7 +18075,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="485" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A485" s="2" t="s">
         <v>103</v>
       </c>
@@ -18104,7 +18105,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="486" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A486" s="2" t="s">
         <v>103</v>
       </c>
@@ -18134,7 +18135,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="487" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A487" s="2" t="s">
         <v>103</v>
       </c>
@@ -18164,7 +18165,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="488" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A488" s="2" t="s">
         <v>103</v>
       </c>
@@ -18194,7 +18195,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="489" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A489" s="2" t="s">
         <v>103</v>
       </c>
@@ -18224,7 +18225,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="490" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A490" s="2" t="s">
         <v>103</v>
       </c>
@@ -18254,7 +18255,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="491" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A491" s="2" t="s">
         <v>103</v>
       </c>
@@ -18284,7 +18285,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="492" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A492" s="2" t="s">
         <v>103</v>
       </c>
@@ -18314,7 +18315,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="493" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A493" s="2" t="s">
         <v>103</v>
       </c>
@@ -18344,7 +18345,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="494" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A494" s="2" t="s">
         <v>103</v>
       </c>
@@ -18374,7 +18375,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="495" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A495" s="2" t="s">
         <v>103</v>
       </c>
@@ -18404,7 +18405,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="496" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A496" s="2" t="s">
         <v>103</v>
       </c>
@@ -18434,7 +18435,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="497" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A497" s="2" t="s">
         <v>103</v>
       </c>
@@ -18464,7 +18465,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="498" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A498" s="2" t="s">
         <v>103</v>
       </c>
@@ -18494,7 +18495,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="499" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A499" s="2" t="s">
         <v>103</v>
       </c>
@@ -18524,7 +18525,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="500" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A500" s="2" t="s">
         <v>103</v>
       </c>
@@ -18554,7 +18555,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="501" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A501" s="2" t="s">
         <v>103</v>
       </c>
@@ -18584,7 +18585,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="502" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A502" s="2" t="s">
         <v>103</v>
       </c>
@@ -18614,7 +18615,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="503" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A503" s="2" t="s">
         <v>103</v>
       </c>
@@ -18644,7 +18645,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="504" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A504" s="2" t="s">
         <v>103</v>
       </c>
@@ -18674,7 +18675,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="505" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A505" s="2" t="s">
         <v>103</v>
       </c>
@@ -18704,7 +18705,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="506" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A506" s="2" t="s">
         <v>103</v>
       </c>
@@ -18734,7 +18735,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="507" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A507" s="2" t="s">
         <v>103</v>
       </c>
@@ -18764,7 +18765,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="508" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A508" s="2" t="s">
         <v>103</v>
       </c>
@@ -18794,7 +18795,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="509" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A509" s="2" t="s">
         <v>103</v>
       </c>
@@ -18824,7 +18825,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="510" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A510" s="2" t="s">
         <v>103</v>
       </c>
@@ -18854,7 +18855,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="511" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A511" s="2" t="s">
         <v>99</v>
       </c>
@@ -18884,7 +18885,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="512" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A512" s="2" t="s">
         <v>99</v>
       </c>
@@ -18914,7 +18915,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="513" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A513" s="2" t="s">
         <v>99</v>
       </c>
@@ -18944,7 +18945,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="514" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A514" s="2" t="s">
         <v>99</v>
       </c>
@@ -18974,7 +18975,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="515" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A515" s="2" t="s">
         <v>99</v>
       </c>
@@ -19004,7 +19005,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="516" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A516" s="2" t="s">
         <v>99</v>
       </c>
@@ -19034,7 +19035,7 @@
         <v>AP269.png</v>
       </c>
     </row>
-    <row r="517" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A517" s="2" t="s">
         <v>99</v>
       </c>
@@ -19064,7 +19065,7 @@
         <v>AP269.png</v>
       </c>
     </row>
-    <row r="518" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A518" s="2" t="s">
         <v>99</v>
       </c>
@@ -19094,7 +19095,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="519" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A519" s="2" t="s">
         <v>99</v>
       </c>
@@ -19124,7 +19125,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="520" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A520" s="2" t="s">
         <v>99</v>
       </c>
@@ -19154,7 +19155,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="521" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A521" s="2" t="s">
         <v>99</v>
       </c>
@@ -19184,7 +19185,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="522" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A522" s="2" t="s">
         <v>99</v>
       </c>
@@ -19214,7 +19215,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="523" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A523" s="2" t="s">
         <v>99</v>
       </c>
@@ -19244,7 +19245,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="524" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A524" s="2" t="s">
         <v>99</v>
       </c>
@@ -19274,7 +19275,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="525" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A525" s="2" t="s">
         <v>99</v>
       </c>
@@ -19304,7 +19305,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="526" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A526" s="2" t="s">
         <v>99</v>
       </c>
@@ -19334,7 +19335,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="527" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A527" s="2" t="s">
         <v>99</v>
       </c>
@@ -19364,7 +19365,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="528" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A528" s="2" t="s">
         <v>99</v>
       </c>
@@ -19394,7 +19395,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="529" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A529" s="2" t="s">
         <v>99</v>
       </c>
@@ -19424,7 +19425,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="530" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A530" s="2" t="s">
         <v>99</v>
       </c>
@@ -19454,7 +19455,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="531" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A531" s="2" t="s">
         <v>99</v>
       </c>
@@ -19484,7 +19485,7 @@
         <v>AP269.png</v>
       </c>
     </row>
-    <row r="532" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A532" s="2" t="s">
         <v>99</v>
       </c>
@@ -19514,7 +19515,7 @@
         <v>AP269.png</v>
       </c>
     </row>
-    <row r="533" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A533" s="2" t="s">
         <v>99</v>
       </c>
@@ -19544,7 +19545,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="534" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A534" s="2" t="s">
         <v>99</v>
       </c>
@@ -19574,7 +19575,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="535" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A535" s="2" t="s">
         <v>99</v>
       </c>
@@ -19604,7 +19605,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="536" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A536" s="2" t="s">
         <v>99</v>
       </c>
@@ -19634,7 +19635,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="537" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A537" s="2" t="s">
         <v>99</v>
       </c>
@@ -19664,7 +19665,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="538" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A538" s="2" t="s">
         <v>99</v>
       </c>
@@ -19694,7 +19695,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="539" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A539" s="2" t="s">
         <v>99</v>
       </c>
@@ -19724,7 +19725,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="540" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A540" s="2" t="s">
         <v>99</v>
       </c>
@@ -19754,7 +19755,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="541" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A541" s="2" t="s">
         <v>99</v>
       </c>
@@ -19784,7 +19785,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="542" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A542" s="2" t="s">
         <v>99</v>
       </c>
@@ -19814,7 +19815,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="543" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A543" s="2" t="s">
         <v>99</v>
       </c>
@@ -19844,7 +19845,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="544" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A544" s="2" t="s">
         <v>99</v>
       </c>
@@ -19874,7 +19875,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="545" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A545" s="2" t="s">
         <v>99</v>
       </c>
@@ -19904,7 +19905,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="546" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A546" s="2" t="s">
         <v>99</v>
       </c>
@@ -19934,7 +19935,7 @@
         <v>BC350.png</v>
       </c>
     </row>
-    <row r="547" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A547" s="2" t="s">
         <v>99</v>
       </c>
@@ -19964,7 +19965,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="548" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A548" s="2" t="s">
         <v>99</v>
       </c>
@@ -19994,7 +19995,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="549" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A549" s="2" t="s">
         <v>99</v>
       </c>
@@ -20024,7 +20025,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="550" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A550" s="2" t="s">
         <v>99</v>
       </c>
@@ -20054,7 +20055,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="551" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A551" s="2" t="s">
         <v>99</v>
       </c>
@@ -20084,7 +20085,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="552" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A552" s="2" t="s">
         <v>99</v>
       </c>
@@ -20114,7 +20115,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="553" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A553" s="2" t="s">
         <v>99</v>
       </c>
@@ -20144,7 +20145,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="554" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A554" s="2" t="s">
         <v>99</v>
       </c>
@@ -20174,7 +20175,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="555" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A555" s="2" t="s">
         <v>99</v>
       </c>
@@ -20204,7 +20205,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="556" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A556" s="2" t="s">
         <v>99</v>
       </c>
@@ -20234,7 +20235,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="557" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A557" s="2" t="s">
         <v>99</v>
       </c>
@@ -20264,7 +20265,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="558" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A558" s="2" t="s">
         <v>99</v>
       </c>
@@ -20294,7 +20295,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="559" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A559" s="2" t="s">
         <v>99</v>
       </c>
@@ -20324,7 +20325,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="560" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A560" s="2" t="s">
         <v>99</v>
       </c>
@@ -20354,7 +20355,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="561" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A561" s="2" t="s">
         <v>99</v>
       </c>
@@ -20384,7 +20385,7 @@
         <v>BC350.png</v>
       </c>
     </row>
-    <row r="562" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A562" s="2" t="s">
         <v>99</v>
       </c>
@@ -20414,7 +20415,7 @@
         <v>AP350.png</v>
       </c>
     </row>
-    <row r="563" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A563" s="2" t="s">
         <v>99</v>
       </c>
@@ -20444,7 +20445,7 @@
         <v>AP350.png</v>
       </c>
     </row>
-    <row r="564" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A564" s="2" t="s">
         <v>99</v>
       </c>
@@ -20474,7 +20475,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="565" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A565" s="2" t="s">
         <v>99</v>
       </c>
@@ -20504,7 +20505,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="566" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A566" s="2" t="s">
         <v>99</v>
       </c>
@@ -20534,7 +20535,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="567" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A567" s="2" t="s">
         <v>99</v>
       </c>
@@ -20564,7 +20565,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="568" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A568" s="2" t="s">
         <v>99</v>
       </c>
@@ -20594,7 +20595,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="569" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A569" s="2" t="s">
         <v>99</v>
       </c>
@@ -20624,7 +20625,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="570" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A570" s="2" t="s">
         <v>99</v>
       </c>
@@ -20654,7 +20655,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="571" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A571" s="2" t="s">
         <v>99</v>
       </c>
@@ -20684,7 +20685,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="572" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A572" s="2" t="s">
         <v>99</v>
       </c>
@@ -20714,7 +20715,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="573" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A573" s="2" t="s">
         <v>99</v>
       </c>
@@ -20744,7 +20745,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="574" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A574" s="2" t="s">
         <v>99</v>
       </c>
@@ -20774,7 +20775,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="575" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A575" s="2" t="s">
         <v>99</v>
       </c>
@@ -20804,7 +20805,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="576" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A576" s="2" t="s">
         <v>99</v>
       </c>
@@ -20834,7 +20835,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="577" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A577" s="2" t="s">
         <v>99</v>
       </c>
@@ -20864,7 +20865,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="578" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A578" s="2" t="s">
         <v>99</v>
       </c>
@@ -20894,7 +20895,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="579" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A579" s="2" t="s">
         <v>99</v>
       </c>
@@ -20924,7 +20925,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="580" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A580" s="2" t="s">
         <v>99</v>
       </c>
@@ -20954,7 +20955,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="581" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A581" s="2" t="s">
         <v>99</v>
       </c>
@@ -20984,7 +20985,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="582" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A582" s="2" t="s">
         <v>99</v>
       </c>
@@ -21014,7 +21015,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="583" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A583" s="2" t="s">
         <v>99</v>
       </c>
@@ -21044,7 +21045,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="584" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A584" s="2" t="s">
         <v>99</v>
       </c>
@@ -21074,7 +21075,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="585" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A585" s="2" t="s">
         <v>99</v>
       </c>
@@ -21104,7 +21105,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="586" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A586" s="2" t="s">
         <v>99</v>
       </c>
@@ -21134,7 +21135,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="587" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A587" s="2" t="s">
         <v>99</v>
       </c>
@@ -21164,7 +21165,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="588" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A588" s="2" t="s">
         <v>99</v>
       </c>
@@ -21194,7 +21195,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="589" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A589" s="2" t="s">
         <v>99</v>
       </c>
@@ -21224,7 +21225,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="590" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A590" s="2" t="s">
         <v>99</v>
       </c>
@@ -21254,7 +21255,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="591" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A591" s="2" t="s">
         <v>99</v>
       </c>
@@ -21284,7 +21285,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="592" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A592" s="2" t="s">
         <v>99</v>
       </c>
@@ -21314,7 +21315,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="593" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A593" s="2" t="s">
         <v>99</v>
       </c>
@@ -21344,7 +21345,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="594" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="594" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A594" s="2" t="s">
         <v>99</v>
       </c>
@@ -21374,7 +21375,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="595" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="595" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A595" s="2" t="s">
         <v>99</v>
       </c>
@@ -21404,7 +21405,7 @@
         <v>BUD350.png</v>
       </c>
     </row>
-    <row r="596" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A596" s="2" t="s">
         <v>99</v>
       </c>
@@ -21434,7 +21435,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="597" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A597" s="2" t="s">
         <v>99</v>
       </c>
@@ -21464,7 +21465,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="598" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="598" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A598" s="2" t="s">
         <v>99</v>
       </c>
@@ -21494,7 +21495,7 @@
         <v>BUD350.png</v>
       </c>
     </row>
-    <row r="599" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="599" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A599" s="2" t="s">
         <v>99</v>
       </c>
@@ -21524,7 +21525,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="600" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="600" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A600" s="2" t="s">
         <v>99</v>
       </c>
@@ -21554,7 +21555,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="601" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="601" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A601" s="2" t="s">
         <v>99</v>
       </c>
@@ -21584,7 +21585,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="602" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="602" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A602" s="2" t="s">
         <v>99</v>
       </c>
@@ -21614,7 +21615,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="603" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A603" s="2" t="s">
         <v>99</v>
       </c>
@@ -21644,7 +21645,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="604" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="604" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A604" s="2" t="s">
         <v>99</v>
       </c>
@@ -21674,7 +21675,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="605" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A605" s="2" t="s">
         <v>99</v>
       </c>
@@ -21704,7 +21705,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="606" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A606" s="2" t="s">
         <v>99</v>
       </c>
@@ -21734,7 +21735,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="607" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A607" s="2" t="s">
         <v>99</v>
       </c>
@@ -21764,7 +21765,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="608" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A608" s="2" t="s">
         <v>99</v>
       </c>
@@ -21794,7 +21795,7 @@
         <v>BUD350.png</v>
       </c>
     </row>
-    <row r="609" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="609" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A609" s="2" t="s">
         <v>99</v>
       </c>
@@ -21824,7 +21825,7 @@
         <v>SPT269.png</v>
       </c>
     </row>
-    <row r="610" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A610" s="2" t="s">
         <v>99</v>
       </c>
@@ -21854,7 +21855,7 @@
         <v>SPT269.png</v>
       </c>
     </row>
-    <row r="611" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="611" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A611" s="2" t="s">
         <v>99</v>
       </c>
@@ -21884,7 +21885,7 @@
         <v>SPT269.png</v>
       </c>
     </row>
-    <row r="612" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="612" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A612" s="2" t="s">
         <v>99</v>
       </c>
@@ -21914,7 +21915,7 @@
         <v>SPT269.png</v>
       </c>
     </row>
-    <row r="613" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="613" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A613" s="2" t="s">
         <v>99</v>
       </c>
@@ -21944,7 +21945,7 @@
         <v>COR269.png</v>
       </c>
     </row>
-    <row r="614" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="614" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A614" s="2" t="s">
         <v>99</v>
       </c>
@@ -21974,7 +21975,7 @@
         <v>COR269.png</v>
       </c>
     </row>
-    <row r="615" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="615" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A615" s="2" t="s">
         <v>99</v>
       </c>
@@ -22004,7 +22005,7 @@
         <v>COR269.png</v>
       </c>
     </row>
-    <row r="616" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="616" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A616" s="2" t="s">
         <v>99</v>
       </c>
@@ -22034,7 +22035,7 @@
         <v>COR269.png</v>
       </c>
     </row>
-    <row r="617" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="617" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A617" s="2" t="s">
         <v>99</v>
       </c>
@@ -22064,7 +22065,7 @@
         <v>SPT350.png</v>
       </c>
     </row>
-    <row r="618" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="618" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A618" s="2" t="s">
         <v>99</v>
       </c>
@@ -22094,7 +22095,7 @@
         <v>SPT350.png</v>
       </c>
     </row>
-    <row r="619" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="619" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A619" s="2" t="s">
         <v>99</v>
       </c>
@@ -22124,7 +22125,7 @@
         <v>SPT350.png</v>
       </c>
     </row>
-    <row r="620" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="620" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A620" s="2" t="s">
         <v>99</v>
       </c>
@@ -22154,7 +22155,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="621" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="621" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A621" s="2" t="s">
         <v>99</v>
       </c>
@@ -22184,7 +22185,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="622" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="622" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A622" s="2" t="s">
         <v>99</v>
       </c>
@@ -22214,7 +22215,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="623" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="623" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A623" s="2" t="s">
         <v>99</v>
       </c>
@@ -22244,7 +22245,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="624" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="624" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A624" s="2" t="s">
         <v>99</v>
       </c>
@@ -22274,7 +22275,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="625" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="625" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A625" s="2" t="s">
         <v>99</v>
       </c>
@@ -22304,7 +22305,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="626" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="626" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A626" s="2" t="s">
         <v>99</v>
       </c>
@@ -22334,7 +22335,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="627" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="627" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A627" s="2" t="s">
         <v>99</v>
       </c>
@@ -22364,7 +22365,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="628" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="628" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A628" s="2" t="s">
         <v>99</v>
       </c>
@@ -22394,7 +22395,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="629" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="629" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A629" s="2" t="s">
         <v>99</v>
       </c>
@@ -22424,7 +22425,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="630" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="630" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A630" s="2" t="s">
         <v>99</v>
       </c>
@@ -22454,7 +22455,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="631" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="631" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A631" s="2" t="s">
         <v>99</v>
       </c>
@@ -22484,7 +22485,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="632" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="632" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A632" s="2" t="s">
         <v>99</v>
       </c>
@@ -22514,7 +22515,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="633" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="633" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A633" s="2" t="s">
         <v>99</v>
       </c>
@@ -22544,7 +22545,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="634" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="634" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A634" s="2" t="s">
         <v>99</v>
       </c>
@@ -22574,7 +22575,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="635" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="635" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A635" s="2" t="s">
         <v>99</v>
       </c>
@@ -22604,7 +22605,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="636" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="636" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A636" s="2" t="s">
         <v>99</v>
       </c>
@@ -22634,7 +22635,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="637" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="637" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A637" s="2" t="s">
         <v>99</v>
       </c>
@@ -22664,7 +22665,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="638" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="638" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A638" s="2" t="s">
         <v>99</v>
       </c>
@@ -22694,7 +22695,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="639" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="639" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A639" s="2" t="s">
         <v>99</v>
       </c>
@@ -22724,7 +22725,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="640" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="640" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A640" s="2" t="s">
         <v>99</v>
       </c>
@@ -22754,7 +22755,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="641" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="641" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A641" s="2" t="s">
         <v>99</v>
       </c>
@@ -22784,7 +22785,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="642" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="642" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A642" s="2" t="s">
         <v>99</v>
       </c>
@@ -22814,7 +22815,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="643" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="643" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A643" s="2" t="s">
         <v>99</v>
       </c>
@@ -22844,7 +22845,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="644" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="644" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A644" s="2" t="s">
         <v>99</v>
       </c>
@@ -22874,7 +22875,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="645" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="645" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A645" s="2" t="s">
         <v>99</v>
       </c>
@@ -22904,7 +22905,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="646" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="646" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A646" s="2" t="s">
         <v>99</v>
       </c>
@@ -22934,7 +22935,7 @@
         <v>COR350.png</v>
       </c>
     </row>
-    <row r="647" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="647" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A647" s="2" t="s">
         <v>99</v>
       </c>
@@ -22964,7 +22965,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="648" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="648" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A648" s="2" t="s">
         <v>99</v>
       </c>
@@ -22994,7 +22995,7 @@
         <v>COR350.png</v>
       </c>
     </row>
-    <row r="649" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="649" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A649" s="2" t="s">
         <v>99</v>
       </c>
@@ -23024,7 +23025,7 @@
         <v>COR350.png</v>
       </c>
     </row>
-    <row r="650" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="650" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A650" s="2" t="s">
         <v>99</v>
       </c>
@@ -23054,7 +23055,7 @@
         <v>COR350.png</v>
       </c>
     </row>
-    <row r="651" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="651" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A651" s="2" t="s">
         <v>99</v>
       </c>
@@ -23084,7 +23085,7 @@
         <v>COR350.png</v>
       </c>
     </row>
-    <row r="652" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="652" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A652" s="2" t="s">
         <v>99</v>
       </c>
@@ -23114,7 +23115,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="653" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="653" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A653" s="2" t="s">
         <v>99</v>
       </c>
@@ -23144,7 +23145,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="654" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="654" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A654" s="2" t="s">
         <v>99</v>
       </c>
@@ -23174,7 +23175,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="655" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="655" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A655" s="2" t="s">
         <v>99</v>
       </c>
@@ -23204,7 +23205,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="656" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="656" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A656" s="2" t="s">
         <v>99</v>
       </c>
@@ -23234,7 +23235,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="657" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="657" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A657" s="2" t="s">
         <v>99</v>
       </c>
@@ -23264,7 +23265,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="658" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="658" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A658" s="2" t="s">
         <v>99</v>
       </c>
@@ -23294,7 +23295,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="659" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="659" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A659" s="2" t="s">
         <v>99</v>
       </c>
@@ -23324,7 +23325,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="660" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="660" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A660" s="2" t="s">
         <v>99</v>
       </c>
@@ -23354,7 +23355,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="661" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="661" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A661" s="2" t="s">
         <v>99</v>
       </c>
@@ -23384,7 +23385,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="662" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="662" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A662" s="2" t="s">
         <v>99</v>
       </c>
@@ -23414,7 +23415,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="663" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="663" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A663" s="2" t="s">
         <v>99</v>
       </c>
@@ -23444,7 +23445,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="664" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="664" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A664" s="2" t="s">
         <v>99</v>
       </c>
@@ -23474,7 +23475,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="665" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="665" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A665" s="2" t="s">
         <v>99</v>
       </c>
@@ -23504,7 +23505,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="666" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="666" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A666" s="2" t="s">
         <v>99</v>
       </c>
@@ -23534,7 +23535,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="667" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="667" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A667" s="2" t="s">
         <v>99</v>
       </c>
@@ -23564,7 +23565,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="668" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="668" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A668" s="2" t="s">
         <v>99</v>
       </c>
@@ -23594,7 +23595,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="669" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="669" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A669" s="2" t="s">
         <v>99</v>
       </c>
@@ -23624,7 +23625,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="670" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="670" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A670" s="2" t="s">
         <v>99</v>
       </c>
@@ -23654,7 +23655,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="671" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="671" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A671" s="2" t="s">
         <v>99</v>
       </c>
@@ -23684,7 +23685,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="672" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="672" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A672" s="2" t="s">
         <v>99</v>
       </c>
@@ -23714,7 +23715,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="673" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="673" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A673" s="2" t="s">
         <v>99</v>
       </c>
@@ -23744,7 +23745,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="674" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="674" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A674" s="2" t="s">
         <v>99</v>
       </c>
@@ -23774,7 +23775,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="675" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="675" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A675" s="2" t="s">
         <v>99</v>
       </c>
@@ -23804,7 +23805,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="676" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="676" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A676" s="2" t="s">
         <v>99</v>
       </c>
@@ -23834,7 +23835,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="677" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="677" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A677" s="2" t="s">
         <v>99</v>
       </c>
@@ -23864,7 +23865,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="678" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="678" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A678" s="2" t="s">
         <v>99</v>
       </c>
@@ -23894,7 +23895,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="679" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="679" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A679" s="2" t="s">
         <v>99</v>
       </c>
@@ -23924,7 +23925,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="680" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="680" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A680" s="2" t="s">
         <v>99</v>
       </c>
@@ -23954,7 +23955,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="681" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="681" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A681" s="2" t="s">
         <v>99</v>
       </c>
@@ -23984,7 +23985,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="682" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="682" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A682" s="2" t="s">
         <v>99</v>
       </c>
@@ -24014,7 +24015,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="683" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="683" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A683" s="2" t="s">
         <v>99</v>
       </c>
@@ -24044,7 +24045,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="684" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="684" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A684" s="2" t="s">
         <v>99</v>
       </c>
@@ -24074,7 +24075,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="685" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="685" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A685" s="2" t="s">
         <v>99</v>
       </c>
@@ -24104,7 +24105,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="686" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="686" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A686" s="2" t="s">
         <v>99</v>
       </c>
@@ -24134,7 +24135,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="687" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="687" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A687" s="2" t="s">
         <v>99</v>
       </c>
@@ -24164,7 +24165,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="688" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="688" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A688" s="2" t="s">
         <v>99</v>
       </c>
@@ -24194,7 +24195,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="689" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="689" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A689" s="2" t="s">
         <v>99</v>
       </c>
@@ -24224,7 +24225,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="690" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="690" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A690" s="2" t="s">
         <v>99</v>
       </c>
@@ -24254,7 +24255,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="691" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="691" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A691" s="2" t="s">
         <v>99</v>
       </c>
@@ -24284,7 +24285,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="692" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="692" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A692" s="2" t="s">
         <v>99</v>
       </c>
@@ -24314,7 +24315,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="693" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="693" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A693" s="2" t="s">
         <v>99</v>
       </c>
@@ -24344,7 +24345,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="694" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="694" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A694" s="2" t="s">
         <v>99</v>
       </c>
@@ -24374,7 +24375,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="695" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="695" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A695" s="2" t="s">
         <v>99</v>
       </c>
@@ -24404,7 +24405,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="696" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="696" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A696" s="2" t="s">
         <v>99</v>
       </c>
@@ -24434,7 +24435,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="697" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="697" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A697" s="2" t="s">
         <v>99</v>
       </c>
@@ -24464,7 +24465,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="698" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="698" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A698" s="2" t="s">
         <v>99</v>
       </c>
@@ -24494,7 +24495,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="699" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="699" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A699" s="2" t="s">
         <v>99</v>
       </c>
@@ -24524,7 +24525,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="700" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="700" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A700" s="2" t="s">
         <v>99</v>
       </c>
@@ -24554,7 +24555,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="701" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="701" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A701" s="2" t="s">
         <v>99</v>
       </c>
@@ -24584,7 +24585,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="702" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="702" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A702" s="2" t="s">
         <v>99</v>
       </c>
@@ -24614,7 +24615,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="703" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="703" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A703" s="2" t="s">
         <v>99</v>
       </c>
@@ -24644,7 +24645,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="704" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="704" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A704" s="2" t="s">
         <v>99</v>
       </c>
@@ -24674,7 +24675,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="705" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="705" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A705" s="2" t="s">
         <v>99</v>
       </c>
@@ -24704,7 +24705,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="706" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="706" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A706" s="2" t="s">
         <v>99</v>
       </c>
@@ -24734,7 +24735,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="707" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="707" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A707" s="2" t="s">
         <v>99</v>
       </c>
@@ -24764,7 +24765,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="708" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="708" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A708" s="2" t="s">
         <v>99</v>
       </c>
@@ -24794,7 +24795,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="709" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="709" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A709" s="2" t="s">
         <v>99</v>
       </c>
@@ -24824,7 +24825,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="710" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="710" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A710" s="2" t="s">
         <v>99</v>
       </c>
@@ -24854,7 +24855,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="711" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="711" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A711" s="2" t="s">
         <v>102</v>
       </c>
@@ -24884,7 +24885,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="712" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="712" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A712" s="2" t="s">
         <v>102</v>
       </c>
@@ -24914,7 +24915,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="713" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="713" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A713" s="2" t="s">
         <v>102</v>
       </c>
@@ -24944,7 +24945,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="714" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="714" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A714" s="2" t="s">
         <v>102</v>
       </c>
@@ -24974,7 +24975,7 @@
         <v>AP269.png</v>
       </c>
     </row>
-    <row r="715" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="715" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A715" s="2" t="s">
         <v>102</v>
       </c>
@@ -25004,7 +25005,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="716" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="716" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A716" s="2" t="s">
         <v>102</v>
       </c>
@@ -25034,7 +25035,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="717" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="717" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A717" s="2" t="s">
         <v>102</v>
       </c>
@@ -25064,7 +25065,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="718" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="718" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A718" s="2" t="s">
         <v>102</v>
       </c>
@@ -25094,7 +25095,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="719" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="719" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A719" s="2" t="s">
         <v>102</v>
       </c>
@@ -25124,7 +25125,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="720" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="720" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A720" s="2" t="s">
         <v>102</v>
       </c>
@@ -25154,7 +25155,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="721" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="721" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A721" s="2" t="s">
         <v>102</v>
       </c>
@@ -25184,7 +25185,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="722" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="722" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A722" s="2" t="s">
         <v>102</v>
       </c>
@@ -25214,7 +25215,7 @@
         <v>AP350.png</v>
       </c>
     </row>
-    <row r="723" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="723" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A723" s="2" t="s">
         <v>102</v>
       </c>
@@ -25244,7 +25245,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="724" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="724" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A724" s="2" t="s">
         <v>102</v>
       </c>
@@ -25274,7 +25275,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="725" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="725" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A725" s="2" t="s">
         <v>102</v>
       </c>
@@ -25304,7 +25305,7 @@
         <v>SPT350.png</v>
       </c>
     </row>
-    <row r="726" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="726" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A726" s="2" t="s">
         <v>102</v>
       </c>
@@ -25334,7 +25335,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="727" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="727" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A727" s="2" t="s">
         <v>102</v>
       </c>
@@ -25364,7 +25365,7 @@
         <v>BUD350.png</v>
       </c>
     </row>
-    <row r="728" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="728" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A728" s="2" t="s">
         <v>102</v>
       </c>
@@ -25394,7 +25395,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="729" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="729" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A729" s="2" t="s">
         <v>102</v>
       </c>
@@ -25424,7 +25425,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="730" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="730" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A730" s="2" t="s">
         <v>102</v>
       </c>
@@ -25454,7 +25455,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="731" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="731" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A731" s="2" t="s">
         <v>102</v>
       </c>
@@ -25484,7 +25485,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="732" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="732" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A732" s="2" t="s">
         <v>102</v>
       </c>
@@ -25514,7 +25515,7 @@
         <v>COR350.png</v>
       </c>
     </row>
-    <row r="733" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="733" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A733" s="2" t="s">
         <v>102</v>
       </c>
@@ -25544,7 +25545,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="734" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="734" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A734" s="2" t="s">
         <v>102</v>
       </c>
@@ -25574,7 +25575,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="735" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="735" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A735" s="2" t="s">
         <v>102</v>
       </c>
@@ -25604,7 +25605,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="736" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="736" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A736" s="2" t="s">
         <v>102</v>
       </c>
@@ -25634,7 +25635,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="737" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="737" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A737" s="2" t="s">
         <v>102</v>
       </c>
@@ -25664,7 +25665,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="738" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="738" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A738" s="2" t="s">
         <v>102</v>
       </c>
@@ -25694,7 +25695,7 @@
         <v>AP269.png</v>
       </c>
     </row>
-    <row r="739" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="739" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A739" s="2" t="s">
         <v>102</v>
       </c>
@@ -25724,7 +25725,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="740" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="740" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A740" s="2" t="s">
         <v>102</v>
       </c>
@@ -25754,7 +25755,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="741" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="741" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A741" s="2" t="s">
         <v>102</v>
       </c>
@@ -25784,7 +25785,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="742" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="742" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A742" s="2" t="s">
         <v>102</v>
       </c>
@@ -25814,7 +25815,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="743" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="743" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A743" s="2" t="s">
         <v>102</v>
       </c>
@@ -25844,7 +25845,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="744" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="744" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A744" s="2" t="s">
         <v>102</v>
       </c>
@@ -25874,7 +25875,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="745" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="745" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A745" s="2" t="s">
         <v>102</v>
       </c>
@@ -25904,7 +25905,7 @@
         <v>AP350.png</v>
       </c>
     </row>
-    <row r="746" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="746" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A746" s="2" t="s">
         <v>102</v>
       </c>
@@ -25934,7 +25935,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="747" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="747" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A747" s="2" t="s">
         <v>102</v>
       </c>
@@ -25964,7 +25965,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="748" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="748" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A748" s="2" t="s">
         <v>102</v>
       </c>
@@ -25994,7 +25995,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="749" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="749" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A749" s="2" t="s">
         <v>102</v>
       </c>
@@ -26024,7 +26025,7 @@
         <v>SPT350.png</v>
       </c>
     </row>
-    <row r="750" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="750" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A750" s="2" t="s">
         <v>102</v>
       </c>
@@ -26054,7 +26055,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="751" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="751" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A751" s="2" t="s">
         <v>102</v>
       </c>
@@ -26084,7 +26085,7 @@
         <v>BUD350.png</v>
       </c>
     </row>
-    <row r="752" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="752" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A752" s="2" t="s">
         <v>102</v>
       </c>
@@ -26114,7 +26115,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="753" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="753" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A753" s="2" t="s">
         <v>102</v>
       </c>
@@ -26144,7 +26145,7 @@
         <v>BC350.png</v>
       </c>
     </row>
-    <row r="754" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="754" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A754" s="2" t="s">
         <v>102</v>
       </c>
@@ -26174,7 +26175,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="755" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="755" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A755" s="2" t="s">
         <v>102</v>
       </c>
@@ -26204,7 +26205,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="756" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="756" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A756" s="2" t="s">
         <v>102</v>
       </c>
@@ -26234,7 +26235,7 @@
         <v>COR350.png</v>
       </c>
     </row>
-    <row r="757" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="757" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A757" s="2" t="s">
         <v>102</v>
       </c>
@@ -26264,7 +26265,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="758" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="758" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A758" s="2" t="s">
         <v>102</v>
       </c>
@@ -26294,7 +26295,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="759" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="759" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A759" s="2" t="s">
         <v>102</v>
       </c>
@@ -26324,7 +26325,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="760" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="760" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A760" s="2" t="s">
         <v>102</v>
       </c>
@@ -26354,7 +26355,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="761" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="761" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A761" s="2" t="s">
         <v>102</v>
       </c>
@@ -26384,7 +26385,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="762" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="762" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A762" s="2" t="s">
         <v>102</v>
       </c>
@@ -26414,7 +26415,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="763" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="763" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A763" s="2" t="s">
         <v>102</v>
       </c>
@@ -26444,7 +26445,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="764" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="764" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A764" s="2" t="s">
         <v>102</v>
       </c>
@@ -26474,7 +26475,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="765" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="765" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A765" s="2" t="s">
         <v>102</v>
       </c>
@@ -26504,7 +26505,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="766" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="766" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A766" s="2" t="s">
         <v>102</v>
       </c>
@@ -26534,7 +26535,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="767" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="767" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A767" s="2" t="s">
         <v>102</v>
       </c>
@@ -26564,7 +26565,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="768" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="768" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A768" s="2" t="s">
         <v>102</v>
       </c>
@@ -26594,7 +26595,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="769" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="769" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A769" s="2" t="s">
         <v>102</v>
       </c>
@@ -26624,7 +26625,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="770" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="770" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A770" s="2" t="s">
         <v>102</v>
       </c>
@@ -26654,7 +26655,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="771" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="771" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A771" s="2" t="s">
         <v>102</v>
       </c>
@@ -26684,7 +26685,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="772" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="772" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A772" s="2" t="s">
         <v>102</v>
       </c>
@@ -26714,7 +26715,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="773" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="773" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A773" s="2" t="s">
         <v>102</v>
       </c>
@@ -26744,7 +26745,7 @@
         <v>SPT269.png</v>
       </c>
     </row>
-    <row r="774" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="774" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A774" s="2" t="s">
         <v>102</v>
       </c>
@@ -26774,7 +26775,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="775" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="775" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A775" s="2" t="s">
         <v>102</v>
       </c>
@@ -26804,7 +26805,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="776" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="776" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A776" s="2" t="s">
         <v>102</v>
       </c>
@@ -26834,7 +26835,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="777" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="777" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A777" s="2" t="s">
         <v>102</v>
       </c>
@@ -26864,7 +26865,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="778" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="778" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A778" s="2" t="s">
         <v>102</v>
       </c>
@@ -26894,7 +26895,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="779" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="779" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A779" s="2" t="s">
         <v>102</v>
       </c>
@@ -26924,7 +26925,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="780" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="780" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A780" s="2" t="s">
         <v>102</v>
       </c>
@@ -26954,7 +26955,7 @@
         <v>COR269.png</v>
       </c>
     </row>
-    <row r="781" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="781" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A781" s="2" t="s">
         <v>102</v>
       </c>
@@ -26984,7 +26985,7 @@
         <v>COR350.png</v>
       </c>
     </row>
-    <row r="782" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="782" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A782" s="2" t="s">
         <v>102</v>
       </c>
@@ -27014,7 +27015,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="783" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="783" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A783" s="2" t="s">
         <v>102</v>
       </c>
@@ -27044,7 +27045,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="784" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="784" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A784" s="2" t="s">
         <v>102</v>
       </c>
@@ -27074,7 +27075,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="785" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="785" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A785" s="2" t="s">
         <v>102</v>
       </c>
@@ -27104,7 +27105,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="786" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="786" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A786" s="2" t="s">
         <v>102</v>
       </c>
@@ -27134,7 +27135,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="787" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="787" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A787" s="2" t="s">
         <v>102</v>
       </c>
@@ -27164,7 +27165,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="788" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="788" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A788" s="2" t="s">
         <v>102</v>
       </c>
@@ -27194,7 +27195,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="789" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="789" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A789" s="2" t="s">
         <v>102</v>
       </c>
@@ -27224,7 +27225,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="790" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="790" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A790" s="2" t="s">
         <v>102</v>
       </c>
@@ -27254,7 +27255,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="791" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="791" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A791" s="2" t="s">
         <v>102</v>
       </c>
@@ -27284,7 +27285,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="792" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="792" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A792" s="2" t="s">
         <v>102</v>
       </c>
@@ -27314,7 +27315,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="793" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="793" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A793" s="2" t="s">
         <v>102</v>
       </c>
@@ -27344,7 +27345,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="794" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="794" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A794" s="2" t="s">
         <v>102</v>
       </c>
@@ -27374,7 +27375,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="795" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="795" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A795" s="2" t="s">
         <v>102</v>
       </c>
@@ -27404,7 +27405,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="796" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="796" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A796" s="2" t="s">
         <v>102</v>
       </c>
@@ -27434,7 +27435,7 @@
         <v>SPT269.png</v>
       </c>
     </row>
-    <row r="797" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="797" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A797" s="2" t="s">
         <v>102</v>
       </c>
@@ -27464,7 +27465,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="798" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="798" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A798" s="2" t="s">
         <v>102</v>
       </c>
@@ -27494,7 +27495,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="799" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="799" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A799" s="2" t="s">
         <v>102</v>
       </c>
@@ -27524,7 +27525,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="800" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="800" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A800" s="2" t="s">
         <v>102</v>
       </c>
@@ -27554,7 +27555,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="801" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="801" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A801" s="2" t="s">
         <v>102</v>
       </c>
@@ -27584,7 +27585,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="802" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="802" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A802" s="2" t="s">
         <v>102</v>
       </c>
@@ -27614,7 +27615,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="803" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="803" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A803" s="2" t="s">
         <v>102</v>
       </c>
@@ -27644,7 +27645,7 @@
         <v>COR269.png</v>
       </c>
     </row>
-    <row r="804" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="804" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A804" s="2" t="s">
         <v>102</v>
       </c>
@@ -27674,7 +27675,7 @@
         <v>COR350.png</v>
       </c>
     </row>
-    <row r="805" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="805" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A805" s="2" t="s">
         <v>102</v>
       </c>
@@ -27704,7 +27705,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="806" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="806" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A806" s="2" t="s">
         <v>102</v>
       </c>
@@ -27734,7 +27735,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="807" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="807" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A807" s="2" t="s">
         <v>102</v>
       </c>
@@ -27764,7 +27765,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="808" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="808" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A808" s="2" t="s">
         <v>102</v>
       </c>
@@ -27794,7 +27795,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="809" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="809" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A809" s="2" t="s">
         <v>102</v>
       </c>
@@ -27824,7 +27825,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="810" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="810" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A810" s="2" t="s">
         <v>102</v>
       </c>
@@ -27854,7 +27855,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="811" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="811" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A811" s="2" t="s">
         <v>102</v>
       </c>
@@ -27884,7 +27885,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="812" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="812" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A812" s="2" t="s">
         <v>102</v>
       </c>
@@ -27914,7 +27915,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="813" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="813" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A813" s="2" t="s">
         <v>102</v>
       </c>
@@ -27944,7 +27945,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="814" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="814" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A814" s="2" t="s">
         <v>102</v>
       </c>
@@ -27974,7 +27975,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="815" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="815" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A815" s="2" t="s">
         <v>102</v>
       </c>
@@ -28004,7 +28005,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="816" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="816" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A816" s="2" t="s">
         <v>102</v>
       </c>
@@ -28034,7 +28035,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="817" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="817" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A817" s="2" t="s">
         <v>102</v>
       </c>
@@ -28064,7 +28065,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="818" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="818" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A818" s="2" t="s">
         <v>102</v>
       </c>
@@ -28094,7 +28095,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="819" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="819" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A819" s="2" t="s">
         <v>102</v>
       </c>
@@ -28124,7 +28125,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="820" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="820" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A820" s="2" t="s">
         <v>102</v>
       </c>
@@ -28154,7 +28155,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="821" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="821" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A821" s="2" t="s">
         <v>102</v>
       </c>
@@ -28184,7 +28185,7 @@
         <v>SPT350.png</v>
       </c>
     </row>
-    <row r="822" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="822" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A822" s="2" t="s">
         <v>102</v>
       </c>
@@ -28214,7 +28215,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="823" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="823" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A823" s="2" t="s">
         <v>102</v>
       </c>
@@ -28244,7 +28245,7 @@
         <v>BUD350.png</v>
       </c>
     </row>
-    <row r="824" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="824" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A824" s="2" t="s">
         <v>102</v>
       </c>
@@ -28274,7 +28275,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="825" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="825" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A825" s="2" t="s">
         <v>102</v>
       </c>
@@ -28304,7 +28305,7 @@
         <v>BC350.png</v>
       </c>
     </row>
-    <row r="826" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="826" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A826" s="2" t="s">
         <v>102</v>
       </c>
@@ -28334,7 +28335,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="827" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="827" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A827" s="2" t="s">
         <v>102</v>
       </c>
@@ -28364,7 +28365,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="828" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="828" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A828" s="2" t="s">
         <v>102</v>
       </c>
@@ -28394,7 +28395,7 @@
         <v>COR350.png</v>
       </c>
     </row>
-    <row r="829" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="829" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A829" s="2" t="s">
         <v>102</v>
       </c>
@@ -28424,7 +28425,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="830" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="830" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A830" s="2" t="s">
         <v>102</v>
       </c>
@@ -28454,7 +28455,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="831" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="831" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A831" s="2" t="s">
         <v>102</v>
       </c>
@@ -28484,7 +28485,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="832" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="832" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A832" s="2" t="s">
         <v>102</v>
       </c>
@@ -28514,7 +28515,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="833" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="833" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A833" s="2" t="s">
         <v>102</v>
       </c>
@@ -28544,7 +28545,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="834" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="834" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A834" s="2" t="s">
         <v>102</v>
       </c>
@@ -28574,7 +28575,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="835" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="835" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A835" s="2" t="s">
         <v>102</v>
       </c>
@@ -28604,7 +28605,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="836" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="836" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A836" s="2" t="s">
         <v>102</v>
       </c>
@@ -28634,7 +28635,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="837" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="837" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A837" s="2" t="s">
         <v>102</v>
       </c>
@@ -28664,7 +28665,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="838" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="838" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A838" s="2" t="s">
         <v>102</v>
       </c>
@@ -28694,7 +28695,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="839" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="839" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A839" s="2" t="s">
         <v>102</v>
       </c>
@@ -28724,7 +28725,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="840" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="840" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A840" s="2" t="s">
         <v>102</v>
       </c>
@@ -28754,7 +28755,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="841" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="841" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A841" s="2" t="s">
         <v>102</v>
       </c>
@@ -28784,7 +28785,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="842" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="842" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A842" s="2" t="s">
         <v>102</v>
       </c>
@@ -28814,7 +28815,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="843" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="843" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A843" s="2" t="s">
         <v>102</v>
       </c>
@@ -28844,7 +28845,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="844" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="844" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A844" s="2" t="s">
         <v>102</v>
       </c>
@@ -28874,7 +28875,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="845" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="845" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A845" s="2" t="s">
         <v>102</v>
       </c>
@@ -28904,7 +28905,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="846" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="846" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A846" s="2" t="s">
         <v>102</v>
       </c>
@@ -28934,7 +28935,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="847" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="847" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A847" s="2" t="s">
         <v>102</v>
       </c>
@@ -28964,7 +28965,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="848" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="848" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A848" s="2" t="s">
         <v>102</v>
       </c>
@@ -28994,7 +28995,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="849" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="849" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A849" s="2" t="s">
         <v>102</v>
       </c>
@@ -29024,7 +29025,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="850" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="850" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A850" s="2" t="s">
         <v>102</v>
       </c>
@@ -29054,7 +29055,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="851" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="851" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A851" s="2" t="s">
         <v>102</v>
       </c>
@@ -29084,7 +29085,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="852" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="852" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A852" s="2" t="s">
         <v>102</v>
       </c>
@@ -29114,7 +29115,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="853" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="853" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A853" s="2" t="s">
         <v>102</v>
       </c>
@@ -29144,7 +29145,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="854" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="854" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A854" s="2" t="s">
         <v>102</v>
       </c>
@@ -29174,7 +29175,7 @@
         <v>SPT269.png</v>
       </c>
     </row>
-    <row r="855" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="855" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A855" s="2" t="s">
         <v>102</v>
       </c>
@@ -29204,7 +29205,7 @@
         <v>SPT269.png</v>
       </c>
     </row>
-    <row r="856" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="856" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A856" s="2" t="s">
         <v>102</v>
       </c>
@@ -29234,7 +29235,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="857" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="857" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A857" s="2" t="s">
         <v>102</v>
       </c>
@@ -29264,7 +29265,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="858" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="858" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A858" s="2" t="s">
         <v>102</v>
       </c>
@@ -29294,7 +29295,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="859" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="859" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A859" s="2" t="s">
         <v>102</v>
       </c>
@@ -29324,7 +29325,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="860" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="860" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A860" s="2" t="s">
         <v>102</v>
       </c>
@@ -29354,7 +29355,7 @@
         <v>COR269.png</v>
       </c>
     </row>
-    <row r="861" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="861" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A861" s="2" t="s">
         <v>102</v>
       </c>
@@ -29384,7 +29385,7 @@
         <v>COR269.png</v>
       </c>
     </row>
-    <row r="862" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="862" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A862" s="2" t="s">
         <v>102</v>
       </c>
@@ -29414,7 +29415,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="863" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="863" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A863" s="2" t="s">
         <v>102</v>
       </c>
@@ -29444,7 +29445,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="864" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="864" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A864" s="2" t="s">
         <v>102</v>
       </c>
@@ -29474,7 +29475,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="865" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="865" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A865" s="2" t="s">
         <v>102</v>
       </c>
@@ -29504,7 +29505,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="866" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="866" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A866" s="2" t="s">
         <v>102</v>
       </c>
@@ -29534,7 +29535,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="867" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="867" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A867" s="2" t="s">
         <v>102</v>
       </c>
@@ -29564,7 +29565,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="868" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="868" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A868" s="2" t="s">
         <v>102</v>
       </c>
@@ -29594,7 +29595,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="869" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="869" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A869" s="2" t="s">
         <v>102</v>
       </c>
@@ -29624,7 +29625,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="870" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="870" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A870" s="2" t="s">
         <v>102</v>
       </c>
@@ -29654,7 +29655,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="871" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="871" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A871" s="2" t="s">
         <v>102</v>
       </c>
@@ -29684,7 +29685,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="872" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="872" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A872" s="2" t="s">
         <v>102</v>
       </c>
@@ -29714,7 +29715,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="873" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="873" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A873" s="2" t="s">
         <v>102</v>
       </c>
@@ -29744,7 +29745,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="874" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="874" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A874" s="2" t="s">
         <v>102</v>
       </c>
@@ -29774,7 +29775,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="875" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="875" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A875" s="2" t="s">
         <v>102</v>
       </c>
@@ -29804,7 +29805,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="876" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="876" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A876" s="2" t="s">
         <v>102</v>
       </c>
@@ -29834,7 +29835,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="877" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="877" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A877" s="2" t="s">
         <v>102</v>
       </c>
@@ -29864,7 +29865,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="878" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="878" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A878" s="2" t="s">
         <v>102</v>
       </c>
@@ -29894,7 +29895,7 @@
         <v>AP269.png</v>
       </c>
     </row>
-    <row r="879" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="879" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A879" s="2" t="s">
         <v>102</v>
       </c>
@@ -29924,7 +29925,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="880" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="880" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A880" s="2" t="s">
         <v>102</v>
       </c>
@@ -29954,7 +29955,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="881" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="881" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A881" s="2" t="s">
         <v>102</v>
       </c>
@@ -29984,7 +29985,7 @@
         <v>AP269.png</v>
       </c>
     </row>
-    <row r="882" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="882" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A882" s="2" t="s">
         <v>102</v>
       </c>
@@ -30014,7 +30015,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="883" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="883" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A883" s="2" t="s">
         <v>102</v>
       </c>
@@ -30044,7 +30045,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="884" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="884" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A884" s="2" t="s">
         <v>102</v>
       </c>
@@ -30074,7 +30075,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="885" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="885" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A885" s="2" t="s">
         <v>102</v>
       </c>
@@ -30104,7 +30105,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="886" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="886" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A886" s="2" t="s">
         <v>102</v>
       </c>
@@ -30134,7 +30135,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="887" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="887" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A887" s="2" t="s">
         <v>102</v>
       </c>
@@ -30164,7 +30165,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="888" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="888" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A888" s="2" t="s">
         <v>102</v>
       </c>
@@ -30194,7 +30195,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="889" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="889" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A889" s="2" t="s">
         <v>102</v>
       </c>
@@ -30224,7 +30225,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="890" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="890" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A890" s="2" t="s">
         <v>102</v>
       </c>
@@ -30254,7 +30255,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="891" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="891" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A891" s="2" t="s">
         <v>102</v>
       </c>
@@ -30284,7 +30285,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="892" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="892" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A892" s="2" t="s">
         <v>102</v>
       </c>
@@ -30314,7 +30315,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="893" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="893" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A893" s="2" t="s">
         <v>102</v>
       </c>
@@ -30344,7 +30345,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="894" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="894" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A894" s="2" t="s">
         <v>102</v>
       </c>
@@ -30374,7 +30375,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="895" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="895" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A895" s="2" t="s">
         <v>102</v>
       </c>
@@ -30404,7 +30405,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="896" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="896" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A896" s="2" t="s">
         <v>102</v>
       </c>
@@ -30434,7 +30435,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="897" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="897" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A897" s="2" t="s">
         <v>102</v>
       </c>
@@ -30464,7 +30465,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="898" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="898" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A898" s="2" t="s">
         <v>98</v>
       </c>
@@ -30494,7 +30495,7 @@
         <v>BEATSLT.png</v>
       </c>
     </row>
-    <row r="899" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="899" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A899" s="2" t="s">
         <v>98</v>
       </c>
@@ -30524,7 +30525,7 @@
         <v>BEATSLT.png</v>
       </c>
     </row>
-    <row r="900" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="900" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A900" s="2" t="s">
         <v>98</v>
       </c>
@@ -30554,7 +30555,7 @@
         <v>BEATSLN.png</v>
       </c>
     </row>
-    <row r="901" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="901" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A901" s="2" t="s">
         <v>98</v>
       </c>
@@ -30584,7 +30585,7 @@
         <v>BEATSLN.png</v>
       </c>
     </row>
-    <row r="902" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="902" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A902" s="2" t="s">
         <v>98</v>
       </c>
@@ -30614,7 +30615,7 @@
         <v>BEATSLT.png</v>
       </c>
     </row>
-    <row r="903" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="903" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A903" s="2" t="s">
         <v>98</v>
       </c>
@@ -30644,7 +30645,7 @@
         <v>BEATSLT.png</v>
       </c>
     </row>
-    <row r="904" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="904" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A904" s="2" t="s">
         <v>98</v>
       </c>
@@ -30674,7 +30675,7 @@
         <v>BEATSLN.png</v>
       </c>
     </row>
-    <row r="905" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="905" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A905" s="2" t="s">
         <v>98</v>
       </c>
@@ -30704,7 +30705,7 @@
         <v>BEATSLN.png</v>
       </c>
     </row>
-    <row r="906" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="906" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A906" s="2" t="s">
         <v>98</v>
       </c>
@@ -30734,7 +30735,7 @@
         <v>FF350.png</v>
       </c>
     </row>
-    <row r="907" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="907" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A907" s="2" t="s">
         <v>98</v>
       </c>
@@ -30764,7 +30765,7 @@
         <v>FFLN.png</v>
       </c>
     </row>
-    <row r="908" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="908" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A908" s="2" t="s">
         <v>98</v>
       </c>
@@ -30794,7 +30795,7 @@
         <v>FF350.png</v>
       </c>
     </row>
-    <row r="909" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="909" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A909" s="2" t="s">
         <v>98</v>
       </c>
@@ -30824,7 +30825,7 @@
         <v>FFLN.png</v>
       </c>
     </row>
-    <row r="910" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="910" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A910" s="2" t="s">
         <v>98</v>
       </c>
@@ -30854,7 +30855,7 @@
         <v>FF350.png</v>
       </c>
     </row>
-    <row r="911" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="911" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A911" s="2" t="s">
         <v>98</v>
       </c>
@@ -30884,7 +30885,7 @@
         <v>FFLN.png</v>
       </c>
     </row>
-    <row r="912" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="912" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A912" s="2" t="s">
         <v>98</v>
       </c>
@@ -30914,7 +30915,7 @@
         <v>FF350.png</v>
       </c>
     </row>
-    <row r="913" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="913" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A913" s="2" t="s">
         <v>98</v>
       </c>
@@ -32044,10 +32045,10 @@
         <v>40</v>
       </c>
       <c r="G950">
-        <v>2.4900000000000002</v>
+        <v>2.39</v>
       </c>
       <c r="H950">
-        <v>2.29</v>
+        <v>2.19</v>
       </c>
       <c r="I950" s="2" t="str">
         <f>_xlfn.XLOOKUP(F950,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -32074,10 +32075,10 @@
         <v>40</v>
       </c>
       <c r="G951">
-        <v>2.4900000000000002</v>
+        <v>2.39</v>
       </c>
       <c r="H951">
-        <v>2.29</v>
+        <v>2.19</v>
       </c>
       <c r="I951" s="2" t="str">
         <f>_xlfn.XLOOKUP(F951,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -32104,10 +32105,10 @@
         <v>40</v>
       </c>
       <c r="G952">
-        <v>2.4900000000000002</v>
+        <v>2.39</v>
       </c>
       <c r="H952">
-        <v>2.29</v>
+        <v>2.19</v>
       </c>
       <c r="I952" s="2" t="str">
         <f>_xlfn.XLOOKUP(F952,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -32134,10 +32135,10 @@
         <v>40</v>
       </c>
       <c r="G953">
-        <v>2.4900000000000002</v>
+        <v>2.39</v>
       </c>
       <c r="H953">
-        <v>2.29</v>
+        <v>2.19</v>
       </c>
       <c r="I953" s="2" t="str">
         <f>_xlfn.XLOOKUP(F953,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -32164,10 +32165,10 @@
         <v>40</v>
       </c>
       <c r="G954">
-        <v>2.4900000000000002</v>
+        <v>2.39</v>
       </c>
       <c r="H954">
-        <v>2.29</v>
+        <v>2.19</v>
       </c>
       <c r="I954" s="2" t="str">
         <f>_xlfn.XLOOKUP(F954,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -32194,10 +32195,10 @@
         <v>41</v>
       </c>
       <c r="G955">
-        <v>2.4900000000000002</v>
+        <v>2.29</v>
       </c>
       <c r="H955">
-        <v>2.29</v>
+        <v>2.09</v>
       </c>
       <c r="I955" s="2" t="str">
         <f>_xlfn.XLOOKUP(F955,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -32224,10 +32225,10 @@
         <v>41</v>
       </c>
       <c r="G956">
-        <v>2.4900000000000002</v>
+        <v>2.29</v>
       </c>
       <c r="H956">
-        <v>2.29</v>
+        <v>2.09</v>
       </c>
       <c r="I956" s="2" t="str">
         <f>_xlfn.XLOOKUP(F956,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -32254,10 +32255,10 @@
         <v>41</v>
       </c>
       <c r="G957">
-        <v>2.4900000000000002</v>
+        <v>2.29</v>
       </c>
       <c r="H957">
-        <v>2.29</v>
+        <v>2.09</v>
       </c>
       <c r="I957" s="2" t="str">
         <f>_xlfn.XLOOKUP(F957,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -32284,10 +32285,10 @@
         <v>41</v>
       </c>
       <c r="G958">
-        <v>2.4900000000000002</v>
+        <v>2.29</v>
       </c>
       <c r="H958">
-        <v>2.29</v>
+        <v>2.09</v>
       </c>
       <c r="I958" s="2" t="str">
         <f>_xlfn.XLOOKUP(F958,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -32314,10 +32315,10 @@
         <v>41</v>
       </c>
       <c r="G959">
-        <v>2.4900000000000002</v>
+        <v>2.29</v>
       </c>
       <c r="H959">
-        <v>2.29</v>
+        <v>2.09</v>
       </c>
       <c r="I959" s="2" t="str">
         <f>_xlfn.XLOOKUP(F959,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -32684,7 +32685,7 @@
         <v>H2OHP1,5.png</v>
       </c>
     </row>
-    <row r="972" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="972" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A972" s="2" t="s">
         <v>98</v>
       </c>
@@ -32714,7 +32715,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="973" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="973" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A973" s="2" t="s">
         <v>98</v>
       </c>
@@ -32744,7 +32745,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="974" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="974" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A974" s="2" t="s">
         <v>98</v>
       </c>
@@ -32774,7 +32775,7 @@
         <v>AP269.png</v>
       </c>
     </row>
-    <row r="975" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="975" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A975" s="2" t="s">
         <v>98</v>
       </c>
@@ -32804,7 +32805,7 @@
         <v>AP269.png</v>
       </c>
     </row>
-    <row r="976" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="976" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A976" s="2" t="s">
         <v>98</v>
       </c>
@@ -32834,7 +32835,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="977" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="977" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A977" s="2" t="s">
         <v>98</v>
       </c>
@@ -32864,7 +32865,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="978" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="978" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A978" s="2" t="s">
         <v>98</v>
       </c>
@@ -32894,7 +32895,7 @@
         <v>AP269.png</v>
       </c>
     </row>
-    <row r="979" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="979" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A979" s="2" t="s">
         <v>98</v>
       </c>
@@ -32924,7 +32925,7 @@
         <v>AP269.png</v>
       </c>
     </row>
-    <row r="980" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="980" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A980" s="2" t="s">
         <v>98</v>
       </c>
@@ -32954,7 +32955,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="981" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="981" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A981" s="2" t="s">
         <v>98</v>
       </c>
@@ -32984,7 +32985,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="982" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="982" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A982" s="2" t="s">
         <v>98</v>
       </c>
@@ -33014,7 +33015,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="983" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="983" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A983" s="2" t="s">
         <v>98</v>
       </c>
@@ -33044,7 +33045,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="984" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="984" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A984" s="2" t="s">
         <v>98</v>
       </c>
@@ -33074,7 +33075,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="985" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="985" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A985" s="2" t="s">
         <v>98</v>
       </c>
@@ -33104,7 +33105,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="986" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="986" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A986" s="2" t="s">
         <v>98</v>
       </c>
@@ -33134,7 +33135,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="987" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="987" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A987" s="2" t="s">
         <v>98</v>
       </c>
@@ -33164,7 +33165,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="988" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="988" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A988" s="2" t="s">
         <v>98</v>
       </c>
@@ -33194,7 +33195,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="989" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="989" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A989" s="2" t="s">
         <v>98</v>
       </c>
@@ -33224,7 +33225,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="990" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="990" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A990" s="2" t="s">
         <v>98</v>
       </c>
@@ -33254,7 +33255,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="991" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="991" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A991" s="2" t="s">
         <v>98</v>
       </c>
@@ -33284,7 +33285,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="992" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="992" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A992" s="2" t="s">
         <v>98</v>
       </c>
@@ -33314,7 +33315,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="993" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="993" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A993" s="2" t="s">
         <v>98</v>
       </c>
@@ -33344,7 +33345,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="994" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="994" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A994" s="2" t="s">
         <v>98</v>
       </c>
@@ -33374,7 +33375,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="995" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="995" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A995" s="2" t="s">
         <v>98</v>
       </c>
@@ -33404,7 +33405,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="996" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="996" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A996" s="2" t="s">
         <v>98</v>
       </c>
@@ -33434,7 +33435,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="997" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="997" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A997" s="2" t="s">
         <v>98</v>
       </c>
@@ -33464,7 +33465,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="998" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="998" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A998" s="2" t="s">
         <v>98</v>
       </c>
@@ -33494,7 +33495,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="999" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="999" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A999" s="2" t="s">
         <v>98</v>
       </c>
@@ -33524,7 +33525,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="1000" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1000" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1000" s="2" t="s">
         <v>98</v>
       </c>
@@ -33554,7 +33555,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="1001" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1001" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1001" s="2" t="s">
         <v>98</v>
       </c>
@@ -33584,7 +33585,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="1002" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1002" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1002" s="2" t="s">
         <v>98</v>
       </c>
@@ -33614,7 +33615,7 @@
         <v>AP269.png</v>
       </c>
     </row>
-    <row r="1003" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1003" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1003" s="2" t="s">
         <v>98</v>
       </c>
@@ -33644,7 +33645,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="1004" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1004" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1004" s="2" t="s">
         <v>98</v>
       </c>
@@ -33674,7 +33675,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="1005" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1005" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1005" s="2" t="s">
         <v>98</v>
       </c>
@@ -33704,7 +33705,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="1006" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1006" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1006" s="2" t="s">
         <v>98</v>
       </c>
@@ -33734,7 +33735,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="1007" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1007" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1007" s="2" t="s">
         <v>98</v>
       </c>
@@ -33764,7 +33765,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="1008" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1008" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1008" s="2" t="s">
         <v>98</v>
       </c>
@@ -33794,7 +33795,7 @@
         <v>AP269.png</v>
       </c>
     </row>
-    <row r="1009" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1009" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1009" s="2" t="s">
         <v>98</v>
       </c>
@@ -33824,7 +33825,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="1010" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1010" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1010" s="2" t="s">
         <v>98</v>
       </c>
@@ -33854,7 +33855,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="1011" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1011" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1011" s="2" t="s">
         <v>98</v>
       </c>
@@ -33884,7 +33885,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="1012" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1012" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1012" s="2" t="s">
         <v>98</v>
       </c>
@@ -33914,7 +33915,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="1013" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1013" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1013" s="2" t="s">
         <v>98</v>
       </c>
@@ -33944,7 +33945,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="1014" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1014" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1014" s="2" t="s">
         <v>98</v>
       </c>
@@ -33974,7 +33975,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="1015" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1015" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1015" s="2" t="s">
         <v>98</v>
       </c>
@@ -34004,7 +34005,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="1016" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1016" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1016" s="2" t="s">
         <v>98</v>
       </c>
@@ -34034,7 +34035,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="1017" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1017" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1017" s="2" t="s">
         <v>98</v>
       </c>
@@ -34064,7 +34065,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="1018" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1018" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1018" s="2" t="s">
         <v>98</v>
       </c>
@@ -34094,7 +34095,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="1019" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1019" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1019" s="2" t="s">
         <v>98</v>
       </c>
@@ -34124,7 +34125,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1020" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1020" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1020" s="2" t="s">
         <v>98</v>
       </c>
@@ -34154,7 +34155,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1021" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1021" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1021" s="2" t="s">
         <v>98</v>
       </c>
@@ -34184,7 +34185,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1022" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1022" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1022" s="2" t="s">
         <v>98</v>
       </c>
@@ -34214,7 +34215,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1023" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1023" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1023" s="2" t="s">
         <v>98</v>
       </c>
@@ -34244,7 +34245,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1024" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1024" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1024" s="2" t="s">
         <v>98</v>
       </c>
@@ -34274,7 +34275,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1025" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1025" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1025" s="2" t="s">
         <v>98</v>
       </c>
@@ -34304,7 +34305,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1026" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1026" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1026" s="2" t="s">
         <v>98</v>
       </c>
@@ -34334,7 +34335,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1027" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1027" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1027" s="2" t="s">
         <v>98</v>
       </c>
@@ -34364,7 +34365,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1028" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1028" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1028" s="2" t="s">
         <v>98</v>
       </c>
@@ -34394,7 +34395,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1029" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1029" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1029" s="2" t="s">
         <v>98</v>
       </c>
@@ -34424,7 +34425,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1030" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1030" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1030" s="2" t="s">
         <v>98</v>
       </c>
@@ -34454,7 +34455,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1031" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1031" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1031" s="2" t="s">
         <v>98</v>
       </c>
@@ -34484,7 +34485,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1032" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1032" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1032" s="2" t="s">
         <v>98</v>
       </c>
@@ -34514,7 +34515,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1033" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1033" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1033" s="2" t="s">
         <v>98</v>
       </c>
@@ -34544,7 +34545,7 @@
         <v>BC350.png</v>
       </c>
     </row>
-    <row r="1034" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1034" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1034" s="2" t="s">
         <v>98</v>
       </c>
@@ -34574,7 +34575,7 @@
         <v>BC350.png</v>
       </c>
     </row>
-    <row r="1035" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1035" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1035" s="2" t="s">
         <v>98</v>
       </c>
@@ -34604,7 +34605,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="1036" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1036" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1036" s="2" t="s">
         <v>98</v>
       </c>
@@ -34634,7 +34635,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="1037" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1037" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1037" s="2" t="s">
         <v>98</v>
       </c>
@@ -34664,7 +34665,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="1038" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1038" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1038" s="2" t="s">
         <v>98</v>
       </c>
@@ -34694,7 +34695,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="1039" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1039" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1039" s="2" t="s">
         <v>98</v>
       </c>
@@ -34724,7 +34725,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="1040" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1040" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1040" s="2" t="s">
         <v>98</v>
       </c>
@@ -34754,7 +34755,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="1041" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1041" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1041" s="2" t="s">
         <v>98</v>
       </c>
@@ -34784,7 +34785,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="1042" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1042" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1042" s="2" t="s">
         <v>98</v>
       </c>
@@ -34814,7 +34815,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="1043" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1043" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1043" s="2" t="s">
         <v>98</v>
       </c>
@@ -34844,7 +34845,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="1044" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1044" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1044" s="2" t="s">
         <v>98</v>
       </c>
@@ -34874,7 +34875,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="1045" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1045" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1045" s="2" t="s">
         <v>98</v>
       </c>
@@ -34904,7 +34905,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="1046" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1046" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1046" s="2" t="s">
         <v>98</v>
       </c>
@@ -34934,7 +34935,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="1047" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1047" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1047" s="2" t="s">
         <v>98</v>
       </c>
@@ -34964,7 +34965,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="1048" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1048" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1048" s="2" t="s">
         <v>98</v>
       </c>
@@ -34994,7 +34995,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="1049" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1049" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1049" s="2" t="s">
         <v>98</v>
       </c>
@@ -35024,7 +35025,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="1050" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1050" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1050" s="2" t="s">
         <v>98</v>
       </c>
@@ -35054,7 +35055,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="1051" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1051" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1051" s="2" t="s">
         <v>98</v>
       </c>
@@ -35084,7 +35085,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="1052" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1052" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1052" s="2" t="s">
         <v>98</v>
       </c>
@@ -35114,7 +35115,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="1053" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1053" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1053" s="2" t="s">
         <v>98</v>
       </c>
@@ -35144,7 +35145,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="1054" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1054" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1054" s="2" t="s">
         <v>98</v>
       </c>
@@ -35174,7 +35175,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="1055" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1055" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1055" s="2" t="s">
         <v>98</v>
       </c>
@@ -35204,7 +35205,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="1056" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1056" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1056" s="2" t="s">
         <v>98</v>
       </c>
@@ -35234,7 +35235,7 @@
         <v>AP350.png</v>
       </c>
     </row>
-    <row r="1057" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1057" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1057" s="2" t="s">
         <v>98</v>
       </c>
@@ -35264,7 +35265,7 @@
         <v>AP350.png</v>
       </c>
     </row>
-    <row r="1058" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1058" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1058" s="2" t="s">
         <v>98</v>
       </c>
@@ -35294,7 +35295,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1059" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1059" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1059" s="2" t="s">
         <v>98</v>
       </c>
@@ -35324,7 +35325,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1060" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1060" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1060" s="2" t="s">
         <v>98</v>
       </c>
@@ -35354,7 +35355,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1061" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1061" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1061" s="2" t="s">
         <v>98</v>
       </c>
@@ -35384,7 +35385,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1062" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1062" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1062" s="2" t="s">
         <v>98</v>
       </c>
@@ -35414,7 +35415,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1063" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1063" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1063" s="2" t="s">
         <v>98</v>
       </c>
@@ -35444,7 +35445,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1064" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1064" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1064" s="2" t="s">
         <v>98</v>
       </c>
@@ -35474,7 +35475,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1065" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1065" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1065" s="2" t="s">
         <v>98</v>
       </c>
@@ -35504,7 +35505,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1066" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1066" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1066" s="2" t="s">
         <v>98</v>
       </c>
@@ -35534,7 +35535,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1067" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1067" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1067" s="2" t="s">
         <v>98</v>
       </c>
@@ -35564,7 +35565,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1068" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1068" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1068" s="2" t="s">
         <v>98</v>
       </c>
@@ -35594,7 +35595,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1069" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1069" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1069" s="2" t="s">
         <v>98</v>
       </c>
@@ -35624,7 +35625,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1070" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1070" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1070" s="2" t="s">
         <v>98</v>
       </c>
@@ -35654,7 +35655,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1071" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1071" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1071" s="2" t="s">
         <v>98</v>
       </c>
@@ -35684,7 +35685,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="1072" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1072" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1072" s="2" t="s">
         <v>98</v>
       </c>
@@ -35714,7 +35715,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="1073" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1073" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1073" s="2" t="s">
         <v>98</v>
       </c>
@@ -35744,7 +35745,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="1074" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1074" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1074" s="2" t="s">
         <v>98</v>
       </c>
@@ -35774,7 +35775,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="1075" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1075" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1075" s="2" t="s">
         <v>98</v>
       </c>
@@ -35804,7 +35805,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="1076" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1076" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1076" s="2" t="s">
         <v>98</v>
       </c>
@@ -35834,7 +35835,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="1077" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1077" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1077" s="2" t="s">
         <v>98</v>
       </c>
@@ -35864,7 +35865,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="1078" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1078" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1078" s="2" t="s">
         <v>98</v>
       </c>
@@ -35894,7 +35895,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="1079" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1079" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1079" s="2" t="s">
         <v>98</v>
       </c>
@@ -35924,7 +35925,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="1080" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1080" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1080" s="2" t="s">
         <v>98</v>
       </c>
@@ -35954,7 +35955,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="1081" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1081" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1081" s="2" t="s">
         <v>98</v>
       </c>
@@ -35984,7 +35985,7 @@
         <v>STE269.png</v>
       </c>
     </row>
-    <row r="1082" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1082" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1082" s="2" t="s">
         <v>98</v>
       </c>
@@ -36014,7 +36015,7 @@
         <v>STE269.png</v>
       </c>
     </row>
-    <row r="1083" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1083" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1083" s="2" t="s">
         <v>98</v>
       </c>
@@ -36044,7 +36045,7 @@
         <v>STE269.png</v>
       </c>
     </row>
-    <row r="1084" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1084" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1084" s="2" t="s">
         <v>98</v>
       </c>
@@ -36074,7 +36075,7 @@
         <v>STE269.png</v>
       </c>
     </row>
-    <row r="1085" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1085" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1085" s="2" t="s">
         <v>98</v>
       </c>
@@ -36104,7 +36105,7 @@
         <v>BUD350.png</v>
       </c>
     </row>
-    <row r="1086" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1086" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1086" s="2" t="s">
         <v>98</v>
       </c>
@@ -36134,7 +36135,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="1087" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1087" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1087" s="2" t="s">
         <v>98</v>
       </c>
@@ -36164,7 +36165,7 @@
         <v>BUD350.png</v>
       </c>
     </row>
-    <row r="1088" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1088" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1088" s="2" t="s">
         <v>98</v>
       </c>
@@ -36194,7 +36195,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="1089" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1089" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1089" s="2" t="s">
         <v>98</v>
       </c>
@@ -36224,7 +36225,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="1090" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1090" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1090" s="2" t="s">
         <v>98</v>
       </c>
@@ -36254,7 +36255,7 @@
         <v>BUD350.png</v>
       </c>
     </row>
-    <row r="1091" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1091" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1091" s="2" t="s">
         <v>98</v>
       </c>
@@ -36284,7 +36285,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="1092" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1092" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1092" s="2" t="s">
         <v>98</v>
       </c>
@@ -36314,7 +36315,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="1093" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1093" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1093" s="2" t="s">
         <v>98</v>
       </c>
@@ -36344,7 +36345,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="1094" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1094" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1094" s="2" t="s">
         <v>98</v>
       </c>
@@ -36374,7 +36375,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="1095" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1095" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1095" s="2" t="s">
         <v>98</v>
       </c>
@@ -36404,7 +36405,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="1096" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1096" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1096" s="2" t="s">
         <v>98</v>
       </c>
@@ -36434,7 +36435,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="1097" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1097" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1097" s="2" t="s">
         <v>98</v>
       </c>
@@ -36464,7 +36465,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="1098" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1098" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1098" s="2" t="s">
         <v>98</v>
       </c>
@@ -36494,7 +36495,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="1099" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1099" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1099" s="2" t="s">
         <v>98</v>
       </c>
@@ -36524,7 +36525,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="1100" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1100" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1100" s="2" t="s">
         <v>98</v>
       </c>
@@ -36554,7 +36555,7 @@
         <v>COR269.png</v>
       </c>
     </row>
-    <row r="1101" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1101" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1101" s="2" t="s">
         <v>98</v>
       </c>
@@ -36584,7 +36585,7 @@
         <v>COR269.png</v>
       </c>
     </row>
-    <row r="1102" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1102" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1102" s="2" t="s">
         <v>98</v>
       </c>
@@ -36614,7 +36615,7 @@
         <v>COR269.png</v>
       </c>
     </row>
-    <row r="1103" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1103" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1103" s="2" t="s">
         <v>98</v>
       </c>
@@ -36644,7 +36645,7 @@
         <v>COR269.png</v>
       </c>
     </row>
-    <row r="1104" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1104" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1104" s="2" t="s">
         <v>98</v>
       </c>
@@ -36674,7 +36675,7 @@
         <v>STE350.png</v>
       </c>
     </row>
-    <row r="1105" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1105" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1105" s="2" t="s">
         <v>98</v>
       </c>
@@ -36704,7 +36705,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="1106" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1106" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1106" s="2" t="s">
         <v>98</v>
       </c>
@@ -36734,7 +36735,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="1107" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1107" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1107" s="2" t="s">
         <v>98</v>
       </c>
@@ -36764,7 +36765,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="1108" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1108" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1108" s="2" t="s">
         <v>98</v>
       </c>
@@ -36794,7 +36795,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="1109" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1109" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1109" s="2" t="s">
         <v>98</v>
       </c>
@@ -36824,7 +36825,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="1110" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1110" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1110" s="2" t="s">
         <v>98</v>
       </c>
@@ -36854,7 +36855,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="1111" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1111" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1111" s="2" t="s">
         <v>98</v>
       </c>
@@ -36884,7 +36885,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="1112" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1112" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1112" s="2" t="s">
         <v>98</v>
       </c>
@@ -36914,7 +36915,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="1113" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1113" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1113" s="2" t="s">
         <v>98</v>
       </c>
@@ -36944,7 +36945,7 @@
         <v>STE350.png</v>
       </c>
     </row>
-    <row r="1114" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1114" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1114" s="2" t="s">
         <v>98</v>
       </c>
@@ -36974,7 +36975,7 @@
         <v>STE350.png</v>
       </c>
     </row>
-    <row r="1115" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1115" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1115" s="2" t="s">
         <v>98</v>
       </c>
@@ -37004,7 +37005,7 @@
         <v>STE350.png</v>
       </c>
     </row>
-    <row r="1116" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1116" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1116" s="2" t="s">
         <v>98</v>
       </c>
@@ -37034,7 +37035,7 @@
         <v>MIC269.png</v>
       </c>
     </row>
-    <row r="1117" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1117" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1117" s="2" t="s">
         <v>98</v>
       </c>
@@ -37064,7 +37065,7 @@
         <v>MIC269.png</v>
       </c>
     </row>
-    <row r="1118" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1118" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1118" s="2" t="s">
         <v>98</v>
       </c>
@@ -37094,7 +37095,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="1119" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1119" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1119" s="2" t="s">
         <v>98</v>
       </c>
@@ -37124,7 +37125,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="1120" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1120" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1120" s="2" t="s">
         <v>98</v>
       </c>
@@ -37154,7 +37155,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="1121" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1121" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1121" s="2" t="s">
         <v>98</v>
       </c>
@@ -37184,7 +37185,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="1122" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1122" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1122" s="2" t="s">
         <v>98</v>
       </c>
@@ -37214,7 +37215,7 @@
         <v>STE350.png</v>
       </c>
     </row>
-    <row r="1123" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1123" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1123" s="2" t="s">
         <v>98</v>
       </c>
@@ -37244,7 +37245,7 @@
         <v>COR350.png</v>
       </c>
     </row>
-    <row r="1124" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1124" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1124" s="2" t="s">
         <v>98</v>
       </c>
@@ -37274,7 +37275,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="1125" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1125" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1125" s="2" t="s">
         <v>98</v>
       </c>
@@ -37304,7 +37305,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="1126" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1126" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1126" s="2" t="s">
         <v>98</v>
       </c>
@@ -37334,7 +37335,7 @@
         <v>COR350.png</v>
       </c>
     </row>
-    <row r="1127" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1127" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1127" s="2" t="s">
         <v>98</v>
       </c>
@@ -37364,7 +37365,7 @@
         <v>COR350.png</v>
       </c>
     </row>
-    <row r="1128" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1128" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1128" s="2" t="s">
         <v>98</v>
       </c>
@@ -37394,7 +37395,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="1129" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1129" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1129" s="2" t="s">
         <v>98</v>
       </c>
@@ -37424,7 +37425,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="1130" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1130" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1130" s="2" t="s">
         <v>98</v>
       </c>
@@ -37454,7 +37455,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="1131" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1131" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1131" s="2" t="s">
         <v>98</v>
       </c>
@@ -37484,7 +37485,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="1132" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1132" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1132" s="2" t="s">
         <v>98</v>
       </c>
@@ -37514,7 +37515,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="1133" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1133" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1133" s="2" t="s">
         <v>98</v>
       </c>
@@ -37544,7 +37545,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="1134" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1134" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1134" s="2" t="s">
         <v>98</v>
       </c>
@@ -37574,7 +37575,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="1135" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1135" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1135" s="2" t="s">
         <v>98</v>
       </c>
@@ -37604,7 +37605,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="1136" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1136" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1136" s="2" t="s">
         <v>98</v>
       </c>
@@ -37634,7 +37635,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="1137" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1137" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1137" s="2" t="s">
         <v>98</v>
       </c>
@@ -37664,7 +37665,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="1138" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1138" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1138" s="2" t="s">
         <v>98</v>
       </c>
@@ -37694,7 +37695,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="1139" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1139" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1139" s="2" t="s">
         <v>98</v>
       </c>
@@ -37724,7 +37725,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="1140" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1140" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1140" s="2" t="s">
         <v>98</v>
       </c>
@@ -37754,7 +37755,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="1141" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1141" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1141" s="2" t="s">
         <v>98</v>
       </c>
@@ -37784,7 +37785,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="1142" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1142" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1142" s="2" t="s">
         <v>98</v>
       </c>
@@ -37814,7 +37815,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="1143" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1143" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1143" s="2" t="s">
         <v>98</v>
       </c>
@@ -37844,7 +37845,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="1144" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1144" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1144" s="2" t="s">
         <v>98</v>
       </c>
@@ -37874,7 +37875,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="1145" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1145" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1145" s="2" t="s">
         <v>98</v>
       </c>
@@ -37904,7 +37905,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="1146" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1146" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1146" s="2" t="s">
         <v>98</v>
       </c>
@@ -37934,7 +37935,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="1147" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1147" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1147" s="2" t="s">
         <v>98</v>
       </c>
@@ -37964,13 +37965,13 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="1148" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1148" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1148" s="2"/>
       <c r="B1148" s="2"/>
       <c r="E1148" s="2"/>
       <c r="I1148" s="2"/>
     </row>
-    <row r="1149" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1149" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1149" s="2" t="s">
         <v>98</v>
       </c>
@@ -38000,7 +38001,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="1150" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1150" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1150" s="2" t="s">
         <v>98</v>
       </c>
@@ -38030,7 +38031,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="1151" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1151" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1151" s="2" t="s">
         <v>98</v>
       </c>
@@ -38060,7 +38061,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="1152" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1152" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1152" s="2" t="s">
         <v>98</v>
       </c>
@@ -38090,7 +38091,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="1153" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1153" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1153" s="2" t="s">
         <v>98</v>
       </c>
@@ -38120,7 +38121,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="1154" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1154" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1154" s="2" t="s">
         <v>98</v>
       </c>
@@ -38150,7 +38151,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="1155" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1155" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1155" s="2" t="s">
         <v>98</v>
       </c>
@@ -38180,7 +38181,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="1156" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1156" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1156" s="2" t="s">
         <v>98</v>
       </c>
@@ -38210,7 +38211,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="1157" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1157" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1157" s="2" t="s">
         <v>98</v>
       </c>
@@ -38240,7 +38241,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="1158" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1158" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1158" s="2" t="s">
         <v>98</v>
       </c>
@@ -38270,7 +38271,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="1159" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1159" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1159" s="2" t="s">
         <v>98</v>
       </c>
@@ -38300,7 +38301,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="1160" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1160" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1160" s="2" t="s">
         <v>98</v>
       </c>
@@ -38330,7 +38331,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="1161" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1161" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1161" s="2" t="s">
         <v>98</v>
       </c>
@@ -38360,7 +38361,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="1162" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1162" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1162" s="2" t="s">
         <v>98</v>
       </c>
@@ -38390,7 +38391,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="1163" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1163" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1163" s="2" t="s">
         <v>98</v>
       </c>
@@ -38420,7 +38421,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="1164" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1164" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1164" s="2" t="s">
         <v>98</v>
       </c>
@@ -38450,7 +38451,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="1165" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1165" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1165" s="2" t="s">
         <v>98</v>
       </c>
@@ -38480,7 +38481,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="1166" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1166" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1166" s="2" t="s">
         <v>98</v>
       </c>
@@ -38510,7 +38511,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="1167" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1167" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1167" s="2" t="s">
         <v>98</v>
       </c>
@@ -38540,7 +38541,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="1168" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1168" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1168" s="2" t="s">
         <v>98</v>
       </c>
@@ -38570,7 +38571,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="1169" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1169" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1169" s="2" t="s">
         <v>98</v>
       </c>
@@ -38600,7 +38601,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="1170" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1170" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1170" s="2" t="s">
         <v>98</v>
       </c>
@@ -38630,7 +38631,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="1171" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1171" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1171" s="2" t="s">
         <v>98</v>
       </c>
@@ -38660,7 +38661,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="1172" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1172" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1172" s="2" t="s">
         <v>98</v>
       </c>
@@ -38690,7 +38691,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="1173" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1173" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1173" s="2" t="s">
         <v>98</v>
       </c>
@@ -38720,7 +38721,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="1174" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1174" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1174" s="2" t="s">
         <v>98</v>
       </c>
@@ -38750,7 +38751,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="1175" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1175" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1175" s="2" t="s">
         <v>98</v>
       </c>
@@ -38780,7 +38781,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="1176" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1176" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1176" s="2" t="s">
         <v>98</v>
       </c>
@@ -38810,7 +38811,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="1177" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1177" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1177" s="2" t="s">
         <v>98</v>
       </c>
@@ -38840,7 +38841,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="1178" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1178" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1178" s="2" t="s">
         <v>98</v>
       </c>
@@ -38870,7 +38871,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="1179" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1179" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1179" s="2" t="s">
         <v>98</v>
       </c>
@@ -38900,7 +38901,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="1180" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1180" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1180" s="2" t="s">
         <v>98</v>
       </c>
@@ -38930,7 +38931,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="1181" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1181" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1181" s="2" t="s">
         <v>98</v>
       </c>
@@ -38960,7 +38961,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="1182" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1182" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1182" s="2" t="s">
         <v>98</v>
       </c>
@@ -38990,7 +38991,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="1183" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1183" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1183" s="2" t="s">
         <v>98</v>
       </c>
@@ -39020,7 +39021,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="1184" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1184" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1184" s="2" t="s">
         <v>98</v>
       </c>
@@ -39050,7 +39051,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="1185" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1185" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1185" s="2" t="s">
         <v>98</v>
       </c>
@@ -39080,7 +39081,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="1186" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1186" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1186" s="2" t="s">
         <v>98</v>
       </c>
@@ -39110,7 +39111,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="1187" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1187" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1187" s="2" t="s">
         <v>98</v>
       </c>
@@ -39140,7 +39141,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="1188" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1188" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1188" s="2" t="s">
         <v>98</v>
       </c>
@@ -39170,7 +39171,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="1189" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1189" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1189" s="2" t="s">
         <v>98</v>
       </c>
@@ -39200,7 +39201,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="1190" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1190" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1190" s="2" t="s">
         <v>98</v>
       </c>
@@ -39230,7 +39231,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="1191" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1191" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1191" s="2" t="s">
         <v>98</v>
       </c>
@@ -39260,7 +39261,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="1192" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1192" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1192" s="2" t="s">
         <v>98</v>
       </c>
@@ -39290,7 +39291,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="1193" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1193" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1193" s="2" t="s">
         <v>98</v>
       </c>
@@ -39320,7 +39321,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="1194" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1194" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1194" s="2" t="s">
         <v>98</v>
       </c>
@@ -39350,7 +39351,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="1195" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1195" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1195" s="2" t="s">
         <v>98</v>
       </c>
@@ -39380,7 +39381,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="1196" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1196" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1196" s="2" t="s">
         <v>98</v>
       </c>
@@ -39410,7 +39411,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="1197" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1197" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1197" s="2" t="s">
         <v>98</v>
       </c>
@@ -39440,7 +39441,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="1198" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1198" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1198" s="2" t="s">
         <v>98</v>
       </c>
@@ -39470,7 +39471,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="1199" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1199" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1199" s="2" t="s">
         <v>98</v>
       </c>
@@ -39500,7 +39501,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="1200" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1200" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1200" s="2" t="s">
         <v>98</v>
       </c>
@@ -39530,7 +39531,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="1201" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1201" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1201" s="2" t="s">
         <v>98</v>
       </c>
@@ -39560,7 +39561,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="1202" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1202" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1202" s="2" t="s">
         <v>98</v>
       </c>
@@ -39590,7 +39591,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="1203" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1203" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1203" s="2" t="s">
         <v>98</v>
       </c>
@@ -39620,7 +39621,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="1204" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1204" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1204" s="2" t="s">
         <v>98</v>
       </c>
@@ -39650,7 +39651,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="1205" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1205" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1205" s="2" t="s">
         <v>98</v>
       </c>
@@ -39680,7 +39681,7 @@
         <v>BC269MP.png</v>
       </c>
     </row>
-    <row r="1206" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1206" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1206" s="2" t="s">
         <v>98</v>
       </c>
@@ -39710,7 +39711,7 @@
         <v>SK269MP.png</v>
       </c>
     </row>
-    <row r="1207" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1207" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1207" s="2" t="s">
         <v>98</v>
       </c>
@@ -39740,7 +39741,7 @@
         <v>BUD269MP.png</v>
       </c>
     </row>
-    <row r="1208" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1208" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1208" s="2" t="s">
         <v>98</v>
       </c>
@@ -39770,7 +39771,7 @@
         <v>ORI269MP.png</v>
       </c>
     </row>
-    <row r="1209" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1209" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1209" s="2" t="s">
         <v>98</v>
       </c>
@@ -39800,7 +39801,7 @@
         <v>STE350.png</v>
       </c>
     </row>
-    <row r="1210" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1210" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1210" s="2" t="s">
         <v>98</v>
       </c>
@@ -39830,7 +39831,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="1211" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1211" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1211" s="2" t="s">
         <v>98</v>
       </c>
@@ -39860,7 +39861,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="1212" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1212" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1212" s="2" t="s">
         <v>98</v>
       </c>
@@ -39890,7 +39891,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="1213" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1213" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1213" s="2" t="s">
         <v>98</v>
       </c>
@@ -39921,7 +39922,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1213" xr:uid="{34B2C8DF-4561-40B2-8E7C-6CD69559B9AE}"/>
+  <autoFilter ref="A1:I1213" xr:uid="{34B2C8DF-4561-40B2-8E7C-6CD69559B9AE}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="NAB"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>

--- a/data/calendario_promocional.xlsx
+++ b/data/calendario_promocional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\99852106\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51B7D5D6-4933-409C-8874-811E727A79F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8581BCE5-E493-46A6-A988-076BFFC64031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11445" yWindow="0" windowWidth="17460" windowHeight="15585" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="11760" windowHeight="15585" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DeparaIMG" sheetId="5" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">CALENDARIO!$A$1:$B$53</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DeparaIMG!$A$1:$D$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">MECANICA!$A$1:$D$49</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">PRODUTOS!$A$1:$I$1217</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">PRODUTOS!$A$1:$I$1218</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6553" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6563" uniqueCount="123">
   <si>
     <t>Data</t>
   </si>
@@ -3548,7 +3548,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34B2C8DF-4561-40B2-8E7C-6CD69559B9AE}">
-  <dimension ref="A1:I1218"/>
+  <dimension ref="A1:I1220"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="20.85546875" customWidth="1"/>
@@ -40070,8 +40070,68 @@
         <v>BC269MP.png</v>
       </c>
     </row>
+    <row r="1219" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1219" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1219" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1219" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1219" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1219" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1219" t="s">
+        <v>117</v>
+      </c>
+      <c r="G1219">
+        <v>3.29</v>
+      </c>
+      <c r="H1219">
+        <v>2.89</v>
+      </c>
+      <c r="I1219" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1219,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BUD269MP.png</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1220" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1220" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1220" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1220" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1220" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1220" t="s">
+        <v>116</v>
+      </c>
+      <c r="G1220">
+        <v>3.09</v>
+      </c>
+      <c r="H1220">
+        <v>2.79</v>
+      </c>
+      <c r="I1220" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1220,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>SK269MP.png</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I1217" xr:uid="{34B2C8DF-4561-40B2-8E7C-6CD69559B9AE}"/>
+  <autoFilter ref="A1:I1218" xr:uid="{34B2C8DF-4561-40B2-8E7C-6CD69559B9AE}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>

--- a/data/calendario_promocional.xlsx
+++ b/data/calendario_promocional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\99852106\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8581BCE5-E493-46A6-A988-076BFFC64031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B92F5DA4-8825-4FA1-97C6-23568D76854D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="11760" windowHeight="15585" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">CALENDARIO!$A$1:$B$53</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DeparaIMG!$A$1:$D$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">MECANICA!$A$1:$D$49</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">PRODUTOS!$A$1:$I$1218</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">PRODUTOS!$A$1:$I$1220</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6563" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6568" uniqueCount="123">
   <si>
     <t>Data</t>
   </si>
@@ -3548,7 +3548,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34B2C8DF-4561-40B2-8E7C-6CD69559B9AE}">
-  <dimension ref="A1:I1220"/>
+  <dimension ref="A1:I1221"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="20.85546875" customWidth="1"/>
@@ -40120,18 +40120,48 @@
         <v>116</v>
       </c>
       <c r="G1220">
-        <v>3.09</v>
+        <v>3.19</v>
       </c>
       <c r="H1220">
-        <v>2.79</v>
+        <v>2.99</v>
       </c>
       <c r="I1220" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1220,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
         <v>SK269MP.png</v>
       </c>
     </row>
+    <row r="1221" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1221" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1221" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1221" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1221" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1221" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1221" t="s">
+        <v>118</v>
+      </c>
+      <c r="G1221">
+        <v>3.69</v>
+      </c>
+      <c r="H1221">
+        <v>3.39</v>
+      </c>
+      <c r="I1221" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1221,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>ORI269MP.png</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I1218" xr:uid="{34B2C8DF-4561-40B2-8E7C-6CD69559B9AE}"/>
+  <autoFilter ref="A1:I1220" xr:uid="{34B2C8DF-4561-40B2-8E7C-6CD69559B9AE}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>

--- a/data/calendario_promocional.xlsx
+++ b/data/calendario_promocional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anheuserbuschinbev-my.sharepoint.com/personal/99854257_ab-inbev_com/Documents/Pasta H OneDrive/Documents/Calendario-main/Calendario-main/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="13_ncr:1_{B92F5DA4-8825-4FA1-97C6-23568D76854D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{638FFA47-8F51-40C5-A8D1-2851DFBF5F53}"/>
+  <xr:revisionPtr revIDLastSave="54" documentId="13_ncr:1_{B92F5DA4-8825-4FA1-97C6-23568D76854D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{341CB539-B4A5-4882-8830-035C4C2E85FD}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6680" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6682" uniqueCount="145">
   <si>
     <t>Data</t>
   </si>
@@ -476,6 +476,12 @@
   <si>
     <t>STEPG350</t>
   </si>
+  <si>
+    <t>STEPG350.png</t>
+  </si>
+  <si>
+    <t>STEPG269.png</t>
+  </si>
 </sst>
 </file>
 
@@ -856,7 +862,7 @@
         <v>AP269</v>
       </c>
       <c r="D2" t="str">
-        <f>C2&amp;".png"</f>
+        <f t="shared" ref="D2:D49" si="0">C2&amp;".png"</f>
         <v>AP269.png</v>
       </c>
     </row>
@@ -872,7 +878,7 @@
         <v>AP269MP</v>
       </c>
       <c r="D3" t="str">
-        <f>C3&amp;".png"</f>
+        <f t="shared" si="0"/>
         <v>AP269MP.png</v>
       </c>
     </row>
@@ -888,7 +894,7 @@
         <v>AP350</v>
       </c>
       <c r="D4" t="str">
-        <f>C4&amp;".png"</f>
+        <f t="shared" si="0"/>
         <v>AP350.png</v>
       </c>
     </row>
@@ -903,7 +909,7 @@
         <v>45</v>
       </c>
       <c r="D5" t="str">
-        <f>C5&amp;".png"</f>
+        <f t="shared" si="0"/>
         <v>BAREP2.png</v>
       </c>
     </row>
@@ -915,11 +921,11 @@
         <v>70</v>
       </c>
       <c r="C6" t="str">
-        <f>SUBSTITUTE(B6," ","")</f>
+        <f t="shared" ref="C6:C15" si="1">SUBSTITUTE(B6," ","")</f>
         <v>BC0350</v>
       </c>
       <c r="D6" t="str">
-        <f>C6&amp;".png"</f>
+        <f t="shared" si="0"/>
         <v>BC0350.png</v>
       </c>
     </row>
@@ -931,11 +937,11 @@
         <v>68</v>
       </c>
       <c r="C7" t="str">
-        <f>SUBSTITUTE(B7," ","")</f>
+        <f t="shared" si="1"/>
         <v>BC269</v>
       </c>
       <c r="D7" t="str">
-        <f>C7&amp;".png"</f>
+        <f t="shared" si="0"/>
         <v>BC269.png</v>
       </c>
     </row>
@@ -947,11 +953,11 @@
         <v>119</v>
       </c>
       <c r="C8" t="str">
-        <f>SUBSTITUTE(B8," ","")</f>
+        <f t="shared" si="1"/>
         <v>BC269MP</v>
       </c>
       <c r="D8" t="str">
-        <f>C8&amp;".png"</f>
+        <f t="shared" si="0"/>
         <v>BC269MP.png</v>
       </c>
     </row>
@@ -963,11 +969,11 @@
         <v>71</v>
       </c>
       <c r="C9" t="str">
-        <f>SUBSTITUTE(B9," ","")</f>
+        <f t="shared" si="1"/>
         <v>BC350</v>
       </c>
       <c r="D9" t="str">
-        <f>C9&amp;".png"</f>
+        <f t="shared" si="0"/>
         <v>BC350.png</v>
       </c>
     </row>
@@ -979,11 +985,11 @@
         <v>107</v>
       </c>
       <c r="C10" t="str">
-        <f>SUBSTITUTE(B10," ","")</f>
+        <f t="shared" si="1"/>
         <v>BEATSLN</v>
       </c>
       <c r="D10" t="str">
-        <f>C10&amp;".png"</f>
+        <f t="shared" si="0"/>
         <v>BEATSLN.png</v>
       </c>
     </row>
@@ -995,11 +1001,11 @@
         <v>106</v>
       </c>
       <c r="C11" t="str">
-        <f>SUBSTITUTE(B11," ","")</f>
+        <f t="shared" si="1"/>
         <v>BEATSLT</v>
       </c>
       <c r="D11" t="str">
-        <f>C11&amp;".png"</f>
+        <f t="shared" si="0"/>
         <v>BEATSLT.png</v>
       </c>
     </row>
@@ -1011,11 +1017,11 @@
         <v>69</v>
       </c>
       <c r="C12" t="str">
-        <f>SUBSTITUTE(B12," ","")</f>
+        <f t="shared" si="1"/>
         <v>BUD269</v>
       </c>
       <c r="D12" t="str">
-        <f>C12&amp;".png"</f>
+        <f t="shared" si="0"/>
         <v>BUD269.png</v>
       </c>
     </row>
@@ -1027,11 +1033,11 @@
         <v>117</v>
       </c>
       <c r="C13" t="str">
-        <f>SUBSTITUTE(B13," ","")</f>
+        <f t="shared" si="1"/>
         <v>BUD269MP</v>
       </c>
       <c r="D13" t="str">
-        <f>C13&amp;".png"</f>
+        <f t="shared" si="0"/>
         <v>BUD269MP.png</v>
       </c>
     </row>
@@ -1043,11 +1049,11 @@
         <v>76</v>
       </c>
       <c r="C14" t="str">
-        <f>SUBSTITUTE(B14," ","")</f>
+        <f t="shared" si="1"/>
         <v>BUD350</v>
       </c>
       <c r="D14" t="str">
-        <f>C14&amp;".png"</f>
+        <f t="shared" si="0"/>
         <v>BUD350.png</v>
       </c>
     </row>
@@ -1059,11 +1065,11 @@
         <v>82</v>
       </c>
       <c r="C15" t="str">
-        <f>SUBSTITUTE(B15," ","")</f>
+        <f t="shared" si="1"/>
         <v>BUDLN</v>
       </c>
       <c r="D15" t="str">
-        <f>C15&amp;".png"</f>
+        <f t="shared" si="0"/>
         <v>BUDLN.png</v>
       </c>
     </row>
@@ -1078,7 +1084,7 @@
         <v>94</v>
       </c>
       <c r="D16" t="str">
-        <f>C16&amp;".png"</f>
+        <f t="shared" si="0"/>
         <v>BUDZERO350.png</v>
       </c>
     </row>
@@ -1093,7 +1099,7 @@
         <v>91</v>
       </c>
       <c r="D17" t="str">
-        <f>C17&amp;".png"</f>
+        <f t="shared" si="0"/>
         <v>BUDZEROLN.png</v>
       </c>
     </row>
@@ -1109,7 +1115,7 @@
         <v>COR269</v>
       </c>
       <c r="D18" t="str">
-        <f>C18&amp;".png"</f>
+        <f t="shared" si="0"/>
         <v>COR269.png</v>
       </c>
     </row>
@@ -1125,7 +1131,7 @@
         <v>COR350</v>
       </c>
       <c r="D19" t="str">
-        <f>C19&amp;".png"</f>
+        <f t="shared" si="0"/>
         <v>COR350.png</v>
       </c>
     </row>
@@ -1140,7 +1146,7 @@
         <v>93</v>
       </c>
       <c r="D20" t="str">
-        <f>C20&amp;".png"</f>
+        <f t="shared" si="0"/>
         <v>CORCERO350.png</v>
       </c>
     </row>
@@ -1155,7 +1161,7 @@
         <v>92</v>
       </c>
       <c r="D21" t="str">
-        <f>C21&amp;".png"</f>
+        <f t="shared" si="0"/>
         <v>CORCEROLN.png</v>
       </c>
     </row>
@@ -1171,7 +1177,7 @@
         <v>CORLN</v>
       </c>
       <c r="D22" t="str">
-        <f>C22&amp;".png"</f>
+        <f t="shared" si="0"/>
         <v>CORLN.png</v>
       </c>
     </row>
@@ -1187,7 +1193,7 @@
         <v>FF350</v>
       </c>
       <c r="D23" t="str">
-        <f>C23&amp;".png"</f>
+        <f t="shared" si="0"/>
         <v>FF350.png</v>
       </c>
     </row>
@@ -1203,7 +1209,7 @@
         <v>FFLN</v>
       </c>
       <c r="D24" t="str">
-        <f>C24&amp;".png"</f>
+        <f t="shared" si="0"/>
         <v>FFLN.png</v>
       </c>
     </row>
@@ -1218,7 +1224,7 @@
         <v>51</v>
       </c>
       <c r="D25" t="str">
-        <f>C25&amp;".png"</f>
+        <f t="shared" si="0"/>
         <v>GCA269.png</v>
       </c>
     </row>
@@ -1233,7 +1239,7 @@
         <v>50</v>
       </c>
       <c r="D26" t="str">
-        <f>C26&amp;".png"</f>
+        <f t="shared" si="0"/>
         <v>GCA350.png</v>
       </c>
     </row>
@@ -1248,7 +1254,7 @@
         <v>48</v>
       </c>
       <c r="D27" t="str">
-        <f>C27&amp;".png"</f>
+        <f t="shared" si="0"/>
         <v>GCAP1,5.png</v>
       </c>
     </row>
@@ -1263,7 +1269,7 @@
         <v>43</v>
       </c>
       <c r="D28" t="str">
-        <f>C28&amp;".png"</f>
+        <f t="shared" si="0"/>
         <v>GCAP1.png</v>
       </c>
     </row>
@@ -1278,7 +1284,7 @@
         <v>47</v>
       </c>
       <c r="D29" t="str">
-        <f>C29&amp;".png"</f>
+        <f t="shared" si="0"/>
         <v>GCAP2.png</v>
       </c>
     </row>
@@ -1293,7 +1299,7 @@
         <v>54</v>
       </c>
       <c r="D30" t="str">
-        <f>C30&amp;".png"</f>
+        <f t="shared" si="0"/>
         <v>H2OHP1,5.png</v>
       </c>
     </row>
@@ -1308,7 +1314,7 @@
         <v>49</v>
       </c>
       <c r="D31" t="str">
-        <f>C31&amp;".png"</f>
+        <f t="shared" si="0"/>
         <v>H2OHP500.png</v>
       </c>
     </row>
@@ -1324,7 +1330,7 @@
         <v>MIC269</v>
       </c>
       <c r="D32" t="str">
-        <f>C32&amp;".png"</f>
+        <f t="shared" si="0"/>
         <v>MIC269.png</v>
       </c>
     </row>
@@ -1340,7 +1346,7 @@
         <v>MIC350</v>
       </c>
       <c r="D33" t="str">
-        <f>C33&amp;".png"</f>
+        <f t="shared" si="0"/>
         <v>MIC350.png</v>
       </c>
     </row>
@@ -1356,7 +1362,7 @@
         <v>MICLN</v>
       </c>
       <c r="D34" t="str">
-        <f>C34&amp;".png"</f>
+        <f t="shared" si="0"/>
         <v>MICLN.png</v>
       </c>
     </row>
@@ -1372,7 +1378,7 @@
         <v>ORI269</v>
       </c>
       <c r="D35" t="str">
-        <f>C35&amp;".png"</f>
+        <f t="shared" si="0"/>
         <v>ORI269.png</v>
       </c>
     </row>
@@ -1388,7 +1394,7 @@
         <v>ORI269MP</v>
       </c>
       <c r="D36" t="str">
-        <f>C36&amp;".png"</f>
+        <f t="shared" si="0"/>
         <v>ORI269MP.png</v>
       </c>
     </row>
@@ -1403,7 +1409,7 @@
         <v>52</v>
       </c>
       <c r="D37" t="str">
-        <f>C37&amp;".png"</f>
+        <f t="shared" si="0"/>
         <v>PC269.png</v>
       </c>
     </row>
@@ -1418,7 +1424,7 @@
         <v>53</v>
       </c>
       <c r="D38" t="str">
-        <f>C38&amp;".png"</f>
+        <f t="shared" si="0"/>
         <v>PCB350.png</v>
       </c>
     </row>
@@ -1433,7 +1439,7 @@
         <v>44</v>
       </c>
       <c r="D39" t="str">
-        <f>C39&amp;".png"</f>
+        <f t="shared" si="0"/>
         <v>PCP2.png</v>
       </c>
     </row>
@@ -1445,11 +1451,11 @@
         <v>66</v>
       </c>
       <c r="C40" t="str">
-        <f>SUBSTITUTE(B40," ","")</f>
+        <f t="shared" ref="C40:C48" si="2">SUBSTITUTE(B40," ","")</f>
         <v>SK269</v>
       </c>
       <c r="D40" t="str">
-        <f>C40&amp;".png"</f>
+        <f t="shared" si="0"/>
         <v>SK269.png</v>
       </c>
     </row>
@@ -1461,11 +1467,11 @@
         <v>116</v>
       </c>
       <c r="C41" t="str">
-        <f>SUBSTITUTE(B41," ","")</f>
+        <f t="shared" si="2"/>
         <v>SK269MP</v>
       </c>
       <c r="D41" t="str">
-        <f>C41&amp;".png"</f>
+        <f t="shared" si="0"/>
         <v>SK269MP.png</v>
       </c>
     </row>
@@ -1477,11 +1483,11 @@
         <v>63</v>
       </c>
       <c r="C42" t="str">
-        <f>SUBSTITUTE(B42," ","")</f>
+        <f t="shared" si="2"/>
         <v>SKZERO269</v>
       </c>
       <c r="D42" t="str">
-        <f>C42&amp;".png"</f>
+        <f t="shared" si="0"/>
         <v>SKZERO269.png</v>
       </c>
     </row>
@@ -1493,11 +1499,11 @@
         <v>64</v>
       </c>
       <c r="C43" t="str">
-        <f>SUBSTITUTE(B43," ","")</f>
+        <f t="shared" si="2"/>
         <v>SKZERO350</v>
       </c>
       <c r="D43" t="str">
-        <f>C43&amp;".png"</f>
+        <f t="shared" si="0"/>
         <v>SKZERO350.png</v>
       </c>
     </row>
@@ -1509,11 +1515,11 @@
         <v>100</v>
       </c>
       <c r="C44" t="str">
-        <f>SUBSTITUTE(B44," ","")</f>
+        <f t="shared" si="2"/>
         <v>SPT269</v>
       </c>
       <c r="D44" t="str">
-        <f>C44&amp;".png"</f>
+        <f t="shared" si="0"/>
         <v>SPT269.png</v>
       </c>
     </row>
@@ -1525,11 +1531,11 @@
         <v>101</v>
       </c>
       <c r="C45" t="str">
-        <f>SUBSTITUTE(B45," ","")</f>
+        <f t="shared" si="2"/>
         <v>SPT350</v>
       </c>
       <c r="D45" t="str">
-        <f>C45&amp;".png"</f>
+        <f t="shared" si="0"/>
         <v>SPT350.png</v>
       </c>
     </row>
@@ -1541,11 +1547,11 @@
         <v>75</v>
       </c>
       <c r="C46" t="str">
-        <f>SUBSTITUTE(B46," ","")</f>
+        <f t="shared" si="2"/>
         <v>STE269</v>
       </c>
       <c r="D46" t="str">
-        <f>C46&amp;".png"</f>
+        <f t="shared" si="0"/>
         <v>STE269.png</v>
       </c>
     </row>
@@ -1557,11 +1563,11 @@
         <v>65</v>
       </c>
       <c r="C47" t="str">
-        <f>SUBSTITUTE(B47," ","")</f>
+        <f t="shared" si="2"/>
         <v>STE350</v>
       </c>
       <c r="D47" t="str">
-        <f>C47&amp;".png"</f>
+        <f t="shared" si="0"/>
         <v>STE350.png</v>
       </c>
     </row>
@@ -1573,11 +1579,11 @@
         <v>84</v>
       </c>
       <c r="C48" t="str">
-        <f>SUBSTITUTE(B48," ","")</f>
+        <f t="shared" si="2"/>
         <v>STELN</v>
       </c>
       <c r="D48" t="str">
-        <f>C48&amp;".png"</f>
+        <f t="shared" si="0"/>
         <v>STELN.png</v>
       </c>
     </row>
@@ -1592,7 +1598,7 @@
         <v>46</v>
       </c>
       <c r="D49" t="str">
-        <f>C49&amp;".png"</f>
+        <f t="shared" si="0"/>
         <v>SUKP2.png</v>
       </c>
     </row>
@@ -1607,7 +1613,7 @@
         <v>139</v>
       </c>
       <c r="D50" t="str">
-        <f t="shared" ref="D50:D51" si="0">C50&amp;".png"</f>
+        <f t="shared" ref="D50:D51" si="3">C50&amp;".png"</f>
         <v>STEPG269.png</v>
       </c>
     </row>
@@ -1622,7 +1628,7 @@
         <v>142</v>
       </c>
       <c r="D51" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>STEPG350.png</v>
       </c>
     </row>
@@ -40536,9 +40542,8 @@
       <c r="H1231">
         <v>4.3899999999999997</v>
       </c>
-      <c r="I1231" t="str">
-        <f t="shared" ref="I1231" si="0">H1231&amp;".png"</f>
-        <v>4,39.png</v>
+      <c r="I1231" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="1232" spans="1:9" x14ac:dyDescent="0.25">
@@ -40769,9 +40774,8 @@
       <c r="H1239">
         <v>5.49</v>
       </c>
-      <c r="I1239" t="str">
-        <f t="shared" ref="I1239" si="1">H1239&amp;".png"</f>
-        <v>5,49.png</v>
+      <c r="I1239" t="s">
+        <v>143</v>
       </c>
     </row>
   </sheetData>

--- a/data/calendario_promocional.xlsx
+++ b/data/calendario_promocional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anheuserbuschinbev-my.sharepoint.com/personal/99854257_ab-inbev_com/Documents/Pasta H OneDrive/Documents/Calendario-main/Calendario-main/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="54" documentId="13_ncr:1_{B92F5DA4-8825-4FA1-97C6-23568D76854D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{341CB539-B4A5-4882-8830-035C4C2E85FD}"/>
+  <xr:revisionPtr revIDLastSave="62" documentId="13_ncr:1_{B92F5DA4-8825-4FA1-97C6-23568D76854D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D36160EA-B22E-40EA-8D96-670187C81BB1}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6682" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6688" uniqueCount="146">
   <si>
     <t>Data</t>
   </si>
@@ -482,6 +482,9 @@
   <si>
     <t>STEPG269.png</t>
   </si>
+  <si>
+    <t>MIC350.png</t>
+  </si>
 </sst>
 </file>
 
@@ -3644,7 +3647,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34B2C8DF-4561-40B2-8E7C-6CD69559B9AE}">
-  <dimension ref="A1:I1239"/>
+  <dimension ref="A1:I1240"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="20.85546875" customWidth="1"/>
@@ -40560,19 +40563,19 @@
         <v>25</v>
       </c>
       <c r="E1232" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1232" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G1232">
-        <v>6.29</v>
+        <v>5.49</v>
       </c>
       <c r="H1232">
-        <v>5.49</v>
-      </c>
-      <c r="I1232" s="2" t="s">
-        <v>133</v>
+        <v>4.99</v>
+      </c>
+      <c r="I1232" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="1233" spans="1:9" x14ac:dyDescent="0.25">
@@ -40592,16 +40595,16 @@
         <v>2</v>
       </c>
       <c r="F1233" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G1233">
-        <v>6.69</v>
+        <v>6.29</v>
       </c>
       <c r="H1233">
-        <v>5.99</v>
+        <v>5.49</v>
       </c>
       <c r="I1233" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="1234" spans="1:9" x14ac:dyDescent="0.25">
@@ -40618,19 +40621,19 @@
         <v>25</v>
       </c>
       <c r="E1234" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1234" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G1234">
-        <v>6.99</v>
+        <v>6.69</v>
       </c>
       <c r="H1234">
-        <v>6.19</v>
+        <v>5.99</v>
       </c>
       <c r="I1234" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="1235" spans="1:9" x14ac:dyDescent="0.25">
@@ -40650,16 +40653,16 @@
         <v>1</v>
       </c>
       <c r="F1235" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G1235">
-        <v>7.99</v>
+        <v>6.99</v>
       </c>
       <c r="H1235">
-        <v>6.99</v>
+        <v>6.19</v>
       </c>
       <c r="I1235" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="1236" spans="1:9" x14ac:dyDescent="0.25">
@@ -40679,7 +40682,7 @@
         <v>1</v>
       </c>
       <c r="F1236" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G1236">
         <v>7.99</v>
@@ -40688,7 +40691,7 @@
         <v>6.99</v>
       </c>
       <c r="I1236" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="1237" spans="1:9" x14ac:dyDescent="0.25">
@@ -40708,16 +40711,16 @@
         <v>1</v>
       </c>
       <c r="F1237" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="G1237">
-        <v>3.49</v>
+        <v>7.99</v>
       </c>
       <c r="H1237">
-        <v>2.99</v>
+        <v>6.99</v>
       </c>
       <c r="I1237" s="2" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
     </row>
     <row r="1238" spans="1:9" x14ac:dyDescent="0.25">
@@ -40734,19 +40737,19 @@
         <v>25</v>
       </c>
       <c r="E1238" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1238" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="G1238">
-        <v>4.29</v>
+        <v>3.49</v>
       </c>
       <c r="H1238">
-        <v>3.49</v>
+        <v>2.99</v>
       </c>
       <c r="I1238" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="1239" spans="1:9" x14ac:dyDescent="0.25">
@@ -40766,15 +40769,44 @@
         <v>2</v>
       </c>
       <c r="F1239" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1239">
+        <v>4.29</v>
+      </c>
+      <c r="H1239">
+        <v>3.49</v>
+      </c>
+      <c r="I1239" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1240" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1240" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1240" t="s">
+        <v>138</v>
+      </c>
+      <c r="D1240" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1240" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1240" t="s">
         <v>141</v>
       </c>
-      <c r="G1239">
+      <c r="G1240">
         <v>5.99</v>
       </c>
-      <c r="H1239">
+      <c r="H1240">
         <v>5.49</v>
       </c>
-      <c r="I1239" t="s">
+      <c r="I1240" t="s">
         <v>143</v>
       </c>
     </row>

--- a/data/calendario_promocional.xlsx
+++ b/data/calendario_promocional.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anheuserbuschinbev-my.sharepoint.com/personal/99854257_ab-inbev_com/Documents/Pasta H OneDrive/Documents/Calendario-main/Calendario-main/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anheuserbuschinbev-my.sharepoint.com/personal/99823517_ab-inbev_com/Documents/001. Projetos/Streamlit Calendario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="62" documentId="13_ncr:1_{B92F5DA4-8825-4FA1-97C6-23568D76854D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D36160EA-B22E-40EA-8D96-670187C81BB1}"/>
+  <xr:revisionPtr revIDLastSave="116" documentId="13_ncr:1_{B92F5DA4-8825-4FA1-97C6-23568D76854D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{967A3C46-9776-4F76-8A93-3233D30BA0AB}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DeparaIMG" sheetId="5" r:id="rId1"/>
@@ -20,10 +20,10 @@
     <sheet name="CONFIG" sheetId="4" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">CALENDARIO!$A$1:$B$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">CALENDARIO!$A$1:$C$289</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DeparaIMG!$A$1:$D$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">MECANICA!$A$1:$D$49</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">PRODUTOS!$A$1:$I$1221</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">PRODUTOS!$A$1:$I$1239</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6688" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7115" uniqueCount="136">
   <si>
     <t>Data</t>
   </si>
@@ -417,51 +417,6 @@
     <t>Core Cash: 45 R$/hl</t>
   </si>
   <si>
-    <t>AP269.png</t>
-  </si>
-  <si>
-    <t>SKZERO269.png</t>
-  </si>
-  <si>
-    <t>SK269.png</t>
-  </si>
-  <si>
-    <t>BC269.png</t>
-  </si>
-  <si>
-    <t>BUD269.png</t>
-  </si>
-  <si>
-    <t>BC0350.png</t>
-  </si>
-  <si>
-    <t>SKZERO350.png</t>
-  </si>
-  <si>
-    <t>ORI269.png</t>
-  </si>
-  <si>
-    <t>STE269.png</t>
-  </si>
-  <si>
-    <t>BUDZERO350.png</t>
-  </si>
-  <si>
-    <t>CORCERO350.png</t>
-  </si>
-  <si>
-    <t>MICLN.png</t>
-  </si>
-  <si>
-    <t>STELN.png</t>
-  </si>
-  <si>
-    <t>CORLN.png</t>
-  </si>
-  <si>
-    <t>CORCEROLN.png</t>
-  </si>
-  <si>
     <t>Teste</t>
   </si>
   <si>
@@ -477,13 +432,28 @@
     <t>STEPG350</t>
   </si>
   <si>
-    <t>STEPG350.png</t>
+    <t>MERCAPROMO</t>
   </si>
   <si>
-    <t>STEPG269.png</t>
+    <t>VAR/ATAC</t>
   </si>
   <si>
-    <t>MIC350.png</t>
+    <t>FORT</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>MercaCO</t>
+  </si>
+  <si>
+    <t>MercaFORT</t>
+  </si>
+  <si>
+    <t>Merca/MercaCO</t>
+  </si>
+  <si>
+    <t>Merca/MercaFORT</t>
   </si>
 </sst>
 </file>
@@ -831,7 +801,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0BF5819-473C-445D-A53D-FC51ACB237C6}">
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
@@ -1610,13 +1580,13 @@
         <v>62</v>
       </c>
       <c r="B50" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="C50" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="D50" t="str">
-        <f t="shared" ref="D50:D51" si="3">C50&amp;".png"</f>
+        <f t="shared" ref="D50:D53" si="3">C50&amp;".png"</f>
         <v>STEPG269.png</v>
       </c>
     </row>
@@ -1625,19 +1595,49 @@
         <v>62</v>
       </c>
       <c r="B51" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="C51" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="D51" t="str">
         <f t="shared" si="3"/>
         <v>STEPG350.png</v>
       </c>
     </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>128</v>
+      </c>
+      <c r="B52" t="s">
+        <v>132</v>
+      </c>
+      <c r="C52" t="s">
+        <v>134</v>
+      </c>
+      <c r="D52" t="str">
+        <f>C52&amp;".png"</f>
+        <v>Merca/MercaCO.png</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>128</v>
+      </c>
+      <c r="B53" t="s">
+        <v>133</v>
+      </c>
+      <c r="C53" t="s">
+        <v>135</v>
+      </c>
+      <c r="D53" t="str">
+        <f t="shared" si="3"/>
+        <v>Merca/MercaFORT.png</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D49" xr:uid="{C0BF5819-473C-445D-A53D-FC51ACB237C6}"/>
-  <conditionalFormatting sqref="C1:C1048576">
+  <conditionalFormatting sqref="C1:C51 C54:C1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -1646,1301 +1646,3438 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B145"/>
+  <dimension ref="A1:C289"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" s="3">
         <v>46266</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
-        <f>A2+1</f>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" s="3">
+        <f>B2+1</f>
         <v>46267</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
-        <f t="shared" ref="A4:A53" si="0">A3+1</f>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" s="3">
+        <f t="shared" ref="B4:B53" si="0">B3+1</f>
         <v>46268</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="3">
         <f t="shared" si="0"/>
         <v>46269</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6" s="3">
         <f t="shared" si="0"/>
         <v>46270</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7" s="3">
         <f t="shared" si="0"/>
         <v>46271</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B8" s="3">
         <f t="shared" si="0"/>
         <v>46272</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="3">
         <f t="shared" si="0"/>
         <v>46273</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" s="3">
         <f t="shared" si="0"/>
         <v>46274</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11" s="3">
         <f t="shared" si="0"/>
         <v>46275</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="3">
         <f t="shared" si="0"/>
         <v>46276</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" s="3">
         <f t="shared" si="0"/>
         <v>46277</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>61</v>
+      </c>
+      <c r="B14" s="3">
         <f t="shared" si="0"/>
         <v>46278</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" s="3">
         <f t="shared" si="0"/>
         <v>46279</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="C15" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B16" s="3">
         <f t="shared" si="0"/>
         <v>46280</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="C16" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>61</v>
+      </c>
+      <c r="B17" s="3">
         <f t="shared" si="0"/>
         <v>46281</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="3">
         <f t="shared" si="0"/>
         <v>46282</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="C18" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19" s="3">
         <f t="shared" si="0"/>
         <v>46283</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="C19" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>61</v>
+      </c>
+      <c r="B20" s="3">
         <f t="shared" si="0"/>
         <v>46284</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="C20" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>61</v>
+      </c>
+      <c r="B21" s="3">
         <f t="shared" si="0"/>
         <v>46285</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="C21" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>61</v>
+      </c>
+      <c r="B22" s="3">
         <f t="shared" si="0"/>
         <v>46286</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="C22" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>61</v>
+      </c>
+      <c r="B23" s="3">
         <f t="shared" si="0"/>
         <v>46287</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="C23" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>61</v>
+      </c>
+      <c r="B24" s="3">
         <f t="shared" si="0"/>
         <v>46288</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="C24" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>61</v>
+      </c>
+      <c r="B25" s="3">
         <f t="shared" si="0"/>
         <v>46289</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="C25" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26" s="3">
         <f t="shared" si="0"/>
         <v>46290</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="C26" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>61</v>
+      </c>
+      <c r="B27" s="3">
         <f t="shared" si="0"/>
         <v>46291</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="C27" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>61</v>
+      </c>
+      <c r="B28" s="3">
         <f t="shared" si="0"/>
         <v>46292</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="C28" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>61</v>
+      </c>
+      <c r="B29" s="3">
         <v>46296</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="3">
+      <c r="C29" s="2"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>61</v>
+      </c>
+      <c r="B30" s="3">
         <f t="shared" si="0"/>
         <v>46297</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="3">
+      <c r="C30" s="2"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>61</v>
+      </c>
+      <c r="B31" s="3">
         <f t="shared" si="0"/>
         <v>46298</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="3">
+      <c r="C31" s="2"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>61</v>
+      </c>
+      <c r="B32" s="3">
         <f t="shared" si="0"/>
         <v>46299</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="3">
+      <c r="C32" s="2"/>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>61</v>
+      </c>
+      <c r="B33" s="3">
         <f t="shared" si="0"/>
         <v>46300</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="C33" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>61</v>
+      </c>
+      <c r="B34" s="3">
         <f t="shared" si="0"/>
         <v>46301</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="C34" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>61</v>
+      </c>
+      <c r="B35" s="3">
         <f t="shared" si="0"/>
         <v>46302</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="C35" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>61</v>
+      </c>
+      <c r="B36" s="3">
         <f t="shared" si="0"/>
         <v>46303</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="C36" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>61</v>
+      </c>
+      <c r="B37" s="3">
         <f t="shared" si="0"/>
         <v>46304</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="C37" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>61</v>
+      </c>
+      <c r="B38" s="3">
         <f t="shared" si="0"/>
         <v>46305</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="C38" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>61</v>
+      </c>
+      <c r="B39" s="3">
         <f t="shared" si="0"/>
         <v>46306</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="C39" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>61</v>
+      </c>
+      <c r="B40" s="3">
         <f t="shared" si="0"/>
         <v>46307</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="C40" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>61</v>
+      </c>
+      <c r="B41" s="3">
         <f t="shared" si="0"/>
         <v>46308</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="C41" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>61</v>
+      </c>
+      <c r="B42" s="3">
         <f t="shared" si="0"/>
         <v>46309</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="C42" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>61</v>
+      </c>
+      <c r="B43" s="3">
         <f t="shared" si="0"/>
         <v>46310</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="C43" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>61</v>
+      </c>
+      <c r="B44" s="3">
         <f t="shared" si="0"/>
         <v>46311</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="C44" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>61</v>
+      </c>
+      <c r="B45" s="3">
         <f t="shared" si="0"/>
         <v>46312</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="C45" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>61</v>
+      </c>
+      <c r="B46" s="3">
         <f t="shared" si="0"/>
         <v>46313</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="C46" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>61</v>
+      </c>
+      <c r="B47" s="3">
         <f t="shared" si="0"/>
         <v>46314</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="C47" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>61</v>
+      </c>
+      <c r="B48" s="3">
         <f t="shared" si="0"/>
         <v>46315</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="C48" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>61</v>
+      </c>
+      <c r="B49" s="3">
         <f t="shared" si="0"/>
         <v>46316</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="C49" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>61</v>
+      </c>
+      <c r="B50" s="3">
         <f t="shared" si="0"/>
         <v>46317</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="C50" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B51" s="3">
         <f t="shared" si="0"/>
         <v>46318</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="C51" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>61</v>
+      </c>
+      <c r="B52" s="3">
         <f t="shared" si="0"/>
         <v>46319</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="C52" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>61</v>
+      </c>
+      <c r="B53" s="3">
         <f t="shared" si="0"/>
         <v>46320</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="C53" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54" s="3">
         <v>46174</v>
       </c>
-      <c r="B54" t="s">
+      <c r="C54" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="5">
-        <f>A54+1</f>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>61</v>
+      </c>
+      <c r="B55" s="5">
+        <f>B54+1</f>
         <v>46175</v>
       </c>
-      <c r="B55" t="s">
+      <c r="C55" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="5">
-        <f t="shared" ref="A56:A119" si="1">A55+1</f>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>61</v>
+      </c>
+      <c r="B56" s="5">
+        <f t="shared" ref="B56:B119" si="1">B55+1</f>
         <v>46176</v>
       </c>
-      <c r="B56" t="s">
+      <c r="C56" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="5">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>61</v>
+      </c>
+      <c r="B57" s="5">
         <f t="shared" si="1"/>
         <v>46177</v>
       </c>
-      <c r="B57" t="s">
+      <c r="C57" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" s="5">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>61</v>
+      </c>
+      <c r="B58" s="5">
         <f t="shared" si="1"/>
         <v>46178</v>
       </c>
-      <c r="B58" t="s">
+      <c r="C58" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="5">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>61</v>
+      </c>
+      <c r="B59" s="5">
         <f t="shared" si="1"/>
         <v>46179</v>
       </c>
-      <c r="B59" t="s">
+      <c r="C59" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" s="5">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>61</v>
+      </c>
+      <c r="B60" s="5">
         <f t="shared" si="1"/>
         <v>46180</v>
       </c>
-      <c r="B60" t="s">
+      <c r="C60" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" s="5">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>61</v>
+      </c>
+      <c r="B61" s="5">
         <f t="shared" si="1"/>
         <v>46181</v>
       </c>
-      <c r="B61" t="s">
+      <c r="C61" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" s="5">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>61</v>
+      </c>
+      <c r="B62" s="5">
         <f t="shared" si="1"/>
         <v>46182</v>
       </c>
-      <c r="B62" t="s">
+      <c r="C62" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" s="5">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>61</v>
+      </c>
+      <c r="B63" s="5">
         <f t="shared" si="1"/>
         <v>46183</v>
       </c>
-      <c r="B63" t="s">
+      <c r="C63" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" s="5">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>61</v>
+      </c>
+      <c r="B64" s="5">
         <f t="shared" si="1"/>
         <v>46184</v>
       </c>
-      <c r="B64" t="s">
+      <c r="C64" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" s="5">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>61</v>
+      </c>
+      <c r="B65" s="5">
         <f t="shared" si="1"/>
         <v>46185</v>
       </c>
-      <c r="B65" t="s">
+      <c r="C65" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" s="5">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>61</v>
+      </c>
+      <c r="B66" s="5">
         <f t="shared" si="1"/>
         <v>46186</v>
       </c>
-      <c r="B66" t="s">
+      <c r="C66" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="5">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>61</v>
+      </c>
+      <c r="B67" s="5">
         <f t="shared" si="1"/>
         <v>46187</v>
       </c>
-      <c r="B67" t="s">
+      <c r="C67" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" s="5">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>61</v>
+      </c>
+      <c r="B68" s="5">
         <f t="shared" si="1"/>
         <v>46188</v>
       </c>
-      <c r="B68" t="s">
+      <c r="C68" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" s="5">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>61</v>
+      </c>
+      <c r="B69" s="5">
         <f t="shared" si="1"/>
         <v>46189</v>
       </c>
-      <c r="B69" t="s">
+      <c r="C69" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" s="5">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>61</v>
+      </c>
+      <c r="B70" s="5">
         <f t="shared" si="1"/>
         <v>46190</v>
       </c>
-      <c r="B70" t="s">
+      <c r="C70" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" s="5">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>61</v>
+      </c>
+      <c r="B71" s="5">
         <f t="shared" si="1"/>
         <v>46191</v>
       </c>
-      <c r="B71" t="s">
+      <c r="C71" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" s="5">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>61</v>
+      </c>
+      <c r="B72" s="5">
         <f t="shared" si="1"/>
         <v>46192</v>
       </c>
-      <c r="B72" t="s">
+      <c r="C72" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" s="5">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>61</v>
+      </c>
+      <c r="B73" s="5">
         <f t="shared" si="1"/>
         <v>46193</v>
       </c>
-      <c r="B73" t="s">
+      <c r="C73" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" s="5">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>61</v>
+      </c>
+      <c r="B74" s="5">
         <f t="shared" si="1"/>
         <v>46194</v>
       </c>
-      <c r="B74" t="s">
+      <c r="C74" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" s="5">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>61</v>
+      </c>
+      <c r="B75" s="5">
         <f t="shared" si="1"/>
         <v>46195</v>
       </c>
-      <c r="B75" t="s">
+      <c r="C75" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76" s="5">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>61</v>
+      </c>
+      <c r="B76" s="5">
         <f t="shared" si="1"/>
         <v>46196</v>
       </c>
-      <c r="B76" t="s">
+      <c r="C76" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77" s="5">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>61</v>
+      </c>
+      <c r="B77" s="5">
         <f t="shared" si="1"/>
         <v>46197</v>
       </c>
-      <c r="B77" t="s">
+      <c r="C77" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" s="5">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>61</v>
+      </c>
+      <c r="B78" s="5">
         <f t="shared" si="1"/>
         <v>46198</v>
       </c>
-      <c r="B78" t="s">
+      <c r="C78" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79" s="5">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>61</v>
+      </c>
+      <c r="B79" s="5">
         <f t="shared" si="1"/>
         <v>46199</v>
       </c>
-      <c r="B79" t="s">
+      <c r="C79" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80" s="5">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>61</v>
+      </c>
+      <c r="B80" s="5">
         <f t="shared" si="1"/>
         <v>46200</v>
       </c>
-      <c r="B80" t="s">
+      <c r="C80" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81" s="5">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>61</v>
+      </c>
+      <c r="B81" s="5">
         <f t="shared" si="1"/>
         <v>46201</v>
       </c>
-      <c r="B81" t="s">
+      <c r="C81" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A82" s="5">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>61</v>
+      </c>
+      <c r="B82" s="5">
         <f t="shared" si="1"/>
         <v>46202</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A83" s="5">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>61</v>
+      </c>
+      <c r="B83" s="5">
         <f t="shared" si="1"/>
         <v>46203</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A84" s="5">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>61</v>
+      </c>
+      <c r="B84" s="5">
         <f t="shared" si="1"/>
         <v>46204</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A85" s="5">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>61</v>
+      </c>
+      <c r="B85" s="5">
         <f t="shared" si="1"/>
         <v>46205</v>
       </c>
-      <c r="B85" t="s">
+      <c r="C85" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A86" s="5">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>61</v>
+      </c>
+      <c r="B86" s="5">
         <f t="shared" si="1"/>
         <v>46206</v>
       </c>
-      <c r="B86" t="s">
+      <c r="C86" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A87" s="5">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>61</v>
+      </c>
+      <c r="B87" s="5">
         <f t="shared" si="1"/>
         <v>46207</v>
       </c>
-      <c r="B87" t="s">
+      <c r="C87" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A88" s="5">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>61</v>
+      </c>
+      <c r="B88" s="5">
         <f t="shared" si="1"/>
         <v>46208</v>
       </c>
-      <c r="B88" t="s">
+      <c r="C88" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A89" s="5">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>61</v>
+      </c>
+      <c r="B89" s="5">
         <f t="shared" si="1"/>
         <v>46209</v>
       </c>
-      <c r="B89" t="s">
+      <c r="C89" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A90" s="5">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>61</v>
+      </c>
+      <c r="B90" s="5">
         <f t="shared" si="1"/>
         <v>46210</v>
       </c>
-      <c r="B90" t="s">
+      <c r="C90" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A91" s="5">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>61</v>
+      </c>
+      <c r="B91" s="5">
         <f t="shared" si="1"/>
         <v>46211</v>
       </c>
-      <c r="B91" t="s">
+      <c r="C91" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A92" s="5">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>61</v>
+      </c>
+      <c r="B92" s="5">
         <f t="shared" si="1"/>
         <v>46212</v>
       </c>
-      <c r="B92" t="s">
+      <c r="C92" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A93" s="5">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>61</v>
+      </c>
+      <c r="B93" s="5">
         <f t="shared" si="1"/>
         <v>46213</v>
       </c>
-      <c r="B93" t="s">
+      <c r="C93" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A94" s="5">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>61</v>
+      </c>
+      <c r="B94" s="5">
         <f t="shared" si="1"/>
         <v>46214</v>
       </c>
-      <c r="B94" t="s">
+      <c r="C94" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A95" s="5">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>61</v>
+      </c>
+      <c r="B95" s="5">
         <f t="shared" si="1"/>
         <v>46215</v>
       </c>
-      <c r="B95" t="s">
+      <c r="C95" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A96" s="5">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>61</v>
+      </c>
+      <c r="B96" s="5">
         <f t="shared" si="1"/>
         <v>46216</v>
       </c>
-      <c r="B96" t="s">
+      <c r="C96" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A97" s="5">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>61</v>
+      </c>
+      <c r="B97" s="5">
         <f t="shared" si="1"/>
         <v>46217</v>
       </c>
-      <c r="B97" t="s">
+      <c r="C97" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A98" s="5">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>61</v>
+      </c>
+      <c r="B98" s="5">
         <f t="shared" si="1"/>
         <v>46218</v>
       </c>
-      <c r="B98" t="s">
+      <c r="C98" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A99" s="5">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>61</v>
+      </c>
+      <c r="B99" s="5">
         <f t="shared" si="1"/>
         <v>46219</v>
       </c>
-      <c r="B99" t="s">
+      <c r="C99" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A100" s="5">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>61</v>
+      </c>
+      <c r="B100" s="5">
         <f t="shared" si="1"/>
         <v>46220</v>
       </c>
-      <c r="B100" t="s">
+      <c r="C100" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A101" s="5">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>61</v>
+      </c>
+      <c r="B101" s="5">
         <f t="shared" si="1"/>
         <v>46221</v>
       </c>
-      <c r="B101" t="s">
+      <c r="C101" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A102" s="5">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>61</v>
+      </c>
+      <c r="B102" s="5">
         <f t="shared" si="1"/>
         <v>46222</v>
       </c>
-      <c r="B102" t="s">
+      <c r="C102" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A103" s="5">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>61</v>
+      </c>
+      <c r="B103" s="5">
         <f t="shared" si="1"/>
         <v>46223</v>
       </c>
-      <c r="B103" t="s">
+      <c r="C103" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A104" s="5">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>61</v>
+      </c>
+      <c r="B104" s="5">
         <f t="shared" si="1"/>
         <v>46224</v>
       </c>
-      <c r="B104" t="s">
+      <c r="C104" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A105" s="5">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>61</v>
+      </c>
+      <c r="B105" s="5">
         <f t="shared" si="1"/>
         <v>46225</v>
       </c>
-      <c r="B105" t="s">
+      <c r="C105" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A106" s="5">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>61</v>
+      </c>
+      <c r="B106" s="5">
         <f t="shared" si="1"/>
         <v>46226</v>
       </c>
-      <c r="B106" t="s">
+      <c r="C106" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A107" s="5">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>61</v>
+      </c>
+      <c r="B107" s="5">
         <f t="shared" si="1"/>
         <v>46227</v>
       </c>
-      <c r="B107" t="s">
+      <c r="C107" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A108" s="5">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>61</v>
+      </c>
+      <c r="B108" s="5">
         <f t="shared" si="1"/>
         <v>46228</v>
       </c>
-      <c r="B108" t="s">
+      <c r="C108" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A109" s="5">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>61</v>
+      </c>
+      <c r="B109" s="5">
         <f t="shared" si="1"/>
         <v>46229</v>
       </c>
-      <c r="B109" t="s">
+      <c r="C109" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A110" s="5">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>61</v>
+      </c>
+      <c r="B110" s="5">
         <f t="shared" si="1"/>
         <v>46230</v>
       </c>
-      <c r="B110" t="s">
+      <c r="C110" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A111" s="5">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>61</v>
+      </c>
+      <c r="B111" s="5">
         <f t="shared" si="1"/>
         <v>46231</v>
       </c>
-      <c r="B111" t="s">
+      <c r="C111" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A112" s="5">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>61</v>
+      </c>
+      <c r="B112" s="5">
         <f t="shared" si="1"/>
         <v>46232</v>
       </c>
-      <c r="B112" t="s">
+      <c r="C112" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A113" s="5">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>61</v>
+      </c>
+      <c r="B113" s="5">
         <f t="shared" si="1"/>
         <v>46233</v>
       </c>
-      <c r="B113" t="s">
+      <c r="C113" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A114" s="5">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>61</v>
+      </c>
+      <c r="B114" s="5">
         <f t="shared" si="1"/>
         <v>46234</v>
       </c>
-      <c r="B114" t="s">
+      <c r="C114" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A115" s="5">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>61</v>
+      </c>
+      <c r="B115" s="5">
         <f t="shared" si="1"/>
         <v>46235</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A116" s="5">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>61</v>
+      </c>
+      <c r="B116" s="5">
         <f t="shared" si="1"/>
         <v>46236</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A117" s="5">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>61</v>
+      </c>
+      <c r="B117" s="5">
         <f t="shared" si="1"/>
         <v>46237</v>
       </c>
-      <c r="B117" t="s">
+      <c r="C117" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A118" s="5">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>61</v>
+      </c>
+      <c r="B118" s="5">
         <f t="shared" si="1"/>
         <v>46238</v>
       </c>
-      <c r="B118" t="s">
+      <c r="C118" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A119" s="5">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>61</v>
+      </c>
+      <c r="B119" s="5">
         <f t="shared" si="1"/>
         <v>46239</v>
       </c>
-      <c r="B119" t="s">
+      <c r="C119" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A120" s="5">
-        <f t="shared" ref="A120:A145" si="2">A119+1</f>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>61</v>
+      </c>
+      <c r="B120" s="5">
+        <f t="shared" ref="B120:B145" si="2">B119+1</f>
         <v>46240</v>
       </c>
-      <c r="B120" t="s">
+      <c r="C120" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A121" s="5">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>61</v>
+      </c>
+      <c r="B121" s="5">
         <f t="shared" si="2"/>
         <v>46241</v>
       </c>
-      <c r="B121" t="s">
+      <c r="C121" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A122" s="5">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>61</v>
+      </c>
+      <c r="B122" s="5">
         <f t="shared" si="2"/>
         <v>46242</v>
       </c>
-      <c r="B122" t="s">
+      <c r="C122" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A123" s="5">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>61</v>
+      </c>
+      <c r="B123" s="5">
         <f t="shared" si="2"/>
         <v>46243</v>
       </c>
-      <c r="B123" t="s">
+      <c r="C123" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A124" s="5">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>61</v>
+      </c>
+      <c r="B124" s="5">
         <f t="shared" si="2"/>
         <v>46244</v>
       </c>
-      <c r="B124" t="s">
+      <c r="C124" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A125" s="5">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>61</v>
+      </c>
+      <c r="B125" s="5">
         <f t="shared" si="2"/>
         <v>46245</v>
       </c>
-      <c r="B125" t="s">
+      <c r="C125" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A126" s="5">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>61</v>
+      </c>
+      <c r="B126" s="5">
         <f t="shared" si="2"/>
         <v>46246</v>
       </c>
-      <c r="B126" t="s">
+      <c r="C126" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A127" s="5">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>61</v>
+      </c>
+      <c r="B127" s="5">
         <f t="shared" si="2"/>
         <v>46247</v>
       </c>
-      <c r="B127" t="s">
+      <c r="C127" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A128" s="5">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>61</v>
+      </c>
+      <c r="B128" s="5">
         <f t="shared" si="2"/>
         <v>46248</v>
       </c>
-      <c r="B128" t="s">
+      <c r="C128" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A129" s="5">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>61</v>
+      </c>
+      <c r="B129" s="5">
         <f t="shared" si="2"/>
         <v>46249</v>
       </c>
-      <c r="B129" t="s">
+      <c r="C129" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A130" s="5">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>61</v>
+      </c>
+      <c r="B130" s="5">
         <f t="shared" si="2"/>
         <v>46250</v>
       </c>
-      <c r="B130" t="s">
+      <c r="C130" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A131" s="5">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>61</v>
+      </c>
+      <c r="B131" s="5">
         <f t="shared" si="2"/>
         <v>46251</v>
       </c>
-      <c r="B131" t="s">
+      <c r="C131" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A132" s="5">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>61</v>
+      </c>
+      <c r="B132" s="5">
         <f t="shared" si="2"/>
         <v>46252</v>
       </c>
-      <c r="B132" t="s">
+      <c r="C132" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A133" s="5">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>61</v>
+      </c>
+      <c r="B133" s="5">
         <f t="shared" si="2"/>
         <v>46253</v>
       </c>
-      <c r="B133" t="s">
+      <c r="C133" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A134" s="5">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>61</v>
+      </c>
+      <c r="B134" s="5">
         <f t="shared" si="2"/>
         <v>46254</v>
       </c>
-      <c r="B134" t="s">
+      <c r="C134" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A135" s="5">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>61</v>
+      </c>
+      <c r="B135" s="5">
         <f t="shared" si="2"/>
         <v>46255</v>
       </c>
-      <c r="B135" t="s">
+      <c r="C135" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A136" s="5">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>61</v>
+      </c>
+      <c r="B136" s="5">
         <f t="shared" si="2"/>
         <v>46256</v>
       </c>
-      <c r="B136" t="s">
+      <c r="C136" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A137" s="5">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>61</v>
+      </c>
+      <c r="B137" s="5">
         <f t="shared" si="2"/>
         <v>46257</v>
       </c>
-      <c r="B137" t="s">
+      <c r="C137" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A138" s="5">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>61</v>
+      </c>
+      <c r="B138" s="5">
         <f t="shared" si="2"/>
         <v>46258</v>
       </c>
-      <c r="B138" t="s">
+      <c r="C138" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A139" s="5">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>61</v>
+      </c>
+      <c r="B139" s="5">
         <f t="shared" si="2"/>
         <v>46259</v>
       </c>
-      <c r="B139" t="s">
+      <c r="C139" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A140" s="5">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>61</v>
+      </c>
+      <c r="B140" s="5">
         <f t="shared" si="2"/>
         <v>46260</v>
       </c>
-      <c r="B140" t="s">
+      <c r="C140" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A141" s="5">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>61</v>
+      </c>
+      <c r="B141" s="5">
         <f t="shared" si="2"/>
         <v>46261</v>
       </c>
-      <c r="B141" t="s">
+      <c r="C141" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A142" s="5">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>61</v>
+      </c>
+      <c r="B142" s="5">
         <f t="shared" si="2"/>
         <v>46262</v>
       </c>
-      <c r="B142" t="s">
+      <c r="C142" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A143" s="5">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>61</v>
+      </c>
+      <c r="B143" s="5">
         <f t="shared" si="2"/>
         <v>46263</v>
       </c>
-      <c r="B143" t="s">
+      <c r="C143" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A144" s="5">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>61</v>
+      </c>
+      <c r="B144" s="5">
         <f t="shared" si="2"/>
         <v>46264</v>
       </c>
-      <c r="B144" t="s">
+      <c r="C144" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A145" s="5">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>61</v>
+      </c>
+      <c r="B145" s="5">
         <f t="shared" si="2"/>
         <v>46265</v>
       </c>
-      <c r="B145" t="s">
+      <c r="C145" t="s">
         <v>21</v>
       </c>
     </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>62</v>
+      </c>
+      <c r="B146" s="3">
+        <v>46266</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>62</v>
+      </c>
+      <c r="B147" s="3">
+        <f>B146+1</f>
+        <v>46267</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>62</v>
+      </c>
+      <c r="B148" s="3">
+        <f t="shared" ref="B148:B197" si="3">B147+1</f>
+        <v>46268</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>62</v>
+      </c>
+      <c r="B149" s="3">
+        <f t="shared" si="3"/>
+        <v>46269</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>62</v>
+      </c>
+      <c r="B150" s="3">
+        <f t="shared" si="3"/>
+        <v>46270</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>62</v>
+      </c>
+      <c r="B151" s="3">
+        <f t="shared" si="3"/>
+        <v>46271</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>62</v>
+      </c>
+      <c r="B152" s="3">
+        <f t="shared" si="3"/>
+        <v>46272</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>62</v>
+      </c>
+      <c r="B153" s="3">
+        <f t="shared" si="3"/>
+        <v>46273</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>62</v>
+      </c>
+      <c r="B154" s="3">
+        <f t="shared" si="3"/>
+        <v>46274</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>62</v>
+      </c>
+      <c r="B155" s="3">
+        <f t="shared" si="3"/>
+        <v>46275</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>62</v>
+      </c>
+      <c r="B156" s="3">
+        <f t="shared" si="3"/>
+        <v>46276</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>62</v>
+      </c>
+      <c r="B157" s="3">
+        <f t="shared" si="3"/>
+        <v>46277</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>62</v>
+      </c>
+      <c r="B158" s="3">
+        <f t="shared" si="3"/>
+        <v>46278</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>62</v>
+      </c>
+      <c r="B159" s="3">
+        <f t="shared" si="3"/>
+        <v>46279</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>62</v>
+      </c>
+      <c r="B160" s="3">
+        <f t="shared" si="3"/>
+        <v>46280</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>62</v>
+      </c>
+      <c r="B161" s="3">
+        <f t="shared" si="3"/>
+        <v>46281</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>62</v>
+      </c>
+      <c r="B162" s="3">
+        <f t="shared" si="3"/>
+        <v>46282</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>62</v>
+      </c>
+      <c r="B163" s="3">
+        <f t="shared" si="3"/>
+        <v>46283</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>62</v>
+      </c>
+      <c r="B164" s="3">
+        <f t="shared" si="3"/>
+        <v>46284</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>62</v>
+      </c>
+      <c r="B165" s="3">
+        <f t="shared" si="3"/>
+        <v>46285</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>62</v>
+      </c>
+      <c r="B166" s="3">
+        <f t="shared" si="3"/>
+        <v>46286</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>62</v>
+      </c>
+      <c r="B167" s="3">
+        <f t="shared" si="3"/>
+        <v>46287</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>62</v>
+      </c>
+      <c r="B168" s="3">
+        <f t="shared" si="3"/>
+        <v>46288</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>62</v>
+      </c>
+      <c r="B169" s="3">
+        <f t="shared" si="3"/>
+        <v>46289</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>62</v>
+      </c>
+      <c r="B170" s="3">
+        <f t="shared" si="3"/>
+        <v>46290</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>62</v>
+      </c>
+      <c r="B171" s="3">
+        <f t="shared" si="3"/>
+        <v>46291</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>62</v>
+      </c>
+      <c r="B172" s="3">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+      <c r="C172" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>62</v>
+      </c>
+      <c r="B173" s="3">
+        <v>46296</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>62</v>
+      </c>
+      <c r="B174" s="3">
+        <f t="shared" si="3"/>
+        <v>46297</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>62</v>
+      </c>
+      <c r="B175" s="3">
+        <f t="shared" si="3"/>
+        <v>46298</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>62</v>
+      </c>
+      <c r="B176" s="3">
+        <f t="shared" si="3"/>
+        <v>46299</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>62</v>
+      </c>
+      <c r="B177" s="3">
+        <f t="shared" si="3"/>
+        <v>46300</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>62</v>
+      </c>
+      <c r="B178" s="3">
+        <f t="shared" si="3"/>
+        <v>46301</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>62</v>
+      </c>
+      <c r="B179" s="3">
+        <f t="shared" si="3"/>
+        <v>46302</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>62</v>
+      </c>
+      <c r="B180" s="3">
+        <f t="shared" si="3"/>
+        <v>46303</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>62</v>
+      </c>
+      <c r="B181" s="3">
+        <f t="shared" si="3"/>
+        <v>46304</v>
+      </c>
+      <c r="C181" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>62</v>
+      </c>
+      <c r="B182" s="3">
+        <f t="shared" si="3"/>
+        <v>46305</v>
+      </c>
+      <c r="C182" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>62</v>
+      </c>
+      <c r="B183" s="3">
+        <f t="shared" si="3"/>
+        <v>46306</v>
+      </c>
+      <c r="C183" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>62</v>
+      </c>
+      <c r="B184" s="3">
+        <f t="shared" si="3"/>
+        <v>46307</v>
+      </c>
+      <c r="C184" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>62</v>
+      </c>
+      <c r="B185" s="3">
+        <f t="shared" si="3"/>
+        <v>46308</v>
+      </c>
+      <c r="C185" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>62</v>
+      </c>
+      <c r="B186" s="3">
+        <f t="shared" si="3"/>
+        <v>46309</v>
+      </c>
+      <c r="C186" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>62</v>
+      </c>
+      <c r="B187" s="3">
+        <f t="shared" si="3"/>
+        <v>46310</v>
+      </c>
+      <c r="C187" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>62</v>
+      </c>
+      <c r="B188" s="3">
+        <f t="shared" si="3"/>
+        <v>46311</v>
+      </c>
+      <c r="C188" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>62</v>
+      </c>
+      <c r="B189" s="3">
+        <f t="shared" si="3"/>
+        <v>46312</v>
+      </c>
+      <c r="C189" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>62</v>
+      </c>
+      <c r="B190" s="3">
+        <f t="shared" si="3"/>
+        <v>46313</v>
+      </c>
+      <c r="C190" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>62</v>
+      </c>
+      <c r="B191" s="3">
+        <f t="shared" si="3"/>
+        <v>46314</v>
+      </c>
+      <c r="C191" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>62</v>
+      </c>
+      <c r="B192" s="3">
+        <f t="shared" si="3"/>
+        <v>46315</v>
+      </c>
+      <c r="C192" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>62</v>
+      </c>
+      <c r="B193" s="3">
+        <f t="shared" si="3"/>
+        <v>46316</v>
+      </c>
+      <c r="C193" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>62</v>
+      </c>
+      <c r="B194" s="3">
+        <f t="shared" si="3"/>
+        <v>46317</v>
+      </c>
+      <c r="C194" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>62</v>
+      </c>
+      <c r="B195" s="3">
+        <f t="shared" si="3"/>
+        <v>46318</v>
+      </c>
+      <c r="C195" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>62</v>
+      </c>
+      <c r="B196" s="3">
+        <f t="shared" si="3"/>
+        <v>46319</v>
+      </c>
+      <c r="C196" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>62</v>
+      </c>
+      <c r="B197" s="3">
+        <f t="shared" si="3"/>
+        <v>46320</v>
+      </c>
+      <c r="C197" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>62</v>
+      </c>
+      <c r="B198" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C198" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>62</v>
+      </c>
+      <c r="B199" s="5">
+        <f>B198+1</f>
+        <v>46175</v>
+      </c>
+      <c r="C199" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>62</v>
+      </c>
+      <c r="B200" s="5">
+        <f t="shared" ref="B200:B263" si="4">B199+1</f>
+        <v>46176</v>
+      </c>
+      <c r="C200" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>62</v>
+      </c>
+      <c r="B201" s="5">
+        <f t="shared" si="4"/>
+        <v>46177</v>
+      </c>
+      <c r="C201" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>62</v>
+      </c>
+      <c r="B202" s="5">
+        <f t="shared" si="4"/>
+        <v>46178</v>
+      </c>
+      <c r="C202" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>62</v>
+      </c>
+      <c r="B203" s="5">
+        <f t="shared" si="4"/>
+        <v>46179</v>
+      </c>
+      <c r="C203" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>62</v>
+      </c>
+      <c r="B204" s="5">
+        <f t="shared" si="4"/>
+        <v>46180</v>
+      </c>
+      <c r="C204" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>62</v>
+      </c>
+      <c r="B205" s="5">
+        <f t="shared" si="4"/>
+        <v>46181</v>
+      </c>
+      <c r="C205" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>62</v>
+      </c>
+      <c r="B206" s="5">
+        <f t="shared" si="4"/>
+        <v>46182</v>
+      </c>
+      <c r="C206" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>62</v>
+      </c>
+      <c r="B207" s="5">
+        <f t="shared" si="4"/>
+        <v>46183</v>
+      </c>
+      <c r="C207" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>62</v>
+      </c>
+      <c r="B208" s="5">
+        <f t="shared" si="4"/>
+        <v>46184</v>
+      </c>
+      <c r="C208" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>62</v>
+      </c>
+      <c r="B209" s="5">
+        <f t="shared" si="4"/>
+        <v>46185</v>
+      </c>
+      <c r="C209" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>62</v>
+      </c>
+      <c r="B210" s="5">
+        <f t="shared" si="4"/>
+        <v>46186</v>
+      </c>
+      <c r="C210" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>62</v>
+      </c>
+      <c r="B211" s="5">
+        <f t="shared" si="4"/>
+        <v>46187</v>
+      </c>
+      <c r="C211" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>62</v>
+      </c>
+      <c r="B212" s="5">
+        <f t="shared" si="4"/>
+        <v>46188</v>
+      </c>
+      <c r="C212" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>62</v>
+      </c>
+      <c r="B213" s="5">
+        <f t="shared" si="4"/>
+        <v>46189</v>
+      </c>
+      <c r="C213" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>62</v>
+      </c>
+      <c r="B214" s="5">
+        <f t="shared" si="4"/>
+        <v>46190</v>
+      </c>
+      <c r="C214" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>62</v>
+      </c>
+      <c r="B215" s="5">
+        <f t="shared" si="4"/>
+        <v>46191</v>
+      </c>
+      <c r="C215" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>62</v>
+      </c>
+      <c r="B216" s="5">
+        <f t="shared" si="4"/>
+        <v>46192</v>
+      </c>
+      <c r="C216" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>62</v>
+      </c>
+      <c r="B217" s="5">
+        <f t="shared" si="4"/>
+        <v>46193</v>
+      </c>
+      <c r="C217" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>62</v>
+      </c>
+      <c r="B218" s="5">
+        <f t="shared" si="4"/>
+        <v>46194</v>
+      </c>
+      <c r="C218" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>62</v>
+      </c>
+      <c r="B219" s="5">
+        <f t="shared" si="4"/>
+        <v>46195</v>
+      </c>
+      <c r="C219" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>62</v>
+      </c>
+      <c r="B220" s="5">
+        <f t="shared" si="4"/>
+        <v>46196</v>
+      </c>
+      <c r="C220" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>62</v>
+      </c>
+      <c r="B221" s="5">
+        <f t="shared" si="4"/>
+        <v>46197</v>
+      </c>
+      <c r="C221" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>62</v>
+      </c>
+      <c r="B222" s="5">
+        <f t="shared" si="4"/>
+        <v>46198</v>
+      </c>
+      <c r="C222" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>62</v>
+      </c>
+      <c r="B223" s="5">
+        <f t="shared" si="4"/>
+        <v>46199</v>
+      </c>
+      <c r="C223" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>62</v>
+      </c>
+      <c r="B224" s="5">
+        <f t="shared" si="4"/>
+        <v>46200</v>
+      </c>
+      <c r="C224" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>62</v>
+      </c>
+      <c r="B225" s="5">
+        <f t="shared" si="4"/>
+        <v>46201</v>
+      </c>
+      <c r="C225" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>62</v>
+      </c>
+      <c r="B226" s="5">
+        <f t="shared" si="4"/>
+        <v>46202</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>62</v>
+      </c>
+      <c r="B227" s="5">
+        <f t="shared" si="4"/>
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>62</v>
+      </c>
+      <c r="B228" s="5">
+        <f t="shared" si="4"/>
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>62</v>
+      </c>
+      <c r="B229" s="5">
+        <f t="shared" si="4"/>
+        <v>46205</v>
+      </c>
+      <c r="C229" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>62</v>
+      </c>
+      <c r="B230" s="5">
+        <f t="shared" si="4"/>
+        <v>46206</v>
+      </c>
+      <c r="C230" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>62</v>
+      </c>
+      <c r="B231" s="5">
+        <f t="shared" si="4"/>
+        <v>46207</v>
+      </c>
+      <c r="C231" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>62</v>
+      </c>
+      <c r="B232" s="5">
+        <f t="shared" si="4"/>
+        <v>46208</v>
+      </c>
+      <c r="C232" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>62</v>
+      </c>
+      <c r="B233" s="5">
+        <f t="shared" si="4"/>
+        <v>46209</v>
+      </c>
+      <c r="C233" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>62</v>
+      </c>
+      <c r="B234" s="5">
+        <f t="shared" si="4"/>
+        <v>46210</v>
+      </c>
+      <c r="C234" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>62</v>
+      </c>
+      <c r="B235" s="5">
+        <f t="shared" si="4"/>
+        <v>46211</v>
+      </c>
+      <c r="C235" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>62</v>
+      </c>
+      <c r="B236" s="5">
+        <f t="shared" si="4"/>
+        <v>46212</v>
+      </c>
+      <c r="C236" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>62</v>
+      </c>
+      <c r="B237" s="5">
+        <f t="shared" si="4"/>
+        <v>46213</v>
+      </c>
+      <c r="C237" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>62</v>
+      </c>
+      <c r="B238" s="5">
+        <f t="shared" si="4"/>
+        <v>46214</v>
+      </c>
+      <c r="C238" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>62</v>
+      </c>
+      <c r="B239" s="5">
+        <f t="shared" si="4"/>
+        <v>46215</v>
+      </c>
+      <c r="C239" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>62</v>
+      </c>
+      <c r="B240" s="5">
+        <f t="shared" si="4"/>
+        <v>46216</v>
+      </c>
+      <c r="C240" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>62</v>
+      </c>
+      <c r="B241" s="5">
+        <f t="shared" si="4"/>
+        <v>46217</v>
+      </c>
+      <c r="C241" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>62</v>
+      </c>
+      <c r="B242" s="5">
+        <f t="shared" si="4"/>
+        <v>46218</v>
+      </c>
+      <c r="C242" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>62</v>
+      </c>
+      <c r="B243" s="5">
+        <f t="shared" si="4"/>
+        <v>46219</v>
+      </c>
+      <c r="C243" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>62</v>
+      </c>
+      <c r="B244" s="5">
+        <f t="shared" si="4"/>
+        <v>46220</v>
+      </c>
+      <c r="C244" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>62</v>
+      </c>
+      <c r="B245" s="5">
+        <f t="shared" si="4"/>
+        <v>46221</v>
+      </c>
+      <c r="C245" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>62</v>
+      </c>
+      <c r="B246" s="5">
+        <f t="shared" si="4"/>
+        <v>46222</v>
+      </c>
+      <c r="C246" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>62</v>
+      </c>
+      <c r="B247" s="5">
+        <f t="shared" si="4"/>
+        <v>46223</v>
+      </c>
+      <c r="C247" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>62</v>
+      </c>
+      <c r="B248" s="5">
+        <f t="shared" si="4"/>
+        <v>46224</v>
+      </c>
+      <c r="C248" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>62</v>
+      </c>
+      <c r="B249" s="5">
+        <f t="shared" si="4"/>
+        <v>46225</v>
+      </c>
+      <c r="C249" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>62</v>
+      </c>
+      <c r="B250" s="5">
+        <f t="shared" si="4"/>
+        <v>46226</v>
+      </c>
+      <c r="C250" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>62</v>
+      </c>
+      <c r="B251" s="5">
+        <f t="shared" si="4"/>
+        <v>46227</v>
+      </c>
+      <c r="C251" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>62</v>
+      </c>
+      <c r="B252" s="5">
+        <f t="shared" si="4"/>
+        <v>46228</v>
+      </c>
+      <c r="C252" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>62</v>
+      </c>
+      <c r="B253" s="5">
+        <f t="shared" si="4"/>
+        <v>46229</v>
+      </c>
+      <c r="C253" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>62</v>
+      </c>
+      <c r="B254" s="5">
+        <f t="shared" si="4"/>
+        <v>46230</v>
+      </c>
+      <c r="C254" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>62</v>
+      </c>
+      <c r="B255" s="5">
+        <f t="shared" si="4"/>
+        <v>46231</v>
+      </c>
+      <c r="C255" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>62</v>
+      </c>
+      <c r="B256" s="5">
+        <f t="shared" si="4"/>
+        <v>46232</v>
+      </c>
+      <c r="C256" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>62</v>
+      </c>
+      <c r="B257" s="5">
+        <f t="shared" si="4"/>
+        <v>46233</v>
+      </c>
+      <c r="C257" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>62</v>
+      </c>
+      <c r="B258" s="5">
+        <f t="shared" si="4"/>
+        <v>46234</v>
+      </c>
+      <c r="C258" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>62</v>
+      </c>
+      <c r="B259" s="5">
+        <f t="shared" si="4"/>
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>62</v>
+      </c>
+      <c r="B260" s="5">
+        <f t="shared" si="4"/>
+        <v>46236</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>62</v>
+      </c>
+      <c r="B261" s="5">
+        <f t="shared" si="4"/>
+        <v>46237</v>
+      </c>
+      <c r="C261" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>62</v>
+      </c>
+      <c r="B262" s="5">
+        <f t="shared" si="4"/>
+        <v>46238</v>
+      </c>
+      <c r="C262" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>62</v>
+      </c>
+      <c r="B263" s="5">
+        <f t="shared" si="4"/>
+        <v>46239</v>
+      </c>
+      <c r="C263" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>62</v>
+      </c>
+      <c r="B264" s="5">
+        <f t="shared" ref="B264:B289" si="5">B263+1</f>
+        <v>46240</v>
+      </c>
+      <c r="C264" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>62</v>
+      </c>
+      <c r="B265" s="5">
+        <f t="shared" si="5"/>
+        <v>46241</v>
+      </c>
+      <c r="C265" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>62</v>
+      </c>
+      <c r="B266" s="5">
+        <f t="shared" si="5"/>
+        <v>46242</v>
+      </c>
+      <c r="C266" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>62</v>
+      </c>
+      <c r="B267" s="5">
+        <f t="shared" si="5"/>
+        <v>46243</v>
+      </c>
+      <c r="C267" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>62</v>
+      </c>
+      <c r="B268" s="5">
+        <f t="shared" si="5"/>
+        <v>46244</v>
+      </c>
+      <c r="C268" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>62</v>
+      </c>
+      <c r="B269" s="5">
+        <f t="shared" si="5"/>
+        <v>46245</v>
+      </c>
+      <c r="C269" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>62</v>
+      </c>
+      <c r="B270" s="5">
+        <f t="shared" si="5"/>
+        <v>46246</v>
+      </c>
+      <c r="C270" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>62</v>
+      </c>
+      <c r="B271" s="5">
+        <f t="shared" si="5"/>
+        <v>46247</v>
+      </c>
+      <c r="C271" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>62</v>
+      </c>
+      <c r="B272" s="5">
+        <f t="shared" si="5"/>
+        <v>46248</v>
+      </c>
+      <c r="C272" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>62</v>
+      </c>
+      <c r="B273" s="5">
+        <f t="shared" si="5"/>
+        <v>46249</v>
+      </c>
+      <c r="C273" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>62</v>
+      </c>
+      <c r="B274" s="5">
+        <f t="shared" si="5"/>
+        <v>46250</v>
+      </c>
+      <c r="C274" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>62</v>
+      </c>
+      <c r="B275" s="5">
+        <f t="shared" si="5"/>
+        <v>46251</v>
+      </c>
+      <c r="C275" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>62</v>
+      </c>
+      <c r="B276" s="5">
+        <f t="shared" si="5"/>
+        <v>46252</v>
+      </c>
+      <c r="C276" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>62</v>
+      </c>
+      <c r="B277" s="5">
+        <f t="shared" si="5"/>
+        <v>46253</v>
+      </c>
+      <c r="C277" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>62</v>
+      </c>
+      <c r="B278" s="5">
+        <f t="shared" si="5"/>
+        <v>46254</v>
+      </c>
+      <c r="C278" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>62</v>
+      </c>
+      <c r="B279" s="5">
+        <f t="shared" si="5"/>
+        <v>46255</v>
+      </c>
+      <c r="C279" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>62</v>
+      </c>
+      <c r="B280" s="5">
+        <f t="shared" si="5"/>
+        <v>46256</v>
+      </c>
+      <c r="C280" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>62</v>
+      </c>
+      <c r="B281" s="5">
+        <f t="shared" si="5"/>
+        <v>46257</v>
+      </c>
+      <c r="C281" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
+        <v>62</v>
+      </c>
+      <c r="B282" s="5">
+        <f t="shared" si="5"/>
+        <v>46258</v>
+      </c>
+      <c r="C282" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>62</v>
+      </c>
+      <c r="B283" s="5">
+        <f t="shared" si="5"/>
+        <v>46259</v>
+      </c>
+      <c r="C283" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>62</v>
+      </c>
+      <c r="B284" s="5">
+        <f t="shared" si="5"/>
+        <v>46260</v>
+      </c>
+      <c r="C284" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>62</v>
+      </c>
+      <c r="B285" s="5">
+        <f t="shared" si="5"/>
+        <v>46261</v>
+      </c>
+      <c r="C285" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>62</v>
+      </c>
+      <c r="B286" s="5">
+        <f t="shared" si="5"/>
+        <v>46262</v>
+      </c>
+      <c r="C286" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>62</v>
+      </c>
+      <c r="B287" s="5">
+        <f t="shared" si="5"/>
+        <v>46263</v>
+      </c>
+      <c r="C287" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
+        <v>62</v>
+      </c>
+      <c r="B288" s="5">
+        <f t="shared" si="5"/>
+        <v>46264</v>
+      </c>
+      <c r="C288" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>62</v>
+      </c>
+      <c r="B289" s="5">
+        <f t="shared" si="5"/>
+        <v>46265</v>
+      </c>
+      <c r="C289" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B53" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:C289" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3647,7 +5784,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34B2C8DF-4561-40B2-8E7C-6CD69559B9AE}">
-  <dimension ref="A1:I1240"/>
+  <dimension ref="A1:I1241"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="20.85546875" customWidth="1"/>
@@ -38064,10 +40201,34 @@
       </c>
     </row>
     <row r="1148" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1148" s="2"/>
-      <c r="B1148" s="2"/>
-      <c r="E1148" s="2"/>
-      <c r="I1148" s="2"/>
+      <c r="A1148" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1148" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1148" t="s">
+        <v>112</v>
+      </c>
+      <c r="D1148" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1148" s="2">
+        <v>2</v>
+      </c>
+      <c r="F1148" t="s">
+        <v>83</v>
+      </c>
+      <c r="G1148">
+        <v>6.69</v>
+      </c>
+      <c r="H1148">
+        <v>5.99</v>
+      </c>
+      <c r="I1148" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1148,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>MICLN.png</v>
+      </c>
     </row>
     <row r="1149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1149" s="2" t="s">
@@ -38080,7 +40241,7 @@
         <v>112</v>
       </c>
       <c r="D1149" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1149" s="2">
         <v>2</v>
@@ -38107,10 +40268,10 @@
         <v>62</v>
       </c>
       <c r="C1150" t="s">
-        <v>112</v>
+        <v>29</v>
       </c>
       <c r="D1150" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E1150" s="2">
         <v>2</v>
@@ -38140,7 +40301,7 @@
         <v>29</v>
       </c>
       <c r="D1151" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1151" s="2">
         <v>2</v>
@@ -38167,10 +40328,10 @@
         <v>62</v>
       </c>
       <c r="C1152" t="s">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="D1152" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E1152" s="2">
         <v>2</v>
@@ -38200,7 +40361,7 @@
         <v>87</v>
       </c>
       <c r="D1153" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1153" s="2">
         <v>2</v>
@@ -38227,10 +40388,10 @@
         <v>62</v>
       </c>
       <c r="C1154" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D1154" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E1154" s="2">
         <v>2</v>
@@ -38260,7 +40421,7 @@
         <v>88</v>
       </c>
       <c r="D1155" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1155" s="2">
         <v>2</v>
@@ -38287,10 +40448,10 @@
         <v>62</v>
       </c>
       <c r="C1156" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="D1156" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E1156" s="2">
         <v>2</v>
@@ -38320,7 +40481,7 @@
         <v>113</v>
       </c>
       <c r="D1157" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1157" s="2">
         <v>2</v>
@@ -38347,7 +40508,7 @@
         <v>62</v>
       </c>
       <c r="C1158" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="D1158" t="s">
         <v>26</v>
@@ -38377,7 +40538,7 @@
         <v>62</v>
       </c>
       <c r="C1159" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D1159" t="s">
         <v>26</v>
@@ -38410,7 +40571,7 @@
         <v>89</v>
       </c>
       <c r="D1160" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E1160" s="2">
         <v>2</v>
@@ -38437,7 +40598,7 @@
         <v>62</v>
       </c>
       <c r="C1161" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D1161" t="s">
         <v>25</v>
@@ -38467,26 +40628,26 @@
         <v>62</v>
       </c>
       <c r="C1162" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="D1162" t="s">
         <v>25</v>
       </c>
       <c r="E1162" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1162" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G1162">
-        <v>6.69</v>
+        <v>6.99</v>
       </c>
       <c r="H1162">
-        <v>5.99</v>
+        <v>6.19</v>
       </c>
       <c r="I1162" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1162,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>MICLN.png</v>
+        <v>STELN.png</v>
       </c>
     </row>
     <row r="1163" spans="1:9" x14ac:dyDescent="0.25">
@@ -38497,7 +40658,7 @@
         <v>62</v>
       </c>
       <c r="C1163" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="D1163" t="s">
         <v>25</v>
@@ -38527,7 +40688,7 @@
         <v>62</v>
       </c>
       <c r="C1164" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="D1164" t="s">
         <v>25</v>
@@ -38557,7 +40718,7 @@
         <v>62</v>
       </c>
       <c r="C1165" t="s">
-        <v>112</v>
+        <v>29</v>
       </c>
       <c r="D1165" t="s">
         <v>25</v>
@@ -38587,7 +40748,7 @@
         <v>62</v>
       </c>
       <c r="C1166" t="s">
-        <v>29</v>
+        <v>88</v>
       </c>
       <c r="D1166" t="s">
         <v>25</v>
@@ -38617,7 +40778,7 @@
         <v>62</v>
       </c>
       <c r="C1167" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D1167" t="s">
         <v>25</v>
@@ -38647,7 +40808,7 @@
         <v>62</v>
       </c>
       <c r="C1168" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D1168" t="s">
         <v>25</v>
@@ -38677,10 +40838,10 @@
         <v>62</v>
       </c>
       <c r="C1169" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="D1169" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1169" s="2">
         <v>1</v>
@@ -38707,7 +40868,7 @@
         <v>62</v>
       </c>
       <c r="C1170" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="D1170" t="s">
         <v>26</v>
@@ -38737,7 +40898,7 @@
         <v>62</v>
       </c>
       <c r="C1171" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="D1171" t="s">
         <v>26</v>
@@ -38767,7 +40928,7 @@
         <v>62</v>
       </c>
       <c r="C1172" t="s">
-        <v>112</v>
+        <v>29</v>
       </c>
       <c r="D1172" t="s">
         <v>26</v>
@@ -38797,7 +40958,7 @@
         <v>62</v>
       </c>
       <c r="C1173" t="s">
-        <v>29</v>
+        <v>88</v>
       </c>
       <c r="D1173" t="s">
         <v>26</v>
@@ -38827,7 +40988,7 @@
         <v>62</v>
       </c>
       <c r="C1174" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D1174" t="s">
         <v>26</v>
@@ -38857,26 +41018,26 @@
         <v>62</v>
       </c>
       <c r="C1175" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D1175" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E1175" s="2">
         <v>1</v>
       </c>
       <c r="F1175" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G1175">
+        <v>7.99</v>
+      </c>
+      <c r="H1175">
         <v>6.99</v>
-      </c>
-      <c r="H1175">
-        <v>6.19</v>
       </c>
       <c r="I1175" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1175,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>STELN.png</v>
+        <v>CORLN.png</v>
       </c>
     </row>
     <row r="1176" spans="1:9" x14ac:dyDescent="0.25">
@@ -38887,10 +41048,10 @@
         <v>62</v>
       </c>
       <c r="C1176" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="D1176" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1176" s="2">
         <v>1</v>
@@ -38917,7 +41078,7 @@
         <v>62</v>
       </c>
       <c r="C1177" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="D1177" t="s">
         <v>26</v>
@@ -38947,7 +41108,7 @@
         <v>62</v>
       </c>
       <c r="C1178" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D1178" t="s">
         <v>26</v>
@@ -38977,10 +41138,10 @@
         <v>62</v>
       </c>
       <c r="C1179" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D1179" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E1179" s="2">
         <v>1</v>
@@ -39007,7 +41168,7 @@
         <v>62</v>
       </c>
       <c r="C1180" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D1180" t="s">
         <v>25</v>
@@ -39037,7 +41198,7 @@
         <v>62</v>
       </c>
       <c r="C1181" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D1181" t="s">
         <v>25</v>
@@ -39046,7 +41207,7 @@
         <v>1</v>
       </c>
       <c r="F1181" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G1181">
         <v>7.99</v>
@@ -39056,7 +41217,7 @@
       </c>
       <c r="I1181" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1181,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>CORLN.png</v>
+        <v>CORCEROLN.png</v>
       </c>
     </row>
     <row r="1182" spans="1:9" x14ac:dyDescent="0.25">
@@ -39067,10 +41228,10 @@
         <v>62</v>
       </c>
       <c r="C1182" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="D1182" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1182" s="2">
         <v>1</v>
@@ -39097,7 +41258,7 @@
         <v>62</v>
       </c>
       <c r="C1183" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="D1183" t="s">
         <v>26</v>
@@ -39127,7 +41288,7 @@
         <v>62</v>
       </c>
       <c r="C1184" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D1184" t="s">
         <v>26</v>
@@ -39157,10 +41318,10 @@
         <v>62</v>
       </c>
       <c r="C1185" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D1185" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E1185" s="2">
         <v>1</v>
@@ -39187,7 +41348,7 @@
         <v>62</v>
       </c>
       <c r="C1186" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D1186" t="s">
         <v>25</v>
@@ -39217,7 +41378,7 @@
         <v>62</v>
       </c>
       <c r="C1187" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="D1187" t="s">
         <v>25</v>
@@ -39226,7 +41387,7 @@
         <v>1</v>
       </c>
       <c r="F1187" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G1187">
         <v>7.99</v>
@@ -39236,7 +41397,7 @@
       </c>
       <c r="I1187" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1187,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>CORCEROLN.png</v>
+        <v>CORLN.png</v>
       </c>
     </row>
     <row r="1188" spans="1:9" x14ac:dyDescent="0.25">
@@ -39250,7 +41411,7 @@
         <v>112</v>
       </c>
       <c r="D1188" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1188" s="2">
         <v>1</v>
@@ -39277,10 +41438,10 @@
         <v>62</v>
       </c>
       <c r="C1189" t="s">
-        <v>112</v>
+        <v>29</v>
       </c>
       <c r="D1189" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E1189" s="2">
         <v>1</v>
@@ -39310,7 +41471,7 @@
         <v>29</v>
       </c>
       <c r="D1190" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1190" s="2">
         <v>1</v>
@@ -39337,10 +41498,10 @@
         <v>62</v>
       </c>
       <c r="C1191" t="s">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="D1191" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E1191" s="2">
         <v>1</v>
@@ -39370,7 +41531,7 @@
         <v>87</v>
       </c>
       <c r="D1192" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1192" s="2">
         <v>1</v>
@@ -39397,7 +41558,7 @@
         <v>62</v>
       </c>
       <c r="C1193" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D1193" t="s">
         <v>26</v>
@@ -39427,10 +41588,10 @@
         <v>62</v>
       </c>
       <c r="C1194" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="D1194" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E1194" s="2">
         <v>1</v>
@@ -39457,7 +41618,7 @@
         <v>62</v>
       </c>
       <c r="C1195" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D1195" t="s">
         <v>25</v>
@@ -39466,7 +41627,7 @@
         <v>1</v>
       </c>
       <c r="F1195" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G1195">
         <v>7.99</v>
@@ -39476,7 +41637,7 @@
       </c>
       <c r="I1195" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1195,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>CORLN.png</v>
+        <v>CORCEROLN.png</v>
       </c>
     </row>
     <row r="1196" spans="1:9" x14ac:dyDescent="0.25">
@@ -39490,7 +41651,7 @@
         <v>112</v>
       </c>
       <c r="D1196" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1196" s="2">
         <v>1</v>
@@ -39517,10 +41678,10 @@
         <v>62</v>
       </c>
       <c r="C1197" t="s">
-        <v>112</v>
+        <v>29</v>
       </c>
       <c r="D1197" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E1197" s="2">
         <v>1</v>
@@ -39550,7 +41711,7 @@
         <v>29</v>
       </c>
       <c r="D1198" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1198" s="2">
         <v>1</v>
@@ -39577,10 +41738,10 @@
         <v>62</v>
       </c>
       <c r="C1199" t="s">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="D1199" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E1199" s="2">
         <v>1</v>
@@ -39610,7 +41771,7 @@
         <v>87</v>
       </c>
       <c r="D1200" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1200" s="2">
         <v>1</v>
@@ -39637,7 +41798,7 @@
         <v>62</v>
       </c>
       <c r="C1201" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D1201" t="s">
         <v>26</v>
@@ -39667,10 +41828,10 @@
         <v>62</v>
       </c>
       <c r="C1202" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="D1202" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E1202" s="2">
         <v>1</v>
@@ -39697,26 +41858,26 @@
         <v>62</v>
       </c>
       <c r="C1203" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="D1203" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1203" s="2">
         <v>1</v>
       </c>
       <c r="F1203" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G1203">
-        <v>7.99</v>
+        <v>6.99</v>
       </c>
       <c r="H1203">
-        <v>6.99</v>
+        <v>6.19</v>
       </c>
       <c r="I1203" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1203,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>CORCEROLN.png</v>
+        <v>STELN.png</v>
       </c>
     </row>
     <row r="1204" spans="1:9" x14ac:dyDescent="0.25">
@@ -39727,7 +41888,7 @@
         <v>62</v>
       </c>
       <c r="C1204" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D1204" t="s">
         <v>26</v>
@@ -39736,17 +41897,17 @@
         <v>1</v>
       </c>
       <c r="F1204" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="G1204">
-        <v>6.99</v>
+        <v>3.09</v>
       </c>
       <c r="H1204">
-        <v>6.19</v>
+        <v>2.79</v>
       </c>
       <c r="I1204" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1204,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>STELN.png</v>
+        <v>BC269MP.png</v>
       </c>
     </row>
     <row r="1205" spans="1:9" x14ac:dyDescent="0.25">
@@ -39763,10 +41924,10 @@
         <v>26</v>
       </c>
       <c r="E1205" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1205" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="G1205">
         <v>3.09</v>
@@ -39776,7 +41937,7 @@
       </c>
       <c r="I1205" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1205,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>BC269MP.png</v>
+        <v>SK269MP.png</v>
       </c>
     </row>
     <row r="1206" spans="1:9" x14ac:dyDescent="0.25">
@@ -39793,20 +41954,20 @@
         <v>26</v>
       </c>
       <c r="E1206" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1206" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G1206">
-        <v>3.09</v>
+        <v>3.29</v>
       </c>
       <c r="H1206">
-        <v>2.79</v>
+        <v>2.89</v>
       </c>
       <c r="I1206" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1206,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>SK269MP.png</v>
+        <v>BUD269MP.png</v>
       </c>
     </row>
     <row r="1207" spans="1:9" x14ac:dyDescent="0.25">
@@ -39823,20 +41984,20 @@
         <v>26</v>
       </c>
       <c r="E1207" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1207" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G1207">
-        <v>3.29</v>
+        <v>3.69</v>
       </c>
       <c r="H1207">
-        <v>2.89</v>
+        <v>3.39</v>
       </c>
       <c r="I1207" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1207,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>BUD269MP.png</v>
+        <v>ORI269MP.png</v>
       </c>
     </row>
     <row r="1208" spans="1:9" x14ac:dyDescent="0.25">
@@ -39847,7 +42008,7 @@
         <v>62</v>
       </c>
       <c r="C1208" t="s">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="D1208" t="s">
         <v>26</v>
@@ -39856,17 +42017,17 @@
         <v>2</v>
       </c>
       <c r="F1208" t="s">
-        <v>118</v>
+        <v>65</v>
       </c>
       <c r="G1208">
-        <v>3.69</v>
+        <v>4.49</v>
       </c>
       <c r="H1208">
-        <v>3.39</v>
+        <v>4.49</v>
       </c>
       <c r="I1208" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1208,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>ORI269MP.png</v>
+        <v>STE350.png</v>
       </c>
     </row>
     <row r="1209" spans="1:9" x14ac:dyDescent="0.25">
@@ -39877,26 +42038,26 @@
         <v>62</v>
       </c>
       <c r="C1209" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="D1209" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E1209" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1209" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G1209">
-        <v>4.49</v>
+        <v>3.49</v>
       </c>
       <c r="H1209">
-        <v>4.49</v>
+        <v>3.09</v>
       </c>
       <c r="I1209" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1209,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>STE350.png</v>
+        <v>BUD269.png</v>
       </c>
     </row>
     <row r="1210" spans="1:9" x14ac:dyDescent="0.25">
@@ -39907,7 +42068,7 @@
         <v>62</v>
       </c>
       <c r="C1210" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D1210" t="s">
         <v>25</v>
@@ -39922,7 +42083,7 @@
         <v>3.49</v>
       </c>
       <c r="H1210">
-        <v>3.09</v>
+        <v>2.99</v>
       </c>
       <c r="I1210" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1210,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -39937,7 +42098,7 @@
         <v>62</v>
       </c>
       <c r="C1211" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D1211" t="s">
         <v>25</v>
@@ -39967,7 +42128,7 @@
         <v>62</v>
       </c>
       <c r="C1212" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D1212" t="s">
         <v>25</v>
@@ -40003,20 +42164,20 @@
         <v>25</v>
       </c>
       <c r="E1213" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1213" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="G1213">
+        <v>4.29</v>
+      </c>
+      <c r="H1213">
         <v>3.49</v>
-      </c>
-      <c r="H1213">
-        <v>2.99</v>
       </c>
       <c r="I1213" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1213,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>BUD269.png</v>
+        <v>STE269.png</v>
       </c>
     </row>
     <row r="1214" spans="1:9" x14ac:dyDescent="0.25">
@@ -40027,7 +42188,7 @@
         <v>62</v>
       </c>
       <c r="C1214" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D1214" t="s">
         <v>25</v>
@@ -40057,7 +42218,7 @@
         <v>62</v>
       </c>
       <c r="C1215" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D1215" t="s">
         <v>25</v>
@@ -40087,7 +42248,7 @@
         <v>62</v>
       </c>
       <c r="C1216" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D1216" t="s">
         <v>25</v>
@@ -40120,23 +42281,23 @@
         <v>89</v>
       </c>
       <c r="D1217" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1217" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1217" t="s">
-        <v>75</v>
+        <v>119</v>
       </c>
       <c r="G1217">
-        <v>4.29</v>
+        <v>2.99</v>
       </c>
       <c r="H1217">
-        <v>3.49</v>
+        <v>2.79</v>
       </c>
       <c r="I1217" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1217,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>STE269.png</v>
+        <v>BC269MP.png</v>
       </c>
     </row>
     <row r="1218" spans="1:9" x14ac:dyDescent="0.25">
@@ -40156,17 +42317,17 @@
         <v>1</v>
       </c>
       <c r="F1218" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G1218">
-        <v>2.99</v>
+        <v>3.29</v>
       </c>
       <c r="H1218">
-        <v>2.79</v>
+        <v>2.89</v>
       </c>
       <c r="I1218" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1218,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>BC269MP.png</v>
+        <v>BUD269MP.png</v>
       </c>
     </row>
     <row r="1219" spans="1:9" x14ac:dyDescent="0.25">
@@ -40183,20 +42344,20 @@
         <v>26</v>
       </c>
       <c r="E1219" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1219" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G1219">
-        <v>3.29</v>
+        <v>3.19</v>
       </c>
       <c r="H1219">
-        <v>2.89</v>
+        <v>2.99</v>
       </c>
       <c r="I1219" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1219,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>BUD269MP.png</v>
+        <v>SK269MP.png</v>
       </c>
     </row>
     <row r="1220" spans="1:9" x14ac:dyDescent="0.25">
@@ -40216,17 +42377,17 @@
         <v>2</v>
       </c>
       <c r="F1220" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G1220">
-        <v>3.19</v>
+        <v>3.69</v>
       </c>
       <c r="H1220">
-        <v>2.99</v>
+        <v>3.39</v>
       </c>
       <c r="I1220" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1220,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>SK269MP.png</v>
+        <v>ORI269MP.png</v>
       </c>
     </row>
     <row r="1221" spans="1:9" x14ac:dyDescent="0.25">
@@ -40237,26 +42398,26 @@
         <v>62</v>
       </c>
       <c r="C1221" t="s">
-        <v>89</v>
+        <v>123</v>
       </c>
       <c r="D1221" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E1221" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1221" t="s">
-        <v>118</v>
+        <v>67</v>
       </c>
       <c r="G1221">
-        <v>3.69</v>
+        <v>3.29</v>
       </c>
       <c r="H1221">
-        <v>3.39</v>
+        <v>2.99</v>
       </c>
       <c r="I1221" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1221,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>ORI269MP.png</v>
+        <v>AP269.png</v>
       </c>
     </row>
     <row r="1222" spans="1:9" x14ac:dyDescent="0.25">
@@ -40267,25 +42428,26 @@
         <v>62</v>
       </c>
       <c r="C1222" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="D1222" t="s">
         <v>25</v>
       </c>
       <c r="E1222" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1222" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="G1222">
-        <v>3.29</v>
+        <v>3.19</v>
       </c>
       <c r="H1222">
         <v>2.99</v>
       </c>
-      <c r="I1222" s="2" t="s">
-        <v>123</v>
+      <c r="I1222" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1222,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>SKZERO269.png</v>
       </c>
     </row>
     <row r="1223" spans="1:9" x14ac:dyDescent="0.25">
@@ -40296,7 +42458,7 @@
         <v>62</v>
       </c>
       <c r="C1223" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="D1223" t="s">
         <v>25</v>
@@ -40305,16 +42467,17 @@
         <v>2</v>
       </c>
       <c r="F1223" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G1223">
-        <v>3.19</v>
+        <v>3.29</v>
       </c>
       <c r="H1223">
         <v>2.99</v>
       </c>
-      <c r="I1223" s="2" t="s">
-        <v>124</v>
+      <c r="I1223" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1223,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>SK269.png</v>
       </c>
     </row>
     <row r="1224" spans="1:9" x14ac:dyDescent="0.25">
@@ -40325,16 +42488,16 @@
         <v>62</v>
       </c>
       <c r="C1224" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="D1224" t="s">
         <v>25</v>
       </c>
       <c r="E1224" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1224" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G1224">
         <v>3.29</v>
@@ -40342,8 +42505,9 @@
       <c r="H1224">
         <v>2.99</v>
       </c>
-      <c r="I1224" s="2" t="s">
-        <v>125</v>
+      <c r="I1224" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1224,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BC269.png</v>
       </c>
     </row>
     <row r="1225" spans="1:9" x14ac:dyDescent="0.25">
@@ -40354,7 +42518,7 @@
         <v>62</v>
       </c>
       <c r="C1225" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="D1225" t="s">
         <v>25</v>
@@ -40363,16 +42527,17 @@
         <v>1</v>
       </c>
       <c r="F1225" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G1225">
-        <v>3.29</v>
+        <v>3.69</v>
       </c>
       <c r="H1225">
-        <v>2.99</v>
-      </c>
-      <c r="I1225" s="2" t="s">
-        <v>126</v>
+        <v>3.19</v>
+      </c>
+      <c r="I1225" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1225,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BC0350.png</v>
       </c>
     </row>
     <row r="1226" spans="1:9" x14ac:dyDescent="0.25">
@@ -40383,13 +42548,13 @@
         <v>62</v>
       </c>
       <c r="C1226" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="D1226" t="s">
         <v>25</v>
       </c>
       <c r="E1226" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1226" t="s">
         <v>70</v>
@@ -40400,8 +42565,9 @@
       <c r="H1226">
         <v>3.19</v>
       </c>
-      <c r="I1226" s="2" t="s">
-        <v>128</v>
+      <c r="I1226" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1226,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BC0350.png</v>
       </c>
     </row>
     <row r="1227" spans="1:9" x14ac:dyDescent="0.25">
@@ -40412,7 +42578,7 @@
         <v>62</v>
       </c>
       <c r="C1227" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="D1227" t="s">
         <v>25</v>
@@ -40421,16 +42587,17 @@
         <v>2</v>
       </c>
       <c r="F1227" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="G1227">
+        <v>3.89</v>
+      </c>
+      <c r="H1227">
         <v>3.69</v>
       </c>
-      <c r="H1227">
-        <v>3.19</v>
-      </c>
-      <c r="I1227" s="2" t="s">
-        <v>128</v>
+      <c r="I1227" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1227,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>SKZERO350.png</v>
       </c>
     </row>
     <row r="1228" spans="1:9" x14ac:dyDescent="0.25">
@@ -40441,7 +42608,7 @@
         <v>62</v>
       </c>
       <c r="C1228" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="D1228" t="s">
         <v>25</v>
@@ -40450,16 +42617,17 @@
         <v>2</v>
       </c>
       <c r="F1228" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="G1228">
         <v>3.89</v>
       </c>
       <c r="H1228">
-        <v>3.69</v>
-      </c>
-      <c r="I1228" s="2" t="s">
-        <v>129</v>
+        <v>3.59</v>
+      </c>
+      <c r="I1228" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1228,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>ORI269.png</v>
       </c>
     </row>
     <row r="1229" spans="1:9" x14ac:dyDescent="0.25">
@@ -40470,25 +42638,26 @@
         <v>62</v>
       </c>
       <c r="C1229" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="D1229" t="s">
         <v>25</v>
       </c>
       <c r="E1229" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1229" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G1229">
-        <v>3.89</v>
+        <v>4.49</v>
       </c>
       <c r="H1229">
-        <v>3.59</v>
-      </c>
-      <c r="I1229" s="2" t="s">
-        <v>130</v>
+        <v>3.49</v>
+      </c>
+      <c r="I1229" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1229,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BUDZERO350.png</v>
       </c>
     </row>
     <row r="1230" spans="1:9" x14ac:dyDescent="0.25">
@@ -40499,7 +42668,7 @@
         <v>62</v>
       </c>
       <c r="C1230" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="D1230" t="s">
         <v>25</v>
@@ -40508,16 +42677,17 @@
         <v>1</v>
       </c>
       <c r="F1230" t="s">
-        <v>74</v>
+        <v>125</v>
       </c>
       <c r="G1230">
-        <v>4.49</v>
+        <v>4.6900000000000004</v>
       </c>
       <c r="H1230">
-        <v>3.49</v>
-      </c>
-      <c r="I1230" s="2" t="s">
-        <v>132</v>
+        <v>4.3899999999999997</v>
+      </c>
+      <c r="I1230" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1230,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>STEPG269.png</v>
       </c>
     </row>
     <row r="1231" spans="1:9" x14ac:dyDescent="0.25">
@@ -40528,7 +42698,7 @@
         <v>62</v>
       </c>
       <c r="C1231" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="D1231" t="s">
         <v>25</v>
@@ -40537,16 +42707,17 @@
         <v>1</v>
       </c>
       <c r="F1231" t="s">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="G1231">
-        <v>4.6900000000000004</v>
+        <v>5.49</v>
       </c>
       <c r="H1231">
-        <v>4.3899999999999997</v>
-      </c>
-      <c r="I1231" t="s">
-        <v>144</v>
+        <v>4.99</v>
+      </c>
+      <c r="I1231" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1231,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>MIC350.png</v>
       </c>
     </row>
     <row r="1232" spans="1:9" x14ac:dyDescent="0.25">
@@ -40557,25 +42728,26 @@
         <v>62</v>
       </c>
       <c r="C1232" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="D1232" t="s">
         <v>25</v>
       </c>
       <c r="E1232" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1232" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G1232">
+        <v>6.29</v>
+      </c>
+      <c r="H1232">
         <v>5.49</v>
       </c>
-      <c r="H1232">
-        <v>4.99</v>
-      </c>
-      <c r="I1232" t="s">
-        <v>145</v>
+      <c r="I1232" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1232,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>CORCERO350.png</v>
       </c>
     </row>
     <row r="1233" spans="1:9" x14ac:dyDescent="0.25">
@@ -40586,7 +42758,7 @@
         <v>62</v>
       </c>
       <c r="C1233" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="D1233" t="s">
         <v>25</v>
@@ -40595,16 +42767,17 @@
         <v>2</v>
       </c>
       <c r="F1233" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G1233">
-        <v>6.29</v>
+        <v>6.69</v>
       </c>
       <c r="H1233">
-        <v>5.49</v>
-      </c>
-      <c r="I1233" s="2" t="s">
-        <v>133</v>
+        <v>5.99</v>
+      </c>
+      <c r="I1233" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1233,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>MICLN.png</v>
       </c>
     </row>
     <row r="1234" spans="1:9" x14ac:dyDescent="0.25">
@@ -40615,25 +42788,26 @@
         <v>62</v>
       </c>
       <c r="C1234" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="D1234" t="s">
         <v>25</v>
       </c>
       <c r="E1234" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1234" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G1234">
-        <v>6.69</v>
+        <v>6.99</v>
       </c>
       <c r="H1234">
-        <v>5.99</v>
-      </c>
-      <c r="I1234" s="2" t="s">
-        <v>134</v>
+        <v>6.19</v>
+      </c>
+      <c r="I1234" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1234,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>STELN.png</v>
       </c>
     </row>
     <row r="1235" spans="1:9" x14ac:dyDescent="0.25">
@@ -40644,7 +42818,7 @@
         <v>62</v>
       </c>
       <c r="C1235" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="D1235" t="s">
         <v>25</v>
@@ -40653,16 +42827,17 @@
         <v>1</v>
       </c>
       <c r="F1235" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G1235">
+        <v>7.99</v>
+      </c>
+      <c r="H1235">
         <v>6.99</v>
       </c>
-      <c r="H1235">
-        <v>6.19</v>
-      </c>
-      <c r="I1235" s="2" t="s">
-        <v>135</v>
+      <c r="I1235" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1235,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>CORLN.png</v>
       </c>
     </row>
     <row r="1236" spans="1:9" x14ac:dyDescent="0.25">
@@ -40673,7 +42848,7 @@
         <v>62</v>
       </c>
       <c r="C1236" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="D1236" t="s">
         <v>25</v>
@@ -40682,7 +42857,7 @@
         <v>1</v>
       </c>
       <c r="F1236" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G1236">
         <v>7.99</v>
@@ -40690,8 +42865,9 @@
       <c r="H1236">
         <v>6.99</v>
       </c>
-      <c r="I1236" s="2" t="s">
-        <v>136</v>
+      <c r="I1236" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1236,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>CORCEROLN.png</v>
       </c>
     </row>
     <row r="1237" spans="1:9" x14ac:dyDescent="0.25">
@@ -40702,7 +42878,7 @@
         <v>62</v>
       </c>
       <c r="C1237" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="D1237" t="s">
         <v>25</v>
@@ -40711,16 +42887,17 @@
         <v>1</v>
       </c>
       <c r="F1237" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="G1237">
-        <v>7.99</v>
+        <v>3.49</v>
       </c>
       <c r="H1237">
-        <v>6.99</v>
-      </c>
-      <c r="I1237" s="2" t="s">
-        <v>137</v>
+        <v>2.99</v>
+      </c>
+      <c r="I1237" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1237,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BUD269.png</v>
       </c>
     </row>
     <row r="1238" spans="1:9" x14ac:dyDescent="0.25">
@@ -40731,25 +42908,26 @@
         <v>62</v>
       </c>
       <c r="C1238" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="D1238" t="s">
         <v>25</v>
       </c>
       <c r="E1238" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1238" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="G1238">
+        <v>4.29</v>
+      </c>
+      <c r="H1238">
         <v>3.49</v>
       </c>
-      <c r="H1238">
-        <v>2.99</v>
-      </c>
-      <c r="I1238" s="2" t="s">
-        <v>127</v>
+      <c r="I1238" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1238,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>STE269.png</v>
       </c>
     </row>
     <row r="1239" spans="1:9" x14ac:dyDescent="0.25">
@@ -40760,7 +42938,7 @@
         <v>62</v>
       </c>
       <c r="C1239" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="D1239" t="s">
         <v>25</v>
@@ -40769,16 +42947,17 @@
         <v>2</v>
       </c>
       <c r="F1239" t="s">
-        <v>75</v>
+        <v>126</v>
       </c>
       <c r="G1239">
-        <v>4.29</v>
+        <v>5.99</v>
       </c>
       <c r="H1239">
-        <v>3.49</v>
-      </c>
-      <c r="I1239" s="2" t="s">
-        <v>131</v>
+        <v>5.49</v>
+      </c>
+      <c r="I1239" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1239,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>STEPG350.png</v>
       </c>
     </row>
     <row r="1240" spans="1:9" x14ac:dyDescent="0.25">
@@ -40786,31 +42965,63 @@
         <v>98</v>
       </c>
       <c r="B1240" s="2" t="s">
-        <v>62</v>
+        <v>128</v>
       </c>
       <c r="C1240" t="s">
-        <v>138</v>
+        <v>105</v>
       </c>
       <c r="D1240" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1240" s="2">
-        <v>2</v>
-      </c>
-      <c r="F1240" t="s">
-        <v>141</v>
-      </c>
-      <c r="G1240">
-        <v>5.99</v>
-      </c>
-      <c r="H1240">
-        <v>5.49</v>
-      </c>
-      <c r="I1240" t="s">
-        <v>143</v>
+        <v>129</v>
+      </c>
+      <c r="E1240" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F1240" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G1240" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H1240" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="I1240" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1240,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>Merca/MercaCO.png</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1241" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1241" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C1241" t="s">
+        <v>130</v>
+      </c>
+      <c r="D1241" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1241" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F1241" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G1241" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H1241" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="I1241" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1241,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>Merca/MercaFORT.png</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I1239" xr:uid="{34B2C8DF-4561-40B2-8E7C-6CD69559B9AE}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>

--- a/data/calendario_promocional.xlsx
+++ b/data/calendario_promocional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anheuserbuschinbev-my.sharepoint.com/personal/99823517_ab-inbev_com/Documents/001. Projetos/Streamlit Calendario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="116" documentId="13_ncr:1_{B92F5DA4-8825-4FA1-97C6-23568D76854D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{967A3C46-9776-4F76-8A93-3233D30BA0AB}"/>
+  <xr:revisionPtr revIDLastSave="164" documentId="13_ncr:1_{B92F5DA4-8825-4FA1-97C6-23568D76854D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA481E14-D7EB-431D-8ADD-442D5928C475}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DeparaIMG" sheetId="5" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="CONFIG" sheetId="4" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">CALENDARIO!$A$1:$C$289</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">CALENDARIO!$A$1:$C$414</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DeparaIMG!$A$1:$D$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">MECANICA!$A$1:$D$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">PRODUTOS!$A$1:$I$1239</definedName>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7115" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7425" uniqueCount="133">
   <si>
     <t>Data</t>
   </si>
@@ -435,15 +435,6 @@
     <t>MERCAPROMO</t>
   </si>
   <si>
-    <t>VAR/ATAC</t>
-  </si>
-  <si>
-    <t>FORT</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>MercaCO</t>
   </si>
   <si>
@@ -1610,10 +1601,10 @@
         <v>128</v>
       </c>
       <c r="B52" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C52" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D52" t="str">
         <f>C52&amp;".png"</f>
@@ -1625,10 +1616,10 @@
         <v>128</v>
       </c>
       <c r="B53" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C53" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D53" t="str">
         <f t="shared" si="3"/>
@@ -1646,7 +1637,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C289"/>
+  <dimension ref="A1:C497"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -1669,9 +1660,9 @@
         <v>61</v>
       </c>
       <c r="B2" s="3">
-        <v>46266</v>
-      </c>
-      <c r="C2" s="2" t="s">
+        <v>46174</v>
+      </c>
+      <c r="C2" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1679,11 +1670,10 @@
       <c r="A3" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="3">
-        <f>B2+1</f>
-        <v>46267</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="B3" s="5">
+        <v>46175</v>
+      </c>
+      <c r="C3" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1691,11 +1681,10 @@
       <c r="A4" t="s">
         <v>61</v>
       </c>
-      <c r="B4" s="3">
-        <f t="shared" ref="B4:B53" si="0">B3+1</f>
-        <v>46268</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="B4" s="5">
+        <v>46176</v>
+      </c>
+      <c r="C4" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1703,11 +1692,10 @@
       <c r="A5" t="s">
         <v>61</v>
       </c>
-      <c r="B5" s="3">
-        <f t="shared" si="0"/>
-        <v>46269</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="B5" s="5">
+        <v>46177</v>
+      </c>
+      <c r="C5" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1715,11 +1703,10 @@
       <c r="A6" t="s">
         <v>61</v>
       </c>
-      <c r="B6" s="3">
-        <f t="shared" si="0"/>
-        <v>46270</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="B6" s="5">
+        <v>46178</v>
+      </c>
+      <c r="C6" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1727,11 +1714,10 @@
       <c r="A7" t="s">
         <v>61</v>
       </c>
-      <c r="B7" s="3">
-        <f t="shared" si="0"/>
-        <v>46271</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="B7" s="5">
+        <v>46179</v>
+      </c>
+      <c r="C7" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1739,11 +1725,10 @@
       <c r="A8" t="s">
         <v>61</v>
       </c>
-      <c r="B8" s="3">
-        <f t="shared" si="0"/>
-        <v>46272</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="B8" s="5">
+        <v>46180</v>
+      </c>
+      <c r="C8" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1751,11 +1736,10 @@
       <c r="A9" t="s">
         <v>61</v>
       </c>
-      <c r="B9" s="3">
-        <f t="shared" si="0"/>
-        <v>46273</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="B9" s="5">
+        <v>46181</v>
+      </c>
+      <c r="C9" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1763,11 +1747,10 @@
       <c r="A10" t="s">
         <v>61</v>
       </c>
-      <c r="B10" s="3">
-        <f t="shared" si="0"/>
-        <v>46274</v>
-      </c>
-      <c r="C10" s="2" t="s">
+      <c r="B10" s="5">
+        <v>46182</v>
+      </c>
+      <c r="C10" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1775,11 +1758,10 @@
       <c r="A11" t="s">
         <v>61</v>
       </c>
-      <c r="B11" s="3">
-        <f t="shared" si="0"/>
-        <v>46275</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="B11" s="5">
+        <v>46183</v>
+      </c>
+      <c r="C11" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1787,11 +1769,10 @@
       <c r="A12" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="3">
-        <f t="shared" si="0"/>
-        <v>46276</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="B12" s="5">
+        <v>46184</v>
+      </c>
+      <c r="C12" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1799,11 +1780,10 @@
       <c r="A13" t="s">
         <v>61</v>
       </c>
-      <c r="B13" s="3">
-        <f t="shared" si="0"/>
-        <v>46277</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="B13" s="5">
+        <v>46185</v>
+      </c>
+      <c r="C13" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1811,11 +1791,10 @@
       <c r="A14" t="s">
         <v>61</v>
       </c>
-      <c r="B14" s="3">
-        <f t="shared" si="0"/>
-        <v>46278</v>
-      </c>
-      <c r="C14" s="2" t="s">
+      <c r="B14" s="5">
+        <v>46186</v>
+      </c>
+      <c r="C14" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1823,23 +1802,21 @@
       <c r="A15" t="s">
         <v>61</v>
       </c>
-      <c r="B15" s="3">
-        <f t="shared" si="0"/>
-        <v>46279</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>21</v>
+      <c r="B15" s="5">
+        <v>46187</v>
+      </c>
+      <c r="C15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>61</v>
       </c>
-      <c r="B16" s="3">
-        <f t="shared" si="0"/>
-        <v>46280</v>
-      </c>
-      <c r="C16" s="2" t="s">
+      <c r="B16" s="5">
+        <v>46188</v>
+      </c>
+      <c r="C16" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1847,11 +1824,10 @@
       <c r="A17" t="s">
         <v>61</v>
       </c>
-      <c r="B17" s="3">
-        <f t="shared" si="0"/>
-        <v>46281</v>
-      </c>
-      <c r="C17" s="2" t="s">
+      <c r="B17" s="5">
+        <v>46189</v>
+      </c>
+      <c r="C17" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1859,11 +1835,10 @@
       <c r="A18" t="s">
         <v>61</v>
       </c>
-      <c r="B18" s="3">
-        <f t="shared" si="0"/>
-        <v>46282</v>
-      </c>
-      <c r="C18" s="2" t="s">
+      <c r="B18" s="5">
+        <v>46190</v>
+      </c>
+      <c r="C18" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1871,11 +1846,10 @@
       <c r="A19" t="s">
         <v>61</v>
       </c>
-      <c r="B19" s="3">
-        <f t="shared" si="0"/>
-        <v>46283</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="B19" s="5">
+        <v>46191</v>
+      </c>
+      <c r="C19" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1883,11 +1857,10 @@
       <c r="A20" t="s">
         <v>61</v>
       </c>
-      <c r="B20" s="3">
-        <f t="shared" si="0"/>
-        <v>46284</v>
-      </c>
-      <c r="C20" s="2" t="s">
+      <c r="B20" s="5">
+        <v>46192</v>
+      </c>
+      <c r="C20" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1895,11 +1868,10 @@
       <c r="A21" t="s">
         <v>61</v>
       </c>
-      <c r="B21" s="3">
-        <f t="shared" si="0"/>
-        <v>46285</v>
-      </c>
-      <c r="C21" s="2" t="s">
+      <c r="B21" s="5">
+        <v>46193</v>
+      </c>
+      <c r="C21" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1907,11 +1879,10 @@
       <c r="A22" t="s">
         <v>61</v>
       </c>
-      <c r="B22" s="3">
-        <f t="shared" si="0"/>
-        <v>46286</v>
-      </c>
-      <c r="C22" s="2" t="s">
+      <c r="B22" s="5">
+        <v>46194</v>
+      </c>
+      <c r="C22" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1919,11 +1890,10 @@
       <c r="A23" t="s">
         <v>61</v>
       </c>
-      <c r="B23" s="3">
-        <f t="shared" si="0"/>
-        <v>46287</v>
-      </c>
-      <c r="C23" s="2" t="s">
+      <c r="B23" s="5">
+        <v>46195</v>
+      </c>
+      <c r="C23" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1931,11 +1901,10 @@
       <c r="A24" t="s">
         <v>61</v>
       </c>
-      <c r="B24" s="3">
-        <f t="shared" si="0"/>
-        <v>46288</v>
-      </c>
-      <c r="C24" s="2" t="s">
+      <c r="B24" s="5">
+        <v>46196</v>
+      </c>
+      <c r="C24" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1943,11 +1912,10 @@
       <c r="A25" t="s">
         <v>61</v>
       </c>
-      <c r="B25" s="3">
-        <f t="shared" si="0"/>
-        <v>46289</v>
-      </c>
-      <c r="C25" s="2" t="s">
+      <c r="B25" s="5">
+        <v>46197</v>
+      </c>
+      <c r="C25" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1955,11 +1923,10 @@
       <c r="A26" t="s">
         <v>61</v>
       </c>
-      <c r="B26" s="3">
-        <f t="shared" si="0"/>
-        <v>46290</v>
-      </c>
-      <c r="C26" s="2" t="s">
+      <c r="B26" s="5">
+        <v>46198</v>
+      </c>
+      <c r="C26" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1967,11 +1934,10 @@
       <c r="A27" t="s">
         <v>61</v>
       </c>
-      <c r="B27" s="3">
-        <f t="shared" si="0"/>
-        <v>46291</v>
-      </c>
-      <c r="C27" s="2" t="s">
+      <c r="B27" s="5">
+        <v>46199</v>
+      </c>
+      <c r="C27" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1979,11 +1945,10 @@
       <c r="A28" t="s">
         <v>61</v>
       </c>
-      <c r="B28" s="3">
-        <f t="shared" si="0"/>
-        <v>46292</v>
-      </c>
-      <c r="C28" s="2" t="s">
+      <c r="B28" s="5">
+        <v>46200</v>
+      </c>
+      <c r="C28" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1991,50 +1956,54 @@
       <c r="A29" t="s">
         <v>61</v>
       </c>
-      <c r="B29" s="3">
-        <v>46296</v>
-      </c>
-      <c r="C29" s="2"/>
+      <c r="B29" s="5">
+        <v>46201</v>
+      </c>
+      <c r="C29" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>61</v>
       </c>
-      <c r="B30" s="3">
-        <f t="shared" si="0"/>
-        <v>46297</v>
-      </c>
-      <c r="C30" s="2"/>
+      <c r="B30" s="5">
+        <v>46205</v>
+      </c>
+      <c r="C30" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>61</v>
       </c>
-      <c r="B31" s="3">
-        <f t="shared" si="0"/>
-        <v>46298</v>
-      </c>
-      <c r="C31" s="2"/>
+      <c r="B31" s="5">
+        <v>46206</v>
+      </c>
+      <c r="C31" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>61</v>
       </c>
-      <c r="B32" s="3">
-        <f t="shared" si="0"/>
-        <v>46299</v>
-      </c>
-      <c r="C32" s="2"/>
+      <c r="B32" s="5">
+        <v>46207</v>
+      </c>
+      <c r="C32" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>61</v>
       </c>
-      <c r="B33" s="3">
-        <f t="shared" si="0"/>
-        <v>46300</v>
-      </c>
-      <c r="C33" s="2" t="s">
+      <c r="B33" s="5">
+        <v>46208</v>
+      </c>
+      <c r="C33" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2042,11 +2011,10 @@
       <c r="A34" t="s">
         <v>61</v>
       </c>
-      <c r="B34" s="3">
-        <f t="shared" si="0"/>
-        <v>46301</v>
-      </c>
-      <c r="C34" s="2" t="s">
+      <c r="B34" s="5">
+        <v>46209</v>
+      </c>
+      <c r="C34" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2054,11 +2022,10 @@
       <c r="A35" t="s">
         <v>61</v>
       </c>
-      <c r="B35" s="3">
-        <f t="shared" si="0"/>
-        <v>46302</v>
-      </c>
-      <c r="C35" s="2" t="s">
+      <c r="B35" s="5">
+        <v>46210</v>
+      </c>
+      <c r="C35" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2066,11 +2033,10 @@
       <c r="A36" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="3">
-        <f t="shared" si="0"/>
-        <v>46303</v>
-      </c>
-      <c r="C36" s="2" t="s">
+      <c r="B36" s="5">
+        <v>46211</v>
+      </c>
+      <c r="C36" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2078,11 +2044,10 @@
       <c r="A37" t="s">
         <v>61</v>
       </c>
-      <c r="B37" s="3">
-        <f t="shared" si="0"/>
-        <v>46304</v>
-      </c>
-      <c r="C37" s="2" t="s">
+      <c r="B37" s="5">
+        <v>46212</v>
+      </c>
+      <c r="C37" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2090,11 +2055,10 @@
       <c r="A38" t="s">
         <v>61</v>
       </c>
-      <c r="B38" s="3">
-        <f t="shared" si="0"/>
-        <v>46305</v>
-      </c>
-      <c r="C38" s="2" t="s">
+      <c r="B38" s="5">
+        <v>46213</v>
+      </c>
+      <c r="C38" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2102,11 +2066,10 @@
       <c r="A39" t="s">
         <v>61</v>
       </c>
-      <c r="B39" s="3">
-        <f t="shared" si="0"/>
-        <v>46306</v>
-      </c>
-      <c r="C39" s="2" t="s">
+      <c r="B39" s="5">
+        <v>46214</v>
+      </c>
+      <c r="C39" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2114,11 +2077,10 @@
       <c r="A40" t="s">
         <v>61</v>
       </c>
-      <c r="B40" s="3">
-        <f t="shared" si="0"/>
-        <v>46307</v>
-      </c>
-      <c r="C40" s="2" t="s">
+      <c r="B40" s="5">
+        <v>46215</v>
+      </c>
+      <c r="C40" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2126,11 +2088,10 @@
       <c r="A41" t="s">
         <v>61</v>
       </c>
-      <c r="B41" s="3">
-        <f t="shared" si="0"/>
-        <v>46308</v>
-      </c>
-      <c r="C41" s="2" t="s">
+      <c r="B41" s="5">
+        <v>46216</v>
+      </c>
+      <c r="C41" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2138,11 +2099,10 @@
       <c r="A42" t="s">
         <v>61</v>
       </c>
-      <c r="B42" s="3">
-        <f t="shared" si="0"/>
-        <v>46309</v>
-      </c>
-      <c r="C42" s="2" t="s">
+      <c r="B42" s="5">
+        <v>46217</v>
+      </c>
+      <c r="C42" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2150,11 +2110,10 @@
       <c r="A43" t="s">
         <v>61</v>
       </c>
-      <c r="B43" s="3">
-        <f t="shared" si="0"/>
-        <v>46310</v>
-      </c>
-      <c r="C43" s="2" t="s">
+      <c r="B43" s="5">
+        <v>46218</v>
+      </c>
+      <c r="C43" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2162,11 +2121,10 @@
       <c r="A44" t="s">
         <v>61</v>
       </c>
-      <c r="B44" s="3">
-        <f t="shared" si="0"/>
-        <v>46311</v>
-      </c>
-      <c r="C44" s="2" t="s">
+      <c r="B44" s="5">
+        <v>46219</v>
+      </c>
+      <c r="C44" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2174,11 +2132,10 @@
       <c r="A45" t="s">
         <v>61</v>
       </c>
-      <c r="B45" s="3">
-        <f t="shared" si="0"/>
-        <v>46312</v>
-      </c>
-      <c r="C45" s="2" t="s">
+      <c r="B45" s="5">
+        <v>46220</v>
+      </c>
+      <c r="C45" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2186,11 +2143,10 @@
       <c r="A46" t="s">
         <v>61</v>
       </c>
-      <c r="B46" s="3">
-        <f t="shared" si="0"/>
-        <v>46313</v>
-      </c>
-      <c r="C46" s="2" t="s">
+      <c r="B46" s="5">
+        <v>46221</v>
+      </c>
+      <c r="C46" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2198,11 +2154,10 @@
       <c r="A47" t="s">
         <v>61</v>
       </c>
-      <c r="B47" s="3">
-        <f t="shared" si="0"/>
-        <v>46314</v>
-      </c>
-      <c r="C47" s="2" t="s">
+      <c r="B47" s="5">
+        <v>46222</v>
+      </c>
+      <c r="C47" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2210,11 +2165,10 @@
       <c r="A48" t="s">
         <v>61</v>
       </c>
-      <c r="B48" s="3">
-        <f t="shared" si="0"/>
-        <v>46315</v>
-      </c>
-      <c r="C48" s="2" t="s">
+      <c r="B48" s="5">
+        <v>46223</v>
+      </c>
+      <c r="C48" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2222,11 +2176,10 @@
       <c r="A49" t="s">
         <v>61</v>
       </c>
-      <c r="B49" s="3">
-        <f t="shared" si="0"/>
-        <v>46316</v>
-      </c>
-      <c r="C49" s="2" t="s">
+      <c r="B49" s="5">
+        <v>46224</v>
+      </c>
+      <c r="C49" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2234,11 +2187,10 @@
       <c r="A50" t="s">
         <v>61</v>
       </c>
-      <c r="B50" s="3">
-        <f t="shared" si="0"/>
-        <v>46317</v>
-      </c>
-      <c r="C50" s="2" t="s">
+      <c r="B50" s="5">
+        <v>46225</v>
+      </c>
+      <c r="C50" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2246,11 +2198,10 @@
       <c r="A51" t="s">
         <v>61</v>
       </c>
-      <c r="B51" s="3">
-        <f t="shared" si="0"/>
-        <v>46318</v>
-      </c>
-      <c r="C51" s="2" t="s">
+      <c r="B51" s="5">
+        <v>46226</v>
+      </c>
+      <c r="C51" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2258,11 +2209,10 @@
       <c r="A52" t="s">
         <v>61</v>
       </c>
-      <c r="B52" s="3">
-        <f t="shared" si="0"/>
-        <v>46319</v>
-      </c>
-      <c r="C52" s="2" t="s">
+      <c r="B52" s="5">
+        <v>46227</v>
+      </c>
+      <c r="C52" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2270,11 +2220,10 @@
       <c r="A53" t="s">
         <v>61</v>
       </c>
-      <c r="B53" s="3">
-        <f t="shared" si="0"/>
-        <v>46320</v>
-      </c>
-      <c r="C53" s="2" t="s">
+      <c r="B53" s="5">
+        <v>46228</v>
+      </c>
+      <c r="C53" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2282,11 +2231,11 @@
       <c r="A54" t="s">
         <v>61</v>
       </c>
-      <c r="B54" s="3">
-        <v>46174</v>
+      <c r="B54" s="5">
+        <v>46229</v>
       </c>
       <c r="C54" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -2294,11 +2243,10 @@
         <v>61</v>
       </c>
       <c r="B55" s="5">
-        <f>B54+1</f>
-        <v>46175</v>
+        <v>46230</v>
       </c>
       <c r="C55" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -2306,11 +2254,10 @@
         <v>61</v>
       </c>
       <c r="B56" s="5">
-        <f t="shared" ref="B56:B119" si="1">B55+1</f>
-        <v>46176</v>
+        <v>46231</v>
       </c>
       <c r="C56" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -2318,11 +2265,10 @@
         <v>61</v>
       </c>
       <c r="B57" s="5">
-        <f t="shared" si="1"/>
-        <v>46177</v>
+        <v>46232</v>
       </c>
       <c r="C57" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -2330,11 +2276,10 @@
         <v>61</v>
       </c>
       <c r="B58" s="5">
-        <f t="shared" si="1"/>
-        <v>46178</v>
+        <v>46233</v>
       </c>
       <c r="C58" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -2342,11 +2287,10 @@
         <v>61</v>
       </c>
       <c r="B59" s="5">
-        <f t="shared" si="1"/>
-        <v>46179</v>
+        <v>46234</v>
       </c>
       <c r="C59" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -2354,8 +2298,7 @@
         <v>61</v>
       </c>
       <c r="B60" s="5">
-        <f t="shared" si="1"/>
-        <v>46180</v>
+        <v>46237</v>
       </c>
       <c r="C60" t="s">
         <v>20</v>
@@ -2366,8 +2309,7 @@
         <v>61</v>
       </c>
       <c r="B61" s="5">
-        <f t="shared" si="1"/>
-        <v>46181</v>
+        <v>46238</v>
       </c>
       <c r="C61" t="s">
         <v>20</v>
@@ -2378,8 +2320,7 @@
         <v>61</v>
       </c>
       <c r="B62" s="5">
-        <f t="shared" si="1"/>
-        <v>46182</v>
+        <v>46239</v>
       </c>
       <c r="C62" t="s">
         <v>20</v>
@@ -2390,8 +2331,7 @@
         <v>61</v>
       </c>
       <c r="B63" s="5">
-        <f t="shared" si="1"/>
-        <v>46183</v>
+        <v>46240</v>
       </c>
       <c r="C63" t="s">
         <v>20</v>
@@ -2402,8 +2342,7 @@
         <v>61</v>
       </c>
       <c r="B64" s="5">
-        <f t="shared" si="1"/>
-        <v>46184</v>
+        <v>46241</v>
       </c>
       <c r="C64" t="s">
         <v>20</v>
@@ -2414,8 +2353,7 @@
         <v>61</v>
       </c>
       <c r="B65" s="5">
-        <f t="shared" si="1"/>
-        <v>46185</v>
+        <v>46242</v>
       </c>
       <c r="C65" t="s">
         <v>20</v>
@@ -2426,8 +2364,7 @@
         <v>61</v>
       </c>
       <c r="B66" s="5">
-        <f t="shared" si="1"/>
-        <v>46186</v>
+        <v>46243</v>
       </c>
       <c r="C66" t="s">
         <v>20</v>
@@ -2438,8 +2375,7 @@
         <v>61</v>
       </c>
       <c r="B67" s="5">
-        <f t="shared" si="1"/>
-        <v>46187</v>
+        <v>46244</v>
       </c>
       <c r="C67" t="s">
         <v>20</v>
@@ -2450,11 +2386,10 @@
         <v>61</v>
       </c>
       <c r="B68" s="5">
-        <f t="shared" si="1"/>
-        <v>46188</v>
+        <v>46245</v>
       </c>
       <c r="C68" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -2462,11 +2397,10 @@
         <v>61</v>
       </c>
       <c r="B69" s="5">
-        <f t="shared" si="1"/>
-        <v>46189</v>
+        <v>46246</v>
       </c>
       <c r="C69" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -2474,11 +2408,10 @@
         <v>61</v>
       </c>
       <c r="B70" s="5">
-        <f t="shared" si="1"/>
-        <v>46190</v>
+        <v>46247</v>
       </c>
       <c r="C70" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -2486,11 +2419,10 @@
         <v>61</v>
       </c>
       <c r="B71" s="5">
-        <f t="shared" si="1"/>
-        <v>46191</v>
+        <v>46248</v>
       </c>
       <c r="C71" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -2498,11 +2430,10 @@
         <v>61</v>
       </c>
       <c r="B72" s="5">
-        <f t="shared" si="1"/>
-        <v>46192</v>
+        <v>46249</v>
       </c>
       <c r="C72" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
@@ -2510,11 +2441,10 @@
         <v>61</v>
       </c>
       <c r="B73" s="5">
-        <f t="shared" si="1"/>
-        <v>46193</v>
+        <v>46250</v>
       </c>
       <c r="C73" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
@@ -2522,8 +2452,7 @@
         <v>61</v>
       </c>
       <c r="B74" s="5">
-        <f t="shared" si="1"/>
-        <v>46194</v>
+        <v>46251</v>
       </c>
       <c r="C74" t="s">
         <v>21</v>
@@ -2534,8 +2463,7 @@
         <v>61</v>
       </c>
       <c r="B75" s="5">
-        <f t="shared" si="1"/>
-        <v>46195</v>
+        <v>46252</v>
       </c>
       <c r="C75" t="s">
         <v>21</v>
@@ -2546,8 +2474,7 @@
         <v>61</v>
       </c>
       <c r="B76" s="5">
-        <f t="shared" si="1"/>
-        <v>46196</v>
+        <v>46253</v>
       </c>
       <c r="C76" t="s">
         <v>21</v>
@@ -2558,8 +2485,7 @@
         <v>61</v>
       </c>
       <c r="B77" s="5">
-        <f t="shared" si="1"/>
-        <v>46197</v>
+        <v>46254</v>
       </c>
       <c r="C77" t="s">
         <v>21</v>
@@ -2570,8 +2496,7 @@
         <v>61</v>
       </c>
       <c r="B78" s="5">
-        <f t="shared" si="1"/>
-        <v>46198</v>
+        <v>46255</v>
       </c>
       <c r="C78" t="s">
         <v>21</v>
@@ -2582,8 +2507,7 @@
         <v>61</v>
       </c>
       <c r="B79" s="5">
-        <f t="shared" si="1"/>
-        <v>46199</v>
+        <v>46256</v>
       </c>
       <c r="C79" t="s">
         <v>21</v>
@@ -2594,8 +2518,7 @@
         <v>61</v>
       </c>
       <c r="B80" s="5">
-        <f t="shared" si="1"/>
-        <v>46200</v>
+        <v>46257</v>
       </c>
       <c r="C80" t="s">
         <v>21</v>
@@ -2606,8 +2529,7 @@
         <v>61</v>
       </c>
       <c r="B81" s="5">
-        <f t="shared" si="1"/>
-        <v>46201</v>
+        <v>46258</v>
       </c>
       <c r="C81" t="s">
         <v>21</v>
@@ -2618,8 +2540,10 @@
         <v>61</v>
       </c>
       <c r="B82" s="5">
-        <f t="shared" si="1"/>
-        <v>46202</v>
+        <v>46259</v>
+      </c>
+      <c r="C82" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -2627,8 +2551,10 @@
         <v>61</v>
       </c>
       <c r="B83" s="5">
-        <f t="shared" si="1"/>
-        <v>46203</v>
+        <v>46260</v>
+      </c>
+      <c r="C83" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
@@ -2636,8 +2562,10 @@
         <v>61</v>
       </c>
       <c r="B84" s="5">
-        <f t="shared" si="1"/>
-        <v>46204</v>
+        <v>46261</v>
+      </c>
+      <c r="C84" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -2645,11 +2573,10 @@
         <v>61</v>
       </c>
       <c r="B85" s="5">
-        <f t="shared" si="1"/>
-        <v>46205</v>
+        <v>46262</v>
       </c>
       <c r="C85" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -2657,11 +2584,10 @@
         <v>61</v>
       </c>
       <c r="B86" s="5">
-        <f t="shared" si="1"/>
-        <v>46206</v>
+        <v>46263</v>
       </c>
       <c r="C86" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -2669,11 +2595,10 @@
         <v>61</v>
       </c>
       <c r="B87" s="5">
-        <f t="shared" si="1"/>
-        <v>46207</v>
+        <v>46264</v>
       </c>
       <c r="C87" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
@@ -2681,22 +2606,20 @@
         <v>61</v>
       </c>
       <c r="B88" s="5">
-        <f t="shared" si="1"/>
-        <v>46208</v>
+        <v>46265</v>
       </c>
       <c r="C88" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>61</v>
       </c>
-      <c r="B89" s="5">
-        <f t="shared" si="1"/>
-        <v>46209</v>
-      </c>
-      <c r="C89" t="s">
+      <c r="B89" s="3">
+        <v>46266</v>
+      </c>
+      <c r="C89" s="2" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2704,11 +2627,10 @@
       <c r="A90" t="s">
         <v>61</v>
       </c>
-      <c r="B90" s="5">
-        <f t="shared" si="1"/>
-        <v>46210</v>
-      </c>
-      <c r="C90" t="s">
+      <c r="B90" s="3">
+        <v>46267</v>
+      </c>
+      <c r="C90" s="2" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2716,11 +2638,10 @@
       <c r="A91" t="s">
         <v>61</v>
       </c>
-      <c r="B91" s="5">
-        <f t="shared" si="1"/>
-        <v>46211</v>
-      </c>
-      <c r="C91" t="s">
+      <c r="B91" s="3">
+        <v>46268</v>
+      </c>
+      <c r="C91" s="2" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2728,11 +2649,10 @@
       <c r="A92" t="s">
         <v>61</v>
       </c>
-      <c r="B92" s="5">
-        <f t="shared" si="1"/>
-        <v>46212</v>
-      </c>
-      <c r="C92" t="s">
+      <c r="B92" s="3">
+        <v>46269</v>
+      </c>
+      <c r="C92" s="2" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2740,11 +2660,10 @@
       <c r="A93" t="s">
         <v>61</v>
       </c>
-      <c r="B93" s="5">
-        <f t="shared" si="1"/>
-        <v>46213</v>
-      </c>
-      <c r="C93" t="s">
+      <c r="B93" s="3">
+        <v>46270</v>
+      </c>
+      <c r="C93" s="2" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2752,11 +2671,10 @@
       <c r="A94" t="s">
         <v>61</v>
       </c>
-      <c r="B94" s="5">
-        <f t="shared" si="1"/>
-        <v>46214</v>
-      </c>
-      <c r="C94" t="s">
+      <c r="B94" s="3">
+        <v>46271</v>
+      </c>
+      <c r="C94" s="2" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2764,11 +2682,10 @@
       <c r="A95" t="s">
         <v>61</v>
       </c>
-      <c r="B95" s="5">
-        <f t="shared" si="1"/>
-        <v>46215</v>
-      </c>
-      <c r="C95" t="s">
+      <c r="B95" s="3">
+        <v>46272</v>
+      </c>
+      <c r="C95" s="2" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2776,83 +2693,76 @@
       <c r="A96" t="s">
         <v>61</v>
       </c>
-      <c r="B96" s="5">
-        <f t="shared" si="1"/>
-        <v>46216</v>
-      </c>
-      <c r="C96" t="s">
-        <v>21</v>
+      <c r="B96" s="3">
+        <v>46273</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>61</v>
       </c>
-      <c r="B97" s="5">
-        <f t="shared" si="1"/>
-        <v>46217</v>
-      </c>
-      <c r="C97" t="s">
-        <v>21</v>
+      <c r="B97" s="3">
+        <v>46274</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>61</v>
       </c>
-      <c r="B98" s="5">
-        <f t="shared" si="1"/>
-        <v>46218</v>
-      </c>
-      <c r="C98" t="s">
-        <v>21</v>
+      <c r="B98" s="3">
+        <v>46275</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>61</v>
       </c>
-      <c r="B99" s="5">
-        <f t="shared" si="1"/>
-        <v>46219</v>
-      </c>
-      <c r="C99" t="s">
-        <v>21</v>
+      <c r="B99" s="3">
+        <v>46276</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>61</v>
       </c>
-      <c r="B100" s="5">
-        <f t="shared" si="1"/>
-        <v>46220</v>
-      </c>
-      <c r="C100" t="s">
-        <v>21</v>
+      <c r="B100" s="3">
+        <v>46277</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>61</v>
       </c>
-      <c r="B101" s="5">
-        <f t="shared" si="1"/>
-        <v>46221</v>
-      </c>
-      <c r="C101" t="s">
-        <v>21</v>
+      <c r="B101" s="3">
+        <v>46278</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>61</v>
       </c>
-      <c r="B102" s="5">
-        <f t="shared" si="1"/>
-        <v>46222</v>
-      </c>
-      <c r="C102" t="s">
+      <c r="B102" s="3">
+        <v>46279</v>
+      </c>
+      <c r="C102" s="2" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2860,11 +2770,10 @@
       <c r="A103" t="s">
         <v>61</v>
       </c>
-      <c r="B103" s="5">
-        <f t="shared" si="1"/>
-        <v>46223</v>
-      </c>
-      <c r="C103" t="s">
+      <c r="B103" s="3">
+        <v>46280</v>
+      </c>
+      <c r="C103" s="2" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2872,11 +2781,10 @@
       <c r="A104" t="s">
         <v>61</v>
       </c>
-      <c r="B104" s="5">
-        <f t="shared" si="1"/>
-        <v>46224</v>
-      </c>
-      <c r="C104" t="s">
+      <c r="B104" s="3">
+        <v>46281</v>
+      </c>
+      <c r="C104" s="2" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2884,11 +2792,10 @@
       <c r="A105" t="s">
         <v>61</v>
       </c>
-      <c r="B105" s="5">
-        <f t="shared" si="1"/>
-        <v>46225</v>
-      </c>
-      <c r="C105" t="s">
+      <c r="B105" s="3">
+        <v>46282</v>
+      </c>
+      <c r="C105" s="2" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2896,11 +2803,10 @@
       <c r="A106" t="s">
         <v>61</v>
       </c>
-      <c r="B106" s="5">
-        <f t="shared" si="1"/>
-        <v>46226</v>
-      </c>
-      <c r="C106" t="s">
+      <c r="B106" s="3">
+        <v>46283</v>
+      </c>
+      <c r="C106" s="2" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2908,11 +2814,10 @@
       <c r="A107" t="s">
         <v>61</v>
       </c>
-      <c r="B107" s="5">
-        <f t="shared" si="1"/>
-        <v>46227</v>
-      </c>
-      <c r="C107" t="s">
+      <c r="B107" s="3">
+        <v>46284</v>
+      </c>
+      <c r="C107" s="2" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2920,11 +2825,10 @@
       <c r="A108" t="s">
         <v>61</v>
       </c>
-      <c r="B108" s="5">
-        <f t="shared" si="1"/>
-        <v>46228</v>
-      </c>
-      <c r="C108" t="s">
+      <c r="B108" s="3">
+        <v>46285</v>
+      </c>
+      <c r="C108" s="2" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2932,11 +2836,10 @@
       <c r="A109" t="s">
         <v>61</v>
       </c>
-      <c r="B109" s="5">
-        <f t="shared" si="1"/>
-        <v>46229</v>
-      </c>
-      <c r="C109" t="s">
+      <c r="B109" s="3">
+        <v>46286</v>
+      </c>
+      <c r="C109" s="2" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2944,11 +2847,10 @@
       <c r="A110" t="s">
         <v>61</v>
       </c>
-      <c r="B110" s="5">
-        <f t="shared" si="1"/>
-        <v>46230</v>
-      </c>
-      <c r="C110" t="s">
+      <c r="B110" s="3">
+        <v>46287</v>
+      </c>
+      <c r="C110" s="2" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2956,11 +2858,10 @@
       <c r="A111" t="s">
         <v>61</v>
       </c>
-      <c r="B111" s="5">
-        <f t="shared" si="1"/>
-        <v>46231</v>
-      </c>
-      <c r="C111" t="s">
+      <c r="B111" s="3">
+        <v>46288</v>
+      </c>
+      <c r="C111" s="2" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2968,11 +2869,10 @@
       <c r="A112" t="s">
         <v>61</v>
       </c>
-      <c r="B112" s="5">
-        <f t="shared" si="1"/>
-        <v>46232</v>
-      </c>
-      <c r="C112" t="s">
+      <c r="B112" s="3">
+        <v>46289</v>
+      </c>
+      <c r="C112" s="2" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2980,11 +2880,10 @@
       <c r="A113" t="s">
         <v>61</v>
       </c>
-      <c r="B113" s="5">
-        <f t="shared" si="1"/>
-        <v>46233</v>
-      </c>
-      <c r="C113" t="s">
+      <c r="B113" s="3">
+        <v>46290</v>
+      </c>
+      <c r="C113" s="2" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2992,11 +2891,10 @@
       <c r="A114" t="s">
         <v>61</v>
       </c>
-      <c r="B114" s="5">
-        <f t="shared" si="1"/>
-        <v>46234</v>
-      </c>
-      <c r="C114" t="s">
+      <c r="B114" s="3">
+        <v>46291</v>
+      </c>
+      <c r="C114" s="2" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3004,29 +2902,32 @@
       <c r="A115" t="s">
         <v>61</v>
       </c>
-      <c r="B115" s="5">
-        <f t="shared" si="1"/>
-        <v>46235</v>
+      <c r="B115" s="3">
+        <v>46292</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>61</v>
       </c>
-      <c r="B116" s="5">
-        <f t="shared" si="1"/>
-        <v>46236</v>
+      <c r="B116" s="3">
+        <v>46300</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>61</v>
       </c>
-      <c r="B117" s="5">
-        <f t="shared" si="1"/>
-        <v>46237</v>
-      </c>
-      <c r="C117" t="s">
+      <c r="B117" s="3">
+        <v>46301</v>
+      </c>
+      <c r="C117" s="2" t="s">
         <v>20</v>
       </c>
     </row>
@@ -3034,11 +2935,10 @@
       <c r="A118" t="s">
         <v>61</v>
       </c>
-      <c r="B118" s="5">
-        <f t="shared" si="1"/>
-        <v>46238</v>
-      </c>
-      <c r="C118" t="s">
+      <c r="B118" s="3">
+        <v>46302</v>
+      </c>
+      <c r="C118" s="2" t="s">
         <v>20</v>
       </c>
     </row>
@@ -3046,11 +2946,10 @@
       <c r="A119" t="s">
         <v>61</v>
       </c>
-      <c r="B119" s="5">
-        <f t="shared" si="1"/>
-        <v>46239</v>
-      </c>
-      <c r="C119" t="s">
+      <c r="B119" s="3">
+        <v>46303</v>
+      </c>
+      <c r="C119" s="2" t="s">
         <v>20</v>
       </c>
     </row>
@@ -3058,11 +2957,10 @@
       <c r="A120" t="s">
         <v>61</v>
       </c>
-      <c r="B120" s="5">
-        <f t="shared" ref="B120:B145" si="2">B119+1</f>
-        <v>46240</v>
-      </c>
-      <c r="C120" t="s">
+      <c r="B120" s="3">
+        <v>46304</v>
+      </c>
+      <c r="C120" s="2" t="s">
         <v>20</v>
       </c>
     </row>
@@ -3070,11 +2968,10 @@
       <c r="A121" t="s">
         <v>61</v>
       </c>
-      <c r="B121" s="5">
-        <f t="shared" si="2"/>
-        <v>46241</v>
-      </c>
-      <c r="C121" t="s">
+      <c r="B121" s="3">
+        <v>46305</v>
+      </c>
+      <c r="C121" s="2" t="s">
         <v>20</v>
       </c>
     </row>
@@ -3082,11 +2979,10 @@
       <c r="A122" t="s">
         <v>61</v>
       </c>
-      <c r="B122" s="5">
-        <f t="shared" si="2"/>
-        <v>46242</v>
-      </c>
-      <c r="C122" t="s">
+      <c r="B122" s="3">
+        <v>46306</v>
+      </c>
+      <c r="C122" s="2" t="s">
         <v>20</v>
       </c>
     </row>
@@ -3094,11 +2990,10 @@
       <c r="A123" t="s">
         <v>61</v>
       </c>
-      <c r="B123" s="5">
-        <f t="shared" si="2"/>
-        <v>46243</v>
-      </c>
-      <c r="C123" t="s">
+      <c r="B123" s="3">
+        <v>46307</v>
+      </c>
+      <c r="C123" s="2" t="s">
         <v>20</v>
       </c>
     </row>
@@ -3106,95 +3001,87 @@
       <c r="A124" t="s">
         <v>61</v>
       </c>
-      <c r="B124" s="5">
-        <f t="shared" si="2"/>
-        <v>46244</v>
-      </c>
-      <c r="C124" t="s">
-        <v>20</v>
+      <c r="B124" s="3">
+        <v>46308</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>61</v>
       </c>
-      <c r="B125" s="5">
-        <f t="shared" si="2"/>
-        <v>46245</v>
-      </c>
-      <c r="C125" t="s">
-        <v>20</v>
+      <c r="B125" s="3">
+        <v>46309</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>61</v>
       </c>
-      <c r="B126" s="5">
-        <f t="shared" si="2"/>
-        <v>46246</v>
-      </c>
-      <c r="C126" t="s">
-        <v>20</v>
+      <c r="B126" s="3">
+        <v>46310</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>61</v>
       </c>
-      <c r="B127" s="5">
-        <f t="shared" si="2"/>
-        <v>46247</v>
-      </c>
-      <c r="C127" t="s">
-        <v>20</v>
+      <c r="B127" s="3">
+        <v>46311</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>61</v>
       </c>
-      <c r="B128" s="5">
-        <f t="shared" si="2"/>
-        <v>46248</v>
-      </c>
-      <c r="C128" t="s">
-        <v>20</v>
+      <c r="B128" s="3">
+        <v>46312</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>61</v>
       </c>
-      <c r="B129" s="5">
-        <f t="shared" si="2"/>
-        <v>46249</v>
-      </c>
-      <c r="C129" t="s">
-        <v>20</v>
+      <c r="B129" s="3">
+        <v>46313</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>61</v>
       </c>
-      <c r="B130" s="5">
-        <f t="shared" si="2"/>
-        <v>46250</v>
-      </c>
-      <c r="C130" t="s">
-        <v>20</v>
+      <c r="B130" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>61</v>
       </c>
-      <c r="B131" s="5">
-        <f t="shared" si="2"/>
-        <v>46251</v>
-      </c>
-      <c r="C131" t="s">
+      <c r="B131" s="3">
+        <v>46315</v>
+      </c>
+      <c r="C131" s="2" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3202,11 +3089,10 @@
       <c r="A132" t="s">
         <v>61</v>
       </c>
-      <c r="B132" s="5">
-        <f t="shared" si="2"/>
-        <v>46252</v>
-      </c>
-      <c r="C132" t="s">
+      <c r="B132" s="3">
+        <v>46316</v>
+      </c>
+      <c r="C132" s="2" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3214,11 +3100,10 @@
       <c r="A133" t="s">
         <v>61</v>
       </c>
-      <c r="B133" s="5">
-        <f t="shared" si="2"/>
-        <v>46253</v>
-      </c>
-      <c r="C133" t="s">
+      <c r="B133" s="3">
+        <v>46317</v>
+      </c>
+      <c r="C133" s="2" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3226,11 +3111,10 @@
       <c r="A134" t="s">
         <v>61</v>
       </c>
-      <c r="B134" s="5">
-        <f t="shared" si="2"/>
-        <v>46254</v>
-      </c>
-      <c r="C134" t="s">
+      <c r="B134" s="3">
+        <v>46318</v>
+      </c>
+      <c r="C134" s="2" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3238,11 +3122,10 @@
       <c r="A135" t="s">
         <v>61</v>
       </c>
-      <c r="B135" s="5">
-        <f t="shared" si="2"/>
-        <v>46255</v>
-      </c>
-      <c r="C135" t="s">
+      <c r="B135" s="3">
+        <v>46319</v>
+      </c>
+      <c r="C135" s="2" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3250,130 +3133,120 @@
       <c r="A136" t="s">
         <v>61</v>
       </c>
-      <c r="B136" s="5">
-        <f t="shared" si="2"/>
-        <v>46256</v>
-      </c>
-      <c r="C136" t="s">
+      <c r="B136" s="3">
+        <v>46320</v>
+      </c>
+      <c r="C136" s="2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>61</v>
-      </c>
-      <c r="B137" s="5">
-        <f t="shared" si="2"/>
-        <v>46257</v>
+        <v>62</v>
+      </c>
+      <c r="B137" s="3">
+        <v>46174</v>
       </c>
       <c r="C137" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B138" s="5">
-        <f t="shared" si="2"/>
-        <v>46258</v>
+        <v>46175</v>
       </c>
       <c r="C138" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B139" s="5">
-        <f t="shared" si="2"/>
-        <v>46259</v>
+        <v>46176</v>
       </c>
       <c r="C139" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B140" s="5">
-        <f t="shared" si="2"/>
-        <v>46260</v>
+        <v>46177</v>
       </c>
       <c r="C140" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B141" s="5">
-        <f t="shared" si="2"/>
-        <v>46261</v>
+        <v>46178</v>
       </c>
       <c r="C141" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B142" s="5">
-        <f t="shared" si="2"/>
-        <v>46262</v>
+        <v>46179</v>
       </c>
       <c r="C142" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B143" s="5">
-        <f t="shared" si="2"/>
-        <v>46263</v>
+        <v>46180</v>
       </c>
       <c r="C143" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B144" s="5">
-        <f t="shared" si="2"/>
-        <v>46264</v>
+        <v>46181</v>
       </c>
       <c r="C144" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B145" s="5">
-        <f t="shared" si="2"/>
-        <v>46265</v>
+        <v>46182</v>
       </c>
       <c r="C145" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>62</v>
       </c>
-      <c r="B146" s="3">
-        <v>46266</v>
-      </c>
-      <c r="C146" s="2" t="s">
+      <c r="B146" s="5">
+        <v>46183</v>
+      </c>
+      <c r="C146" t="s">
         <v>20</v>
       </c>
     </row>
@@ -3381,11 +3254,10 @@
       <c r="A147" t="s">
         <v>62</v>
       </c>
-      <c r="B147" s="3">
-        <f>B146+1</f>
-        <v>46267</v>
-      </c>
-      <c r="C147" s="2" t="s">
+      <c r="B147" s="5">
+        <v>46184</v>
+      </c>
+      <c r="C147" t="s">
         <v>20</v>
       </c>
     </row>
@@ -3393,11 +3265,10 @@
       <c r="A148" t="s">
         <v>62</v>
       </c>
-      <c r="B148" s="3">
-        <f t="shared" ref="B148:B197" si="3">B147+1</f>
-        <v>46268</v>
-      </c>
-      <c r="C148" s="2" t="s">
+      <c r="B148" s="5">
+        <v>46185</v>
+      </c>
+      <c r="C148" t="s">
         <v>20</v>
       </c>
     </row>
@@ -3405,11 +3276,10 @@
       <c r="A149" t="s">
         <v>62</v>
       </c>
-      <c r="B149" s="3">
-        <f t="shared" si="3"/>
-        <v>46269</v>
-      </c>
-      <c r="C149" s="2" t="s">
+      <c r="B149" s="5">
+        <v>46186</v>
+      </c>
+      <c r="C149" t="s">
         <v>20</v>
       </c>
     </row>
@@ -3417,11 +3287,10 @@
       <c r="A150" t="s">
         <v>62</v>
       </c>
-      <c r="B150" s="3">
-        <f t="shared" si="3"/>
-        <v>46270</v>
-      </c>
-      <c r="C150" s="2" t="s">
+      <c r="B150" s="5">
+        <v>46187</v>
+      </c>
+      <c r="C150" t="s">
         <v>20</v>
       </c>
     </row>
@@ -3429,107 +3298,98 @@
       <c r="A151" t="s">
         <v>62</v>
       </c>
-      <c r="B151" s="3">
-        <f t="shared" si="3"/>
-        <v>46271</v>
-      </c>
-      <c r="C151" s="2" t="s">
-        <v>20</v>
+      <c r="B151" s="5">
+        <v>46188</v>
+      </c>
+      <c r="C151" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>62</v>
       </c>
-      <c r="B152" s="3">
-        <f t="shared" si="3"/>
-        <v>46272</v>
-      </c>
-      <c r="C152" s="2" t="s">
-        <v>20</v>
+      <c r="B152" s="5">
+        <v>46189</v>
+      </c>
+      <c r="C152" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>62</v>
       </c>
-      <c r="B153" s="3">
-        <f t="shared" si="3"/>
-        <v>46273</v>
-      </c>
-      <c r="C153" s="2" t="s">
-        <v>20</v>
+      <c r="B153" s="5">
+        <v>46190</v>
+      </c>
+      <c r="C153" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>62</v>
       </c>
-      <c r="B154" s="3">
-        <f t="shared" si="3"/>
-        <v>46274</v>
-      </c>
-      <c r="C154" s="2" t="s">
-        <v>20</v>
+      <c r="B154" s="5">
+        <v>46191</v>
+      </c>
+      <c r="C154" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>62</v>
       </c>
-      <c r="B155" s="3">
-        <f t="shared" si="3"/>
-        <v>46275</v>
-      </c>
-      <c r="C155" s="2" t="s">
-        <v>20</v>
+      <c r="B155" s="5">
+        <v>46192</v>
+      </c>
+      <c r="C155" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>62</v>
       </c>
-      <c r="B156" s="3">
-        <f t="shared" si="3"/>
-        <v>46276</v>
-      </c>
-      <c r="C156" s="2" t="s">
-        <v>20</v>
+      <c r="B156" s="5">
+        <v>46193</v>
+      </c>
+      <c r="C156" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>62</v>
       </c>
-      <c r="B157" s="3">
-        <f t="shared" si="3"/>
-        <v>46277</v>
-      </c>
-      <c r="C157" s="2" t="s">
-        <v>20</v>
+      <c r="B157" s="5">
+        <v>46194</v>
+      </c>
+      <c r="C157" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>62</v>
       </c>
-      <c r="B158" s="3">
-        <f t="shared" si="3"/>
-        <v>46278</v>
-      </c>
-      <c r="C158" s="2" t="s">
-        <v>20</v>
+      <c r="B158" s="5">
+        <v>46195</v>
+      </c>
+      <c r="C158" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>62</v>
       </c>
-      <c r="B159" s="3">
-        <f t="shared" si="3"/>
-        <v>46279</v>
-      </c>
-      <c r="C159" s="2" t="s">
+      <c r="B159" s="5">
+        <v>46196</v>
+      </c>
+      <c r="C159" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3537,11 +3397,10 @@
       <c r="A160" t="s">
         <v>62</v>
       </c>
-      <c r="B160" s="3">
-        <f t="shared" si="3"/>
-        <v>46280</v>
-      </c>
-      <c r="C160" s="2" t="s">
+      <c r="B160" s="5">
+        <v>46197</v>
+      </c>
+      <c r="C160" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3549,11 +3408,10 @@
       <c r="A161" t="s">
         <v>62</v>
       </c>
-      <c r="B161" s="3">
-        <f t="shared" si="3"/>
-        <v>46281</v>
-      </c>
-      <c r="C161" s="2" t="s">
+      <c r="B161" s="5">
+        <v>46198</v>
+      </c>
+      <c r="C161" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3561,11 +3419,10 @@
       <c r="A162" t="s">
         <v>62</v>
       </c>
-      <c r="B162" s="3">
-        <f t="shared" si="3"/>
-        <v>46282</v>
-      </c>
-      <c r="C162" s="2" t="s">
+      <c r="B162" s="5">
+        <v>46199</v>
+      </c>
+      <c r="C162" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3573,11 +3430,10 @@
       <c r="A163" t="s">
         <v>62</v>
       </c>
-      <c r="B163" s="3">
-        <f t="shared" si="3"/>
-        <v>46283</v>
-      </c>
-      <c r="C163" s="2" t="s">
+      <c r="B163" s="5">
+        <v>46200</v>
+      </c>
+      <c r="C163" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3585,11 +3441,10 @@
       <c r="A164" t="s">
         <v>62</v>
       </c>
-      <c r="B164" s="3">
-        <f t="shared" si="3"/>
-        <v>46284</v>
-      </c>
-      <c r="C164" s="2" t="s">
+      <c r="B164" s="5">
+        <v>46201</v>
+      </c>
+      <c r="C164" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3597,106 +3452,98 @@
       <c r="A165" t="s">
         <v>62</v>
       </c>
-      <c r="B165" s="3">
-        <f t="shared" si="3"/>
-        <v>46285</v>
-      </c>
-      <c r="C165" s="2" t="s">
-        <v>21</v>
+      <c r="B165" s="5">
+        <v>46205</v>
+      </c>
+      <c r="C165" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>62</v>
       </c>
-      <c r="B166" s="3">
-        <f t="shared" si="3"/>
-        <v>46286</v>
-      </c>
-      <c r="C166" s="2" t="s">
-        <v>21</v>
+      <c r="B166" s="5">
+        <v>46206</v>
+      </c>
+      <c r="C166" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>62</v>
       </c>
-      <c r="B167" s="3">
-        <f t="shared" si="3"/>
-        <v>46287</v>
-      </c>
-      <c r="C167" s="2" t="s">
-        <v>21</v>
+      <c r="B167" s="5">
+        <v>46207</v>
+      </c>
+      <c r="C167" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>62</v>
       </c>
-      <c r="B168" s="3">
-        <f t="shared" si="3"/>
-        <v>46288</v>
-      </c>
-      <c r="C168" s="2" t="s">
-        <v>21</v>
+      <c r="B168" s="5">
+        <v>46208</v>
+      </c>
+      <c r="C168" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>62</v>
       </c>
-      <c r="B169" s="3">
-        <f t="shared" si="3"/>
-        <v>46289</v>
-      </c>
-      <c r="C169" s="2" t="s">
-        <v>21</v>
+      <c r="B169" s="5">
+        <v>46209</v>
+      </c>
+      <c r="C169" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>62</v>
       </c>
-      <c r="B170" s="3">
-        <f t="shared" si="3"/>
-        <v>46290</v>
-      </c>
-      <c r="C170" s="2" t="s">
-        <v>21</v>
+      <c r="B170" s="5">
+        <v>46210</v>
+      </c>
+      <c r="C170" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>62</v>
       </c>
-      <c r="B171" s="3">
-        <f t="shared" si="3"/>
-        <v>46291</v>
-      </c>
-      <c r="C171" s="2" t="s">
-        <v>21</v>
+      <c r="B171" s="5">
+        <v>46211</v>
+      </c>
+      <c r="C171" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>62</v>
       </c>
-      <c r="B172" s="3">
-        <f t="shared" si="3"/>
-        <v>46292</v>
-      </c>
-      <c r="C172" s="2" t="s">
-        <v>21</v>
+      <c r="B172" s="5">
+        <v>46212</v>
+      </c>
+      <c r="C172" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>62</v>
       </c>
-      <c r="B173" s="3">
-        <v>46296</v>
-      </c>
-      <c r="C173" s="2" t="s">
+      <c r="B173" s="5">
+        <v>46213</v>
+      </c>
+      <c r="C173" t="s">
         <v>20</v>
       </c>
     </row>
@@ -3704,11 +3551,10 @@
       <c r="A174" t="s">
         <v>62</v>
       </c>
-      <c r="B174" s="3">
-        <f t="shared" si="3"/>
-        <v>46297</v>
-      </c>
-      <c r="C174" s="2" t="s">
+      <c r="B174" s="5">
+        <v>46214</v>
+      </c>
+      <c r="C174" t="s">
         <v>20</v>
       </c>
     </row>
@@ -3716,11 +3562,10 @@
       <c r="A175" t="s">
         <v>62</v>
       </c>
-      <c r="B175" s="3">
-        <f t="shared" si="3"/>
-        <v>46298</v>
-      </c>
-      <c r="C175" s="2" t="s">
+      <c r="B175" s="5">
+        <v>46215</v>
+      </c>
+      <c r="C175" t="s">
         <v>20</v>
       </c>
     </row>
@@ -3728,119 +3573,109 @@
       <c r="A176" t="s">
         <v>62</v>
       </c>
-      <c r="B176" s="3">
-        <f t="shared" si="3"/>
-        <v>46299</v>
-      </c>
-      <c r="C176" s="2" t="s">
-        <v>20</v>
+      <c r="B176" s="5">
+        <v>46216</v>
+      </c>
+      <c r="C176" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>62</v>
       </c>
-      <c r="B177" s="3">
-        <f t="shared" si="3"/>
-        <v>46300</v>
-      </c>
-      <c r="C177" s="2" t="s">
-        <v>20</v>
+      <c r="B177" s="5">
+        <v>46217</v>
+      </c>
+      <c r="C177" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>62</v>
       </c>
-      <c r="B178" s="3">
-        <f t="shared" si="3"/>
-        <v>46301</v>
-      </c>
-      <c r="C178" s="2" t="s">
-        <v>20</v>
+      <c r="B178" s="5">
+        <v>46218</v>
+      </c>
+      <c r="C178" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>62</v>
       </c>
-      <c r="B179" s="3">
-        <f t="shared" si="3"/>
-        <v>46302</v>
-      </c>
-      <c r="C179" s="2" t="s">
-        <v>20</v>
+      <c r="B179" s="5">
+        <v>46219</v>
+      </c>
+      <c r="C179" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>62</v>
       </c>
-      <c r="B180" s="3">
-        <f t="shared" si="3"/>
-        <v>46303</v>
-      </c>
-      <c r="C180" s="2" t="s">
-        <v>20</v>
+      <c r="B180" s="5">
+        <v>46220</v>
+      </c>
+      <c r="C180" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>62</v>
       </c>
-      <c r="B181" s="3">
-        <f t="shared" si="3"/>
-        <v>46304</v>
-      </c>
-      <c r="C181" s="2" t="s">
-        <v>20</v>
+      <c r="B181" s="5">
+        <v>46221</v>
+      </c>
+      <c r="C181" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>62</v>
       </c>
-      <c r="B182" s="3">
-        <f t="shared" si="3"/>
-        <v>46305</v>
-      </c>
-      <c r="C182" s="2" t="s">
-        <v>20</v>
+      <c r="B182" s="5">
+        <v>46222</v>
+      </c>
+      <c r="C182" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>62</v>
       </c>
-      <c r="B183" s="3">
-        <f t="shared" si="3"/>
-        <v>46306</v>
-      </c>
-      <c r="C183" s="2" t="s">
-        <v>20</v>
+      <c r="B183" s="5">
+        <v>46223</v>
+      </c>
+      <c r="C183" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>62</v>
       </c>
-      <c r="B184" s="3">
-        <f t="shared" si="3"/>
-        <v>46307</v>
-      </c>
-      <c r="C184" s="2" t="s">
-        <v>20</v>
+      <c r="B184" s="5">
+        <v>46224</v>
+      </c>
+      <c r="C184" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>62</v>
       </c>
-      <c r="B185" s="3">
-        <f t="shared" si="3"/>
-        <v>46308</v>
-      </c>
-      <c r="C185" s="2" t="s">
+      <c r="B185" s="5">
+        <v>46225</v>
+      </c>
+      <c r="C185" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3848,11 +3683,10 @@
       <c r="A186" t="s">
         <v>62</v>
       </c>
-      <c r="B186" s="3">
-        <f t="shared" si="3"/>
-        <v>46309</v>
-      </c>
-      <c r="C186" s="2" t="s">
+      <c r="B186" s="5">
+        <v>46226</v>
+      </c>
+      <c r="C186" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3860,11 +3694,10 @@
       <c r="A187" t="s">
         <v>62</v>
       </c>
-      <c r="B187" s="3">
-        <f t="shared" si="3"/>
-        <v>46310</v>
-      </c>
-      <c r="C187" s="2" t="s">
+      <c r="B187" s="5">
+        <v>46227</v>
+      </c>
+      <c r="C187" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3872,11 +3705,10 @@
       <c r="A188" t="s">
         <v>62</v>
       </c>
-      <c r="B188" s="3">
-        <f t="shared" si="3"/>
-        <v>46311</v>
-      </c>
-      <c r="C188" s="2" t="s">
+      <c r="B188" s="5">
+        <v>46228</v>
+      </c>
+      <c r="C188" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3884,11 +3716,10 @@
       <c r="A189" t="s">
         <v>62</v>
       </c>
-      <c r="B189" s="3">
-        <f t="shared" si="3"/>
-        <v>46312</v>
-      </c>
-      <c r="C189" s="2" t="s">
+      <c r="B189" s="5">
+        <v>46229</v>
+      </c>
+      <c r="C189" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3896,11 +3727,10 @@
       <c r="A190" t="s">
         <v>62</v>
       </c>
-      <c r="B190" s="3">
-        <f t="shared" si="3"/>
-        <v>46313</v>
-      </c>
-      <c r="C190" s="2" t="s">
+      <c r="B190" s="5">
+        <v>46230</v>
+      </c>
+      <c r="C190" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3908,11 +3738,10 @@
       <c r="A191" t="s">
         <v>62</v>
       </c>
-      <c r="B191" s="3">
-        <f t="shared" si="3"/>
-        <v>46314</v>
-      </c>
-      <c r="C191" s="2" t="s">
+      <c r="B191" s="5">
+        <v>46231</v>
+      </c>
+      <c r="C191" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3920,11 +3749,10 @@
       <c r="A192" t="s">
         <v>62</v>
       </c>
-      <c r="B192" s="3">
-        <f t="shared" si="3"/>
-        <v>46315</v>
-      </c>
-      <c r="C192" s="2" t="s">
+      <c r="B192" s="5">
+        <v>46232</v>
+      </c>
+      <c r="C192" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3932,11 +3760,10 @@
       <c r="A193" t="s">
         <v>62</v>
       </c>
-      <c r="B193" s="3">
-        <f t="shared" si="3"/>
-        <v>46316</v>
-      </c>
-      <c r="C193" s="2" t="s">
+      <c r="B193" s="5">
+        <v>46233</v>
+      </c>
+      <c r="C193" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3944,11 +3771,10 @@
       <c r="A194" t="s">
         <v>62</v>
       </c>
-      <c r="B194" s="3">
-        <f t="shared" si="3"/>
-        <v>46317</v>
-      </c>
-      <c r="C194" s="2" t="s">
+      <c r="B194" s="5">
+        <v>46234</v>
+      </c>
+      <c r="C194" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3956,44 +3782,41 @@
       <c r="A195" t="s">
         <v>62</v>
       </c>
-      <c r="B195" s="3">
-        <f t="shared" si="3"/>
-        <v>46318</v>
-      </c>
-      <c r="C195" s="2" t="s">
-        <v>21</v>
+      <c r="B195" s="5">
+        <v>46237</v>
+      </c>
+      <c r="C195" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>62</v>
       </c>
-      <c r="B196" s="3">
-        <f t="shared" si="3"/>
-        <v>46319</v>
-      </c>
-      <c r="C196" s="2" t="s">
-        <v>21</v>
+      <c r="B196" s="5">
+        <v>46238</v>
+      </c>
+      <c r="C196" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>62</v>
       </c>
-      <c r="B197" s="3">
-        <f t="shared" si="3"/>
-        <v>46320</v>
-      </c>
-      <c r="C197" s="2" t="s">
-        <v>21</v>
+      <c r="B197" s="5">
+        <v>46239</v>
+      </c>
+      <c r="C197" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>62</v>
       </c>
-      <c r="B198" s="3">
-        <v>46174</v>
+      <c r="B198" s="5">
+        <v>46240</v>
       </c>
       <c r="C198" t="s">
         <v>20</v>
@@ -4004,8 +3827,7 @@
         <v>62</v>
       </c>
       <c r="B199" s="5">
-        <f>B198+1</f>
-        <v>46175</v>
+        <v>46241</v>
       </c>
       <c r="C199" t="s">
         <v>20</v>
@@ -4016,8 +3838,7 @@
         <v>62</v>
       </c>
       <c r="B200" s="5">
-        <f t="shared" ref="B200:B263" si="4">B199+1</f>
-        <v>46176</v>
+        <v>46242</v>
       </c>
       <c r="C200" t="s">
         <v>20</v>
@@ -4028,8 +3849,7 @@
         <v>62</v>
       </c>
       <c r="B201" s="5">
-        <f t="shared" si="4"/>
-        <v>46177</v>
+        <v>46243</v>
       </c>
       <c r="C201" t="s">
         <v>20</v>
@@ -4040,8 +3860,7 @@
         <v>62</v>
       </c>
       <c r="B202" s="5">
-        <f t="shared" si="4"/>
-        <v>46178</v>
+        <v>46244</v>
       </c>
       <c r="C202" t="s">
         <v>20</v>
@@ -4052,8 +3871,7 @@
         <v>62</v>
       </c>
       <c r="B203" s="5">
-        <f t="shared" si="4"/>
-        <v>46179</v>
+        <v>46245</v>
       </c>
       <c r="C203" t="s">
         <v>20</v>
@@ -4064,8 +3882,7 @@
         <v>62</v>
       </c>
       <c r="B204" s="5">
-        <f t="shared" si="4"/>
-        <v>46180</v>
+        <v>46246</v>
       </c>
       <c r="C204" t="s">
         <v>20</v>
@@ -4076,8 +3893,7 @@
         <v>62</v>
       </c>
       <c r="B205" s="5">
-        <f t="shared" si="4"/>
-        <v>46181</v>
+        <v>46247</v>
       </c>
       <c r="C205" t="s">
         <v>20</v>
@@ -4088,8 +3904,7 @@
         <v>62</v>
       </c>
       <c r="B206" s="5">
-        <f t="shared" si="4"/>
-        <v>46182</v>
+        <v>46248</v>
       </c>
       <c r="C206" t="s">
         <v>20</v>
@@ -4100,8 +3915,7 @@
         <v>62</v>
       </c>
       <c r="B207" s="5">
-        <f t="shared" si="4"/>
-        <v>46183</v>
+        <v>46249</v>
       </c>
       <c r="C207" t="s">
         <v>20</v>
@@ -4112,8 +3926,7 @@
         <v>62</v>
       </c>
       <c r="B208" s="5">
-        <f t="shared" si="4"/>
-        <v>46184</v>
+        <v>46250</v>
       </c>
       <c r="C208" t="s">
         <v>20</v>
@@ -4124,11 +3937,10 @@
         <v>62</v>
       </c>
       <c r="B209" s="5">
-        <f t="shared" si="4"/>
-        <v>46185</v>
+        <v>46251</v>
       </c>
       <c r="C209" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -4136,11 +3948,10 @@
         <v>62</v>
       </c>
       <c r="B210" s="5">
-        <f t="shared" si="4"/>
-        <v>46186</v>
+        <v>46252</v>
       </c>
       <c r="C210" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -4148,11 +3959,10 @@
         <v>62</v>
       </c>
       <c r="B211" s="5">
-        <f t="shared" si="4"/>
-        <v>46187</v>
+        <v>46253</v>
       </c>
       <c r="C211" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -4160,8 +3970,7 @@
         <v>62</v>
       </c>
       <c r="B212" s="5">
-        <f t="shared" si="4"/>
-        <v>46188</v>
+        <v>46254</v>
       </c>
       <c r="C212" t="s">
         <v>21</v>
@@ -4172,8 +3981,7 @@
         <v>62</v>
       </c>
       <c r="B213" s="5">
-        <f t="shared" si="4"/>
-        <v>46189</v>
+        <v>46255</v>
       </c>
       <c r="C213" t="s">
         <v>21</v>
@@ -4184,8 +3992,7 @@
         <v>62</v>
       </c>
       <c r="B214" s="5">
-        <f t="shared" si="4"/>
-        <v>46190</v>
+        <v>46256</v>
       </c>
       <c r="C214" t="s">
         <v>21</v>
@@ -4196,8 +4003,7 @@
         <v>62</v>
       </c>
       <c r="B215" s="5">
-        <f t="shared" si="4"/>
-        <v>46191</v>
+        <v>46257</v>
       </c>
       <c r="C215" t="s">
         <v>21</v>
@@ -4208,8 +4014,7 @@
         <v>62</v>
       </c>
       <c r="B216" s="5">
-        <f t="shared" si="4"/>
-        <v>46192</v>
+        <v>46258</v>
       </c>
       <c r="C216" t="s">
         <v>21</v>
@@ -4220,8 +4025,7 @@
         <v>62</v>
       </c>
       <c r="B217" s="5">
-        <f t="shared" si="4"/>
-        <v>46193</v>
+        <v>46259</v>
       </c>
       <c r="C217" t="s">
         <v>21</v>
@@ -4232,8 +4036,7 @@
         <v>62</v>
       </c>
       <c r="B218" s="5">
-        <f t="shared" si="4"/>
-        <v>46194</v>
+        <v>46260</v>
       </c>
       <c r="C218" t="s">
         <v>21</v>
@@ -4244,8 +4047,7 @@
         <v>62</v>
       </c>
       <c r="B219" s="5">
-        <f t="shared" si="4"/>
-        <v>46195</v>
+        <v>46261</v>
       </c>
       <c r="C219" t="s">
         <v>21</v>
@@ -4256,8 +4058,7 @@
         <v>62</v>
       </c>
       <c r="B220" s="5">
-        <f t="shared" si="4"/>
-        <v>46196</v>
+        <v>46262</v>
       </c>
       <c r="C220" t="s">
         <v>21</v>
@@ -4268,8 +4069,7 @@
         <v>62</v>
       </c>
       <c r="B221" s="5">
-        <f t="shared" si="4"/>
-        <v>46197</v>
+        <v>46263</v>
       </c>
       <c r="C221" t="s">
         <v>21</v>
@@ -4280,8 +4080,7 @@
         <v>62</v>
       </c>
       <c r="B222" s="5">
-        <f t="shared" si="4"/>
-        <v>46198</v>
+        <v>46264</v>
       </c>
       <c r="C222" t="s">
         <v>21</v>
@@ -4292,8 +4091,7 @@
         <v>62</v>
       </c>
       <c r="B223" s="5">
-        <f t="shared" si="4"/>
-        <v>46199</v>
+        <v>46265</v>
       </c>
       <c r="C223" t="s">
         <v>21</v>
@@ -4303,62 +4101,65 @@
       <c r="A224" t="s">
         <v>62</v>
       </c>
-      <c r="B224" s="5">
-        <f t="shared" si="4"/>
-        <v>46200</v>
-      </c>
-      <c r="C224" t="s">
-        <v>21</v>
+      <c r="B224" s="3">
+        <v>46266</v>
+      </c>
+      <c r="C224" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>62</v>
       </c>
-      <c r="B225" s="5">
-        <f t="shared" si="4"/>
-        <v>46201</v>
-      </c>
-      <c r="C225" t="s">
-        <v>21</v>
+      <c r="B225" s="3">
+        <v>46267</v>
+      </c>
+      <c r="C225" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>62</v>
       </c>
-      <c r="B226" s="5">
-        <f t="shared" si="4"/>
-        <v>46202</v>
+      <c r="B226" s="3">
+        <v>46268</v>
+      </c>
+      <c r="C226" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>62</v>
       </c>
-      <c r="B227" s="5">
-        <f t="shared" si="4"/>
-        <v>46203</v>
+      <c r="B227" s="3">
+        <v>46269</v>
+      </c>
+      <c r="C227" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>62</v>
       </c>
-      <c r="B228" s="5">
-        <f t="shared" si="4"/>
-        <v>46204</v>
+      <c r="B228" s="3">
+        <v>46270</v>
+      </c>
+      <c r="C228" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>62</v>
       </c>
-      <c r="B229" s="5">
-        <f t="shared" si="4"/>
-        <v>46205</v>
-      </c>
-      <c r="C229" t="s">
+      <c r="B229" s="3">
+        <v>46271</v>
+      </c>
+      <c r="C229" s="2" t="s">
         <v>20</v>
       </c>
     </row>
@@ -4366,11 +4167,10 @@
       <c r="A230" t="s">
         <v>62</v>
       </c>
-      <c r="B230" s="5">
-        <f t="shared" si="4"/>
-        <v>46206</v>
-      </c>
-      <c r="C230" t="s">
+      <c r="B230" s="3">
+        <v>46272</v>
+      </c>
+      <c r="C230" s="2" t="s">
         <v>20</v>
       </c>
     </row>
@@ -4378,11 +4178,10 @@
       <c r="A231" t="s">
         <v>62</v>
       </c>
-      <c r="B231" s="5">
-        <f t="shared" si="4"/>
-        <v>46207</v>
-      </c>
-      <c r="C231" t="s">
+      <c r="B231" s="3">
+        <v>46273</v>
+      </c>
+      <c r="C231" s="2" t="s">
         <v>20</v>
       </c>
     </row>
@@ -4390,11 +4189,10 @@
       <c r="A232" t="s">
         <v>62</v>
       </c>
-      <c r="B232" s="5">
-        <f t="shared" si="4"/>
-        <v>46208</v>
-      </c>
-      <c r="C232" t="s">
+      <c r="B232" s="3">
+        <v>46274</v>
+      </c>
+      <c r="C232" s="2" t="s">
         <v>20</v>
       </c>
     </row>
@@ -4402,11 +4200,10 @@
       <c r="A233" t="s">
         <v>62</v>
       </c>
-      <c r="B233" s="5">
-        <f t="shared" si="4"/>
-        <v>46209</v>
-      </c>
-      <c r="C233" t="s">
+      <c r="B233" s="3">
+        <v>46275</v>
+      </c>
+      <c r="C233" s="2" t="s">
         <v>20</v>
       </c>
     </row>
@@ -4414,11 +4211,10 @@
       <c r="A234" t="s">
         <v>62</v>
       </c>
-      <c r="B234" s="5">
-        <f t="shared" si="4"/>
-        <v>46210</v>
-      </c>
-      <c r="C234" t="s">
+      <c r="B234" s="3">
+        <v>46276</v>
+      </c>
+      <c r="C234" s="2" t="s">
         <v>20</v>
       </c>
     </row>
@@ -4426,11 +4222,10 @@
       <c r="A235" t="s">
         <v>62</v>
       </c>
-      <c r="B235" s="5">
-        <f t="shared" si="4"/>
-        <v>46211</v>
-      </c>
-      <c r="C235" t="s">
+      <c r="B235" s="3">
+        <v>46277</v>
+      </c>
+      <c r="C235" s="2" t="s">
         <v>20</v>
       </c>
     </row>
@@ -4438,11 +4233,10 @@
       <c r="A236" t="s">
         <v>62</v>
       </c>
-      <c r="B236" s="5">
-        <f t="shared" si="4"/>
-        <v>46212</v>
-      </c>
-      <c r="C236" t="s">
+      <c r="B236" s="3">
+        <v>46278</v>
+      </c>
+      <c r="C236" s="2" t="s">
         <v>20</v>
       </c>
     </row>
@@ -4450,47 +4244,43 @@
       <c r="A237" t="s">
         <v>62</v>
       </c>
-      <c r="B237" s="5">
-        <f t="shared" si="4"/>
-        <v>46213</v>
-      </c>
-      <c r="C237" t="s">
-        <v>20</v>
+      <c r="B237" s="3">
+        <v>46279</v>
+      </c>
+      <c r="C237" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>62</v>
       </c>
-      <c r="B238" s="5">
-        <f t="shared" si="4"/>
-        <v>46214</v>
-      </c>
-      <c r="C238" t="s">
-        <v>20</v>
+      <c r="B238" s="3">
+        <v>46280</v>
+      </c>
+      <c r="C238" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>62</v>
       </c>
-      <c r="B239" s="5">
-        <f t="shared" si="4"/>
-        <v>46215</v>
-      </c>
-      <c r="C239" t="s">
-        <v>20</v>
+      <c r="B239" s="3">
+        <v>46281</v>
+      </c>
+      <c r="C239" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>62</v>
       </c>
-      <c r="B240" s="5">
-        <f t="shared" si="4"/>
-        <v>46216</v>
-      </c>
-      <c r="C240" t="s">
+      <c r="B240" s="3">
+        <v>46282</v>
+      </c>
+      <c r="C240" s="2" t="s">
         <v>21</v>
       </c>
     </row>
@@ -4498,11 +4288,10 @@
       <c r="A241" t="s">
         <v>62</v>
       </c>
-      <c r="B241" s="5">
-        <f t="shared" si="4"/>
-        <v>46217</v>
-      </c>
-      <c r="C241" t="s">
+      <c r="B241" s="3">
+        <v>46283</v>
+      </c>
+      <c r="C241" s="2" t="s">
         <v>21</v>
       </c>
     </row>
@@ -4510,11 +4299,10 @@
       <c r="A242" t="s">
         <v>62</v>
       </c>
-      <c r="B242" s="5">
-        <f t="shared" si="4"/>
-        <v>46218</v>
-      </c>
-      <c r="C242" t="s">
+      <c r="B242" s="3">
+        <v>46284</v>
+      </c>
+      <c r="C242" s="2" t="s">
         <v>21</v>
       </c>
     </row>
@@ -4522,11 +4310,10 @@
       <c r="A243" t="s">
         <v>62</v>
       </c>
-      <c r="B243" s="5">
-        <f t="shared" si="4"/>
-        <v>46219</v>
-      </c>
-      <c r="C243" t="s">
+      <c r="B243" s="3">
+        <v>46285</v>
+      </c>
+      <c r="C243" s="2" t="s">
         <v>21</v>
       </c>
     </row>
@@ -4534,11 +4321,10 @@
       <c r="A244" t="s">
         <v>62</v>
       </c>
-      <c r="B244" s="5">
-        <f t="shared" si="4"/>
-        <v>46220</v>
-      </c>
-      <c r="C244" t="s">
+      <c r="B244" s="3">
+        <v>46286</v>
+      </c>
+      <c r="C244" s="2" t="s">
         <v>21</v>
       </c>
     </row>
@@ -4546,11 +4332,10 @@
       <c r="A245" t="s">
         <v>62</v>
       </c>
-      <c r="B245" s="5">
-        <f t="shared" si="4"/>
-        <v>46221</v>
-      </c>
-      <c r="C245" t="s">
+      <c r="B245" s="3">
+        <v>46287</v>
+      </c>
+      <c r="C245" s="2" t="s">
         <v>21</v>
       </c>
     </row>
@@ -4558,11 +4343,10 @@
       <c r="A246" t="s">
         <v>62</v>
       </c>
-      <c r="B246" s="5">
-        <f t="shared" si="4"/>
-        <v>46222</v>
-      </c>
-      <c r="C246" t="s">
+      <c r="B246" s="3">
+        <v>46288</v>
+      </c>
+      <c r="C246" s="2" t="s">
         <v>21</v>
       </c>
     </row>
@@ -4570,11 +4354,10 @@
       <c r="A247" t="s">
         <v>62</v>
       </c>
-      <c r="B247" s="5">
-        <f t="shared" si="4"/>
-        <v>46223</v>
-      </c>
-      <c r="C247" t="s">
+      <c r="B247" s="3">
+        <v>46289</v>
+      </c>
+      <c r="C247" s="2" t="s">
         <v>21</v>
       </c>
     </row>
@@ -4582,11 +4365,10 @@
       <c r="A248" t="s">
         <v>62</v>
       </c>
-      <c r="B248" s="5">
-        <f t="shared" si="4"/>
-        <v>46224</v>
-      </c>
-      <c r="C248" t="s">
+      <c r="B248" s="3">
+        <v>46290</v>
+      </c>
+      <c r="C248" s="2" t="s">
         <v>21</v>
       </c>
     </row>
@@ -4594,11 +4376,10 @@
       <c r="A249" t="s">
         <v>62</v>
       </c>
-      <c r="B249" s="5">
-        <f t="shared" si="4"/>
-        <v>46225</v>
-      </c>
-      <c r="C249" t="s">
+      <c r="B249" s="3">
+        <v>46291</v>
+      </c>
+      <c r="C249" s="2" t="s">
         <v>21</v>
       </c>
     </row>
@@ -4606,11 +4387,10 @@
       <c r="A250" t="s">
         <v>62</v>
       </c>
-      <c r="B250" s="5">
-        <f t="shared" si="4"/>
-        <v>46226</v>
-      </c>
-      <c r="C250" t="s">
+      <c r="B250" s="3">
+        <v>46292</v>
+      </c>
+      <c r="C250" s="2" t="s">
         <v>21</v>
       </c>
     </row>
@@ -4618,125 +4398,120 @@
       <c r="A251" t="s">
         <v>62</v>
       </c>
-      <c r="B251" s="5">
-        <f t="shared" si="4"/>
-        <v>46227</v>
-      </c>
-      <c r="C251" t="s">
-        <v>21</v>
+      <c r="B251" s="3">
+        <v>46296</v>
+      </c>
+      <c r="C251" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>62</v>
       </c>
-      <c r="B252" s="5">
-        <f t="shared" si="4"/>
-        <v>46228</v>
-      </c>
-      <c r="C252" t="s">
-        <v>21</v>
+      <c r="B252" s="3">
+        <v>46297</v>
+      </c>
+      <c r="C252" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>62</v>
       </c>
-      <c r="B253" s="5">
-        <f t="shared" si="4"/>
-        <v>46229</v>
-      </c>
-      <c r="C253" t="s">
-        <v>21</v>
+      <c r="B253" s="3">
+        <v>46298</v>
+      </c>
+      <c r="C253" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>62</v>
       </c>
-      <c r="B254" s="5">
-        <f t="shared" si="4"/>
-        <v>46230</v>
-      </c>
-      <c r="C254" t="s">
-        <v>21</v>
+      <c r="B254" s="3">
+        <v>46299</v>
+      </c>
+      <c r="C254" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>62</v>
       </c>
-      <c r="B255" s="5">
-        <f t="shared" si="4"/>
-        <v>46231</v>
-      </c>
-      <c r="C255" t="s">
-        <v>21</v>
+      <c r="B255" s="3">
+        <v>46300</v>
+      </c>
+      <c r="C255" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>62</v>
       </c>
-      <c r="B256" s="5">
-        <f t="shared" si="4"/>
-        <v>46232</v>
-      </c>
-      <c r="C256" t="s">
-        <v>21</v>
+      <c r="B256" s="3">
+        <v>46301</v>
+      </c>
+      <c r="C256" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>62</v>
       </c>
-      <c r="B257" s="5">
-        <f t="shared" si="4"/>
-        <v>46233</v>
-      </c>
-      <c r="C257" t="s">
-        <v>21</v>
+      <c r="B257" s="3">
+        <v>46302</v>
+      </c>
+      <c r="C257" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>62</v>
       </c>
-      <c r="B258" s="5">
-        <f t="shared" si="4"/>
-        <v>46234</v>
-      </c>
-      <c r="C258" t="s">
-        <v>21</v>
+      <c r="B258" s="3">
+        <v>46303</v>
+      </c>
+      <c r="C258" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>62</v>
       </c>
-      <c r="B259" s="5">
-        <f t="shared" si="4"/>
-        <v>46235</v>
+      <c r="B259" s="3">
+        <v>46304</v>
+      </c>
+      <c r="C259" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>62</v>
       </c>
-      <c r="B260" s="5">
-        <f t="shared" si="4"/>
-        <v>46236</v>
+      <c r="B260" s="3">
+        <v>46305</v>
+      </c>
+      <c r="C260" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>62</v>
       </c>
-      <c r="B261" s="5">
-        <f t="shared" si="4"/>
-        <v>46237</v>
-      </c>
-      <c r="C261" t="s">
+      <c r="B261" s="3">
+        <v>46306</v>
+      </c>
+      <c r="C261" s="2" t="s">
         <v>20</v>
       </c>
     </row>
@@ -4744,11 +4519,10 @@
       <c r="A262" t="s">
         <v>62</v>
       </c>
-      <c r="B262" s="5">
-        <f t="shared" si="4"/>
-        <v>46238</v>
-      </c>
-      <c r="C262" t="s">
+      <c r="B262" s="3">
+        <v>46307</v>
+      </c>
+      <c r="C262" s="2" t="s">
         <v>20</v>
       </c>
     </row>
@@ -4756,328 +4530,2017 @@
       <c r="A263" t="s">
         <v>62</v>
       </c>
-      <c r="B263" s="5">
-        <f t="shared" si="4"/>
-        <v>46239</v>
-      </c>
-      <c r="C263" t="s">
-        <v>20</v>
+      <c r="B263" s="3">
+        <v>46308</v>
+      </c>
+      <c r="C263" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>62</v>
       </c>
-      <c r="B264" s="5">
-        <f t="shared" ref="B264:B289" si="5">B263+1</f>
-        <v>46240</v>
-      </c>
-      <c r="C264" t="s">
-        <v>20</v>
+      <c r="B264" s="3">
+        <v>46309</v>
+      </c>
+      <c r="C264" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>62</v>
       </c>
-      <c r="B265" s="5">
-        <f t="shared" si="5"/>
-        <v>46241</v>
-      </c>
-      <c r="C265" t="s">
-        <v>20</v>
+      <c r="B265" s="3">
+        <v>46310</v>
+      </c>
+      <c r="C265" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>62</v>
       </c>
-      <c r="B266" s="5">
-        <f t="shared" si="5"/>
-        <v>46242</v>
-      </c>
-      <c r="C266" t="s">
-        <v>20</v>
+      <c r="B266" s="3">
+        <v>46311</v>
+      </c>
+      <c r="C266" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>62</v>
       </c>
-      <c r="B267" s="5">
-        <f t="shared" si="5"/>
-        <v>46243</v>
-      </c>
-      <c r="C267" t="s">
-        <v>20</v>
+      <c r="B267" s="3">
+        <v>46312</v>
+      </c>
+      <c r="C267" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>62</v>
       </c>
-      <c r="B268" s="5">
-        <f t="shared" si="5"/>
-        <v>46244</v>
-      </c>
-      <c r="C268" t="s">
-        <v>20</v>
+      <c r="B268" s="3">
+        <v>46313</v>
+      </c>
+      <c r="C268" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>62</v>
       </c>
-      <c r="B269" s="5">
-        <f t="shared" si="5"/>
-        <v>46245</v>
-      </c>
-      <c r="C269" t="s">
-        <v>20</v>
+      <c r="B269" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C269" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>62</v>
       </c>
-      <c r="B270" s="5">
-        <f t="shared" si="5"/>
-        <v>46246</v>
-      </c>
-      <c r="C270" t="s">
-        <v>20</v>
+      <c r="B270" s="3">
+        <v>46315</v>
+      </c>
+      <c r="C270" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>62</v>
       </c>
-      <c r="B271" s="5">
-        <f t="shared" si="5"/>
-        <v>46247</v>
-      </c>
-      <c r="C271" t="s">
-        <v>20</v>
+      <c r="B271" s="3">
+        <v>46316</v>
+      </c>
+      <c r="C271" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>62</v>
       </c>
-      <c r="B272" s="5">
-        <f t="shared" si="5"/>
-        <v>46248</v>
-      </c>
-      <c r="C272" t="s">
-        <v>20</v>
+      <c r="B272" s="3">
+        <v>46317</v>
+      </c>
+      <c r="C272" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>62</v>
       </c>
-      <c r="B273" s="5">
-        <f t="shared" si="5"/>
-        <v>46249</v>
-      </c>
-      <c r="C273" t="s">
-        <v>20</v>
+      <c r="B273" s="3">
+        <v>46318</v>
+      </c>
+      <c r="C273" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>62</v>
       </c>
-      <c r="B274" s="5">
-        <f t="shared" si="5"/>
-        <v>46250</v>
-      </c>
-      <c r="C274" t="s">
-        <v>20</v>
+      <c r="B274" s="3">
+        <v>46319</v>
+      </c>
+      <c r="C274" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>62</v>
       </c>
-      <c r="B275" s="5">
-        <f t="shared" si="5"/>
+      <c r="B275" s="3">
+        <v>46320</v>
+      </c>
+      <c r="C275" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>104</v>
+      </c>
+      <c r="B328" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C328" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>104</v>
+      </c>
+      <c r="B329" s="5">
+        <v>46175</v>
+      </c>
+      <c r="C329" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>104</v>
+      </c>
+      <c r="B330" s="5">
+        <v>46176</v>
+      </c>
+      <c r="C330" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>104</v>
+      </c>
+      <c r="B331" s="5">
+        <v>46177</v>
+      </c>
+      <c r="C331" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>104</v>
+      </c>
+      <c r="B332" s="5">
+        <v>46178</v>
+      </c>
+      <c r="C332" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>104</v>
+      </c>
+      <c r="B333" s="5">
+        <v>46179</v>
+      </c>
+      <c r="C333" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>104</v>
+      </c>
+      <c r="B334" s="5">
+        <v>46180</v>
+      </c>
+      <c r="C334" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>104</v>
+      </c>
+      <c r="B335" s="5">
+        <v>46181</v>
+      </c>
+      <c r="C335" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>104</v>
+      </c>
+      <c r="B336" s="5">
+        <v>46182</v>
+      </c>
+      <c r="C336" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
+        <v>104</v>
+      </c>
+      <c r="B337" s="5">
+        <v>46183</v>
+      </c>
+      <c r="C337" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>104</v>
+      </c>
+      <c r="B338" s="5">
+        <v>46184</v>
+      </c>
+      <c r="C338" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>104</v>
+      </c>
+      <c r="B339" s="5">
+        <v>46185</v>
+      </c>
+      <c r="C339" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>104</v>
+      </c>
+      <c r="B340" s="5">
+        <v>46186</v>
+      </c>
+      <c r="C340" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>104</v>
+      </c>
+      <c r="B341" s="5">
+        <v>46187</v>
+      </c>
+      <c r="C341" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>104</v>
+      </c>
+      <c r="B342" s="5">
+        <v>46188</v>
+      </c>
+      <c r="C342" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>104</v>
+      </c>
+      <c r="B343" s="5">
+        <v>46189</v>
+      </c>
+      <c r="C343" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>104</v>
+      </c>
+      <c r="B344" s="5">
+        <v>46190</v>
+      </c>
+      <c r="C344" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
+        <v>104</v>
+      </c>
+      <c r="B345" s="5">
+        <v>46191</v>
+      </c>
+      <c r="C345" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>104</v>
+      </c>
+      <c r="B346" s="5">
+        <v>46192</v>
+      </c>
+      <c r="C346" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>104</v>
+      </c>
+      <c r="B347" s="5">
+        <v>46193</v>
+      </c>
+      <c r="C347" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>104</v>
+      </c>
+      <c r="B348" s="5">
+        <v>46194</v>
+      </c>
+      <c r="C348" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>104</v>
+      </c>
+      <c r="B349" s="5">
+        <v>46195</v>
+      </c>
+      <c r="C349" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>104</v>
+      </c>
+      <c r="B350" s="5">
+        <v>46196</v>
+      </c>
+      <c r="C350" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>104</v>
+      </c>
+      <c r="B351" s="5">
+        <v>46197</v>
+      </c>
+      <c r="C351" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
+        <v>104</v>
+      </c>
+      <c r="B352" s="5">
+        <v>46198</v>
+      </c>
+      <c r="C352" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>104</v>
+      </c>
+      <c r="B353" s="5">
+        <v>46199</v>
+      </c>
+      <c r="C353" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>104</v>
+      </c>
+      <c r="B354" s="5">
+        <v>46200</v>
+      </c>
+      <c r="C354" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
+        <v>104</v>
+      </c>
+      <c r="B355" s="5">
+        <v>46201</v>
+      </c>
+      <c r="C355" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>104</v>
+      </c>
+      <c r="B356" s="5">
+        <v>46205</v>
+      </c>
+      <c r="C356" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>104</v>
+      </c>
+      <c r="B357" s="5">
+        <v>46206</v>
+      </c>
+      <c r="C357" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A358" t="s">
+        <v>104</v>
+      </c>
+      <c r="B358" s="5">
+        <v>46207</v>
+      </c>
+      <c r="C358" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A359" t="s">
+        <v>104</v>
+      </c>
+      <c r="B359" s="5">
+        <v>46208</v>
+      </c>
+      <c r="C359" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A360" t="s">
+        <v>104</v>
+      </c>
+      <c r="B360" s="5">
+        <v>46209</v>
+      </c>
+      <c r="C360" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A361" t="s">
+        <v>104</v>
+      </c>
+      <c r="B361" s="5">
+        <v>46210</v>
+      </c>
+      <c r="C361" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
+        <v>104</v>
+      </c>
+      <c r="B362" s="5">
+        <v>46211</v>
+      </c>
+      <c r="C362" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A363" t="s">
+        <v>104</v>
+      </c>
+      <c r="B363" s="5">
+        <v>46212</v>
+      </c>
+      <c r="C363" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A364" t="s">
+        <v>104</v>
+      </c>
+      <c r="B364" s="5">
+        <v>46213</v>
+      </c>
+      <c r="C364" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="365" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A365" t="s">
+        <v>104</v>
+      </c>
+      <c r="B365" s="5">
+        <v>46214</v>
+      </c>
+      <c r="C365" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="366" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A366" t="s">
+        <v>104</v>
+      </c>
+      <c r="B366" s="5">
+        <v>46215</v>
+      </c>
+      <c r="C366" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="367" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A367" t="s">
+        <v>104</v>
+      </c>
+      <c r="B367" s="5">
+        <v>46216</v>
+      </c>
+      <c r="C367" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="368" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A368" t="s">
+        <v>104</v>
+      </c>
+      <c r="B368" s="5">
+        <v>46217</v>
+      </c>
+      <c r="C368" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
+        <v>104</v>
+      </c>
+      <c r="B369" s="5">
+        <v>46218</v>
+      </c>
+      <c r="C369" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
+        <v>104</v>
+      </c>
+      <c r="B370" s="5">
+        <v>46219</v>
+      </c>
+      <c r="C370" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A371" t="s">
+        <v>104</v>
+      </c>
+      <c r="B371" s="5">
+        <v>46220</v>
+      </c>
+      <c r="C371" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A372" t="s">
+        <v>104</v>
+      </c>
+      <c r="B372" s="5">
+        <v>46221</v>
+      </c>
+      <c r="C372" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A373" t="s">
+        <v>104</v>
+      </c>
+      <c r="B373" s="5">
+        <v>46222</v>
+      </c>
+      <c r="C373" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="374" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A374" t="s">
+        <v>104</v>
+      </c>
+      <c r="B374" s="5">
+        <v>46223</v>
+      </c>
+      <c r="C374" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A375" t="s">
+        <v>104</v>
+      </c>
+      <c r="B375" s="5">
+        <v>46224</v>
+      </c>
+      <c r="C375" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A376" t="s">
+        <v>104</v>
+      </c>
+      <c r="B376" s="5">
+        <v>46225</v>
+      </c>
+      <c r="C376" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A377" t="s">
+        <v>104</v>
+      </c>
+      <c r="B377" s="5">
+        <v>46226</v>
+      </c>
+      <c r="C377" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="378" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A378" t="s">
+        <v>104</v>
+      </c>
+      <c r="B378" s="5">
+        <v>46227</v>
+      </c>
+      <c r="C378" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="379" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A379" t="s">
+        <v>104</v>
+      </c>
+      <c r="B379" s="5">
+        <v>46228</v>
+      </c>
+      <c r="C379" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="380" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A380" t="s">
+        <v>104</v>
+      </c>
+      <c r="B380" s="5">
+        <v>46229</v>
+      </c>
+      <c r="C380" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="381" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A381" t="s">
+        <v>104</v>
+      </c>
+      <c r="B381" s="5">
+        <v>46230</v>
+      </c>
+      <c r="C381" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A382" t="s">
+        <v>104</v>
+      </c>
+      <c r="B382" s="5">
+        <v>46231</v>
+      </c>
+      <c r="C382" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="383" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A383" t="s">
+        <v>104</v>
+      </c>
+      <c r="B383" s="5">
+        <v>46232</v>
+      </c>
+      <c r="C383" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="384" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A384" t="s">
+        <v>104</v>
+      </c>
+      <c r="B384" s="5">
+        <v>46233</v>
+      </c>
+      <c r="C384" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="385" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A385" t="s">
+        <v>104</v>
+      </c>
+      <c r="B385" s="5">
+        <v>46234</v>
+      </c>
+      <c r="C385" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="386" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A386" t="s">
+        <v>104</v>
+      </c>
+      <c r="B386" s="5">
+        <v>46237</v>
+      </c>
+      <c r="C386" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="387" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A387" t="s">
+        <v>104</v>
+      </c>
+      <c r="B387" s="5">
+        <v>46238</v>
+      </c>
+      <c r="C387" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="388" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A388" t="s">
+        <v>104</v>
+      </c>
+      <c r="B388" s="5">
+        <v>46239</v>
+      </c>
+      <c r="C388" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="389" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A389" t="s">
+        <v>104</v>
+      </c>
+      <c r="B389" s="5">
+        <v>46240</v>
+      </c>
+      <c r="C389" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A390" t="s">
+        <v>104</v>
+      </c>
+      <c r="B390" s="5">
+        <v>46241</v>
+      </c>
+      <c r="C390" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="391" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A391" t="s">
+        <v>104</v>
+      </c>
+      <c r="B391" s="5">
+        <v>46242</v>
+      </c>
+      <c r="C391" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="392" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A392" t="s">
+        <v>104</v>
+      </c>
+      <c r="B392" s="5">
+        <v>46243</v>
+      </c>
+      <c r="C392" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="393" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A393" t="s">
+        <v>104</v>
+      </c>
+      <c r="B393" s="5">
+        <v>46244</v>
+      </c>
+      <c r="C393" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="394" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A394" t="s">
+        <v>104</v>
+      </c>
+      <c r="B394" s="5">
+        <v>46245</v>
+      </c>
+      <c r="C394" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="395" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A395" t="s">
+        <v>104</v>
+      </c>
+      <c r="B395" s="5">
+        <v>46246</v>
+      </c>
+      <c r="C395" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="396" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A396" t="s">
+        <v>104</v>
+      </c>
+      <c r="B396" s="5">
+        <v>46247</v>
+      </c>
+      <c r="C396" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="397" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A397" t="s">
+        <v>104</v>
+      </c>
+      <c r="B397" s="5">
+        <v>46248</v>
+      </c>
+      <c r="C397" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="398" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A398" t="s">
+        <v>104</v>
+      </c>
+      <c r="B398" s="5">
+        <v>46249</v>
+      </c>
+      <c r="C398" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="399" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A399" t="s">
+        <v>104</v>
+      </c>
+      <c r="B399" s="5">
+        <v>46250</v>
+      </c>
+      <c r="C399" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="400" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A400" t="s">
+        <v>104</v>
+      </c>
+      <c r="B400" s="5">
         <v>46251</v>
       </c>
-      <c r="C275" t="s">
+      <c r="C400" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A276" t="s">
-        <v>62</v>
-      </c>
-      <c r="B276" s="5">
-        <f t="shared" si="5"/>
+    <row r="401" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A401" t="s">
+        <v>104</v>
+      </c>
+      <c r="B401" s="5">
         <v>46252</v>
       </c>
-      <c r="C276" t="s">
+      <c r="C401" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A277" t="s">
-        <v>62</v>
-      </c>
-      <c r="B277" s="5">
-        <f t="shared" si="5"/>
+    <row r="402" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A402" t="s">
+        <v>104</v>
+      </c>
+      <c r="B402" s="5">
         <v>46253</v>
       </c>
-      <c r="C277" t="s">
+      <c r="C402" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A278" t="s">
-        <v>62</v>
-      </c>
-      <c r="B278" s="5">
-        <f t="shared" si="5"/>
+    <row r="403" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A403" t="s">
+        <v>104</v>
+      </c>
+      <c r="B403" s="5">
         <v>46254</v>
       </c>
-      <c r="C278" t="s">
+      <c r="C403" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A279" t="s">
-        <v>62</v>
-      </c>
-      <c r="B279" s="5">
-        <f t="shared" si="5"/>
+    <row r="404" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A404" t="s">
+        <v>104</v>
+      </c>
+      <c r="B404" s="5">
         <v>46255</v>
       </c>
-      <c r="C279" t="s">
+      <c r="C404" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A280" t="s">
-        <v>62</v>
-      </c>
-      <c r="B280" s="5">
-        <f t="shared" si="5"/>
+    <row r="405" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A405" t="s">
+        <v>104</v>
+      </c>
+      <c r="B405" s="5">
         <v>46256</v>
       </c>
-      <c r="C280" t="s">
+      <c r="C405" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A281" t="s">
-        <v>62</v>
-      </c>
-      <c r="B281" s="5">
-        <f t="shared" si="5"/>
+    <row r="406" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A406" t="s">
+        <v>104</v>
+      </c>
+      <c r="B406" s="5">
         <v>46257</v>
       </c>
-      <c r="C281" t="s">
+      <c r="C406" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A282" t="s">
-        <v>62</v>
-      </c>
-      <c r="B282" s="5">
-        <f t="shared" si="5"/>
+    <row r="407" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A407" t="s">
+        <v>104</v>
+      </c>
+      <c r="B407" s="5">
         <v>46258</v>
       </c>
-      <c r="C282" t="s">
+      <c r="C407" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A283" t="s">
-        <v>62</v>
-      </c>
-      <c r="B283" s="5">
-        <f t="shared" si="5"/>
+    <row r="408" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A408" t="s">
+        <v>104</v>
+      </c>
+      <c r="B408" s="5">
         <v>46259</v>
       </c>
-      <c r="C283" t="s">
+      <c r="C408" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A284" t="s">
-        <v>62</v>
-      </c>
-      <c r="B284" s="5">
-        <f t="shared" si="5"/>
+    <row r="409" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A409" t="s">
+        <v>104</v>
+      </c>
+      <c r="B409" s="5">
         <v>46260</v>
       </c>
-      <c r="C284" t="s">
+      <c r="C409" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A285" t="s">
-        <v>62</v>
-      </c>
-      <c r="B285" s="5">
-        <f t="shared" si="5"/>
+    <row r="410" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A410" t="s">
+        <v>104</v>
+      </c>
+      <c r="B410" s="5">
         <v>46261</v>
       </c>
-      <c r="C285" t="s">
+      <c r="C410" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A286" t="s">
-        <v>62</v>
-      </c>
-      <c r="B286" s="5">
-        <f t="shared" si="5"/>
+    <row r="411" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A411" t="s">
+        <v>104</v>
+      </c>
+      <c r="B411" s="5">
         <v>46262</v>
       </c>
-      <c r="C286" t="s">
+      <c r="C411" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A287" t="s">
-        <v>62</v>
-      </c>
-      <c r="B287" s="5">
-        <f t="shared" si="5"/>
+    <row r="412" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A412" t="s">
+        <v>104</v>
+      </c>
+      <c r="B412" s="5">
         <v>46263</v>
       </c>
-      <c r="C287" t="s">
+      <c r="C412" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A288" t="s">
-        <v>62</v>
-      </c>
-      <c r="B288" s="5">
-        <f t="shared" si="5"/>
+    <row r="413" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A413" t="s">
+        <v>104</v>
+      </c>
+      <c r="B413" s="5">
         <v>46264</v>
       </c>
-      <c r="C288" t="s">
+      <c r="C413" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A289" t="s">
-        <v>62</v>
-      </c>
-      <c r="B289" s="5">
-        <f t="shared" si="5"/>
+    <row r="414" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A414" t="s">
+        <v>104</v>
+      </c>
+      <c r="B414" s="5">
         <v>46265</v>
       </c>
-      <c r="C289" t="s">
+      <c r="C414" t="s">
         <v>21</v>
       </c>
     </row>
+    <row r="415" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A415" t="s">
+        <v>104</v>
+      </c>
+      <c r="B415" s="3">
+        <v>46266</v>
+      </c>
+      <c r="C415" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="416" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A416" t="s">
+        <v>104</v>
+      </c>
+      <c r="B416" s="3">
+        <v>46267</v>
+      </c>
+      <c r="C416" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="417" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A417" t="s">
+        <v>104</v>
+      </c>
+      <c r="B417" s="3">
+        <v>46268</v>
+      </c>
+      <c r="C417" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="418" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A418" t="s">
+        <v>104</v>
+      </c>
+      <c r="B418" s="3">
+        <v>46269</v>
+      </c>
+      <c r="C418" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="419" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A419" t="s">
+        <v>104</v>
+      </c>
+      <c r="B419" s="3">
+        <v>46270</v>
+      </c>
+      <c r="C419" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="420" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A420" t="s">
+        <v>104</v>
+      </c>
+      <c r="B420" s="3">
+        <v>46271</v>
+      </c>
+      <c r="C420" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="421" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A421" t="s">
+        <v>104</v>
+      </c>
+      <c r="B421" s="3">
+        <v>46272</v>
+      </c>
+      <c r="C421" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="422" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A422" t="s">
+        <v>104</v>
+      </c>
+      <c r="B422" s="3">
+        <v>46273</v>
+      </c>
+      <c r="C422" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="423" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A423" t="s">
+        <v>104</v>
+      </c>
+      <c r="B423" s="3">
+        <v>46274</v>
+      </c>
+      <c r="C423" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="424" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A424" t="s">
+        <v>104</v>
+      </c>
+      <c r="B424" s="3">
+        <v>46275</v>
+      </c>
+      <c r="C424" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="425" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A425" t="s">
+        <v>104</v>
+      </c>
+      <c r="B425" s="3">
+        <v>46276</v>
+      </c>
+      <c r="C425" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="426" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A426" t="s">
+        <v>104</v>
+      </c>
+      <c r="B426" s="3">
+        <v>46277</v>
+      </c>
+      <c r="C426" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="427" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A427" t="s">
+        <v>104</v>
+      </c>
+      <c r="B427" s="3">
+        <v>46278</v>
+      </c>
+      <c r="C427" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="428" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A428" t="s">
+        <v>104</v>
+      </c>
+      <c r="B428" s="3">
+        <v>46279</v>
+      </c>
+      <c r="C428" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="429" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A429" t="s">
+        <v>104</v>
+      </c>
+      <c r="B429" s="3">
+        <v>46280</v>
+      </c>
+      <c r="C429" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="430" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A430" t="s">
+        <v>104</v>
+      </c>
+      <c r="B430" s="3">
+        <v>46281</v>
+      </c>
+      <c r="C430" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="431" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A431" t="s">
+        <v>104</v>
+      </c>
+      <c r="B431" s="3">
+        <v>46282</v>
+      </c>
+      <c r="C431" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="432" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A432" t="s">
+        <v>104</v>
+      </c>
+      <c r="B432" s="3">
+        <v>46283</v>
+      </c>
+      <c r="C432" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="433" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A433" t="s">
+        <v>104</v>
+      </c>
+      <c r="B433" s="3">
+        <v>46284</v>
+      </c>
+      <c r="C433" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="434" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A434" t="s">
+        <v>104</v>
+      </c>
+      <c r="B434" s="3">
+        <v>46285</v>
+      </c>
+      <c r="C434" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="435" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A435" t="s">
+        <v>104</v>
+      </c>
+      <c r="B435" s="3">
+        <v>46286</v>
+      </c>
+      <c r="C435" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="436" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A436" t="s">
+        <v>104</v>
+      </c>
+      <c r="B436" s="3">
+        <v>46287</v>
+      </c>
+      <c r="C436" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="437" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A437" t="s">
+        <v>104</v>
+      </c>
+      <c r="B437" s="3">
+        <v>46288</v>
+      </c>
+      <c r="C437" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="438" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A438" t="s">
+        <v>104</v>
+      </c>
+      <c r="B438" s="3">
+        <v>46289</v>
+      </c>
+      <c r="C438" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="439" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A439" t="s">
+        <v>104</v>
+      </c>
+      <c r="B439" s="3">
+        <v>46290</v>
+      </c>
+      <c r="C439" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="440" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A440" t="s">
+        <v>104</v>
+      </c>
+      <c r="B440" s="3">
+        <v>46291</v>
+      </c>
+      <c r="C440" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="441" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A441" t="s">
+        <v>104</v>
+      </c>
+      <c r="B441" s="3">
+        <v>46292</v>
+      </c>
+      <c r="C441" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="442" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A442" t="s">
+        <v>104</v>
+      </c>
+      <c r="B442" s="3">
+        <v>46296</v>
+      </c>
+      <c r="C442" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="443" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A443" t="s">
+        <v>104</v>
+      </c>
+      <c r="B443" s="3">
+        <v>46297</v>
+      </c>
+      <c r="C443" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="444" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A444" t="s">
+        <v>104</v>
+      </c>
+      <c r="B444" s="3">
+        <v>46298</v>
+      </c>
+      <c r="C444" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="445" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A445" t="s">
+        <v>104</v>
+      </c>
+      <c r="B445" s="3">
+        <v>46299</v>
+      </c>
+      <c r="C445" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="446" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A446" t="s">
+        <v>104</v>
+      </c>
+      <c r="B446" s="3">
+        <v>46300</v>
+      </c>
+      <c r="C446" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="447" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A447" t="s">
+        <v>104</v>
+      </c>
+      <c r="B447" s="3">
+        <v>46301</v>
+      </c>
+      <c r="C447" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="448" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A448" t="s">
+        <v>104</v>
+      </c>
+      <c r="B448" s="3">
+        <v>46302</v>
+      </c>
+      <c r="C448" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="449" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A449" t="s">
+        <v>104</v>
+      </c>
+      <c r="B449" s="3">
+        <v>46303</v>
+      </c>
+      <c r="C449" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="450" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A450" t="s">
+        <v>104</v>
+      </c>
+      <c r="B450" s="3">
+        <v>46304</v>
+      </c>
+      <c r="C450" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="451" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A451" t="s">
+        <v>104</v>
+      </c>
+      <c r="B451" s="3">
+        <v>46305</v>
+      </c>
+      <c r="C451" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="452" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A452" t="s">
+        <v>104</v>
+      </c>
+      <c r="B452" s="3">
+        <v>46306</v>
+      </c>
+      <c r="C452" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="453" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A453" t="s">
+        <v>104</v>
+      </c>
+      <c r="B453" s="3">
+        <v>46307</v>
+      </c>
+      <c r="C453" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="454" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A454" t="s">
+        <v>104</v>
+      </c>
+      <c r="B454" s="3">
+        <v>46308</v>
+      </c>
+      <c r="C454" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="455" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A455" t="s">
+        <v>104</v>
+      </c>
+      <c r="B455" s="3">
+        <v>46309</v>
+      </c>
+      <c r="C455" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="456" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A456" t="s">
+        <v>104</v>
+      </c>
+      <c r="B456" s="3">
+        <v>46310</v>
+      </c>
+      <c r="C456" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="457" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A457" t="s">
+        <v>104</v>
+      </c>
+      <c r="B457" s="3">
+        <v>46311</v>
+      </c>
+      <c r="C457" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="458" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A458" t="s">
+        <v>104</v>
+      </c>
+      <c r="B458" s="3">
+        <v>46312</v>
+      </c>
+      <c r="C458" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="459" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A459" t="s">
+        <v>104</v>
+      </c>
+      <c r="B459" s="3">
+        <v>46313</v>
+      </c>
+      <c r="C459" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="460" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A460" t="s">
+        <v>104</v>
+      </c>
+      <c r="B460" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C460" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="461" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A461" t="s">
+        <v>104</v>
+      </c>
+      <c r="B461" s="3">
+        <v>46315</v>
+      </c>
+      <c r="C461" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="462" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A462" t="s">
+        <v>104</v>
+      </c>
+      <c r="B462" s="3">
+        <v>46316</v>
+      </c>
+      <c r="C462" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="463" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A463" t="s">
+        <v>104</v>
+      </c>
+      <c r="B463" s="3">
+        <v>46317</v>
+      </c>
+      <c r="C463" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="464" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A464" t="s">
+        <v>104</v>
+      </c>
+      <c r="B464" s="3">
+        <v>46318</v>
+      </c>
+      <c r="C464" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="465" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A465" t="s">
+        <v>104</v>
+      </c>
+      <c r="B465" s="3">
+        <v>46319</v>
+      </c>
+      <c r="C465" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="466" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A466" t="s">
+        <v>104</v>
+      </c>
+      <c r="B466" s="3">
+        <v>46320</v>
+      </c>
+      <c r="C466" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="467" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A467" t="s">
+        <v>128</v>
+      </c>
+      <c r="B467" s="3">
+        <v>46296</v>
+      </c>
+      <c r="C467" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="468" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A468" t="s">
+        <v>128</v>
+      </c>
+      <c r="B468" s="3">
+        <v>46297</v>
+      </c>
+      <c r="C468" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="469" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A469" t="s">
+        <v>128</v>
+      </c>
+      <c r="B469" s="3">
+        <v>46298</v>
+      </c>
+      <c r="C469" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="470" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A470" t="s">
+        <v>128</v>
+      </c>
+      <c r="B470" s="3">
+        <v>46299</v>
+      </c>
+      <c r="C470" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="471" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A471" t="s">
+        <v>128</v>
+      </c>
+      <c r="B471" s="3">
+        <v>46300</v>
+      </c>
+      <c r="C471" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="472" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A472" t="s">
+        <v>128</v>
+      </c>
+      <c r="B472" s="3">
+        <v>46301</v>
+      </c>
+      <c r="C472" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="473" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A473" t="s">
+        <v>128</v>
+      </c>
+      <c r="B473" s="3">
+        <v>46302</v>
+      </c>
+      <c r="C473" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="474" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A474" t="s">
+        <v>128</v>
+      </c>
+      <c r="B474" s="3">
+        <v>46303</v>
+      </c>
+      <c r="C474" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="475" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A475" t="s">
+        <v>128</v>
+      </c>
+      <c r="B475" s="3">
+        <v>46304</v>
+      </c>
+      <c r="C475" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="476" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A476" t="s">
+        <v>128</v>
+      </c>
+      <c r="B476" s="3">
+        <v>46305</v>
+      </c>
+      <c r="C476" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="477" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A477" t="s">
+        <v>128</v>
+      </c>
+      <c r="B477" s="3">
+        <v>46306</v>
+      </c>
+      <c r="C477" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="478" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A478" t="s">
+        <v>128</v>
+      </c>
+      <c r="B478" s="3">
+        <v>46307</v>
+      </c>
+      <c r="C478" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="479" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A479" t="s">
+        <v>128</v>
+      </c>
+      <c r="B479" s="3">
+        <v>46308</v>
+      </c>
+      <c r="C479" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="480" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A480" t="s">
+        <v>128</v>
+      </c>
+      <c r="B480" s="3">
+        <v>46309</v>
+      </c>
+      <c r="C480" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="481" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A481" t="s">
+        <v>128</v>
+      </c>
+      <c r="B481" s="3">
+        <v>46310</v>
+      </c>
+      <c r="C481" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="482" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A482" t="s">
+        <v>128</v>
+      </c>
+      <c r="B482" s="3">
+        <v>46311</v>
+      </c>
+      <c r="C482" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="483" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A483" t="s">
+        <v>128</v>
+      </c>
+      <c r="B483" s="3">
+        <v>46312</v>
+      </c>
+      <c r="C483" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="484" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A484" t="s">
+        <v>128</v>
+      </c>
+      <c r="B484" s="3">
+        <v>46313</v>
+      </c>
+      <c r="C484" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="485" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A485" t="s">
+        <v>128</v>
+      </c>
+      <c r="B485" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C485" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="486" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A486" t="s">
+        <v>128</v>
+      </c>
+      <c r="B486" s="3">
+        <v>46315</v>
+      </c>
+      <c r="C486" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="487" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A487" t="s">
+        <v>128</v>
+      </c>
+      <c r="B487" s="3">
+        <v>46316</v>
+      </c>
+      <c r="C487" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="488" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A488" t="s">
+        <v>128</v>
+      </c>
+      <c r="B488" s="3">
+        <v>46317</v>
+      </c>
+      <c r="C488" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="489" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A489" t="s">
+        <v>128</v>
+      </c>
+      <c r="B489" s="3">
+        <v>46318</v>
+      </c>
+      <c r="C489" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="490" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A490" t="s">
+        <v>128</v>
+      </c>
+      <c r="B490" s="3">
+        <v>46319</v>
+      </c>
+      <c r="C490" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="491" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A491" t="s">
+        <v>128</v>
+      </c>
+      <c r="B491" s="3">
+        <v>46320</v>
+      </c>
+      <c r="C491" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="492" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A492" t="s">
+        <v>128</v>
+      </c>
+      <c r="B492" s="5">
+        <v>46321</v>
+      </c>
+      <c r="C492" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="493" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A493" t="s">
+        <v>128</v>
+      </c>
+      <c r="B493" s="5">
+        <v>46322</v>
+      </c>
+      <c r="C493" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="494" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A494" t="s">
+        <v>128</v>
+      </c>
+      <c r="B494" s="5">
+        <v>46323</v>
+      </c>
+      <c r="C494" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="495" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A495" t="s">
+        <v>128</v>
+      </c>
+      <c r="B495" s="5">
+        <v>46324</v>
+      </c>
+      <c r="C495" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="496" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A496" t="s">
+        <v>128</v>
+      </c>
+      <c r="B496" s="5">
+        <v>46325</v>
+      </c>
+      <c r="C496" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="497" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A497" t="s">
+        <v>128</v>
+      </c>
+      <c r="B497" s="5">
+        <v>46326</v>
+      </c>
+      <c r="C497" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C289" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:C414" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5784,7 +7247,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34B2C8DF-4561-40B2-8E7C-6CD69559B9AE}">
-  <dimension ref="A1:I1241"/>
+  <dimension ref="A1:I1239"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="20.85546875" customWidth="1"/>
@@ -42958,66 +44421,6 @@
       <c r="I1239" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1239,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
         <v>STEPG350.png</v>
-      </c>
-    </row>
-    <row r="1240" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1240" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B1240" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C1240" t="s">
-        <v>105</v>
-      </c>
-      <c r="D1240" t="s">
-        <v>129</v>
-      </c>
-      <c r="E1240" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="F1240" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G1240" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="H1240" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="I1240" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1240,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>Merca/MercaCO.png</v>
-      </c>
-    </row>
-    <row r="1241" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1241" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B1241" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C1241" t="s">
-        <v>130</v>
-      </c>
-      <c r="D1241" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1241" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="F1241" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="G1241" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="H1241" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="I1241" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1241,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>Merca/MercaFORT.png</v>
       </c>
     </row>
   </sheetData>

--- a/data/calendario_promocional.xlsx
+++ b/data/calendario_promocional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anheuserbuschinbev-my.sharepoint.com/personal/99823517_ab-inbev_com/Documents/001. Projetos/Streamlit Calendario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="164" documentId="13_ncr:1_{B92F5DA4-8825-4FA1-97C6-23568D76854D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA481E14-D7EB-431D-8ADD-442D5928C475}"/>
+  <xr:revisionPtr revIDLastSave="183" documentId="13_ncr:1_{B92F5DA4-8825-4FA1-97C6-23568D76854D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08B1661C-F40C-459C-8322-3959D1A907FC}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">CALENDARIO!$A$1:$C$414</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DeparaIMG!$A$1:$D$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">MECANICA!$A$1:$D$49</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">PRODUTOS!$A$1:$I$1239</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">PRODUTOS!$A$1:$I$1220</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7425" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7370" uniqueCount="137">
   <si>
     <t>Data</t>
   </si>
@@ -417,9 +417,6 @@
     <t>Core Cash: 45 R$/hl</t>
   </si>
   <si>
-    <t>Teste</t>
-  </si>
-  <si>
     <t>STEPG269</t>
   </si>
   <si>
@@ -445,6 +442,21 @@
   </si>
   <si>
     <t>Merca/MercaFORT</t>
+  </si>
+  <si>
+    <t>CERV: Máximo 8 combos por CPF</t>
+  </si>
+  <si>
+    <t>NAB: Máximo 8 combos por CPF</t>
+  </si>
+  <si>
+    <t>MATCH: Máximo 4 combos por CPF</t>
+  </si>
+  <si>
+    <t>LEVE 15</t>
+  </si>
+  <si>
+    <t>PAGUE 12</t>
   </si>
 </sst>
 </file>
@@ -1571,10 +1583,10 @@
         <v>62</v>
       </c>
       <c r="B50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C50" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D50" t="str">
         <f t="shared" ref="D50:D53" si="3">C50&amp;".png"</f>
@@ -1586,10 +1598,10 @@
         <v>62</v>
       </c>
       <c r="B51" t="s">
+        <v>125</v>
+      </c>
+      <c r="C51" t="s">
         <v>126</v>
-      </c>
-      <c r="C51" t="s">
-        <v>127</v>
       </c>
       <c r="D51" t="str">
         <f t="shared" si="3"/>
@@ -1598,13 +1610,13 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>127</v>
+      </c>
+      <c r="B52" t="s">
         <v>128</v>
       </c>
-      <c r="B52" t="s">
-        <v>129</v>
-      </c>
       <c r="C52" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D52" t="str">
         <f>C52&amp;".png"</f>
@@ -1613,13 +1625,13 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B53" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C53" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D53" t="str">
         <f t="shared" si="3"/>
@@ -6200,7 +6212,7 @@
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B467" s="3">
         <v>46296</v>
@@ -6211,7 +6223,7 @@
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B468" s="3">
         <v>46297</v>
@@ -6222,7 +6234,7 @@
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B469" s="3">
         <v>46298</v>
@@ -6233,7 +6245,7 @@
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B470" s="3">
         <v>46299</v>
@@ -6244,7 +6256,7 @@
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B471" s="3">
         <v>46300</v>
@@ -6255,7 +6267,7 @@
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B472" s="3">
         <v>46301</v>
@@ -6266,7 +6278,7 @@
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B473" s="3">
         <v>46302</v>
@@ -6277,7 +6289,7 @@
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B474" s="3">
         <v>46303</v>
@@ -6288,7 +6300,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B475" s="3">
         <v>46304</v>
@@ -6299,7 +6311,7 @@
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B476" s="3">
         <v>46305</v>
@@ -6310,7 +6322,7 @@
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B477" s="3">
         <v>46306</v>
@@ -6321,7 +6333,7 @@
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B478" s="3">
         <v>46307</v>
@@ -6332,7 +6344,7 @@
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B479" s="3">
         <v>46308</v>
@@ -6343,7 +6355,7 @@
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B480" s="3">
         <v>46309</v>
@@ -6354,7 +6366,7 @@
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B481" s="3">
         <v>46310</v>
@@ -6365,7 +6377,7 @@
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B482" s="3">
         <v>46311</v>
@@ -6376,7 +6388,7 @@
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B483" s="3">
         <v>46312</v>
@@ -6387,7 +6399,7 @@
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B484" s="3">
         <v>46313</v>
@@ -6398,7 +6410,7 @@
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B485" s="3">
         <v>46314</v>
@@ -6409,7 +6421,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B486" s="3">
         <v>46315</v>
@@ -6420,7 +6432,7 @@
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B487" s="3">
         <v>46316</v>
@@ -6431,7 +6443,7 @@
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B488" s="3">
         <v>46317</v>
@@ -6442,7 +6454,7 @@
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B489" s="3">
         <v>46318</v>
@@ -6453,7 +6465,7 @@
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B490" s="3">
         <v>46319</v>
@@ -6464,7 +6476,7 @@
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B491" s="3">
         <v>46320</v>
@@ -6475,7 +6487,7 @@
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B492" s="5">
         <v>46321</v>
@@ -6486,7 +6498,7 @@
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B493" s="5">
         <v>46322</v>
@@ -6497,7 +6509,7 @@
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B494" s="5">
         <v>46323</v>
@@ -6508,7 +6520,7 @@
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B495" s="5">
         <v>46324</v>
@@ -6519,7 +6531,7 @@
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B496" s="5">
         <v>46325</v>
@@ -6530,7 +6542,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B497" s="5">
         <v>46326</v>
@@ -6547,7 +6559,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D40F4A5-E774-499A-A01D-1C21EEE25028}">
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="47.5703125" bestFit="1" customWidth="1"/>
@@ -7239,6 +7251,48 @@
         <v>96</v>
       </c>
     </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D49" xr:uid="{6D40F4A5-E774-499A-A01D-1C21EEE25028}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -7247,7 +7301,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34B2C8DF-4561-40B2-8E7C-6CD69559B9AE}">
-  <dimension ref="A1:I1239"/>
+  <dimension ref="A1:I1224"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="20.85546875" customWidth="1"/>
@@ -43858,29 +43912,29 @@
         <v>98</v>
       </c>
       <c r="B1221" s="2" t="s">
-        <v>62</v>
+        <v>127</v>
       </c>
       <c r="C1221" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="D1221" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1221" s="2">
         <v>1</v>
       </c>
       <c r="F1221" t="s">
-        <v>67</v>
-      </c>
-      <c r="G1221">
-        <v>3.29</v>
-      </c>
-      <c r="H1221">
-        <v>2.99</v>
+        <v>119</v>
+      </c>
+      <c r="G1221" t="s">
+        <v>135</v>
+      </c>
+      <c r="H1221" t="s">
+        <v>136</v>
       </c>
       <c r="I1221" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1221,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>AP269.png</v>
+        <v>BC269MP.png</v>
       </c>
     </row>
     <row r="1222" spans="1:9" x14ac:dyDescent="0.25">
@@ -43888,29 +43942,29 @@
         <v>98</v>
       </c>
       <c r="B1222" s="2" t="s">
-        <v>62</v>
+        <v>127</v>
       </c>
       <c r="C1222" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="D1222" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1222" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1222" t="s">
-        <v>63</v>
-      </c>
-      <c r="G1222">
-        <v>3.19</v>
-      </c>
-      <c r="H1222">
-        <v>2.99</v>
+        <v>117</v>
+      </c>
+      <c r="G1222" t="s">
+        <v>135</v>
+      </c>
+      <c r="H1222" t="s">
+        <v>136</v>
       </c>
       <c r="I1222" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1222,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>SKZERO269.png</v>
+        <v>BUD269MP.png</v>
       </c>
     </row>
     <row r="1223" spans="1:9" x14ac:dyDescent="0.25">
@@ -43918,29 +43972,29 @@
         <v>98</v>
       </c>
       <c r="B1223" s="2" t="s">
-        <v>62</v>
+        <v>127</v>
       </c>
       <c r="C1223" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="D1223" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1223" s="2">
         <v>2</v>
       </c>
       <c r="F1223" t="s">
-        <v>66</v>
-      </c>
-      <c r="G1223">
-        <v>3.29</v>
-      </c>
-      <c r="H1223">
-        <v>2.99</v>
+        <v>116</v>
+      </c>
+      <c r="G1223" t="s">
+        <v>135</v>
+      </c>
+      <c r="H1223" t="s">
+        <v>136</v>
       </c>
       <c r="I1223" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1223,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>SK269.png</v>
+        <v>SK269MP.png</v>
       </c>
     </row>
     <row r="1224" spans="1:9" x14ac:dyDescent="0.25">
@@ -43948,483 +44002,33 @@
         <v>98</v>
       </c>
       <c r="B1224" s="2" t="s">
-        <v>62</v>
+        <v>127</v>
       </c>
       <c r="C1224" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="D1224" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1224" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1224" t="s">
-        <v>68</v>
-      </c>
-      <c r="G1224">
-        <v>3.29</v>
-      </c>
-      <c r="H1224">
-        <v>2.99</v>
+        <v>118</v>
+      </c>
+      <c r="G1224" t="s">
+        <v>135</v>
+      </c>
+      <c r="H1224" t="s">
+        <v>136</v>
       </c>
       <c r="I1224" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1224,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>BC269.png</v>
-      </c>
-    </row>
-    <row r="1225" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1225" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B1225" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1225" t="s">
-        <v>123</v>
-      </c>
-      <c r="D1225" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1225" s="2">
-        <v>1</v>
-      </c>
-      <c r="F1225" t="s">
-        <v>70</v>
-      </c>
-      <c r="G1225">
-        <v>3.69</v>
-      </c>
-      <c r="H1225">
-        <v>3.19</v>
-      </c>
-      <c r="I1225" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1225,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>BC0350.png</v>
-      </c>
-    </row>
-    <row r="1226" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1226" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B1226" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1226" t="s">
-        <v>123</v>
-      </c>
-      <c r="D1226" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1226" s="2">
-        <v>2</v>
-      </c>
-      <c r="F1226" t="s">
-        <v>70</v>
-      </c>
-      <c r="G1226">
-        <v>3.69</v>
-      </c>
-      <c r="H1226">
-        <v>3.19</v>
-      </c>
-      <c r="I1226" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1226,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>BC0350.png</v>
-      </c>
-    </row>
-    <row r="1227" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1227" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B1227" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1227" t="s">
-        <v>123</v>
-      </c>
-      <c r="D1227" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1227" s="2">
-        <v>2</v>
-      </c>
-      <c r="F1227" t="s">
-        <v>64</v>
-      </c>
-      <c r="G1227">
-        <v>3.89</v>
-      </c>
-      <c r="H1227">
-        <v>3.69</v>
-      </c>
-      <c r="I1227" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1227,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>SKZERO350.png</v>
-      </c>
-    </row>
-    <row r="1228" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1228" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B1228" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1228" t="s">
-        <v>123</v>
-      </c>
-      <c r="D1228" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1228" s="2">
-        <v>2</v>
-      </c>
-      <c r="F1228" t="s">
-        <v>72</v>
-      </c>
-      <c r="G1228">
-        <v>3.89</v>
-      </c>
-      <c r="H1228">
-        <v>3.59</v>
-      </c>
-      <c r="I1228" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1228,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>ORI269.png</v>
-      </c>
-    </row>
-    <row r="1229" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1229" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B1229" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1229" t="s">
-        <v>123</v>
-      </c>
-      <c r="D1229" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1229" s="2">
-        <v>1</v>
-      </c>
-      <c r="F1229" t="s">
-        <v>74</v>
-      </c>
-      <c r="G1229">
-        <v>4.49</v>
-      </c>
-      <c r="H1229">
-        <v>3.49</v>
-      </c>
-      <c r="I1229" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1229,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>BUDZERO350.png</v>
-      </c>
-    </row>
-    <row r="1230" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1230" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B1230" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1230" t="s">
-        <v>123</v>
-      </c>
-      <c r="D1230" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1230" s="2">
-        <v>1</v>
-      </c>
-      <c r="F1230" t="s">
-        <v>125</v>
-      </c>
-      <c r="G1230">
-        <v>4.6900000000000004</v>
-      </c>
-      <c r="H1230">
-        <v>4.3899999999999997</v>
-      </c>
-      <c r="I1230" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1230,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>STEPG269.png</v>
-      </c>
-    </row>
-    <row r="1231" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1231" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B1231" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1231" t="s">
-        <v>123</v>
-      </c>
-      <c r="D1231" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1231" s="2">
-        <v>1</v>
-      </c>
-      <c r="F1231" t="s">
-        <v>78</v>
-      </c>
-      <c r="G1231">
-        <v>5.49</v>
-      </c>
-      <c r="H1231">
-        <v>4.99</v>
-      </c>
-      <c r="I1231" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1231,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>MIC350.png</v>
-      </c>
-    </row>
-    <row r="1232" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1232" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B1232" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1232" t="s">
-        <v>123</v>
-      </c>
-      <c r="D1232" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1232" s="2">
-        <v>2</v>
-      </c>
-      <c r="F1232" t="s">
-        <v>80</v>
-      </c>
-      <c r="G1232">
-        <v>6.29</v>
-      </c>
-      <c r="H1232">
-        <v>5.49</v>
-      </c>
-      <c r="I1232" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1232,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>CORCERO350.png</v>
-      </c>
-    </row>
-    <row r="1233" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1233" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B1233" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1233" t="s">
-        <v>123</v>
-      </c>
-      <c r="D1233" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1233" s="2">
-        <v>2</v>
-      </c>
-      <c r="F1233" t="s">
-        <v>83</v>
-      </c>
-      <c r="G1233">
-        <v>6.69</v>
-      </c>
-      <c r="H1233">
-        <v>5.99</v>
-      </c>
-      <c r="I1233" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1233,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>MICLN.png</v>
-      </c>
-    </row>
-    <row r="1234" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1234" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B1234" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1234" t="s">
-        <v>123</v>
-      </c>
-      <c r="D1234" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1234" s="2">
-        <v>1</v>
-      </c>
-      <c r="F1234" t="s">
-        <v>84</v>
-      </c>
-      <c r="G1234">
-        <v>6.99</v>
-      </c>
-      <c r="H1234">
-        <v>6.19</v>
-      </c>
-      <c r="I1234" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1234,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>STELN.png</v>
-      </c>
-    </row>
-    <row r="1235" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1235" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B1235" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1235" t="s">
-        <v>123</v>
-      </c>
-      <c r="D1235" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1235" s="2">
-        <v>1</v>
-      </c>
-      <c r="F1235" t="s">
-        <v>85</v>
-      </c>
-      <c r="G1235">
-        <v>7.99</v>
-      </c>
-      <c r="H1235">
-        <v>6.99</v>
-      </c>
-      <c r="I1235" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1235,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>CORLN.png</v>
-      </c>
-    </row>
-    <row r="1236" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1236" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B1236" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1236" t="s">
-        <v>123</v>
-      </c>
-      <c r="D1236" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1236" s="2">
-        <v>1</v>
-      </c>
-      <c r="F1236" t="s">
-        <v>86</v>
-      </c>
-      <c r="G1236">
-        <v>7.99</v>
-      </c>
-      <c r="H1236">
-        <v>6.99</v>
-      </c>
-      <c r="I1236" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1236,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>CORCEROLN.png</v>
-      </c>
-    </row>
-    <row r="1237" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1237" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B1237" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1237" t="s">
-        <v>123</v>
-      </c>
-      <c r="D1237" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1237" s="2">
-        <v>1</v>
-      </c>
-      <c r="F1237" t="s">
-        <v>69</v>
-      </c>
-      <c r="G1237">
-        <v>3.49</v>
-      </c>
-      <c r="H1237">
-        <v>2.99</v>
-      </c>
-      <c r="I1237" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1237,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>BUD269.png</v>
-      </c>
-    </row>
-    <row r="1238" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1238" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B1238" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1238" t="s">
-        <v>123</v>
-      </c>
-      <c r="D1238" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1238" s="2">
-        <v>2</v>
-      </c>
-      <c r="F1238" t="s">
-        <v>75</v>
-      </c>
-      <c r="G1238">
-        <v>4.29</v>
-      </c>
-      <c r="H1238">
-        <v>3.49</v>
-      </c>
-      <c r="I1238" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1238,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>STE269.png</v>
-      </c>
-    </row>
-    <row r="1239" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1239" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B1239" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1239" t="s">
-        <v>123</v>
-      </c>
-      <c r="D1239" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1239" s="2">
-        <v>2</v>
-      </c>
-      <c r="F1239" t="s">
-        <v>126</v>
-      </c>
-      <c r="G1239">
-        <v>5.99</v>
-      </c>
-      <c r="H1239">
-        <v>5.49</v>
-      </c>
-      <c r="I1239" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1239,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>STEPG350.png</v>
+        <v>ORI269MP.png</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1239" xr:uid="{34B2C8DF-4561-40B2-8E7C-6CD69559B9AE}"/>
+  <autoFilter ref="A1:I1220" xr:uid="{34B2C8DF-4561-40B2-8E7C-6CD69559B9AE}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>

--- a/data/calendario_promocional.xlsx
+++ b/data/calendario_promocional.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anheuserbuschinbev-my.sharepoint.com/personal/99823517_ab-inbev_com/Documents/001. Projetos/Streamlit Calendario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="183" documentId="13_ncr:1_{B92F5DA4-8825-4FA1-97C6-23568D76854D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08B1661C-F40C-459C-8322-3959D1A907FC}"/>
+  <xr:revisionPtr revIDLastSave="398" documentId="13_ncr:1_{B92F5DA4-8825-4FA1-97C6-23568D76854D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16AF9812-B7A1-466C-B370-66E68547DB2D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,11 +21,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">CALENDARIO!$A$1:$C$414</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DeparaIMG!$A$1:$D$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DeparaIMG!$A$1:$D$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">MECANICA!$A$1:$D$49</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">PRODUTOS!$A$1:$I$1220</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">PRODUTOS!$A$1:$I$1327</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcMode="manual"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7370" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8174" uniqueCount="157">
   <si>
     <t>Data</t>
   </si>
@@ -432,18 +433,6 @@
     <t>MERCAPROMO</t>
   </si>
   <si>
-    <t>MercaCO</t>
-  </si>
-  <si>
-    <t>MercaFORT</t>
-  </si>
-  <si>
-    <t>Merca/MercaCO</t>
-  </si>
-  <si>
-    <t>Merca/MercaFORT</t>
-  </si>
-  <si>
     <t>CERV: Máximo 8 combos por CPF</t>
   </si>
   <si>
@@ -453,10 +442,82 @@
     <t>MATCH: Máximo 4 combos por CPF</t>
   </si>
   <si>
-    <t>LEVE 15</t>
+    <t>VAR/ATAC</t>
   </si>
   <si>
-    <t>PAGUE 12</t>
+    <t>Leve:6</t>
+  </si>
+  <si>
+    <t>Pague:5</t>
+  </si>
+  <si>
+    <t>Leve:15</t>
+  </si>
+  <si>
+    <t>Pague:12</t>
+  </si>
+  <si>
+    <t>Leve:12</t>
+  </si>
+  <si>
+    <t>Pague:10</t>
+  </si>
+  <si>
+    <t>Leve:8</t>
+  </si>
+  <si>
+    <t>Pague:7</t>
+  </si>
+  <si>
+    <t>SPT LN</t>
+  </si>
+  <si>
+    <t>Leve:3</t>
+  </si>
+  <si>
+    <t>Desconto:20%</t>
+  </si>
+  <si>
+    <t>PC SAB 350</t>
+  </si>
+  <si>
+    <t>GATORADE</t>
+  </si>
+  <si>
+    <t>BEATS - FF</t>
+  </si>
+  <si>
+    <t>Leve 2 Beats( LT ou LN )</t>
+  </si>
+  <si>
+    <t>Leve 1 Flying Fish</t>
+  </si>
+  <si>
+    <t>BEATSFF</t>
+  </si>
+  <si>
+    <t>FORT DF/GO</t>
+  </si>
+  <si>
+    <t>FORT MT/MS</t>
+  </si>
+  <si>
+    <t>BC269.png</t>
+  </si>
+  <si>
+    <t>CORCEROLN.png</t>
+  </si>
+  <si>
+    <t>STELN.png</t>
+  </si>
+  <si>
+    <t>MIC350.png</t>
+  </si>
+  <si>
+    <t>BUD269.png</t>
+  </si>
+  <si>
+    <t>Pague:13</t>
   </si>
 </sst>
 </file>
@@ -804,7 +865,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0BF5819-473C-445D-A53D-FC51ACB237C6}">
-  <dimension ref="A1:D53"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
@@ -826,7 +888,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>62</v>
       </c>
@@ -842,7 +904,7 @@
         <v>AP269.png</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>62</v>
       </c>
@@ -858,7 +920,7 @@
         <v>AP269MP.png</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>62</v>
       </c>
@@ -874,7 +936,7 @@
         <v>AP350.png</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>61</v>
       </c>
@@ -889,7 +951,7 @@
         <v>BAREP2.png</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>62</v>
       </c>
@@ -905,7 +967,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>62</v>
       </c>
@@ -921,7 +983,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>62</v>
       </c>
@@ -937,7 +999,7 @@
         <v>BC269MP.png</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>62</v>
       </c>
@@ -953,7 +1015,7 @@
         <v>BC350.png</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>104</v>
       </c>
@@ -969,7 +1031,7 @@
         <v>BEATSLN.png</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>104</v>
       </c>
@@ -985,7 +1047,7 @@
         <v>BEATSLT.png</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>62</v>
       </c>
@@ -1001,7 +1063,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>62</v>
       </c>
@@ -1017,7 +1079,7 @@
         <v>BUD269MP.png</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>62</v>
       </c>
@@ -1033,7 +1095,7 @@
         <v>BUD350.png</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>62</v>
       </c>
@@ -1049,7 +1111,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>62</v>
       </c>
@@ -1064,7 +1126,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>62</v>
       </c>
@@ -1079,7 +1141,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>62</v>
       </c>
@@ -1095,7 +1157,7 @@
         <v>COR269.png</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>62</v>
       </c>
@@ -1111,7 +1173,7 @@
         <v>COR350.png</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>62</v>
       </c>
@@ -1126,7 +1188,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>62</v>
       </c>
@@ -1141,7 +1203,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>62</v>
       </c>
@@ -1157,7 +1219,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>104</v>
       </c>
@@ -1173,7 +1235,7 @@
         <v>FF350.png</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>104</v>
       </c>
@@ -1189,7 +1251,7 @@
         <v>FFLN.png</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>61</v>
       </c>
@@ -1204,7 +1266,7 @@
         <v>GCA269.png</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>61</v>
       </c>
@@ -1219,7 +1281,7 @@
         <v>GCA350.png</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>61</v>
       </c>
@@ -1234,7 +1296,7 @@
         <v>GCAP1,5.png</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>61</v>
       </c>
@@ -1249,7 +1311,7 @@
         <v>GCAP1.png</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>61</v>
       </c>
@@ -1264,7 +1326,7 @@
         <v>GCAP2.png</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>61</v>
       </c>
@@ -1279,7 +1341,7 @@
         <v>H2OHP1,5.png</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>61</v>
       </c>
@@ -1294,7 +1356,7 @@
         <v>H2OHP500.png</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>62</v>
       </c>
@@ -1310,7 +1372,7 @@
         <v>MIC269.png</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>62</v>
       </c>
@@ -1326,7 +1388,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>62</v>
       </c>
@@ -1342,7 +1404,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>62</v>
       </c>
@@ -1358,7 +1420,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>62</v>
       </c>
@@ -1374,7 +1436,7 @@
         <v>ORI269MP.png</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>61</v>
       </c>
@@ -1389,7 +1451,7 @@
         <v>PC269.png</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>61</v>
       </c>
@@ -1404,7 +1466,7 @@
         <v>PCB350.png</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>61</v>
       </c>
@@ -1419,7 +1481,7 @@
         <v>PCP2.png</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>62</v>
       </c>
@@ -1435,7 +1497,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>62</v>
       </c>
@@ -1451,7 +1513,7 @@
         <v>SK269MP.png</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>62</v>
       </c>
@@ -1467,7 +1529,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>62</v>
       </c>
@@ -1515,7 +1577,7 @@
         <v>SPT350.png</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>62</v>
       </c>
@@ -1531,7 +1593,7 @@
         <v>STE269.png</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>62</v>
       </c>
@@ -1547,7 +1609,7 @@
         <v>STE350.png</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>62</v>
       </c>
@@ -1563,7 +1625,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>61</v>
       </c>
@@ -1578,7 +1640,7 @@
         <v>SUKP2.png</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>62</v>
       </c>
@@ -1589,11 +1651,11 @@
         <v>123</v>
       </c>
       <c r="D50" t="str">
-        <f t="shared" ref="D50:D53" si="3">C50&amp;".png"</f>
+        <f t="shared" ref="D50:D52" si="3">C50&amp;".png"</f>
         <v>STEPG269.png</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>62</v>
       </c>
@@ -1610,37 +1672,77 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>127</v>
+        <v>62</v>
       </c>
       <c r="B52" t="s">
-        <v>128</v>
-      </c>
-      <c r="C52" t="s">
-        <v>130</v>
+        <v>140</v>
+      </c>
+      <c r="C52" t="str">
+        <f t="shared" ref="C52" si="4">SUBSTITUTE(B52," ","")</f>
+        <v>SPTLN</v>
       </c>
       <c r="D52" t="str">
-        <f>C52&amp;".png"</f>
-        <v>Merca/MercaCO.png</v>
+        <f t="shared" si="3"/>
+        <v>SPTLN.png</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>127</v>
+        <v>61</v>
       </c>
       <c r="B53" t="s">
-        <v>129</v>
-      </c>
-      <c r="C53" t="s">
-        <v>131</v>
+        <v>143</v>
+      </c>
+      <c r="C53" t="str">
+        <f t="shared" ref="C53:C55" si="5">SUBSTITUTE(B53," ","")</f>
+        <v>PCSAB350</v>
       </c>
       <c r="D53" t="str">
-        <f t="shared" si="3"/>
-        <v>Merca/MercaFORT.png</v>
+        <f t="shared" ref="D53:D55" si="6">C53&amp;".png"</f>
+        <v>PCSAB350.png</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54" t="s">
+        <v>144</v>
+      </c>
+      <c r="C54" t="str">
+        <f t="shared" si="5"/>
+        <v>GATORADE</v>
+      </c>
+      <c r="D54" t="str">
+        <f t="shared" si="6"/>
+        <v>GATORADE.png</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>62</v>
+      </c>
+      <c r="B55" t="s">
+        <v>145</v>
+      </c>
+      <c r="C55" t="s">
+        <v>148</v>
+      </c>
+      <c r="D55" t="str">
+        <f t="shared" si="6"/>
+        <v>BEATSFF.png</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D49" xr:uid="{C0BF5819-473C-445D-A53D-FC51ACB237C6}"/>
-  <conditionalFormatting sqref="C1:C51 C54:C1048576">
+  <autoFilter ref="A1:D51" xr:uid="{C0BF5819-473C-445D-A53D-FC51ACB237C6}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="SPT 269"/>
+        <filter val="SPT 350"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="C1:C1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -7262,7 +7364,7 @@
         <v>127</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -7276,7 +7378,7 @@
         <v>127</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -7290,7 +7392,7 @@
         <v>127</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -7301,7 +7403,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34B2C8DF-4561-40B2-8E7C-6CD69559B9AE}">
-  <dimension ref="A1:I1224"/>
+  <dimension ref="A1:I1337"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="20.85546875" customWidth="1"/>
@@ -43915,26 +44017,26 @@
         <v>127</v>
       </c>
       <c r="C1221" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="D1221" t="s">
-        <v>26</v>
+        <v>131</v>
       </c>
       <c r="E1221" s="2">
         <v>1</v>
       </c>
       <c r="F1221" t="s">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="G1221" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H1221" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="I1221" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1221,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>BC269MP.png</v>
+        <v>MICLN.png</v>
       </c>
     </row>
     <row r="1222" spans="1:9" x14ac:dyDescent="0.25">
@@ -43945,26 +44047,26 @@
         <v>127</v>
       </c>
       <c r="C1222" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="D1222" t="s">
-        <v>26</v>
+        <v>131</v>
       </c>
       <c r="E1222" s="2">
         <v>1</v>
       </c>
       <c r="F1222" t="s">
-        <v>117</v>
+        <v>67</v>
       </c>
       <c r="G1222" t="s">
+        <v>134</v>
+      </c>
+      <c r="H1222" t="s">
         <v>135</v>
-      </c>
-      <c r="H1222" t="s">
-        <v>136</v>
       </c>
       <c r="I1222" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1222,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>BUD269MP.png</v>
+        <v>AP269.png</v>
       </c>
     </row>
     <row r="1223" spans="1:9" x14ac:dyDescent="0.25">
@@ -43975,26 +44077,26 @@
         <v>127</v>
       </c>
       <c r="C1223" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="D1223" t="s">
-        <v>26</v>
+        <v>131</v>
       </c>
       <c r="E1223" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1223" t="s">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="G1223" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H1223" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I1223" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1223,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>SK269MP.png</v>
+        <v>CORCERO350.png</v>
       </c>
     </row>
     <row r="1224" spans="1:9" x14ac:dyDescent="0.25">
@@ -44005,30 +44107,3410 @@
         <v>127</v>
       </c>
       <c r="C1224" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="D1224" t="s">
-        <v>26</v>
+        <v>131</v>
       </c>
       <c r="E1224" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1224" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="G1224" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H1224" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="I1224" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1224,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>ORI269MP.png</v>
+        <v>SPTLN.png</v>
+      </c>
+    </row>
+    <row r="1225" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1225" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1225" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1225" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1225" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1225">
+        <v>2</v>
+      </c>
+      <c r="F1225" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1225" t="s">
+        <v>134</v>
+      </c>
+      <c r="H1225" t="s">
+        <v>135</v>
+      </c>
+      <c r="I1225" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1225,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BC269.png</v>
+      </c>
+    </row>
+    <row r="1226" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1226" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1226" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1226" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1226" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1226">
+        <v>2</v>
+      </c>
+      <c r="F1226" t="s">
+        <v>86</v>
+      </c>
+      <c r="G1226" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1226" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1226" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1226,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>CORCEROLN.png</v>
+      </c>
+    </row>
+    <row r="1227" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1227" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1227" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1227" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1227" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1227">
+        <v>2</v>
+      </c>
+      <c r="F1227" t="s">
+        <v>84</v>
+      </c>
+      <c r="G1227" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1227" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1227" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1227,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>STELN.png</v>
+      </c>
+    </row>
+    <row r="1228" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1228" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1228" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1228" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1228" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1228">
+        <v>2</v>
+      </c>
+      <c r="F1228" t="s">
+        <v>78</v>
+      </c>
+      <c r="G1228" t="s">
+        <v>138</v>
+      </c>
+      <c r="H1228" t="s">
+        <v>139</v>
+      </c>
+      <c r="I1228" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1228,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>MIC350.png</v>
+      </c>
+    </row>
+    <row r="1229" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1229" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1229" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1229" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1229" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1229">
+        <v>2</v>
+      </c>
+      <c r="F1229" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1229" t="s">
+        <v>134</v>
+      </c>
+      <c r="H1229" t="s">
+        <v>135</v>
+      </c>
+      <c r="I1229" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1229,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BUD269.png</v>
+      </c>
+    </row>
+    <row r="1230" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1230" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1230" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1230" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1230" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1230">
+        <v>1</v>
+      </c>
+      <c r="F1230" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1230" t="s">
+        <v>134</v>
+      </c>
+      <c r="H1230" t="s">
+        <v>135</v>
+      </c>
+      <c r="I1230" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1230,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>AP269.png</v>
+      </c>
+    </row>
+    <row r="1231" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1231" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1231" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1231" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1231" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1231">
+        <v>1</v>
+      </c>
+      <c r="F1231" t="s">
+        <v>83</v>
+      </c>
+      <c r="G1231" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1231" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1231" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1231,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>MICLN.png</v>
+      </c>
+    </row>
+    <row r="1232" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1232" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1232" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1232" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1232" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1232">
+        <v>1</v>
+      </c>
+      <c r="F1232" t="s">
+        <v>80</v>
+      </c>
+      <c r="G1232" t="s">
+        <v>136</v>
+      </c>
+      <c r="H1232" t="s">
+        <v>137</v>
+      </c>
+      <c r="I1232" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1232,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>CORCERO350.png</v>
+      </c>
+    </row>
+    <row r="1233" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1233" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1233" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1233" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1233" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1233">
+        <v>1</v>
+      </c>
+      <c r="F1233" t="s">
+        <v>140</v>
+      </c>
+      <c r="G1233" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1233" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1233" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1233,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>SPTLN.png</v>
+      </c>
+    </row>
+    <row r="1234" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1234" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1234" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1234" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1234" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1234">
+        <v>2</v>
+      </c>
+      <c r="F1234" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1234" t="s">
+        <v>134</v>
+      </c>
+      <c r="H1234" t="s">
+        <v>135</v>
+      </c>
+      <c r="I1234" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1234,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BC269.png</v>
+      </c>
+    </row>
+    <row r="1235" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1235" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1235" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1235" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1235" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1235">
+        <v>2</v>
+      </c>
+      <c r="F1235" t="s">
+        <v>86</v>
+      </c>
+      <c r="G1235" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1235" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1235" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1235,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>CORCEROLN.png</v>
+      </c>
+    </row>
+    <row r="1236" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1236" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1236" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1236" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1236" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1236">
+        <v>2</v>
+      </c>
+      <c r="F1236" t="s">
+        <v>84</v>
+      </c>
+      <c r="G1236" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1236" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1236" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1236,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>STELN.png</v>
+      </c>
+    </row>
+    <row r="1237" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1237" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1237" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1237" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1237" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1237">
+        <v>2</v>
+      </c>
+      <c r="F1237" t="s">
+        <v>78</v>
+      </c>
+      <c r="G1237" t="s">
+        <v>138</v>
+      </c>
+      <c r="H1237" t="s">
+        <v>139</v>
+      </c>
+      <c r="I1237" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1237,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>MIC350.png</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1238" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1238" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1238" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1238" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1238">
+        <v>2</v>
+      </c>
+      <c r="F1238" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1238" t="s">
+        <v>134</v>
+      </c>
+      <c r="H1238" t="s">
+        <v>135</v>
+      </c>
+      <c r="I1238" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1238,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BUD269.png</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1239" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1239" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1239" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1239" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1239">
+        <v>1</v>
+      </c>
+      <c r="F1239" t="s">
+        <v>66</v>
+      </c>
+      <c r="G1239" t="s">
+        <v>134</v>
+      </c>
+      <c r="H1239" t="s">
+        <v>135</v>
+      </c>
+      <c r="I1239" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1239,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>SK269.png</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1240" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1240" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1240" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1240" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1240">
+        <v>1</v>
+      </c>
+      <c r="F1240" t="s">
+        <v>83</v>
+      </c>
+      <c r="G1240" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1240" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1240" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1240,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>MICLN.png</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1241" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1241" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1241" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1241" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1241">
+        <v>1</v>
+      </c>
+      <c r="F1241" t="s">
+        <v>80</v>
+      </c>
+      <c r="G1241" t="s">
+        <v>136</v>
+      </c>
+      <c r="H1241" t="s">
+        <v>137</v>
+      </c>
+      <c r="I1241" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1241,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>CORCERO350.png</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1242" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1242" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1242" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1242" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1242">
+        <v>1</v>
+      </c>
+      <c r="F1242" t="s">
+        <v>140</v>
+      </c>
+      <c r="G1242" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1242" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1242" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1242,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>SPTLN.png</v>
+      </c>
+    </row>
+    <row r="1243" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1243" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1243" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1243" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1243" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1243">
+        <v>2</v>
+      </c>
+      <c r="F1243" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1243" t="s">
+        <v>134</v>
+      </c>
+      <c r="H1243" t="s">
+        <v>135</v>
+      </c>
+      <c r="I1243" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1243,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BC269.png</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1244" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1244" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1244" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1244" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1244">
+        <v>2</v>
+      </c>
+      <c r="F1244" t="s">
+        <v>86</v>
+      </c>
+      <c r="G1244" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1244" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1244" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1244,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>CORCEROLN.png</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1245" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1245" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1245" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1245" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1245">
+        <v>2</v>
+      </c>
+      <c r="F1245" t="s">
+        <v>84</v>
+      </c>
+      <c r="G1245" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1245" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1245" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1245,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>STELN.png</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1246" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1246" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1246" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1246" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1246">
+        <v>2</v>
+      </c>
+      <c r="F1246" t="s">
+        <v>78</v>
+      </c>
+      <c r="G1246" t="s">
+        <v>138</v>
+      </c>
+      <c r="H1246" t="s">
+        <v>139</v>
+      </c>
+      <c r="I1246" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1246,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>MIC350.png</v>
+      </c>
+    </row>
+    <row r="1247" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1247" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1247" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1247" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1247" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1247">
+        <v>2</v>
+      </c>
+      <c r="F1247" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1247" t="s">
+        <v>134</v>
+      </c>
+      <c r="H1247" t="s">
+        <v>135</v>
+      </c>
+      <c r="I1247" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1247,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BUD269.png</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1248" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1248" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1248" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1248" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1248">
+        <v>1</v>
+      </c>
+      <c r="F1248" t="s">
+        <v>66</v>
+      </c>
+      <c r="G1248" t="s">
+        <v>134</v>
+      </c>
+      <c r="H1248" t="s">
+        <v>135</v>
+      </c>
+      <c r="I1248" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1248,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>SK269.png</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1249" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1249" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1249" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1249" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1249">
+        <v>2</v>
+      </c>
+      <c r="F1249" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1249" t="s">
+        <v>134</v>
+      </c>
+      <c r="H1249" t="s">
+        <v>135</v>
+      </c>
+      <c r="I1249" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1249,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>AP269.png</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1250" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1250" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1250" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1250" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1250">
+        <v>1</v>
+      </c>
+      <c r="F1250" t="s">
+        <v>83</v>
+      </c>
+      <c r="G1250" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1250" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1250" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1250,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>MICLN.png</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1251" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1251" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1251" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1251" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1251">
+        <v>1</v>
+      </c>
+      <c r="F1251" t="s">
+        <v>80</v>
+      </c>
+      <c r="G1251" t="s">
+        <v>136</v>
+      </c>
+      <c r="H1251" t="s">
+        <v>137</v>
+      </c>
+      <c r="I1251" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1251,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>CORCERO350.png</v>
+      </c>
+    </row>
+    <row r="1252" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1252" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1252" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1252" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1252" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1252">
+        <v>1</v>
+      </c>
+      <c r="F1252" t="s">
+        <v>140</v>
+      </c>
+      <c r="G1252" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1252" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1252" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1252,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>SPTLN.png</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1253" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1253" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1253" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1253" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1253">
+        <v>2</v>
+      </c>
+      <c r="F1253" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1253" t="s">
+        <v>134</v>
+      </c>
+      <c r="H1253" t="s">
+        <v>135</v>
+      </c>
+      <c r="I1253" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1253,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BC269.png</v>
+      </c>
+    </row>
+    <row r="1254" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1254" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1254" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1254" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1254" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1254">
+        <v>2</v>
+      </c>
+      <c r="F1254" t="s">
+        <v>86</v>
+      </c>
+      <c r="G1254" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1254" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1254" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1254,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>CORCEROLN.png</v>
+      </c>
+    </row>
+    <row r="1255" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1255" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1255" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1255" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1255" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1255">
+        <v>2</v>
+      </c>
+      <c r="F1255" t="s">
+        <v>84</v>
+      </c>
+      <c r="G1255" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1255" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1255" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1255,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>STELN.png</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1256" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1256" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1256" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1256" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1256">
+        <v>2</v>
+      </c>
+      <c r="F1256" t="s">
+        <v>78</v>
+      </c>
+      <c r="G1256" t="s">
+        <v>138</v>
+      </c>
+      <c r="H1256" t="s">
+        <v>139</v>
+      </c>
+      <c r="I1256" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1256,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>MIC350.png</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1257" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1257" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1257" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1257" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1257">
+        <v>2</v>
+      </c>
+      <c r="F1257" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1257" t="s">
+        <v>134</v>
+      </c>
+      <c r="H1257" t="s">
+        <v>135</v>
+      </c>
+      <c r="I1257" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1257,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BUD269.png</v>
+      </c>
+    </row>
+    <row r="1258" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1258" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1258" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1258" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1258" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1258">
+        <v>1</v>
+      </c>
+      <c r="F1258" t="s">
+        <v>38</v>
+      </c>
+      <c r="G1258" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1258" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1258" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1258,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>GCA350.png</v>
+      </c>
+    </row>
+    <row r="1259" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1259" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1259" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1259" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1259" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1259">
+        <v>1</v>
+      </c>
+      <c r="F1259" t="s">
+        <v>143</v>
+      </c>
+      <c r="G1259" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1259" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1259" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1259,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>PCSAB350.png</v>
+      </c>
+    </row>
+    <row r="1260" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1260" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1260" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1260" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1260" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1260">
+        <v>1</v>
+      </c>
+      <c r="F1260" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1260" t="s">
+        <v>141</v>
+      </c>
+      <c r="H1260" t="s">
+        <v>142</v>
+      </c>
+      <c r="I1260" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1260,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>GCAP2.png</v>
+      </c>
+    </row>
+    <row r="1261" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1261" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1261" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1261" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1261" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1261">
+        <v>2</v>
+      </c>
+      <c r="F1261" t="s">
+        <v>144</v>
+      </c>
+      <c r="G1261" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1261" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1261" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1261,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>GATORADE.png</v>
+      </c>
+    </row>
+    <row r="1262" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1262" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1262" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1262" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1262" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1262">
+        <v>2</v>
+      </c>
+      <c r="F1262" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1262" t="s">
+        <v>141</v>
+      </c>
+      <c r="H1262" t="s">
+        <v>142</v>
+      </c>
+      <c r="I1262" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1262,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>PCP2.png</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1263" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1263" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1263" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1263" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1263">
+        <v>2</v>
+      </c>
+      <c r="F1263" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1263" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1263" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1263" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1263,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>H2OHP500.png</v>
+      </c>
+    </row>
+    <row r="1264" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1264" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1264" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1264" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1264" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1264">
+        <v>1</v>
+      </c>
+      <c r="F1264" t="s">
+        <v>38</v>
+      </c>
+      <c r="G1264" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1264" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1264" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1264,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>GCA350.png</v>
+      </c>
+    </row>
+    <row r="1265" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1265" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1265" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1265" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1265" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1265">
+        <v>1</v>
+      </c>
+      <c r="F1265" t="s">
+        <v>143</v>
+      </c>
+      <c r="G1265" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1265" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1265" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1265,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>PCSAB350.png</v>
+      </c>
+    </row>
+    <row r="1266" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1266" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1266" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1266" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1266" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1266">
+        <v>1</v>
+      </c>
+      <c r="F1266" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1266" t="s">
+        <v>141</v>
+      </c>
+      <c r="H1266" t="s">
+        <v>142</v>
+      </c>
+      <c r="I1266" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1266,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>GCAP2.png</v>
+      </c>
+    </row>
+    <row r="1267" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1267" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1267" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1267" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1267" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1267">
+        <v>2</v>
+      </c>
+      <c r="F1267" t="s">
+        <v>144</v>
+      </c>
+      <c r="G1267" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1267" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1267" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1267,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>GATORADE.png</v>
+      </c>
+    </row>
+    <row r="1268" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1268" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1268" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1268" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1268" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1268">
+        <v>2</v>
+      </c>
+      <c r="F1268" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1268" t="s">
+        <v>141</v>
+      </c>
+      <c r="H1268" t="s">
+        <v>142</v>
+      </c>
+      <c r="I1268" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1268,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>PCP2.png</v>
+      </c>
+    </row>
+    <row r="1269" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1269" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1269" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1269" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1269" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1269">
+        <v>2</v>
+      </c>
+      <c r="F1269" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1269" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1269" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1269" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1269,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>H2OHP500.png</v>
+      </c>
+    </row>
+    <row r="1270" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1270" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1270" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1270" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1270" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1270">
+        <v>1</v>
+      </c>
+      <c r="F1270" t="s">
+        <v>38</v>
+      </c>
+      <c r="G1270" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1270" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1270" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1270,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>GCA350.png</v>
+      </c>
+    </row>
+    <row r="1271" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1271" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1271" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1271" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1271" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1271">
+        <v>1</v>
+      </c>
+      <c r="F1271" t="s">
+        <v>143</v>
+      </c>
+      <c r="G1271" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1271" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1271" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1271,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>PCSAB350.png</v>
+      </c>
+    </row>
+    <row r="1272" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1272" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1272" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1272" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1272" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1272">
+        <v>1</v>
+      </c>
+      <c r="F1272" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1272" t="s">
+        <v>141</v>
+      </c>
+      <c r="H1272" t="s">
+        <v>142</v>
+      </c>
+      <c r="I1272" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1272,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>GCAP2.png</v>
+      </c>
+    </row>
+    <row r="1273" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1273" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1273" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1273" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1273" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1273">
+        <v>2</v>
+      </c>
+      <c r="F1273" t="s">
+        <v>144</v>
+      </c>
+      <c r="G1273" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1273" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1273" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1273,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>GATORADE.png</v>
+      </c>
+    </row>
+    <row r="1274" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1274" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1274" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1274" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1274" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1274">
+        <v>2</v>
+      </c>
+      <c r="F1274" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1274" t="s">
+        <v>141</v>
+      </c>
+      <c r="H1274" t="s">
+        <v>142</v>
+      </c>
+      <c r="I1274" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1274,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>PCP2.png</v>
+      </c>
+    </row>
+    <row r="1275" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1275" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1275" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1275" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1275" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1275">
+        <v>2</v>
+      </c>
+      <c r="F1275" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1275" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1275" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1275" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1275,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>H2OHP500.png</v>
+      </c>
+    </row>
+    <row r="1276" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1276" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1276" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1276" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1276" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1276">
+        <v>1</v>
+      </c>
+      <c r="F1276" t="s">
+        <v>38</v>
+      </c>
+      <c r="G1276" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1276" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1276" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1276,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>GCA350.png</v>
+      </c>
+    </row>
+    <row r="1277" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1277" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1277" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1277" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1277" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1277">
+        <v>1</v>
+      </c>
+      <c r="F1277" t="s">
+        <v>143</v>
+      </c>
+      <c r="G1277" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1277" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1277" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1277,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>PCSAB350.png</v>
+      </c>
+    </row>
+    <row r="1278" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1278" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1278" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1278" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1278" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1278">
+        <v>1</v>
+      </c>
+      <c r="F1278" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1278" t="s">
+        <v>141</v>
+      </c>
+      <c r="H1278" t="s">
+        <v>142</v>
+      </c>
+      <c r="I1278" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1278,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>GCAP2.png</v>
+      </c>
+    </row>
+    <row r="1279" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1279" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1279" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1279" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1279" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1279">
+        <v>2</v>
+      </c>
+      <c r="F1279" t="s">
+        <v>144</v>
+      </c>
+      <c r="G1279" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1279" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1279" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1279,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>GATORADE.png</v>
+      </c>
+    </row>
+    <row r="1280" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1280" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1280" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1280" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1280" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1280">
+        <v>2</v>
+      </c>
+      <c r="F1280" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1280" t="s">
+        <v>141</v>
+      </c>
+      <c r="H1280" t="s">
+        <v>142</v>
+      </c>
+      <c r="I1280" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1280,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>PCP2.png</v>
+      </c>
+    </row>
+    <row r="1281" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1281" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1281" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1281" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1281" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1281">
+        <v>2</v>
+      </c>
+      <c r="F1281" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1281" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1281" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1281" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1281,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>H2OHP500.png</v>
+      </c>
+    </row>
+    <row r="1282" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1282" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1282" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1282" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1282" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1282">
+        <v>1</v>
+      </c>
+      <c r="F1282" t="s">
+        <v>106</v>
+      </c>
+      <c r="G1282" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1282" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1282" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1282,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BEATSLT.png</v>
+      </c>
+    </row>
+    <row r="1283" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1283" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1283" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1283" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1283" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1283">
+        <v>1</v>
+      </c>
+      <c r="F1283" t="s">
+        <v>106</v>
+      </c>
+      <c r="G1283" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1283" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1283" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1283,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BEATSLT.png</v>
+      </c>
+    </row>
+    <row r="1284" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1284" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1284" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1284" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1284" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1284">
+        <v>1</v>
+      </c>
+      <c r="F1284" t="s">
+        <v>106</v>
+      </c>
+      <c r="G1284" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1284" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1284" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1284,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BEATSLT.png</v>
+      </c>
+    </row>
+    <row r="1285" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1285" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1285" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1285" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1285" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1285">
+        <v>1</v>
+      </c>
+      <c r="F1285" t="s">
+        <v>106</v>
+      </c>
+      <c r="G1285" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1285" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1285" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1285,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BEATSLT.png</v>
+      </c>
+    </row>
+    <row r="1286" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1286" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1286" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1286" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1286" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1286">
+        <v>2</v>
+      </c>
+      <c r="F1286" t="s">
+        <v>107</v>
+      </c>
+      <c r="G1286" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1286" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1286" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1286,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BEATSLN.png</v>
+      </c>
+    </row>
+    <row r="1287" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1287" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1287" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1287" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1287" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1287">
+        <v>2</v>
+      </c>
+      <c r="F1287" t="s">
+        <v>107</v>
+      </c>
+      <c r="G1287" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1287" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1287" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1287,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BEATSLN.png</v>
+      </c>
+    </row>
+    <row r="1288" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1288" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1288" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1288" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1288" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1288">
+        <v>2</v>
+      </c>
+      <c r="F1288" t="s">
+        <v>107</v>
+      </c>
+      <c r="G1288" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1288" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1288" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1288,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BEATSLN.png</v>
+      </c>
+    </row>
+    <row r="1289" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1289" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1289" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1289" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1289" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1289">
+        <v>2</v>
+      </c>
+      <c r="F1289" t="s">
+        <v>107</v>
+      </c>
+      <c r="G1289" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1289" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1289" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1289,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BEATSLN.png</v>
+      </c>
+    </row>
+    <row r="1290" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1290" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1290" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1290" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1290" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1290">
+        <v>1</v>
+      </c>
+      <c r="F1290" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1290" t="s">
+        <v>146</v>
+      </c>
+      <c r="H1290" t="s">
+        <v>147</v>
+      </c>
+      <c r="I1290" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1290,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BEATSFF.png</v>
+      </c>
+    </row>
+    <row r="1291" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1291" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1291" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1291" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1291" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1291">
+        <v>1</v>
+      </c>
+      <c r="F1291" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1291" t="s">
+        <v>146</v>
+      </c>
+      <c r="H1291" t="s">
+        <v>147</v>
+      </c>
+      <c r="I1291" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1291,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BEATSFF.png</v>
+      </c>
+    </row>
+    <row r="1292" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1292" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1292" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1292" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1292" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1292">
+        <v>1</v>
+      </c>
+      <c r="F1292" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1292" t="s">
+        <v>146</v>
+      </c>
+      <c r="H1292" t="s">
+        <v>147</v>
+      </c>
+      <c r="I1292" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1292,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BEATSFF.png</v>
+      </c>
+    </row>
+    <row r="1293" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1293" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1293" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1293" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1293" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1293">
+        <v>1</v>
+      </c>
+      <c r="F1293" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1293" t="s">
+        <v>146</v>
+      </c>
+      <c r="H1293" t="s">
+        <v>147</v>
+      </c>
+      <c r="I1293" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1293,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BEATSFF.png</v>
+      </c>
+    </row>
+    <row r="1294" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1294" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1294" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1294" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1294" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1294">
+        <v>2</v>
+      </c>
+      <c r="F1294" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1294" t="s">
+        <v>146</v>
+      </c>
+      <c r="H1294" t="s">
+        <v>147</v>
+      </c>
+      <c r="I1294" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1294,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BEATSFF.png</v>
+      </c>
+    </row>
+    <row r="1295" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1295" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1295" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1295" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1295" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1295">
+        <v>2</v>
+      </c>
+      <c r="F1295" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1295" t="s">
+        <v>146</v>
+      </c>
+      <c r="H1295" t="s">
+        <v>147</v>
+      </c>
+      <c r="I1295" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1295,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BEATSFF.png</v>
+      </c>
+    </row>
+    <row r="1296" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1296" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1296" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1296" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1296" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1296">
+        <v>2</v>
+      </c>
+      <c r="F1296" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1296" t="s">
+        <v>146</v>
+      </c>
+      <c r="H1296" t="s">
+        <v>147</v>
+      </c>
+      <c r="I1296" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1296,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BEATSFF.png</v>
+      </c>
+    </row>
+    <row r="1297" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1297" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1297" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1297" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1297" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1297">
+        <v>2</v>
+      </c>
+      <c r="F1297" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1297" t="s">
+        <v>146</v>
+      </c>
+      <c r="H1297" t="s">
+        <v>147</v>
+      </c>
+      <c r="I1297" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1297,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BEATSFF.png</v>
+      </c>
+    </row>
+    <row r="1298" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1298" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1298" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1298" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1298" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1298">
+        <v>1</v>
+      </c>
+      <c r="F1298" t="s">
+        <v>106</v>
+      </c>
+      <c r="G1298" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1298" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1298" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1298,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BEATSLT.png</v>
+      </c>
+    </row>
+    <row r="1299" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1299" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1299" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1299" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1299" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1299">
+        <v>1</v>
+      </c>
+      <c r="F1299" t="s">
+        <v>106</v>
+      </c>
+      <c r="G1299" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1299" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1299" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1299,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BEATSLT.png</v>
+      </c>
+    </row>
+    <row r="1300" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1300" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1300" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1300" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1300" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1300">
+        <v>2</v>
+      </c>
+      <c r="F1300" t="s">
+        <v>107</v>
+      </c>
+      <c r="G1300" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1300" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1300" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1300,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BEATSLN.png</v>
+      </c>
+    </row>
+    <row r="1301" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1301" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1301" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1301" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1301" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1301">
+        <v>2</v>
+      </c>
+      <c r="F1301" t="s">
+        <v>107</v>
+      </c>
+      <c r="G1301" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1301" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1301" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1301,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BEATSLN.png</v>
+      </c>
+    </row>
+    <row r="1302" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1302" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1302" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1302" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1302" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1302">
+        <v>1</v>
+      </c>
+      <c r="F1302" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1302" t="s">
+        <v>146</v>
+      </c>
+      <c r="H1302" t="s">
+        <v>147</v>
+      </c>
+      <c r="I1302" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1302,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BEATSFF.png</v>
+      </c>
+    </row>
+    <row r="1303" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1303" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1303" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1303" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1303" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1303">
+        <v>1</v>
+      </c>
+      <c r="F1303" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1303" t="s">
+        <v>146</v>
+      </c>
+      <c r="H1303" t="s">
+        <v>147</v>
+      </c>
+      <c r="I1303" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1303,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BEATSFF.png</v>
+      </c>
+    </row>
+    <row r="1304" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1304" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1304" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1304" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1304" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1304">
+        <v>2</v>
+      </c>
+      <c r="F1304" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1304" t="s">
+        <v>146</v>
+      </c>
+      <c r="H1304" t="s">
+        <v>147</v>
+      </c>
+      <c r="I1304" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1304,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BEATSFF.png</v>
+      </c>
+    </row>
+    <row r="1305" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1305" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1305" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1305" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1305" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1305">
+        <v>2</v>
+      </c>
+      <c r="F1305" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1305" t="s">
+        <v>146</v>
+      </c>
+      <c r="H1305" t="s">
+        <v>147</v>
+      </c>
+      <c r="I1305" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1305,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BEATSFF.png</v>
+      </c>
+    </row>
+    <row r="1306" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1306" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1306" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1306" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1306" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1306">
+        <v>1</v>
+      </c>
+      <c r="F1306" t="s">
+        <v>38</v>
+      </c>
+      <c r="G1306" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1306" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1306" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1306,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>GCA350.png</v>
+      </c>
+    </row>
+    <row r="1307" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1307" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1307" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1307" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1307" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1307">
+        <v>1</v>
+      </c>
+      <c r="F1307" t="s">
+        <v>143</v>
+      </c>
+      <c r="G1307" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1307" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1307" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1307,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>PCSAB350.png</v>
+      </c>
+    </row>
+    <row r="1308" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1308" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1308" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1308" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1308" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1308">
+        <v>1</v>
+      </c>
+      <c r="F1308" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1308" t="s">
+        <v>141</v>
+      </c>
+      <c r="H1308" t="s">
+        <v>142</v>
+      </c>
+      <c r="I1308" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1308,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>GCAP2.png</v>
+      </c>
+    </row>
+    <row r="1309" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1309" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1309" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1309" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1309" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1309">
+        <v>2</v>
+      </c>
+      <c r="F1309" t="s">
+        <v>144</v>
+      </c>
+      <c r="G1309" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1309" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1309" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1309,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>GATORADE.png</v>
+      </c>
+    </row>
+    <row r="1310" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1310" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1310" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1310" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1310" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1310">
+        <v>2</v>
+      </c>
+      <c r="F1310" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1310" t="s">
+        <v>141</v>
+      </c>
+      <c r="H1310" t="s">
+        <v>142</v>
+      </c>
+      <c r="I1310" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1310,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>PCP2.png</v>
+      </c>
+    </row>
+    <row r="1311" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1311" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1311" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1311" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1311" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1311">
+        <v>2</v>
+      </c>
+      <c r="F1311" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1311" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1311" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1311" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1311,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>H2OHP500.png</v>
+      </c>
+    </row>
+    <row r="1312" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1312" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1312" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1312" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1312" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1312">
+        <v>1</v>
+      </c>
+      <c r="F1312" t="s">
+        <v>38</v>
+      </c>
+      <c r="G1312" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1312" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1312" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1312,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>GCA350.png</v>
+      </c>
+    </row>
+    <row r="1313" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1313" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1313" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1313" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1313" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1313">
+        <v>1</v>
+      </c>
+      <c r="F1313" t="s">
+        <v>143</v>
+      </c>
+      <c r="G1313" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1313" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1313" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1313,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>PCSAB350.png</v>
+      </c>
+    </row>
+    <row r="1314" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1314" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1314" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1314" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1314" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1314">
+        <v>1</v>
+      </c>
+      <c r="F1314" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1314" t="s">
+        <v>141</v>
+      </c>
+      <c r="H1314" t="s">
+        <v>142</v>
+      </c>
+      <c r="I1314" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1314,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>GCAP2.png</v>
+      </c>
+    </row>
+    <row r="1315" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1315" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1315" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1315" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1315" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1315">
+        <v>2</v>
+      </c>
+      <c r="F1315" t="s">
+        <v>144</v>
+      </c>
+      <c r="G1315" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1315" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1315" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1315,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>GATORADE.png</v>
+      </c>
+    </row>
+    <row r="1316" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1316" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1316" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1316" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1316" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1316">
+        <v>2</v>
+      </c>
+      <c r="F1316" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1316" t="s">
+        <v>141</v>
+      </c>
+      <c r="H1316" t="s">
+        <v>142</v>
+      </c>
+      <c r="I1316" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1316,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>PCP2.png</v>
+      </c>
+    </row>
+    <row r="1317" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1317" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1317" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1317" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1317" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1317">
+        <v>2</v>
+      </c>
+      <c r="F1317" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1317" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1317" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1317" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1317,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>H2OHP500.png</v>
+      </c>
+    </row>
+    <row r="1318" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1318" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1318" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1318" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1318" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1318">
+        <v>2</v>
+      </c>
+      <c r="F1318" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1318" t="s">
+        <v>134</v>
+      </c>
+      <c r="H1318" t="s">
+        <v>135</v>
+      </c>
+      <c r="I1318" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="1319" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1319" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1319" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1319" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1319" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1319">
+        <v>2</v>
+      </c>
+      <c r="F1319" t="s">
+        <v>86</v>
+      </c>
+      <c r="G1319" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1319" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1319" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="1320" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1320" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1320" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1320" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1320" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1320">
+        <v>2</v>
+      </c>
+      <c r="F1320" t="s">
+        <v>84</v>
+      </c>
+      <c r="G1320" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1320" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1320" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="1321" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1321" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1321" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1321" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1321" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1321">
+        <v>2</v>
+      </c>
+      <c r="F1321" t="s">
+        <v>78</v>
+      </c>
+      <c r="G1321" t="s">
+        <v>138</v>
+      </c>
+      <c r="H1321" t="s">
+        <v>139</v>
+      </c>
+      <c r="I1321" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="1322" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1322" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1322" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1322" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1322" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1322">
+        <v>2</v>
+      </c>
+      <c r="F1322" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1322" t="s">
+        <v>134</v>
+      </c>
+      <c r="H1322" t="s">
+        <v>135</v>
+      </c>
+      <c r="I1322" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="1323" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1323" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1323" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1323" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1323" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1323">
+        <v>2</v>
+      </c>
+      <c r="F1323" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1323" t="s">
+        <v>134</v>
+      </c>
+      <c r="H1323" t="s">
+        <v>135</v>
+      </c>
+      <c r="I1323" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="1324" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1324" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1324" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1324" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1324" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1324">
+        <v>2</v>
+      </c>
+      <c r="F1324" t="s">
+        <v>86</v>
+      </c>
+      <c r="G1324" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1324" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1324" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="1325" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1325" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1325" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1325" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1325" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1325">
+        <v>2</v>
+      </c>
+      <c r="F1325" t="s">
+        <v>84</v>
+      </c>
+      <c r="G1325" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1325" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1325" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="1326" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1326" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1326" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1326" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1326" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1326">
+        <v>2</v>
+      </c>
+      <c r="F1326" t="s">
+        <v>78</v>
+      </c>
+      <c r="G1326" t="s">
+        <v>138</v>
+      </c>
+      <c r="H1326" t="s">
+        <v>139</v>
+      </c>
+      <c r="I1326" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="1327" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1327" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1327" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1327" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1327" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1327">
+        <v>2</v>
+      </c>
+      <c r="F1327" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1327" t="s">
+        <v>134</v>
+      </c>
+      <c r="H1327" t="s">
+        <v>135</v>
+      </c>
+      <c r="I1327" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="1328" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1328" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1328" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1328" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1328" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1328" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1328" t="s">
+        <v>83</v>
+      </c>
+      <c r="G1328" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1328" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1328" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1328,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>MICLN.png</v>
+      </c>
+    </row>
+    <row r="1329" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1329" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1329" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1329" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1329" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1329" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1329" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1329" t="s">
+        <v>134</v>
+      </c>
+      <c r="H1329" t="s">
+        <v>135</v>
+      </c>
+      <c r="I1329" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1329,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>AP269.png</v>
+      </c>
+    </row>
+    <row r="1330" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1330" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1330" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1330" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1330" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1330" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1330" t="s">
+        <v>80</v>
+      </c>
+      <c r="G1330" t="s">
+        <v>136</v>
+      </c>
+      <c r="H1330" t="s">
+        <v>137</v>
+      </c>
+      <c r="I1330" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1330,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>CORCERO350.png</v>
+      </c>
+    </row>
+    <row r="1331" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1331" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1331" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1331" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1331" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1331" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1331" t="s">
+        <v>84</v>
+      </c>
+      <c r="G1331" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1331" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1331" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1331,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>STELN.png</v>
+      </c>
+    </row>
+    <row r="1332" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1332" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1332" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1332" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1332" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1332" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1332" t="s">
+        <v>72</v>
+      </c>
+      <c r="G1332" t="s">
+        <v>134</v>
+      </c>
+      <c r="H1332" t="s">
+        <v>156</v>
+      </c>
+      <c r="I1332" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1332,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>ORI269.png</v>
+      </c>
+    </row>
+    <row r="1333" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1333" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1333" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1333" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1333" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1333">
+        <v>1</v>
+      </c>
+      <c r="F1333" t="s">
+        <v>66</v>
+      </c>
+      <c r="G1333" t="s">
+        <v>134</v>
+      </c>
+      <c r="H1333" t="s">
+        <v>135</v>
+      </c>
+      <c r="I1333" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1333,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>SK269.png</v>
+      </c>
+    </row>
+    <row r="1334" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1334" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1334" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1334" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1334" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1334">
+        <v>1</v>
+      </c>
+      <c r="F1334" t="s">
+        <v>83</v>
+      </c>
+      <c r="G1334" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1334" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1334" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1334,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>MICLN.png</v>
+      </c>
+    </row>
+    <row r="1335" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1335" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1335" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1335" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1335" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1335">
+        <v>1</v>
+      </c>
+      <c r="F1335" t="s">
+        <v>80</v>
+      </c>
+      <c r="G1335" t="s">
+        <v>136</v>
+      </c>
+      <c r="H1335" t="s">
+        <v>137</v>
+      </c>
+      <c r="I1335" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1335,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>CORCERO350.png</v>
+      </c>
+    </row>
+    <row r="1336" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1336" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1336" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1336" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1336" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1336">
+        <v>1</v>
+      </c>
+      <c r="F1336" t="s">
+        <v>84</v>
+      </c>
+      <c r="G1336" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1336" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1336" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1336,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>STELN.png</v>
+      </c>
+    </row>
+    <row r="1337" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1337" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1337" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1337" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1337" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1337" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1337" t="s">
+        <v>72</v>
+      </c>
+      <c r="G1337" t="s">
+        <v>134</v>
+      </c>
+      <c r="H1337" t="s">
+        <v>156</v>
+      </c>
+      <c r="I1337" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1337,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>ORI269.png</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1220" xr:uid="{34B2C8DF-4561-40B2-8E7C-6CD69559B9AE}"/>
+  <autoFilter ref="A1:I1327" xr:uid="{34B2C8DF-4561-40B2-8E7C-6CD69559B9AE}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>

--- a/data/calendario_promocional.xlsx
+++ b/data/calendario_promocional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anheuserbuschinbev-my.sharepoint.com/personal/99823517_ab-inbev_com/Documents/001. Projetos/Streamlit Calendario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="398" documentId="13_ncr:1_{B92F5DA4-8825-4FA1-97C6-23568D76854D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16AF9812-B7A1-466C-B370-66E68547DB2D}"/>
+  <xr:revisionPtr revIDLastSave="447" documentId="13_ncr:1_{B92F5DA4-8825-4FA1-97C6-23568D76854D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69902979-EDBB-476C-886E-9CB7EB8051C0}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,10 +23,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">CALENDARIO!$A$1:$C$414</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DeparaIMG!$A$1:$D$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">MECANICA!$A$1:$D$49</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">PRODUTOS!$A$1:$I$1327</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">PRODUTOS!$A$1:$I$1220</definedName>
   </definedNames>
   <calcPr calcId="191029" calcMode="manual"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -47,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8174" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8281" uniqueCount="157">
   <si>
     <t>Data</t>
   </si>
@@ -502,22 +501,22 @@
     <t>FORT MT/MS</t>
   </si>
   <si>
-    <t>BC269.png</t>
+    <t>Pague:13</t>
   </si>
   <si>
-    <t>CORCEROLN.png</t>
+    <t>Leve 2 Beats</t>
   </si>
   <si>
-    <t>STELN.png</t>
+    <t>Leve 1 FF</t>
   </si>
   <si>
-    <t>MIC350.png</t>
+    <t>cerv</t>
   </si>
   <si>
-    <t>BUD269.png</t>
+    <t>nab</t>
   </si>
   <si>
-    <t>Pague:13</t>
+    <t>match</t>
   </si>
 </sst>
 </file>
@@ -1694,7 +1693,7 @@
         <v>143</v>
       </c>
       <c r="C53" t="str">
-        <f t="shared" ref="C53:C55" si="5">SUBSTITUTE(B53," ","")</f>
+        <f t="shared" ref="C53:C54" si="5">SUBSTITUTE(B53," ","")</f>
         <v>PCSAB350</v>
       </c>
       <c r="D53" t="str">
@@ -44026,17 +44025,16 @@
         <v>1</v>
       </c>
       <c r="F1221" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="G1221" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H1221" t="s">
-        <v>133</v>
-      </c>
-      <c r="I1221" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1221,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>MICLN.png</v>
+        <v>135</v>
+      </c>
+      <c r="I1221" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1222" spans="1:9" x14ac:dyDescent="0.25">
@@ -44047,12 +44045,12 @@
         <v>127</v>
       </c>
       <c r="C1222" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D1222" t="s">
         <v>131</v>
       </c>
-      <c r="E1222" s="2">
+      <c r="E1222">
         <v>1</v>
       </c>
       <c r="F1222" t="s">
@@ -44064,9 +44062,8 @@
       <c r="H1222" t="s">
         <v>135</v>
       </c>
-      <c r="I1222" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1222,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>AP269.png</v>
+      <c r="I1222" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1223" spans="1:9" x14ac:dyDescent="0.25">
@@ -44077,26 +44074,25 @@
         <v>127</v>
       </c>
       <c r="C1223" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="D1223" t="s">
         <v>131</v>
       </c>
-      <c r="E1223" s="2">
-        <v>1</v>
+      <c r="E1223">
+        <v>2</v>
       </c>
       <c r="F1223" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="G1223" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H1223" t="s">
-        <v>137</v>
-      </c>
-      <c r="I1223" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1223,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>CORCERO350.png</v>
+        <v>135</v>
+      </c>
+      <c r="I1223" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1224" spans="1:9" x14ac:dyDescent="0.25">
@@ -44107,7 +44103,7 @@
         <v>127</v>
       </c>
       <c r="C1224" t="s">
-        <v>28</v>
+        <v>149</v>
       </c>
       <c r="D1224" t="s">
         <v>131</v>
@@ -44116,17 +44112,16 @@
         <v>1</v>
       </c>
       <c r="F1224" t="s">
-        <v>140</v>
+        <v>67</v>
       </c>
       <c r="G1224" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H1224" t="s">
-        <v>133</v>
-      </c>
-      <c r="I1224" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1224,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>SPTLN.png</v>
+        <v>135</v>
+      </c>
+      <c r="I1224" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1225" spans="1:9" x14ac:dyDescent="0.25">
@@ -44137,16 +44132,16 @@
         <v>127</v>
       </c>
       <c r="C1225" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
       <c r="D1225" t="s">
         <v>131</v>
       </c>
       <c r="E1225">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1225" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G1225" t="s">
         <v>134</v>
@@ -44154,9 +44149,8 @@
       <c r="H1225" t="s">
         <v>135</v>
       </c>
-      <c r="I1225" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1225,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>BC269.png</v>
+      <c r="I1225" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1226" spans="1:9" x14ac:dyDescent="0.25">
@@ -44167,26 +44161,25 @@
         <v>127</v>
       </c>
       <c r="C1226" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="D1226" t="s">
         <v>131</v>
       </c>
       <c r="E1226">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1226" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="G1226" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H1226" t="s">
-        <v>133</v>
-      </c>
-      <c r="I1226" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1226,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>CORCEROLN.png</v>
+        <v>135</v>
+      </c>
+      <c r="I1226" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1227" spans="1:9" x14ac:dyDescent="0.25">
@@ -44197,26 +44190,25 @@
         <v>127</v>
       </c>
       <c r="C1227" t="s">
-        <v>28</v>
+        <v>150</v>
       </c>
       <c r="D1227" t="s">
         <v>131</v>
       </c>
       <c r="E1227">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1227" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="G1227" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H1227" t="s">
-        <v>133</v>
-      </c>
-      <c r="I1227" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1227,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>STELN.png</v>
+        <v>135</v>
+      </c>
+      <c r="I1227" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1228" spans="1:9" x14ac:dyDescent="0.25">
@@ -44236,17 +44228,16 @@
         <v>2</v>
       </c>
       <c r="F1228" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="G1228" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H1228" t="s">
-        <v>139</v>
-      </c>
-      <c r="I1228" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1228,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>MIC350.png</v>
+        <v>135</v>
+      </c>
+      <c r="I1228" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1229" spans="1:9" x14ac:dyDescent="0.25">
@@ -44257,7 +44248,7 @@
         <v>127</v>
       </c>
       <c r="C1229" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D1229" t="s">
         <v>131</v>
@@ -44266,7 +44257,7 @@
         <v>2</v>
       </c>
       <c r="F1229" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G1229" t="s">
         <v>134</v>
@@ -44274,9 +44265,8 @@
       <c r="H1229" t="s">
         <v>135</v>
       </c>
-      <c r="I1229" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1229,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>BUD269.png</v>
+      <c r="I1229" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1230" spans="1:9" x14ac:dyDescent="0.25">
@@ -44287,16 +44277,16 @@
         <v>127</v>
       </c>
       <c r="C1230" t="s">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="D1230" t="s">
         <v>131</v>
       </c>
       <c r="E1230">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1230" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G1230" t="s">
         <v>134</v>
@@ -44304,9 +44294,8 @@
       <c r="H1230" t="s">
         <v>135</v>
       </c>
-      <c r="I1230" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1230,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>AP269.png</v>
+      <c r="I1230" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1231" spans="1:9" x14ac:dyDescent="0.25">
@@ -44317,26 +44306,25 @@
         <v>127</v>
       </c>
       <c r="C1231" t="s">
-        <v>29</v>
+        <v>88</v>
       </c>
       <c r="D1231" t="s">
         <v>131</v>
       </c>
       <c r="E1231">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1231" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="G1231" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H1231" t="s">
-        <v>133</v>
-      </c>
-      <c r="I1231" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1231,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>MICLN.png</v>
+        <v>135</v>
+      </c>
+      <c r="I1231" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1232" spans="1:9" x14ac:dyDescent="0.25">
@@ -44347,26 +44335,25 @@
         <v>127</v>
       </c>
       <c r="C1232" t="s">
-        <v>29</v>
+        <v>149</v>
       </c>
       <c r="D1232" t="s">
         <v>131</v>
       </c>
       <c r="E1232">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1232" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="G1232" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H1232" t="s">
-        <v>137</v>
-      </c>
-      <c r="I1232" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1232,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>CORCERO350.png</v>
+        <v>135</v>
+      </c>
+      <c r="I1232" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1233" spans="1:9" x14ac:dyDescent="0.25">
@@ -44377,26 +44364,25 @@
         <v>127</v>
       </c>
       <c r="C1233" t="s">
-        <v>29</v>
+        <v>150</v>
       </c>
       <c r="D1233" t="s">
         <v>131</v>
       </c>
       <c r="E1233">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1233" t="s">
-        <v>140</v>
+        <v>68</v>
       </c>
       <c r="G1233" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H1233" t="s">
-        <v>133</v>
-      </c>
-      <c r="I1233" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1233,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>SPTLN.png</v>
+        <v>135</v>
+      </c>
+      <c r="I1233" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1234" spans="1:9" x14ac:dyDescent="0.25">
@@ -44407,7 +44393,7 @@
         <v>127</v>
       </c>
       <c r="C1234" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D1234" t="s">
         <v>131</v>
@@ -44416,7 +44402,7 @@
         <v>2</v>
       </c>
       <c r="F1234" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G1234" t="s">
         <v>134</v>
@@ -44424,9 +44410,8 @@
       <c r="H1234" t="s">
         <v>135</v>
       </c>
-      <c r="I1234" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1234,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>BC269.png</v>
+      <c r="I1234" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1235" spans="1:9" x14ac:dyDescent="0.25">
@@ -44446,17 +44431,16 @@
         <v>2</v>
       </c>
       <c r="F1235" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="G1235" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H1235" t="s">
-        <v>133</v>
-      </c>
-      <c r="I1235" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1235,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>CORCEROLN.png</v>
+        <v>135</v>
+      </c>
+      <c r="I1235" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1236" spans="1:9" x14ac:dyDescent="0.25">
@@ -44467,7 +44451,7 @@
         <v>127</v>
       </c>
       <c r="C1236" t="s">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="D1236" t="s">
         <v>131</v>
@@ -44476,17 +44460,16 @@
         <v>2</v>
       </c>
       <c r="F1236" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G1236" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H1236" t="s">
-        <v>133</v>
-      </c>
-      <c r="I1236" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1236,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>STELN.png</v>
+        <v>135</v>
+      </c>
+      <c r="I1236" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1237" spans="1:9" x14ac:dyDescent="0.25">
@@ -44497,7 +44480,7 @@
         <v>127</v>
       </c>
       <c r="C1237" t="s">
-        <v>29</v>
+        <v>88</v>
       </c>
       <c r="D1237" t="s">
         <v>131</v>
@@ -44506,17 +44489,16 @@
         <v>2</v>
       </c>
       <c r="F1237" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="G1237" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H1237" t="s">
-        <v>139</v>
-      </c>
-      <c r="I1237" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1237,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>MIC350.png</v>
+        <v>135</v>
+      </c>
+      <c r="I1237" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1238" spans="1:9" x14ac:dyDescent="0.25">
@@ -44527,7 +44509,7 @@
         <v>127</v>
       </c>
       <c r="C1238" t="s">
-        <v>29</v>
+        <v>149</v>
       </c>
       <c r="D1238" t="s">
         <v>131</v>
@@ -44544,9 +44526,8 @@
       <c r="H1238" t="s">
         <v>135</v>
       </c>
-      <c r="I1238" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1238,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>BUD269.png</v>
+      <c r="I1238" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1239" spans="1:9" x14ac:dyDescent="0.25">
@@ -44557,16 +44538,16 @@
         <v>127</v>
       </c>
       <c r="C1239" t="s">
-        <v>87</v>
+        <v>150</v>
       </c>
       <c r="D1239" t="s">
         <v>131</v>
       </c>
       <c r="E1239">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1239" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G1239" t="s">
         <v>134</v>
@@ -44574,9 +44555,8 @@
       <c r="H1239" t="s">
         <v>135</v>
       </c>
-      <c r="I1239" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1239,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>SK269.png</v>
+      <c r="I1239" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1240" spans="1:9" x14ac:dyDescent="0.25">
@@ -44587,26 +44567,25 @@
         <v>127</v>
       </c>
       <c r="C1240" t="s">
-        <v>87</v>
+        <v>149</v>
       </c>
       <c r="D1240" t="s">
         <v>131</v>
       </c>
-      <c r="E1240">
+      <c r="E1240" s="2">
         <v>1</v>
       </c>
       <c r="F1240" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="G1240" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H1240" t="s">
-        <v>133</v>
-      </c>
-      <c r="I1240" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1240,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>MICLN.png</v>
+        <v>151</v>
+      </c>
+      <c r="I1240" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1241" spans="1:9" x14ac:dyDescent="0.25">
@@ -44617,26 +44596,25 @@
         <v>127</v>
       </c>
       <c r="C1241" t="s">
-        <v>87</v>
+        <v>150</v>
       </c>
       <c r="D1241" t="s">
         <v>131</v>
       </c>
-      <c r="E1241">
+      <c r="E1241" s="2">
         <v>1</v>
       </c>
       <c r="F1241" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="G1241" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H1241" t="s">
-        <v>137</v>
-      </c>
-      <c r="I1241" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1241,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>CORCERO350.png</v>
+        <v>151</v>
+      </c>
+      <c r="I1241" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1242" spans="1:9" x14ac:dyDescent="0.25">
@@ -44647,26 +44625,25 @@
         <v>127</v>
       </c>
       <c r="C1242" t="s">
-        <v>87</v>
+        <v>28</v>
       </c>
       <c r="D1242" t="s">
         <v>131</v>
       </c>
       <c r="E1242">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1242" t="s">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="G1242" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="H1242" t="s">
-        <v>133</v>
-      </c>
-      <c r="I1242" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1242,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>SPTLN.png</v>
+        <v>139</v>
+      </c>
+      <c r="I1242" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1243" spans="1:9" x14ac:dyDescent="0.25">
@@ -44677,7 +44654,7 @@
         <v>127</v>
       </c>
       <c r="C1243" t="s">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="D1243" t="s">
         <v>131</v>
@@ -44686,17 +44663,16 @@
         <v>2</v>
       </c>
       <c r="F1243" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="G1243" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="H1243" t="s">
-        <v>135</v>
-      </c>
-      <c r="I1243" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1243,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>BC269.png</v>
+        <v>139</v>
+      </c>
+      <c r="I1243" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1244" spans="1:9" x14ac:dyDescent="0.25">
@@ -44716,17 +44692,16 @@
         <v>2</v>
       </c>
       <c r="F1244" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="G1244" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="H1244" t="s">
-        <v>133</v>
-      </c>
-      <c r="I1244" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1244,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>CORCEROLN.png</v>
+        <v>139</v>
+      </c>
+      <c r="I1244" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1245" spans="1:9" x14ac:dyDescent="0.25">
@@ -44737,7 +44712,7 @@
         <v>127</v>
       </c>
       <c r="C1245" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D1245" t="s">
         <v>131</v>
@@ -44746,17 +44721,16 @@
         <v>2</v>
       </c>
       <c r="F1245" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="G1245" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="H1245" t="s">
-        <v>133</v>
-      </c>
-      <c r="I1245" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1245,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>STELN.png</v>
+        <v>139</v>
+      </c>
+      <c r="I1245" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1246" spans="1:9" x14ac:dyDescent="0.25">
@@ -44767,7 +44741,7 @@
         <v>127</v>
       </c>
       <c r="C1246" t="s">
-        <v>87</v>
+        <v>149</v>
       </c>
       <c r="D1246" t="s">
         <v>131</v>
@@ -44784,9 +44758,8 @@
       <c r="H1246" t="s">
         <v>139</v>
       </c>
-      <c r="I1246" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1246,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>MIC350.png</v>
+      <c r="I1246" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1247" spans="1:9" x14ac:dyDescent="0.25">
@@ -44797,7 +44770,7 @@
         <v>127</v>
       </c>
       <c r="C1247" t="s">
-        <v>87</v>
+        <v>150</v>
       </c>
       <c r="D1247" t="s">
         <v>131</v>
@@ -44806,17 +44779,16 @@
         <v>2</v>
       </c>
       <c r="F1247" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="G1247" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="H1247" t="s">
-        <v>135</v>
-      </c>
-      <c r="I1247" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1247,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>BUD269.png</v>
+        <v>139</v>
+      </c>
+      <c r="I1247" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1248" spans="1:9" x14ac:dyDescent="0.25">
@@ -44827,26 +44799,25 @@
         <v>127</v>
       </c>
       <c r="C1248" t="s">
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="D1248" t="s">
         <v>131</v>
       </c>
-      <c r="E1248">
+      <c r="E1248" s="2">
         <v>1</v>
       </c>
       <c r="F1248" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="G1248" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H1248" t="s">
-        <v>135</v>
-      </c>
-      <c r="I1248" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1248,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>SK269.png</v>
+        <v>137</v>
+      </c>
+      <c r="I1248" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1249" spans="1:9" x14ac:dyDescent="0.25">
@@ -44857,26 +44828,25 @@
         <v>127</v>
       </c>
       <c r="C1249" t="s">
-        <v>88</v>
+        <v>29</v>
       </c>
       <c r="D1249" t="s">
         <v>131</v>
       </c>
       <c r="E1249">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1249" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="G1249" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H1249" t="s">
-        <v>135</v>
-      </c>
-      <c r="I1249" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1249,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>AP269.png</v>
+        <v>137</v>
+      </c>
+      <c r="I1249" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1250" spans="1:9" x14ac:dyDescent="0.25">
@@ -44887,7 +44857,7 @@
         <v>127</v>
       </c>
       <c r="C1250" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D1250" t="s">
         <v>131</v>
@@ -44896,17 +44866,16 @@
         <v>1</v>
       </c>
       <c r="F1250" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G1250" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H1250" t="s">
-        <v>133</v>
-      </c>
-      <c r="I1250" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1250,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>MICLN.png</v>
+        <v>137</v>
+      </c>
+      <c r="I1250" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1251" spans="1:9" x14ac:dyDescent="0.25">
@@ -44934,9 +44903,8 @@
       <c r="H1251" t="s">
         <v>137</v>
       </c>
-      <c r="I1251" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1251,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>CORCERO350.png</v>
+      <c r="I1251" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1252" spans="1:9" x14ac:dyDescent="0.25">
@@ -44947,26 +44915,25 @@
         <v>127</v>
       </c>
       <c r="C1252" t="s">
-        <v>88</v>
+        <v>149</v>
       </c>
       <c r="D1252" t="s">
         <v>131</v>
       </c>
-      <c r="E1252">
+      <c r="E1252" s="2">
         <v>1</v>
       </c>
       <c r="F1252" t="s">
-        <v>140</v>
+        <v>80</v>
       </c>
       <c r="G1252" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H1252" t="s">
-        <v>133</v>
-      </c>
-      <c r="I1252" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1252,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>SPTLN.png</v>
+        <v>137</v>
+      </c>
+      <c r="I1252" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1253" spans="1:9" x14ac:dyDescent="0.25">
@@ -44977,26 +44944,25 @@
         <v>127</v>
       </c>
       <c r="C1253" t="s">
-        <v>88</v>
+        <v>150</v>
       </c>
       <c r="D1253" t="s">
         <v>131</v>
       </c>
       <c r="E1253">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1253" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="G1253" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H1253" t="s">
-        <v>135</v>
-      </c>
-      <c r="I1253" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1253,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>BC269.png</v>
+        <v>137</v>
+      </c>
+      <c r="I1253" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1254" spans="1:9" x14ac:dyDescent="0.25">
@@ -45007,16 +44973,16 @@
         <v>127</v>
       </c>
       <c r="C1254" t="s">
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="D1254" t="s">
         <v>131</v>
       </c>
-      <c r="E1254">
-        <v>2</v>
+      <c r="E1254" s="2">
+        <v>1</v>
       </c>
       <c r="F1254" t="s">
-        <v>86</v>
+        <v>140</v>
       </c>
       <c r="G1254" t="s">
         <v>132</v>
@@ -45024,9 +44990,8 @@
       <c r="H1254" t="s">
         <v>133</v>
       </c>
-      <c r="I1254" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1254,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>CORCEROLN.png</v>
+      <c r="I1254" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1255" spans="1:9" x14ac:dyDescent="0.25">
@@ -45037,16 +45002,16 @@
         <v>127</v>
       </c>
       <c r="C1255" t="s">
-        <v>88</v>
+        <v>29</v>
       </c>
       <c r="D1255" t="s">
         <v>131</v>
       </c>
       <c r="E1255">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1255" t="s">
-        <v>84</v>
+        <v>140</v>
       </c>
       <c r="G1255" t="s">
         <v>132</v>
@@ -45054,9 +45019,8 @@
       <c r="H1255" t="s">
         <v>133</v>
       </c>
-      <c r="I1255" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1255,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>STELN.png</v>
+      <c r="I1255" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1256" spans="1:9" x14ac:dyDescent="0.25">
@@ -45067,26 +45031,25 @@
         <v>127</v>
       </c>
       <c r="C1256" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D1256" t="s">
         <v>131</v>
       </c>
       <c r="E1256">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1256" t="s">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="G1256" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="H1256" t="s">
-        <v>139</v>
-      </c>
-      <c r="I1256" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1256,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>MIC350.png</v>
+        <v>133</v>
+      </c>
+      <c r="I1256" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1257" spans="1:9" x14ac:dyDescent="0.25">
@@ -45103,20 +45066,19 @@
         <v>131</v>
       </c>
       <c r="E1257">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1257" t="s">
-        <v>69</v>
+        <v>140</v>
       </c>
       <c r="G1257" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="H1257" t="s">
-        <v>135</v>
-      </c>
-      <c r="I1257" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1257,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>BUD269.png</v>
+        <v>133</v>
+      </c>
+      <c r="I1257" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1258" spans="1:9" x14ac:dyDescent="0.25">
@@ -45133,10 +45095,10 @@
         <v>131</v>
       </c>
       <c r="E1258">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1258" t="s">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="G1258" t="s">
         <v>132</v>
@@ -45144,9 +45106,8 @@
       <c r="H1258" t="s">
         <v>133</v>
       </c>
-      <c r="I1258" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1258,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>GCA350.png</v>
+      <c r="I1258" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1259" spans="1:9" x14ac:dyDescent="0.25">
@@ -45157,16 +45118,16 @@
         <v>127</v>
       </c>
       <c r="C1259" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D1259" t="s">
         <v>131</v>
       </c>
       <c r="E1259">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1259" t="s">
-        <v>143</v>
+        <v>84</v>
       </c>
       <c r="G1259" t="s">
         <v>132</v>
@@ -45174,9 +45135,8 @@
       <c r="H1259" t="s">
         <v>133</v>
       </c>
-      <c r="I1259" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1259,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>PCSAB350.png</v>
+      <c r="I1259" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1260" spans="1:9" x14ac:dyDescent="0.25">
@@ -45187,26 +45147,25 @@
         <v>127</v>
       </c>
       <c r="C1260" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
       <c r="D1260" t="s">
         <v>131</v>
       </c>
       <c r="E1260">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1260" t="s">
-        <v>37</v>
+        <v>84</v>
       </c>
       <c r="G1260" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="H1260" t="s">
-        <v>142</v>
-      </c>
-      <c r="I1260" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1260,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>GCAP2.png</v>
+        <v>133</v>
+      </c>
+      <c r="I1260" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1261" spans="1:9" x14ac:dyDescent="0.25">
@@ -45217,7 +45176,7 @@
         <v>127</v>
       </c>
       <c r="C1261" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="D1261" t="s">
         <v>131</v>
@@ -45226,7 +45185,7 @@
         <v>2</v>
       </c>
       <c r="F1261" t="s">
-        <v>144</v>
+        <v>84</v>
       </c>
       <c r="G1261" t="s">
         <v>132</v>
@@ -45234,9 +45193,8 @@
       <c r="H1261" t="s">
         <v>133</v>
       </c>
-      <c r="I1261" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1261,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>GATORADE.png</v>
+      <c r="I1261" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1262" spans="1:9" x14ac:dyDescent="0.25">
@@ -45247,7 +45205,7 @@
         <v>127</v>
       </c>
       <c r="C1262" t="s">
-        <v>28</v>
+        <v>149</v>
       </c>
       <c r="D1262" t="s">
         <v>131</v>
@@ -45256,17 +45214,16 @@
         <v>2</v>
       </c>
       <c r="F1262" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
       <c r="G1262" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="H1262" t="s">
-        <v>142</v>
-      </c>
-      <c r="I1262" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1262,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>PCP2.png</v>
+        <v>133</v>
+      </c>
+      <c r="I1262" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1263" spans="1:9" x14ac:dyDescent="0.25">
@@ -45277,7 +45234,7 @@
         <v>127</v>
       </c>
       <c r="C1263" t="s">
-        <v>28</v>
+        <v>150</v>
       </c>
       <c r="D1263" t="s">
         <v>131</v>
@@ -45286,7 +45243,7 @@
         <v>2</v>
       </c>
       <c r="F1263" t="s">
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="G1263" t="s">
         <v>132</v>
@@ -45294,9 +45251,8 @@
       <c r="H1263" t="s">
         <v>133</v>
       </c>
-      <c r="I1263" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1263,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>H2OHP500.png</v>
+      <c r="I1263" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1264" spans="1:9" x14ac:dyDescent="0.25">
@@ -45307,16 +45263,16 @@
         <v>127</v>
       </c>
       <c r="C1264" t="s">
-        <v>29</v>
+        <v>149</v>
       </c>
       <c r="D1264" t="s">
         <v>131</v>
       </c>
-      <c r="E1264">
+      <c r="E1264" s="2">
         <v>1</v>
       </c>
       <c r="F1264" t="s">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="G1264" t="s">
         <v>132</v>
@@ -45324,9 +45280,8 @@
       <c r="H1264" t="s">
         <v>133</v>
       </c>
-      <c r="I1264" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1264,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>GCA350.png</v>
+      <c r="I1264" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1265" spans="1:9" x14ac:dyDescent="0.25">
@@ -45337,7 +45292,7 @@
         <v>127</v>
       </c>
       <c r="C1265" t="s">
-        <v>29</v>
+        <v>150</v>
       </c>
       <c r="D1265" t="s">
         <v>131</v>
@@ -45346,7 +45301,7 @@
         <v>1</v>
       </c>
       <c r="F1265" t="s">
-        <v>143</v>
+        <v>84</v>
       </c>
       <c r="G1265" t="s">
         <v>132</v>
@@ -45354,9 +45309,8 @@
       <c r="H1265" t="s">
         <v>133</v>
       </c>
-      <c r="I1265" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1265,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>PCSAB350.png</v>
+      <c r="I1265" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1266" spans="1:9" x14ac:dyDescent="0.25">
@@ -45367,26 +45321,25 @@
         <v>127</v>
       </c>
       <c r="C1266" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D1266" t="s">
         <v>131</v>
       </c>
-      <c r="E1266">
+      <c r="E1266" s="2">
         <v>1</v>
       </c>
       <c r="F1266" t="s">
-        <v>37</v>
+        <v>83</v>
       </c>
       <c r="G1266" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="H1266" t="s">
-        <v>142</v>
-      </c>
-      <c r="I1266" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1266,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>GCAP2.png</v>
+        <v>133</v>
+      </c>
+      <c r="I1266" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1267" spans="1:9" x14ac:dyDescent="0.25">
@@ -45403,10 +45356,10 @@
         <v>131</v>
       </c>
       <c r="E1267">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1267" t="s">
-        <v>144</v>
+        <v>83</v>
       </c>
       <c r="G1267" t="s">
         <v>132</v>
@@ -45414,9 +45367,8 @@
       <c r="H1267" t="s">
         <v>133</v>
       </c>
-      <c r="I1267" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1267,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>GATORADE.png</v>
+      <c r="I1267" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1268" spans="1:9" x14ac:dyDescent="0.25">
@@ -45427,26 +45379,25 @@
         <v>127</v>
       </c>
       <c r="C1268" t="s">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="D1268" t="s">
         <v>131</v>
       </c>
       <c r="E1268">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1268" t="s">
-        <v>33</v>
+        <v>83</v>
       </c>
       <c r="G1268" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="H1268" t="s">
-        <v>142</v>
-      </c>
-      <c r="I1268" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1268,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>PCP2.png</v>
+        <v>133</v>
+      </c>
+      <c r="I1268" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1269" spans="1:9" x14ac:dyDescent="0.25">
@@ -45457,16 +45408,16 @@
         <v>127</v>
       </c>
       <c r="C1269" t="s">
-        <v>29</v>
+        <v>88</v>
       </c>
       <c r="D1269" t="s">
         <v>131</v>
       </c>
       <c r="E1269">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1269" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="G1269" t="s">
         <v>132</v>
@@ -45474,9 +45425,8 @@
       <c r="H1269" t="s">
         <v>133</v>
       </c>
-      <c r="I1269" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1269,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>H2OHP500.png</v>
+      <c r="I1269" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1270" spans="1:9" x14ac:dyDescent="0.25">
@@ -45487,16 +45437,16 @@
         <v>127</v>
       </c>
       <c r="C1270" t="s">
-        <v>87</v>
+        <v>149</v>
       </c>
       <c r="D1270" t="s">
         <v>131</v>
       </c>
-      <c r="E1270">
+      <c r="E1270" s="2">
         <v>1</v>
       </c>
       <c r="F1270" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
       <c r="G1270" t="s">
         <v>132</v>
@@ -45504,9 +45454,8 @@
       <c r="H1270" t="s">
         <v>133</v>
       </c>
-      <c r="I1270" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1270,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>GCA350.png</v>
+      <c r="I1270" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1271" spans="1:9" x14ac:dyDescent="0.25">
@@ -45517,7 +45466,7 @@
         <v>127</v>
       </c>
       <c r="C1271" t="s">
-        <v>87</v>
+        <v>150</v>
       </c>
       <c r="D1271" t="s">
         <v>131</v>
@@ -45526,7 +45475,7 @@
         <v>1</v>
       </c>
       <c r="F1271" t="s">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="G1271" t="s">
         <v>132</v>
@@ -45534,9 +45483,8 @@
       <c r="H1271" t="s">
         <v>133</v>
       </c>
-      <c r="I1271" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1271,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>PCSAB350.png</v>
+      <c r="I1271" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1272" spans="1:9" x14ac:dyDescent="0.25">
@@ -45547,26 +45495,25 @@
         <v>127</v>
       </c>
       <c r="C1272" t="s">
-        <v>87</v>
+        <v>28</v>
       </c>
       <c r="D1272" t="s">
         <v>131</v>
       </c>
       <c r="E1272">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1272" t="s">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="G1272" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="H1272" t="s">
-        <v>142</v>
-      </c>
-      <c r="I1272" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1272,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>GCAP2.png</v>
+        <v>133</v>
+      </c>
+      <c r="I1272" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1273" spans="1:9" x14ac:dyDescent="0.25">
@@ -45577,7 +45524,7 @@
         <v>127</v>
       </c>
       <c r="C1273" t="s">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="D1273" t="s">
         <v>131</v>
@@ -45586,7 +45533,7 @@
         <v>2</v>
       </c>
       <c r="F1273" t="s">
-        <v>144</v>
+        <v>86</v>
       </c>
       <c r="G1273" t="s">
         <v>132</v>
@@ -45594,9 +45541,8 @@
       <c r="H1273" t="s">
         <v>133</v>
       </c>
-      <c r="I1273" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1273,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>GATORADE.png</v>
+      <c r="I1273" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1274" spans="1:9" x14ac:dyDescent="0.25">
@@ -45616,17 +45562,16 @@
         <v>2</v>
       </c>
       <c r="F1274" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="G1274" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="H1274" t="s">
-        <v>142</v>
-      </c>
-      <c r="I1274" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1274,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>PCP2.png</v>
+        <v>133</v>
+      </c>
+      <c r="I1274" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1275" spans="1:9" x14ac:dyDescent="0.25">
@@ -45637,7 +45582,7 @@
         <v>127</v>
       </c>
       <c r="C1275" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D1275" t="s">
         <v>131</v>
@@ -45646,7 +45591,7 @@
         <v>2</v>
       </c>
       <c r="F1275" t="s">
-        <v>35</v>
+        <v>86</v>
       </c>
       <c r="G1275" t="s">
         <v>132</v>
@@ -45654,9 +45599,8 @@
       <c r="H1275" t="s">
         <v>133</v>
       </c>
-      <c r="I1275" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1275,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>H2OHP500.png</v>
+      <c r="I1275" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1276" spans="1:9" x14ac:dyDescent="0.25">
@@ -45667,16 +45611,16 @@
         <v>127</v>
       </c>
       <c r="C1276" t="s">
-        <v>88</v>
+        <v>149</v>
       </c>
       <c r="D1276" t="s">
         <v>131</v>
       </c>
       <c r="E1276">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1276" t="s">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="G1276" t="s">
         <v>132</v>
@@ -45684,9 +45628,8 @@
       <c r="H1276" t="s">
         <v>133</v>
       </c>
-      <c r="I1276" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1276,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>GCA350.png</v>
+      <c r="I1276" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1277" spans="1:9" x14ac:dyDescent="0.25">
@@ -45697,16 +45640,16 @@
         <v>127</v>
       </c>
       <c r="C1277" t="s">
-        <v>88</v>
+        <v>150</v>
       </c>
       <c r="D1277" t="s">
         <v>131</v>
       </c>
       <c r="E1277">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1277" t="s">
-        <v>143</v>
+        <v>86</v>
       </c>
       <c r="G1277" t="s">
         <v>132</v>
@@ -45714,9 +45657,8 @@
       <c r="H1277" t="s">
         <v>133</v>
       </c>
-      <c r="I1277" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1277,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>PCSAB350.png</v>
+      <c r="I1277" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="1278" spans="1:9" x14ac:dyDescent="0.25">
@@ -45727,7 +45669,7 @@
         <v>127</v>
       </c>
       <c r="C1278" t="s">
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="D1278" t="s">
         <v>131</v>
@@ -45736,17 +45678,16 @@
         <v>1</v>
       </c>
       <c r="F1278" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G1278" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="H1278" t="s">
-        <v>142</v>
-      </c>
-      <c r="I1278" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1278,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>GCAP2.png</v>
+        <v>133</v>
+      </c>
+      <c r="I1278" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="1279" spans="1:9" x14ac:dyDescent="0.25">
@@ -45757,16 +45698,16 @@
         <v>127</v>
       </c>
       <c r="C1279" t="s">
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="D1279" t="s">
         <v>131</v>
       </c>
       <c r="E1279">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1279" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G1279" t="s">
         <v>132</v>
@@ -45774,9 +45715,8 @@
       <c r="H1279" t="s">
         <v>133</v>
       </c>
-      <c r="I1279" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1279,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>GATORADE.png</v>
+      <c r="I1279" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="1280" spans="1:9" x14ac:dyDescent="0.25">
@@ -45787,16 +45727,16 @@
         <v>127</v>
       </c>
       <c r="C1280" t="s">
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="D1280" t="s">
         <v>131</v>
       </c>
       <c r="E1280">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1280" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G1280" t="s">
         <v>141</v>
@@ -45804,9 +45744,8 @@
       <c r="H1280" t="s">
         <v>142</v>
       </c>
-      <c r="I1280" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1280,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>PCP2.png</v>
+      <c r="I1280" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="1281" spans="1:9" x14ac:dyDescent="0.25">
@@ -45817,7 +45756,7 @@
         <v>127</v>
       </c>
       <c r="C1281" t="s">
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="D1281" t="s">
         <v>131</v>
@@ -45826,7 +45765,7 @@
         <v>2</v>
       </c>
       <c r="F1281" t="s">
-        <v>35</v>
+        <v>144</v>
       </c>
       <c r="G1281" t="s">
         <v>132</v>
@@ -45834,9 +45773,8 @@
       <c r="H1281" t="s">
         <v>133</v>
       </c>
-      <c r="I1281" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1281,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>H2OHP500.png</v>
+      <c r="I1281" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="1282" spans="1:9" x14ac:dyDescent="0.25">
@@ -45853,20 +45791,19 @@
         <v>131</v>
       </c>
       <c r="E1282">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1282" t="s">
-        <v>106</v>
+        <v>33</v>
       </c>
       <c r="G1282" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="H1282" t="s">
-        <v>133</v>
-      </c>
-      <c r="I1282" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1282,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>BEATSLT.png</v>
+        <v>142</v>
+      </c>
+      <c r="I1282" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="1283" spans="1:9" x14ac:dyDescent="0.25">
@@ -45877,16 +45814,16 @@
         <v>127</v>
       </c>
       <c r="C1283" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D1283" t="s">
         <v>131</v>
       </c>
       <c r="E1283">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1283" t="s">
-        <v>106</v>
+        <v>35</v>
       </c>
       <c r="G1283" t="s">
         <v>132</v>
@@ -45894,9 +45831,8 @@
       <c r="H1283" t="s">
         <v>133</v>
       </c>
-      <c r="I1283" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1283,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>BEATSLT.png</v>
+      <c r="I1283" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="1284" spans="1:9" x14ac:dyDescent="0.25">
@@ -45907,7 +45843,7 @@
         <v>127</v>
       </c>
       <c r="C1284" t="s">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="D1284" t="s">
         <v>131</v>
@@ -45916,7 +45852,7 @@
         <v>1</v>
       </c>
       <c r="F1284" t="s">
-        <v>106</v>
+        <v>38</v>
       </c>
       <c r="G1284" t="s">
         <v>132</v>
@@ -45924,9 +45860,8 @@
       <c r="H1284" t="s">
         <v>133</v>
       </c>
-      <c r="I1284" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1284,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>BEATSLT.png</v>
+      <c r="I1284" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="1285" spans="1:9" x14ac:dyDescent="0.25">
@@ -45937,7 +45872,7 @@
         <v>127</v>
       </c>
       <c r="C1285" t="s">
-        <v>88</v>
+        <v>29</v>
       </c>
       <c r="D1285" t="s">
         <v>131</v>
@@ -45946,7 +45881,7 @@
         <v>1</v>
       </c>
       <c r="F1285" t="s">
-        <v>106</v>
+        <v>143</v>
       </c>
       <c r="G1285" t="s">
         <v>132</v>
@@ -45954,9 +45889,8 @@
       <c r="H1285" t="s">
         <v>133</v>
       </c>
-      <c r="I1285" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1285,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>BEATSLT.png</v>
+      <c r="I1285" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="1286" spans="1:9" x14ac:dyDescent="0.25">
@@ -45967,26 +45901,25 @@
         <v>127</v>
       </c>
       <c r="C1286" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D1286" t="s">
         <v>131</v>
       </c>
       <c r="E1286">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1286" t="s">
-        <v>107</v>
+        <v>37</v>
       </c>
       <c r="G1286" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="H1286" t="s">
-        <v>133</v>
-      </c>
-      <c r="I1286" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1286,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>BEATSLN.png</v>
+        <v>142</v>
+      </c>
+      <c r="I1286" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="1287" spans="1:9" x14ac:dyDescent="0.25">
@@ -46006,7 +45939,7 @@
         <v>2</v>
       </c>
       <c r="F1287" t="s">
-        <v>107</v>
+        <v>144</v>
       </c>
       <c r="G1287" t="s">
         <v>132</v>
@@ -46014,9 +45947,8 @@
       <c r="H1287" t="s">
         <v>133</v>
       </c>
-      <c r="I1287" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1287,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>BEATSLN.png</v>
+      <c r="I1287" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="1288" spans="1:9" x14ac:dyDescent="0.25">
@@ -46027,7 +45959,7 @@
         <v>127</v>
       </c>
       <c r="C1288" t="s">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="D1288" t="s">
         <v>131</v>
@@ -46036,17 +45968,16 @@
         <v>2</v>
       </c>
       <c r="F1288" t="s">
-        <v>107</v>
+        <v>33</v>
       </c>
       <c r="G1288" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="H1288" t="s">
-        <v>133</v>
-      </c>
-      <c r="I1288" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1288,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>BEATSLN.png</v>
+        <v>142</v>
+      </c>
+      <c r="I1288" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="1289" spans="1:9" x14ac:dyDescent="0.25">
@@ -46057,7 +45988,7 @@
         <v>127</v>
       </c>
       <c r="C1289" t="s">
-        <v>88</v>
+        <v>29</v>
       </c>
       <c r="D1289" t="s">
         <v>131</v>
@@ -46066,7 +45997,7 @@
         <v>2</v>
       </c>
       <c r="F1289" t="s">
-        <v>107</v>
+        <v>35</v>
       </c>
       <c r="G1289" t="s">
         <v>132</v>
@@ -46074,9 +46005,8 @@
       <c r="H1289" t="s">
         <v>133</v>
       </c>
-      <c r="I1289" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1289,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>BEATSLN.png</v>
+      <c r="I1289" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="1290" spans="1:9" x14ac:dyDescent="0.25">
@@ -46087,7 +46017,7 @@
         <v>127</v>
       </c>
       <c r="C1290" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
       <c r="D1290" t="s">
         <v>131</v>
@@ -46096,17 +46026,16 @@
         <v>1</v>
       </c>
       <c r="F1290" t="s">
-        <v>145</v>
+        <v>38</v>
       </c>
       <c r="G1290" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="H1290" t="s">
-        <v>147</v>
-      </c>
-      <c r="I1290" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1290,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>BEATSFF.png</v>
+        <v>133</v>
+      </c>
+      <c r="I1290" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="1291" spans="1:9" x14ac:dyDescent="0.25">
@@ -46117,7 +46046,7 @@
         <v>127</v>
       </c>
       <c r="C1291" t="s">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="D1291" t="s">
         <v>131</v>
@@ -46126,17 +46055,16 @@
         <v>1</v>
       </c>
       <c r="F1291" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G1291" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="H1291" t="s">
-        <v>147</v>
-      </c>
-      <c r="I1291" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1291,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>BEATSFF.png</v>
+        <v>133</v>
+      </c>
+      <c r="I1291" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="1292" spans="1:9" x14ac:dyDescent="0.25">
@@ -46156,17 +46084,16 @@
         <v>1</v>
       </c>
       <c r="F1292" t="s">
-        <v>145</v>
+        <v>37</v>
       </c>
       <c r="G1292" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="H1292" t="s">
-        <v>147</v>
-      </c>
-      <c r="I1292" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1292,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>BEATSFF.png</v>
+        <v>142</v>
+      </c>
+      <c r="I1292" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="1293" spans="1:9" x14ac:dyDescent="0.25">
@@ -46177,26 +46104,25 @@
         <v>127</v>
       </c>
       <c r="C1293" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D1293" t="s">
         <v>131</v>
       </c>
       <c r="E1293">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1293" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G1293" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="H1293" t="s">
-        <v>147</v>
-      </c>
-      <c r="I1293" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1293,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>BEATSFF.png</v>
+        <v>133</v>
+      </c>
+      <c r="I1293" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="1294" spans="1:9" x14ac:dyDescent="0.25">
@@ -46207,7 +46133,7 @@
         <v>127</v>
       </c>
       <c r="C1294" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
       <c r="D1294" t="s">
         <v>131</v>
@@ -46216,17 +46142,16 @@
         <v>2</v>
       </c>
       <c r="F1294" t="s">
-        <v>145</v>
+        <v>33</v>
       </c>
       <c r="G1294" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="H1294" t="s">
-        <v>147</v>
-      </c>
-      <c r="I1294" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1294,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>BEATSFF.png</v>
+        <v>142</v>
+      </c>
+      <c r="I1294" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="1295" spans="1:9" x14ac:dyDescent="0.25">
@@ -46237,7 +46162,7 @@
         <v>127</v>
       </c>
       <c r="C1295" t="s">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="D1295" t="s">
         <v>131</v>
@@ -46246,17 +46171,16 @@
         <v>2</v>
       </c>
       <c r="F1295" t="s">
-        <v>145</v>
+        <v>35</v>
       </c>
       <c r="G1295" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="H1295" t="s">
-        <v>147</v>
-      </c>
-      <c r="I1295" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1295,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>BEATSFF.png</v>
+        <v>133</v>
+      </c>
+      <c r="I1295" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="1296" spans="1:9" x14ac:dyDescent="0.25">
@@ -46267,26 +46191,25 @@
         <v>127</v>
       </c>
       <c r="C1296" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D1296" t="s">
         <v>131</v>
       </c>
       <c r="E1296">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1296" t="s">
-        <v>145</v>
+        <v>38</v>
       </c>
       <c r="G1296" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="H1296" t="s">
-        <v>147</v>
-      </c>
-      <c r="I1296" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1296,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>BEATSFF.png</v>
+        <v>133</v>
+      </c>
+      <c r="I1296" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="1297" spans="1:9" x14ac:dyDescent="0.25">
@@ -46303,20 +46226,19 @@
         <v>131</v>
       </c>
       <c r="E1297">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1297" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G1297" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="H1297" t="s">
-        <v>147</v>
-      </c>
-      <c r="I1297" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1297,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>BEATSFF.png</v>
+        <v>133</v>
+      </c>
+      <c r="I1297" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="1298" spans="1:9" x14ac:dyDescent="0.25">
@@ -46327,7 +46249,7 @@
         <v>127</v>
       </c>
       <c r="C1298" t="s">
-        <v>149</v>
+        <v>88</v>
       </c>
       <c r="D1298" t="s">
         <v>131</v>
@@ -46336,17 +46258,16 @@
         <v>1</v>
       </c>
       <c r="F1298" t="s">
-        <v>106</v>
+        <v>37</v>
       </c>
       <c r="G1298" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="H1298" t="s">
-        <v>133</v>
-      </c>
-      <c r="I1298" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1298,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>BEATSLT.png</v>
+        <v>142</v>
+      </c>
+      <c r="I1298" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="1299" spans="1:9" x14ac:dyDescent="0.25">
@@ -46357,16 +46278,16 @@
         <v>127</v>
       </c>
       <c r="C1299" t="s">
-        <v>150</v>
+        <v>88</v>
       </c>
       <c r="D1299" t="s">
         <v>131</v>
       </c>
       <c r="E1299">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1299" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="G1299" t="s">
         <v>132</v>
@@ -46374,9 +46295,8 @@
       <c r="H1299" t="s">
         <v>133</v>
       </c>
-      <c r="I1299" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1299,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>BEATSLT.png</v>
+      <c r="I1299" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="1300" spans="1:9" x14ac:dyDescent="0.25">
@@ -46387,7 +46307,7 @@
         <v>127</v>
       </c>
       <c r="C1300" t="s">
-        <v>149</v>
+        <v>88</v>
       </c>
       <c r="D1300" t="s">
         <v>131</v>
@@ -46396,17 +46316,16 @@
         <v>2</v>
       </c>
       <c r="F1300" t="s">
-        <v>107</v>
+        <v>33</v>
       </c>
       <c r="G1300" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="H1300" t="s">
-        <v>133</v>
-      </c>
-      <c r="I1300" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1300,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>BEATSLN.png</v>
+        <v>142</v>
+      </c>
+      <c r="I1300" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="1301" spans="1:9" x14ac:dyDescent="0.25">
@@ -46417,7 +46336,7 @@
         <v>127</v>
       </c>
       <c r="C1301" t="s">
-        <v>150</v>
+        <v>88</v>
       </c>
       <c r="D1301" t="s">
         <v>131</v>
@@ -46426,7 +46345,7 @@
         <v>2</v>
       </c>
       <c r="F1301" t="s">
-        <v>107</v>
+        <v>35</v>
       </c>
       <c r="G1301" t="s">
         <v>132</v>
@@ -46434,9 +46353,8 @@
       <c r="H1301" t="s">
         <v>133</v>
       </c>
-      <c r="I1301" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1301,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>BEATSLN.png</v>
+      <c r="I1301" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="1302" spans="1:9" x14ac:dyDescent="0.25">
@@ -46456,17 +46374,16 @@
         <v>1</v>
       </c>
       <c r="F1302" t="s">
-        <v>145</v>
+        <v>38</v>
       </c>
       <c r="G1302" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="H1302" t="s">
-        <v>147</v>
-      </c>
-      <c r="I1302" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1302,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>BEATSFF.png</v>
+        <v>133</v>
+      </c>
+      <c r="I1302" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="1303" spans="1:9" x14ac:dyDescent="0.25">
@@ -46477,7 +46394,7 @@
         <v>127</v>
       </c>
       <c r="C1303" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D1303" t="s">
         <v>131</v>
@@ -46486,17 +46403,16 @@
         <v>1</v>
       </c>
       <c r="F1303" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G1303" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="H1303" t="s">
-        <v>147</v>
-      </c>
-      <c r="I1303" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1303,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>BEATSFF.png</v>
+        <v>133</v>
+      </c>
+      <c r="I1303" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="1304" spans="1:9" x14ac:dyDescent="0.25">
@@ -46513,20 +46429,19 @@
         <v>131</v>
       </c>
       <c r="E1304">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1304" t="s">
-        <v>145</v>
+        <v>37</v>
       </c>
       <c r="G1304" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="H1304" t="s">
-        <v>147</v>
-      </c>
-      <c r="I1304" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1304,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>BEATSFF.png</v>
+        <v>142</v>
+      </c>
+      <c r="I1304" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="1305" spans="1:9" x14ac:dyDescent="0.25">
@@ -46537,7 +46452,7 @@
         <v>127</v>
       </c>
       <c r="C1305" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D1305" t="s">
         <v>131</v>
@@ -46546,17 +46461,16 @@
         <v>2</v>
       </c>
       <c r="F1305" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G1305" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="H1305" t="s">
-        <v>147</v>
-      </c>
-      <c r="I1305" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1305,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>BEATSFF.png</v>
+        <v>133</v>
+      </c>
+      <c r="I1305" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="1306" spans="1:9" x14ac:dyDescent="0.25">
@@ -46573,20 +46487,19 @@
         <v>131</v>
       </c>
       <c r="E1306">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1306" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="G1306" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="H1306" t="s">
-        <v>133</v>
-      </c>
-      <c r="I1306" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1306,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>GCA350.png</v>
+        <v>142</v>
+      </c>
+      <c r="I1306" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="1307" spans="1:9" x14ac:dyDescent="0.25">
@@ -46603,10 +46516,10 @@
         <v>131</v>
       </c>
       <c r="E1307">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1307" t="s">
-        <v>143</v>
+        <v>35</v>
       </c>
       <c r="G1307" t="s">
         <v>132</v>
@@ -46614,9 +46527,8 @@
       <c r="H1307" t="s">
         <v>133</v>
       </c>
-      <c r="I1307" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1307,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>PCSAB350.png</v>
+      <c r="I1307" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="1308" spans="1:9" x14ac:dyDescent="0.25">
@@ -46627,7 +46539,7 @@
         <v>127</v>
       </c>
       <c r="C1308" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D1308" t="s">
         <v>131</v>
@@ -46636,17 +46548,16 @@
         <v>1</v>
       </c>
       <c r="F1308" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G1308" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="H1308" t="s">
-        <v>142</v>
-      </c>
-      <c r="I1308" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1308,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>GCAP2.png</v>
+        <v>133</v>
+      </c>
+      <c r="I1308" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="1309" spans="1:9" x14ac:dyDescent="0.25">
@@ -46657,16 +46568,16 @@
         <v>127</v>
       </c>
       <c r="C1309" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D1309" t="s">
         <v>131</v>
       </c>
       <c r="E1309">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1309" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G1309" t="s">
         <v>132</v>
@@ -46674,9 +46585,8 @@
       <c r="H1309" t="s">
         <v>133</v>
       </c>
-      <c r="I1309" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1309,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>GATORADE.png</v>
+      <c r="I1309" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="1310" spans="1:9" x14ac:dyDescent="0.25">
@@ -46687,16 +46597,16 @@
         <v>127</v>
       </c>
       <c r="C1310" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D1310" t="s">
         <v>131</v>
       </c>
       <c r="E1310">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1310" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G1310" t="s">
         <v>141</v>
@@ -46704,9 +46614,8 @@
       <c r="H1310" t="s">
         <v>142</v>
       </c>
-      <c r="I1310" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1310,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>PCP2.png</v>
+      <c r="I1310" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="1311" spans="1:9" x14ac:dyDescent="0.25">
@@ -46717,7 +46626,7 @@
         <v>127</v>
       </c>
       <c r="C1311" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D1311" t="s">
         <v>131</v>
@@ -46726,7 +46635,7 @@
         <v>2</v>
       </c>
       <c r="F1311" t="s">
-        <v>35</v>
+        <v>144</v>
       </c>
       <c r="G1311" t="s">
         <v>132</v>
@@ -46734,9 +46643,8 @@
       <c r="H1311" t="s">
         <v>133</v>
       </c>
-      <c r="I1311" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1311,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>H2OHP500.png</v>
+      <c r="I1311" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="1312" spans="1:9" x14ac:dyDescent="0.25">
@@ -46753,20 +46661,19 @@
         <v>131</v>
       </c>
       <c r="E1312">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1312" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="G1312" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="H1312" t="s">
-        <v>133</v>
-      </c>
-      <c r="I1312" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1312,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>GCA350.png</v>
+        <v>142</v>
+      </c>
+      <c r="I1312" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="1313" spans="1:9" x14ac:dyDescent="0.25">
@@ -46783,10 +46690,10 @@
         <v>131</v>
       </c>
       <c r="E1313">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1313" t="s">
-        <v>143</v>
+        <v>35</v>
       </c>
       <c r="G1313" t="s">
         <v>132</v>
@@ -46794,9 +46701,8 @@
       <c r="H1313" t="s">
         <v>133</v>
       </c>
-      <c r="I1313" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1313,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>PCSAB350.png</v>
+      <c r="I1313" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="1314" spans="1:9" x14ac:dyDescent="0.25">
@@ -46807,7 +46713,7 @@
         <v>127</v>
       </c>
       <c r="C1314" t="s">
-        <v>150</v>
+        <v>28</v>
       </c>
       <c r="D1314" t="s">
         <v>131</v>
@@ -46816,17 +46722,16 @@
         <v>1</v>
       </c>
       <c r="F1314" t="s">
-        <v>37</v>
+        <v>106</v>
       </c>
       <c r="G1314" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="H1314" t="s">
-        <v>142</v>
-      </c>
-      <c r="I1314" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1314,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>GCAP2.png</v>
+        <v>133</v>
+      </c>
+      <c r="I1314" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="1315" spans="1:9" x14ac:dyDescent="0.25">
@@ -46837,16 +46742,16 @@
         <v>127</v>
       </c>
       <c r="C1315" t="s">
-        <v>150</v>
+        <v>29</v>
       </c>
       <c r="D1315" t="s">
         <v>131</v>
       </c>
       <c r="E1315">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1315" t="s">
-        <v>144</v>
+        <v>106</v>
       </c>
       <c r="G1315" t="s">
         <v>132</v>
@@ -46854,9 +46759,8 @@
       <c r="H1315" t="s">
         <v>133</v>
       </c>
-      <c r="I1315" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1315,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>GATORADE.png</v>
+      <c r="I1315" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="1316" spans="1:9" x14ac:dyDescent="0.25">
@@ -46867,26 +46771,25 @@
         <v>127</v>
       </c>
       <c r="C1316" t="s">
-        <v>150</v>
+        <v>87</v>
       </c>
       <c r="D1316" t="s">
         <v>131</v>
       </c>
       <c r="E1316">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1316" t="s">
-        <v>33</v>
+        <v>106</v>
       </c>
       <c r="G1316" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="H1316" t="s">
-        <v>142</v>
-      </c>
-      <c r="I1316" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1316,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>PCP2.png</v>
+        <v>133</v>
+      </c>
+      <c r="I1316" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="1317" spans="1:9" x14ac:dyDescent="0.25">
@@ -46897,16 +46800,16 @@
         <v>127</v>
       </c>
       <c r="C1317" t="s">
-        <v>150</v>
+        <v>88</v>
       </c>
       <c r="D1317" t="s">
         <v>131</v>
       </c>
       <c r="E1317">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1317" t="s">
-        <v>35</v>
+        <v>106</v>
       </c>
       <c r="G1317" t="s">
         <v>132</v>
@@ -46914,9 +46817,8 @@
       <c r="H1317" t="s">
         <v>133</v>
       </c>
-      <c r="I1317" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1317,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>H2OHP500.png</v>
+      <c r="I1317" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="1318" spans="1:9" x14ac:dyDescent="0.25">
@@ -46927,7 +46829,7 @@
         <v>127</v>
       </c>
       <c r="C1318" t="s">
-        <v>149</v>
+        <v>28</v>
       </c>
       <c r="D1318" t="s">
         <v>131</v>
@@ -46936,16 +46838,16 @@
         <v>2</v>
       </c>
       <c r="F1318" t="s">
-        <v>68</v>
+        <v>107</v>
       </c>
       <c r="G1318" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="H1318" t="s">
-        <v>135</v>
-      </c>
-      <c r="I1318" s="2" t="s">
-        <v>151</v>
+        <v>133</v>
+      </c>
+      <c r="I1318" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="1319" spans="1:9" x14ac:dyDescent="0.25">
@@ -46956,7 +46858,7 @@
         <v>127</v>
       </c>
       <c r="C1319" t="s">
-        <v>149</v>
+        <v>29</v>
       </c>
       <c r="D1319" t="s">
         <v>131</v>
@@ -46965,7 +46867,7 @@
         <v>2</v>
       </c>
       <c r="F1319" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="G1319" t="s">
         <v>132</v>
@@ -46973,8 +46875,8 @@
       <c r="H1319" t="s">
         <v>133</v>
       </c>
-      <c r="I1319" s="2" t="s">
-        <v>152</v>
+      <c r="I1319" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="1320" spans="1:9" x14ac:dyDescent="0.25">
@@ -46985,7 +46887,7 @@
         <v>127</v>
       </c>
       <c r="C1320" t="s">
-        <v>149</v>
+        <v>87</v>
       </c>
       <c r="D1320" t="s">
         <v>131</v>
@@ -46994,7 +46896,7 @@
         <v>2</v>
       </c>
       <c r="F1320" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="G1320" t="s">
         <v>132</v>
@@ -47002,8 +46904,8 @@
       <c r="H1320" t="s">
         <v>133</v>
       </c>
-      <c r="I1320" s="2" t="s">
-        <v>153</v>
+      <c r="I1320" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="1321" spans="1:9" x14ac:dyDescent="0.25">
@@ -47014,7 +46916,7 @@
         <v>127</v>
       </c>
       <c r="C1321" t="s">
-        <v>149</v>
+        <v>88</v>
       </c>
       <c r="D1321" t="s">
         <v>131</v>
@@ -47023,16 +46925,16 @@
         <v>2</v>
       </c>
       <c r="F1321" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="G1321" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="H1321" t="s">
-        <v>139</v>
-      </c>
-      <c r="I1321" s="2" t="s">
-        <v>154</v>
+        <v>133</v>
+      </c>
+      <c r="I1321" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="1322" spans="1:9" x14ac:dyDescent="0.25">
@@ -47043,25 +46945,25 @@
         <v>127</v>
       </c>
       <c r="C1322" t="s">
-        <v>149</v>
+        <v>28</v>
       </c>
       <c r="D1322" t="s">
         <v>131</v>
       </c>
       <c r="E1322">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1322" t="s">
-        <v>69</v>
+        <v>145</v>
       </c>
       <c r="G1322" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="H1322" t="s">
-        <v>135</v>
-      </c>
-      <c r="I1322" s="2" t="s">
-        <v>155</v>
+        <v>147</v>
+      </c>
+      <c r="I1322" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="1323" spans="1:9" x14ac:dyDescent="0.25">
@@ -47072,25 +46974,25 @@
         <v>127</v>
       </c>
       <c r="C1323" t="s">
-        <v>150</v>
+        <v>29</v>
       </c>
       <c r="D1323" t="s">
         <v>131</v>
       </c>
       <c r="E1323">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1323" t="s">
-        <v>68</v>
+        <v>145</v>
       </c>
       <c r="G1323" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="H1323" t="s">
-        <v>135</v>
-      </c>
-      <c r="I1323" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
+      </c>
+      <c r="I1323" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="1324" spans="1:9" x14ac:dyDescent="0.25">
@@ -47101,25 +47003,25 @@
         <v>127</v>
       </c>
       <c r="C1324" t="s">
-        <v>150</v>
+        <v>87</v>
       </c>
       <c r="D1324" t="s">
         <v>131</v>
       </c>
       <c r="E1324">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1324" t="s">
-        <v>86</v>
+        <v>145</v>
       </c>
       <c r="G1324" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="H1324" t="s">
-        <v>133</v>
-      </c>
-      <c r="I1324" s="2" t="s">
-        <v>152</v>
+        <v>147</v>
+      </c>
+      <c r="I1324" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="1325" spans="1:9" x14ac:dyDescent="0.25">
@@ -47130,25 +47032,25 @@
         <v>127</v>
       </c>
       <c r="C1325" t="s">
-        <v>150</v>
+        <v>88</v>
       </c>
       <c r="D1325" t="s">
         <v>131</v>
       </c>
       <c r="E1325">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1325" t="s">
-        <v>84</v>
+        <v>145</v>
       </c>
       <c r="G1325" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="H1325" t="s">
-        <v>133</v>
-      </c>
-      <c r="I1325" s="2" t="s">
-        <v>153</v>
+        <v>147</v>
+      </c>
+      <c r="I1325" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="1326" spans="1:9" x14ac:dyDescent="0.25">
@@ -47159,7 +47061,7 @@
         <v>127</v>
       </c>
       <c r="C1326" t="s">
-        <v>150</v>
+        <v>28</v>
       </c>
       <c r="D1326" t="s">
         <v>131</v>
@@ -47168,16 +47070,16 @@
         <v>2</v>
       </c>
       <c r="F1326" t="s">
-        <v>78</v>
+        <v>145</v>
       </c>
       <c r="G1326" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H1326" t="s">
-        <v>139</v>
-      </c>
-      <c r="I1326" s="2" t="s">
-        <v>154</v>
+        <v>147</v>
+      </c>
+      <c r="I1326" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="1327" spans="1:9" x14ac:dyDescent="0.25">
@@ -47188,7 +47090,7 @@
         <v>127</v>
       </c>
       <c r="C1327" t="s">
-        <v>150</v>
+        <v>29</v>
       </c>
       <c r="D1327" t="s">
         <v>131</v>
@@ -47197,16 +47099,16 @@
         <v>2</v>
       </c>
       <c r="F1327" t="s">
-        <v>69</v>
+        <v>145</v>
       </c>
       <c r="G1327" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="H1327" t="s">
-        <v>135</v>
-      </c>
-      <c r="I1327" s="2" t="s">
-        <v>155</v>
+        <v>147</v>
+      </c>
+      <c r="I1327" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="1328" spans="1:9" x14ac:dyDescent="0.25">
@@ -47217,26 +47119,25 @@
         <v>127</v>
       </c>
       <c r="C1328" t="s">
-        <v>149</v>
+        <v>87</v>
       </c>
       <c r="D1328" t="s">
         <v>131</v>
       </c>
-      <c r="E1328" s="2">
-        <v>1</v>
+      <c r="E1328">
+        <v>2</v>
       </c>
       <c r="F1328" t="s">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="G1328" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="H1328" t="s">
-        <v>133</v>
-      </c>
-      <c r="I1328" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1328,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>MICLN.png</v>
+        <v>147</v>
+      </c>
+      <c r="I1328" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="1329" spans="1:9" x14ac:dyDescent="0.25">
@@ -47247,26 +47148,25 @@
         <v>127</v>
       </c>
       <c r="C1329" t="s">
-        <v>149</v>
+        <v>88</v>
       </c>
       <c r="D1329" t="s">
         <v>131</v>
       </c>
-      <c r="E1329" s="2">
-        <v>1</v>
+      <c r="E1329">
+        <v>2</v>
       </c>
       <c r="F1329" t="s">
-        <v>67</v>
+        <v>145</v>
       </c>
       <c r="G1329" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="H1329" t="s">
-        <v>135</v>
-      </c>
-      <c r="I1329" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1329,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>AP269.png</v>
+        <v>147</v>
+      </c>
+      <c r="I1329" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="1330" spans="1:9" x14ac:dyDescent="0.25">
@@ -47282,21 +47182,20 @@
       <c r="D1330" t="s">
         <v>131</v>
       </c>
-      <c r="E1330" s="2">
+      <c r="E1330">
         <v>1</v>
       </c>
       <c r="F1330" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="G1330" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="H1330" t="s">
-        <v>137</v>
-      </c>
-      <c r="I1330" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1330,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>CORCERO350.png</v>
+        <v>133</v>
+      </c>
+      <c r="I1330" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="1331" spans="1:9" x14ac:dyDescent="0.25">
@@ -47307,16 +47206,16 @@
         <v>127</v>
       </c>
       <c r="C1331" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D1331" t="s">
         <v>131</v>
       </c>
-      <c r="E1331" s="2">
+      <c r="E1331">
         <v>1</v>
       </c>
       <c r="F1331" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="G1331" t="s">
         <v>132</v>
@@ -47324,9 +47223,8 @@
       <c r="H1331" t="s">
         <v>133</v>
       </c>
-      <c r="I1331" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1331,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>STELN.png</v>
+      <c r="I1331" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="1332" spans="1:9" x14ac:dyDescent="0.25">
@@ -47342,21 +47240,20 @@
       <c r="D1332" t="s">
         <v>131</v>
       </c>
-      <c r="E1332" s="2">
-        <v>1</v>
+      <c r="E1332">
+        <v>2</v>
       </c>
       <c r="F1332" t="s">
-        <v>72</v>
+        <v>107</v>
       </c>
       <c r="G1332" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="H1332" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1332" t="s">
         <v>156</v>
-      </c>
-      <c r="I1332" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1332,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>ORI269.png</v>
       </c>
     </row>
     <row r="1333" spans="1:9" x14ac:dyDescent="0.25">
@@ -47373,20 +47270,19 @@
         <v>131</v>
       </c>
       <c r="E1333">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1333" t="s">
-        <v>66</v>
+        <v>107</v>
       </c>
       <c r="G1333" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="H1333" t="s">
-        <v>135</v>
-      </c>
-      <c r="I1333" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1333,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>SK269.png</v>
+        <v>133</v>
+      </c>
+      <c r="I1333" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="1334" spans="1:9" x14ac:dyDescent="0.25">
@@ -47397,7 +47293,7 @@
         <v>127</v>
       </c>
       <c r="C1334" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D1334" t="s">
         <v>131</v>
@@ -47406,17 +47302,16 @@
         <v>1</v>
       </c>
       <c r="F1334" t="s">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="G1334" t="s">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="H1334" t="s">
-        <v>133</v>
-      </c>
-      <c r="I1334" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1334,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>MICLN.png</v>
+        <v>153</v>
+      </c>
+      <c r="I1334" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="1335" spans="1:9" x14ac:dyDescent="0.25">
@@ -47436,17 +47331,16 @@
         <v>1</v>
       </c>
       <c r="F1335" t="s">
-        <v>80</v>
+        <v>145</v>
       </c>
       <c r="G1335" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="H1335" t="s">
-        <v>137</v>
-      </c>
-      <c r="I1335" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1335,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>CORCERO350.png</v>
+        <v>153</v>
+      </c>
+      <c r="I1335" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="1336" spans="1:9" x14ac:dyDescent="0.25">
@@ -47457,26 +47351,25 @@
         <v>127</v>
       </c>
       <c r="C1336" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D1336" t="s">
         <v>131</v>
       </c>
       <c r="E1336">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1336" t="s">
-        <v>84</v>
+        <v>145</v>
       </c>
       <c r="G1336" t="s">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="H1336" t="s">
-        <v>133</v>
-      </c>
-      <c r="I1336" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1336,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>STELN.png</v>
+        <v>153</v>
+      </c>
+      <c r="I1336" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="1337" spans="1:9" x14ac:dyDescent="0.25">
@@ -47492,25 +47385,24 @@
       <c r="D1337" t="s">
         <v>131</v>
       </c>
-      <c r="E1337" s="2">
-        <v>1</v>
+      <c r="E1337">
+        <v>2</v>
       </c>
       <c r="F1337" t="s">
-        <v>72</v>
+        <v>145</v>
       </c>
       <c r="G1337" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="H1337" t="s">
+        <v>153</v>
+      </c>
+      <c r="I1337" t="s">
         <v>156</v>
       </c>
-      <c r="I1337" s="2" t="str">
-        <f>_xlfn.XLOOKUP(F1337,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
-        <v>ORI269.png</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1327" xr:uid="{34B2C8DF-4561-40B2-8E7C-6CD69559B9AE}"/>
+  <autoFilter ref="A1:I1220" xr:uid="{34B2C8DF-4561-40B2-8E7C-6CD69559B9AE}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>

--- a/data/calendario_promocional.xlsx
+++ b/data/calendario_promocional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anheuserbuschinbev-my.sharepoint.com/personal/99823517_ab-inbev_com/Documents/001. Projetos/Streamlit Calendario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="447" documentId="13_ncr:1_{B92F5DA4-8825-4FA1-97C6-23568D76854D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69902979-EDBB-476C-886E-9CB7EB8051C0}"/>
+  <xr:revisionPtr revIDLastSave="454" documentId="13_ncr:1_{B92F5DA4-8825-4FA1-97C6-23568D76854D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{901F1BC3-1319-45BA-8D27-3BEFC474BFDC}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">CALENDARIO!$A$1:$C$414</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DeparaIMG!$A$1:$D$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">MECANICA!$A$1:$D$49</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">PRODUTOS!$A$1:$I$1220</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">PRODUTOS!$A$1:$I$1337</definedName>
   </definedNames>
   <calcPr calcId="191029" calcMode="manual"/>
   <extLst>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8281" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8164" uniqueCount="153">
   <si>
     <t>Data</t>
   </si>
@@ -489,9 +489,6 @@
     <t>Leve 2 Beats( LT ou LN )</t>
   </si>
   <si>
-    <t>Leve 1 Flying Fish</t>
-  </si>
-  <si>
     <t>BEATSFF</t>
   </si>
   <si>
@@ -507,16 +504,7 @@
     <t>Leve 2 Beats</t>
   </si>
   <si>
-    <t>Leve 1 FF</t>
-  </si>
-  <si>
-    <t>cerv</t>
-  </si>
-  <si>
-    <t>nab</t>
-  </si>
-  <si>
-    <t>match</t>
+    <t>Ganhe 1 Flying Fish</t>
   </si>
 </sst>
 </file>
@@ -1725,7 +1713,7 @@
         <v>145</v>
       </c>
       <c r="C55" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D55" t="str">
         <f t="shared" si="6"/>
@@ -44033,8 +44021,9 @@
       <c r="H1221" t="s">
         <v>135</v>
       </c>
-      <c r="I1221" t="s">
-        <v>154</v>
+      <c r="I1221" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1221,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>AP269.png</v>
       </c>
     </row>
     <row r="1222" spans="1:9" x14ac:dyDescent="0.25">
@@ -44062,8 +44051,9 @@
       <c r="H1222" t="s">
         <v>135</v>
       </c>
-      <c r="I1222" t="s">
-        <v>154</v>
+      <c r="I1222" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1222,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>AP269.png</v>
       </c>
     </row>
     <row r="1223" spans="1:9" x14ac:dyDescent="0.25">
@@ -44091,8 +44081,9 @@
       <c r="H1223" t="s">
         <v>135</v>
       </c>
-      <c r="I1223" t="s">
-        <v>154</v>
+      <c r="I1223" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1223,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>AP269.png</v>
       </c>
     </row>
     <row r="1224" spans="1:9" x14ac:dyDescent="0.25">
@@ -44103,7 +44094,7 @@
         <v>127</v>
       </c>
       <c r="C1224" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D1224" t="s">
         <v>131</v>
@@ -44120,8 +44111,9 @@
       <c r="H1224" t="s">
         <v>135</v>
       </c>
-      <c r="I1224" t="s">
-        <v>154</v>
+      <c r="I1224" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1224,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>AP269.png</v>
       </c>
     </row>
     <row r="1225" spans="1:9" x14ac:dyDescent="0.25">
@@ -44149,8 +44141,9 @@
       <c r="H1225" t="s">
         <v>135</v>
       </c>
-      <c r="I1225" t="s">
-        <v>154</v>
+      <c r="I1225" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1225,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>SK269.png</v>
       </c>
     </row>
     <row r="1226" spans="1:9" x14ac:dyDescent="0.25">
@@ -44178,8 +44171,9 @@
       <c r="H1226" t="s">
         <v>135</v>
       </c>
-      <c r="I1226" t="s">
-        <v>154</v>
+      <c r="I1226" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1226,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>SK269.png</v>
       </c>
     </row>
     <row r="1227" spans="1:9" x14ac:dyDescent="0.25">
@@ -44190,7 +44184,7 @@
         <v>127</v>
       </c>
       <c r="C1227" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D1227" t="s">
         <v>131</v>
@@ -44207,8 +44201,9 @@
       <c r="H1227" t="s">
         <v>135</v>
       </c>
-      <c r="I1227" t="s">
-        <v>154</v>
+      <c r="I1227" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1227,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>SK269.png</v>
       </c>
     </row>
     <row r="1228" spans="1:9" x14ac:dyDescent="0.25">
@@ -44236,8 +44231,9 @@
       <c r="H1228" t="s">
         <v>135</v>
       </c>
-      <c r="I1228" t="s">
-        <v>154</v>
+      <c r="I1228" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1228,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BC269.png</v>
       </c>
     </row>
     <row r="1229" spans="1:9" x14ac:dyDescent="0.25">
@@ -44265,8 +44261,9 @@
       <c r="H1229" t="s">
         <v>135</v>
       </c>
-      <c r="I1229" t="s">
-        <v>154</v>
+      <c r="I1229" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1229,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BC269.png</v>
       </c>
     </row>
     <row r="1230" spans="1:9" x14ac:dyDescent="0.25">
@@ -44294,8 +44291,9 @@
       <c r="H1230" t="s">
         <v>135</v>
       </c>
-      <c r="I1230" t="s">
-        <v>154</v>
+      <c r="I1230" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1230,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BC269.png</v>
       </c>
     </row>
     <row r="1231" spans="1:9" x14ac:dyDescent="0.25">
@@ -44323,8 +44321,9 @@
       <c r="H1231" t="s">
         <v>135</v>
       </c>
-      <c r="I1231" t="s">
-        <v>154</v>
+      <c r="I1231" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1231,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BC269.png</v>
       </c>
     </row>
     <row r="1232" spans="1:9" x14ac:dyDescent="0.25">
@@ -44335,7 +44334,7 @@
         <v>127</v>
       </c>
       <c r="C1232" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D1232" t="s">
         <v>131</v>
@@ -44352,8 +44351,9 @@
       <c r="H1232" t="s">
         <v>135</v>
       </c>
-      <c r="I1232" t="s">
-        <v>154</v>
+      <c r="I1232" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1232,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BC269.png</v>
       </c>
     </row>
     <row r="1233" spans="1:9" x14ac:dyDescent="0.25">
@@ -44364,7 +44364,7 @@
         <v>127</v>
       </c>
       <c r="C1233" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D1233" t="s">
         <v>131</v>
@@ -44381,8 +44381,9 @@
       <c r="H1233" t="s">
         <v>135</v>
       </c>
-      <c r="I1233" t="s">
-        <v>154</v>
+      <c r="I1233" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1233,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BC269.png</v>
       </c>
     </row>
     <row r="1234" spans="1:9" x14ac:dyDescent="0.25">
@@ -44410,8 +44411,9 @@
       <c r="H1234" t="s">
         <v>135</v>
       </c>
-      <c r="I1234" t="s">
-        <v>154</v>
+      <c r="I1234" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1234,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BUD269.png</v>
       </c>
     </row>
     <row r="1235" spans="1:9" x14ac:dyDescent="0.25">
@@ -44439,8 +44441,9 @@
       <c r="H1235" t="s">
         <v>135</v>
       </c>
-      <c r="I1235" t="s">
-        <v>154</v>
+      <c r="I1235" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1235,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BUD269.png</v>
       </c>
     </row>
     <row r="1236" spans="1:9" x14ac:dyDescent="0.25">
@@ -44468,8 +44471,9 @@
       <c r="H1236" t="s">
         <v>135</v>
       </c>
-      <c r="I1236" t="s">
-        <v>154</v>
+      <c r="I1236" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1236,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BUD269.png</v>
       </c>
     </row>
     <row r="1237" spans="1:9" x14ac:dyDescent="0.25">
@@ -44497,8 +44501,9 @@
       <c r="H1237" t="s">
         <v>135</v>
       </c>
-      <c r="I1237" t="s">
-        <v>154</v>
+      <c r="I1237" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1237,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BUD269.png</v>
       </c>
     </row>
     <row r="1238" spans="1:9" x14ac:dyDescent="0.25">
@@ -44509,7 +44514,7 @@
         <v>127</v>
       </c>
       <c r="C1238" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D1238" t="s">
         <v>131</v>
@@ -44526,8 +44531,9 @@
       <c r="H1238" t="s">
         <v>135</v>
       </c>
-      <c r="I1238" t="s">
-        <v>154</v>
+      <c r="I1238" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1238,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BUD269.png</v>
       </c>
     </row>
     <row r="1239" spans="1:9" x14ac:dyDescent="0.25">
@@ -44538,7 +44544,7 @@
         <v>127</v>
       </c>
       <c r="C1239" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D1239" t="s">
         <v>131</v>
@@ -44555,8 +44561,9 @@
       <c r="H1239" t="s">
         <v>135</v>
       </c>
-      <c r="I1239" t="s">
-        <v>154</v>
+      <c r="I1239" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1239,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BUD269.png</v>
       </c>
     </row>
     <row r="1240" spans="1:9" x14ac:dyDescent="0.25">
@@ -44567,7 +44574,7 @@
         <v>127</v>
       </c>
       <c r="C1240" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D1240" t="s">
         <v>131</v>
@@ -44582,10 +44589,11 @@
         <v>134</v>
       </c>
       <c r="H1240" t="s">
-        <v>151</v>
-      </c>
-      <c r="I1240" t="s">
-        <v>154</v>
+        <v>150</v>
+      </c>
+      <c r="I1240" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1240,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>ORI269.png</v>
       </c>
     </row>
     <row r="1241" spans="1:9" x14ac:dyDescent="0.25">
@@ -44596,7 +44604,7 @@
         <v>127</v>
       </c>
       <c r="C1241" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D1241" t="s">
         <v>131</v>
@@ -44611,10 +44619,11 @@
         <v>134</v>
       </c>
       <c r="H1241" t="s">
-        <v>151</v>
-      </c>
-      <c r="I1241" t="s">
-        <v>154</v>
+        <v>150</v>
+      </c>
+      <c r="I1241" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1241,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>ORI269.png</v>
       </c>
     </row>
     <row r="1242" spans="1:9" x14ac:dyDescent="0.25">
@@ -44642,8 +44651,9 @@
       <c r="H1242" t="s">
         <v>139</v>
       </c>
-      <c r="I1242" t="s">
-        <v>154</v>
+      <c r="I1242" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1242,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>MIC350.png</v>
       </c>
     </row>
     <row r="1243" spans="1:9" x14ac:dyDescent="0.25">
@@ -44671,8 +44681,9 @@
       <c r="H1243" t="s">
         <v>139</v>
       </c>
-      <c r="I1243" t="s">
-        <v>154</v>
+      <c r="I1243" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1243,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>MIC350.png</v>
       </c>
     </row>
     <row r="1244" spans="1:9" x14ac:dyDescent="0.25">
@@ -44700,8 +44711,9 @@
       <c r="H1244" t="s">
         <v>139</v>
       </c>
-      <c r="I1244" t="s">
-        <v>154</v>
+      <c r="I1244" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1244,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>MIC350.png</v>
       </c>
     </row>
     <row r="1245" spans="1:9" x14ac:dyDescent="0.25">
@@ -44729,8 +44741,9 @@
       <c r="H1245" t="s">
         <v>139</v>
       </c>
-      <c r="I1245" t="s">
-        <v>154</v>
+      <c r="I1245" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1245,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>MIC350.png</v>
       </c>
     </row>
     <row r="1246" spans="1:9" x14ac:dyDescent="0.25">
@@ -44741,7 +44754,7 @@
         <v>127</v>
       </c>
       <c r="C1246" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D1246" t="s">
         <v>131</v>
@@ -44758,8 +44771,9 @@
       <c r="H1246" t="s">
         <v>139</v>
       </c>
-      <c r="I1246" t="s">
-        <v>154</v>
+      <c r="I1246" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1246,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>MIC350.png</v>
       </c>
     </row>
     <row r="1247" spans="1:9" x14ac:dyDescent="0.25">
@@ -44770,7 +44784,7 @@
         <v>127</v>
       </c>
       <c r="C1247" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D1247" t="s">
         <v>131</v>
@@ -44787,8 +44801,9 @@
       <c r="H1247" t="s">
         <v>139</v>
       </c>
-      <c r="I1247" t="s">
-        <v>154</v>
+      <c r="I1247" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1247,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>MIC350.png</v>
       </c>
     </row>
     <row r="1248" spans="1:9" x14ac:dyDescent="0.25">
@@ -44816,8 +44831,9 @@
       <c r="H1248" t="s">
         <v>137</v>
       </c>
-      <c r="I1248" t="s">
-        <v>154</v>
+      <c r="I1248" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1248,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>CORCERO350.png</v>
       </c>
     </row>
     <row r="1249" spans="1:9" x14ac:dyDescent="0.25">
@@ -44845,8 +44861,9 @@
       <c r="H1249" t="s">
         <v>137</v>
       </c>
-      <c r="I1249" t="s">
-        <v>154</v>
+      <c r="I1249" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1249,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>CORCERO350.png</v>
       </c>
     </row>
     <row r="1250" spans="1:9" x14ac:dyDescent="0.25">
@@ -44874,8 +44891,9 @@
       <c r="H1250" t="s">
         <v>137</v>
       </c>
-      <c r="I1250" t="s">
-        <v>154</v>
+      <c r="I1250" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1250,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>CORCERO350.png</v>
       </c>
     </row>
     <row r="1251" spans="1:9" x14ac:dyDescent="0.25">
@@ -44903,8 +44921,9 @@
       <c r="H1251" t="s">
         <v>137</v>
       </c>
-      <c r="I1251" t="s">
-        <v>154</v>
+      <c r="I1251" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1251,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>CORCERO350.png</v>
       </c>
     </row>
     <row r="1252" spans="1:9" x14ac:dyDescent="0.25">
@@ -44915,7 +44934,7 @@
         <v>127</v>
       </c>
       <c r="C1252" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D1252" t="s">
         <v>131</v>
@@ -44932,8 +44951,9 @@
       <c r="H1252" t="s">
         <v>137</v>
       </c>
-      <c r="I1252" t="s">
-        <v>154</v>
+      <c r="I1252" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1252,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>CORCERO350.png</v>
       </c>
     </row>
     <row r="1253" spans="1:9" x14ac:dyDescent="0.25">
@@ -44944,7 +44964,7 @@
         <v>127</v>
       </c>
       <c r="C1253" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D1253" t="s">
         <v>131</v>
@@ -44961,8 +44981,9 @@
       <c r="H1253" t="s">
         <v>137</v>
       </c>
-      <c r="I1253" t="s">
-        <v>154</v>
+      <c r="I1253" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1253,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>CORCERO350.png</v>
       </c>
     </row>
     <row r="1254" spans="1:9" x14ac:dyDescent="0.25">
@@ -44990,8 +45011,9 @@
       <c r="H1254" t="s">
         <v>133</v>
       </c>
-      <c r="I1254" t="s">
-        <v>154</v>
+      <c r="I1254" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1254,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>SPTLN.png</v>
       </c>
     </row>
     <row r="1255" spans="1:9" x14ac:dyDescent="0.25">
@@ -45019,8 +45041,9 @@
       <c r="H1255" t="s">
         <v>133</v>
       </c>
-      <c r="I1255" t="s">
-        <v>154</v>
+      <c r="I1255" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1255,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>SPTLN.png</v>
       </c>
     </row>
     <row r="1256" spans="1:9" x14ac:dyDescent="0.25">
@@ -45048,8 +45071,9 @@
       <c r="H1256" t="s">
         <v>133</v>
       </c>
-      <c r="I1256" t="s">
-        <v>154</v>
+      <c r="I1256" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1256,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>SPTLN.png</v>
       </c>
     </row>
     <row r="1257" spans="1:9" x14ac:dyDescent="0.25">
@@ -45077,8 +45101,9 @@
       <c r="H1257" t="s">
         <v>133</v>
       </c>
-      <c r="I1257" t="s">
-        <v>154</v>
+      <c r="I1257" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1257,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>SPTLN.png</v>
       </c>
     </row>
     <row r="1258" spans="1:9" x14ac:dyDescent="0.25">
@@ -45106,8 +45131,9 @@
       <c r="H1258" t="s">
         <v>133</v>
       </c>
-      <c r="I1258" t="s">
-        <v>154</v>
+      <c r="I1258" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1258,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>STELN.png</v>
       </c>
     </row>
     <row r="1259" spans="1:9" x14ac:dyDescent="0.25">
@@ -45135,8 +45161,9 @@
       <c r="H1259" t="s">
         <v>133</v>
       </c>
-      <c r="I1259" t="s">
-        <v>154</v>
+      <c r="I1259" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1259,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>STELN.png</v>
       </c>
     </row>
     <row r="1260" spans="1:9" x14ac:dyDescent="0.25">
@@ -45164,8 +45191,9 @@
       <c r="H1260" t="s">
         <v>133</v>
       </c>
-      <c r="I1260" t="s">
-        <v>154</v>
+      <c r="I1260" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1260,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>STELN.png</v>
       </c>
     </row>
     <row r="1261" spans="1:9" x14ac:dyDescent="0.25">
@@ -45193,8 +45221,9 @@
       <c r="H1261" t="s">
         <v>133</v>
       </c>
-      <c r="I1261" t="s">
-        <v>154</v>
+      <c r="I1261" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1261,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>STELN.png</v>
       </c>
     </row>
     <row r="1262" spans="1:9" x14ac:dyDescent="0.25">
@@ -45205,7 +45234,7 @@
         <v>127</v>
       </c>
       <c r="C1262" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D1262" t="s">
         <v>131</v>
@@ -45222,8 +45251,9 @@
       <c r="H1262" t="s">
         <v>133</v>
       </c>
-      <c r="I1262" t="s">
-        <v>154</v>
+      <c r="I1262" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1262,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>STELN.png</v>
       </c>
     </row>
     <row r="1263" spans="1:9" x14ac:dyDescent="0.25">
@@ -45234,7 +45264,7 @@
         <v>127</v>
       </c>
       <c r="C1263" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D1263" t="s">
         <v>131</v>
@@ -45251,8 +45281,9 @@
       <c r="H1263" t="s">
         <v>133</v>
       </c>
-      <c r="I1263" t="s">
-        <v>154</v>
+      <c r="I1263" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1263,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>STELN.png</v>
       </c>
     </row>
     <row r="1264" spans="1:9" x14ac:dyDescent="0.25">
@@ -45263,7 +45294,7 @@
         <v>127</v>
       </c>
       <c r="C1264" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D1264" t="s">
         <v>131</v>
@@ -45280,8 +45311,9 @@
       <c r="H1264" t="s">
         <v>133</v>
       </c>
-      <c r="I1264" t="s">
-        <v>154</v>
+      <c r="I1264" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1264,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>STELN.png</v>
       </c>
     </row>
     <row r="1265" spans="1:9" x14ac:dyDescent="0.25">
@@ -45292,7 +45324,7 @@
         <v>127</v>
       </c>
       <c r="C1265" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D1265" t="s">
         <v>131</v>
@@ -45309,8 +45341,9 @@
       <c r="H1265" t="s">
         <v>133</v>
       </c>
-      <c r="I1265" t="s">
-        <v>154</v>
+      <c r="I1265" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1265,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>STELN.png</v>
       </c>
     </row>
     <row r="1266" spans="1:9" x14ac:dyDescent="0.25">
@@ -45338,8 +45371,9 @@
       <c r="H1266" t="s">
         <v>133</v>
       </c>
-      <c r="I1266" t="s">
-        <v>154</v>
+      <c r="I1266" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1266,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>MICLN.png</v>
       </c>
     </row>
     <row r="1267" spans="1:9" x14ac:dyDescent="0.25">
@@ -45367,8 +45401,9 @@
       <c r="H1267" t="s">
         <v>133</v>
       </c>
-      <c r="I1267" t="s">
-        <v>154</v>
+      <c r="I1267" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1267,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>MICLN.png</v>
       </c>
     </row>
     <row r="1268" spans="1:9" x14ac:dyDescent="0.25">
@@ -45396,8 +45431,9 @@
       <c r="H1268" t="s">
         <v>133</v>
       </c>
-      <c r="I1268" t="s">
-        <v>154</v>
+      <c r="I1268" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1268,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>MICLN.png</v>
       </c>
     </row>
     <row r="1269" spans="1:9" x14ac:dyDescent="0.25">
@@ -45425,8 +45461,9 @@
       <c r="H1269" t="s">
         <v>133</v>
       </c>
-      <c r="I1269" t="s">
-        <v>154</v>
+      <c r="I1269" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1269,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>MICLN.png</v>
       </c>
     </row>
     <row r="1270" spans="1:9" x14ac:dyDescent="0.25">
@@ -45437,7 +45474,7 @@
         <v>127</v>
       </c>
       <c r="C1270" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D1270" t="s">
         <v>131</v>
@@ -45454,8 +45491,9 @@
       <c r="H1270" t="s">
         <v>133</v>
       </c>
-      <c r="I1270" t="s">
-        <v>154</v>
+      <c r="I1270" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1270,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>MICLN.png</v>
       </c>
     </row>
     <row r="1271" spans="1:9" x14ac:dyDescent="0.25">
@@ -45466,7 +45504,7 @@
         <v>127</v>
       </c>
       <c r="C1271" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D1271" t="s">
         <v>131</v>
@@ -45483,8 +45521,9 @@
       <c r="H1271" t="s">
         <v>133</v>
       </c>
-      <c r="I1271" t="s">
-        <v>154</v>
+      <c r="I1271" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1271,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>MICLN.png</v>
       </c>
     </row>
     <row r="1272" spans="1:9" x14ac:dyDescent="0.25">
@@ -45512,8 +45551,9 @@
       <c r="H1272" t="s">
         <v>133</v>
       </c>
-      <c r="I1272" t="s">
-        <v>154</v>
+      <c r="I1272" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1272,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>CORCEROLN.png</v>
       </c>
     </row>
     <row r="1273" spans="1:9" x14ac:dyDescent="0.25">
@@ -45541,8 +45581,9 @@
       <c r="H1273" t="s">
         <v>133</v>
       </c>
-      <c r="I1273" t="s">
-        <v>154</v>
+      <c r="I1273" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1273,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>CORCEROLN.png</v>
       </c>
     </row>
     <row r="1274" spans="1:9" x14ac:dyDescent="0.25">
@@ -45570,8 +45611,9 @@
       <c r="H1274" t="s">
         <v>133</v>
       </c>
-      <c r="I1274" t="s">
-        <v>154</v>
+      <c r="I1274" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1274,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>CORCEROLN.png</v>
       </c>
     </row>
     <row r="1275" spans="1:9" x14ac:dyDescent="0.25">
@@ -45599,8 +45641,9 @@
       <c r="H1275" t="s">
         <v>133</v>
       </c>
-      <c r="I1275" t="s">
-        <v>154</v>
+      <c r="I1275" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1275,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>CORCEROLN.png</v>
       </c>
     </row>
     <row r="1276" spans="1:9" x14ac:dyDescent="0.25">
@@ -45611,7 +45654,7 @@
         <v>127</v>
       </c>
       <c r="C1276" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D1276" t="s">
         <v>131</v>
@@ -45628,8 +45671,9 @@
       <c r="H1276" t="s">
         <v>133</v>
       </c>
-      <c r="I1276" t="s">
-        <v>154</v>
+      <c r="I1276" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1276,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>CORCEROLN.png</v>
       </c>
     </row>
     <row r="1277" spans="1:9" x14ac:dyDescent="0.25">
@@ -45640,7 +45684,7 @@
         <v>127</v>
       </c>
       <c r="C1277" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D1277" t="s">
         <v>131</v>
@@ -45657,8 +45701,9 @@
       <c r="H1277" t="s">
         <v>133</v>
       </c>
-      <c r="I1277" t="s">
-        <v>154</v>
+      <c r="I1277" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1277,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>CORCEROLN.png</v>
       </c>
     </row>
     <row r="1278" spans="1:9" x14ac:dyDescent="0.25">
@@ -45686,8 +45731,9 @@
       <c r="H1278" t="s">
         <v>133</v>
       </c>
-      <c r="I1278" t="s">
-        <v>155</v>
+      <c r="I1278" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1278,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>GCA350.png</v>
       </c>
     </row>
     <row r="1279" spans="1:9" x14ac:dyDescent="0.25">
@@ -45715,8 +45761,9 @@
       <c r="H1279" t="s">
         <v>133</v>
       </c>
-      <c r="I1279" t="s">
-        <v>155</v>
+      <c r="I1279" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1279,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>PCSAB350.png</v>
       </c>
     </row>
     <row r="1280" spans="1:9" x14ac:dyDescent="0.25">
@@ -45744,8 +45791,9 @@
       <c r="H1280" t="s">
         <v>142</v>
       </c>
-      <c r="I1280" t="s">
-        <v>155</v>
+      <c r="I1280" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1280,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>GCAP2.png</v>
       </c>
     </row>
     <row r="1281" spans="1:9" x14ac:dyDescent="0.25">
@@ -45773,8 +45821,9 @@
       <c r="H1281" t="s">
         <v>133</v>
       </c>
-      <c r="I1281" t="s">
-        <v>155</v>
+      <c r="I1281" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1281,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>GATORADE.png</v>
       </c>
     </row>
     <row r="1282" spans="1:9" x14ac:dyDescent="0.25">
@@ -45802,8 +45851,9 @@
       <c r="H1282" t="s">
         <v>142</v>
       </c>
-      <c r="I1282" t="s">
-        <v>155</v>
+      <c r="I1282" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1282,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>PCP2.png</v>
       </c>
     </row>
     <row r="1283" spans="1:9" x14ac:dyDescent="0.25">
@@ -45831,8 +45881,9 @@
       <c r="H1283" t="s">
         <v>133</v>
       </c>
-      <c r="I1283" t="s">
-        <v>155</v>
+      <c r="I1283" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1283,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>H2OHP500.png</v>
       </c>
     </row>
     <row r="1284" spans="1:9" x14ac:dyDescent="0.25">
@@ -45860,8 +45911,9 @@
       <c r="H1284" t="s">
         <v>133</v>
       </c>
-      <c r="I1284" t="s">
-        <v>155</v>
+      <c r="I1284" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1284,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>GCA350.png</v>
       </c>
     </row>
     <row r="1285" spans="1:9" x14ac:dyDescent="0.25">
@@ -45889,8 +45941,9 @@
       <c r="H1285" t="s">
         <v>133</v>
       </c>
-      <c r="I1285" t="s">
-        <v>155</v>
+      <c r="I1285" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1285,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>PCSAB350.png</v>
       </c>
     </row>
     <row r="1286" spans="1:9" x14ac:dyDescent="0.25">
@@ -45918,8 +45971,9 @@
       <c r="H1286" t="s">
         <v>142</v>
       </c>
-      <c r="I1286" t="s">
-        <v>155</v>
+      <c r="I1286" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1286,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>GCAP2.png</v>
       </c>
     </row>
     <row r="1287" spans="1:9" x14ac:dyDescent="0.25">
@@ -45947,8 +46001,9 @@
       <c r="H1287" t="s">
         <v>133</v>
       </c>
-      <c r="I1287" t="s">
-        <v>155</v>
+      <c r="I1287" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1287,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>GATORADE.png</v>
       </c>
     </row>
     <row r="1288" spans="1:9" x14ac:dyDescent="0.25">
@@ -45976,8 +46031,9 @@
       <c r="H1288" t="s">
         <v>142</v>
       </c>
-      <c r="I1288" t="s">
-        <v>155</v>
+      <c r="I1288" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1288,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>PCP2.png</v>
       </c>
     </row>
     <row r="1289" spans="1:9" x14ac:dyDescent="0.25">
@@ -46005,8 +46061,9 @@
       <c r="H1289" t="s">
         <v>133</v>
       </c>
-      <c r="I1289" t="s">
-        <v>155</v>
+      <c r="I1289" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1289,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>H2OHP500.png</v>
       </c>
     </row>
     <row r="1290" spans="1:9" x14ac:dyDescent="0.25">
@@ -46034,8 +46091,9 @@
       <c r="H1290" t="s">
         <v>133</v>
       </c>
-      <c r="I1290" t="s">
-        <v>155</v>
+      <c r="I1290" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1290,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>GCA350.png</v>
       </c>
     </row>
     <row r="1291" spans="1:9" x14ac:dyDescent="0.25">
@@ -46063,8 +46121,9 @@
       <c r="H1291" t="s">
         <v>133</v>
       </c>
-      <c r="I1291" t="s">
-        <v>155</v>
+      <c r="I1291" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1291,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>PCSAB350.png</v>
       </c>
     </row>
     <row r="1292" spans="1:9" x14ac:dyDescent="0.25">
@@ -46092,8 +46151,9 @@
       <c r="H1292" t="s">
         <v>142</v>
       </c>
-      <c r="I1292" t="s">
-        <v>155</v>
+      <c r="I1292" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1292,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>GCAP2.png</v>
       </c>
     </row>
     <row r="1293" spans="1:9" x14ac:dyDescent="0.25">
@@ -46121,8 +46181,9 @@
       <c r="H1293" t="s">
         <v>133</v>
       </c>
-      <c r="I1293" t="s">
-        <v>155</v>
+      <c r="I1293" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1293,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>GATORADE.png</v>
       </c>
     </row>
     <row r="1294" spans="1:9" x14ac:dyDescent="0.25">
@@ -46150,8 +46211,9 @@
       <c r="H1294" t="s">
         <v>142</v>
       </c>
-      <c r="I1294" t="s">
-        <v>155</v>
+      <c r="I1294" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1294,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>PCP2.png</v>
       </c>
     </row>
     <row r="1295" spans="1:9" x14ac:dyDescent="0.25">
@@ -46179,8 +46241,9 @@
       <c r="H1295" t="s">
         <v>133</v>
       </c>
-      <c r="I1295" t="s">
-        <v>155</v>
+      <c r="I1295" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1295,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>H2OHP500.png</v>
       </c>
     </row>
     <row r="1296" spans="1:9" x14ac:dyDescent="0.25">
@@ -46208,8 +46271,9 @@
       <c r="H1296" t="s">
         <v>133</v>
       </c>
-      <c r="I1296" t="s">
-        <v>155</v>
+      <c r="I1296" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1296,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>GCA350.png</v>
       </c>
     </row>
     <row r="1297" spans="1:9" x14ac:dyDescent="0.25">
@@ -46237,8 +46301,9 @@
       <c r="H1297" t="s">
         <v>133</v>
       </c>
-      <c r="I1297" t="s">
-        <v>155</v>
+      <c r="I1297" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1297,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>PCSAB350.png</v>
       </c>
     </row>
     <row r="1298" spans="1:9" x14ac:dyDescent="0.25">
@@ -46266,8 +46331,9 @@
       <c r="H1298" t="s">
         <v>142</v>
       </c>
-      <c r="I1298" t="s">
-        <v>155</v>
+      <c r="I1298" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1298,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>GCAP2.png</v>
       </c>
     </row>
     <row r="1299" spans="1:9" x14ac:dyDescent="0.25">
@@ -46295,8 +46361,9 @@
       <c r="H1299" t="s">
         <v>133</v>
       </c>
-      <c r="I1299" t="s">
-        <v>155</v>
+      <c r="I1299" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1299,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>GATORADE.png</v>
       </c>
     </row>
     <row r="1300" spans="1:9" x14ac:dyDescent="0.25">
@@ -46324,8 +46391,9 @@
       <c r="H1300" t="s">
         <v>142</v>
       </c>
-      <c r="I1300" t="s">
-        <v>155</v>
+      <c r="I1300" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1300,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>PCP2.png</v>
       </c>
     </row>
     <row r="1301" spans="1:9" x14ac:dyDescent="0.25">
@@ -46353,8 +46421,9 @@
       <c r="H1301" t="s">
         <v>133</v>
       </c>
-      <c r="I1301" t="s">
-        <v>155</v>
+      <c r="I1301" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1301,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>H2OHP500.png</v>
       </c>
     </row>
     <row r="1302" spans="1:9" x14ac:dyDescent="0.25">
@@ -46365,7 +46434,7 @@
         <v>127</v>
       </c>
       <c r="C1302" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D1302" t="s">
         <v>131</v>
@@ -46382,8 +46451,9 @@
       <c r="H1302" t="s">
         <v>133</v>
       </c>
-      <c r="I1302" t="s">
-        <v>155</v>
+      <c r="I1302" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1302,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>GCA350.png</v>
       </c>
     </row>
     <row r="1303" spans="1:9" x14ac:dyDescent="0.25">
@@ -46394,7 +46464,7 @@
         <v>127</v>
       </c>
       <c r="C1303" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D1303" t="s">
         <v>131</v>
@@ -46411,8 +46481,9 @@
       <c r="H1303" t="s">
         <v>133</v>
       </c>
-      <c r="I1303" t="s">
-        <v>155</v>
+      <c r="I1303" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1303,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>PCSAB350.png</v>
       </c>
     </row>
     <row r="1304" spans="1:9" x14ac:dyDescent="0.25">
@@ -46423,7 +46494,7 @@
         <v>127</v>
       </c>
       <c r="C1304" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D1304" t="s">
         <v>131</v>
@@ -46440,8 +46511,9 @@
       <c r="H1304" t="s">
         <v>142</v>
       </c>
-      <c r="I1304" t="s">
-        <v>155</v>
+      <c r="I1304" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1304,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>GCAP2.png</v>
       </c>
     </row>
     <row r="1305" spans="1:9" x14ac:dyDescent="0.25">
@@ -46452,7 +46524,7 @@
         <v>127</v>
       </c>
       <c r="C1305" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D1305" t="s">
         <v>131</v>
@@ -46469,8 +46541,9 @@
       <c r="H1305" t="s">
         <v>133</v>
       </c>
-      <c r="I1305" t="s">
-        <v>155</v>
+      <c r="I1305" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1305,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>GATORADE.png</v>
       </c>
     </row>
     <row r="1306" spans="1:9" x14ac:dyDescent="0.25">
@@ -46481,7 +46554,7 @@
         <v>127</v>
       </c>
       <c r="C1306" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D1306" t="s">
         <v>131</v>
@@ -46498,8 +46571,9 @@
       <c r="H1306" t="s">
         <v>142</v>
       </c>
-      <c r="I1306" t="s">
-        <v>155</v>
+      <c r="I1306" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1306,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>PCP2.png</v>
       </c>
     </row>
     <row r="1307" spans="1:9" x14ac:dyDescent="0.25">
@@ -46510,7 +46584,7 @@
         <v>127</v>
       </c>
       <c r="C1307" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D1307" t="s">
         <v>131</v>
@@ -46527,8 +46601,9 @@
       <c r="H1307" t="s">
         <v>133</v>
       </c>
-      <c r="I1307" t="s">
-        <v>155</v>
+      <c r="I1307" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1307,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>H2OHP500.png</v>
       </c>
     </row>
     <row r="1308" spans="1:9" x14ac:dyDescent="0.25">
@@ -46539,7 +46614,7 @@
         <v>127</v>
       </c>
       <c r="C1308" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D1308" t="s">
         <v>131</v>
@@ -46556,8 +46631,9 @@
       <c r="H1308" t="s">
         <v>133</v>
       </c>
-      <c r="I1308" t="s">
-        <v>155</v>
+      <c r="I1308" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1308,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>GCA350.png</v>
       </c>
     </row>
     <row r="1309" spans="1:9" x14ac:dyDescent="0.25">
@@ -46568,7 +46644,7 @@
         <v>127</v>
       </c>
       <c r="C1309" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D1309" t="s">
         <v>131</v>
@@ -46585,8 +46661,9 @@
       <c r="H1309" t="s">
         <v>133</v>
       </c>
-      <c r="I1309" t="s">
-        <v>155</v>
+      <c r="I1309" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1309,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>PCSAB350.png</v>
       </c>
     </row>
     <row r="1310" spans="1:9" x14ac:dyDescent="0.25">
@@ -46597,7 +46674,7 @@
         <v>127</v>
       </c>
       <c r="C1310" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D1310" t="s">
         <v>131</v>
@@ -46614,8 +46691,9 @@
       <c r="H1310" t="s">
         <v>142</v>
       </c>
-      <c r="I1310" t="s">
-        <v>155</v>
+      <c r="I1310" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1310,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>GCAP2.png</v>
       </c>
     </row>
     <row r="1311" spans="1:9" x14ac:dyDescent="0.25">
@@ -46626,7 +46704,7 @@
         <v>127</v>
       </c>
       <c r="C1311" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D1311" t="s">
         <v>131</v>
@@ -46643,8 +46721,9 @@
       <c r="H1311" t="s">
         <v>133</v>
       </c>
-      <c r="I1311" t="s">
-        <v>155</v>
+      <c r="I1311" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1311,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>GATORADE.png</v>
       </c>
     </row>
     <row r="1312" spans="1:9" x14ac:dyDescent="0.25">
@@ -46655,7 +46734,7 @@
         <v>127</v>
       </c>
       <c r="C1312" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D1312" t="s">
         <v>131</v>
@@ -46672,8 +46751,9 @@
       <c r="H1312" t="s">
         <v>142</v>
       </c>
-      <c r="I1312" t="s">
-        <v>155</v>
+      <c r="I1312" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1312,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>PCP2.png</v>
       </c>
     </row>
     <row r="1313" spans="1:9" x14ac:dyDescent="0.25">
@@ -46684,7 +46764,7 @@
         <v>127</v>
       </c>
       <c r="C1313" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D1313" t="s">
         <v>131</v>
@@ -46701,8 +46781,9 @@
       <c r="H1313" t="s">
         <v>133</v>
       </c>
-      <c r="I1313" t="s">
-        <v>155</v>
+      <c r="I1313" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1313,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>H2OHP500.png</v>
       </c>
     </row>
     <row r="1314" spans="1:9" x14ac:dyDescent="0.25">
@@ -46730,8 +46811,9 @@
       <c r="H1314" t="s">
         <v>133</v>
       </c>
-      <c r="I1314" t="s">
-        <v>156</v>
+      <c r="I1314" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1314,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BEATSLT.png</v>
       </c>
     </row>
     <row r="1315" spans="1:9" x14ac:dyDescent="0.25">
@@ -46759,8 +46841,9 @@
       <c r="H1315" t="s">
         <v>133</v>
       </c>
-      <c r="I1315" t="s">
-        <v>156</v>
+      <c r="I1315" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1315,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BEATSLT.png</v>
       </c>
     </row>
     <row r="1316" spans="1:9" x14ac:dyDescent="0.25">
@@ -46788,8 +46871,9 @@
       <c r="H1316" t="s">
         <v>133</v>
       </c>
-      <c r="I1316" t="s">
-        <v>156</v>
+      <c r="I1316" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1316,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BEATSLT.png</v>
       </c>
     </row>
     <row r="1317" spans="1:9" x14ac:dyDescent="0.25">
@@ -46817,8 +46901,9 @@
       <c r="H1317" t="s">
         <v>133</v>
       </c>
-      <c r="I1317" t="s">
-        <v>156</v>
+      <c r="I1317" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1317,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BEATSLT.png</v>
       </c>
     </row>
     <row r="1318" spans="1:9" x14ac:dyDescent="0.25">
@@ -46846,8 +46931,9 @@
       <c r="H1318" t="s">
         <v>133</v>
       </c>
-      <c r="I1318" t="s">
-        <v>156</v>
+      <c r="I1318" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1318,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BEATSLN.png</v>
       </c>
     </row>
     <row r="1319" spans="1:9" x14ac:dyDescent="0.25">
@@ -46875,8 +46961,9 @@
       <c r="H1319" t="s">
         <v>133</v>
       </c>
-      <c r="I1319" t="s">
-        <v>156</v>
+      <c r="I1319" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1319,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BEATSLN.png</v>
       </c>
     </row>
     <row r="1320" spans="1:9" x14ac:dyDescent="0.25">
@@ -46904,8 +46991,9 @@
       <c r="H1320" t="s">
         <v>133</v>
       </c>
-      <c r="I1320" t="s">
-        <v>156</v>
+      <c r="I1320" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1320,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BEATSLN.png</v>
       </c>
     </row>
     <row r="1321" spans="1:9" x14ac:dyDescent="0.25">
@@ -46933,8 +47021,9 @@
       <c r="H1321" t="s">
         <v>133</v>
       </c>
-      <c r="I1321" t="s">
-        <v>156</v>
+      <c r="I1321" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1321,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BEATSLN.png</v>
       </c>
     </row>
     <row r="1322" spans="1:9" x14ac:dyDescent="0.25">
@@ -46960,10 +47049,11 @@
         <v>146</v>
       </c>
       <c r="H1322" t="s">
-        <v>147</v>
-      </c>
-      <c r="I1322" t="s">
-        <v>156</v>
+        <v>152</v>
+      </c>
+      <c r="I1322" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1322,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BEATSFF.png</v>
       </c>
     </row>
     <row r="1323" spans="1:9" x14ac:dyDescent="0.25">
@@ -46989,10 +47079,11 @@
         <v>146</v>
       </c>
       <c r="H1323" t="s">
-        <v>147</v>
-      </c>
-      <c r="I1323" t="s">
-        <v>156</v>
+        <v>152</v>
+      </c>
+      <c r="I1323" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1323,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BEATSFF.png</v>
       </c>
     </row>
     <row r="1324" spans="1:9" x14ac:dyDescent="0.25">
@@ -47018,10 +47109,11 @@
         <v>146</v>
       </c>
       <c r="H1324" t="s">
-        <v>147</v>
-      </c>
-      <c r="I1324" t="s">
-        <v>156</v>
+        <v>152</v>
+      </c>
+      <c r="I1324" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1324,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BEATSFF.png</v>
       </c>
     </row>
     <row r="1325" spans="1:9" x14ac:dyDescent="0.25">
@@ -47047,10 +47139,11 @@
         <v>146</v>
       </c>
       <c r="H1325" t="s">
-        <v>147</v>
-      </c>
-      <c r="I1325" t="s">
-        <v>156</v>
+        <v>152</v>
+      </c>
+      <c r="I1325" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1325,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BEATSFF.png</v>
       </c>
     </row>
     <row r="1326" spans="1:9" x14ac:dyDescent="0.25">
@@ -47076,10 +47169,11 @@
         <v>146</v>
       </c>
       <c r="H1326" t="s">
-        <v>147</v>
-      </c>
-      <c r="I1326" t="s">
-        <v>156</v>
+        <v>152</v>
+      </c>
+      <c r="I1326" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1326,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BEATSFF.png</v>
       </c>
     </row>
     <row r="1327" spans="1:9" x14ac:dyDescent="0.25">
@@ -47105,10 +47199,11 @@
         <v>146</v>
       </c>
       <c r="H1327" t="s">
-        <v>147</v>
-      </c>
-      <c r="I1327" t="s">
-        <v>156</v>
+        <v>152</v>
+      </c>
+      <c r="I1327" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1327,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BEATSFF.png</v>
       </c>
     </row>
     <row r="1328" spans="1:9" x14ac:dyDescent="0.25">
@@ -47134,10 +47229,11 @@
         <v>146</v>
       </c>
       <c r="H1328" t="s">
-        <v>147</v>
-      </c>
-      <c r="I1328" t="s">
-        <v>156</v>
+        <v>152</v>
+      </c>
+      <c r="I1328" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1328,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BEATSFF.png</v>
       </c>
     </row>
     <row r="1329" spans="1:9" x14ac:dyDescent="0.25">
@@ -47163,10 +47259,11 @@
         <v>146</v>
       </c>
       <c r="H1329" t="s">
-        <v>147</v>
-      </c>
-      <c r="I1329" t="s">
-        <v>156</v>
+        <v>152</v>
+      </c>
+      <c r="I1329" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1329,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BEATSFF.png</v>
       </c>
     </row>
     <row r="1330" spans="1:9" x14ac:dyDescent="0.25">
@@ -47177,7 +47274,7 @@
         <v>127</v>
       </c>
       <c r="C1330" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D1330" t="s">
         <v>131</v>
@@ -47194,8 +47291,9 @@
       <c r="H1330" t="s">
         <v>133</v>
       </c>
-      <c r="I1330" t="s">
-        <v>156</v>
+      <c r="I1330" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1330,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BEATSLT.png</v>
       </c>
     </row>
     <row r="1331" spans="1:9" x14ac:dyDescent="0.25">
@@ -47206,7 +47304,7 @@
         <v>127</v>
       </c>
       <c r="C1331" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D1331" t="s">
         <v>131</v>
@@ -47223,8 +47321,9 @@
       <c r="H1331" t="s">
         <v>133</v>
       </c>
-      <c r="I1331" t="s">
-        <v>156</v>
+      <c r="I1331" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1331,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BEATSLT.png</v>
       </c>
     </row>
     <row r="1332" spans="1:9" x14ac:dyDescent="0.25">
@@ -47235,7 +47334,7 @@
         <v>127</v>
       </c>
       <c r="C1332" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D1332" t="s">
         <v>131</v>
@@ -47252,8 +47351,9 @@
       <c r="H1332" t="s">
         <v>133</v>
       </c>
-      <c r="I1332" t="s">
-        <v>156</v>
+      <c r="I1332" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1332,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BEATSLN.png</v>
       </c>
     </row>
     <row r="1333" spans="1:9" x14ac:dyDescent="0.25">
@@ -47264,7 +47364,7 @@
         <v>127</v>
       </c>
       <c r="C1333" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D1333" t="s">
         <v>131</v>
@@ -47281,8 +47381,9 @@
       <c r="H1333" t="s">
         <v>133</v>
       </c>
-      <c r="I1333" t="s">
-        <v>156</v>
+      <c r="I1333" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1333,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BEATSLN.png</v>
       </c>
     </row>
     <row r="1334" spans="1:9" x14ac:dyDescent="0.25">
@@ -47293,7 +47394,7 @@
         <v>127</v>
       </c>
       <c r="C1334" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D1334" t="s">
         <v>131</v>
@@ -47305,13 +47406,14 @@
         <v>145</v>
       </c>
       <c r="G1334" t="s">
+        <v>151</v>
+      </c>
+      <c r="H1334" t="s">
         <v>152</v>
       </c>
-      <c r="H1334" t="s">
-        <v>153</v>
-      </c>
-      <c r="I1334" t="s">
-        <v>156</v>
+      <c r="I1334" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1334,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BEATSFF.png</v>
       </c>
     </row>
     <row r="1335" spans="1:9" x14ac:dyDescent="0.25">
@@ -47322,7 +47424,7 @@
         <v>127</v>
       </c>
       <c r="C1335" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D1335" t="s">
         <v>131</v>
@@ -47334,13 +47436,14 @@
         <v>145</v>
       </c>
       <c r="G1335" t="s">
+        <v>151</v>
+      </c>
+      <c r="H1335" t="s">
         <v>152</v>
       </c>
-      <c r="H1335" t="s">
-        <v>153</v>
-      </c>
-      <c r="I1335" t="s">
-        <v>156</v>
+      <c r="I1335" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1335,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BEATSFF.png</v>
       </c>
     </row>
     <row r="1336" spans="1:9" x14ac:dyDescent="0.25">
@@ -47351,7 +47454,7 @@
         <v>127</v>
       </c>
       <c r="C1336" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D1336" t="s">
         <v>131</v>
@@ -47363,13 +47466,14 @@
         <v>145</v>
       </c>
       <c r="G1336" t="s">
+        <v>151</v>
+      </c>
+      <c r="H1336" t="s">
         <v>152</v>
       </c>
-      <c r="H1336" t="s">
-        <v>153</v>
-      </c>
-      <c r="I1336" t="s">
-        <v>156</v>
+      <c r="I1336" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1336,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BEATSFF.png</v>
       </c>
     </row>
     <row r="1337" spans="1:9" x14ac:dyDescent="0.25">
@@ -47380,7 +47484,7 @@
         <v>127</v>
       </c>
       <c r="C1337" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D1337" t="s">
         <v>131</v>
@@ -47392,17 +47496,18 @@
         <v>145</v>
       </c>
       <c r="G1337" t="s">
+        <v>151</v>
+      </c>
+      <c r="H1337" t="s">
         <v>152</v>
       </c>
-      <c r="H1337" t="s">
-        <v>153</v>
-      </c>
-      <c r="I1337" t="s">
-        <v>156</v>
+      <c r="I1337" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1337,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
+        <v>BEATSFF.png</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1220" xr:uid="{34B2C8DF-4561-40B2-8E7C-6CD69559B9AE}"/>
+  <autoFilter ref="A1:I1337" xr:uid="{34B2C8DF-4561-40B2-8E7C-6CD69559B9AE}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>

--- a/data/calendario_promocional.xlsx
+++ b/data/calendario_promocional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anheuserbuschinbev-my.sharepoint.com/personal/99823517_ab-inbev_com/Documents/001. Projetos/Streamlit Calendario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="454" documentId="13_ncr:1_{B92F5DA4-8825-4FA1-97C6-23568D76854D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{901F1BC3-1319-45BA-8D27-3BEFC474BFDC}"/>
+  <xr:revisionPtr revIDLastSave="461" documentId="13_ncr:1_{B92F5DA4-8825-4FA1-97C6-23568D76854D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67BCB717-267C-409F-9171-008B811C896D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8164" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8164" uniqueCount="152">
   <si>
     <t>Data</t>
   </si>
@@ -486,9 +486,6 @@
     <t>BEATS - FF</t>
   </si>
   <si>
-    <t>Leve 2 Beats( LT ou LN )</t>
-  </si>
-  <si>
     <t>BEATSFF</t>
   </si>
   <si>
@@ -504,7 +501,7 @@
     <t>Leve 2 Beats</t>
   </si>
   <si>
-    <t>Ganhe 1 Flying Fish</t>
+    <t>Ganhe 1 FF</t>
   </si>
 </sst>
 </file>
@@ -1713,7 +1710,7 @@
         <v>145</v>
       </c>
       <c r="C55" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D55" t="str">
         <f t="shared" si="6"/>
@@ -44094,7 +44091,7 @@
         <v>127</v>
       </c>
       <c r="C1224" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D1224" t="s">
         <v>131</v>
@@ -44184,7 +44181,7 @@
         <v>127</v>
       </c>
       <c r="C1227" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D1227" t="s">
         <v>131</v>
@@ -44334,7 +44331,7 @@
         <v>127</v>
       </c>
       <c r="C1232" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D1232" t="s">
         <v>131</v>
@@ -44364,7 +44361,7 @@
         <v>127</v>
       </c>
       <c r="C1233" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D1233" t="s">
         <v>131</v>
@@ -44514,7 +44511,7 @@
         <v>127</v>
       </c>
       <c r="C1238" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D1238" t="s">
         <v>131</v>
@@ -44544,7 +44541,7 @@
         <v>127</v>
       </c>
       <c r="C1239" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D1239" t="s">
         <v>131</v>
@@ -44574,7 +44571,7 @@
         <v>127</v>
       </c>
       <c r="C1240" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D1240" t="s">
         <v>131</v>
@@ -44589,7 +44586,7 @@
         <v>134</v>
       </c>
       <c r="H1240" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I1240" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1240,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -44604,7 +44601,7 @@
         <v>127</v>
       </c>
       <c r="C1241" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D1241" t="s">
         <v>131</v>
@@ -44619,7 +44616,7 @@
         <v>134</v>
       </c>
       <c r="H1241" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I1241" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1241,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -44754,7 +44751,7 @@
         <v>127</v>
       </c>
       <c r="C1246" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D1246" t="s">
         <v>131</v>
@@ -44784,7 +44781,7 @@
         <v>127</v>
       </c>
       <c r="C1247" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D1247" t="s">
         <v>131</v>
@@ -44934,7 +44931,7 @@
         <v>127</v>
       </c>
       <c r="C1252" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D1252" t="s">
         <v>131</v>
@@ -44964,7 +44961,7 @@
         <v>127</v>
       </c>
       <c r="C1253" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D1253" t="s">
         <v>131</v>
@@ -45234,7 +45231,7 @@
         <v>127</v>
       </c>
       <c r="C1262" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D1262" t="s">
         <v>131</v>
@@ -45264,7 +45261,7 @@
         <v>127</v>
       </c>
       <c r="C1263" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D1263" t="s">
         <v>131</v>
@@ -45294,7 +45291,7 @@
         <v>127</v>
       </c>
       <c r="C1264" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D1264" t="s">
         <v>131</v>
@@ -45324,7 +45321,7 @@
         <v>127</v>
       </c>
       <c r="C1265" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D1265" t="s">
         <v>131</v>
@@ -45474,7 +45471,7 @@
         <v>127</v>
       </c>
       <c r="C1270" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D1270" t="s">
         <v>131</v>
@@ -45504,7 +45501,7 @@
         <v>127</v>
       </c>
       <c r="C1271" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D1271" t="s">
         <v>131</v>
@@ -45654,7 +45651,7 @@
         <v>127</v>
       </c>
       <c r="C1276" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D1276" t="s">
         <v>131</v>
@@ -45684,7 +45681,7 @@
         <v>127</v>
       </c>
       <c r="C1277" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D1277" t="s">
         <v>131</v>
@@ -46434,7 +46431,7 @@
         <v>127</v>
       </c>
       <c r="C1302" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D1302" t="s">
         <v>131</v>
@@ -46464,7 +46461,7 @@
         <v>127</v>
       </c>
       <c r="C1303" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D1303" t="s">
         <v>131</v>
@@ -46494,7 +46491,7 @@
         <v>127</v>
       </c>
       <c r="C1304" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D1304" t="s">
         <v>131</v>
@@ -46524,7 +46521,7 @@
         <v>127</v>
       </c>
       <c r="C1305" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D1305" t="s">
         <v>131</v>
@@ -46554,7 +46551,7 @@
         <v>127</v>
       </c>
       <c r="C1306" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D1306" t="s">
         <v>131</v>
@@ -46584,7 +46581,7 @@
         <v>127</v>
       </c>
       <c r="C1307" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D1307" t="s">
         <v>131</v>
@@ -46614,7 +46611,7 @@
         <v>127</v>
       </c>
       <c r="C1308" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D1308" t="s">
         <v>131</v>
@@ -46644,7 +46641,7 @@
         <v>127</v>
       </c>
       <c r="C1309" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D1309" t="s">
         <v>131</v>
@@ -46674,7 +46671,7 @@
         <v>127</v>
       </c>
       <c r="C1310" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D1310" t="s">
         <v>131</v>
@@ -46704,7 +46701,7 @@
         <v>127</v>
       </c>
       <c r="C1311" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D1311" t="s">
         <v>131</v>
@@ -46734,7 +46731,7 @@
         <v>127</v>
       </c>
       <c r="C1312" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D1312" t="s">
         <v>131</v>
@@ -46764,7 +46761,7 @@
         <v>127</v>
       </c>
       <c r="C1313" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D1313" t="s">
         <v>131</v>
@@ -47046,10 +47043,10 @@
         <v>145</v>
       </c>
       <c r="G1322" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="H1322" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I1322" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1322,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -47076,10 +47073,10 @@
         <v>145</v>
       </c>
       <c r="G1323" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="H1323" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I1323" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1323,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -47106,10 +47103,10 @@
         <v>145</v>
       </c>
       <c r="G1324" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="H1324" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I1324" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1324,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -47136,10 +47133,10 @@
         <v>145</v>
       </c>
       <c r="G1325" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="H1325" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I1325" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1325,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -47166,10 +47163,10 @@
         <v>145</v>
       </c>
       <c r="G1326" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="H1326" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I1326" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1326,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -47196,10 +47193,10 @@
         <v>145</v>
       </c>
       <c r="G1327" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="H1327" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I1327" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1327,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -47226,10 +47223,10 @@
         <v>145</v>
       </c>
       <c r="G1328" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="H1328" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I1328" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1328,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -47256,10 +47253,10 @@
         <v>145</v>
       </c>
       <c r="G1329" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="H1329" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I1329" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1329,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -47274,7 +47271,7 @@
         <v>127</v>
       </c>
       <c r="C1330" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D1330" t="s">
         <v>131</v>
@@ -47304,7 +47301,7 @@
         <v>127</v>
       </c>
       <c r="C1331" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D1331" t="s">
         <v>131</v>
@@ -47334,7 +47331,7 @@
         <v>127</v>
       </c>
       <c r="C1332" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D1332" t="s">
         <v>131</v>
@@ -47364,7 +47361,7 @@
         <v>127</v>
       </c>
       <c r="C1333" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D1333" t="s">
         <v>131</v>
@@ -47394,7 +47391,7 @@
         <v>127</v>
       </c>
       <c r="C1334" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D1334" t="s">
         <v>131</v>
@@ -47406,10 +47403,10 @@
         <v>145</v>
       </c>
       <c r="G1334" t="s">
+        <v>150</v>
+      </c>
+      <c r="H1334" t="s">
         <v>151</v>
-      </c>
-      <c r="H1334" t="s">
-        <v>152</v>
       </c>
       <c r="I1334" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1334,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -47424,7 +47421,7 @@
         <v>127</v>
       </c>
       <c r="C1335" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D1335" t="s">
         <v>131</v>
@@ -47436,10 +47433,10 @@
         <v>145</v>
       </c>
       <c r="G1335" t="s">
+        <v>150</v>
+      </c>
+      <c r="H1335" t="s">
         <v>151</v>
-      </c>
-      <c r="H1335" t="s">
-        <v>152</v>
       </c>
       <c r="I1335" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1335,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -47454,7 +47451,7 @@
         <v>127</v>
       </c>
       <c r="C1336" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D1336" t="s">
         <v>131</v>
@@ -47466,10 +47463,10 @@
         <v>145</v>
       </c>
       <c r="G1336" t="s">
+        <v>150</v>
+      </c>
+      <c r="H1336" t="s">
         <v>151</v>
-      </c>
-      <c r="H1336" t="s">
-        <v>152</v>
       </c>
       <c r="I1336" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1336,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -47484,7 +47481,7 @@
         <v>127</v>
       </c>
       <c r="C1337" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D1337" t="s">
         <v>131</v>
@@ -47496,10 +47493,10 @@
         <v>145</v>
       </c>
       <c r="G1337" t="s">
+        <v>150</v>
+      </c>
+      <c r="H1337" t="s">
         <v>151</v>
-      </c>
-      <c r="H1337" t="s">
-        <v>152</v>
       </c>
       <c r="I1337" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1337,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>

--- a/data/calendario_promocional.xlsx
+++ b/data/calendario_promocional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anheuserbuschinbev-my.sharepoint.com/personal/99823517_ab-inbev_com/Documents/001. Projetos/Streamlit Calendario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="461" documentId="13_ncr:1_{B92F5DA4-8825-4FA1-97C6-23568D76854D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67BCB717-267C-409F-9171-008B811C896D}"/>
+  <xr:revisionPtr revIDLastSave="470" documentId="13_ncr:1_{B92F5DA4-8825-4FA1-97C6-23568D76854D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7611367-DAC2-4E52-AACB-2F537632EDB1}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8164" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8164" uniqueCount="151">
   <si>
     <t>Data</t>
   </si>
@@ -439,9 +439,6 @@
   </si>
   <si>
     <t>MATCH: Máximo 4 combos por CPF</t>
-  </si>
-  <si>
-    <t>VAR/ATAC</t>
   </si>
   <si>
     <t>Leve:6</t>
@@ -1659,7 +1656,7 @@
         <v>62</v>
       </c>
       <c r="B52" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C52" t="str">
         <f t="shared" ref="C52" si="4">SUBSTITUTE(B52," ","")</f>
@@ -1675,7 +1672,7 @@
         <v>61</v>
       </c>
       <c r="B53" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C53" t="str">
         <f t="shared" ref="C53:C54" si="5">SUBSTITUTE(B53," ","")</f>
@@ -1691,7 +1688,7 @@
         <v>61</v>
       </c>
       <c r="B54" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C54" t="str">
         <f t="shared" si="5"/>
@@ -1707,10 +1704,10 @@
         <v>62</v>
       </c>
       <c r="B55" t="s">
+        <v>144</v>
+      </c>
+      <c r="C55" t="s">
         <v>145</v>
-      </c>
-      <c r="C55" t="s">
-        <v>146</v>
       </c>
       <c r="D55" t="str">
         <f t="shared" si="6"/>
@@ -44004,7 +44001,7 @@
         <v>28</v>
       </c>
       <c r="D1221" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1221" s="2">
         <v>1</v>
@@ -44013,10 +44010,10 @@
         <v>67</v>
       </c>
       <c r="G1221" t="s">
+        <v>133</v>
+      </c>
+      <c r="H1221" t="s">
         <v>134</v>
-      </c>
-      <c r="H1221" t="s">
-        <v>135</v>
       </c>
       <c r="I1221" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1221,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -44034,7 +44031,7 @@
         <v>29</v>
       </c>
       <c r="D1222" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1222">
         <v>1</v>
@@ -44043,10 +44040,10 @@
         <v>67</v>
       </c>
       <c r="G1222" t="s">
+        <v>133</v>
+      </c>
+      <c r="H1222" t="s">
         <v>134</v>
-      </c>
-      <c r="H1222" t="s">
-        <v>135</v>
       </c>
       <c r="I1222" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1222,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -44064,7 +44061,7 @@
         <v>88</v>
       </c>
       <c r="D1223" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1223">
         <v>2</v>
@@ -44073,10 +44070,10 @@
         <v>67</v>
       </c>
       <c r="G1223" t="s">
+        <v>133</v>
+      </c>
+      <c r="H1223" t="s">
         <v>134</v>
-      </c>
-      <c r="H1223" t="s">
-        <v>135</v>
       </c>
       <c r="I1223" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1223,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -44091,10 +44088,10 @@
         <v>127</v>
       </c>
       <c r="C1224" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D1224" t="s">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="E1224" s="2">
         <v>1</v>
@@ -44103,10 +44100,10 @@
         <v>67</v>
       </c>
       <c r="G1224" t="s">
+        <v>133</v>
+      </c>
+      <c r="H1224" t="s">
         <v>134</v>
-      </c>
-      <c r="H1224" t="s">
-        <v>135</v>
       </c>
       <c r="I1224" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1224,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -44124,7 +44121,7 @@
         <v>87</v>
       </c>
       <c r="D1225" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1225">
         <v>1</v>
@@ -44133,10 +44130,10 @@
         <v>66</v>
       </c>
       <c r="G1225" t="s">
+        <v>133</v>
+      </c>
+      <c r="H1225" t="s">
         <v>134</v>
-      </c>
-      <c r="H1225" t="s">
-        <v>135</v>
       </c>
       <c r="I1225" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1225,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -44154,7 +44151,7 @@
         <v>88</v>
       </c>
       <c r="D1226" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1226">
         <v>1</v>
@@ -44163,10 +44160,10 @@
         <v>66</v>
       </c>
       <c r="G1226" t="s">
+        <v>133</v>
+      </c>
+      <c r="H1226" t="s">
         <v>134</v>
-      </c>
-      <c r="H1226" t="s">
-        <v>135</v>
       </c>
       <c r="I1226" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1226,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -44181,10 +44178,10 @@
         <v>127</v>
       </c>
       <c r="C1227" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D1227" t="s">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="E1227">
         <v>1</v>
@@ -44193,10 +44190,10 @@
         <v>66</v>
       </c>
       <c r="G1227" t="s">
+        <v>133</v>
+      </c>
+      <c r="H1227" t="s">
         <v>134</v>
-      </c>
-      <c r="H1227" t="s">
-        <v>135</v>
       </c>
       <c r="I1227" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1227,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -44214,7 +44211,7 @@
         <v>28</v>
       </c>
       <c r="D1228" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1228">
         <v>2</v>
@@ -44223,10 +44220,10 @@
         <v>68</v>
       </c>
       <c r="G1228" t="s">
+        <v>133</v>
+      </c>
+      <c r="H1228" t="s">
         <v>134</v>
-      </c>
-      <c r="H1228" t="s">
-        <v>135</v>
       </c>
       <c r="I1228" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1228,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -44244,7 +44241,7 @@
         <v>29</v>
       </c>
       <c r="D1229" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1229">
         <v>2</v>
@@ -44253,10 +44250,10 @@
         <v>68</v>
       </c>
       <c r="G1229" t="s">
+        <v>133</v>
+      </c>
+      <c r="H1229" t="s">
         <v>134</v>
-      </c>
-      <c r="H1229" t="s">
-        <v>135</v>
       </c>
       <c r="I1229" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1229,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -44274,7 +44271,7 @@
         <v>87</v>
       </c>
       <c r="D1230" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1230">
         <v>2</v>
@@ -44283,10 +44280,10 @@
         <v>68</v>
       </c>
       <c r="G1230" t="s">
+        <v>133</v>
+      </c>
+      <c r="H1230" t="s">
         <v>134</v>
-      </c>
-      <c r="H1230" t="s">
-        <v>135</v>
       </c>
       <c r="I1230" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1230,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -44304,7 +44301,7 @@
         <v>88</v>
       </c>
       <c r="D1231" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1231">
         <v>2</v>
@@ -44313,10 +44310,10 @@
         <v>68</v>
       </c>
       <c r="G1231" t="s">
+        <v>133</v>
+      </c>
+      <c r="H1231" t="s">
         <v>134</v>
-      </c>
-      <c r="H1231" t="s">
-        <v>135</v>
       </c>
       <c r="I1231" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1231,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -44331,10 +44328,10 @@
         <v>127</v>
       </c>
       <c r="C1232" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D1232" t="s">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="E1232">
         <v>2</v>
@@ -44343,10 +44340,10 @@
         <v>68</v>
       </c>
       <c r="G1232" t="s">
+        <v>133</v>
+      </c>
+      <c r="H1232" t="s">
         <v>134</v>
-      </c>
-      <c r="H1232" t="s">
-        <v>135</v>
       </c>
       <c r="I1232" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1232,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -44361,10 +44358,10 @@
         <v>127</v>
       </c>
       <c r="C1233" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D1233" t="s">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="E1233">
         <v>2</v>
@@ -44373,10 +44370,10 @@
         <v>68</v>
       </c>
       <c r="G1233" t="s">
+        <v>133</v>
+      </c>
+      <c r="H1233" t="s">
         <v>134</v>
-      </c>
-      <c r="H1233" t="s">
-        <v>135</v>
       </c>
       <c r="I1233" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1233,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -44394,7 +44391,7 @@
         <v>28</v>
       </c>
       <c r="D1234" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1234">
         <v>2</v>
@@ -44403,10 +44400,10 @@
         <v>69</v>
       </c>
       <c r="G1234" t="s">
+        <v>133</v>
+      </c>
+      <c r="H1234" t="s">
         <v>134</v>
-      </c>
-      <c r="H1234" t="s">
-        <v>135</v>
       </c>
       <c r="I1234" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1234,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -44424,7 +44421,7 @@
         <v>29</v>
       </c>
       <c r="D1235" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1235">
         <v>2</v>
@@ -44433,10 +44430,10 @@
         <v>69</v>
       </c>
       <c r="G1235" t="s">
+        <v>133</v>
+      </c>
+      <c r="H1235" t="s">
         <v>134</v>
-      </c>
-      <c r="H1235" t="s">
-        <v>135</v>
       </c>
       <c r="I1235" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1235,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -44454,7 +44451,7 @@
         <v>87</v>
       </c>
       <c r="D1236" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1236">
         <v>2</v>
@@ -44463,10 +44460,10 @@
         <v>69</v>
       </c>
       <c r="G1236" t="s">
+        <v>133</v>
+      </c>
+      <c r="H1236" t="s">
         <v>134</v>
-      </c>
-      <c r="H1236" t="s">
-        <v>135</v>
       </c>
       <c r="I1236" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1236,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -44484,7 +44481,7 @@
         <v>88</v>
       </c>
       <c r="D1237" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1237">
         <v>2</v>
@@ -44493,10 +44490,10 @@
         <v>69</v>
       </c>
       <c r="G1237" t="s">
+        <v>133</v>
+      </c>
+      <c r="H1237" t="s">
         <v>134</v>
-      </c>
-      <c r="H1237" t="s">
-        <v>135</v>
       </c>
       <c r="I1237" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1237,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -44511,10 +44508,10 @@
         <v>127</v>
       </c>
       <c r="C1238" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D1238" t="s">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="E1238">
         <v>2</v>
@@ -44523,10 +44520,10 @@
         <v>69</v>
       </c>
       <c r="G1238" t="s">
+        <v>133</v>
+      </c>
+      <c r="H1238" t="s">
         <v>134</v>
-      </c>
-      <c r="H1238" t="s">
-        <v>135</v>
       </c>
       <c r="I1238" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1238,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -44541,10 +44538,10 @@
         <v>127</v>
       </c>
       <c r="C1239" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D1239" t="s">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="E1239">
         <v>2</v>
@@ -44553,10 +44550,10 @@
         <v>69</v>
       </c>
       <c r="G1239" t="s">
+        <v>133</v>
+      </c>
+      <c r="H1239" t="s">
         <v>134</v>
-      </c>
-      <c r="H1239" t="s">
-        <v>135</v>
       </c>
       <c r="I1239" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1239,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -44571,10 +44568,10 @@
         <v>127</v>
       </c>
       <c r="C1240" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D1240" t="s">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="E1240" s="2">
         <v>1</v>
@@ -44583,10 +44580,10 @@
         <v>72</v>
       </c>
       <c r="G1240" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H1240" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I1240" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1240,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -44601,10 +44598,10 @@
         <v>127</v>
       </c>
       <c r="C1241" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D1241" t="s">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="E1241" s="2">
         <v>1</v>
@@ -44613,10 +44610,10 @@
         <v>72</v>
       </c>
       <c r="G1241" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H1241" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I1241" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1241,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -44634,7 +44631,7 @@
         <v>28</v>
       </c>
       <c r="D1242" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1242">
         <v>2</v>
@@ -44643,10 +44640,10 @@
         <v>78</v>
       </c>
       <c r="G1242" t="s">
+        <v>137</v>
+      </c>
+      <c r="H1242" t="s">
         <v>138</v>
-      </c>
-      <c r="H1242" t="s">
-        <v>139</v>
       </c>
       <c r="I1242" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1242,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -44664,7 +44661,7 @@
         <v>29</v>
       </c>
       <c r="D1243" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1243">
         <v>2</v>
@@ -44673,10 +44670,10 @@
         <v>78</v>
       </c>
       <c r="G1243" t="s">
+        <v>137</v>
+      </c>
+      <c r="H1243" t="s">
         <v>138</v>
-      </c>
-      <c r="H1243" t="s">
-        <v>139</v>
       </c>
       <c r="I1243" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1243,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -44694,7 +44691,7 @@
         <v>87</v>
       </c>
       <c r="D1244" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1244">
         <v>2</v>
@@ -44703,10 +44700,10 @@
         <v>78</v>
       </c>
       <c r="G1244" t="s">
+        <v>137</v>
+      </c>
+      <c r="H1244" t="s">
         <v>138</v>
-      </c>
-      <c r="H1244" t="s">
-        <v>139</v>
       </c>
       <c r="I1244" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1244,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -44724,7 +44721,7 @@
         <v>88</v>
       </c>
       <c r="D1245" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1245">
         <v>2</v>
@@ -44733,10 +44730,10 @@
         <v>78</v>
       </c>
       <c r="G1245" t="s">
+        <v>137</v>
+      </c>
+      <c r="H1245" t="s">
         <v>138</v>
-      </c>
-      <c r="H1245" t="s">
-        <v>139</v>
       </c>
       <c r="I1245" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1245,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -44751,10 +44748,10 @@
         <v>127</v>
       </c>
       <c r="C1246" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D1246" t="s">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="E1246">
         <v>2</v>
@@ -44763,10 +44760,10 @@
         <v>78</v>
       </c>
       <c r="G1246" t="s">
+        <v>137</v>
+      </c>
+      <c r="H1246" t="s">
         <v>138</v>
-      </c>
-      <c r="H1246" t="s">
-        <v>139</v>
       </c>
       <c r="I1246" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1246,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -44781,10 +44778,10 @@
         <v>127</v>
       </c>
       <c r="C1247" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D1247" t="s">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="E1247">
         <v>2</v>
@@ -44793,10 +44790,10 @@
         <v>78</v>
       </c>
       <c r="G1247" t="s">
+        <v>137</v>
+      </c>
+      <c r="H1247" t="s">
         <v>138</v>
-      </c>
-      <c r="H1247" t="s">
-        <v>139</v>
       </c>
       <c r="I1247" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1247,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -44814,7 +44811,7 @@
         <v>28</v>
       </c>
       <c r="D1248" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1248" s="2">
         <v>1</v>
@@ -44823,10 +44820,10 @@
         <v>80</v>
       </c>
       <c r="G1248" t="s">
+        <v>135</v>
+      </c>
+      <c r="H1248" t="s">
         <v>136</v>
-      </c>
-      <c r="H1248" t="s">
-        <v>137</v>
       </c>
       <c r="I1248" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1248,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -44844,7 +44841,7 @@
         <v>29</v>
       </c>
       <c r="D1249" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1249">
         <v>1</v>
@@ -44853,10 +44850,10 @@
         <v>80</v>
       </c>
       <c r="G1249" t="s">
+        <v>135</v>
+      </c>
+      <c r="H1249" t="s">
         <v>136</v>
-      </c>
-      <c r="H1249" t="s">
-        <v>137</v>
       </c>
       <c r="I1249" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1249,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -44874,7 +44871,7 @@
         <v>87</v>
       </c>
       <c r="D1250" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1250">
         <v>1</v>
@@ -44883,10 +44880,10 @@
         <v>80</v>
       </c>
       <c r="G1250" t="s">
+        <v>135</v>
+      </c>
+      <c r="H1250" t="s">
         <v>136</v>
-      </c>
-      <c r="H1250" t="s">
-        <v>137</v>
       </c>
       <c r="I1250" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1250,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -44904,7 +44901,7 @@
         <v>88</v>
       </c>
       <c r="D1251" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1251">
         <v>1</v>
@@ -44913,10 +44910,10 @@
         <v>80</v>
       </c>
       <c r="G1251" t="s">
+        <v>135</v>
+      </c>
+      <c r="H1251" t="s">
         <v>136</v>
-      </c>
-      <c r="H1251" t="s">
-        <v>137</v>
       </c>
       <c r="I1251" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1251,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -44931,10 +44928,10 @@
         <v>127</v>
       </c>
       <c r="C1252" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D1252" t="s">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="E1252" s="2">
         <v>1</v>
@@ -44943,10 +44940,10 @@
         <v>80</v>
       </c>
       <c r="G1252" t="s">
+        <v>135</v>
+      </c>
+      <c r="H1252" t="s">
         <v>136</v>
-      </c>
-      <c r="H1252" t="s">
-        <v>137</v>
       </c>
       <c r="I1252" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1252,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -44961,10 +44958,10 @@
         <v>127</v>
       </c>
       <c r="C1253" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D1253" t="s">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="E1253">
         <v>1</v>
@@ -44973,10 +44970,10 @@
         <v>80</v>
       </c>
       <c r="G1253" t="s">
+        <v>135</v>
+      </c>
+      <c r="H1253" t="s">
         <v>136</v>
-      </c>
-      <c r="H1253" t="s">
-        <v>137</v>
       </c>
       <c r="I1253" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1253,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -44994,19 +44991,19 @@
         <v>28</v>
       </c>
       <c r="D1254" t="s">
+        <v>127</v>
+      </c>
+      <c r="E1254" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1254" t="s">
+        <v>139</v>
+      </c>
+      <c r="G1254" t="s">
         <v>131</v>
       </c>
-      <c r="E1254" s="2">
-        <v>1</v>
-      </c>
-      <c r="F1254" t="s">
-        <v>140</v>
-      </c>
-      <c r="G1254" t="s">
+      <c r="H1254" t="s">
         <v>132</v>
-      </c>
-      <c r="H1254" t="s">
-        <v>133</v>
       </c>
       <c r="I1254" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1254,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -45024,19 +45021,19 @@
         <v>29</v>
       </c>
       <c r="D1255" t="s">
+        <v>127</v>
+      </c>
+      <c r="E1255">
+        <v>1</v>
+      </c>
+      <c r="F1255" t="s">
+        <v>139</v>
+      </c>
+      <c r="G1255" t="s">
         <v>131</v>
       </c>
-      <c r="E1255">
-        <v>1</v>
-      </c>
-      <c r="F1255" t="s">
-        <v>140</v>
-      </c>
-      <c r="G1255" t="s">
+      <c r="H1255" t="s">
         <v>132</v>
-      </c>
-      <c r="H1255" t="s">
-        <v>133</v>
       </c>
       <c r="I1255" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1255,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -45054,19 +45051,19 @@
         <v>87</v>
       </c>
       <c r="D1256" t="s">
+        <v>127</v>
+      </c>
+      <c r="E1256">
+        <v>1</v>
+      </c>
+      <c r="F1256" t="s">
+        <v>139</v>
+      </c>
+      <c r="G1256" t="s">
         <v>131</v>
       </c>
-      <c r="E1256">
-        <v>1</v>
-      </c>
-      <c r="F1256" t="s">
-        <v>140</v>
-      </c>
-      <c r="G1256" t="s">
+      <c r="H1256" t="s">
         <v>132</v>
-      </c>
-      <c r="H1256" t="s">
-        <v>133</v>
       </c>
       <c r="I1256" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1256,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -45084,19 +45081,19 @@
         <v>88</v>
       </c>
       <c r="D1257" t="s">
+        <v>127</v>
+      </c>
+      <c r="E1257">
+        <v>1</v>
+      </c>
+      <c r="F1257" t="s">
+        <v>139</v>
+      </c>
+      <c r="G1257" t="s">
         <v>131</v>
       </c>
-      <c r="E1257">
-        <v>1</v>
-      </c>
-      <c r="F1257" t="s">
-        <v>140</v>
-      </c>
-      <c r="G1257" t="s">
+      <c r="H1257" t="s">
         <v>132</v>
-      </c>
-      <c r="H1257" t="s">
-        <v>133</v>
       </c>
       <c r="I1257" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1257,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -45114,7 +45111,7 @@
         <v>28</v>
       </c>
       <c r="D1258" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1258">
         <v>2</v>
@@ -45123,10 +45120,10 @@
         <v>84</v>
       </c>
       <c r="G1258" t="s">
+        <v>131</v>
+      </c>
+      <c r="H1258" t="s">
         <v>132</v>
-      </c>
-      <c r="H1258" t="s">
-        <v>133</v>
       </c>
       <c r="I1258" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1258,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -45144,7 +45141,7 @@
         <v>29</v>
       </c>
       <c r="D1259" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1259">
         <v>2</v>
@@ -45153,10 +45150,10 @@
         <v>84</v>
       </c>
       <c r="G1259" t="s">
+        <v>131</v>
+      </c>
+      <c r="H1259" t="s">
         <v>132</v>
-      </c>
-      <c r="H1259" t="s">
-        <v>133</v>
       </c>
       <c r="I1259" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1259,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -45174,7 +45171,7 @@
         <v>87</v>
       </c>
       <c r="D1260" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1260">
         <v>2</v>
@@ -45183,10 +45180,10 @@
         <v>84</v>
       </c>
       <c r="G1260" t="s">
+        <v>131</v>
+      </c>
+      <c r="H1260" t="s">
         <v>132</v>
-      </c>
-      <c r="H1260" t="s">
-        <v>133</v>
       </c>
       <c r="I1260" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1260,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -45204,7 +45201,7 @@
         <v>88</v>
       </c>
       <c r="D1261" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1261">
         <v>2</v>
@@ -45213,10 +45210,10 @@
         <v>84</v>
       </c>
       <c r="G1261" t="s">
+        <v>131</v>
+      </c>
+      <c r="H1261" t="s">
         <v>132</v>
-      </c>
-      <c r="H1261" t="s">
-        <v>133</v>
       </c>
       <c r="I1261" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1261,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -45231,10 +45228,10 @@
         <v>127</v>
       </c>
       <c r="C1262" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D1262" t="s">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="E1262">
         <v>2</v>
@@ -45243,10 +45240,10 @@
         <v>84</v>
       </c>
       <c r="G1262" t="s">
+        <v>131</v>
+      </c>
+      <c r="H1262" t="s">
         <v>132</v>
-      </c>
-      <c r="H1262" t="s">
-        <v>133</v>
       </c>
       <c r="I1262" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1262,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -45261,10 +45258,10 @@
         <v>127</v>
       </c>
       <c r="C1263" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D1263" t="s">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="E1263">
         <v>2</v>
@@ -45273,10 +45270,10 @@
         <v>84</v>
       </c>
       <c r="G1263" t="s">
+        <v>131</v>
+      </c>
+      <c r="H1263" t="s">
         <v>132</v>
-      </c>
-      <c r="H1263" t="s">
-        <v>133</v>
       </c>
       <c r="I1263" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1263,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -45291,10 +45288,10 @@
         <v>127</v>
       </c>
       <c r="C1264" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D1264" t="s">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="E1264" s="2">
         <v>1</v>
@@ -45303,10 +45300,10 @@
         <v>84</v>
       </c>
       <c r="G1264" t="s">
+        <v>131</v>
+      </c>
+      <c r="H1264" t="s">
         <v>132</v>
-      </c>
-      <c r="H1264" t="s">
-        <v>133</v>
       </c>
       <c r="I1264" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1264,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -45321,10 +45318,10 @@
         <v>127</v>
       </c>
       <c r="C1265" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D1265" t="s">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="E1265">
         <v>1</v>
@@ -45333,10 +45330,10 @@
         <v>84</v>
       </c>
       <c r="G1265" t="s">
+        <v>131</v>
+      </c>
+      <c r="H1265" t="s">
         <v>132</v>
-      </c>
-      <c r="H1265" t="s">
-        <v>133</v>
       </c>
       <c r="I1265" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1265,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -45354,7 +45351,7 @@
         <v>28</v>
       </c>
       <c r="D1266" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1266" s="2">
         <v>1</v>
@@ -45363,10 +45360,10 @@
         <v>83</v>
       </c>
       <c r="G1266" t="s">
+        <v>131</v>
+      </c>
+      <c r="H1266" t="s">
         <v>132</v>
-      </c>
-      <c r="H1266" t="s">
-        <v>133</v>
       </c>
       <c r="I1266" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1266,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -45384,7 +45381,7 @@
         <v>29</v>
       </c>
       <c r="D1267" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1267">
         <v>1</v>
@@ -45393,10 +45390,10 @@
         <v>83</v>
       </c>
       <c r="G1267" t="s">
+        <v>131</v>
+      </c>
+      <c r="H1267" t="s">
         <v>132</v>
-      </c>
-      <c r="H1267" t="s">
-        <v>133</v>
       </c>
       <c r="I1267" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1267,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -45414,7 +45411,7 @@
         <v>87</v>
       </c>
       <c r="D1268" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1268">
         <v>1</v>
@@ -45423,10 +45420,10 @@
         <v>83</v>
       </c>
       <c r="G1268" t="s">
+        <v>131</v>
+      </c>
+      <c r="H1268" t="s">
         <v>132</v>
-      </c>
-      <c r="H1268" t="s">
-        <v>133</v>
       </c>
       <c r="I1268" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1268,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -45444,7 +45441,7 @@
         <v>88</v>
       </c>
       <c r="D1269" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1269">
         <v>1</v>
@@ -45453,10 +45450,10 @@
         <v>83</v>
       </c>
       <c r="G1269" t="s">
+        <v>131</v>
+      </c>
+      <c r="H1269" t="s">
         <v>132</v>
-      </c>
-      <c r="H1269" t="s">
-        <v>133</v>
       </c>
       <c r="I1269" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1269,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -45471,10 +45468,10 @@
         <v>127</v>
       </c>
       <c r="C1270" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D1270" t="s">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="E1270" s="2">
         <v>1</v>
@@ -45483,10 +45480,10 @@
         <v>83</v>
       </c>
       <c r="G1270" t="s">
+        <v>131</v>
+      </c>
+      <c r="H1270" t="s">
         <v>132</v>
-      </c>
-      <c r="H1270" t="s">
-        <v>133</v>
       </c>
       <c r="I1270" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1270,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -45501,10 +45498,10 @@
         <v>127</v>
       </c>
       <c r="C1271" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D1271" t="s">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="E1271">
         <v>1</v>
@@ -45513,10 +45510,10 @@
         <v>83</v>
       </c>
       <c r="G1271" t="s">
+        <v>131</v>
+      </c>
+      <c r="H1271" t="s">
         <v>132</v>
-      </c>
-      <c r="H1271" t="s">
-        <v>133</v>
       </c>
       <c r="I1271" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1271,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -45534,7 +45531,7 @@
         <v>28</v>
       </c>
       <c r="D1272" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1272">
         <v>2</v>
@@ -45543,10 +45540,10 @@
         <v>86</v>
       </c>
       <c r="G1272" t="s">
+        <v>131</v>
+      </c>
+      <c r="H1272" t="s">
         <v>132</v>
-      </c>
-      <c r="H1272" t="s">
-        <v>133</v>
       </c>
       <c r="I1272" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1272,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -45564,7 +45561,7 @@
         <v>29</v>
       </c>
       <c r="D1273" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1273">
         <v>2</v>
@@ -45573,10 +45570,10 @@
         <v>86</v>
       </c>
       <c r="G1273" t="s">
+        <v>131</v>
+      </c>
+      <c r="H1273" t="s">
         <v>132</v>
-      </c>
-      <c r="H1273" t="s">
-        <v>133</v>
       </c>
       <c r="I1273" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1273,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -45594,7 +45591,7 @@
         <v>87</v>
       </c>
       <c r="D1274" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1274">
         <v>2</v>
@@ -45603,10 +45600,10 @@
         <v>86</v>
       </c>
       <c r="G1274" t="s">
+        <v>131</v>
+      </c>
+      <c r="H1274" t="s">
         <v>132</v>
-      </c>
-      <c r="H1274" t="s">
-        <v>133</v>
       </c>
       <c r="I1274" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1274,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -45624,7 +45621,7 @@
         <v>88</v>
       </c>
       <c r="D1275" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1275">
         <v>2</v>
@@ -45633,10 +45630,10 @@
         <v>86</v>
       </c>
       <c r="G1275" t="s">
+        <v>131</v>
+      </c>
+      <c r="H1275" t="s">
         <v>132</v>
-      </c>
-      <c r="H1275" t="s">
-        <v>133</v>
       </c>
       <c r="I1275" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1275,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -45651,10 +45648,10 @@
         <v>127</v>
       </c>
       <c r="C1276" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D1276" t="s">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="E1276">
         <v>2</v>
@@ -45663,10 +45660,10 @@
         <v>86</v>
       </c>
       <c r="G1276" t="s">
+        <v>131</v>
+      </c>
+      <c r="H1276" t="s">
         <v>132</v>
-      </c>
-      <c r="H1276" t="s">
-        <v>133</v>
       </c>
       <c r="I1276" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1276,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -45681,10 +45678,10 @@
         <v>127</v>
       </c>
       <c r="C1277" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D1277" t="s">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="E1277">
         <v>2</v>
@@ -45693,10 +45690,10 @@
         <v>86</v>
       </c>
       <c r="G1277" t="s">
+        <v>131</v>
+      </c>
+      <c r="H1277" t="s">
         <v>132</v>
-      </c>
-      <c r="H1277" t="s">
-        <v>133</v>
       </c>
       <c r="I1277" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1277,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -45714,7 +45711,7 @@
         <v>28</v>
       </c>
       <c r="D1278" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1278">
         <v>1</v>
@@ -45723,10 +45720,10 @@
         <v>38</v>
       </c>
       <c r="G1278" t="s">
+        <v>131</v>
+      </c>
+      <c r="H1278" t="s">
         <v>132</v>
-      </c>
-      <c r="H1278" t="s">
-        <v>133</v>
       </c>
       <c r="I1278" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1278,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -45744,19 +45741,19 @@
         <v>28</v>
       </c>
       <c r="D1279" t="s">
+        <v>127</v>
+      </c>
+      <c r="E1279">
+        <v>1</v>
+      </c>
+      <c r="F1279" t="s">
+        <v>142</v>
+      </c>
+      <c r="G1279" t="s">
         <v>131</v>
       </c>
-      <c r="E1279">
-        <v>1</v>
-      </c>
-      <c r="F1279" t="s">
-        <v>143</v>
-      </c>
-      <c r="G1279" t="s">
+      <c r="H1279" t="s">
         <v>132</v>
-      </c>
-      <c r="H1279" t="s">
-        <v>133</v>
       </c>
       <c r="I1279" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1279,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -45774,7 +45771,7 @@
         <v>28</v>
       </c>
       <c r="D1280" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1280">
         <v>1</v>
@@ -45783,10 +45780,10 @@
         <v>37</v>
       </c>
       <c r="G1280" t="s">
+        <v>140</v>
+      </c>
+      <c r="H1280" t="s">
         <v>141</v>
-      </c>
-      <c r="H1280" t="s">
-        <v>142</v>
       </c>
       <c r="I1280" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1280,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -45804,19 +45801,19 @@
         <v>28</v>
       </c>
       <c r="D1281" t="s">
+        <v>127</v>
+      </c>
+      <c r="E1281">
+        <v>2</v>
+      </c>
+      <c r="F1281" t="s">
+        <v>143</v>
+      </c>
+      <c r="G1281" t="s">
         <v>131</v>
       </c>
-      <c r="E1281">
-        <v>2</v>
-      </c>
-      <c r="F1281" t="s">
-        <v>144</v>
-      </c>
-      <c r="G1281" t="s">
+      <c r="H1281" t="s">
         <v>132</v>
-      </c>
-      <c r="H1281" t="s">
-        <v>133</v>
       </c>
       <c r="I1281" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1281,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -45834,7 +45831,7 @@
         <v>28</v>
       </c>
       <c r="D1282" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1282">
         <v>2</v>
@@ -45843,10 +45840,10 @@
         <v>33</v>
       </c>
       <c r="G1282" t="s">
+        <v>140</v>
+      </c>
+      <c r="H1282" t="s">
         <v>141</v>
-      </c>
-      <c r="H1282" t="s">
-        <v>142</v>
       </c>
       <c r="I1282" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1282,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -45864,7 +45861,7 @@
         <v>28</v>
       </c>
       <c r="D1283" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1283">
         <v>2</v>
@@ -45873,10 +45870,10 @@
         <v>35</v>
       </c>
       <c r="G1283" t="s">
+        <v>131</v>
+      </c>
+      <c r="H1283" t="s">
         <v>132</v>
-      </c>
-      <c r="H1283" t="s">
-        <v>133</v>
       </c>
       <c r="I1283" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1283,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -45894,7 +45891,7 @@
         <v>29</v>
       </c>
       <c r="D1284" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1284">
         <v>1</v>
@@ -45903,10 +45900,10 @@
         <v>38</v>
       </c>
       <c r="G1284" t="s">
+        <v>131</v>
+      </c>
+      <c r="H1284" t="s">
         <v>132</v>
-      </c>
-      <c r="H1284" t="s">
-        <v>133</v>
       </c>
       <c r="I1284" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1284,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -45924,19 +45921,19 @@
         <v>29</v>
       </c>
       <c r="D1285" t="s">
+        <v>127</v>
+      </c>
+      <c r="E1285">
+        <v>1</v>
+      </c>
+      <c r="F1285" t="s">
+        <v>142</v>
+      </c>
+      <c r="G1285" t="s">
         <v>131</v>
       </c>
-      <c r="E1285">
-        <v>1</v>
-      </c>
-      <c r="F1285" t="s">
-        <v>143</v>
-      </c>
-      <c r="G1285" t="s">
+      <c r="H1285" t="s">
         <v>132</v>
-      </c>
-      <c r="H1285" t="s">
-        <v>133</v>
       </c>
       <c r="I1285" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1285,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -45954,7 +45951,7 @@
         <v>29</v>
       </c>
       <c r="D1286" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1286">
         <v>1</v>
@@ -45963,10 +45960,10 @@
         <v>37</v>
       </c>
       <c r="G1286" t="s">
+        <v>140</v>
+      </c>
+      <c r="H1286" t="s">
         <v>141</v>
-      </c>
-      <c r="H1286" t="s">
-        <v>142</v>
       </c>
       <c r="I1286" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1286,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -45984,19 +45981,19 @@
         <v>29</v>
       </c>
       <c r="D1287" t="s">
+        <v>127</v>
+      </c>
+      <c r="E1287">
+        <v>2</v>
+      </c>
+      <c r="F1287" t="s">
+        <v>143</v>
+      </c>
+      <c r="G1287" t="s">
         <v>131</v>
       </c>
-      <c r="E1287">
-        <v>2</v>
-      </c>
-      <c r="F1287" t="s">
-        <v>144</v>
-      </c>
-      <c r="G1287" t="s">
+      <c r="H1287" t="s">
         <v>132</v>
-      </c>
-      <c r="H1287" t="s">
-        <v>133</v>
       </c>
       <c r="I1287" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1287,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -46014,7 +46011,7 @@
         <v>29</v>
       </c>
       <c r="D1288" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1288">
         <v>2</v>
@@ -46023,10 +46020,10 @@
         <v>33</v>
       </c>
       <c r="G1288" t="s">
+        <v>140</v>
+      </c>
+      <c r="H1288" t="s">
         <v>141</v>
-      </c>
-      <c r="H1288" t="s">
-        <v>142</v>
       </c>
       <c r="I1288" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1288,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -46044,7 +46041,7 @@
         <v>29</v>
       </c>
       <c r="D1289" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1289">
         <v>2</v>
@@ -46053,10 +46050,10 @@
         <v>35</v>
       </c>
       <c r="G1289" t="s">
+        <v>131</v>
+      </c>
+      <c r="H1289" t="s">
         <v>132</v>
-      </c>
-      <c r="H1289" t="s">
-        <v>133</v>
       </c>
       <c r="I1289" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1289,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -46074,7 +46071,7 @@
         <v>87</v>
       </c>
       <c r="D1290" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1290">
         <v>1</v>
@@ -46083,10 +46080,10 @@
         <v>38</v>
       </c>
       <c r="G1290" t="s">
+        <v>131</v>
+      </c>
+      <c r="H1290" t="s">
         <v>132</v>
-      </c>
-      <c r="H1290" t="s">
-        <v>133</v>
       </c>
       <c r="I1290" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1290,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -46104,19 +46101,19 @@
         <v>87</v>
       </c>
       <c r="D1291" t="s">
+        <v>127</v>
+      </c>
+      <c r="E1291">
+        <v>1</v>
+      </c>
+      <c r="F1291" t="s">
+        <v>142</v>
+      </c>
+      <c r="G1291" t="s">
         <v>131</v>
       </c>
-      <c r="E1291">
-        <v>1</v>
-      </c>
-      <c r="F1291" t="s">
-        <v>143</v>
-      </c>
-      <c r="G1291" t="s">
+      <c r="H1291" t="s">
         <v>132</v>
-      </c>
-      <c r="H1291" t="s">
-        <v>133</v>
       </c>
       <c r="I1291" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1291,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -46134,7 +46131,7 @@
         <v>87</v>
       </c>
       <c r="D1292" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1292">
         <v>1</v>
@@ -46143,10 +46140,10 @@
         <v>37</v>
       </c>
       <c r="G1292" t="s">
+        <v>140</v>
+      </c>
+      <c r="H1292" t="s">
         <v>141</v>
-      </c>
-      <c r="H1292" t="s">
-        <v>142</v>
       </c>
       <c r="I1292" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1292,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -46164,19 +46161,19 @@
         <v>87</v>
       </c>
       <c r="D1293" t="s">
+        <v>127</v>
+      </c>
+      <c r="E1293">
+        <v>2</v>
+      </c>
+      <c r="F1293" t="s">
+        <v>143</v>
+      </c>
+      <c r="G1293" t="s">
         <v>131</v>
       </c>
-      <c r="E1293">
-        <v>2</v>
-      </c>
-      <c r="F1293" t="s">
-        <v>144</v>
-      </c>
-      <c r="G1293" t="s">
+      <c r="H1293" t="s">
         <v>132</v>
-      </c>
-      <c r="H1293" t="s">
-        <v>133</v>
       </c>
       <c r="I1293" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1293,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -46194,7 +46191,7 @@
         <v>87</v>
       </c>
       <c r="D1294" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1294">
         <v>2</v>
@@ -46203,10 +46200,10 @@
         <v>33</v>
       </c>
       <c r="G1294" t="s">
+        <v>140</v>
+      </c>
+      <c r="H1294" t="s">
         <v>141</v>
-      </c>
-      <c r="H1294" t="s">
-        <v>142</v>
       </c>
       <c r="I1294" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1294,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -46224,7 +46221,7 @@
         <v>87</v>
       </c>
       <c r="D1295" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1295">
         <v>2</v>
@@ -46233,10 +46230,10 @@
         <v>35</v>
       </c>
       <c r="G1295" t="s">
+        <v>131</v>
+      </c>
+      <c r="H1295" t="s">
         <v>132</v>
-      </c>
-      <c r="H1295" t="s">
-        <v>133</v>
       </c>
       <c r="I1295" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1295,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -46254,7 +46251,7 @@
         <v>88</v>
       </c>
       <c r="D1296" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1296">
         <v>1</v>
@@ -46263,10 +46260,10 @@
         <v>38</v>
       </c>
       <c r="G1296" t="s">
+        <v>131</v>
+      </c>
+      <c r="H1296" t="s">
         <v>132</v>
-      </c>
-      <c r="H1296" t="s">
-        <v>133</v>
       </c>
       <c r="I1296" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1296,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -46284,19 +46281,19 @@
         <v>88</v>
       </c>
       <c r="D1297" t="s">
+        <v>127</v>
+      </c>
+      <c r="E1297">
+        <v>1</v>
+      </c>
+      <c r="F1297" t="s">
+        <v>142</v>
+      </c>
+      <c r="G1297" t="s">
         <v>131</v>
       </c>
-      <c r="E1297">
-        <v>1</v>
-      </c>
-      <c r="F1297" t="s">
-        <v>143</v>
-      </c>
-      <c r="G1297" t="s">
+      <c r="H1297" t="s">
         <v>132</v>
-      </c>
-      <c r="H1297" t="s">
-        <v>133</v>
       </c>
       <c r="I1297" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1297,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -46314,7 +46311,7 @@
         <v>88</v>
       </c>
       <c r="D1298" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1298">
         <v>1</v>
@@ -46323,10 +46320,10 @@
         <v>37</v>
       </c>
       <c r="G1298" t="s">
+        <v>140</v>
+      </c>
+      <c r="H1298" t="s">
         <v>141</v>
-      </c>
-      <c r="H1298" t="s">
-        <v>142</v>
       </c>
       <c r="I1298" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1298,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -46344,19 +46341,19 @@
         <v>88</v>
       </c>
       <c r="D1299" t="s">
+        <v>127</v>
+      </c>
+      <c r="E1299">
+        <v>2</v>
+      </c>
+      <c r="F1299" t="s">
+        <v>143</v>
+      </c>
+      <c r="G1299" t="s">
         <v>131</v>
       </c>
-      <c r="E1299">
-        <v>2</v>
-      </c>
-      <c r="F1299" t="s">
-        <v>144</v>
-      </c>
-      <c r="G1299" t="s">
+      <c r="H1299" t="s">
         <v>132</v>
-      </c>
-      <c r="H1299" t="s">
-        <v>133</v>
       </c>
       <c r="I1299" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1299,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -46374,7 +46371,7 @@
         <v>88</v>
       </c>
       <c r="D1300" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1300">
         <v>2</v>
@@ -46383,10 +46380,10 @@
         <v>33</v>
       </c>
       <c r="G1300" t="s">
+        <v>140</v>
+      </c>
+      <c r="H1300" t="s">
         <v>141</v>
-      </c>
-      <c r="H1300" t="s">
-        <v>142</v>
       </c>
       <c r="I1300" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1300,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -46404,7 +46401,7 @@
         <v>88</v>
       </c>
       <c r="D1301" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1301">
         <v>2</v>
@@ -46413,10 +46410,10 @@
         <v>35</v>
       </c>
       <c r="G1301" t="s">
+        <v>131</v>
+      </c>
+      <c r="H1301" t="s">
         <v>132</v>
-      </c>
-      <c r="H1301" t="s">
-        <v>133</v>
       </c>
       <c r="I1301" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1301,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -46431,10 +46428,10 @@
         <v>127</v>
       </c>
       <c r="C1302" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D1302" t="s">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="E1302">
         <v>1</v>
@@ -46443,10 +46440,10 @@
         <v>38</v>
       </c>
       <c r="G1302" t="s">
+        <v>131</v>
+      </c>
+      <c r="H1302" t="s">
         <v>132</v>
-      </c>
-      <c r="H1302" t="s">
-        <v>133</v>
       </c>
       <c r="I1302" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1302,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -46461,22 +46458,22 @@
         <v>127</v>
       </c>
       <c r="C1303" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D1303" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1303">
+        <v>1</v>
+      </c>
+      <c r="F1303" t="s">
+        <v>142</v>
+      </c>
+      <c r="G1303" t="s">
         <v>131</v>
       </c>
-      <c r="E1303">
-        <v>1</v>
-      </c>
-      <c r="F1303" t="s">
-        <v>143</v>
-      </c>
-      <c r="G1303" t="s">
+      <c r="H1303" t="s">
         <v>132</v>
-      </c>
-      <c r="H1303" t="s">
-        <v>133</v>
       </c>
       <c r="I1303" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1303,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -46491,10 +46488,10 @@
         <v>127</v>
       </c>
       <c r="C1304" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D1304" t="s">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="E1304">
         <v>1</v>
@@ -46503,10 +46500,10 @@
         <v>37</v>
       </c>
       <c r="G1304" t="s">
+        <v>140</v>
+      </c>
+      <c r="H1304" t="s">
         <v>141</v>
-      </c>
-      <c r="H1304" t="s">
-        <v>142</v>
       </c>
       <c r="I1304" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1304,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -46521,22 +46518,22 @@
         <v>127</v>
       </c>
       <c r="C1305" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D1305" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1305">
+        <v>2</v>
+      </c>
+      <c r="F1305" t="s">
+        <v>143</v>
+      </c>
+      <c r="G1305" t="s">
         <v>131</v>
       </c>
-      <c r="E1305">
-        <v>2</v>
-      </c>
-      <c r="F1305" t="s">
-        <v>144</v>
-      </c>
-      <c r="G1305" t="s">
+      <c r="H1305" t="s">
         <v>132</v>
-      </c>
-      <c r="H1305" t="s">
-        <v>133</v>
       </c>
       <c r="I1305" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1305,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -46551,10 +46548,10 @@
         <v>127</v>
       </c>
       <c r="C1306" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D1306" t="s">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="E1306">
         <v>2</v>
@@ -46563,10 +46560,10 @@
         <v>33</v>
       </c>
       <c r="G1306" t="s">
+        <v>140</v>
+      </c>
+      <c r="H1306" t="s">
         <v>141</v>
-      </c>
-      <c r="H1306" t="s">
-        <v>142</v>
       </c>
       <c r="I1306" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1306,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -46581,10 +46578,10 @@
         <v>127</v>
       </c>
       <c r="C1307" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D1307" t="s">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="E1307">
         <v>2</v>
@@ -46593,10 +46590,10 @@
         <v>35</v>
       </c>
       <c r="G1307" t="s">
+        <v>131</v>
+      </c>
+      <c r="H1307" t="s">
         <v>132</v>
-      </c>
-      <c r="H1307" t="s">
-        <v>133</v>
       </c>
       <c r="I1307" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1307,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -46611,10 +46608,10 @@
         <v>127</v>
       </c>
       <c r="C1308" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D1308" t="s">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="E1308">
         <v>1</v>
@@ -46623,10 +46620,10 @@
         <v>38</v>
       </c>
       <c r="G1308" t="s">
+        <v>131</v>
+      </c>
+      <c r="H1308" t="s">
         <v>132</v>
-      </c>
-      <c r="H1308" t="s">
-        <v>133</v>
       </c>
       <c r="I1308" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1308,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -46641,22 +46638,22 @@
         <v>127</v>
       </c>
       <c r="C1309" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D1309" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1309">
+        <v>1</v>
+      </c>
+      <c r="F1309" t="s">
+        <v>142</v>
+      </c>
+      <c r="G1309" t="s">
         <v>131</v>
       </c>
-      <c r="E1309">
-        <v>1</v>
-      </c>
-      <c r="F1309" t="s">
-        <v>143</v>
-      </c>
-      <c r="G1309" t="s">
+      <c r="H1309" t="s">
         <v>132</v>
-      </c>
-      <c r="H1309" t="s">
-        <v>133</v>
       </c>
       <c r="I1309" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1309,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -46671,10 +46668,10 @@
         <v>127</v>
       </c>
       <c r="C1310" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D1310" t="s">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="E1310">
         <v>1</v>
@@ -46683,10 +46680,10 @@
         <v>37</v>
       </c>
       <c r="G1310" t="s">
+        <v>140</v>
+      </c>
+      <c r="H1310" t="s">
         <v>141</v>
-      </c>
-      <c r="H1310" t="s">
-        <v>142</v>
       </c>
       <c r="I1310" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1310,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -46701,22 +46698,22 @@
         <v>127</v>
       </c>
       <c r="C1311" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D1311" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1311">
+        <v>2</v>
+      </c>
+      <c r="F1311" t="s">
+        <v>143</v>
+      </c>
+      <c r="G1311" t="s">
         <v>131</v>
       </c>
-      <c r="E1311">
-        <v>2</v>
-      </c>
-      <c r="F1311" t="s">
-        <v>144</v>
-      </c>
-      <c r="G1311" t="s">
+      <c r="H1311" t="s">
         <v>132</v>
-      </c>
-      <c r="H1311" t="s">
-        <v>133</v>
       </c>
       <c r="I1311" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1311,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -46731,10 +46728,10 @@
         <v>127</v>
       </c>
       <c r="C1312" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D1312" t="s">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="E1312">
         <v>2</v>
@@ -46743,10 +46740,10 @@
         <v>33</v>
       </c>
       <c r="G1312" t="s">
+        <v>140</v>
+      </c>
+      <c r="H1312" t="s">
         <v>141</v>
-      </c>
-      <c r="H1312" t="s">
-        <v>142</v>
       </c>
       <c r="I1312" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1312,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -46761,10 +46758,10 @@
         <v>127</v>
       </c>
       <c r="C1313" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D1313" t="s">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="E1313">
         <v>2</v>
@@ -46773,10 +46770,10 @@
         <v>35</v>
       </c>
       <c r="G1313" t="s">
+        <v>131</v>
+      </c>
+      <c r="H1313" t="s">
         <v>132</v>
-      </c>
-      <c r="H1313" t="s">
-        <v>133</v>
       </c>
       <c r="I1313" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1313,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -46794,7 +46791,7 @@
         <v>28</v>
       </c>
       <c r="D1314" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1314">
         <v>1</v>
@@ -46803,10 +46800,10 @@
         <v>106</v>
       </c>
       <c r="G1314" t="s">
+        <v>131</v>
+      </c>
+      <c r="H1314" t="s">
         <v>132</v>
-      </c>
-      <c r="H1314" t="s">
-        <v>133</v>
       </c>
       <c r="I1314" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1314,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -46824,7 +46821,7 @@
         <v>29</v>
       </c>
       <c r="D1315" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1315">
         <v>1</v>
@@ -46833,10 +46830,10 @@
         <v>106</v>
       </c>
       <c r="G1315" t="s">
+        <v>131</v>
+      </c>
+      <c r="H1315" t="s">
         <v>132</v>
-      </c>
-      <c r="H1315" t="s">
-        <v>133</v>
       </c>
       <c r="I1315" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1315,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -46854,7 +46851,7 @@
         <v>87</v>
       </c>
       <c r="D1316" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1316">
         <v>1</v>
@@ -46863,10 +46860,10 @@
         <v>106</v>
       </c>
       <c r="G1316" t="s">
+        <v>131</v>
+      </c>
+      <c r="H1316" t="s">
         <v>132</v>
-      </c>
-      <c r="H1316" t="s">
-        <v>133</v>
       </c>
       <c r="I1316" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1316,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -46884,7 +46881,7 @@
         <v>88</v>
       </c>
       <c r="D1317" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1317">
         <v>1</v>
@@ -46893,10 +46890,10 @@
         <v>106</v>
       </c>
       <c r="G1317" t="s">
+        <v>131</v>
+      </c>
+      <c r="H1317" t="s">
         <v>132</v>
-      </c>
-      <c r="H1317" t="s">
-        <v>133</v>
       </c>
       <c r="I1317" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1317,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -46914,7 +46911,7 @@
         <v>28</v>
       </c>
       <c r="D1318" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1318">
         <v>2</v>
@@ -46923,10 +46920,10 @@
         <v>107</v>
       </c>
       <c r="G1318" t="s">
+        <v>131</v>
+      </c>
+      <c r="H1318" t="s">
         <v>132</v>
-      </c>
-      <c r="H1318" t="s">
-        <v>133</v>
       </c>
       <c r="I1318" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1318,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -46944,7 +46941,7 @@
         <v>29</v>
       </c>
       <c r="D1319" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1319">
         <v>2</v>
@@ -46953,10 +46950,10 @@
         <v>107</v>
       </c>
       <c r="G1319" t="s">
+        <v>131</v>
+      </c>
+      <c r="H1319" t="s">
         <v>132</v>
-      </c>
-      <c r="H1319" t="s">
-        <v>133</v>
       </c>
       <c r="I1319" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1319,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -46974,7 +46971,7 @@
         <v>87</v>
       </c>
       <c r="D1320" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1320">
         <v>2</v>
@@ -46983,10 +46980,10 @@
         <v>107</v>
       </c>
       <c r="G1320" t="s">
+        <v>131</v>
+      </c>
+      <c r="H1320" t="s">
         <v>132</v>
-      </c>
-      <c r="H1320" t="s">
-        <v>133</v>
       </c>
       <c r="I1320" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1320,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -47004,7 +47001,7 @@
         <v>88</v>
       </c>
       <c r="D1321" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1321">
         <v>2</v>
@@ -47013,10 +47010,10 @@
         <v>107</v>
       </c>
       <c r="G1321" t="s">
+        <v>131</v>
+      </c>
+      <c r="H1321" t="s">
         <v>132</v>
-      </c>
-      <c r="H1321" t="s">
-        <v>133</v>
       </c>
       <c r="I1321" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1321,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -47034,19 +47031,19 @@
         <v>28</v>
       </c>
       <c r="D1322" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1322">
         <v>1</v>
       </c>
       <c r="F1322" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G1322" t="s">
+        <v>149</v>
+      </c>
+      <c r="H1322" t="s">
         <v>150</v>
-      </c>
-      <c r="H1322" t="s">
-        <v>151</v>
       </c>
       <c r="I1322" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1322,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -47064,19 +47061,19 @@
         <v>29</v>
       </c>
       <c r="D1323" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1323">
         <v>1</v>
       </c>
       <c r="F1323" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G1323" t="s">
+        <v>149</v>
+      </c>
+      <c r="H1323" t="s">
         <v>150</v>
-      </c>
-      <c r="H1323" t="s">
-        <v>151</v>
       </c>
       <c r="I1323" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1323,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -47094,19 +47091,19 @@
         <v>87</v>
       </c>
       <c r="D1324" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1324">
         <v>1</v>
       </c>
       <c r="F1324" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G1324" t="s">
+        <v>149</v>
+      </c>
+      <c r="H1324" t="s">
         <v>150</v>
-      </c>
-      <c r="H1324" t="s">
-        <v>151</v>
       </c>
       <c r="I1324" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1324,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -47124,19 +47121,19 @@
         <v>88</v>
       </c>
       <c r="D1325" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1325">
         <v>1</v>
       </c>
       <c r="F1325" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G1325" t="s">
+        <v>149</v>
+      </c>
+      <c r="H1325" t="s">
         <v>150</v>
-      </c>
-      <c r="H1325" t="s">
-        <v>151</v>
       </c>
       <c r="I1325" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1325,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -47154,19 +47151,19 @@
         <v>28</v>
       </c>
       <c r="D1326" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1326">
         <v>2</v>
       </c>
       <c r="F1326" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G1326" t="s">
+        <v>149</v>
+      </c>
+      <c r="H1326" t="s">
         <v>150</v>
-      </c>
-      <c r="H1326" t="s">
-        <v>151</v>
       </c>
       <c r="I1326" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1326,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -47184,19 +47181,19 @@
         <v>29</v>
       </c>
       <c r="D1327" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1327">
         <v>2</v>
       </c>
       <c r="F1327" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G1327" t="s">
+        <v>149</v>
+      </c>
+      <c r="H1327" t="s">
         <v>150</v>
-      </c>
-      <c r="H1327" t="s">
-        <v>151</v>
       </c>
       <c r="I1327" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1327,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -47214,19 +47211,19 @@
         <v>87</v>
       </c>
       <c r="D1328" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1328">
         <v>2</v>
       </c>
       <c r="F1328" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G1328" t="s">
+        <v>149</v>
+      </c>
+      <c r="H1328" t="s">
         <v>150</v>
-      </c>
-      <c r="H1328" t="s">
-        <v>151</v>
       </c>
       <c r="I1328" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1328,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -47244,19 +47241,19 @@
         <v>88</v>
       </c>
       <c r="D1329" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E1329">
         <v>2</v>
       </c>
       <c r="F1329" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G1329" t="s">
+        <v>149</v>
+      </c>
+      <c r="H1329" t="s">
         <v>150</v>
-      </c>
-      <c r="H1329" t="s">
-        <v>151</v>
       </c>
       <c r="I1329" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1329,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -47271,10 +47268,10 @@
         <v>127</v>
       </c>
       <c r="C1330" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D1330" t="s">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="E1330">
         <v>1</v>
@@ -47283,10 +47280,10 @@
         <v>106</v>
       </c>
       <c r="G1330" t="s">
+        <v>131</v>
+      </c>
+      <c r="H1330" t="s">
         <v>132</v>
-      </c>
-      <c r="H1330" t="s">
-        <v>133</v>
       </c>
       <c r="I1330" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1330,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -47301,10 +47298,10 @@
         <v>127</v>
       </c>
       <c r="C1331" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D1331" t="s">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="E1331">
         <v>1</v>
@@ -47313,10 +47310,10 @@
         <v>106</v>
       </c>
       <c r="G1331" t="s">
+        <v>131</v>
+      </c>
+      <c r="H1331" t="s">
         <v>132</v>
-      </c>
-      <c r="H1331" t="s">
-        <v>133</v>
       </c>
       <c r="I1331" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1331,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -47331,10 +47328,10 @@
         <v>127</v>
       </c>
       <c r="C1332" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D1332" t="s">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="E1332">
         <v>2</v>
@@ -47343,10 +47340,10 @@
         <v>107</v>
       </c>
       <c r="G1332" t="s">
+        <v>131</v>
+      </c>
+      <c r="H1332" t="s">
         <v>132</v>
-      </c>
-      <c r="H1332" t="s">
-        <v>133</v>
       </c>
       <c r="I1332" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1332,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -47361,10 +47358,10 @@
         <v>127</v>
       </c>
       <c r="C1333" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D1333" t="s">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="E1333">
         <v>2</v>
@@ -47373,10 +47370,10 @@
         <v>107</v>
       </c>
       <c r="G1333" t="s">
+        <v>131</v>
+      </c>
+      <c r="H1333" t="s">
         <v>132</v>
-      </c>
-      <c r="H1333" t="s">
-        <v>133</v>
       </c>
       <c r="I1333" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1333,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -47391,22 +47388,22 @@
         <v>127</v>
       </c>
       <c r="C1334" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D1334" t="s">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="E1334">
         <v>1</v>
       </c>
       <c r="F1334" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G1334" t="s">
+        <v>149</v>
+      </c>
+      <c r="H1334" t="s">
         <v>150</v>
-      </c>
-      <c r="H1334" t="s">
-        <v>151</v>
       </c>
       <c r="I1334" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1334,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -47421,22 +47418,22 @@
         <v>127</v>
       </c>
       <c r="C1335" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D1335" t="s">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="E1335">
         <v>1</v>
       </c>
       <c r="F1335" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G1335" t="s">
+        <v>149</v>
+      </c>
+      <c r="H1335" t="s">
         <v>150</v>
-      </c>
-      <c r="H1335" t="s">
-        <v>151</v>
       </c>
       <c r="I1335" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1335,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -47451,22 +47448,22 @@
         <v>127</v>
       </c>
       <c r="C1336" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D1336" t="s">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="E1336">
         <v>2</v>
       </c>
       <c r="F1336" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G1336" t="s">
+        <v>149</v>
+      </c>
+      <c r="H1336" t="s">
         <v>150</v>
-      </c>
-      <c r="H1336" t="s">
-        <v>151</v>
       </c>
       <c r="I1336" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1336,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>
@@ -47481,22 +47478,22 @@
         <v>127</v>
       </c>
       <c r="C1337" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D1337" t="s">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="E1337">
         <v>2</v>
       </c>
       <c r="F1337" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G1337" t="s">
+        <v>149</v>
+      </c>
+      <c r="H1337" t="s">
         <v>150</v>
-      </c>
-      <c r="H1337" t="s">
-        <v>151</v>
       </c>
       <c r="I1337" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1337,DeparaIMG!B:B,DeparaIMG!D:D,,0)</f>

--- a/data/calendario_promocional.xlsx
+++ b/data/calendario_promocional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anheuserbuschinbev-my.sharepoint.com/personal/99823517_ab-inbev_com/Documents/001. Projetos/Streamlit Calendario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="484" documentId="13_ncr:1_{B92F5DA4-8825-4FA1-97C6-23568D76854D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF10EF96-52B5-4AD2-A27E-4ACF32E399BF}"/>
+  <xr:revisionPtr revIDLastSave="486" documentId="13_ncr:1_{B92F5DA4-8825-4FA1-97C6-23568D76854D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50C67F16-56A0-4467-9F28-6B883D116E59}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DeparaIMG" sheetId="5" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8502" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8446" uniqueCount="160">
   <si>
     <t>Data</t>
   </si>
@@ -501,9 +501,6 @@
     <t>Ganhe 1 FF</t>
   </si>
   <si>
-    <t>Power Pack</t>
-  </si>
-  <si>
     <t>sk 269</t>
   </si>
   <si>
@@ -1748,7 +1745,7 @@
         <v>62</v>
       </c>
       <c r="B56" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C56" t="str">
         <f>SUBSTITUTE(B56," ","")</f>
@@ -47552,11 +47549,11 @@
       <c r="D1338" t="s">
         <v>25</v>
       </c>
-      <c r="E1338" t="s">
+      <c r="E1338">
+        <v>3</v>
+      </c>
+      <c r="F1338" t="s">
         <v>151</v>
-      </c>
-      <c r="F1338" t="s">
-        <v>152</v>
       </c>
       <c r="G1338">
         <v>3.29</v>
@@ -47582,11 +47579,11 @@
       <c r="D1339" t="s">
         <v>25</v>
       </c>
-      <c r="E1339" t="s">
-        <v>151</v>
+      <c r="E1339">
+        <v>3</v>
       </c>
       <c r="F1339" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G1339">
         <v>3.39</v>
@@ -47612,11 +47609,11 @@
       <c r="D1340" t="s">
         <v>25</v>
       </c>
-      <c r="E1340" t="s">
-        <v>151</v>
+      <c r="E1340">
+        <v>3</v>
       </c>
       <c r="F1340" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G1340">
         <v>3.99</v>
@@ -47642,11 +47639,11 @@
       <c r="D1341" t="s">
         <v>25</v>
       </c>
-      <c r="E1341" t="s">
-        <v>151</v>
+      <c r="E1341">
+        <v>3</v>
       </c>
       <c r="F1341" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G1341">
         <v>4.29</v>
@@ -47672,11 +47669,11 @@
       <c r="D1342" t="s">
         <v>25</v>
       </c>
-      <c r="E1342" t="s">
-        <v>151</v>
+      <c r="E1342">
+        <v>3</v>
       </c>
       <c r="F1342" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G1342">
         <v>4.6900000000000004</v>
@@ -47702,11 +47699,11 @@
       <c r="D1343" t="s">
         <v>25</v>
       </c>
-      <c r="E1343" t="s">
-        <v>151</v>
+      <c r="E1343">
+        <v>3</v>
       </c>
       <c r="F1343" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G1343">
         <v>3.79</v>
@@ -47732,11 +47729,11 @@
       <c r="D1344" t="s">
         <v>25</v>
       </c>
-      <c r="E1344" t="s">
-        <v>151</v>
+      <c r="E1344">
+        <v>3</v>
       </c>
       <c r="F1344" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G1344">
         <v>6.49</v>
@@ -47762,11 +47759,11 @@
       <c r="D1345" t="s">
         <v>25</v>
       </c>
-      <c r="E1345" t="s">
+      <c r="E1345">
+        <v>3</v>
+      </c>
+      <c r="F1345" t="s">
         <v>151</v>
-      </c>
-      <c r="F1345" t="s">
-        <v>152</v>
       </c>
       <c r="G1345">
         <v>3.29</v>
@@ -47792,11 +47789,11 @@
       <c r="D1346" t="s">
         <v>25</v>
       </c>
-      <c r="E1346" t="s">
-        <v>151</v>
+      <c r="E1346">
+        <v>3</v>
       </c>
       <c r="F1346" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G1346">
         <v>3.49</v>
@@ -47822,11 +47819,11 @@
       <c r="D1347" t="s">
         <v>25</v>
       </c>
-      <c r="E1347" t="s">
-        <v>151</v>
+      <c r="E1347">
+        <v>3</v>
       </c>
       <c r="F1347" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G1347">
         <v>3.59</v>
@@ -47852,11 +47849,11 @@
       <c r="D1348" t="s">
         <v>25</v>
       </c>
-      <c r="E1348" t="s">
-        <v>151</v>
+      <c r="E1348">
+        <v>3</v>
       </c>
       <c r="F1348" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G1348">
         <v>3.99</v>
@@ -47882,11 +47879,11 @@
       <c r="D1349" t="s">
         <v>25</v>
       </c>
-      <c r="E1349" t="s">
-        <v>151</v>
+      <c r="E1349">
+        <v>3</v>
       </c>
       <c r="F1349" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G1349">
         <v>4.29</v>
@@ -47912,11 +47909,11 @@
       <c r="D1350" t="s">
         <v>25</v>
       </c>
-      <c r="E1350" t="s">
-        <v>151</v>
+      <c r="E1350">
+        <v>3</v>
       </c>
       <c r="F1350" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G1350">
         <v>4.6900000000000004</v>
@@ -47942,11 +47939,11 @@
       <c r="D1351" t="s">
         <v>25</v>
       </c>
-      <c r="E1351" t="s">
-        <v>151</v>
+      <c r="E1351">
+        <v>3</v>
       </c>
       <c r="F1351" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G1351">
         <v>3.99</v>
@@ -47972,11 +47969,11 @@
       <c r="D1352" t="s">
         <v>25</v>
       </c>
-      <c r="E1352" t="s">
-        <v>151</v>
+      <c r="E1352">
+        <v>3</v>
       </c>
       <c r="F1352" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G1352">
         <v>6.49</v>
@@ -48002,8 +47999,8 @@
       <c r="D1353" t="s">
         <v>25</v>
       </c>
-      <c r="E1353" t="s">
-        <v>151</v>
+      <c r="E1353">
+        <v>3</v>
       </c>
       <c r="F1353" t="s">
         <v>66</v>
@@ -48032,11 +48029,11 @@
       <c r="D1354" t="s">
         <v>25</v>
       </c>
-      <c r="E1354" t="s">
-        <v>151</v>
+      <c r="E1354">
+        <v>3</v>
       </c>
       <c r="F1354" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G1354">
         <v>3.49</v>
@@ -48062,8 +48059,8 @@
       <c r="D1355" t="s">
         <v>25</v>
       </c>
-      <c r="E1355" t="s">
-        <v>151</v>
+      <c r="E1355">
+        <v>3</v>
       </c>
       <c r="F1355" t="s">
         <v>100</v>
@@ -48092,8 +48089,8 @@
       <c r="D1356" t="s">
         <v>25</v>
       </c>
-      <c r="E1356" t="s">
-        <v>151</v>
+      <c r="E1356">
+        <v>3</v>
       </c>
       <c r="F1356" t="s">
         <v>75</v>
@@ -48122,8 +48119,8 @@
       <c r="D1357" t="s">
         <v>25</v>
       </c>
-      <c r="E1357" t="s">
-        <v>151</v>
+      <c r="E1357">
+        <v>3</v>
       </c>
       <c r="F1357" t="s">
         <v>77</v>
@@ -48152,8 +48149,8 @@
       <c r="D1358" t="s">
         <v>25</v>
       </c>
-      <c r="E1358" t="s">
-        <v>151</v>
+      <c r="E1358">
+        <v>3</v>
       </c>
       <c r="F1358" t="s">
         <v>71</v>
@@ -48182,8 +48179,8 @@
       <c r="D1359" t="s">
         <v>26</v>
       </c>
-      <c r="E1359" t="s">
-        <v>151</v>
+      <c r="E1359">
+        <v>3</v>
       </c>
       <c r="F1359" t="s">
         <v>76</v>
@@ -48212,8 +48209,8 @@
       <c r="D1360" t="s">
         <v>25</v>
       </c>
-      <c r="E1360" t="s">
-        <v>151</v>
+      <c r="E1360">
+        <v>3</v>
       </c>
       <c r="F1360" t="s">
         <v>139</v>
@@ -48242,8 +48239,8 @@
       <c r="D1361" t="s">
         <v>25</v>
       </c>
-      <c r="E1361" t="s">
-        <v>151</v>
+      <c r="E1361">
+        <v>3</v>
       </c>
       <c r="F1361" t="s">
         <v>66</v>
@@ -48272,11 +48269,11 @@
       <c r="D1362" t="s">
         <v>25</v>
       </c>
-      <c r="E1362" t="s">
-        <v>151</v>
+      <c r="E1362">
+        <v>3</v>
       </c>
       <c r="F1362" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G1362">
         <v>3.49</v>
@@ -48302,8 +48299,8 @@
       <c r="D1363" t="s">
         <v>25</v>
       </c>
-      <c r="E1363" t="s">
-        <v>151</v>
+      <c r="E1363">
+        <v>3</v>
       </c>
       <c r="F1363" t="s">
         <v>100</v>
@@ -48332,8 +48329,8 @@
       <c r="D1364" t="s">
         <v>25</v>
       </c>
-      <c r="E1364" t="s">
-        <v>151</v>
+      <c r="E1364">
+        <v>3</v>
       </c>
       <c r="F1364" t="s">
         <v>75</v>
@@ -48362,8 +48359,8 @@
       <c r="D1365" t="s">
         <v>25</v>
       </c>
-      <c r="E1365" t="s">
-        <v>151</v>
+      <c r="E1365">
+        <v>3</v>
       </c>
       <c r="F1365" t="s">
         <v>77</v>
@@ -48392,8 +48389,8 @@
       <c r="D1366" t="s">
         <v>25</v>
       </c>
-      <c r="E1366" t="s">
-        <v>151</v>
+      <c r="E1366">
+        <v>3</v>
       </c>
       <c r="F1366" t="s">
         <v>71</v>
@@ -48422,8 +48419,8 @@
       <c r="D1367" t="s">
         <v>26</v>
       </c>
-      <c r="E1367" t="s">
-        <v>151</v>
+      <c r="E1367">
+        <v>3</v>
       </c>
       <c r="F1367" t="s">
         <v>101</v>
@@ -48452,8 +48449,8 @@
       <c r="D1368" t="s">
         <v>26</v>
       </c>
-      <c r="E1368" t="s">
-        <v>151</v>
+      <c r="E1368">
+        <v>3</v>
       </c>
       <c r="F1368" t="s">
         <v>65</v>
@@ -48482,8 +48479,8 @@
       <c r="D1369" t="s">
         <v>25</v>
       </c>
-      <c r="E1369" t="s">
-        <v>151</v>
+      <c r="E1369">
+        <v>3</v>
       </c>
       <c r="F1369" t="s">
         <v>139</v>
@@ -48512,11 +48509,11 @@
       <c r="D1370" t="s">
         <v>25</v>
       </c>
-      <c r="E1370" t="s">
+      <c r="E1370">
+        <v>3</v>
+      </c>
+      <c r="F1370" t="s">
         <v>151</v>
-      </c>
-      <c r="F1370" t="s">
-        <v>152</v>
       </c>
       <c r="G1370">
         <v>3.09</v>
@@ -48542,11 +48539,11 @@
       <c r="D1371" t="s">
         <v>25</v>
       </c>
-      <c r="E1371" t="s">
-        <v>151</v>
+      <c r="E1371">
+        <v>3</v>
       </c>
       <c r="F1371" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G1371">
         <v>3.49</v>
@@ -48572,11 +48569,11 @@
       <c r="D1372" t="s">
         <v>25</v>
       </c>
-      <c r="E1372" t="s">
-        <v>151</v>
+      <c r="E1372">
+        <v>3</v>
       </c>
       <c r="F1372" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G1372">
         <v>3.49</v>
@@ -48602,11 +48599,11 @@
       <c r="D1373" t="s">
         <v>25</v>
       </c>
-      <c r="E1373" t="s">
-        <v>151</v>
+      <c r="E1373">
+        <v>3</v>
       </c>
       <c r="F1373" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G1373">
         <v>3.99</v>
@@ -48632,11 +48629,11 @@
       <c r="D1374" t="s">
         <v>25</v>
       </c>
-      <c r="E1374" t="s">
-        <v>151</v>
+      <c r="E1374">
+        <v>3</v>
       </c>
       <c r="F1374" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G1374">
         <v>4.29</v>
@@ -48662,11 +48659,11 @@
       <c r="D1375" t="s">
         <v>25</v>
       </c>
-      <c r="E1375" t="s">
-        <v>151</v>
+      <c r="E1375">
+        <v>3</v>
       </c>
       <c r="F1375" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G1375">
         <v>4.6900000000000004</v>
@@ -48692,11 +48689,11 @@
       <c r="D1376" t="s">
         <v>25</v>
       </c>
-      <c r="E1376" t="s">
-        <v>151</v>
+      <c r="E1376">
+        <v>3</v>
       </c>
       <c r="F1376" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G1376">
         <v>3.99</v>
@@ -48722,11 +48719,11 @@
       <c r="D1377" t="s">
         <v>25</v>
       </c>
-      <c r="E1377" t="s">
-        <v>151</v>
+      <c r="E1377">
+        <v>3</v>
       </c>
       <c r="F1377" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G1377">
         <v>6.49</v>
@@ -48752,11 +48749,11 @@
       <c r="D1378" t="s">
         <v>25</v>
       </c>
-      <c r="E1378" t="s">
+      <c r="E1378">
+        <v>3</v>
+      </c>
+      <c r="F1378" t="s">
         <v>151</v>
-      </c>
-      <c r="F1378" t="s">
-        <v>152</v>
       </c>
       <c r="G1378">
         <v>3.39</v>
@@ -48782,11 +48779,11 @@
       <c r="D1379" t="s">
         <v>25</v>
       </c>
-      <c r="E1379" t="s">
-        <v>151</v>
+      <c r="E1379">
+        <v>3</v>
       </c>
       <c r="F1379" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G1379">
         <v>3.49</v>
@@ -48812,11 +48809,11 @@
       <c r="D1380" t="s">
         <v>25</v>
       </c>
-      <c r="E1380" t="s">
-        <v>151</v>
+      <c r="E1380">
+        <v>3</v>
       </c>
       <c r="F1380" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G1380">
         <v>3.49</v>
@@ -48842,11 +48839,11 @@
       <c r="D1381" t="s">
         <v>25</v>
       </c>
-      <c r="E1381" t="s">
-        <v>151</v>
+      <c r="E1381">
+        <v>3</v>
       </c>
       <c r="F1381" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G1381">
         <v>3.99</v>
@@ -48872,11 +48869,11 @@
       <c r="D1382" t="s">
         <v>25</v>
       </c>
-      <c r="E1382" t="s">
-        <v>151</v>
+      <c r="E1382">
+        <v>3</v>
       </c>
       <c r="F1382" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G1382">
         <v>4.29</v>
@@ -48902,11 +48899,11 @@
       <c r="D1383" t="s">
         <v>25</v>
       </c>
-      <c r="E1383" t="s">
-        <v>151</v>
+      <c r="E1383">
+        <v>3</v>
       </c>
       <c r="F1383" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G1383">
         <v>4.6900000000000004</v>
@@ -48932,11 +48929,11 @@
       <c r="D1384" t="s">
         <v>25</v>
       </c>
-      <c r="E1384" t="s">
-        <v>151</v>
+      <c r="E1384">
+        <v>3</v>
       </c>
       <c r="F1384" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G1384">
         <v>3.79</v>
@@ -48962,11 +48959,11 @@
       <c r="D1385" t="s">
         <v>25</v>
       </c>
-      <c r="E1385" t="s">
-        <v>151</v>
+      <c r="E1385">
+        <v>3</v>
       </c>
       <c r="F1385" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G1385">
         <v>6.49</v>
@@ -48992,11 +48989,11 @@
       <c r="D1386" t="s">
         <v>25</v>
       </c>
-      <c r="E1386" t="s">
+      <c r="E1386">
+        <v>3</v>
+      </c>
+      <c r="F1386" t="s">
         <v>151</v>
-      </c>
-      <c r="F1386" t="s">
-        <v>152</v>
       </c>
       <c r="G1386">
         <v>3.39</v>
@@ -49022,11 +49019,11 @@
       <c r="D1387" t="s">
         <v>25</v>
       </c>
-      <c r="E1387" t="s">
-        <v>151</v>
+      <c r="E1387">
+        <v>3</v>
       </c>
       <c r="F1387" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G1387">
         <v>3.49</v>
@@ -49052,11 +49049,11 @@
       <c r="D1388" t="s">
         <v>25</v>
       </c>
-      <c r="E1388" t="s">
-        <v>151</v>
+      <c r="E1388">
+        <v>3</v>
       </c>
       <c r="F1388" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G1388">
         <v>3.49</v>
@@ -49082,11 +49079,11 @@
       <c r="D1389" t="s">
         <v>25</v>
       </c>
-      <c r="E1389" t="s">
-        <v>151</v>
+      <c r="E1389">
+        <v>3</v>
       </c>
       <c r="F1389" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G1389">
         <v>3.99</v>
@@ -49112,11 +49109,11 @@
       <c r="D1390" t="s">
         <v>25</v>
       </c>
-      <c r="E1390" t="s">
-        <v>151</v>
+      <c r="E1390">
+        <v>3</v>
       </c>
       <c r="F1390" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G1390">
         <v>4.29</v>
@@ -49142,11 +49139,11 @@
       <c r="D1391" t="s">
         <v>25</v>
       </c>
-      <c r="E1391" t="s">
-        <v>151</v>
+      <c r="E1391">
+        <v>3</v>
       </c>
       <c r="F1391" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G1391">
         <v>4.6900000000000004</v>
@@ -49172,11 +49169,11 @@
       <c r="D1392" t="s">
         <v>25</v>
       </c>
-      <c r="E1392" t="s">
-        <v>151</v>
+      <c r="E1392">
+        <v>3</v>
       </c>
       <c r="F1392" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G1392">
         <v>3.79</v>
@@ -49202,11 +49199,11 @@
       <c r="D1393" t="s">
         <v>25</v>
       </c>
-      <c r="E1393" t="s">
-        <v>151</v>
+      <c r="E1393">
+        <v>3</v>
       </c>
       <c r="F1393" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G1393">
         <v>6.49</v>

--- a/data/calendario_promocional.xlsx
+++ b/data/calendario_promocional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anheuserbuschinbev-my.sharepoint.com/personal/99823517_ab-inbev_com/Documents/001. Projetos/Streamlit Calendario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="486" documentId="13_ncr:1_{B92F5DA4-8825-4FA1-97C6-23568D76854D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50C67F16-56A0-4467-9F28-6B883D116E59}"/>
+  <xr:revisionPtr revIDLastSave="492" documentId="13_ncr:1_{B92F5DA4-8825-4FA1-97C6-23568D76854D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9CFBA5F-BD28-4EE7-A8D0-95EB3276B4B9}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8446" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8502" uniqueCount="161">
   <si>
     <t>Data</t>
   </si>
@@ -527,6 +527,9 @@
   <si>
     <t>BDM 269</t>
   </si>
+  <si>
+    <t>PP</t>
+  </si>
 </sst>
 </file>
 
@@ -47549,8 +47552,8 @@
       <c r="D1338" t="s">
         <v>25</v>
       </c>
-      <c r="E1338">
-        <v>3</v>
+      <c r="E1338" t="s">
+        <v>160</v>
       </c>
       <c r="F1338" t="s">
         <v>151</v>
@@ -47579,8 +47582,8 @@
       <c r="D1339" t="s">
         <v>25</v>
       </c>
-      <c r="E1339">
-        <v>3</v>
+      <c r="E1339" t="s">
+        <v>160</v>
       </c>
       <c r="F1339" t="s">
         <v>152</v>
@@ -47609,8 +47612,8 @@
       <c r="D1340" t="s">
         <v>25</v>
       </c>
-      <c r="E1340">
-        <v>3</v>
+      <c r="E1340" t="s">
+        <v>160</v>
       </c>
       <c r="F1340" t="s">
         <v>153</v>
@@ -47639,8 +47642,8 @@
       <c r="D1341" t="s">
         <v>25</v>
       </c>
-      <c r="E1341">
-        <v>3</v>
+      <c r="E1341" t="s">
+        <v>160</v>
       </c>
       <c r="F1341" t="s">
         <v>154</v>
@@ -47669,8 +47672,8 @@
       <c r="D1342" t="s">
         <v>25</v>
       </c>
-      <c r="E1342">
-        <v>3</v>
+      <c r="E1342" t="s">
+        <v>160</v>
       </c>
       <c r="F1342" t="s">
         <v>155</v>
@@ -47699,8 +47702,8 @@
       <c r="D1343" t="s">
         <v>25</v>
       </c>
-      <c r="E1343">
-        <v>3</v>
+      <c r="E1343" t="s">
+        <v>160</v>
       </c>
       <c r="F1343" t="s">
         <v>156</v>
@@ -47729,8 +47732,8 @@
       <c r="D1344" t="s">
         <v>25</v>
       </c>
-      <c r="E1344">
-        <v>3</v>
+      <c r="E1344" t="s">
+        <v>160</v>
       </c>
       <c r="F1344" t="s">
         <v>157</v>
@@ -47759,8 +47762,8 @@
       <c r="D1345" t="s">
         <v>25</v>
       </c>
-      <c r="E1345">
-        <v>3</v>
+      <c r="E1345" t="s">
+        <v>160</v>
       </c>
       <c r="F1345" t="s">
         <v>151</v>
@@ -47789,8 +47792,8 @@
       <c r="D1346" t="s">
         <v>25</v>
       </c>
-      <c r="E1346">
-        <v>3</v>
+      <c r="E1346" t="s">
+        <v>160</v>
       </c>
       <c r="F1346" t="s">
         <v>158</v>
@@ -47819,8 +47822,8 @@
       <c r="D1347" t="s">
         <v>25</v>
       </c>
-      <c r="E1347">
-        <v>3</v>
+      <c r="E1347" t="s">
+        <v>160</v>
       </c>
       <c r="F1347" t="s">
         <v>152</v>
@@ -47849,8 +47852,8 @@
       <c r="D1348" t="s">
         <v>25</v>
       </c>
-      <c r="E1348">
-        <v>3</v>
+      <c r="E1348" t="s">
+        <v>160</v>
       </c>
       <c r="F1348" t="s">
         <v>153</v>
@@ -47879,8 +47882,8 @@
       <c r="D1349" t="s">
         <v>25</v>
       </c>
-      <c r="E1349">
-        <v>3</v>
+      <c r="E1349" t="s">
+        <v>160</v>
       </c>
       <c r="F1349" t="s">
         <v>154</v>
@@ -47909,8 +47912,8 @@
       <c r="D1350" t="s">
         <v>25</v>
       </c>
-      <c r="E1350">
-        <v>3</v>
+      <c r="E1350" t="s">
+        <v>160</v>
       </c>
       <c r="F1350" t="s">
         <v>155</v>
@@ -47939,8 +47942,8 @@
       <c r="D1351" t="s">
         <v>25</v>
       </c>
-      <c r="E1351">
-        <v>3</v>
+      <c r="E1351" t="s">
+        <v>160</v>
       </c>
       <c r="F1351" t="s">
         <v>156</v>
@@ -47969,8 +47972,8 @@
       <c r="D1352" t="s">
         <v>25</v>
       </c>
-      <c r="E1352">
-        <v>3</v>
+      <c r="E1352" t="s">
+        <v>160</v>
       </c>
       <c r="F1352" t="s">
         <v>157</v>
@@ -47999,8 +48002,8 @@
       <c r="D1353" t="s">
         <v>25</v>
       </c>
-      <c r="E1353">
-        <v>3</v>
+      <c r="E1353" t="s">
+        <v>160</v>
       </c>
       <c r="F1353" t="s">
         <v>66</v>
@@ -48029,8 +48032,8 @@
       <c r="D1354" t="s">
         <v>25</v>
       </c>
-      <c r="E1354">
-        <v>3</v>
+      <c r="E1354" t="s">
+        <v>160</v>
       </c>
       <c r="F1354" t="s">
         <v>152</v>
@@ -48059,8 +48062,8 @@
       <c r="D1355" t="s">
         <v>25</v>
       </c>
-      <c r="E1355">
-        <v>3</v>
+      <c r="E1355" t="s">
+        <v>160</v>
       </c>
       <c r="F1355" t="s">
         <v>100</v>
@@ -48089,8 +48092,8 @@
       <c r="D1356" t="s">
         <v>25</v>
       </c>
-      <c r="E1356">
-        <v>3</v>
+      <c r="E1356" t="s">
+        <v>160</v>
       </c>
       <c r="F1356" t="s">
         <v>75</v>
@@ -48119,8 +48122,8 @@
       <c r="D1357" t="s">
         <v>25</v>
       </c>
-      <c r="E1357">
-        <v>3</v>
+      <c r="E1357" t="s">
+        <v>160</v>
       </c>
       <c r="F1357" t="s">
         <v>77</v>
@@ -48149,8 +48152,8 @@
       <c r="D1358" t="s">
         <v>25</v>
       </c>
-      <c r="E1358">
-        <v>3</v>
+      <c r="E1358" t="s">
+        <v>160</v>
       </c>
       <c r="F1358" t="s">
         <v>71</v>
@@ -48179,8 +48182,8 @@
       <c r="D1359" t="s">
         <v>26</v>
       </c>
-      <c r="E1359">
-        <v>3</v>
+      <c r="E1359" t="s">
+        <v>160</v>
       </c>
       <c r="F1359" t="s">
         <v>76</v>
@@ -48209,8 +48212,8 @@
       <c r="D1360" t="s">
         <v>25</v>
       </c>
-      <c r="E1360">
-        <v>3</v>
+      <c r="E1360" t="s">
+        <v>160</v>
       </c>
       <c r="F1360" t="s">
         <v>139</v>
@@ -48239,8 +48242,8 @@
       <c r="D1361" t="s">
         <v>25</v>
       </c>
-      <c r="E1361">
-        <v>3</v>
+      <c r="E1361" t="s">
+        <v>160</v>
       </c>
       <c r="F1361" t="s">
         <v>66</v>
@@ -48269,8 +48272,8 @@
       <c r="D1362" t="s">
         <v>25</v>
       </c>
-      <c r="E1362">
-        <v>3</v>
+      <c r="E1362" t="s">
+        <v>160</v>
       </c>
       <c r="F1362" t="s">
         <v>152</v>
@@ -48299,8 +48302,8 @@
       <c r="D1363" t="s">
         <v>25</v>
       </c>
-      <c r="E1363">
-        <v>3</v>
+      <c r="E1363" t="s">
+        <v>160</v>
       </c>
       <c r="F1363" t="s">
         <v>100</v>
@@ -48329,8 +48332,8 @@
       <c r="D1364" t="s">
         <v>25</v>
       </c>
-      <c r="E1364">
-        <v>3</v>
+      <c r="E1364" t="s">
+        <v>160</v>
       </c>
       <c r="F1364" t="s">
         <v>75</v>
@@ -48359,8 +48362,8 @@
       <c r="D1365" t="s">
         <v>25</v>
       </c>
-      <c r="E1365">
-        <v>3</v>
+      <c r="E1365" t="s">
+        <v>160</v>
       </c>
       <c r="F1365" t="s">
         <v>77</v>
@@ -48389,8 +48392,8 @@
       <c r="D1366" t="s">
         <v>25</v>
       </c>
-      <c r="E1366">
-        <v>3</v>
+      <c r="E1366" t="s">
+        <v>160</v>
       </c>
       <c r="F1366" t="s">
         <v>71</v>
@@ -48419,8 +48422,8 @@
       <c r="D1367" t="s">
         <v>26</v>
       </c>
-      <c r="E1367">
-        <v>3</v>
+      <c r="E1367" t="s">
+        <v>160</v>
       </c>
       <c r="F1367" t="s">
         <v>101</v>
@@ -48449,8 +48452,8 @@
       <c r="D1368" t="s">
         <v>26</v>
       </c>
-      <c r="E1368">
-        <v>3</v>
+      <c r="E1368" t="s">
+        <v>160</v>
       </c>
       <c r="F1368" t="s">
         <v>65</v>
@@ -48479,8 +48482,8 @@
       <c r="D1369" t="s">
         <v>25</v>
       </c>
-      <c r="E1369">
-        <v>3</v>
+      <c r="E1369" t="s">
+        <v>160</v>
       </c>
       <c r="F1369" t="s">
         <v>139</v>
@@ -48509,8 +48512,8 @@
       <c r="D1370" t="s">
         <v>25</v>
       </c>
-      <c r="E1370">
-        <v>3</v>
+      <c r="E1370" t="s">
+        <v>160</v>
       </c>
       <c r="F1370" t="s">
         <v>151</v>
@@ -48539,8 +48542,8 @@
       <c r="D1371" t="s">
         <v>25</v>
       </c>
-      <c r="E1371">
-        <v>3</v>
+      <c r="E1371" t="s">
+        <v>160</v>
       </c>
       <c r="F1371" t="s">
         <v>158</v>
@@ -48569,8 +48572,8 @@
       <c r="D1372" t="s">
         <v>25</v>
       </c>
-      <c r="E1372">
-        <v>3</v>
+      <c r="E1372" t="s">
+        <v>160</v>
       </c>
       <c r="F1372" t="s">
         <v>152</v>
@@ -48599,8 +48602,8 @@
       <c r="D1373" t="s">
         <v>25</v>
       </c>
-      <c r="E1373">
-        <v>3</v>
+      <c r="E1373" t="s">
+        <v>160</v>
       </c>
       <c r="F1373" t="s">
         <v>153</v>
@@ -48629,8 +48632,8 @@
       <c r="D1374" t="s">
         <v>25</v>
       </c>
-      <c r="E1374">
-        <v>3</v>
+      <c r="E1374" t="s">
+        <v>160</v>
       </c>
       <c r="F1374" t="s">
         <v>154</v>
@@ -48659,8 +48662,8 @@
       <c r="D1375" t="s">
         <v>25</v>
       </c>
-      <c r="E1375">
-        <v>3</v>
+      <c r="E1375" t="s">
+        <v>160</v>
       </c>
       <c r="F1375" t="s">
         <v>155</v>
@@ -48689,8 +48692,8 @@
       <c r="D1376" t="s">
         <v>25</v>
       </c>
-      <c r="E1376">
-        <v>3</v>
+      <c r="E1376" t="s">
+        <v>160</v>
       </c>
       <c r="F1376" t="s">
         <v>156</v>
@@ -48719,8 +48722,8 @@
       <c r="D1377" t="s">
         <v>25</v>
       </c>
-      <c r="E1377">
-        <v>3</v>
+      <c r="E1377" t="s">
+        <v>160</v>
       </c>
       <c r="F1377" t="s">
         <v>157</v>
@@ -48749,8 +48752,8 @@
       <c r="D1378" t="s">
         <v>25</v>
       </c>
-      <c r="E1378">
-        <v>3</v>
+      <c r="E1378" t="s">
+        <v>160</v>
       </c>
       <c r="F1378" t="s">
         <v>151</v>
@@ -48779,8 +48782,8 @@
       <c r="D1379" t="s">
         <v>25</v>
       </c>
-      <c r="E1379">
-        <v>3</v>
+      <c r="E1379" t="s">
+        <v>160</v>
       </c>
       <c r="F1379" t="s">
         <v>158</v>
@@ -48809,8 +48812,8 @@
       <c r="D1380" t="s">
         <v>25</v>
       </c>
-      <c r="E1380">
-        <v>3</v>
+      <c r="E1380" t="s">
+        <v>160</v>
       </c>
       <c r="F1380" t="s">
         <v>152</v>
@@ -48839,8 +48842,8 @@
       <c r="D1381" t="s">
         <v>25</v>
       </c>
-      <c r="E1381">
-        <v>3</v>
+      <c r="E1381" t="s">
+        <v>160</v>
       </c>
       <c r="F1381" t="s">
         <v>153</v>
@@ -48869,8 +48872,8 @@
       <c r="D1382" t="s">
         <v>25</v>
       </c>
-      <c r="E1382">
-        <v>3</v>
+      <c r="E1382" t="s">
+        <v>160</v>
       </c>
       <c r="F1382" t="s">
         <v>154</v>
@@ -48899,8 +48902,8 @@
       <c r="D1383" t="s">
         <v>25</v>
       </c>
-      <c r="E1383">
-        <v>3</v>
+      <c r="E1383" t="s">
+        <v>160</v>
       </c>
       <c r="F1383" t="s">
         <v>155</v>
@@ -48929,8 +48932,8 @@
       <c r="D1384" t="s">
         <v>25</v>
       </c>
-      <c r="E1384">
-        <v>3</v>
+      <c r="E1384" t="s">
+        <v>160</v>
       </c>
       <c r="F1384" t="s">
         <v>156</v>
@@ -48959,8 +48962,8 @@
       <c r="D1385" t="s">
         <v>25</v>
       </c>
-      <c r="E1385">
-        <v>3</v>
+      <c r="E1385" t="s">
+        <v>160</v>
       </c>
       <c r="F1385" t="s">
         <v>157</v>
@@ -48984,13 +48987,13 @@
         <v>62</v>
       </c>
       <c r="C1386" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D1386" t="s">
         <v>25</v>
       </c>
-      <c r="E1386">
-        <v>3</v>
+      <c r="E1386" t="s">
+        <v>160</v>
       </c>
       <c r="F1386" t="s">
         <v>151</v>
@@ -49014,13 +49017,13 @@
         <v>62</v>
       </c>
       <c r="C1387" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D1387" t="s">
         <v>25</v>
       </c>
-      <c r="E1387">
-        <v>3</v>
+      <c r="E1387" t="s">
+        <v>160</v>
       </c>
       <c r="F1387" t="s">
         <v>158</v>
@@ -49044,13 +49047,13 @@
         <v>62</v>
       </c>
       <c r="C1388" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D1388" t="s">
         <v>25</v>
       </c>
-      <c r="E1388">
-        <v>3</v>
+      <c r="E1388" t="s">
+        <v>160</v>
       </c>
       <c r="F1388" t="s">
         <v>152</v>
@@ -49074,13 +49077,13 @@
         <v>62</v>
       </c>
       <c r="C1389" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D1389" t="s">
         <v>25</v>
       </c>
-      <c r="E1389">
-        <v>3</v>
+      <c r="E1389" t="s">
+        <v>160</v>
       </c>
       <c r="F1389" t="s">
         <v>153</v>
@@ -49104,13 +49107,13 @@
         <v>62</v>
       </c>
       <c r="C1390" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D1390" t="s">
         <v>25</v>
       </c>
-      <c r="E1390">
-        <v>3</v>
+      <c r="E1390" t="s">
+        <v>160</v>
       </c>
       <c r="F1390" t="s">
         <v>154</v>
@@ -49134,13 +49137,13 @@
         <v>62</v>
       </c>
       <c r="C1391" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D1391" t="s">
         <v>25</v>
       </c>
-      <c r="E1391">
-        <v>3</v>
+      <c r="E1391" t="s">
+        <v>160</v>
       </c>
       <c r="F1391" t="s">
         <v>155</v>
@@ -49164,13 +49167,13 @@
         <v>62</v>
       </c>
       <c r="C1392" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D1392" t="s">
         <v>25</v>
       </c>
-      <c r="E1392">
-        <v>3</v>
+      <c r="E1392" t="s">
+        <v>160</v>
       </c>
       <c r="F1392" t="s">
         <v>156</v>
@@ -49194,13 +49197,13 @@
         <v>62</v>
       </c>
       <c r="C1393" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D1393" t="s">
         <v>25</v>
       </c>
-      <c r="E1393">
-        <v>3</v>
+      <c r="E1393" t="s">
+        <v>160</v>
       </c>
       <c r="F1393" t="s">
         <v>157</v>

--- a/data/calendario_promocional.xlsx
+++ b/data/calendario_promocional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anheuserbuschinbev-my.sharepoint.com/personal/99823517_ab-inbev_com/Documents/001. Projetos/Streamlit Calendario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="492" documentId="13_ncr:1_{B92F5DA4-8825-4FA1-97C6-23568D76854D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9CFBA5F-BD28-4EE7-A8D0-95EB3276B4B9}"/>
+  <xr:revisionPtr revIDLastSave="498" documentId="13_ncr:1_{B92F5DA4-8825-4FA1-97C6-23568D76854D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1C3F60E-EA86-4974-85E1-17ED1F7E0BFD}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8502" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8502" uniqueCount="153">
   <si>
     <t>Data</t>
   </si>
@@ -501,30 +501,6 @@
     <t>Ganhe 1 FF</t>
   </si>
   <si>
-    <t>sk 269</t>
-  </si>
-  <si>
-    <t>bdm 269</t>
-  </si>
-  <si>
-    <t>spt 269</t>
-  </si>
-  <si>
-    <t>ste 269</t>
-  </si>
-  <si>
-    <t>cor 269</t>
-  </si>
-  <si>
-    <t>bc 350</t>
-  </si>
-  <si>
-    <t>spt ln</t>
-  </si>
-  <si>
-    <t>bud 269</t>
-  </si>
-  <si>
     <t>BDM 269</t>
   </si>
   <si>
@@ -1748,7 +1724,7 @@
         <v>62</v>
       </c>
       <c r="B56" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="C56" t="str">
         <f>SUBSTITUTE(B56," ","")</f>
@@ -47553,10 +47529,10 @@
         <v>25</v>
       </c>
       <c r="E1338" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1338" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="G1338">
         <v>3.29</v>
@@ -47583,10 +47559,10 @@
         <v>25</v>
       </c>
       <c r="E1339" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1339" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G1339">
         <v>3.39</v>
@@ -47613,10 +47589,10 @@
         <v>25</v>
       </c>
       <c r="E1340" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1340" t="s">
-        <v>153</v>
+        <v>100</v>
       </c>
       <c r="G1340">
         <v>3.99</v>
@@ -47643,10 +47619,10 @@
         <v>25</v>
       </c>
       <c r="E1341" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1341" t="s">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="G1341">
         <v>4.29</v>
@@ -47673,10 +47649,10 @@
         <v>25</v>
       </c>
       <c r="E1342" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1342" t="s">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="G1342">
         <v>4.6900000000000004</v>
@@ -47703,10 +47679,10 @@
         <v>25</v>
       </c>
       <c r="E1343" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1343" t="s">
-        <v>156</v>
+        <v>71</v>
       </c>
       <c r="G1343">
         <v>3.79</v>
@@ -47733,10 +47709,10 @@
         <v>25</v>
       </c>
       <c r="E1344" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1344" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="G1344">
         <v>6.49</v>
@@ -47763,10 +47739,10 @@
         <v>25</v>
       </c>
       <c r="E1345" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1345" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="G1345">
         <v>3.29</v>
@@ -47793,10 +47769,10 @@
         <v>25</v>
       </c>
       <c r="E1346" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1346" t="s">
-        <v>158</v>
+        <v>69</v>
       </c>
       <c r="G1346">
         <v>3.49</v>
@@ -47823,10 +47799,10 @@
         <v>25</v>
       </c>
       <c r="E1347" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1347" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G1347">
         <v>3.59</v>
@@ -47853,10 +47829,10 @@
         <v>25</v>
       </c>
       <c r="E1348" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1348" t="s">
-        <v>153</v>
+        <v>100</v>
       </c>
       <c r="G1348">
         <v>3.99</v>
@@ -47883,10 +47859,10 @@
         <v>25</v>
       </c>
       <c r="E1349" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1349" t="s">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="G1349">
         <v>4.29</v>
@@ -47913,10 +47889,10 @@
         <v>25</v>
       </c>
       <c r="E1350" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1350" t="s">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="G1350">
         <v>4.6900000000000004</v>
@@ -47943,10 +47919,10 @@
         <v>25</v>
       </c>
       <c r="E1351" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1351" t="s">
-        <v>156</v>
+        <v>71</v>
       </c>
       <c r="G1351">
         <v>3.99</v>
@@ -47973,10 +47949,10 @@
         <v>25</v>
       </c>
       <c r="E1352" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1352" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="G1352">
         <v>6.49</v>
@@ -48003,7 +47979,7 @@
         <v>25</v>
       </c>
       <c r="E1353" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1353" t="s">
         <v>66</v>
@@ -48033,10 +48009,10 @@
         <v>25</v>
       </c>
       <c r="E1354" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1354" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G1354">
         <v>3.49</v>
@@ -48063,7 +48039,7 @@
         <v>25</v>
       </c>
       <c r="E1355" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1355" t="s">
         <v>100</v>
@@ -48093,7 +48069,7 @@
         <v>25</v>
       </c>
       <c r="E1356" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1356" t="s">
         <v>75</v>
@@ -48123,7 +48099,7 @@
         <v>25</v>
       </c>
       <c r="E1357" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1357" t="s">
         <v>77</v>
@@ -48153,7 +48129,7 @@
         <v>25</v>
       </c>
       <c r="E1358" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1358" t="s">
         <v>71</v>
@@ -48183,7 +48159,7 @@
         <v>26</v>
       </c>
       <c r="E1359" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1359" t="s">
         <v>76</v>
@@ -48213,7 +48189,7 @@
         <v>25</v>
       </c>
       <c r="E1360" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1360" t="s">
         <v>139</v>
@@ -48243,7 +48219,7 @@
         <v>25</v>
       </c>
       <c r="E1361" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1361" t="s">
         <v>66</v>
@@ -48273,10 +48249,10 @@
         <v>25</v>
       </c>
       <c r="E1362" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1362" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G1362">
         <v>3.49</v>
@@ -48303,7 +48279,7 @@
         <v>25</v>
       </c>
       <c r="E1363" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1363" t="s">
         <v>100</v>
@@ -48333,7 +48309,7 @@
         <v>25</v>
       </c>
       <c r="E1364" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1364" t="s">
         <v>75</v>
@@ -48363,7 +48339,7 @@
         <v>25</v>
       </c>
       <c r="E1365" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1365" t="s">
         <v>77</v>
@@ -48393,7 +48369,7 @@
         <v>25</v>
       </c>
       <c r="E1366" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1366" t="s">
         <v>71</v>
@@ -48423,7 +48399,7 @@
         <v>26</v>
       </c>
       <c r="E1367" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1367" t="s">
         <v>101</v>
@@ -48453,7 +48429,7 @@
         <v>26</v>
       </c>
       <c r="E1368" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1368" t="s">
         <v>65</v>
@@ -48483,7 +48459,7 @@
         <v>25</v>
       </c>
       <c r="E1369" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1369" t="s">
         <v>139</v>
@@ -48513,10 +48489,10 @@
         <v>25</v>
       </c>
       <c r="E1370" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1370" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="G1370">
         <v>3.09</v>
@@ -48543,10 +48519,10 @@
         <v>25</v>
       </c>
       <c r="E1371" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1371" t="s">
-        <v>158</v>
+        <v>69</v>
       </c>
       <c r="G1371">
         <v>3.49</v>
@@ -48573,10 +48549,10 @@
         <v>25</v>
       </c>
       <c r="E1372" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1372" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G1372">
         <v>3.49</v>
@@ -48603,10 +48579,10 @@
         <v>25</v>
       </c>
       <c r="E1373" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1373" t="s">
-        <v>153</v>
+        <v>100</v>
       </c>
       <c r="G1373">
         <v>3.99</v>
@@ -48633,10 +48609,10 @@
         <v>25</v>
       </c>
       <c r="E1374" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1374" t="s">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="G1374">
         <v>4.29</v>
@@ -48663,10 +48639,10 @@
         <v>25</v>
       </c>
       <c r="E1375" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1375" t="s">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="G1375">
         <v>4.6900000000000004</v>
@@ -48693,10 +48669,10 @@
         <v>25</v>
       </c>
       <c r="E1376" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1376" t="s">
-        <v>156</v>
+        <v>71</v>
       </c>
       <c r="G1376">
         <v>3.99</v>
@@ -48723,10 +48699,10 @@
         <v>25</v>
       </c>
       <c r="E1377" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1377" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="G1377">
         <v>6.49</v>
@@ -48753,10 +48729,10 @@
         <v>25</v>
       </c>
       <c r="E1378" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1378" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="G1378">
         <v>3.39</v>
@@ -48783,10 +48759,10 @@
         <v>25</v>
       </c>
       <c r="E1379" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1379" t="s">
-        <v>158</v>
+        <v>69</v>
       </c>
       <c r="G1379">
         <v>3.49</v>
@@ -48813,10 +48789,10 @@
         <v>25</v>
       </c>
       <c r="E1380" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1380" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G1380">
         <v>3.49</v>
@@ -48843,10 +48819,10 @@
         <v>25</v>
       </c>
       <c r="E1381" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1381" t="s">
-        <v>153</v>
+        <v>100</v>
       </c>
       <c r="G1381">
         <v>3.99</v>
@@ -48873,10 +48849,10 @@
         <v>25</v>
       </c>
       <c r="E1382" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1382" t="s">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="G1382">
         <v>4.29</v>
@@ -48903,10 +48879,10 @@
         <v>25</v>
       </c>
       <c r="E1383" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1383" t="s">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="G1383">
         <v>4.6900000000000004</v>
@@ -48933,10 +48909,10 @@
         <v>25</v>
       </c>
       <c r="E1384" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1384" t="s">
-        <v>156</v>
+        <v>71</v>
       </c>
       <c r="G1384">
         <v>3.79</v>
@@ -48963,10 +48939,10 @@
         <v>25</v>
       </c>
       <c r="E1385" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1385" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="G1385">
         <v>6.49</v>
@@ -48993,10 +48969,10 @@
         <v>25</v>
       </c>
       <c r="E1386" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1386" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="G1386">
         <v>3.39</v>
@@ -49023,10 +48999,10 @@
         <v>25</v>
       </c>
       <c r="E1387" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1387" t="s">
-        <v>158</v>
+        <v>69</v>
       </c>
       <c r="G1387">
         <v>3.49</v>
@@ -49053,10 +49029,10 @@
         <v>25</v>
       </c>
       <c r="E1388" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1388" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G1388">
         <v>3.49</v>
@@ -49083,10 +49059,10 @@
         <v>25</v>
       </c>
       <c r="E1389" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1389" t="s">
-        <v>153</v>
+        <v>100</v>
       </c>
       <c r="G1389">
         <v>3.99</v>
@@ -49113,10 +49089,10 @@
         <v>25</v>
       </c>
       <c r="E1390" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1390" t="s">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="G1390">
         <v>4.29</v>
@@ -49143,10 +49119,10 @@
         <v>25</v>
       </c>
       <c r="E1391" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1391" t="s">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="G1391">
         <v>4.6900000000000004</v>
@@ -49173,10 +49149,10 @@
         <v>25</v>
       </c>
       <c r="E1392" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1392" t="s">
-        <v>156</v>
+        <v>71</v>
       </c>
       <c r="G1392">
         <v>3.79</v>
@@ -49203,10 +49179,10 @@
         <v>25</v>
       </c>
       <c r="E1393" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F1393" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="G1393">
         <v>6.49</v>

--- a/data/calendario_promocional.xlsx
+++ b/data/calendario_promocional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anheuserbuschinbev-my.sharepoint.com/personal/99823517_ab-inbev_com/Documents/001. Projetos/Streamlit Calendario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="696" documentId="13_ncr:1_{B92F5DA4-8825-4FA1-97C6-23568D76854D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90628E71-81B2-4F95-90B0-1754537BCE98}"/>
+  <xr:revisionPtr revIDLastSave="714" documentId="13_ncr:1_{B92F5DA4-8825-4FA1-97C6-23568D76854D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC493920-7A39-4D53-B078-0CB82763F2FE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,9 +20,9 @@
     <sheet name="CONFIG" sheetId="4" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">CALENDARIO!$A$1:$C$414</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">CALENDARIO!$A$1:$C$497</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DeparaIMG!$A$1:$F$56</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">MECANICA!$A$1:$D$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">MECANICA!$A$1:$D$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">PRODUTOS!$A$1:$I$1535</definedName>
   </definedNames>
   <calcPr calcId="191029" calcMode="manual"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9291" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9393" uniqueCount="161">
   <si>
     <t>Data</t>
   </si>
@@ -2135,7 +2135,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C497"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:C526"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -2153,7 +2154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>61</v>
       </c>
@@ -2164,7 +2165,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>61</v>
       </c>
@@ -2175,7 +2176,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>61</v>
       </c>
@@ -2186,7 +2187,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>61</v>
       </c>
@@ -2197,7 +2198,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>61</v>
       </c>
@@ -2208,7 +2209,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>61</v>
       </c>
@@ -2219,7 +2220,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>61</v>
       </c>
@@ -2230,7 +2231,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>61</v>
       </c>
@@ -2241,7 +2242,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>61</v>
       </c>
@@ -2252,7 +2253,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>61</v>
       </c>
@@ -2263,7 +2264,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>61</v>
       </c>
@@ -2274,7 +2275,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>61</v>
       </c>
@@ -2285,7 +2286,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>61</v>
       </c>
@@ -2296,7 +2297,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>61</v>
       </c>
@@ -2307,7 +2308,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>61</v>
       </c>
@@ -2318,7 +2319,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>61</v>
       </c>
@@ -2329,7 +2330,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>61</v>
       </c>
@@ -2340,7 +2341,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>61</v>
       </c>
@@ -2351,7 +2352,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>61</v>
       </c>
@@ -2362,7 +2363,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>61</v>
       </c>
@@ -2373,7 +2374,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>61</v>
       </c>
@@ -2384,7 +2385,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>61</v>
       </c>
@@ -2395,7 +2396,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>61</v>
       </c>
@@ -2406,7 +2407,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>61</v>
       </c>
@@ -2417,7 +2418,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>61</v>
       </c>
@@ -2428,7 +2429,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>61</v>
       </c>
@@ -2439,7 +2440,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>61</v>
       </c>
@@ -2450,7 +2451,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>61</v>
       </c>
@@ -2461,7 +2462,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>61</v>
       </c>
@@ -2472,7 +2473,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>61</v>
       </c>
@@ -2483,7 +2484,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>61</v>
       </c>
@@ -2494,7 +2495,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>61</v>
       </c>
@@ -2505,7 +2506,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>61</v>
       </c>
@@ -2516,7 +2517,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>61</v>
       </c>
@@ -2527,7 +2528,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>61</v>
       </c>
@@ -2538,7 +2539,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>61</v>
       </c>
@@ -2549,7 +2550,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>61</v>
       </c>
@@ -2560,7 +2561,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>61</v>
       </c>
@@ -2571,7 +2572,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>61</v>
       </c>
@@ -2582,7 +2583,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>61</v>
       </c>
@@ -2593,7 +2594,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>61</v>
       </c>
@@ -2604,7 +2605,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>61</v>
       </c>
@@ -2615,7 +2616,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>61</v>
       </c>
@@ -2626,7 +2627,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>61</v>
       </c>
@@ -2637,7 +2638,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>61</v>
       </c>
@@ -2648,7 +2649,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>61</v>
       </c>
@@ -2659,7 +2660,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>61</v>
       </c>
@@ -2670,7 +2671,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>61</v>
       </c>
@@ -2681,7 +2682,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>61</v>
       </c>
@@ -2692,7 +2693,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>61</v>
       </c>
@@ -2703,7 +2704,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>61</v>
       </c>
@@ -2714,7 +2715,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>61</v>
       </c>
@@ -2725,7 +2726,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>61</v>
       </c>
@@ -2736,7 +2737,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>61</v>
       </c>
@@ -2747,7 +2748,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>61</v>
       </c>
@@ -2758,7 +2759,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>61</v>
       </c>
@@ -2769,7 +2770,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>61</v>
       </c>
@@ -2780,7 +2781,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>61</v>
       </c>
@@ -2791,7 +2792,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>61</v>
       </c>
@@ -2802,7 +2803,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>61</v>
       </c>
@@ -2813,7 +2814,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>61</v>
       </c>
@@ -2824,7 +2825,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>61</v>
       </c>
@@ -2835,7 +2836,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>61</v>
       </c>
@@ -2846,7 +2847,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>61</v>
       </c>
@@ -2857,7 +2858,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>61</v>
       </c>
@@ -2868,7 +2869,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>61</v>
       </c>
@@ -2879,7 +2880,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>61</v>
       </c>
@@ -2890,7 +2891,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>61</v>
       </c>
@@ -2901,7 +2902,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>61</v>
       </c>
@@ -2912,7 +2913,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>61</v>
       </c>
@@ -2923,7 +2924,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>61</v>
       </c>
@@ -2934,7 +2935,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>61</v>
       </c>
@@ -2945,7 +2946,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>61</v>
       </c>
@@ -2956,7 +2957,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>61</v>
       </c>
@@ -2967,7 +2968,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>61</v>
       </c>
@@ -2978,7 +2979,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>61</v>
       </c>
@@ -2989,7 +2990,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>61</v>
       </c>
@@ -3000,7 +3001,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>61</v>
       </c>
@@ -3011,7 +3012,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>61</v>
       </c>
@@ -3022,7 +3023,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>61</v>
       </c>
@@ -3033,7 +3034,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>61</v>
       </c>
@@ -3044,7 +3045,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>61</v>
       </c>
@@ -3055,7 +3056,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>61</v>
       </c>
@@ -3066,7 +3067,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>61</v>
       </c>
@@ -3077,7 +3078,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>61</v>
       </c>
@@ -3088,7 +3089,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>61</v>
       </c>
@@ -3099,7 +3100,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>61</v>
       </c>
@@ -3110,7 +3111,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>61</v>
       </c>
@@ -3121,7 +3122,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>61</v>
       </c>
@@ -3132,7 +3133,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>61</v>
       </c>
@@ -3143,7 +3144,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>61</v>
       </c>
@@ -3154,7 +3155,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>61</v>
       </c>
@@ -3165,7 +3166,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>61</v>
       </c>
@@ -3176,7 +3177,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>61</v>
       </c>
@@ -3187,7 +3188,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>61</v>
       </c>
@@ -3198,7 +3199,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>61</v>
       </c>
@@ -3209,7 +3210,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>61</v>
       </c>
@@ -3220,7 +3221,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>61</v>
       </c>
@@ -3231,7 +3232,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>61</v>
       </c>
@@ -3242,7 +3243,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>61</v>
       </c>
@@ -3253,7 +3254,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>61</v>
       </c>
@@ -3264,7 +3265,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>61</v>
       </c>
@@ -3275,7 +3276,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>61</v>
       </c>
@@ -3286,7 +3287,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>61</v>
       </c>
@@ -3297,7 +3298,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>61</v>
       </c>
@@ -3308,7 +3309,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>61</v>
       </c>
@@ -3319,7 +3320,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>61</v>
       </c>
@@ -3330,7 +3331,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>61</v>
       </c>
@@ -3341,7 +3342,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>61</v>
       </c>
@@ -3352,7 +3353,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>61</v>
       </c>
@@ -3363,7 +3364,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>61</v>
       </c>
@@ -3374,7 +3375,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>61</v>
       </c>
@@ -3385,7 +3386,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>61</v>
       </c>
@@ -3396,7 +3397,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>61</v>
       </c>
@@ -3407,7 +3408,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>61</v>
       </c>
@@ -3418,7 +3419,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>61</v>
       </c>
@@ -3429,7 +3430,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>61</v>
       </c>
@@ -3440,7 +3441,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>61</v>
       </c>
@@ -3451,7 +3452,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>61</v>
       </c>
@@ -3462,7 +3463,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>61</v>
       </c>
@@ -3473,7 +3474,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>61</v>
       </c>
@@ -3484,7 +3485,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>61</v>
       </c>
@@ -3495,7 +3496,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>61</v>
       </c>
@@ -3506,7 +3507,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>61</v>
       </c>
@@ -3517,7 +3518,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>61</v>
       </c>
@@ -3528,7 +3529,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>61</v>
       </c>
@@ -3539,7 +3540,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>61</v>
       </c>
@@ -3550,7 +3551,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>61</v>
       </c>
@@ -3561,7 +3562,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>61</v>
       </c>
@@ -3572,7 +3573,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>61</v>
       </c>
@@ -3583,7 +3584,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>61</v>
       </c>
@@ -3594,7 +3595,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>61</v>
       </c>
@@ -3605,7 +3606,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>61</v>
       </c>
@@ -3616,7 +3617,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>61</v>
       </c>
@@ -3627,7 +3628,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>61</v>
       </c>
@@ -5167,7 +5168,59 @@
         <v>21</v>
       </c>
     </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="277" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="278" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="279" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="280" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="281" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="282" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="283" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="284" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="285" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="286" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="287" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="288" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="289" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="290" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="291" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="292" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="293" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="294" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="295" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="296" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="297" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="298" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="299" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="300" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="301" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="302" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="303" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="304" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="305" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="306" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="307" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="308" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="309" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="310" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="311" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="312" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="313" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="314" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="315" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="316" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="317" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="318" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="319" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="320" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="321" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="322" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="323" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="324" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="325" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="326" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="327" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="328" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>104</v>
       </c>
@@ -5178,7 +5231,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>104</v>
       </c>
@@ -5189,7 +5242,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>104</v>
       </c>
@@ -5200,7 +5253,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>104</v>
       </c>
@@ -5211,7 +5264,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>104</v>
       </c>
@@ -5222,7 +5275,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>104</v>
       </c>
@@ -5233,7 +5286,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>104</v>
       </c>
@@ -5244,7 +5297,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>104</v>
       </c>
@@ -5255,7 +5308,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>104</v>
       </c>
@@ -5266,7 +5319,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>104</v>
       </c>
@@ -5277,7 +5330,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>104</v>
       </c>
@@ -5288,7 +5341,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>104</v>
       </c>
@@ -5299,7 +5352,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>104</v>
       </c>
@@ -5310,7 +5363,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>104</v>
       </c>
@@ -5321,7 +5374,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>104</v>
       </c>
@@ -5332,7 +5385,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>104</v>
       </c>
@@ -5343,7 +5396,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>104</v>
       </c>
@@ -5354,7 +5407,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>104</v>
       </c>
@@ -5365,7 +5418,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>104</v>
       </c>
@@ -5376,7 +5429,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>104</v>
       </c>
@@ -5387,7 +5440,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>104</v>
       </c>
@@ -5398,7 +5451,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>104</v>
       </c>
@@ -5409,7 +5462,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>104</v>
       </c>
@@ -5420,7 +5473,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>104</v>
       </c>
@@ -5431,7 +5484,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>104</v>
       </c>
@@ -5442,7 +5495,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>104</v>
       </c>
@@ -5453,7 +5506,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>104</v>
       </c>
@@ -5464,7 +5517,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>104</v>
       </c>
@@ -5475,7 +5528,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>104</v>
       </c>
@@ -5486,7 +5539,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>104</v>
       </c>
@@ -5497,7 +5550,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>104</v>
       </c>
@@ -5508,7 +5561,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>104</v>
       </c>
@@ -5519,7 +5572,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>104</v>
       </c>
@@ -5530,7 +5583,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>104</v>
       </c>
@@ -5541,7 +5594,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>104</v>
       </c>
@@ -5552,7 +5605,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>104</v>
       </c>
@@ -5563,7 +5616,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>104</v>
       </c>
@@ -5574,7 +5627,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="365" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>104</v>
       </c>
@@ -5585,7 +5638,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="366" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>104</v>
       </c>
@@ -5596,7 +5649,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="367" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>104</v>
       </c>
@@ -5607,7 +5660,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="368" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>104</v>
       </c>
@@ -5618,7 +5671,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="369" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>104</v>
       </c>
@@ -5629,7 +5682,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="370" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>104</v>
       </c>
@@ -5640,7 +5693,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="371" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>104</v>
       </c>
@@ -5651,7 +5704,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="372" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>104</v>
       </c>
@@ -5662,7 +5715,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="373" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>104</v>
       </c>
@@ -5673,7 +5726,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="374" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>104</v>
       </c>
@@ -5684,7 +5737,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="375" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>104</v>
       </c>
@@ -5695,7 +5748,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="376" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>104</v>
       </c>
@@ -5706,7 +5759,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="377" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>104</v>
       </c>
@@ -5717,7 +5770,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="378" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>104</v>
       </c>
@@ -5728,7 +5781,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="379" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>104</v>
       </c>
@@ -5739,7 +5792,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="380" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>104</v>
       </c>
@@ -5750,7 +5803,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="381" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>104</v>
       </c>
@@ -5761,7 +5814,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="382" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>104</v>
       </c>
@@ -5772,7 +5825,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="383" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>104</v>
       </c>
@@ -5783,7 +5836,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="384" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>104</v>
       </c>
@@ -5794,7 +5847,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="385" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>104</v>
       </c>
@@ -5805,7 +5858,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="386" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>104</v>
       </c>
@@ -5816,7 +5869,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="387" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>104</v>
       </c>
@@ -5827,7 +5880,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="388" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>104</v>
       </c>
@@ -5838,7 +5891,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="389" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>104</v>
       </c>
@@ -5849,7 +5902,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="390" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>104</v>
       </c>
@@ -5860,7 +5913,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="391" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>104</v>
       </c>
@@ -5871,7 +5924,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="392" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>104</v>
       </c>
@@ -5882,7 +5935,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="393" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>104</v>
       </c>
@@ -5893,7 +5946,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="394" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>104</v>
       </c>
@@ -5904,7 +5957,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="395" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>104</v>
       </c>
@@ -5915,7 +5968,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="396" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>104</v>
       </c>
@@ -5926,7 +5979,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="397" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>104</v>
       </c>
@@ -5937,7 +5990,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="398" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>104</v>
       </c>
@@ -5948,7 +6001,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="399" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>104</v>
       </c>
@@ -5959,7 +6012,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="400" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>104</v>
       </c>
@@ -5970,7 +6023,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="401" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>104</v>
       </c>
@@ -5981,7 +6034,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="402" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>104</v>
       </c>
@@ -5992,7 +6045,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="403" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>104</v>
       </c>
@@ -6003,7 +6056,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="404" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>104</v>
       </c>
@@ -6014,7 +6067,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="405" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>104</v>
       </c>
@@ -6025,7 +6078,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="406" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>104</v>
       </c>
@@ -6036,7 +6089,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="407" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>104</v>
       </c>
@@ -6047,7 +6100,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="408" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>104</v>
       </c>
@@ -6058,7 +6111,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="409" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>104</v>
       </c>
@@ -6069,7 +6122,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="410" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>104</v>
       </c>
@@ -6080,7 +6133,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="411" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>104</v>
       </c>
@@ -6091,7 +6144,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="412" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>104</v>
       </c>
@@ -6102,7 +6155,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="413" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>104</v>
       </c>
@@ -6113,7 +6166,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="414" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>104</v>
       </c>
@@ -6124,7 +6177,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="415" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>104</v>
       </c>
@@ -6135,7 +6188,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="416" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>104</v>
       </c>
@@ -6146,7 +6199,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="417" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>104</v>
       </c>
@@ -6157,7 +6210,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="418" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>104</v>
       </c>
@@ -6168,7 +6221,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="419" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>104</v>
       </c>
@@ -6179,7 +6232,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="420" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>104</v>
       </c>
@@ -6190,7 +6243,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="421" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>104</v>
       </c>
@@ -6201,7 +6254,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="422" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>104</v>
       </c>
@@ -6212,7 +6265,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="423" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>104</v>
       </c>
@@ -6223,7 +6276,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="424" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>104</v>
       </c>
@@ -6234,7 +6287,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="425" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>104</v>
       </c>
@@ -6245,7 +6298,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="426" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>104</v>
       </c>
@@ -6256,7 +6309,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="427" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>104</v>
       </c>
@@ -6267,7 +6320,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="428" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>104</v>
       </c>
@@ -6278,7 +6331,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="429" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>104</v>
       </c>
@@ -6289,7 +6342,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="430" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>104</v>
       </c>
@@ -6300,7 +6353,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="431" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>104</v>
       </c>
@@ -6311,7 +6364,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="432" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>104</v>
       </c>
@@ -6322,7 +6375,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="433" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>104</v>
       </c>
@@ -6333,7 +6386,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="434" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>104</v>
       </c>
@@ -6344,7 +6397,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="435" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>104</v>
       </c>
@@ -6355,7 +6408,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="436" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>104</v>
       </c>
@@ -6366,7 +6419,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="437" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>104</v>
       </c>
@@ -6377,7 +6430,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="438" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>104</v>
       </c>
@@ -6388,7 +6441,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="439" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>104</v>
       </c>
@@ -6399,7 +6452,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="440" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>104</v>
       </c>
@@ -6410,7 +6463,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="441" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>104</v>
       </c>
@@ -6421,7 +6474,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="442" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>104</v>
       </c>
@@ -6432,7 +6485,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="443" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>104</v>
       </c>
@@ -6443,7 +6496,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="444" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>104</v>
       </c>
@@ -6454,7 +6507,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="445" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>104</v>
       </c>
@@ -6465,7 +6518,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="446" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>104</v>
       </c>
@@ -6476,7 +6529,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="447" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>104</v>
       </c>
@@ -6487,7 +6540,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="448" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>104</v>
       </c>
@@ -6498,7 +6551,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="449" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>104</v>
       </c>
@@ -6509,7 +6562,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="450" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>104</v>
       </c>
@@ -6520,7 +6573,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="451" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>104</v>
       </c>
@@ -6531,7 +6584,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="452" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>104</v>
       </c>
@@ -6542,7 +6595,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="453" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>104</v>
       </c>
@@ -6553,7 +6606,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="454" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>104</v>
       </c>
@@ -6564,7 +6617,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="455" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>104</v>
       </c>
@@ -6575,7 +6628,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="456" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>104</v>
       </c>
@@ -6586,7 +6639,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="457" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>104</v>
       </c>
@@ -6597,7 +6650,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="458" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>104</v>
       </c>
@@ -6608,7 +6661,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="459" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>104</v>
       </c>
@@ -6619,7 +6672,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="460" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>104</v>
       </c>
@@ -6630,7 +6683,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="461" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>104</v>
       </c>
@@ -6641,7 +6694,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="462" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>104</v>
       </c>
@@ -6652,7 +6705,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="463" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>104</v>
       </c>
@@ -6663,7 +6716,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="464" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>104</v>
       </c>
@@ -6674,7 +6727,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="465" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>104</v>
       </c>
@@ -6685,7 +6738,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="466" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>104</v>
       </c>
@@ -6696,7 +6749,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="467" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>127</v>
       </c>
@@ -6707,7 +6760,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="468" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>127</v>
       </c>
@@ -6718,7 +6771,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="469" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>127</v>
       </c>
@@ -6729,7 +6782,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="470" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>127</v>
       </c>
@@ -6740,7 +6793,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="471" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>127</v>
       </c>
@@ -6751,7 +6804,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="472" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>127</v>
       </c>
@@ -6762,7 +6815,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="473" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>127</v>
       </c>
@@ -6773,7 +6826,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="474" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>127</v>
       </c>
@@ -6784,7 +6837,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="475" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>127</v>
       </c>
@@ -6795,7 +6848,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="476" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>127</v>
       </c>
@@ -6806,7 +6859,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="477" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>127</v>
       </c>
@@ -6817,7 +6870,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="478" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>127</v>
       </c>
@@ -6828,7 +6881,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="479" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>127</v>
       </c>
@@ -6839,7 +6892,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="480" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>127</v>
       </c>
@@ -6850,7 +6903,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="481" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>127</v>
       </c>
@@ -6861,7 +6914,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="482" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>127</v>
       </c>
@@ -6872,7 +6925,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="483" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>127</v>
       </c>
@@ -6883,7 +6936,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="484" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>127</v>
       </c>
@@ -6894,7 +6947,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="485" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>127</v>
       </c>
@@ -6905,7 +6958,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="486" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>127</v>
       </c>
@@ -6916,7 +6969,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="487" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>127</v>
       </c>
@@ -6927,7 +6980,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="488" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>127</v>
       </c>
@@ -6938,7 +6991,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="489" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>127</v>
       </c>
@@ -6949,7 +7002,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="490" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>127</v>
       </c>
@@ -6960,7 +7013,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="491" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>127</v>
       </c>
@@ -6971,7 +7024,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="492" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>127</v>
       </c>
@@ -6982,7 +7035,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="493" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>127</v>
       </c>
@@ -6993,7 +7046,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="494" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>127</v>
       </c>
@@ -7004,7 +7057,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="495" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>127</v>
       </c>
@@ -7015,7 +7068,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="496" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>127</v>
       </c>
@@ -7026,7 +7079,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="497" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>127</v>
       </c>
@@ -7037,15 +7090,369 @@
         <v>21</v>
       </c>
     </row>
+    <row r="498" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A498" t="s">
+        <v>62</v>
+      </c>
+      <c r="B498" s="3">
+        <v>46327</v>
+      </c>
+      <c r="C498" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="499" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A499" t="s">
+        <v>62</v>
+      </c>
+      <c r="B499" s="3">
+        <f>B498+1</f>
+        <v>46328</v>
+      </c>
+      <c r="C499" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="500" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A500" t="s">
+        <v>62</v>
+      </c>
+      <c r="B500" s="3">
+        <f t="shared" ref="B500:B526" si="0">B499+1</f>
+        <v>46329</v>
+      </c>
+      <c r="C500" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="501" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A501" t="s">
+        <v>62</v>
+      </c>
+      <c r="B501" s="3">
+        <f t="shared" si="0"/>
+        <v>46330</v>
+      </c>
+      <c r="C501" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="502" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A502" t="s">
+        <v>62</v>
+      </c>
+      <c r="B502" s="3">
+        <f t="shared" si="0"/>
+        <v>46331</v>
+      </c>
+      <c r="C502" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="503" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A503" t="s">
+        <v>62</v>
+      </c>
+      <c r="B503" s="3">
+        <f t="shared" si="0"/>
+        <v>46332</v>
+      </c>
+      <c r="C503" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="504" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A504" t="s">
+        <v>62</v>
+      </c>
+      <c r="B504" s="3">
+        <f t="shared" si="0"/>
+        <v>46333</v>
+      </c>
+      <c r="C504" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="505" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A505" t="s">
+        <v>62</v>
+      </c>
+      <c r="B505" s="3">
+        <f t="shared" si="0"/>
+        <v>46334</v>
+      </c>
+      <c r="C505" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="506" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A506" t="s">
+        <v>62</v>
+      </c>
+      <c r="B506" s="3">
+        <f t="shared" si="0"/>
+        <v>46335</v>
+      </c>
+      <c r="C506" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="507" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A507" t="s">
+        <v>62</v>
+      </c>
+      <c r="B507" s="3">
+        <f t="shared" si="0"/>
+        <v>46336</v>
+      </c>
+      <c r="C507" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="508" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A508" t="s">
+        <v>62</v>
+      </c>
+      <c r="B508" s="3">
+        <f t="shared" si="0"/>
+        <v>46337</v>
+      </c>
+      <c r="C508" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="509" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A509" t="s">
+        <v>62</v>
+      </c>
+      <c r="B509" s="3">
+        <f t="shared" si="0"/>
+        <v>46338</v>
+      </c>
+      <c r="C509" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="510" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A510" t="s">
+        <v>62</v>
+      </c>
+      <c r="B510" s="3">
+        <f t="shared" si="0"/>
+        <v>46339</v>
+      </c>
+      <c r="C510" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="511" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A511" t="s">
+        <v>62</v>
+      </c>
+      <c r="B511" s="3">
+        <f t="shared" si="0"/>
+        <v>46340</v>
+      </c>
+      <c r="C511" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="512" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A512" t="s">
+        <v>62</v>
+      </c>
+      <c r="B512" s="3">
+        <f t="shared" si="0"/>
+        <v>46341</v>
+      </c>
+      <c r="C512" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="513" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A513" t="s">
+        <v>62</v>
+      </c>
+      <c r="B513" s="3">
+        <f t="shared" si="0"/>
+        <v>46342</v>
+      </c>
+      <c r="C513" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="514" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A514" t="s">
+        <v>62</v>
+      </c>
+      <c r="B514" s="3">
+        <f t="shared" si="0"/>
+        <v>46343</v>
+      </c>
+      <c r="C514" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="515" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A515" t="s">
+        <v>62</v>
+      </c>
+      <c r="B515" s="3">
+        <f t="shared" si="0"/>
+        <v>46344</v>
+      </c>
+      <c r="C515" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="516" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A516" t="s">
+        <v>62</v>
+      </c>
+      <c r="B516" s="3">
+        <f t="shared" si="0"/>
+        <v>46345</v>
+      </c>
+      <c r="C516" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="517" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A517" t="s">
+        <v>62</v>
+      </c>
+      <c r="B517" s="3">
+        <f t="shared" si="0"/>
+        <v>46346</v>
+      </c>
+      <c r="C517" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="518" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A518" t="s">
+        <v>62</v>
+      </c>
+      <c r="B518" s="3">
+        <f t="shared" si="0"/>
+        <v>46347</v>
+      </c>
+      <c r="C518" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="519" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A519" t="s">
+        <v>62</v>
+      </c>
+      <c r="B519" s="3">
+        <f t="shared" si="0"/>
+        <v>46348</v>
+      </c>
+      <c r="C519" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="520" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A520" t="s">
+        <v>62</v>
+      </c>
+      <c r="B520" s="3">
+        <f t="shared" si="0"/>
+        <v>46349</v>
+      </c>
+      <c r="C520" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="521" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A521" t="s">
+        <v>62</v>
+      </c>
+      <c r="B521" s="3">
+        <f t="shared" si="0"/>
+        <v>46350</v>
+      </c>
+      <c r="C521" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="522" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A522" t="s">
+        <v>62</v>
+      </c>
+      <c r="B522" s="3">
+        <f t="shared" si="0"/>
+        <v>46351</v>
+      </c>
+      <c r="C522" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="523" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A523" t="s">
+        <v>62</v>
+      </c>
+      <c r="B523" s="3">
+        <f t="shared" si="0"/>
+        <v>46352</v>
+      </c>
+      <c r="C523" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="524" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A524" t="s">
+        <v>62</v>
+      </c>
+      <c r="B524" s="3">
+        <f t="shared" si="0"/>
+        <v>46353</v>
+      </c>
+      <c r="C524" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="525" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A525" t="s">
+        <v>62</v>
+      </c>
+      <c r="B525" s="3">
+        <f t="shared" si="0"/>
+        <v>46354</v>
+      </c>
+      <c r="C525" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="526" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A526" t="s">
+        <v>62</v>
+      </c>
+      <c r="B526" s="3">
+        <f t="shared" si="0"/>
+        <v>46355</v>
+      </c>
+      <c r="C526" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C414" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:C497" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="CERV"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D40F4A5-E774-499A-A01D-1C21EEE25028}">
-  <dimension ref="A1:D52"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="47.5703125" bestFit="1" customWidth="1"/>
@@ -7065,7 +7472,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -7079,7 +7486,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -7093,7 +7500,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -7107,7 +7514,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -7121,7 +7528,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -7135,7 +7542,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -7149,7 +7556,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -7163,7 +7570,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -7177,7 +7584,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
@@ -7191,7 +7598,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -7205,7 +7612,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
@@ -7219,7 +7626,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>10</v>
       </c>
@@ -7233,7 +7640,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>10</v>
       </c>
@@ -7345,7 +7752,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>103</v>
       </c>
@@ -7359,7 +7766,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>103</v>
       </c>
@@ -7373,7 +7780,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>103</v>
       </c>
@@ -7387,7 +7794,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>103</v>
       </c>
@@ -7401,7 +7808,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>103</v>
       </c>
@@ -7415,7 +7822,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>103</v>
       </c>
@@ -7429,7 +7836,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>99</v>
       </c>
@@ -7443,7 +7850,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>99</v>
       </c>
@@ -7457,7 +7864,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>99</v>
       </c>
@@ -7471,7 +7878,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>99</v>
       </c>
@@ -7485,7 +7892,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>99</v>
       </c>
@@ -7499,7 +7906,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>99</v>
       </c>
@@ -7513,7 +7920,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>102</v>
       </c>
@@ -7527,7 +7934,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>102</v>
       </c>
@@ -7541,7 +7948,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>102</v>
       </c>
@@ -7555,7 +7962,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>102</v>
       </c>
@@ -7569,7 +7976,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>102</v>
       </c>
@@ -7583,7 +7990,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>102</v>
       </c>
@@ -7779,8 +8186,168 @@
         <v>130</v>
       </c>
     </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D49" xr:uid="{6D40F4A5-E774-499A-A01D-1C21EEE25028}"/>
+  <autoFilter ref="A1:D52" xr:uid="{6D40F4A5-E774-499A-A01D-1C21EEE25028}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Outubro"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>

--- a/data/calendario_promocional.xlsx
+++ b/data/calendario_promocional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anheuserbuschinbev-my.sharepoint.com/personal/99823517_ab-inbev_com/Documents/001. Projetos/Streamlit Calendario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="714" documentId="13_ncr:1_{B92F5DA4-8825-4FA1-97C6-23568D76854D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC493920-7A39-4D53-B078-0CB82763F2FE}"/>
+  <xr:revisionPtr revIDLastSave="733" documentId="13_ncr:1_{B92F5DA4-8825-4FA1-97C6-23568D76854D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00E215A7-FBB7-4FAA-8C22-C9870E1A935D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DeparaIMG" sheetId="5" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="CONFIG" sheetId="4" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">CALENDARIO!$A$1:$C$497</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">CALENDARIO!$A$1:$C$526</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DeparaIMG!$A$1:$F$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">MECANICA!$A$1:$D$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">PRODUTOS!$A$1:$I$1535</definedName>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9393" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9497" uniqueCount="161">
   <si>
     <t>Data</t>
   </si>
@@ -2136,7 +2136,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:C526"/>
+  <dimension ref="A1:C578"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -2154,7 +2154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>61</v>
       </c>
@@ -2165,7 +2165,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>61</v>
       </c>
@@ -2176,7 +2176,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>61</v>
       </c>
@@ -2187,7 +2187,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>61</v>
       </c>
@@ -2198,7 +2198,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>61</v>
       </c>
@@ -2209,7 +2209,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>61</v>
       </c>
@@ -2220,7 +2220,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>61</v>
       </c>
@@ -2231,7 +2231,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>61</v>
       </c>
@@ -2242,7 +2242,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>61</v>
       </c>
@@ -2253,7 +2253,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>61</v>
       </c>
@@ -2264,7 +2264,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>61</v>
       </c>
@@ -2275,7 +2275,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>61</v>
       </c>
@@ -2286,7 +2286,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>61</v>
       </c>
@@ -2297,7 +2297,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>61</v>
       </c>
@@ -2308,7 +2308,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>61</v>
       </c>
@@ -2319,7 +2319,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>61</v>
       </c>
@@ -2330,7 +2330,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>61</v>
       </c>
@@ -2341,7 +2341,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>61</v>
       </c>
@@ -2352,7 +2352,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>61</v>
       </c>
@@ -2363,7 +2363,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>61</v>
       </c>
@@ -2374,7 +2374,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>61</v>
       </c>
@@ -2385,7 +2385,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>61</v>
       </c>
@@ -2396,7 +2396,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>61</v>
       </c>
@@ -2407,7 +2407,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>61</v>
       </c>
@@ -2418,7 +2418,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>61</v>
       </c>
@@ -2429,7 +2429,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>61</v>
       </c>
@@ -2440,7 +2440,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>61</v>
       </c>
@@ -2451,7 +2451,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>61</v>
       </c>
@@ -2462,7 +2462,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>61</v>
       </c>
@@ -2473,7 +2473,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>61</v>
       </c>
@@ -2484,7 +2484,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>61</v>
       </c>
@@ -2495,7 +2495,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>61</v>
       </c>
@@ -2506,7 +2506,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>61</v>
       </c>
@@ -2517,7 +2517,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>61</v>
       </c>
@@ -2528,7 +2528,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>61</v>
       </c>
@@ -2539,7 +2539,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>61</v>
       </c>
@@ -2550,7 +2550,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>61</v>
       </c>
@@ -2561,7 +2561,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="39" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>61</v>
       </c>
@@ -2572,7 +2572,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>61</v>
       </c>
@@ -2583,7 +2583,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>61</v>
       </c>
@@ -2594,7 +2594,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="42" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>61</v>
       </c>
@@ -2605,7 +2605,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>61</v>
       </c>
@@ -2616,7 +2616,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="44" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>61</v>
       </c>
@@ -2627,7 +2627,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="45" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>61</v>
       </c>
@@ -2638,7 +2638,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="46" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>61</v>
       </c>
@@ -2649,7 +2649,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="47" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>61</v>
       </c>
@@ -2660,7 +2660,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="48" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>61</v>
       </c>
@@ -2671,7 +2671,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="49" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>61</v>
       </c>
@@ -2682,7 +2682,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="50" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>61</v>
       </c>
@@ -2693,7 +2693,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="51" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>61</v>
       </c>
@@ -2704,7 +2704,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="52" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>61</v>
       </c>
@@ -2715,7 +2715,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="53" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>61</v>
       </c>
@@ -2726,7 +2726,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="54" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>61</v>
       </c>
@@ -2737,7 +2737,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="55" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>61</v>
       </c>
@@ -2748,7 +2748,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="56" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>61</v>
       </c>
@@ -2759,7 +2759,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="57" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>61</v>
       </c>
@@ -2770,7 +2770,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="58" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>61</v>
       </c>
@@ -2781,7 +2781,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="59" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>61</v>
       </c>
@@ -2792,7 +2792,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="60" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>61</v>
       </c>
@@ -2803,7 +2803,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="61" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>61</v>
       </c>
@@ -2814,7 +2814,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="62" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>61</v>
       </c>
@@ -2825,7 +2825,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="63" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>61</v>
       </c>
@@ -2836,7 +2836,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="64" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>61</v>
       </c>
@@ -2847,7 +2847,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="65" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>61</v>
       </c>
@@ -2858,7 +2858,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="66" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>61</v>
       </c>
@@ -2869,7 +2869,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="67" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>61</v>
       </c>
@@ -2880,7 +2880,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="68" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>61</v>
       </c>
@@ -2891,7 +2891,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="69" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>61</v>
       </c>
@@ -2902,7 +2902,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="70" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>61</v>
       </c>
@@ -2913,7 +2913,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="71" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>61</v>
       </c>
@@ -2924,7 +2924,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="72" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>61</v>
       </c>
@@ -2935,7 +2935,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="73" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>61</v>
       </c>
@@ -2946,7 +2946,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="74" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>61</v>
       </c>
@@ -2957,7 +2957,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="75" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>61</v>
       </c>
@@ -2968,7 +2968,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="76" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>61</v>
       </c>
@@ -2979,7 +2979,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="77" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>61</v>
       </c>
@@ -2990,7 +2990,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="78" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>61</v>
       </c>
@@ -3001,7 +3001,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="79" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>61</v>
       </c>
@@ -3012,7 +3012,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="80" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>61</v>
       </c>
@@ -3023,7 +3023,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="81" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>61</v>
       </c>
@@ -3034,7 +3034,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="82" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>61</v>
       </c>
@@ -3045,7 +3045,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="83" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>61</v>
       </c>
@@ -3056,7 +3056,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="84" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>61</v>
       </c>
@@ -3067,7 +3067,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="85" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>61</v>
       </c>
@@ -3078,7 +3078,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="86" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>61</v>
       </c>
@@ -3089,7 +3089,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="87" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>61</v>
       </c>
@@ -3100,7 +3100,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="88" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>61</v>
       </c>
@@ -3111,7 +3111,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="89" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>61</v>
       </c>
@@ -3122,7 +3122,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="90" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>61</v>
       </c>
@@ -3133,7 +3133,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="91" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>61</v>
       </c>
@@ -3144,7 +3144,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="92" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>61</v>
       </c>
@@ -3155,7 +3155,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="93" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>61</v>
       </c>
@@ -3166,7 +3166,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="94" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>61</v>
       </c>
@@ -3177,7 +3177,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="95" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>61</v>
       </c>
@@ -3188,7 +3188,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="96" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>61</v>
       </c>
@@ -3199,7 +3199,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="97" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>61</v>
       </c>
@@ -3210,7 +3210,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="98" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>61</v>
       </c>
@@ -3221,7 +3221,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="99" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>61</v>
       </c>
@@ -3232,7 +3232,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="100" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>61</v>
       </c>
@@ -3243,7 +3243,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="101" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>61</v>
       </c>
@@ -3254,7 +3254,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="102" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>61</v>
       </c>
@@ -3265,7 +3265,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="103" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>61</v>
       </c>
@@ -3276,7 +3276,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="104" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>61</v>
       </c>
@@ -3287,7 +3287,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="105" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>61</v>
       </c>
@@ -3298,7 +3298,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="106" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>61</v>
       </c>
@@ -3309,7 +3309,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="107" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>61</v>
       </c>
@@ -3320,7 +3320,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="108" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>61</v>
       </c>
@@ -3331,7 +3331,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="109" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>61</v>
       </c>
@@ -3342,7 +3342,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="110" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>61</v>
       </c>
@@ -3353,7 +3353,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="111" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>61</v>
       </c>
@@ -3364,7 +3364,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="112" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>61</v>
       </c>
@@ -3375,7 +3375,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="113" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>61</v>
       </c>
@@ -3386,7 +3386,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="114" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>61</v>
       </c>
@@ -3397,7 +3397,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="115" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>61</v>
       </c>
@@ -3408,7 +3408,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="116" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>61</v>
       </c>
@@ -3419,7 +3419,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="117" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>61</v>
       </c>
@@ -3430,7 +3430,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="118" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>61</v>
       </c>
@@ -3441,7 +3441,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="119" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>61</v>
       </c>
@@ -3452,7 +3452,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="120" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>61</v>
       </c>
@@ -3463,7 +3463,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="121" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>61</v>
       </c>
@@ -3474,7 +3474,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="122" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>61</v>
       </c>
@@ -3485,7 +3485,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="123" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>61</v>
       </c>
@@ -3496,7 +3496,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="124" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>61</v>
       </c>
@@ -3507,7 +3507,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="125" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>61</v>
       </c>
@@ -3518,7 +3518,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="126" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>61</v>
       </c>
@@ -3529,7 +3529,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="127" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>61</v>
       </c>
@@ -3540,7 +3540,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="128" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>61</v>
       </c>
@@ -3551,7 +3551,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="129" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>61</v>
       </c>
@@ -3562,7 +3562,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="130" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>61</v>
       </c>
@@ -3573,7 +3573,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="131" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>61</v>
       </c>
@@ -3584,7 +3584,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="132" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>61</v>
       </c>
@@ -3595,7 +3595,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="133" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>61</v>
       </c>
@@ -3606,7 +3606,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="134" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>61</v>
       </c>
@@ -3617,7 +3617,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="135" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>61</v>
       </c>
@@ -3628,7 +3628,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="136" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>61</v>
       </c>
@@ -3639,7 +3639,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>62</v>
       </c>
@@ -3650,7 +3650,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>62</v>
       </c>
@@ -3661,7 +3661,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>62</v>
       </c>
@@ -3672,7 +3672,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>62</v>
       </c>
@@ -3683,7 +3683,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>62</v>
       </c>
@@ -3694,7 +3694,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>62</v>
       </c>
@@ -3705,7 +3705,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>62</v>
       </c>
@@ -3716,7 +3716,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>62</v>
       </c>
@@ -3727,7 +3727,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>62</v>
       </c>
@@ -3738,7 +3738,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>62</v>
       </c>
@@ -3749,7 +3749,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>62</v>
       </c>
@@ -3760,7 +3760,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>62</v>
       </c>
@@ -3771,7 +3771,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>62</v>
       </c>
@@ -3782,7 +3782,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>62</v>
       </c>
@@ -3793,7 +3793,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>62</v>
       </c>
@@ -3804,7 +3804,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>62</v>
       </c>
@@ -3815,7 +3815,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>62</v>
       </c>
@@ -3826,7 +3826,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>62</v>
       </c>
@@ -3837,7 +3837,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>62</v>
       </c>
@@ -3848,7 +3848,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>62</v>
       </c>
@@ -3859,7 +3859,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>62</v>
       </c>
@@ -3870,7 +3870,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>62</v>
       </c>
@@ -3881,7 +3881,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>62</v>
       </c>
@@ -3892,7 +3892,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>62</v>
       </c>
@@ -3903,7 +3903,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>62</v>
       </c>
@@ -3914,7 +3914,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>62</v>
       </c>
@@ -3925,7 +3925,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>62</v>
       </c>
@@ -3936,7 +3936,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>62</v>
       </c>
@@ -3947,7 +3947,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>62</v>
       </c>
@@ -3958,7 +3958,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>62</v>
       </c>
@@ -3969,7 +3969,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>62</v>
       </c>
@@ -3980,7 +3980,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>62</v>
       </c>
@@ -3991,7 +3991,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>62</v>
       </c>
@@ -4002,7 +4002,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>62</v>
       </c>
@@ -4013,7 +4013,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>62</v>
       </c>
@@ -4024,7 +4024,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>62</v>
       </c>
@@ -4035,7 +4035,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>62</v>
       </c>
@@ -4046,7 +4046,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>62</v>
       </c>
@@ -4057,7 +4057,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>62</v>
       </c>
@@ -4068,7 +4068,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>62</v>
       </c>
@@ -4079,7 +4079,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>62</v>
       </c>
@@ -4090,7 +4090,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>62</v>
       </c>
@@ -4101,7 +4101,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>62</v>
       </c>
@@ -4112,7 +4112,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>62</v>
       </c>
@@ -4123,7 +4123,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>62</v>
       </c>
@@ -4134,7 +4134,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>62</v>
       </c>
@@ -4145,7 +4145,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>62</v>
       </c>
@@ -4156,7 +4156,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>62</v>
       </c>
@@ -4167,7 +4167,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>62</v>
       </c>
@@ -4178,7 +4178,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>62</v>
       </c>
@@ -4189,7 +4189,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>62</v>
       </c>
@@ -4200,7 +4200,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>62</v>
       </c>
@@ -4211,7 +4211,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>62</v>
       </c>
@@ -4222,7 +4222,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>62</v>
       </c>
@@ -4233,7 +4233,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>62</v>
       </c>
@@ -4244,7 +4244,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>62</v>
       </c>
@@ -4255,7 +4255,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>62</v>
       </c>
@@ -4266,7 +4266,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>62</v>
       </c>
@@ -4277,7 +4277,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>62</v>
       </c>
@@ -4288,7 +4288,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>62</v>
       </c>
@@ -4299,7 +4299,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>62</v>
       </c>
@@ -4310,7 +4310,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>62</v>
       </c>
@@ -4321,7 +4321,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>62</v>
       </c>
@@ -4332,7 +4332,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>62</v>
       </c>
@@ -4343,7 +4343,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>62</v>
       </c>
@@ -4354,7 +4354,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>62</v>
       </c>
@@ -4365,7 +4365,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>62</v>
       </c>
@@ -4376,7 +4376,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>62</v>
       </c>
@@ -4387,7 +4387,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>62</v>
       </c>
@@ -4398,7 +4398,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>62</v>
       </c>
@@ -4409,7 +4409,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>62</v>
       </c>
@@ -4420,7 +4420,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>62</v>
       </c>
@@ -4431,7 +4431,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>62</v>
       </c>
@@ -4442,7 +4442,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>62</v>
       </c>
@@ -4453,7 +4453,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>62</v>
       </c>
@@ -4464,7 +4464,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>62</v>
       </c>
@@ -4475,7 +4475,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>62</v>
       </c>
@@ -4486,7 +4486,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>62</v>
       </c>
@@ -4497,7 +4497,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>62</v>
       </c>
@@ -4508,7 +4508,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>62</v>
       </c>
@@ -4519,7 +4519,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>62</v>
       </c>
@@ -4530,7 +4530,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>62</v>
       </c>
@@ -4541,7 +4541,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>62</v>
       </c>
@@ -4552,7 +4552,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>62</v>
       </c>
@@ -4563,7 +4563,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>62</v>
       </c>
@@ -4574,7 +4574,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>62</v>
       </c>
@@ -4585,7 +4585,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>62</v>
       </c>
@@ -4596,7 +4596,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>62</v>
       </c>
@@ -4607,7 +4607,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>62</v>
       </c>
@@ -4618,7 +4618,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>62</v>
       </c>
@@ -4629,7 +4629,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>62</v>
       </c>
@@ -4640,7 +4640,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>62</v>
       </c>
@@ -4651,7 +4651,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>62</v>
       </c>
@@ -4662,7 +4662,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>62</v>
       </c>
@@ -4673,7 +4673,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>62</v>
       </c>
@@ -4684,7 +4684,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>62</v>
       </c>
@@ -4695,7 +4695,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>62</v>
       </c>
@@ -4706,7 +4706,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>62</v>
       </c>
@@ -4717,7 +4717,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>62</v>
       </c>
@@ -4728,7 +4728,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>62</v>
       </c>
@@ -4739,7 +4739,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>62</v>
       </c>
@@ -4750,7 +4750,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>62</v>
       </c>
@@ -4761,7 +4761,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>62</v>
       </c>
@@ -4772,7 +4772,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>62</v>
       </c>
@@ -4783,7 +4783,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>62</v>
       </c>
@@ -4794,7 +4794,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>62</v>
       </c>
@@ -4805,7 +4805,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>62</v>
       </c>
@@ -4816,7 +4816,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>62</v>
       </c>
@@ -4827,7 +4827,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>62</v>
       </c>
@@ -4838,7 +4838,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>62</v>
       </c>
@@ -4849,7 +4849,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>62</v>
       </c>
@@ -4860,7 +4860,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>62</v>
       </c>
@@ -4871,7 +4871,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>62</v>
       </c>
@@ -4882,7 +4882,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>62</v>
       </c>
@@ -4893,7 +4893,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>62</v>
       </c>
@@ -4904,7 +4904,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>62</v>
       </c>
@@ -4915,7 +4915,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>62</v>
       </c>
@@ -4926,7 +4926,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>62</v>
       </c>
@@ -4937,7 +4937,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>62</v>
       </c>
@@ -4948,7 +4948,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>62</v>
       </c>
@@ -4959,7 +4959,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>62</v>
       </c>
@@ -4970,7 +4970,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>62</v>
       </c>
@@ -4981,7 +4981,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>62</v>
       </c>
@@ -4992,7 +4992,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>62</v>
       </c>
@@ -5003,7 +5003,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>62</v>
       </c>
@@ -5014,7 +5014,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>62</v>
       </c>
@@ -5025,7 +5025,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>62</v>
       </c>
@@ -5036,7 +5036,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>62</v>
       </c>
@@ -5047,7 +5047,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>62</v>
       </c>
@@ -5058,7 +5058,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>62</v>
       </c>
@@ -5069,7 +5069,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>62</v>
       </c>
@@ -5080,7 +5080,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>62</v>
       </c>
@@ -5091,7 +5091,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>62</v>
       </c>
@@ -5102,7 +5102,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>62</v>
       </c>
@@ -5113,7 +5113,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>62</v>
       </c>
@@ -5124,7 +5124,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>62</v>
       </c>
@@ -5135,7 +5135,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>62</v>
       </c>
@@ -5146,7 +5146,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>62</v>
       </c>
@@ -5157,7 +5157,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>62</v>
       </c>
@@ -7090,7 +7090,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="498" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>62</v>
       </c>
@@ -7101,7 +7101,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="499" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>62</v>
       </c>
@@ -7113,7 +7113,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="500" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>62</v>
       </c>
@@ -7125,7 +7125,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="501" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>62</v>
       </c>
@@ -7137,7 +7137,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="502" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>62</v>
       </c>
@@ -7149,7 +7149,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="503" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>62</v>
       </c>
@@ -7161,7 +7161,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="504" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>62</v>
       </c>
@@ -7173,7 +7173,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="505" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>62</v>
       </c>
@@ -7185,7 +7185,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="506" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>62</v>
       </c>
@@ -7197,7 +7197,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="507" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>62</v>
       </c>
@@ -7209,7 +7209,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="508" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>62</v>
       </c>
@@ -7221,7 +7221,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="509" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>62</v>
       </c>
@@ -7233,7 +7233,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="510" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>62</v>
       </c>
@@ -7245,7 +7245,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="511" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>62</v>
       </c>
@@ -7257,7 +7257,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="512" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>62</v>
       </c>
@@ -7269,7 +7269,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="513" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>62</v>
       </c>
@@ -7281,7 +7281,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="514" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>62</v>
       </c>
@@ -7293,7 +7293,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="515" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>62</v>
       </c>
@@ -7305,7 +7305,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="516" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>62</v>
       </c>
@@ -7317,7 +7317,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="517" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>62</v>
       </c>
@@ -7329,7 +7329,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="518" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>62</v>
       </c>
@@ -7341,7 +7341,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="519" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>62</v>
       </c>
@@ -7353,7 +7353,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="520" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>62</v>
       </c>
@@ -7365,7 +7365,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="521" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>62</v>
       </c>
@@ -7377,7 +7377,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="522" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>62</v>
       </c>
@@ -7389,7 +7389,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="523" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>62</v>
       </c>
@@ -7401,7 +7401,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="524" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>62</v>
       </c>
@@ -7413,7 +7413,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="525" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>62</v>
       </c>
@@ -7425,7 +7425,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="526" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>62</v>
       </c>
@@ -7437,11 +7437,607 @@
         <v>21</v>
       </c>
     </row>
+    <row r="527" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A527" t="s">
+        <v>61</v>
+      </c>
+      <c r="B527" s="3">
+        <v>46327</v>
+      </c>
+      <c r="C527" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="528" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A528" t="s">
+        <v>61</v>
+      </c>
+      <c r="B528" s="3">
+        <f>B527+1</f>
+        <v>46328</v>
+      </c>
+      <c r="C528" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="529" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A529" t="s">
+        <v>61</v>
+      </c>
+      <c r="B529" s="3">
+        <f t="shared" ref="B529:B552" si="1">B528+1</f>
+        <v>46329</v>
+      </c>
+      <c r="C529" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="530" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A530" t="s">
+        <v>61</v>
+      </c>
+      <c r="B530" s="3">
+        <f t="shared" si="1"/>
+        <v>46330</v>
+      </c>
+      <c r="C530" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="531" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A531" t="s">
+        <v>61</v>
+      </c>
+      <c r="B531" s="3">
+        <f t="shared" si="1"/>
+        <v>46331</v>
+      </c>
+      <c r="C531" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="532" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A532" t="s">
+        <v>61</v>
+      </c>
+      <c r="B532" s="3">
+        <f t="shared" si="1"/>
+        <v>46332</v>
+      </c>
+      <c r="C532" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="533" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A533" t="s">
+        <v>61</v>
+      </c>
+      <c r="B533" s="3">
+        <f t="shared" si="1"/>
+        <v>46333</v>
+      </c>
+      <c r="C533" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="534" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A534" t="s">
+        <v>61</v>
+      </c>
+      <c r="B534" s="3">
+        <f t="shared" si="1"/>
+        <v>46334</v>
+      </c>
+      <c r="C534" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="535" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A535" t="s">
+        <v>61</v>
+      </c>
+      <c r="B535" s="3">
+        <v>46338</v>
+      </c>
+      <c r="C535" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="536" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A536" t="s">
+        <v>61</v>
+      </c>
+      <c r="B536" s="3">
+        <f t="shared" si="1"/>
+        <v>46339</v>
+      </c>
+      <c r="C536" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="537" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A537" t="s">
+        <v>61</v>
+      </c>
+      <c r="B537" s="3">
+        <f t="shared" si="1"/>
+        <v>46340</v>
+      </c>
+      <c r="C537" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="538" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A538" t="s">
+        <v>61</v>
+      </c>
+      <c r="B538" s="3">
+        <f t="shared" si="1"/>
+        <v>46341</v>
+      </c>
+      <c r="C538" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="539" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A539" t="s">
+        <v>61</v>
+      </c>
+      <c r="B539" s="3">
+        <f t="shared" si="1"/>
+        <v>46342</v>
+      </c>
+      <c r="C539" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="540" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A540" t="s">
+        <v>61</v>
+      </c>
+      <c r="B540" s="3">
+        <f t="shared" si="1"/>
+        <v>46343</v>
+      </c>
+      <c r="C540" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="541" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A541" t="s">
+        <v>61</v>
+      </c>
+      <c r="B541" s="3">
+        <f t="shared" si="1"/>
+        <v>46344</v>
+      </c>
+      <c r="C541" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="542" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A542" t="s">
+        <v>61</v>
+      </c>
+      <c r="B542" s="3">
+        <f t="shared" si="1"/>
+        <v>46345</v>
+      </c>
+      <c r="C542" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="543" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A543" t="s">
+        <v>61</v>
+      </c>
+      <c r="B543" s="3">
+        <f t="shared" si="1"/>
+        <v>46346</v>
+      </c>
+      <c r="C543" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="544" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A544" t="s">
+        <v>61</v>
+      </c>
+      <c r="B544" s="3">
+        <f t="shared" si="1"/>
+        <v>46347</v>
+      </c>
+      <c r="C544" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="545" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A545" t="s">
+        <v>61</v>
+      </c>
+      <c r="B545" s="3">
+        <f t="shared" si="1"/>
+        <v>46348</v>
+      </c>
+      <c r="C545" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="546" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A546" t="s">
+        <v>61</v>
+      </c>
+      <c r="B546" s="3">
+        <f t="shared" si="1"/>
+        <v>46349</v>
+      </c>
+      <c r="C546" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="547" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A547" t="s">
+        <v>61</v>
+      </c>
+      <c r="B547" s="3">
+        <f t="shared" si="1"/>
+        <v>46350</v>
+      </c>
+      <c r="C547" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="548" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A548" t="s">
+        <v>61</v>
+      </c>
+      <c r="B548" s="3">
+        <f t="shared" si="1"/>
+        <v>46351</v>
+      </c>
+      <c r="C548" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="549" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A549" t="s">
+        <v>61</v>
+      </c>
+      <c r="B549" s="3">
+        <f t="shared" si="1"/>
+        <v>46352</v>
+      </c>
+      <c r="C549" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="550" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A550" t="s">
+        <v>61</v>
+      </c>
+      <c r="B550" s="3">
+        <f t="shared" si="1"/>
+        <v>46353</v>
+      </c>
+      <c r="C550" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="551" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A551" t="s">
+        <v>61</v>
+      </c>
+      <c r="B551" s="3">
+        <f t="shared" si="1"/>
+        <v>46354</v>
+      </c>
+      <c r="C551" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="552" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A552" t="s">
+        <v>61</v>
+      </c>
+      <c r="B552" s="3">
+        <f t="shared" si="1"/>
+        <v>46355</v>
+      </c>
+      <c r="C552" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="553" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A553" t="s">
+        <v>104</v>
+      </c>
+      <c r="B553" s="3">
+        <v>46327</v>
+      </c>
+      <c r="C553" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="554" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A554" t="s">
+        <v>104</v>
+      </c>
+      <c r="B554" s="3">
+        <v>46328</v>
+      </c>
+      <c r="C554" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="555" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A555" t="s">
+        <v>104</v>
+      </c>
+      <c r="B555" s="3">
+        <v>46329</v>
+      </c>
+      <c r="C555" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="556" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A556" t="s">
+        <v>104</v>
+      </c>
+      <c r="B556" s="3">
+        <v>46330</v>
+      </c>
+      <c r="C556" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="557" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A557" t="s">
+        <v>104</v>
+      </c>
+      <c r="B557" s="3">
+        <v>46331</v>
+      </c>
+      <c r="C557" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="558" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A558" t="s">
+        <v>104</v>
+      </c>
+      <c r="B558" s="3">
+        <v>46332</v>
+      </c>
+      <c r="C558" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="559" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A559" t="s">
+        <v>104</v>
+      </c>
+      <c r="B559" s="3">
+        <v>46333</v>
+      </c>
+      <c r="C559" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="560" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A560" t="s">
+        <v>104</v>
+      </c>
+      <c r="B560" s="3">
+        <v>46334</v>
+      </c>
+      <c r="C560" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="561" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A561" t="s">
+        <v>104</v>
+      </c>
+      <c r="B561" s="3">
+        <v>46338</v>
+      </c>
+      <c r="C561" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="562" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A562" t="s">
+        <v>104</v>
+      </c>
+      <c r="B562" s="3">
+        <v>46339</v>
+      </c>
+      <c r="C562" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="563" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A563" t="s">
+        <v>104</v>
+      </c>
+      <c r="B563" s="3">
+        <v>46340</v>
+      </c>
+      <c r="C563" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="564" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A564" t="s">
+        <v>104</v>
+      </c>
+      <c r="B564" s="3">
+        <v>46341</v>
+      </c>
+      <c r="C564" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="565" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A565" t="s">
+        <v>104</v>
+      </c>
+      <c r="B565" s="3">
+        <v>46342</v>
+      </c>
+      <c r="C565" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="566" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A566" t="s">
+        <v>104</v>
+      </c>
+      <c r="B566" s="3">
+        <v>46343</v>
+      </c>
+      <c r="C566" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="567" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A567" t="s">
+        <v>104</v>
+      </c>
+      <c r="B567" s="3">
+        <v>46344</v>
+      </c>
+      <c r="C567" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="568" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A568" t="s">
+        <v>104</v>
+      </c>
+      <c r="B568" s="3">
+        <v>46345</v>
+      </c>
+      <c r="C568" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="569" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A569" t="s">
+        <v>104</v>
+      </c>
+      <c r="B569" s="3">
+        <v>46346</v>
+      </c>
+      <c r="C569" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="570" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A570" t="s">
+        <v>104</v>
+      </c>
+      <c r="B570" s="3">
+        <v>46347</v>
+      </c>
+      <c r="C570" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="571" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A571" t="s">
+        <v>104</v>
+      </c>
+      <c r="B571" s="3">
+        <v>46348</v>
+      </c>
+      <c r="C571" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="572" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A572" t="s">
+        <v>104</v>
+      </c>
+      <c r="B572" s="3">
+        <v>46349</v>
+      </c>
+      <c r="C572" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="573" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A573" t="s">
+        <v>104</v>
+      </c>
+      <c r="B573" s="3">
+        <v>46350</v>
+      </c>
+      <c r="C573" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="574" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A574" t="s">
+        <v>104</v>
+      </c>
+      <c r="B574" s="3">
+        <v>46351</v>
+      </c>
+      <c r="C574" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="575" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A575" t="s">
+        <v>104</v>
+      </c>
+      <c r="B575" s="3">
+        <v>46352</v>
+      </c>
+      <c r="C575" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="576" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A576" t="s">
+        <v>104</v>
+      </c>
+      <c r="B576" s="3">
+        <v>46353</v>
+      </c>
+      <c r="C576" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="577" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A577" t="s">
+        <v>104</v>
+      </c>
+      <c r="B577" s="3">
+        <v>46354</v>
+      </c>
+      <c r="C577" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="578" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A578" t="s">
+        <v>104</v>
+      </c>
+      <c r="B578" s="3">
+        <v>46355</v>
+      </c>
+      <c r="C578" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C497" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter ref="A1:C526" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="CERV"/>
+        <filter val="NAB"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/data/calendario_promocional.xlsx
+++ b/data/calendario_promocional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anheuserbuschinbev-my.sharepoint.com/personal/99823517_ab-inbev_com/Documents/001. Projetos/Streamlit Calendario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="733" documentId="13_ncr:1_{B92F5DA4-8825-4FA1-97C6-23568D76854D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00E215A7-FBB7-4FAA-8C22-C9870E1A935D}"/>
+  <xr:revisionPtr revIDLastSave="812" documentId="13_ncr:1_{B92F5DA4-8825-4FA1-97C6-23568D76854D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F09FEBB7-5496-45DF-A044-65D2825F9E0F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DeparaIMG" sheetId="5" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">CALENDARIO!$A$1:$C$526</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DeparaIMG!$A$1:$F$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">MECANICA!$A$1:$D$52</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">PRODUTOS!$A$1:$I$1535</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">PRODUTOS!$A$1:$I$1591</definedName>
   </definedNames>
   <calcPr calcId="191029" calcMode="manual"/>
   <extLst>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9497" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9833" uniqueCount="162">
   <si>
     <t>Data</t>
   </si>
@@ -504,9 +504,6 @@
     <t>BDM 269</t>
   </si>
   <si>
-    <t>PP</t>
-  </si>
-  <si>
     <t>Promax</t>
   </si>
   <si>
@@ -529,6 +526,12 @@
   </si>
   <si>
     <t>Pague 2</t>
+  </si>
+  <si>
+    <t>POWER PACKS</t>
+  </si>
+  <si>
+    <t>POWER PACKS - PÓS REPASSE - 16/11</t>
   </si>
 </sst>
 </file>
@@ -891,10 +894,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>7</v>
@@ -1086,10 +1089,10 @@
         <v>104</v>
       </c>
       <c r="B10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>107</v>
@@ -1108,10 +1111,10 @@
         <v>104</v>
       </c>
       <c r="B11" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C11" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>106</v>
@@ -2015,10 +2018,10 @@
         <v>61</v>
       </c>
       <c r="B53" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C53" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D53" t="s">
         <v>142</v>
@@ -2037,10 +2040,10 @@
         <v>61</v>
       </c>
       <c r="B54" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C54" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D54" t="s">
         <v>143</v>
@@ -2059,10 +2062,10 @@
         <v>62</v>
       </c>
       <c r="B55" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C55" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D55" t="s">
         <v>144</v>
@@ -2108,10 +2111,10 @@
         <v>90969</v>
       </c>
       <c r="D57" t="s">
+        <v>156</v>
+      </c>
+      <c r="E57" t="s">
         <v>157</v>
-      </c>
-      <c r="E57" t="s">
-        <v>158</v>
       </c>
       <c r="F57" t="str">
         <f t="shared" ref="F57" si="7">E57&amp;".png"</f>
@@ -2135,7 +2138,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:C578"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3639,7 +3641,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="137" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>62</v>
       </c>
@@ -3650,7 +3652,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="138" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>62</v>
       </c>
@@ -3661,7 +3663,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="139" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>62</v>
       </c>
@@ -3672,7 +3674,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="140" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>62</v>
       </c>
@@ -3683,7 +3685,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="141" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>62</v>
       </c>
@@ -3694,7 +3696,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="142" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>62</v>
       </c>
@@ -3705,7 +3707,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="143" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>62</v>
       </c>
@@ -3716,7 +3718,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="144" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>62</v>
       </c>
@@ -3727,7 +3729,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="145" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>62</v>
       </c>
@@ -3738,7 +3740,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="146" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>62</v>
       </c>
@@ -3749,7 +3751,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="147" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>62</v>
       </c>
@@ -3760,7 +3762,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="148" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>62</v>
       </c>
@@ -3771,7 +3773,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="149" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>62</v>
       </c>
@@ -3782,7 +3784,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="150" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>62</v>
       </c>
@@ -3793,7 +3795,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="151" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>62</v>
       </c>
@@ -3804,7 +3806,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="152" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>62</v>
       </c>
@@ -3815,7 +3817,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="153" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>62</v>
       </c>
@@ -3826,7 +3828,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="154" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>62</v>
       </c>
@@ -3837,7 +3839,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="155" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>62</v>
       </c>
@@ -3848,7 +3850,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="156" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>62</v>
       </c>
@@ -3859,7 +3861,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="157" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>62</v>
       </c>
@@ -3870,7 +3872,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="158" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>62</v>
       </c>
@@ -3881,7 +3883,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="159" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>62</v>
       </c>
@@ -3892,7 +3894,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="160" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>62</v>
       </c>
@@ -3903,7 +3905,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="161" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>62</v>
       </c>
@@ -3914,7 +3916,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="162" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>62</v>
       </c>
@@ -3925,7 +3927,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="163" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>62</v>
       </c>
@@ -3936,7 +3938,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="164" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>62</v>
       </c>
@@ -3947,7 +3949,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="165" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>62</v>
       </c>
@@ -3958,7 +3960,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="166" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>62</v>
       </c>
@@ -3969,7 +3971,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="167" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>62</v>
       </c>
@@ -3980,7 +3982,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="168" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>62</v>
       </c>
@@ -3991,7 +3993,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="169" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>62</v>
       </c>
@@ -4002,7 +4004,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="170" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>62</v>
       </c>
@@ -4013,7 +4015,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="171" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>62</v>
       </c>
@@ -4024,7 +4026,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="172" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>62</v>
       </c>
@@ -4035,7 +4037,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="173" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>62</v>
       </c>
@@ -4046,7 +4048,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="174" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>62</v>
       </c>
@@ -4057,7 +4059,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="175" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>62</v>
       </c>
@@ -4068,7 +4070,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="176" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>62</v>
       </c>
@@ -4079,7 +4081,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="177" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>62</v>
       </c>
@@ -4090,7 +4092,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="178" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>62</v>
       </c>
@@ -4101,7 +4103,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="179" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>62</v>
       </c>
@@ -4112,7 +4114,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="180" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>62</v>
       </c>
@@ -4123,7 +4125,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="181" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>62</v>
       </c>
@@ -4134,7 +4136,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="182" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>62</v>
       </c>
@@ -4145,7 +4147,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="183" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>62</v>
       </c>
@@ -4156,7 +4158,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="184" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>62</v>
       </c>
@@ -4167,7 +4169,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="185" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>62</v>
       </c>
@@ -4178,7 +4180,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="186" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>62</v>
       </c>
@@ -4189,7 +4191,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="187" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>62</v>
       </c>
@@ -4200,7 +4202,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="188" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>62</v>
       </c>
@@ -4211,7 +4213,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="189" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>62</v>
       </c>
@@ -4222,7 +4224,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="190" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>62</v>
       </c>
@@ -4233,7 +4235,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="191" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>62</v>
       </c>
@@ -4244,7 +4246,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="192" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>62</v>
       </c>
@@ -4255,7 +4257,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="193" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>62</v>
       </c>
@@ -4266,7 +4268,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="194" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>62</v>
       </c>
@@ -4277,7 +4279,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="195" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>62</v>
       </c>
@@ -4288,7 +4290,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="196" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>62</v>
       </c>
@@ -4299,7 +4301,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="197" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>62</v>
       </c>
@@ -4310,7 +4312,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="198" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>62</v>
       </c>
@@ -4321,7 +4323,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="199" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>62</v>
       </c>
@@ -4332,7 +4334,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="200" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>62</v>
       </c>
@@ -4343,7 +4345,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="201" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>62</v>
       </c>
@@ -4354,7 +4356,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="202" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>62</v>
       </c>
@@ -4365,7 +4367,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="203" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>62</v>
       </c>
@@ -4376,7 +4378,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="204" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>62</v>
       </c>
@@ -4387,7 +4389,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="205" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>62</v>
       </c>
@@ -4398,7 +4400,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="206" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>62</v>
       </c>
@@ -4409,7 +4411,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="207" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>62</v>
       </c>
@@ -4420,7 +4422,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="208" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>62</v>
       </c>
@@ -4431,7 +4433,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="209" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>62</v>
       </c>
@@ -4442,7 +4444,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="210" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>62</v>
       </c>
@@ -4453,7 +4455,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="211" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>62</v>
       </c>
@@ -4464,7 +4466,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="212" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>62</v>
       </c>
@@ -4475,7 +4477,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="213" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>62</v>
       </c>
@@ -4486,7 +4488,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="214" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>62</v>
       </c>
@@ -4497,7 +4499,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="215" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>62</v>
       </c>
@@ -4508,7 +4510,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="216" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>62</v>
       </c>
@@ -4519,7 +4521,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="217" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>62</v>
       </c>
@@ -4530,7 +4532,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="218" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>62</v>
       </c>
@@ -4541,7 +4543,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="219" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>62</v>
       </c>
@@ -4552,7 +4554,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="220" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>62</v>
       </c>
@@ -4563,7 +4565,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="221" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>62</v>
       </c>
@@ -4574,7 +4576,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="222" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>62</v>
       </c>
@@ -4585,7 +4587,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="223" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>62</v>
       </c>
@@ -4596,7 +4598,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="224" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>62</v>
       </c>
@@ -4607,7 +4609,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="225" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>62</v>
       </c>
@@ -4618,7 +4620,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="226" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>62</v>
       </c>
@@ -4629,7 +4631,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="227" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>62</v>
       </c>
@@ -4640,7 +4642,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="228" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>62</v>
       </c>
@@ -4651,7 +4653,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="229" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>62</v>
       </c>
@@ -4662,7 +4664,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="230" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>62</v>
       </c>
@@ -4673,7 +4675,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="231" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>62</v>
       </c>
@@ -4684,7 +4686,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="232" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>62</v>
       </c>
@@ -4695,7 +4697,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="233" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>62</v>
       </c>
@@ -4706,7 +4708,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="234" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>62</v>
       </c>
@@ -4717,7 +4719,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="235" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>62</v>
       </c>
@@ -4728,7 +4730,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="236" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>62</v>
       </c>
@@ -4739,7 +4741,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="237" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>62</v>
       </c>
@@ -4750,7 +4752,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="238" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>62</v>
       </c>
@@ -4761,7 +4763,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="239" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>62</v>
       </c>
@@ -4772,7 +4774,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="240" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>62</v>
       </c>
@@ -4783,7 +4785,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="241" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>62</v>
       </c>
@@ -4794,7 +4796,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="242" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>62</v>
       </c>
@@ -4805,7 +4807,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="243" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>62</v>
       </c>
@@ -4816,7 +4818,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="244" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>62</v>
       </c>
@@ -4827,7 +4829,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="245" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>62</v>
       </c>
@@ -4838,7 +4840,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="246" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>62</v>
       </c>
@@ -4849,7 +4851,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="247" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>62</v>
       </c>
@@ -4860,7 +4862,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="248" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>62</v>
       </c>
@@ -4871,7 +4873,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="249" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>62</v>
       </c>
@@ -4882,7 +4884,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="250" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>62</v>
       </c>
@@ -4893,7 +4895,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="251" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>62</v>
       </c>
@@ -4904,7 +4906,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="252" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>62</v>
       </c>
@@ -4915,7 +4917,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="253" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>62</v>
       </c>
@@ -4926,7 +4928,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="254" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>62</v>
       </c>
@@ -4937,7 +4939,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="255" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>62</v>
       </c>
@@ -4948,7 +4950,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="256" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>62</v>
       </c>
@@ -4959,7 +4961,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="257" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>62</v>
       </c>
@@ -4970,7 +4972,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="258" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>62</v>
       </c>
@@ -4981,7 +4983,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="259" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>62</v>
       </c>
@@ -4992,7 +4994,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="260" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>62</v>
       </c>
@@ -5003,7 +5005,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="261" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>62</v>
       </c>
@@ -5014,7 +5016,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="262" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>62</v>
       </c>
@@ -5025,7 +5027,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="263" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>62</v>
       </c>
@@ -5036,7 +5038,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="264" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>62</v>
       </c>
@@ -5047,7 +5049,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="265" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>62</v>
       </c>
@@ -5058,7 +5060,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="266" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>62</v>
       </c>
@@ -5069,7 +5071,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="267" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>62</v>
       </c>
@@ -5080,7 +5082,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="268" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>62</v>
       </c>
@@ -5091,7 +5093,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="269" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>62</v>
       </c>
@@ -5102,7 +5104,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="270" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>62</v>
       </c>
@@ -5113,7 +5115,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="271" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>62</v>
       </c>
@@ -5124,7 +5126,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="272" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>62</v>
       </c>
@@ -5135,7 +5137,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="273" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>62</v>
       </c>
@@ -5146,7 +5148,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="274" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>62</v>
       </c>
@@ -5157,7 +5159,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="275" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>62</v>
       </c>
@@ -5168,59 +5170,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="276" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="277" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="278" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="279" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="280" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="281" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="282" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="283" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="284" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="285" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="286" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="287" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="288" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="289" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="290" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="291" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="292" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="293" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="294" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="295" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="296" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="297" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="298" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="299" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="300" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="301" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="302" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="303" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="304" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="305" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="306" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="307" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="308" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="309" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="310" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="311" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="312" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="313" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="314" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="315" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="316" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="317" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="318" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="319" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="320" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="321" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="322" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="323" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="324" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="325" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="326" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="327" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="328" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>104</v>
       </c>
@@ -5231,7 +5181,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="329" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>104</v>
       </c>
@@ -5242,7 +5192,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="330" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>104</v>
       </c>
@@ -5253,7 +5203,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="331" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>104</v>
       </c>
@@ -5264,7 +5214,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="332" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>104</v>
       </c>
@@ -5275,7 +5225,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="333" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>104</v>
       </c>
@@ -5286,7 +5236,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="334" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>104</v>
       </c>
@@ -5297,7 +5247,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="335" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>104</v>
       </c>
@@ -5308,7 +5258,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="336" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>104</v>
       </c>
@@ -5319,7 +5269,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="337" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>104</v>
       </c>
@@ -5330,7 +5280,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="338" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>104</v>
       </c>
@@ -5341,7 +5291,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="339" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>104</v>
       </c>
@@ -5352,7 +5302,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="340" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>104</v>
       </c>
@@ -5363,7 +5313,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="341" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>104</v>
       </c>
@@ -5374,7 +5324,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="342" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>104</v>
       </c>
@@ -5385,7 +5335,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="343" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>104</v>
       </c>
@@ -5396,7 +5346,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="344" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>104</v>
       </c>
@@ -5407,7 +5357,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="345" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>104</v>
       </c>
@@ -5418,7 +5368,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="346" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>104</v>
       </c>
@@ -5429,7 +5379,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="347" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>104</v>
       </c>
@@ -5440,7 +5390,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="348" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>104</v>
       </c>
@@ -5451,7 +5401,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="349" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>104</v>
       </c>
@@ -5462,7 +5412,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="350" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>104</v>
       </c>
@@ -5473,7 +5423,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="351" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>104</v>
       </c>
@@ -5484,7 +5434,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="352" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>104</v>
       </c>
@@ -5495,7 +5445,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="353" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>104</v>
       </c>
@@ -5506,7 +5456,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="354" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>104</v>
       </c>
@@ -5517,7 +5467,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="355" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>104</v>
       </c>
@@ -5528,7 +5478,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="356" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>104</v>
       </c>
@@ -5539,7 +5489,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="357" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>104</v>
       </c>
@@ -5550,7 +5500,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="358" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>104</v>
       </c>
@@ -5561,7 +5511,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="359" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>104</v>
       </c>
@@ -5572,7 +5522,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="360" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>104</v>
       </c>
@@ -5583,7 +5533,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="361" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>104</v>
       </c>
@@ -5594,7 +5544,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="362" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>104</v>
       </c>
@@ -5605,7 +5555,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="363" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>104</v>
       </c>
@@ -5616,7 +5566,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="364" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>104</v>
       </c>
@@ -5627,7 +5577,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="365" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>104</v>
       </c>
@@ -5638,7 +5588,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="366" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>104</v>
       </c>
@@ -5649,7 +5599,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="367" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>104</v>
       </c>
@@ -5660,7 +5610,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="368" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>104</v>
       </c>
@@ -5671,7 +5621,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="369" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>104</v>
       </c>
@@ -5682,7 +5632,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="370" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>104</v>
       </c>
@@ -5693,7 +5643,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="371" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>104</v>
       </c>
@@ -5704,7 +5654,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="372" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>104</v>
       </c>
@@ -5715,7 +5665,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="373" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>104</v>
       </c>
@@ -5726,7 +5676,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="374" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>104</v>
       </c>
@@ -5737,7 +5687,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="375" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>104</v>
       </c>
@@ -5748,7 +5698,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="376" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>104</v>
       </c>
@@ -5759,7 +5709,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="377" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>104</v>
       </c>
@@ -5770,7 +5720,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="378" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>104</v>
       </c>
@@ -5781,7 +5731,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="379" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>104</v>
       </c>
@@ -5792,7 +5742,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="380" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>104</v>
       </c>
@@ -5803,7 +5753,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="381" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>104</v>
       </c>
@@ -5814,7 +5764,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="382" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>104</v>
       </c>
@@ -5825,7 +5775,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="383" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>104</v>
       </c>
@@ -5836,7 +5786,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="384" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>104</v>
       </c>
@@ -5847,7 +5797,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="385" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>104</v>
       </c>
@@ -5858,7 +5808,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="386" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>104</v>
       </c>
@@ -5869,7 +5819,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="387" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>104</v>
       </c>
@@ -5880,7 +5830,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="388" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>104</v>
       </c>
@@ -5891,7 +5841,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="389" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>104</v>
       </c>
@@ -5902,7 +5852,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="390" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>104</v>
       </c>
@@ -5913,7 +5863,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="391" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>104</v>
       </c>
@@ -5924,7 +5874,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="392" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>104</v>
       </c>
@@ -5935,7 +5885,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="393" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>104</v>
       </c>
@@ -5946,7 +5896,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="394" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>104</v>
       </c>
@@ -5957,7 +5907,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="395" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>104</v>
       </c>
@@ -5968,7 +5918,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="396" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>104</v>
       </c>
@@ -5979,7 +5929,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="397" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>104</v>
       </c>
@@ -5990,7 +5940,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="398" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>104</v>
       </c>
@@ -6001,7 +5951,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="399" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>104</v>
       </c>
@@ -6012,7 +5962,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="400" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>104</v>
       </c>
@@ -6023,7 +5973,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="401" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>104</v>
       </c>
@@ -6034,7 +5984,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="402" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>104</v>
       </c>
@@ -6045,7 +5995,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="403" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>104</v>
       </c>
@@ -6056,7 +6006,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="404" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>104</v>
       </c>
@@ -6067,7 +6017,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="405" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>104</v>
       </c>
@@ -6078,7 +6028,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="406" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>104</v>
       </c>
@@ -6089,7 +6039,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="407" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>104</v>
       </c>
@@ -6100,7 +6050,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="408" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>104</v>
       </c>
@@ -6111,7 +6061,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="409" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>104</v>
       </c>
@@ -6122,7 +6072,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="410" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>104</v>
       </c>
@@ -6133,7 +6083,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="411" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>104</v>
       </c>
@@ -6144,7 +6094,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="412" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>104</v>
       </c>
@@ -6155,7 +6105,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="413" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>104</v>
       </c>
@@ -6166,7 +6116,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="414" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>104</v>
       </c>
@@ -6177,7 +6127,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="415" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>104</v>
       </c>
@@ -6188,7 +6138,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="416" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>104</v>
       </c>
@@ -6199,7 +6149,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="417" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>104</v>
       </c>
@@ -6210,7 +6160,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="418" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>104</v>
       </c>
@@ -6221,7 +6171,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="419" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>104</v>
       </c>
@@ -6232,7 +6182,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="420" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>104</v>
       </c>
@@ -6243,7 +6193,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="421" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>104</v>
       </c>
@@ -6254,7 +6204,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="422" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>104</v>
       </c>
@@ -6265,7 +6215,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="423" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>104</v>
       </c>
@@ -6276,7 +6226,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="424" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>104</v>
       </c>
@@ -6287,7 +6237,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="425" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>104</v>
       </c>
@@ -6298,7 +6248,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="426" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>104</v>
       </c>
@@ -6309,7 +6259,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="427" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>104</v>
       </c>
@@ -6320,7 +6270,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="428" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>104</v>
       </c>
@@ -6331,7 +6281,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="429" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>104</v>
       </c>
@@ -6342,7 +6292,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="430" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>104</v>
       </c>
@@ -6353,7 +6303,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="431" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>104</v>
       </c>
@@ -6364,7 +6314,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="432" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>104</v>
       </c>
@@ -6375,7 +6325,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="433" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>104</v>
       </c>
@@ -6386,7 +6336,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="434" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>104</v>
       </c>
@@ -6397,7 +6347,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="435" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>104</v>
       </c>
@@ -6408,7 +6358,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="436" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>104</v>
       </c>
@@ -6419,7 +6369,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="437" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>104</v>
       </c>
@@ -6430,7 +6380,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="438" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>104</v>
       </c>
@@ -6441,7 +6391,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="439" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>104</v>
       </c>
@@ -6452,7 +6402,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="440" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>104</v>
       </c>
@@ -6463,7 +6413,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="441" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>104</v>
       </c>
@@ -6474,7 +6424,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="442" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>104</v>
       </c>
@@ -6485,7 +6435,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="443" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>104</v>
       </c>
@@ -6496,7 +6446,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="444" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>104</v>
       </c>
@@ -6507,7 +6457,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="445" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>104</v>
       </c>
@@ -6518,7 +6468,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="446" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>104</v>
       </c>
@@ -6529,7 +6479,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="447" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>104</v>
       </c>
@@ -6540,7 +6490,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="448" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>104</v>
       </c>
@@ -6551,7 +6501,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="449" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>104</v>
       </c>
@@ -6562,7 +6512,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="450" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>104</v>
       </c>
@@ -6573,7 +6523,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="451" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>104</v>
       </c>
@@ -6584,7 +6534,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="452" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>104</v>
       </c>
@@ -6595,7 +6545,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="453" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>104</v>
       </c>
@@ -6606,7 +6556,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="454" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>104</v>
       </c>
@@ -6617,7 +6567,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="455" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>104</v>
       </c>
@@ -6628,7 +6578,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="456" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>104</v>
       </c>
@@ -6639,7 +6589,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="457" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>104</v>
       </c>
@@ -6650,7 +6600,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="458" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>104</v>
       </c>
@@ -6661,7 +6611,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="459" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>104</v>
       </c>
@@ -6672,7 +6622,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="460" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>104</v>
       </c>
@@ -6683,7 +6633,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="461" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>104</v>
       </c>
@@ -6694,7 +6644,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="462" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>104</v>
       </c>
@@ -6705,7 +6655,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="463" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>104</v>
       </c>
@@ -6716,7 +6666,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="464" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>104</v>
       </c>
@@ -6727,7 +6677,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="465" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>104</v>
       </c>
@@ -6738,7 +6688,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="466" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>104</v>
       </c>
@@ -6749,7 +6699,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="467" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>127</v>
       </c>
@@ -6760,7 +6710,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="468" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>127</v>
       </c>
@@ -6771,7 +6721,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="469" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>127</v>
       </c>
@@ -6782,7 +6732,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="470" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>127</v>
       </c>
@@ -6793,7 +6743,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="471" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>127</v>
       </c>
@@ -6804,7 +6754,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="472" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>127</v>
       </c>
@@ -6815,7 +6765,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="473" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>127</v>
       </c>
@@ -6826,7 +6776,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="474" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>127</v>
       </c>
@@ -6837,7 +6787,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="475" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>127</v>
       </c>
@@ -6848,7 +6798,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="476" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>127</v>
       </c>
@@ -6859,7 +6809,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="477" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>127</v>
       </c>
@@ -6870,7 +6820,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="478" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>127</v>
       </c>
@@ -6881,7 +6831,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="479" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>127</v>
       </c>
@@ -6892,7 +6842,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="480" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>127</v>
       </c>
@@ -6903,7 +6853,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="481" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>127</v>
       </c>
@@ -6914,7 +6864,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="482" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>127</v>
       </c>
@@ -6925,7 +6875,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="483" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>127</v>
       </c>
@@ -6936,7 +6886,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="484" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>127</v>
       </c>
@@ -6947,7 +6897,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="485" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>127</v>
       </c>
@@ -6958,7 +6908,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="486" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>127</v>
       </c>
@@ -6969,7 +6919,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="487" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>127</v>
       </c>
@@ -6980,7 +6930,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="488" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>127</v>
       </c>
@@ -6991,7 +6941,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="489" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>127</v>
       </c>
@@ -7002,7 +6952,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="490" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>127</v>
       </c>
@@ -7013,7 +6963,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="491" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>127</v>
       </c>
@@ -7024,7 +6974,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="492" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>127</v>
       </c>
@@ -7035,7 +6985,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="493" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>127</v>
       </c>
@@ -7046,7 +6996,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="494" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>127</v>
       </c>
@@ -7057,7 +7007,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="495" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>127</v>
       </c>
@@ -7068,7 +7018,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="496" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>127</v>
       </c>
@@ -7079,7 +7029,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="497" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>127</v>
       </c>
@@ -7090,7 +7040,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="498" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>62</v>
       </c>
@@ -7101,7 +7051,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="499" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>62</v>
       </c>
@@ -7113,7 +7063,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="500" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>62</v>
       </c>
@@ -7125,7 +7075,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="501" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>62</v>
       </c>
@@ -7137,7 +7087,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="502" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>62</v>
       </c>
@@ -7149,7 +7099,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="503" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>62</v>
       </c>
@@ -7161,7 +7111,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="504" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>62</v>
       </c>
@@ -7173,7 +7123,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="505" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>62</v>
       </c>
@@ -7185,7 +7135,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="506" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>62</v>
       </c>
@@ -7197,7 +7147,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="507" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>62</v>
       </c>
@@ -7209,7 +7159,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="508" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>62</v>
       </c>
@@ -7221,7 +7171,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="509" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>62</v>
       </c>
@@ -7233,7 +7183,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="510" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>62</v>
       </c>
@@ -7245,7 +7195,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="511" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>62</v>
       </c>
@@ -7257,7 +7207,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="512" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>62</v>
       </c>
@@ -7269,7 +7219,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="513" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>62</v>
       </c>
@@ -7281,7 +7231,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="514" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>62</v>
       </c>
@@ -7293,7 +7243,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="515" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>62</v>
       </c>
@@ -7305,7 +7255,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="516" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>62</v>
       </c>
@@ -7317,7 +7267,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="517" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>62</v>
       </c>
@@ -7329,7 +7279,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="518" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>62</v>
       </c>
@@ -7341,7 +7291,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="519" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>62</v>
       </c>
@@ -7353,7 +7303,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="520" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>62</v>
       </c>
@@ -7365,7 +7315,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="521" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>62</v>
       </c>
@@ -7377,7 +7327,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="522" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>62</v>
       </c>
@@ -7389,7 +7339,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="523" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>62</v>
       </c>
@@ -7401,7 +7351,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="524" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>62</v>
       </c>
@@ -7413,7 +7363,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="525" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>62</v>
       </c>
@@ -7425,7 +7375,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="526" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>62</v>
       </c>
@@ -8034,13 +7984,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C526" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="NAB"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:C526" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -8784,7 +8728,7 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>61</v>
@@ -8798,7 +8742,7 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>61</v>
@@ -8812,7 +8756,7 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>61</v>
@@ -8826,7 +8770,7 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>61</v>
@@ -8840,7 +8784,7 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>61</v>
@@ -8854,7 +8798,7 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>61</v>
@@ -8868,7 +8812,7 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>61</v>
@@ -8882,7 +8826,7 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>104</v>
@@ -8896,7 +8840,7 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>104</v>
@@ -8910,7 +8854,7 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>104</v>
@@ -8924,7 +8868,7 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>104</v>
@@ -8950,7 +8894,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34B2C8DF-4561-40B2-8E7C-6CD69559B9AE}">
-  <dimension ref="A1:I1535"/>
+  <dimension ref="A1:I1591"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="20.85546875" customWidth="1"/>
@@ -49080,7 +49024,7 @@
         <v>25</v>
       </c>
       <c r="E1338" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1338" t="s">
         <v>66</v>
@@ -49110,7 +49054,7 @@
         <v>25</v>
       </c>
       <c r="E1339" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1339" t="s">
         <v>151</v>
@@ -49140,7 +49084,7 @@
         <v>25</v>
       </c>
       <c r="E1340" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1340" t="s">
         <v>100</v>
@@ -49170,7 +49114,7 @@
         <v>25</v>
       </c>
       <c r="E1341" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1341" t="s">
         <v>75</v>
@@ -49200,7 +49144,7 @@
         <v>25</v>
       </c>
       <c r="E1342" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1342" t="s">
         <v>77</v>
@@ -49230,7 +49174,7 @@
         <v>25</v>
       </c>
       <c r="E1343" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1343" t="s">
         <v>71</v>
@@ -49260,7 +49204,7 @@
         <v>25</v>
       </c>
       <c r="E1344" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1344" t="s">
         <v>139</v>
@@ -49290,7 +49234,7 @@
         <v>25</v>
       </c>
       <c r="E1345" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1345" t="s">
         <v>66</v>
@@ -49320,7 +49264,7 @@
         <v>25</v>
       </c>
       <c r="E1346" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1346" t="s">
         <v>69</v>
@@ -49350,7 +49294,7 @@
         <v>25</v>
       </c>
       <c r="E1347" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1347" t="s">
         <v>151</v>
@@ -49380,7 +49324,7 @@
         <v>25</v>
       </c>
       <c r="E1348" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1348" t="s">
         <v>100</v>
@@ -49410,7 +49354,7 @@
         <v>25</v>
       </c>
       <c r="E1349" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1349" t="s">
         <v>75</v>
@@ -49440,7 +49384,7 @@
         <v>25</v>
       </c>
       <c r="E1350" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1350" t="s">
         <v>77</v>
@@ -49470,7 +49414,7 @@
         <v>25</v>
       </c>
       <c r="E1351" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1351" t="s">
         <v>71</v>
@@ -49500,7 +49444,7 @@
         <v>25</v>
       </c>
       <c r="E1352" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1352" t="s">
         <v>139</v>
@@ -49530,7 +49474,7 @@
         <v>25</v>
       </c>
       <c r="E1353" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1353" t="s">
         <v>66</v>
@@ -49560,7 +49504,7 @@
         <v>25</v>
       </c>
       <c r="E1354" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1354" t="s">
         <v>151</v>
@@ -49590,7 +49534,7 @@
         <v>25</v>
       </c>
       <c r="E1355" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1355" t="s">
         <v>100</v>
@@ -49620,7 +49564,7 @@
         <v>25</v>
       </c>
       <c r="E1356" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1356" t="s">
         <v>75</v>
@@ -49650,7 +49594,7 @@
         <v>25</v>
       </c>
       <c r="E1357" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1357" t="s">
         <v>77</v>
@@ -49680,7 +49624,7 @@
         <v>25</v>
       </c>
       <c r="E1358" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1358" t="s">
         <v>71</v>
@@ -49710,7 +49654,7 @@
         <v>26</v>
       </c>
       <c r="E1359" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1359" t="s">
         <v>76</v>
@@ -49740,7 +49684,7 @@
         <v>25</v>
       </c>
       <c r="E1360" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1360" t="s">
         <v>139</v>
@@ -49770,7 +49714,7 @@
         <v>25</v>
       </c>
       <c r="E1361" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1361" t="s">
         <v>66</v>
@@ -49800,7 +49744,7 @@
         <v>25</v>
       </c>
       <c r="E1362" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1362" t="s">
         <v>151</v>
@@ -49830,7 +49774,7 @@
         <v>25</v>
       </c>
       <c r="E1363" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1363" t="s">
         <v>100</v>
@@ -49860,7 +49804,7 @@
         <v>25</v>
       </c>
       <c r="E1364" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1364" t="s">
         <v>75</v>
@@ -49890,7 +49834,7 @@
         <v>25</v>
       </c>
       <c r="E1365" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1365" t="s">
         <v>77</v>
@@ -49920,7 +49864,7 @@
         <v>25</v>
       </c>
       <c r="E1366" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1366" t="s">
         <v>71</v>
@@ -49950,7 +49894,7 @@
         <v>26</v>
       </c>
       <c r="E1367" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1367" t="s">
         <v>101</v>
@@ -49980,7 +49924,7 @@
         <v>26</v>
       </c>
       <c r="E1368" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1368" t="s">
         <v>65</v>
@@ -50010,7 +49954,7 @@
         <v>25</v>
       </c>
       <c r="E1369" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1369" t="s">
         <v>139</v>
@@ -50040,7 +49984,7 @@
         <v>25</v>
       </c>
       <c r="E1370" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1370" t="s">
         <v>66</v>
@@ -50070,7 +50014,7 @@
         <v>25</v>
       </c>
       <c r="E1371" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1371" t="s">
         <v>69</v>
@@ -50100,7 +50044,7 @@
         <v>25</v>
       </c>
       <c r="E1372" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1372" t="s">
         <v>151</v>
@@ -50130,7 +50074,7 @@
         <v>25</v>
       </c>
       <c r="E1373" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1373" t="s">
         <v>100</v>
@@ -50160,7 +50104,7 @@
         <v>25</v>
       </c>
       <c r="E1374" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1374" t="s">
         <v>75</v>
@@ -50190,7 +50134,7 @@
         <v>25</v>
       </c>
       <c r="E1375" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1375" t="s">
         <v>77</v>
@@ -50220,7 +50164,7 @@
         <v>25</v>
       </c>
       <c r="E1376" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1376" t="s">
         <v>71</v>
@@ -50250,7 +50194,7 @@
         <v>25</v>
       </c>
       <c r="E1377" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1377" t="s">
         <v>139</v>
@@ -50280,7 +50224,7 @@
         <v>25</v>
       </c>
       <c r="E1378" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1378" t="s">
         <v>66</v>
@@ -50310,7 +50254,7 @@
         <v>25</v>
       </c>
       <c r="E1379" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1379" t="s">
         <v>69</v>
@@ -50340,7 +50284,7 @@
         <v>25</v>
       </c>
       <c r="E1380" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1380" t="s">
         <v>151</v>
@@ -50370,7 +50314,7 @@
         <v>25</v>
       </c>
       <c r="E1381" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1381" t="s">
         <v>100</v>
@@ -50400,7 +50344,7 @@
         <v>25</v>
       </c>
       <c r="E1382" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1382" t="s">
         <v>75</v>
@@ -50430,7 +50374,7 @@
         <v>25</v>
       </c>
       <c r="E1383" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1383" t="s">
         <v>77</v>
@@ -50460,7 +50404,7 @@
         <v>25</v>
       </c>
       <c r="E1384" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1384" t="s">
         <v>71</v>
@@ -50490,7 +50434,7 @@
         <v>25</v>
       </c>
       <c r="E1385" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1385" t="s">
         <v>139</v>
@@ -50520,7 +50464,7 @@
         <v>25</v>
       </c>
       <c r="E1386" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1386" t="s">
         <v>66</v>
@@ -50550,7 +50494,7 @@
         <v>25</v>
       </c>
       <c r="E1387" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1387" t="s">
         <v>69</v>
@@ -50580,7 +50524,7 @@
         <v>25</v>
       </c>
       <c r="E1388" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1388" t="s">
         <v>151</v>
@@ -50610,7 +50554,7 @@
         <v>25</v>
       </c>
       <c r="E1389" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1389" t="s">
         <v>100</v>
@@ -50640,7 +50584,7 @@
         <v>25</v>
       </c>
       <c r="E1390" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1390" t="s">
         <v>75</v>
@@ -50670,7 +50614,7 @@
         <v>25</v>
       </c>
       <c r="E1391" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1391" t="s">
         <v>77</v>
@@ -50700,7 +50644,7 @@
         <v>25</v>
       </c>
       <c r="E1392" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1392" t="s">
         <v>71</v>
@@ -50730,7 +50674,7 @@
         <v>25</v>
       </c>
       <c r="E1393" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1393" t="s">
         <v>139</v>
@@ -50748,7 +50692,7 @@
     </row>
     <row r="1394" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1394" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1394" t="s">
         <v>61</v>
@@ -50778,7 +50722,7 @@
     </row>
     <row r="1395" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1395" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1395" t="s">
         <v>61</v>
@@ -50808,7 +50752,7 @@
     </row>
     <row r="1396" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1396" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1396" t="s">
         <v>61</v>
@@ -50838,7 +50782,7 @@
     </row>
     <row r="1397" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1397" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1397" t="s">
         <v>61</v>
@@ -50868,7 +50812,7 @@
     </row>
     <row r="1398" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1398" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1398" t="s">
         <v>61</v>
@@ -50898,7 +50842,7 @@
     </row>
     <row r="1399" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1399" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1399" t="s">
         <v>61</v>
@@ -50928,7 +50872,7 @@
     </row>
     <row r="1400" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1400" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1400" t="s">
         <v>61</v>
@@ -50958,7 +50902,7 @@
     </row>
     <row r="1401" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1401" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1401" t="s">
         <v>61</v>
@@ -50988,7 +50932,7 @@
     </row>
     <row r="1402" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1402" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1402" t="s">
         <v>61</v>
@@ -51018,7 +50962,7 @@
     </row>
     <row r="1403" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1403" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1403" t="s">
         <v>61</v>
@@ -51048,7 +50992,7 @@
     </row>
     <row r="1404" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1404" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1404" t="s">
         <v>61</v>
@@ -51078,7 +51022,7 @@
     </row>
     <row r="1405" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1405" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1405" t="s">
         <v>61</v>
@@ -51108,7 +51052,7 @@
     </row>
     <row r="1406" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1406" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1406" t="s">
         <v>61</v>
@@ -51138,7 +51082,7 @@
     </row>
     <row r="1407" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1407" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1407" t="s">
         <v>61</v>
@@ -51168,7 +51112,7 @@
     </row>
     <row r="1408" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1408" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1408" t="s">
         <v>61</v>
@@ -51198,7 +51142,7 @@
     </row>
     <row r="1409" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1409" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1409" t="s">
         <v>61</v>
@@ -51228,7 +51172,7 @@
     </row>
     <row r="1410" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1410" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1410" t="s">
         <v>61</v>
@@ -51258,7 +51202,7 @@
     </row>
     <row r="1411" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1411" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1411" t="s">
         <v>61</v>
@@ -51288,7 +51232,7 @@
     </row>
     <row r="1412" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1412" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1412" t="s">
         <v>61</v>
@@ -51318,7 +51262,7 @@
     </row>
     <row r="1413" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1413" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1413" t="s">
         <v>61</v>
@@ -51348,7 +51292,7 @@
     </row>
     <row r="1414" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1414" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1414" t="s">
         <v>61</v>
@@ -51378,7 +51322,7 @@
     </row>
     <row r="1415" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1415" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1415" t="s">
         <v>61</v>
@@ -51408,7 +51352,7 @@
     </row>
     <row r="1416" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1416" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1416" t="s">
         <v>61</v>
@@ -51438,7 +51382,7 @@
     </row>
     <row r="1417" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1417" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1417" t="s">
         <v>61</v>
@@ -51468,7 +51412,7 @@
     </row>
     <row r="1418" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1418" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1418" t="s">
         <v>61</v>
@@ -51498,7 +51442,7 @@
     </row>
     <row r="1419" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1419" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1419" t="s">
         <v>61</v>
@@ -51528,7 +51472,7 @@
     </row>
     <row r="1420" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1420" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1420" t="s">
         <v>61</v>
@@ -51558,7 +51502,7 @@
     </row>
     <row r="1421" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1421" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1421" t="s">
         <v>61</v>
@@ -51588,7 +51532,7 @@
     </row>
     <row r="1422" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1422" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1422" t="s">
         <v>61</v>
@@ -51618,7 +51562,7 @@
     </row>
     <row r="1423" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1423" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1423" t="s">
         <v>61</v>
@@ -51648,7 +51592,7 @@
     </row>
     <row r="1424" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1424" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1424" t="s">
         <v>61</v>
@@ -51678,7 +51622,7 @@
     </row>
     <row r="1425" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1425" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1425" t="s">
         <v>61</v>
@@ -51708,7 +51652,7 @@
     </row>
     <row r="1426" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1426" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1426" t="s">
         <v>61</v>
@@ -51738,7 +51682,7 @@
     </row>
     <row r="1427" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1427" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1427" t="s">
         <v>61</v>
@@ -51768,7 +51712,7 @@
     </row>
     <row r="1428" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1428" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1428" t="s">
         <v>61</v>
@@ -51798,7 +51742,7 @@
     </row>
     <row r="1429" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1429" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1429" t="s">
         <v>61</v>
@@ -51828,7 +51772,7 @@
     </row>
     <row r="1430" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1430" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1430" t="s">
         <v>61</v>
@@ -51858,7 +51802,7 @@
     </row>
     <row r="1431" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1431" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1431" t="s">
         <v>61</v>
@@ -51888,7 +51832,7 @@
     </row>
     <row r="1432" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1432" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1432" t="s">
         <v>61</v>
@@ -51918,7 +51862,7 @@
     </row>
     <row r="1433" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1433" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1433" t="s">
         <v>61</v>
@@ -51948,7 +51892,7 @@
     </row>
     <row r="1434" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1434" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1434" t="s">
         <v>61</v>
@@ -51963,7 +51907,7 @@
         <v>1</v>
       </c>
       <c r="F1434" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G1434">
         <v>3.39</v>
@@ -51978,7 +51922,7 @@
     </row>
     <row r="1435" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1435" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1435" t="s">
         <v>61</v>
@@ -52008,7 +51952,7 @@
     </row>
     <row r="1436" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1436" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1436" t="s">
         <v>61</v>
@@ -52038,7 +51982,7 @@
     </row>
     <row r="1437" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1437" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1437" t="s">
         <v>61</v>
@@ -52068,7 +52012,7 @@
     </row>
     <row r="1438" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1438" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1438" t="s">
         <v>61</v>
@@ -52098,7 +52042,7 @@
     </row>
     <row r="1439" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1439" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1439" t="s">
         <v>61</v>
@@ -52128,7 +52072,7 @@
     </row>
     <row r="1440" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1440" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1440" t="s">
         <v>61</v>
@@ -52158,7 +52102,7 @@
     </row>
     <row r="1441" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1441" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1441" t="s">
         <v>61</v>
@@ -52188,7 +52132,7 @@
     </row>
     <row r="1442" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1442" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1442" t="s">
         <v>61</v>
@@ -52218,7 +52162,7 @@
     </row>
     <row r="1443" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1443" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1443" t="s">
         <v>61</v>
@@ -52248,7 +52192,7 @@
     </row>
     <row r="1444" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1444" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1444" t="s">
         <v>61</v>
@@ -52278,7 +52222,7 @@
     </row>
     <row r="1445" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1445" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1445" t="s">
         <v>61</v>
@@ -52308,7 +52252,7 @@
     </row>
     <row r="1446" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1446" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1446" t="s">
         <v>61</v>
@@ -52338,7 +52282,7 @@
     </row>
     <row r="1447" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1447" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1447" t="s">
         <v>61</v>
@@ -52368,7 +52312,7 @@
     </row>
     <row r="1448" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1448" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1448" t="s">
         <v>61</v>
@@ -52398,7 +52342,7 @@
     </row>
     <row r="1449" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1449" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1449" t="s">
         <v>61</v>
@@ -52428,7 +52372,7 @@
     </row>
     <row r="1450" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1450" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1450" t="s">
         <v>61</v>
@@ -52458,7 +52402,7 @@
     </row>
     <row r="1451" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1451" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1451" t="s">
         <v>61</v>
@@ -52488,7 +52432,7 @@
     </row>
     <row r="1452" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1452" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1452" t="s">
         <v>61</v>
@@ -52518,7 +52462,7 @@
     </row>
     <row r="1453" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1453" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1453" t="s">
         <v>61</v>
@@ -52548,7 +52492,7 @@
     </row>
     <row r="1454" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1454" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1454" t="s">
         <v>61</v>
@@ -52578,7 +52522,7 @@
     </row>
     <row r="1455" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1455" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1455" t="s">
         <v>61</v>
@@ -52608,7 +52552,7 @@
     </row>
     <row r="1456" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1456" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1456" t="s">
         <v>61</v>
@@ -52638,7 +52582,7 @@
     </row>
     <row r="1457" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1457" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1457" t="s">
         <v>61</v>
@@ -52668,7 +52612,7 @@
     </row>
     <row r="1458" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1458" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1458" t="s">
         <v>61</v>
@@ -52698,7 +52642,7 @@
     </row>
     <row r="1459" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1459" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1459" t="s">
         <v>61</v>
@@ -52728,7 +52672,7 @@
     </row>
     <row r="1460" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1460" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1460" t="s">
         <v>61</v>
@@ -52758,7 +52702,7 @@
     </row>
     <row r="1461" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1461" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1461" t="s">
         <v>61</v>
@@ -52788,7 +52732,7 @@
     </row>
     <row r="1462" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1462" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1462" t="s">
         <v>61</v>
@@ -52818,7 +52762,7 @@
     </row>
     <row r="1463" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1463" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1463" t="s">
         <v>61</v>
@@ -52848,7 +52792,7 @@
     </row>
     <row r="1464" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1464" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1464" s="2" t="s">
         <v>62</v>
@@ -52860,7 +52804,7 @@
         <v>25</v>
       </c>
       <c r="E1464" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1464" t="s">
         <v>66</v>
@@ -52878,7 +52822,7 @@
     </row>
     <row r="1465" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1465" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1465" t="s">
         <v>62</v>
@@ -52890,7 +52834,7 @@
         <v>25</v>
       </c>
       <c r="E1465" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1465" t="s">
         <v>151</v>
@@ -52908,7 +52852,7 @@
     </row>
     <row r="1466" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1466" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1466" t="s">
         <v>62</v>
@@ -52920,7 +52864,7 @@
         <v>25</v>
       </c>
       <c r="E1466" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1466" t="s">
         <v>100</v>
@@ -52938,7 +52882,7 @@
     </row>
     <row r="1467" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1467" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1467" t="s">
         <v>62</v>
@@ -52950,7 +52894,7 @@
         <v>25</v>
       </c>
       <c r="E1467" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1467" t="s">
         <v>75</v>
@@ -52968,7 +52912,7 @@
     </row>
     <row r="1468" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1468" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1468" t="s">
         <v>62</v>
@@ -52980,7 +52924,7 @@
         <v>25</v>
       </c>
       <c r="E1468" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1468" t="s">
         <v>77</v>
@@ -52998,7 +52942,7 @@
     </row>
     <row r="1469" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1469" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1469" t="s">
         <v>62</v>
@@ -53010,7 +52954,7 @@
         <v>25</v>
       </c>
       <c r="E1469" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1469" t="s">
         <v>71</v>
@@ -53028,7 +52972,7 @@
     </row>
     <row r="1470" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1470" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1470" t="s">
         <v>62</v>
@@ -53040,7 +52984,7 @@
         <v>25</v>
       </c>
       <c r="E1470" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1470" t="s">
         <v>139</v>
@@ -53058,7 +53002,7 @@
     </row>
     <row r="1471" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1471" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1471" t="s">
         <v>62</v>
@@ -53070,7 +53014,7 @@
         <v>25</v>
       </c>
       <c r="E1471" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1471" t="s">
         <v>66</v>
@@ -53088,7 +53032,7 @@
     </row>
     <row r="1472" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1472" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1472" t="s">
         <v>62</v>
@@ -53100,7 +53044,7 @@
         <v>25</v>
       </c>
       <c r="E1472" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1472" t="s">
         <v>69</v>
@@ -53118,7 +53062,7 @@
     </row>
     <row r="1473" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1473" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1473" t="s">
         <v>62</v>
@@ -53130,7 +53074,7 @@
         <v>25</v>
       </c>
       <c r="E1473" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1473" t="s">
         <v>151</v>
@@ -53148,7 +53092,7 @@
     </row>
     <row r="1474" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1474" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1474" t="s">
         <v>62</v>
@@ -53160,7 +53104,7 @@
         <v>25</v>
       </c>
       <c r="E1474" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1474" t="s">
         <v>100</v>
@@ -53178,7 +53122,7 @@
     </row>
     <row r="1475" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1475" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1475" t="s">
         <v>62</v>
@@ -53190,7 +53134,7 @@
         <v>25</v>
       </c>
       <c r="E1475" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1475" t="s">
         <v>75</v>
@@ -53208,7 +53152,7 @@
     </row>
     <row r="1476" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1476" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1476" t="s">
         <v>62</v>
@@ -53220,7 +53164,7 @@
         <v>25</v>
       </c>
       <c r="E1476" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1476" t="s">
         <v>77</v>
@@ -53238,7 +53182,7 @@
     </row>
     <row r="1477" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1477" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1477" t="s">
         <v>62</v>
@@ -53250,7 +53194,7 @@
         <v>25</v>
       </c>
       <c r="E1477" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1477" t="s">
         <v>71</v>
@@ -53268,7 +53212,7 @@
     </row>
     <row r="1478" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1478" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1478" t="s">
         <v>62</v>
@@ -53280,7 +53224,7 @@
         <v>25</v>
       </c>
       <c r="E1478" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1478" t="s">
         <v>139</v>
@@ -53298,7 +53242,7 @@
     </row>
     <row r="1479" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1479" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1479" t="s">
         <v>62</v>
@@ -53310,7 +53254,7 @@
         <v>25</v>
       </c>
       <c r="E1479" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1479" t="s">
         <v>66</v>
@@ -53328,7 +53272,7 @@
     </row>
     <row r="1480" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1480" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1480" t="s">
         <v>62</v>
@@ -53340,7 +53284,7 @@
         <v>25</v>
       </c>
       <c r="E1480" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1480" t="s">
         <v>151</v>
@@ -53358,7 +53302,7 @@
     </row>
     <row r="1481" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1481" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1481" t="s">
         <v>62</v>
@@ -53370,7 +53314,7 @@
         <v>25</v>
       </c>
       <c r="E1481" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1481" t="s">
         <v>100</v>
@@ -53388,7 +53332,7 @@
     </row>
     <row r="1482" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1482" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1482" t="s">
         <v>62</v>
@@ -53400,7 +53344,7 @@
         <v>25</v>
       </c>
       <c r="E1482" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1482" t="s">
         <v>75</v>
@@ -53418,7 +53362,7 @@
     </row>
     <row r="1483" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1483" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1483" t="s">
         <v>62</v>
@@ -53430,7 +53374,7 @@
         <v>25</v>
       </c>
       <c r="E1483" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1483" t="s">
         <v>77</v>
@@ -53448,7 +53392,7 @@
     </row>
     <row r="1484" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1484" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1484" t="s">
         <v>62</v>
@@ -53460,7 +53404,7 @@
         <v>25</v>
       </c>
       <c r="E1484" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1484" t="s">
         <v>71</v>
@@ -53478,7 +53422,7 @@
     </row>
     <row r="1485" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1485" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1485" t="s">
         <v>62</v>
@@ -53490,7 +53434,7 @@
         <v>26</v>
       </c>
       <c r="E1485" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1485" t="s">
         <v>76</v>
@@ -53508,7 +53452,7 @@
     </row>
     <row r="1486" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1486" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1486" t="s">
         <v>62</v>
@@ -53520,7 +53464,7 @@
         <v>25</v>
       </c>
       <c r="E1486" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1486" t="s">
         <v>139</v>
@@ -53538,7 +53482,7 @@
     </row>
     <row r="1487" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1487" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1487" t="s">
         <v>62</v>
@@ -53550,7 +53494,7 @@
         <v>25</v>
       </c>
       <c r="E1487" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1487" t="s">
         <v>66</v>
@@ -53568,7 +53512,7 @@
     </row>
     <row r="1488" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1488" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1488" t="s">
         <v>62</v>
@@ -53580,7 +53524,7 @@
         <v>25</v>
       </c>
       <c r="E1488" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1488" t="s">
         <v>151</v>
@@ -53598,7 +53542,7 @@
     </row>
     <row r="1489" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1489" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1489" t="s">
         <v>62</v>
@@ -53610,7 +53554,7 @@
         <v>25</v>
       </c>
       <c r="E1489" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1489" t="s">
         <v>100</v>
@@ -53628,7 +53572,7 @@
     </row>
     <row r="1490" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1490" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1490" t="s">
         <v>62</v>
@@ -53640,7 +53584,7 @@
         <v>25</v>
       </c>
       <c r="E1490" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1490" t="s">
         <v>75</v>
@@ -53658,7 +53602,7 @@
     </row>
     <row r="1491" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1491" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1491" t="s">
         <v>62</v>
@@ -53670,7 +53614,7 @@
         <v>25</v>
       </c>
       <c r="E1491" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1491" t="s">
         <v>77</v>
@@ -53688,7 +53632,7 @@
     </row>
     <row r="1492" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1492" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1492" t="s">
         <v>62</v>
@@ -53700,7 +53644,7 @@
         <v>25</v>
       </c>
       <c r="E1492" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1492" t="s">
         <v>71</v>
@@ -53718,7 +53662,7 @@
     </row>
     <row r="1493" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1493" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1493" t="s">
         <v>62</v>
@@ -53730,7 +53674,7 @@
         <v>26</v>
       </c>
       <c r="E1493" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1493" t="s">
         <v>101</v>
@@ -53748,7 +53692,7 @@
     </row>
     <row r="1494" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1494" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1494" t="s">
         <v>62</v>
@@ -53760,7 +53704,7 @@
         <v>26</v>
       </c>
       <c r="E1494" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1494" t="s">
         <v>65</v>
@@ -53778,7 +53722,7 @@
     </row>
     <row r="1495" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1495" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1495" t="s">
         <v>62</v>
@@ -53790,7 +53734,7 @@
         <v>25</v>
       </c>
       <c r="E1495" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1495" t="s">
         <v>139</v>
@@ -53808,7 +53752,7 @@
     </row>
     <row r="1496" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1496" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1496" t="s">
         <v>62</v>
@@ -53820,7 +53764,7 @@
         <v>25</v>
       </c>
       <c r="E1496" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1496" t="s">
         <v>66</v>
@@ -53838,7 +53782,7 @@
     </row>
     <row r="1497" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1497" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1497" t="s">
         <v>62</v>
@@ -53850,7 +53794,7 @@
         <v>25</v>
       </c>
       <c r="E1497" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1497" t="s">
         <v>69</v>
@@ -53868,7 +53812,7 @@
     </row>
     <row r="1498" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1498" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1498" t="s">
         <v>62</v>
@@ -53880,7 +53824,7 @@
         <v>25</v>
       </c>
       <c r="E1498" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1498" t="s">
         <v>151</v>
@@ -53898,7 +53842,7 @@
     </row>
     <row r="1499" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1499" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1499" t="s">
         <v>62</v>
@@ -53910,7 +53854,7 @@
         <v>25</v>
       </c>
       <c r="E1499" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1499" t="s">
         <v>100</v>
@@ -53928,7 +53872,7 @@
     </row>
     <row r="1500" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1500" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1500" t="s">
         <v>62</v>
@@ -53940,7 +53884,7 @@
         <v>25</v>
       </c>
       <c r="E1500" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1500" t="s">
         <v>75</v>
@@ -53958,7 +53902,7 @@
     </row>
     <row r="1501" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1501" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1501" t="s">
         <v>62</v>
@@ -53970,7 +53914,7 @@
         <v>25</v>
       </c>
       <c r="E1501" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1501" t="s">
         <v>77</v>
@@ -53988,7 +53932,7 @@
     </row>
     <row r="1502" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1502" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1502" t="s">
         <v>62</v>
@@ -54000,7 +53944,7 @@
         <v>25</v>
       </c>
       <c r="E1502" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1502" t="s">
         <v>71</v>
@@ -54018,7 +53962,7 @@
     </row>
     <row r="1503" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1503" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1503" t="s">
         <v>62</v>
@@ -54030,7 +53974,7 @@
         <v>25</v>
       </c>
       <c r="E1503" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1503" t="s">
         <v>139</v>
@@ -54048,7 +53992,7 @@
     </row>
     <row r="1504" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1504" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1504" t="s">
         <v>62</v>
@@ -54060,7 +54004,7 @@
         <v>25</v>
       </c>
       <c r="E1504" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1504" t="s">
         <v>66</v>
@@ -54078,7 +54022,7 @@
     </row>
     <row r="1505" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1505" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1505" t="s">
         <v>62</v>
@@ -54090,7 +54034,7 @@
         <v>25</v>
       </c>
       <c r="E1505" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1505" t="s">
         <v>69</v>
@@ -54108,7 +54052,7 @@
     </row>
     <row r="1506" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1506" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1506" t="s">
         <v>62</v>
@@ -54120,7 +54064,7 @@
         <v>25</v>
       </c>
       <c r="E1506" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1506" t="s">
         <v>151</v>
@@ -54138,7 +54082,7 @@
     </row>
     <row r="1507" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1507" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1507" t="s">
         <v>62</v>
@@ -54150,7 +54094,7 @@
         <v>25</v>
       </c>
       <c r="E1507" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1507" t="s">
         <v>100</v>
@@ -54168,7 +54112,7 @@
     </row>
     <row r="1508" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1508" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1508" t="s">
         <v>62</v>
@@ -54180,7 +54124,7 @@
         <v>25</v>
       </c>
       <c r="E1508" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1508" t="s">
         <v>75</v>
@@ -54198,7 +54142,7 @@
     </row>
     <row r="1509" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1509" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1509" t="s">
         <v>62</v>
@@ -54210,7 +54154,7 @@
         <v>25</v>
       </c>
       <c r="E1509" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1509" t="s">
         <v>77</v>
@@ -54228,7 +54172,7 @@
     </row>
     <row r="1510" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1510" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1510" t="s">
         <v>62</v>
@@ -54240,7 +54184,7 @@
         <v>25</v>
       </c>
       <c r="E1510" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1510" t="s">
         <v>71</v>
@@ -54258,7 +54202,7 @@
     </row>
     <row r="1511" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1511" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1511" t="s">
         <v>62</v>
@@ -54270,7 +54214,7 @@
         <v>25</v>
       </c>
       <c r="E1511" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1511" t="s">
         <v>139</v>
@@ -54288,7 +54232,7 @@
     </row>
     <row r="1512" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1512" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1512" t="s">
         <v>62</v>
@@ -54300,7 +54244,7 @@
         <v>25</v>
       </c>
       <c r="E1512" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1512" t="s">
         <v>66</v>
@@ -54318,7 +54262,7 @@
     </row>
     <row r="1513" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1513" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1513" t="s">
         <v>62</v>
@@ -54330,7 +54274,7 @@
         <v>25</v>
       </c>
       <c r="E1513" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1513" t="s">
         <v>69</v>
@@ -54348,7 +54292,7 @@
     </row>
     <row r="1514" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1514" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1514" t="s">
         <v>62</v>
@@ -54360,7 +54304,7 @@
         <v>25</v>
       </c>
       <c r="E1514" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1514" t="s">
         <v>151</v>
@@ -54378,7 +54322,7 @@
     </row>
     <row r="1515" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1515" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1515" t="s">
         <v>62</v>
@@ -54390,7 +54334,7 @@
         <v>25</v>
       </c>
       <c r="E1515" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1515" t="s">
         <v>100</v>
@@ -54408,7 +54352,7 @@
     </row>
     <row r="1516" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1516" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1516" t="s">
         <v>62</v>
@@ -54420,7 +54364,7 @@
         <v>25</v>
       </c>
       <c r="E1516" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1516" t="s">
         <v>75</v>
@@ -54438,7 +54382,7 @@
     </row>
     <row r="1517" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1517" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1517" t="s">
         <v>62</v>
@@ -54450,7 +54394,7 @@
         <v>25</v>
       </c>
       <c r="E1517" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1517" t="s">
         <v>77</v>
@@ -54468,7 +54412,7 @@
     </row>
     <row r="1518" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1518" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1518" t="s">
         <v>62</v>
@@ -54480,7 +54424,7 @@
         <v>25</v>
       </c>
       <c r="E1518" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1518" t="s">
         <v>71</v>
@@ -54498,7 +54442,7 @@
     </row>
     <row r="1519" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1519" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1519" t="s">
         <v>62</v>
@@ -54510,7 +54454,7 @@
         <v>25</v>
       </c>
       <c r="E1519" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F1519" t="s">
         <v>139</v>
@@ -54528,7 +54472,7 @@
     </row>
     <row r="1520" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1520" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1520" s="2" t="s">
         <v>104</v>
@@ -54558,7 +54502,7 @@
     </row>
     <row r="1521" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1521" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1521" s="2" t="s">
         <v>104</v>
@@ -54588,7 +54532,7 @@
     </row>
     <row r="1522" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1522" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1522" s="2" t="s">
         <v>104</v>
@@ -54618,7 +54562,7 @@
     </row>
     <row r="1523" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1523" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1523" s="2" t="s">
         <v>104</v>
@@ -54648,7 +54592,7 @@
     </row>
     <row r="1524" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1524" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1524" s="2" t="s">
         <v>104</v>
@@ -54666,10 +54610,10 @@
         <v>106</v>
       </c>
       <c r="G1524" t="s">
+        <v>158</v>
+      </c>
+      <c r="H1524" t="s">
         <v>159</v>
-      </c>
-      <c r="H1524" t="s">
-        <v>160</v>
       </c>
       <c r="I1524" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1524,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
@@ -54678,7 +54622,7 @@
     </row>
     <row r="1525" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1525" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1525" s="2" t="s">
         <v>104</v>
@@ -54696,10 +54640,10 @@
         <v>106</v>
       </c>
       <c r="G1525" t="s">
+        <v>158</v>
+      </c>
+      <c r="H1525" t="s">
         <v>159</v>
-      </c>
-      <c r="H1525" t="s">
-        <v>160</v>
       </c>
       <c r="I1525" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1525,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
@@ -54708,7 +54652,7 @@
     </row>
     <row r="1526" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1526" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1526" s="2" t="s">
         <v>104</v>
@@ -54726,10 +54670,10 @@
         <v>107</v>
       </c>
       <c r="G1526" t="s">
+        <v>158</v>
+      </c>
+      <c r="H1526" t="s">
         <v>159</v>
-      </c>
-      <c r="H1526" t="s">
-        <v>160</v>
       </c>
       <c r="I1526" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1526,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
@@ -54738,7 +54682,7 @@
     </row>
     <row r="1527" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1527" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1527" s="2" t="s">
         <v>104</v>
@@ -54756,10 +54700,10 @@
         <v>107</v>
       </c>
       <c r="G1527" t="s">
+        <v>158</v>
+      </c>
+      <c r="H1527" t="s">
         <v>159</v>
-      </c>
-      <c r="H1527" t="s">
-        <v>160</v>
       </c>
       <c r="I1527" s="2" t="str">
         <f>_xlfn.XLOOKUP(F1527,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
@@ -54768,7 +54712,7 @@
     </row>
     <row r="1528" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1528" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1528" s="2" t="s">
         <v>104</v>
@@ -54798,7 +54742,7 @@
     </row>
     <row r="1529" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1529" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1529" s="2" t="s">
         <v>104</v>
@@ -54828,7 +54772,7 @@
     </row>
     <row r="1530" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1530" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1530" s="2" t="s">
         <v>104</v>
@@ -54858,7 +54802,7 @@
     </row>
     <row r="1531" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1531" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1531" s="2" t="s">
         <v>104</v>
@@ -54888,7 +54832,7 @@
     </row>
     <row r="1532" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1532" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1532" s="2" t="s">
         <v>104</v>
@@ -54918,7 +54862,7 @@
     </row>
     <row r="1533" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1533" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1533" s="2" t="s">
         <v>104</v>
@@ -54948,7 +54892,7 @@
     </row>
     <row r="1534" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1534" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1534" s="2" t="s">
         <v>104</v>
@@ -54978,7 +54922,7 @@
     </row>
     <row r="1535" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1535" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1535" s="2" t="s">
         <v>104</v>
@@ -55006,8 +54950,1688 @@
         <v>FFLN.png</v>
       </c>
     </row>
+    <row r="1536" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1536" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1536" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1536" t="s">
+        <v>113</v>
+      </c>
+      <c r="D1536" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1536" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1536" t="s">
+        <v>66</v>
+      </c>
+      <c r="G1536">
+        <v>3.39</v>
+      </c>
+      <c r="H1536">
+        <v>3.09</v>
+      </c>
+      <c r="I1536" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1536,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>SK269.png</v>
+      </c>
+    </row>
+    <row r="1537" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1537" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1537" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1537" t="s">
+        <v>113</v>
+      </c>
+      <c r="D1537" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1537" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1537" t="s">
+        <v>151</v>
+      </c>
+      <c r="G1537">
+        <v>3.49</v>
+      </c>
+      <c r="H1537">
+        <v>2.5900000000000003</v>
+      </c>
+      <c r="I1537" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1537,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>BDM269.png</v>
+      </c>
+    </row>
+    <row r="1538" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1538" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1538" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1538" t="s">
+        <v>113</v>
+      </c>
+      <c r="D1538" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1538" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1538" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1538">
+        <v>3.99</v>
+      </c>
+      <c r="H1538">
+        <v>3.49</v>
+      </c>
+      <c r="I1538" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1538,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>SPT269.png</v>
+      </c>
+    </row>
+    <row r="1539" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1539" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1539" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1539" t="s">
+        <v>113</v>
+      </c>
+      <c r="D1539" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1539" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1539" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1539">
+        <v>4.29</v>
+      </c>
+      <c r="H1539">
+        <v>3.49</v>
+      </c>
+      <c r="I1539" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1539,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>STE269.png</v>
+      </c>
+    </row>
+    <row r="1540" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1540" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1540" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1540" t="s">
+        <v>113</v>
+      </c>
+      <c r="D1540" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1540" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1540" t="s">
+        <v>77</v>
+      </c>
+      <c r="G1540">
+        <v>4.79</v>
+      </c>
+      <c r="H1540">
+        <v>4.09</v>
+      </c>
+      <c r="I1540" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1540,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>COR269.png</v>
+      </c>
+    </row>
+    <row r="1541" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1541" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1541" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1541" t="s">
+        <v>113</v>
+      </c>
+      <c r="D1541" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1541" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1541" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1541">
+        <v>3.79</v>
+      </c>
+      <c r="H1541">
+        <v>3.39</v>
+      </c>
+      <c r="I1541" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1541,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>BC350.png</v>
+      </c>
+    </row>
+    <row r="1542" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1542" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1542" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1542" t="s">
+        <v>113</v>
+      </c>
+      <c r="D1542" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1542" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1542" t="s">
+        <v>139</v>
+      </c>
+      <c r="G1542">
+        <v>6.59</v>
+      </c>
+      <c r="H1542">
+        <v>6.09</v>
+      </c>
+      <c r="I1542" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1542,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>SPTLN.png</v>
+      </c>
+    </row>
+    <row r="1543" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1543" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1543" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1543" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1543" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1543" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1543" t="s">
+        <v>66</v>
+      </c>
+      <c r="G1543">
+        <v>3.19</v>
+      </c>
+      <c r="H1543">
+        <v>2.99</v>
+      </c>
+      <c r="I1543" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1543,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>SK269.png</v>
+      </c>
+    </row>
+    <row r="1544" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1544" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1544" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1544" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1544" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1544" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1544" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1544">
+        <v>3.6900000000000004</v>
+      </c>
+      <c r="H1544">
+        <v>3.1900000000000004</v>
+      </c>
+      <c r="I1544" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1544,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>BUD269.png</v>
+      </c>
+    </row>
+    <row r="1545" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1545" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1545" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1545" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1545" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1545" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1545" t="s">
+        <v>151</v>
+      </c>
+      <c r="G1545">
+        <v>3.69</v>
+      </c>
+      <c r="H1545">
+        <v>3.19</v>
+      </c>
+      <c r="I1545" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1545,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>BDM269.png</v>
+      </c>
+    </row>
+    <row r="1546" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1546" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1546" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1546" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1546" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1546" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1546" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1546">
+        <v>3.99</v>
+      </c>
+      <c r="H1546">
+        <v>3.49</v>
+      </c>
+      <c r="I1546" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1546,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>SPT269.png</v>
+      </c>
+    </row>
+    <row r="1547" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1547" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1547" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1547" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1547" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1547" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1547" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1547">
+        <v>4.29</v>
+      </c>
+      <c r="H1547">
+        <v>3.49</v>
+      </c>
+      <c r="I1547" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1547,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>STE269.png</v>
+      </c>
+    </row>
+    <row r="1548" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1548" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1548" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1548" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1548" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1548" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1548" t="s">
+        <v>77</v>
+      </c>
+      <c r="G1548">
+        <v>4.79</v>
+      </c>
+      <c r="H1548">
+        <v>4.09</v>
+      </c>
+      <c r="I1548" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1548,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>COR269.png</v>
+      </c>
+    </row>
+    <row r="1549" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1549" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1549" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1549" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1549" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1549" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1549" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1549">
+        <v>3.99</v>
+      </c>
+      <c r="H1549">
+        <v>3.69</v>
+      </c>
+      <c r="I1549" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1549,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>BC350.png</v>
+      </c>
+    </row>
+    <row r="1550" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1550" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1550" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1550" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1550" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1550" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1550" t="s">
+        <v>139</v>
+      </c>
+      <c r="G1550">
+        <v>6.59</v>
+      </c>
+      <c r="H1550">
+        <v>6.09</v>
+      </c>
+      <c r="I1550" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1550,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>SPTLN.png</v>
+      </c>
+    </row>
+    <row r="1551" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1551" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1551" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1551" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1551" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1551" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1551" t="s">
+        <v>66</v>
+      </c>
+      <c r="G1551">
+        <v>3.19</v>
+      </c>
+      <c r="H1551">
+        <v>2.99</v>
+      </c>
+      <c r="I1551" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1551,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>SK269.png</v>
+      </c>
+    </row>
+    <row r="1552" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1552" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1552" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1552" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1552" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1552" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1552" t="s">
+        <v>151</v>
+      </c>
+      <c r="G1552">
+        <v>3.5900000000000003</v>
+      </c>
+      <c r="H1552">
+        <v>3.0900000000000003</v>
+      </c>
+      <c r="I1552" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1552,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>BDM269.png</v>
+      </c>
+    </row>
+    <row r="1553" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1553" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1553" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1553" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1553" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1553" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1553" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1553">
+        <v>3.99</v>
+      </c>
+      <c r="H1553">
+        <v>3.49</v>
+      </c>
+      <c r="I1553" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1553,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>SPT269.png</v>
+      </c>
+    </row>
+    <row r="1554" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1554" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1554" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1554" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1554" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1554" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1554" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1554">
+        <v>4.29</v>
+      </c>
+      <c r="H1554">
+        <v>3.49</v>
+      </c>
+      <c r="I1554" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1554,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>STE269.png</v>
+      </c>
+    </row>
+    <row r="1555" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1555" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1555" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1555" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1555" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1555" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1555" t="s">
+        <v>77</v>
+      </c>
+      <c r="G1555">
+        <v>4.79</v>
+      </c>
+      <c r="H1555">
+        <v>4.09</v>
+      </c>
+      <c r="I1555" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1555,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>COR269.png</v>
+      </c>
+    </row>
+    <row r="1556" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1556" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1556" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1556" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1556" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1556" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1556" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1556">
+        <v>3.89</v>
+      </c>
+      <c r="H1556">
+        <v>3.59</v>
+      </c>
+      <c r="I1556" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1556,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>BC350.png</v>
+      </c>
+    </row>
+    <row r="1557" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1557" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1557" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1557" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1557" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1557" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1557" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1557">
+        <v>4.59</v>
+      </c>
+      <c r="H1557">
+        <v>3.99</v>
+      </c>
+      <c r="I1557" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1557,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>BUD350.png</v>
+      </c>
+    </row>
+    <row r="1558" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1558" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1558" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1558" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1558" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1558" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1558" t="s">
+        <v>139</v>
+      </c>
+      <c r="G1558">
+        <v>6.59</v>
+      </c>
+      <c r="H1558">
+        <v>6.09</v>
+      </c>
+      <c r="I1558" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1558,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>SPTLN.png</v>
+      </c>
+    </row>
+    <row r="1559" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1559" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1559" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1559" t="s">
+        <v>112</v>
+      </c>
+      <c r="D1559" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1559" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1559" t="s">
+        <v>66</v>
+      </c>
+      <c r="G1559">
+        <v>3.19</v>
+      </c>
+      <c r="H1559">
+        <v>2.99</v>
+      </c>
+      <c r="I1559" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1559,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>SK269.png</v>
+      </c>
+    </row>
+    <row r="1560" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1560" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1560" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1560" t="s">
+        <v>112</v>
+      </c>
+      <c r="D1560" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1560" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1560" t="s">
+        <v>151</v>
+      </c>
+      <c r="G1560">
+        <v>3.5900000000000003</v>
+      </c>
+      <c r="H1560">
+        <v>3.0900000000000003</v>
+      </c>
+      <c r="I1560" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1560,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>BDM269.png</v>
+      </c>
+    </row>
+    <row r="1561" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1561" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1561" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1561" t="s">
+        <v>112</v>
+      </c>
+      <c r="D1561" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1561" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1561" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1561">
+        <v>3.99</v>
+      </c>
+      <c r="H1561">
+        <v>3.49</v>
+      </c>
+      <c r="I1561" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1561,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>SPT269.png</v>
+      </c>
+    </row>
+    <row r="1562" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1562" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1562" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1562" t="s">
+        <v>112</v>
+      </c>
+      <c r="D1562" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1562" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1562" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1562">
+        <v>4.29</v>
+      </c>
+      <c r="H1562">
+        <v>3.49</v>
+      </c>
+      <c r="I1562" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1562,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>STE269.png</v>
+      </c>
+    </row>
+    <row r="1563" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1563" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1563" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1563" t="s">
+        <v>112</v>
+      </c>
+      <c r="D1563" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1563" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1563" t="s">
+        <v>77</v>
+      </c>
+      <c r="G1563">
+        <v>4.6900000000000004</v>
+      </c>
+      <c r="H1563">
+        <v>4.09</v>
+      </c>
+      <c r="I1563" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1563,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>COR269.png</v>
+      </c>
+    </row>
+    <row r="1564" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1564" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1564" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1564" t="s">
+        <v>112</v>
+      </c>
+      <c r="D1564" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1564" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1564" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1564">
+        <v>3.89</v>
+      </c>
+      <c r="H1564">
+        <v>3.59</v>
+      </c>
+      <c r="I1564" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1564,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>BC350.png</v>
+      </c>
+    </row>
+    <row r="1565" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1565" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1565" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1565" t="s">
+        <v>112</v>
+      </c>
+      <c r="D1565" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1565" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1565" t="s">
+        <v>101</v>
+      </c>
+      <c r="G1565">
+        <v>5.29</v>
+      </c>
+      <c r="H1565">
+        <v>4.79</v>
+      </c>
+      <c r="I1565" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1565,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>SPT350.png</v>
+      </c>
+    </row>
+    <row r="1566" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1566" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1566" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1566" t="s">
+        <v>112</v>
+      </c>
+      <c r="D1566" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1566" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1566" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1566">
+        <v>5.59</v>
+      </c>
+      <c r="H1566">
+        <v>4.59</v>
+      </c>
+      <c r="I1566" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1566,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>STE350.png</v>
+      </c>
+    </row>
+    <row r="1567" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1567" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1567" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1567" t="s">
+        <v>112</v>
+      </c>
+      <c r="D1567" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1567" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1567" t="s">
+        <v>139</v>
+      </c>
+      <c r="G1567">
+        <v>6.59</v>
+      </c>
+      <c r="H1567">
+        <v>6.09</v>
+      </c>
+      <c r="I1567" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1567,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>SPTLN.png</v>
+      </c>
+    </row>
+    <row r="1568" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1568" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1568" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1568" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1568" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1568" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1568" t="s">
+        <v>66</v>
+      </c>
+      <c r="G1568">
+        <v>3.19</v>
+      </c>
+      <c r="H1568">
+        <v>2.99</v>
+      </c>
+      <c r="I1568" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1568,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>SK269.png</v>
+      </c>
+    </row>
+    <row r="1569" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1569" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1569" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1569" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1569" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1569" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1569" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1569">
+        <v>3.6900000000000004</v>
+      </c>
+      <c r="H1569">
+        <v>3.29</v>
+      </c>
+      <c r="I1569" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1569,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>BUD269.png</v>
+      </c>
+    </row>
+    <row r="1570" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1570" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1570" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1570" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1570" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1570" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1570" t="s">
+        <v>151</v>
+      </c>
+      <c r="G1570">
+        <v>3.5900000000000003</v>
+      </c>
+      <c r="H1570">
+        <v>3.0900000000000003</v>
+      </c>
+      <c r="I1570" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1570,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>BDM269.png</v>
+      </c>
+    </row>
+    <row r="1571" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1571" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1571" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1571" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1571" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1571" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1571" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1571">
+        <v>3.99</v>
+      </c>
+      <c r="H1571">
+        <v>3.49</v>
+      </c>
+      <c r="I1571" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1571,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>SPT269.png</v>
+      </c>
+    </row>
+    <row r="1572" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1572" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1572" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1572" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1572" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1572" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1572" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1572">
+        <v>4.29</v>
+      </c>
+      <c r="H1572">
+        <v>3.49</v>
+      </c>
+      <c r="I1572" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1572,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>STE269.png</v>
+      </c>
+    </row>
+    <row r="1573" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1573" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1573" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1573" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1573" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1573" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1573" t="s">
+        <v>77</v>
+      </c>
+      <c r="G1573">
+        <v>4.79</v>
+      </c>
+      <c r="H1573">
+        <v>4.09</v>
+      </c>
+      <c r="I1573" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1573,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>COR269.png</v>
+      </c>
+    </row>
+    <row r="1574" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1574" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1574" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1574" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1574" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1574" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1574" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1574">
+        <v>3.99</v>
+      </c>
+      <c r="H1574">
+        <v>3.69</v>
+      </c>
+      <c r="I1574" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1574,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>BC350.png</v>
+      </c>
+    </row>
+    <row r="1575" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1575" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1575" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1575" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1575" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1575" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1575" t="s">
+        <v>139</v>
+      </c>
+      <c r="G1575">
+        <v>6.59</v>
+      </c>
+      <c r="H1575">
+        <v>6.09</v>
+      </c>
+      <c r="I1575" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1575,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>SPTLN.png</v>
+      </c>
+    </row>
+    <row r="1576" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1576" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1576" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1576" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1576" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1576" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1576" t="s">
+        <v>66</v>
+      </c>
+      <c r="G1576">
+        <v>3.39</v>
+      </c>
+      <c r="H1576">
+        <v>3.09</v>
+      </c>
+      <c r="I1576" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1576,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>SK269.png</v>
+      </c>
+    </row>
+    <row r="1577" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1577" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1577" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1577" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1577" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1577" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1577" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1577">
+        <v>3.6900000000000004</v>
+      </c>
+      <c r="H1577">
+        <v>3.29</v>
+      </c>
+      <c r="I1577" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1577,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>BUD269.png</v>
+      </c>
+    </row>
+    <row r="1578" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1578" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1578" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1578" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1578" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1578" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1578" t="s">
+        <v>151</v>
+      </c>
+      <c r="G1578">
+        <v>3.5900000000000003</v>
+      </c>
+      <c r="H1578">
+        <v>3.0900000000000003</v>
+      </c>
+      <c r="I1578" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1578,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>BDM269.png</v>
+      </c>
+    </row>
+    <row r="1579" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1579" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1579" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1579" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1579" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1579" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1579" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1579">
+        <v>3.99</v>
+      </c>
+      <c r="H1579">
+        <v>3.49</v>
+      </c>
+      <c r="I1579" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1579,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>SPT269.png</v>
+      </c>
+    </row>
+    <row r="1580" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1580" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1580" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1580" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1580" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1580" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1580" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1580">
+        <v>4.29</v>
+      </c>
+      <c r="H1580">
+        <v>3.49</v>
+      </c>
+      <c r="I1580" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1580,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>STE269.png</v>
+      </c>
+    </row>
+    <row r="1581" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1581" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1581" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1581" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1581" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1581" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1581" t="s">
+        <v>77</v>
+      </c>
+      <c r="G1581">
+        <v>4.79</v>
+      </c>
+      <c r="H1581">
+        <v>4.09</v>
+      </c>
+      <c r="I1581" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1581,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>COR269.png</v>
+      </c>
+    </row>
+    <row r="1582" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1582" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1582" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1582" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1582" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1582" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1582" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1582">
+        <v>3.89</v>
+      </c>
+      <c r="H1582">
+        <v>3.59</v>
+      </c>
+      <c r="I1582" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1582,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>BC350.png</v>
+      </c>
+    </row>
+    <row r="1583" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1583" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1583" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1583" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1583" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1583" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1583" t="s">
+        <v>139</v>
+      </c>
+      <c r="G1583">
+        <v>6.59</v>
+      </c>
+      <c r="H1583">
+        <v>6.09</v>
+      </c>
+      <c r="I1583" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1583,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>SPTLN.png</v>
+      </c>
+    </row>
+    <row r="1584" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1584" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1584" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1584" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1584" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1584" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1584" t="s">
+        <v>66</v>
+      </c>
+      <c r="G1584">
+        <v>3.39</v>
+      </c>
+      <c r="H1584">
+        <v>3.09</v>
+      </c>
+      <c r="I1584" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1584,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>SK269.png</v>
+      </c>
+    </row>
+    <row r="1585" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1585" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1585" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1585" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1585" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1585" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1585" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1585">
+        <v>3.6900000000000004</v>
+      </c>
+      <c r="H1585">
+        <v>3.29</v>
+      </c>
+      <c r="I1585" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1585,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>BUD269.png</v>
+      </c>
+    </row>
+    <row r="1586" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1586" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1586" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1586" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1586" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1586" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1586" t="s">
+        <v>151</v>
+      </c>
+      <c r="G1586">
+        <v>3.5900000000000003</v>
+      </c>
+      <c r="H1586">
+        <v>3.0900000000000003</v>
+      </c>
+      <c r="I1586" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1586,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>BDM269.png</v>
+      </c>
+    </row>
+    <row r="1587" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1587" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1587" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1587" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1587" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1587" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1587" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1587">
+        <v>3.99</v>
+      </c>
+      <c r="H1587">
+        <v>3.49</v>
+      </c>
+      <c r="I1587" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1587,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>SPT269.png</v>
+      </c>
+    </row>
+    <row r="1588" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1588" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1588" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1588" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1588" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1588" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1588" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1588">
+        <v>4.29</v>
+      </c>
+      <c r="H1588">
+        <v>3.49</v>
+      </c>
+      <c r="I1588" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1588,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>STE269.png</v>
+      </c>
+    </row>
+    <row r="1589" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1589" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1589" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1589" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1589" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1589" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1589" t="s">
+        <v>77</v>
+      </c>
+      <c r="G1589">
+        <v>4.79</v>
+      </c>
+      <c r="H1589">
+        <v>4.09</v>
+      </c>
+      <c r="I1589" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1589,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>COR269.png</v>
+      </c>
+    </row>
+    <row r="1590" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1590" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1590" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1590" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1590" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1590" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1590" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1590">
+        <v>3.89</v>
+      </c>
+      <c r="H1590">
+        <v>3.59</v>
+      </c>
+      <c r="I1590" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1590,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>BC350.png</v>
+      </c>
+    </row>
+    <row r="1591" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1591" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1591" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1591" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1591" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1591" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1591" t="s">
+        <v>139</v>
+      </c>
+      <c r="G1591">
+        <v>6.59</v>
+      </c>
+      <c r="H1591">
+        <v>6.09</v>
+      </c>
+      <c r="I1591" s="2" t="str">
+        <f>_xlfn.XLOOKUP(F1591,DeparaIMG!D:D,DeparaIMG!F:F,,0)</f>
+        <v>SPTLN.png</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I1535" xr:uid="{34B2C8DF-4561-40B2-8E7C-6CD69559B9AE}"/>
+  <autoFilter ref="A1:I1591" xr:uid="{34B2C8DF-4561-40B2-8E7C-6CD69559B9AE}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>

--- a/data/calendario_promocional.xlsx
+++ b/data/calendario_promocional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anheuserbuschinbev-my.sharepoint.com/personal/99823517_ab-inbev_com/Documents/001. Projetos/Streamlit Calendario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="845" documentId="13_ncr:1_{B92F5DA4-8825-4FA1-97C6-23568D76854D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9807711-1360-4A34-853E-8509433FC426}"/>
+  <xr:revisionPtr revIDLastSave="851" documentId="13_ncr:1_{B92F5DA4-8825-4FA1-97C6-23568D76854D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87309BBA-F5C3-422B-BE63-157767644090}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DeparaIMG" sheetId="5" r:id="rId1"/>
@@ -882,7 +882,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0BF5819-473C-445D-A53D-FC51ACB237C6}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:F57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -912,7 +911,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>62</v>
       </c>
@@ -934,7 +933,7 @@
         <v>AP269.png</v>
       </c>
     </row>
-    <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>62</v>
       </c>
@@ -956,7 +955,7 @@
         <v>AP269MP.png</v>
       </c>
     </row>
-    <row r="4" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>62</v>
       </c>
@@ -978,7 +977,7 @@
         <v>AP350.png</v>
       </c>
     </row>
-    <row r="5" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>61</v>
       </c>
@@ -999,7 +998,7 @@
         <v>BAREP2.png</v>
       </c>
     </row>
-    <row r="6" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>62</v>
       </c>
@@ -1021,7 +1020,7 @@
         <v>BC0350.png</v>
       </c>
     </row>
-    <row r="7" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>62</v>
       </c>
@@ -1043,7 +1042,7 @@
         <v>BC269.png</v>
       </c>
     </row>
-    <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>62</v>
       </c>
@@ -1065,7 +1064,7 @@
         <v>BC269MP.png</v>
       </c>
     </row>
-    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>62</v>
       </c>
@@ -1087,7 +1086,7 @@
         <v>BC350.png</v>
       </c>
     </row>
-    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>104</v>
       </c>
@@ -1109,7 +1108,7 @@
         <v>BEATSLN.png</v>
       </c>
     </row>
-    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>104</v>
       </c>
@@ -1131,7 +1130,7 @@
         <v>BEATSLT.png</v>
       </c>
     </row>
-    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>62</v>
       </c>
@@ -1153,7 +1152,7 @@
         <v>BUD269.png</v>
       </c>
     </row>
-    <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>62</v>
       </c>
@@ -1175,7 +1174,7 @@
         <v>BUD269MP.png</v>
       </c>
     </row>
-    <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>62</v>
       </c>
@@ -1197,7 +1196,7 @@
         <v>BUD350.png</v>
       </c>
     </row>
-    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>62</v>
       </c>
@@ -1219,7 +1218,7 @@
         <v>BUDLN.png</v>
       </c>
     </row>
-    <row r="16" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>62</v>
       </c>
@@ -1240,7 +1239,7 @@
         <v>BUDZERO350.png</v>
       </c>
     </row>
-    <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>62</v>
       </c>
@@ -1261,7 +1260,7 @@
         <v>BUDZEROLN.png</v>
       </c>
     </row>
-    <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>62</v>
       </c>
@@ -1283,7 +1282,7 @@
         <v>COR269.png</v>
       </c>
     </row>
-    <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>62</v>
       </c>
@@ -1305,7 +1304,7 @@
         <v>COR350.png</v>
       </c>
     </row>
-    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>62</v>
       </c>
@@ -1326,7 +1325,7 @@
         <v>CORCERO350.png</v>
       </c>
     </row>
-    <row r="21" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>62</v>
       </c>
@@ -1347,7 +1346,7 @@
         <v>CORCEROLN.png</v>
       </c>
     </row>
-    <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>62</v>
       </c>
@@ -1369,7 +1368,7 @@
         <v>CORLN.png</v>
       </c>
     </row>
-    <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>104</v>
       </c>
@@ -1391,7 +1390,7 @@
         <v>FF350.png</v>
       </c>
     </row>
-    <row r="24" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>104</v>
       </c>
@@ -1413,7 +1412,7 @@
         <v>FFLN.png</v>
       </c>
     </row>
-    <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>61</v>
       </c>
@@ -1434,7 +1433,7 @@
         <v>GCA269.png</v>
       </c>
     </row>
-    <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>61</v>
       </c>
@@ -1455,7 +1454,7 @@
         <v>GCA350.png</v>
       </c>
     </row>
-    <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>61</v>
       </c>
@@ -1476,7 +1475,7 @@
         <v>GCAP1,5.png</v>
       </c>
     </row>
-    <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>61</v>
       </c>
@@ -1497,7 +1496,7 @@
         <v>GCAP1.png</v>
       </c>
     </row>
-    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>61</v>
       </c>
@@ -1518,7 +1517,7 @@
         <v>GCAP2.png</v>
       </c>
     </row>
-    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>61</v>
       </c>
@@ -1539,7 +1538,7 @@
         <v>H2OHP1,5.png</v>
       </c>
     </row>
-    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>61</v>
       </c>
@@ -1560,7 +1559,7 @@
         <v>H2OHP500.png</v>
       </c>
     </row>
-    <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>62</v>
       </c>
@@ -1582,7 +1581,7 @@
         <v>MIC269.png</v>
       </c>
     </row>
-    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>62</v>
       </c>
@@ -1604,7 +1603,7 @@
         <v>MIC350.png</v>
       </c>
     </row>
-    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>62</v>
       </c>
@@ -1626,7 +1625,7 @@
         <v>MICLN.png</v>
       </c>
     </row>
-    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>62</v>
       </c>
@@ -1648,7 +1647,7 @@
         <v>ORI269.png</v>
       </c>
     </row>
-    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>62</v>
       </c>
@@ -1670,7 +1669,7 @@
         <v>ORI269MP.png</v>
       </c>
     </row>
-    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>61</v>
       </c>
@@ -1691,7 +1690,7 @@
         <v>PC269.png</v>
       </c>
     </row>
-    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>61</v>
       </c>
@@ -1712,7 +1711,7 @@
         <v>PCB350.png</v>
       </c>
     </row>
-    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>61</v>
       </c>
@@ -1733,7 +1732,7 @@
         <v>PCP2.png</v>
       </c>
     </row>
-    <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>62</v>
       </c>
@@ -1755,7 +1754,7 @@
         <v>SK269.png</v>
       </c>
     </row>
-    <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>62</v>
       </c>
@@ -1777,7 +1776,7 @@
         <v>SK269MP.png</v>
       </c>
     </row>
-    <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>62</v>
       </c>
@@ -1799,7 +1798,7 @@
         <v>SKZERO269.png</v>
       </c>
     </row>
-    <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>62</v>
       </c>
@@ -1821,7 +1820,7 @@
         <v>SKZERO350.png</v>
       </c>
     </row>
-    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>62</v>
       </c>
@@ -1843,7 +1842,7 @@
         <v>SPT269.png</v>
       </c>
     </row>
-    <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>62</v>
       </c>
@@ -1865,7 +1864,7 @@
         <v>SPT350.png</v>
       </c>
     </row>
-    <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>62</v>
       </c>
@@ -1887,7 +1886,7 @@
         <v>STE269.png</v>
       </c>
     </row>
-    <row r="47" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>62</v>
       </c>
@@ -1909,7 +1908,7 @@
         <v>STE350.png</v>
       </c>
     </row>
-    <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>62</v>
       </c>
@@ -1931,7 +1930,7 @@
         <v>STELN.png</v>
       </c>
     </row>
-    <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>61</v>
       </c>
@@ -1952,7 +1951,7 @@
         <v>SUKP2.png</v>
       </c>
     </row>
-    <row r="50" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>62</v>
       </c>
@@ -1973,7 +1972,7 @@
         <v>STEPG269.png</v>
       </c>
     </row>
-    <row r="51" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>62</v>
       </c>
@@ -1994,7 +1993,7 @@
         <v>STEPG350.png</v>
       </c>
     </row>
-    <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>62</v>
       </c>
@@ -2038,7 +2037,7 @@
         <v>PCSAB350.png</v>
       </c>
     </row>
-    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>61</v>
       </c>
@@ -2060,7 +2059,7 @@
         <v>GATORADE.png</v>
       </c>
     </row>
-    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>62</v>
       </c>
@@ -2081,7 +2080,7 @@
         <v>BEATSFF.png</v>
       </c>
     </row>
-    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>62</v>
       </c>
@@ -2125,13 +2124,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F56" xr:uid="{C0BF5819-473C-445D-A53D-FC51ACB237C6}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="PC SAB 350"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:F56" xr:uid="{C0BF5819-473C-445D-A53D-FC51ACB237C6}"/>
   <conditionalFormatting sqref="E1:E1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
@@ -2141,7 +2134,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:C578"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2160,7 +2152,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>61</v>
       </c>
@@ -2171,7 +2163,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>61</v>
       </c>
@@ -2182,7 +2174,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>61</v>
       </c>
@@ -2193,7 +2185,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>61</v>
       </c>
@@ -2204,7 +2196,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>61</v>
       </c>
@@ -2215,7 +2207,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>61</v>
       </c>
@@ -2226,7 +2218,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>61</v>
       </c>
@@ -2237,7 +2229,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>61</v>
       </c>
@@ -2248,7 +2240,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>61</v>
       </c>
@@ -2259,7 +2251,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>61</v>
       </c>
@@ -2270,7 +2262,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>61</v>
       </c>
@@ -2281,7 +2273,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>61</v>
       </c>
@@ -2292,7 +2284,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>61</v>
       </c>
@@ -2303,7 +2295,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>61</v>
       </c>
@@ -2314,7 +2306,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>61</v>
       </c>
@@ -2325,7 +2317,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>61</v>
       </c>
@@ -2336,7 +2328,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>61</v>
       </c>
@@ -2347,7 +2339,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>61</v>
       </c>
@@ -2358,7 +2350,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>61</v>
       </c>
@@ -2369,7 +2361,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>61</v>
       </c>
@@ -2380,7 +2372,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>61</v>
       </c>
@@ -2391,7 +2383,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>61</v>
       </c>
@@ -2402,7 +2394,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>61</v>
       </c>
@@ -2413,7 +2405,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>61</v>
       </c>
@@ -2424,7 +2416,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>61</v>
       </c>
@@ -2435,7 +2427,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>61</v>
       </c>
@@ -2446,7 +2438,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>61</v>
       </c>
@@ -2457,7 +2449,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>61</v>
       </c>
@@ -2468,7 +2460,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>61</v>
       </c>
@@ -2479,7 +2471,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>61</v>
       </c>
@@ -2490,7 +2482,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>61</v>
       </c>
@@ -2501,7 +2493,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>61</v>
       </c>
@@ -2512,7 +2504,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>61</v>
       </c>
@@ -2523,7 +2515,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>61</v>
       </c>
@@ -2534,7 +2526,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>61</v>
       </c>
@@ -2545,7 +2537,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>61</v>
       </c>
@@ -2556,7 +2548,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>61</v>
       </c>
@@ -2567,7 +2559,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="39" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>61</v>
       </c>
@@ -2578,7 +2570,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>61</v>
       </c>
@@ -2589,7 +2581,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>61</v>
       </c>
@@ -2600,7 +2592,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="42" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>61</v>
       </c>
@@ -2611,7 +2603,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>61</v>
       </c>
@@ -2622,7 +2614,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="44" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>61</v>
       </c>
@@ -2633,7 +2625,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="45" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>61</v>
       </c>
@@ -2644,7 +2636,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="46" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>61</v>
       </c>
@@ -2655,7 +2647,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="47" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>61</v>
       </c>
@@ -2666,7 +2658,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="48" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>61</v>
       </c>
@@ -2677,7 +2669,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="49" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>61</v>
       </c>
@@ -2688,7 +2680,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="50" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>61</v>
       </c>
@@ -2699,7 +2691,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="51" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>61</v>
       </c>
@@ -2710,7 +2702,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="52" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>61</v>
       </c>
@@ -2721,7 +2713,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="53" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>61</v>
       </c>
@@ -2732,7 +2724,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="54" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>61</v>
       </c>
@@ -2743,7 +2735,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="55" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>61</v>
       </c>
@@ -2754,7 +2746,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="56" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>61</v>
       </c>
@@ -2765,7 +2757,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="57" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>61</v>
       </c>
@@ -2776,7 +2768,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="58" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>61</v>
       </c>
@@ -2787,7 +2779,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="59" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>61</v>
       </c>
@@ -2798,7 +2790,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="60" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>61</v>
       </c>
@@ -2809,7 +2801,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="61" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>61</v>
       </c>
@@ -2820,7 +2812,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="62" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>61</v>
       </c>
@@ -2831,7 +2823,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="63" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>61</v>
       </c>
@@ -2842,7 +2834,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="64" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>61</v>
       </c>
@@ -2853,7 +2845,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="65" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>61</v>
       </c>
@@ -2864,7 +2856,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="66" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>61</v>
       </c>
@@ -2875,7 +2867,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="67" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>61</v>
       </c>
@@ -2886,7 +2878,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="68" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>61</v>
       </c>
@@ -2897,7 +2889,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="69" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>61</v>
       </c>
@@ -2908,7 +2900,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="70" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>61</v>
       </c>
@@ -2919,7 +2911,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="71" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>61</v>
       </c>
@@ -2930,7 +2922,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="72" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>61</v>
       </c>
@@ -2941,7 +2933,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="73" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>61</v>
       </c>
@@ -2952,7 +2944,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="74" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>61</v>
       </c>
@@ -2963,7 +2955,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="75" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>61</v>
       </c>
@@ -2974,7 +2966,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="76" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>61</v>
       </c>
@@ -2985,7 +2977,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="77" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>61</v>
       </c>
@@ -2996,7 +2988,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="78" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>61</v>
       </c>
@@ -3007,7 +2999,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="79" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>61</v>
       </c>
@@ -3018,7 +3010,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="80" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>61</v>
       </c>
@@ -3029,7 +3021,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="81" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>61</v>
       </c>
@@ -3040,7 +3032,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="82" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>61</v>
       </c>
@@ -3051,7 +3043,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="83" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>61</v>
       </c>
@@ -3062,7 +3054,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="84" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>61</v>
       </c>
@@ -3073,7 +3065,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="85" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>61</v>
       </c>
@@ -3084,7 +3076,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="86" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>61</v>
       </c>
@@ -3095,7 +3087,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="87" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>61</v>
       </c>
@@ -3106,7 +3098,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="88" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>61</v>
       </c>
@@ -3117,7 +3109,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="89" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>61</v>
       </c>
@@ -3128,7 +3120,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="90" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>61</v>
       </c>
@@ -3139,7 +3131,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="91" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>61</v>
       </c>
@@ -3150,7 +3142,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="92" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>61</v>
       </c>
@@ -3161,7 +3153,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="93" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>61</v>
       </c>
@@ -3172,7 +3164,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="94" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>61</v>
       </c>
@@ -3183,7 +3175,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="95" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>61</v>
       </c>
@@ -3194,7 +3186,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="96" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>61</v>
       </c>
@@ -3205,7 +3197,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="97" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>61</v>
       </c>
@@ -3216,7 +3208,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="98" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>61</v>
       </c>
@@ -3227,7 +3219,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="99" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>61</v>
       </c>
@@ -3238,7 +3230,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="100" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>61</v>
       </c>
@@ -3249,7 +3241,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="101" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>61</v>
       </c>
@@ -3260,7 +3252,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="102" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>61</v>
       </c>
@@ -3271,7 +3263,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="103" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>61</v>
       </c>
@@ -3282,7 +3274,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="104" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>61</v>
       </c>
@@ -3293,7 +3285,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="105" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>61</v>
       </c>
@@ -3304,7 +3296,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="106" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>61</v>
       </c>
@@ -3315,7 +3307,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="107" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>61</v>
       </c>
@@ -3326,7 +3318,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="108" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>61</v>
       </c>
@@ -3337,7 +3329,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="109" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>61</v>
       </c>
@@ -3348,7 +3340,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="110" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>61</v>
       </c>
@@ -3359,7 +3351,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="111" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>61</v>
       </c>
@@ -3370,7 +3362,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="112" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>61</v>
       </c>
@@ -3381,7 +3373,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="113" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>61</v>
       </c>
@@ -3392,7 +3384,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="114" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>61</v>
       </c>
@@ -3403,7 +3395,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="115" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>61</v>
       </c>
@@ -3414,7 +3406,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="116" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>61</v>
       </c>
@@ -3425,7 +3417,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="117" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>61</v>
       </c>
@@ -3436,7 +3428,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="118" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>61</v>
       </c>
@@ -3447,7 +3439,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="119" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>61</v>
       </c>
@@ -3458,7 +3450,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="120" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>61</v>
       </c>
@@ -3469,7 +3461,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="121" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>61</v>
       </c>
@@ -3480,7 +3472,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="122" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>61</v>
       </c>
@@ -3491,7 +3483,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="123" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>61</v>
       </c>
@@ -3502,7 +3494,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="124" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>61</v>
       </c>
@@ -3513,7 +3505,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="125" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>61</v>
       </c>
@@ -3524,7 +3516,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="126" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>61</v>
       </c>
@@ -3535,7 +3527,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="127" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>61</v>
       </c>
@@ -3546,7 +3538,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="128" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>61</v>
       </c>
@@ -3557,7 +3549,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="129" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>61</v>
       </c>
@@ -3568,7 +3560,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="130" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>61</v>
       </c>
@@ -3579,7 +3571,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="131" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>61</v>
       </c>
@@ -3590,7 +3582,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="132" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>61</v>
       </c>
@@ -3601,7 +3593,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="133" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>61</v>
       </c>
@@ -3612,7 +3604,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="134" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>61</v>
       </c>
@@ -3623,7 +3615,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="135" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>61</v>
       </c>
@@ -3634,7 +3626,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="136" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>61</v>
       </c>
@@ -3645,7 +3637,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="137" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>62</v>
       </c>
@@ -3656,7 +3648,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="138" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>62</v>
       </c>
@@ -3667,7 +3659,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="139" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>62</v>
       </c>
@@ -3678,7 +3670,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="140" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>62</v>
       </c>
@@ -3689,7 +3681,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="141" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>62</v>
       </c>
@@ -3700,7 +3692,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="142" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>62</v>
       </c>
@@ -3711,7 +3703,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="143" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>62</v>
       </c>
@@ -3722,7 +3714,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="144" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>62</v>
       </c>
@@ -3733,7 +3725,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="145" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>62</v>
       </c>
@@ -3744,7 +3736,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="146" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>62</v>
       </c>
@@ -3755,7 +3747,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="147" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>62</v>
       </c>
@@ -3766,7 +3758,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="148" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>62</v>
       </c>
@@ -3777,7 +3769,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="149" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>62</v>
       </c>
@@ -3788,7 +3780,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="150" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>62</v>
       </c>
@@ -3799,7 +3791,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="151" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>62</v>
       </c>
@@ -3810,7 +3802,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="152" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>62</v>
       </c>
@@ -3821,7 +3813,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="153" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>62</v>
       </c>
@@ -3832,7 +3824,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="154" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>62</v>
       </c>
@@ -3843,7 +3835,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="155" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>62</v>
       </c>
@@ -3854,7 +3846,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="156" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>62</v>
       </c>
@@ -3865,7 +3857,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="157" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>62</v>
       </c>
@@ -3876,7 +3868,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="158" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>62</v>
       </c>
@@ -3887,7 +3879,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="159" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>62</v>
       </c>
@@ -3898,7 +3890,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="160" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>62</v>
       </c>
@@ -3909,7 +3901,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="161" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>62</v>
       </c>
@@ -3920,7 +3912,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="162" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>62</v>
       </c>
@@ -3931,7 +3923,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="163" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>62</v>
       </c>
@@ -3942,7 +3934,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="164" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>62</v>
       </c>
@@ -3953,7 +3945,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="165" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>62</v>
       </c>
@@ -3964,7 +3956,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="166" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>62</v>
       </c>
@@ -3975,7 +3967,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="167" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>62</v>
       </c>
@@ -3986,7 +3978,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="168" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>62</v>
       </c>
@@ -3997,7 +3989,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="169" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>62</v>
       </c>
@@ -4008,7 +4000,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="170" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>62</v>
       </c>
@@ -4019,7 +4011,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="171" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>62</v>
       </c>
@@ -4030,7 +4022,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="172" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>62</v>
       </c>
@@ -4041,7 +4033,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="173" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>62</v>
       </c>
@@ -4052,7 +4044,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="174" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>62</v>
       </c>
@@ -4063,7 +4055,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="175" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>62</v>
       </c>
@@ -4074,7 +4066,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="176" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>62</v>
       </c>
@@ -4085,7 +4077,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="177" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>62</v>
       </c>
@@ -4096,7 +4088,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="178" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>62</v>
       </c>
@@ -4107,7 +4099,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="179" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>62</v>
       </c>
@@ -4118,7 +4110,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="180" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>62</v>
       </c>
@@ -4129,7 +4121,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="181" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>62</v>
       </c>
@@ -4140,7 +4132,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="182" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>62</v>
       </c>
@@ -4151,7 +4143,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="183" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>62</v>
       </c>
@@ -4162,7 +4154,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="184" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>62</v>
       </c>
@@ -4173,7 +4165,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="185" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>62</v>
       </c>
@@ -4184,7 +4176,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="186" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>62</v>
       </c>
@@ -4195,7 +4187,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="187" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>62</v>
       </c>
@@ -4206,7 +4198,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="188" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>62</v>
       </c>
@@ -4217,7 +4209,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="189" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>62</v>
       </c>
@@ -4228,7 +4220,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="190" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>62</v>
       </c>
@@ -4239,7 +4231,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="191" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>62</v>
       </c>
@@ -4250,7 +4242,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="192" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>62</v>
       </c>
@@ -4261,7 +4253,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="193" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>62</v>
       </c>
@@ -4272,7 +4264,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="194" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>62</v>
       </c>
@@ -4283,7 +4275,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="195" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>62</v>
       </c>
@@ -4294,7 +4286,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="196" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>62</v>
       </c>
@@ -4305,7 +4297,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="197" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>62</v>
       </c>
@@ -4316,7 +4308,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="198" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>62</v>
       </c>
@@ -4327,7 +4319,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="199" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>62</v>
       </c>
@@ -4338,7 +4330,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="200" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>62</v>
       </c>
@@ -4349,7 +4341,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="201" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>62</v>
       </c>
@@ -4360,7 +4352,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="202" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>62</v>
       </c>
@@ -4371,7 +4363,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="203" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>62</v>
       </c>
@@ -4382,7 +4374,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="204" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>62</v>
       </c>
@@ -4393,7 +4385,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="205" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>62</v>
       </c>
@@ -4404,7 +4396,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="206" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>62</v>
       </c>
@@ -4415,7 +4407,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="207" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>62</v>
       </c>
@@ -4426,7 +4418,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="208" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>62</v>
       </c>
@@ -4437,7 +4429,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="209" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>62</v>
       </c>
@@ -4448,7 +4440,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="210" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>62</v>
       </c>
@@ -4459,7 +4451,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="211" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>62</v>
       </c>
@@ -4470,7 +4462,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="212" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>62</v>
       </c>
@@ -4481,7 +4473,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="213" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>62</v>
       </c>
@@ -4492,7 +4484,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="214" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>62</v>
       </c>
@@ -4503,7 +4495,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="215" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>62</v>
       </c>
@@ -4514,7 +4506,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="216" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>62</v>
       </c>
@@ -4525,7 +4517,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="217" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>62</v>
       </c>
@@ -4536,7 +4528,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="218" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>62</v>
       </c>
@@ -4547,7 +4539,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="219" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>62</v>
       </c>
@@ -4558,7 +4550,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="220" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>62</v>
       </c>
@@ -4569,7 +4561,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="221" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>62</v>
       </c>
@@ -4580,7 +4572,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="222" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>62</v>
       </c>
@@ -4591,7 +4583,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="223" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>62</v>
       </c>
@@ -4602,7 +4594,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="224" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>62</v>
       </c>
@@ -4613,7 +4605,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="225" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>62</v>
       </c>
@@ -4624,7 +4616,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="226" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>62</v>
       </c>
@@ -4635,7 +4627,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="227" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>62</v>
       </c>
@@ -4646,7 +4638,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="228" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>62</v>
       </c>
@@ -4657,7 +4649,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="229" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>62</v>
       </c>
@@ -4668,7 +4660,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="230" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>62</v>
       </c>
@@ -4679,7 +4671,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="231" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>62</v>
       </c>
@@ -4690,7 +4682,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="232" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>62</v>
       </c>
@@ -4701,7 +4693,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="233" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>62</v>
       </c>
@@ -4712,7 +4704,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="234" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>62</v>
       </c>
@@ -4723,7 +4715,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="235" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>62</v>
       </c>
@@ -4734,7 +4726,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="236" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>62</v>
       </c>
@@ -4745,7 +4737,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="237" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>62</v>
       </c>
@@ -4756,7 +4748,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="238" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>62</v>
       </c>
@@ -4767,7 +4759,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="239" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>62</v>
       </c>
@@ -4778,7 +4770,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="240" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>62</v>
       </c>
@@ -4789,7 +4781,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="241" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>62</v>
       </c>
@@ -4800,7 +4792,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="242" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>62</v>
       </c>
@@ -4811,7 +4803,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="243" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>62</v>
       </c>
@@ -4822,7 +4814,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="244" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>62</v>
       </c>
@@ -4833,7 +4825,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="245" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>62</v>
       </c>
@@ -4844,7 +4836,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="246" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>62</v>
       </c>
@@ -4855,7 +4847,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="247" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>62</v>
       </c>
@@ -4866,7 +4858,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="248" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>62</v>
       </c>
@@ -4877,7 +4869,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="249" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>62</v>
       </c>
@@ -4888,7 +4880,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="250" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>62</v>
       </c>
@@ -4899,7 +4891,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="251" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>62</v>
       </c>
@@ -4910,7 +4902,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="252" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>62</v>
       </c>
@@ -4921,7 +4913,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="253" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>62</v>
       </c>
@@ -4932,7 +4924,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="254" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>62</v>
       </c>
@@ -4943,7 +4935,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="255" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>62</v>
       </c>
@@ -4954,7 +4946,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="256" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>62</v>
       </c>
@@ -4965,7 +4957,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="257" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>62</v>
       </c>
@@ -4976,7 +4968,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="258" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>62</v>
       </c>
@@ -4987,7 +4979,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="259" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>62</v>
       </c>
@@ -4998,7 +4990,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="260" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>62</v>
       </c>
@@ -5009,7 +5001,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="261" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>62</v>
       </c>
@@ -5020,7 +5012,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="262" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>62</v>
       </c>
@@ -5031,7 +5023,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="263" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>62</v>
       </c>
@@ -5042,7 +5034,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="264" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>62</v>
       </c>
@@ -5053,7 +5045,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="265" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>62</v>
       </c>
@@ -5064,7 +5056,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="266" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>62</v>
       </c>
@@ -5075,7 +5067,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="267" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>62</v>
       </c>
@@ -5086,7 +5078,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="268" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>62</v>
       </c>
@@ -5097,7 +5089,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="269" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>62</v>
       </c>
@@ -5108,7 +5100,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="270" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>62</v>
       </c>
@@ -5119,7 +5111,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="271" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>62</v>
       </c>
@@ -5130,7 +5122,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="272" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>62</v>
       </c>
@@ -5141,7 +5133,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="273" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>62</v>
       </c>
@@ -5152,7 +5144,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="274" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>62</v>
       </c>
@@ -5163,7 +5155,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="275" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>62</v>
       </c>
@@ -5174,59 +5166,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="276" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="277" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="278" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="279" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="280" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="281" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="282" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="283" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="284" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="285" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="286" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="287" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="288" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="289" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="290" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="291" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="292" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="293" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="294" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="295" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="296" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="297" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="298" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="299" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="300" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="301" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="302" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="303" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="304" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="305" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="306" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="307" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="308" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="309" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="310" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="311" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="312" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="313" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="314" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="315" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="316" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="317" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="318" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="319" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="320" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="321" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="322" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="323" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="324" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="325" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="326" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="327" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="328" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>104</v>
       </c>
@@ -5237,7 +5177,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="329" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>104</v>
       </c>
@@ -5248,7 +5188,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="330" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>104</v>
       </c>
@@ -5259,7 +5199,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="331" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>104</v>
       </c>
@@ -5270,7 +5210,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="332" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>104</v>
       </c>
@@ -5281,7 +5221,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="333" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>104</v>
       </c>
@@ -5292,7 +5232,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="334" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>104</v>
       </c>
@@ -5303,7 +5243,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="335" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>104</v>
       </c>
@@ -5314,7 +5254,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="336" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>104</v>
       </c>
@@ -5325,7 +5265,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="337" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>104</v>
       </c>
@@ -5336,7 +5276,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="338" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>104</v>
       </c>
@@ -5347,7 +5287,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="339" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>104</v>
       </c>
@@ -5358,7 +5298,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="340" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>104</v>
       </c>
@@ -5369,7 +5309,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="341" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>104</v>
       </c>
@@ -5380,7 +5320,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="342" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>104</v>
       </c>
@@ -5391,7 +5331,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="343" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>104</v>
       </c>
@@ -5402,7 +5342,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="344" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>104</v>
       </c>
@@ -5413,7 +5353,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="345" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>104</v>
       </c>
@@ -5424,7 +5364,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="346" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>104</v>
       </c>
@@ -5435,7 +5375,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="347" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>104</v>
       </c>
@@ -5446,7 +5386,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="348" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>104</v>
       </c>
@@ -5457,7 +5397,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="349" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>104</v>
       </c>
@@ -5468,7 +5408,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="350" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>104</v>
       </c>
@@ -5479,7 +5419,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="351" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>104</v>
       </c>
@@ -5490,7 +5430,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="352" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>104</v>
       </c>
@@ -5501,7 +5441,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="353" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>104</v>
       </c>
@@ -5512,7 +5452,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="354" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>104</v>
       </c>
@@ -5523,7 +5463,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="355" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>104</v>
       </c>
@@ -5534,7 +5474,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="356" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>104</v>
       </c>
@@ -5545,7 +5485,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="357" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>104</v>
       </c>
@@ -5556,7 +5496,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="358" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>104</v>
       </c>
@@ -5567,7 +5507,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="359" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>104</v>
       </c>
@@ -5578,7 +5518,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="360" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>104</v>
       </c>
@@ -5589,7 +5529,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="361" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>104</v>
       </c>
@@ -5600,7 +5540,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="362" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>104</v>
       </c>
@@ -5611,7 +5551,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="363" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>104</v>
       </c>
@@ -5622,7 +5562,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="364" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>104</v>
       </c>
@@ -5633,7 +5573,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="365" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>104</v>
       </c>
@@ -5644,7 +5584,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="366" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>104</v>
       </c>
@@ -5655,7 +5595,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="367" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>104</v>
       </c>
@@ -5666,7 +5606,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="368" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>104</v>
       </c>
@@ -5677,7 +5617,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="369" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>104</v>
       </c>
@@ -5688,7 +5628,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="370" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>104</v>
       </c>
@@ -5699,7 +5639,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="371" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>104</v>
       </c>
@@ -5710,7 +5650,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="372" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>104</v>
       </c>
@@ -5721,7 +5661,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="373" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>104</v>
       </c>
@@ -5732,7 +5672,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="374" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>104</v>
       </c>
@@ -5743,7 +5683,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="375" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>104</v>
       </c>
@@ -5754,7 +5694,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="376" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>104</v>
       </c>
@@ -5765,7 +5705,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="377" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>104</v>
       </c>
@@ -5776,7 +5716,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="378" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>104</v>
       </c>
@@ -5787,7 +5727,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="379" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>104</v>
       </c>
@@ -5798,7 +5738,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="380" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>104</v>
       </c>
@@ -5809,7 +5749,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="381" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>104</v>
       </c>
@@ -5820,7 +5760,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="382" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>104</v>
       </c>
@@ -5831,7 +5771,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="383" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>104</v>
       </c>
@@ -5842,7 +5782,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="384" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>104</v>
       </c>
@@ -5853,7 +5793,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="385" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>104</v>
       </c>
@@ -5864,7 +5804,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="386" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>104</v>
       </c>
@@ -5875,7 +5815,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="387" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>104</v>
       </c>
@@ -5886,7 +5826,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="388" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>104</v>
       </c>
@@ -5897,7 +5837,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="389" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>104</v>
       </c>
@@ -5908,7 +5848,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="390" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>104</v>
       </c>
@@ -5919,7 +5859,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="391" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>104</v>
       </c>
@@ -5930,7 +5870,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="392" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>104</v>
       </c>
@@ -5941,7 +5881,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="393" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>104</v>
       </c>
@@ -5952,7 +5892,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="394" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>104</v>
       </c>
@@ -5963,7 +5903,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="395" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>104</v>
       </c>
@@ -5974,7 +5914,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="396" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>104</v>
       </c>
@@ -5985,7 +5925,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="397" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>104</v>
       </c>
@@ -5996,7 +5936,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="398" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>104</v>
       </c>
@@ -6007,7 +5947,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="399" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>104</v>
       </c>
@@ -6018,7 +5958,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="400" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>104</v>
       </c>
@@ -6029,7 +5969,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="401" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>104</v>
       </c>
@@ -6040,7 +5980,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="402" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>104</v>
       </c>
@@ -6051,7 +5991,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="403" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>104</v>
       </c>
@@ -6062,7 +6002,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="404" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>104</v>
       </c>
@@ -6073,7 +6013,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="405" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>104</v>
       </c>
@@ -6084,7 +6024,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="406" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>104</v>
       </c>
@@ -6095,7 +6035,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="407" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>104</v>
       </c>
@@ -6106,7 +6046,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="408" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>104</v>
       </c>
@@ -6117,7 +6057,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="409" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>104</v>
       </c>
@@ -6128,7 +6068,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="410" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>104</v>
       </c>
@@ -6139,7 +6079,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="411" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>104</v>
       </c>
@@ -6150,7 +6090,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="412" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>104</v>
       </c>
@@ -6161,7 +6101,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="413" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>104</v>
       </c>
@@ -6172,7 +6112,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="414" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>104</v>
       </c>
@@ -6183,7 +6123,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="415" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>104</v>
       </c>
@@ -6194,7 +6134,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="416" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>104</v>
       </c>
@@ -6205,7 +6145,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="417" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>104</v>
       </c>
@@ -6216,7 +6156,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="418" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>104</v>
       </c>
@@ -6227,7 +6167,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="419" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>104</v>
       </c>
@@ -6238,7 +6178,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="420" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>104</v>
       </c>
@@ -6249,7 +6189,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="421" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>104</v>
       </c>
@@ -6260,7 +6200,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="422" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>104</v>
       </c>
@@ -6271,7 +6211,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="423" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>104</v>
       </c>
@@ -6282,7 +6222,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="424" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>104</v>
       </c>
@@ -6293,7 +6233,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="425" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>104</v>
       </c>
@@ -6304,7 +6244,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="426" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>104</v>
       </c>
@@ -6315,7 +6255,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="427" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>104</v>
       </c>
@@ -6326,7 +6266,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="428" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>104</v>
       </c>
@@ -6337,7 +6277,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="429" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>104</v>
       </c>
@@ -6348,7 +6288,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="430" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>104</v>
       </c>
@@ -6359,7 +6299,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="431" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>104</v>
       </c>
@@ -6370,7 +6310,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="432" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>104</v>
       </c>
@@ -6381,7 +6321,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="433" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>104</v>
       </c>
@@ -6392,7 +6332,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="434" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>104</v>
       </c>
@@ -6403,7 +6343,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="435" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>104</v>
       </c>
@@ -6414,7 +6354,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="436" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>104</v>
       </c>
@@ -6425,7 +6365,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="437" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>104</v>
       </c>
@@ -6436,7 +6376,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="438" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>104</v>
       </c>
@@ -6447,7 +6387,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="439" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>104</v>
       </c>
@@ -6458,7 +6398,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="440" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>104</v>
       </c>
@@ -6469,7 +6409,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="441" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>104</v>
       </c>
@@ -6480,7 +6420,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="442" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>104</v>
       </c>
@@ -6491,7 +6431,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="443" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>104</v>
       </c>
@@ -6502,7 +6442,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="444" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>104</v>
       </c>
@@ -6513,7 +6453,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="445" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>104</v>
       </c>
@@ -6524,7 +6464,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="446" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>104</v>
       </c>
@@ -6535,7 +6475,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="447" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>104</v>
       </c>
@@ -6546,7 +6486,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="448" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>104</v>
       </c>
@@ -6557,7 +6497,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="449" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>104</v>
       </c>
@@ -6568,7 +6508,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="450" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>104</v>
       </c>
@@ -6579,7 +6519,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="451" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>104</v>
       </c>
@@ -6590,7 +6530,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="452" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>104</v>
       </c>
@@ -6601,7 +6541,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="453" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>104</v>
       </c>
@@ -6612,7 +6552,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="454" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>104</v>
       </c>
@@ -6623,7 +6563,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="455" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>104</v>
       </c>
@@ -6634,7 +6574,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="456" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>104</v>
       </c>
@@ -6645,7 +6585,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="457" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>104</v>
       </c>
@@ -6656,7 +6596,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="458" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>104</v>
       </c>
@@ -6667,7 +6607,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="459" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>104</v>
       </c>
@@ -6678,7 +6618,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="460" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>104</v>
       </c>
@@ -6689,7 +6629,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="461" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>104</v>
       </c>
@@ -6700,7 +6640,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="462" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>104</v>
       </c>
@@ -6711,7 +6651,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="463" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>104</v>
       </c>
@@ -6722,7 +6662,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="464" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>104</v>
       </c>
@@ -6733,7 +6673,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="465" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>104</v>
       </c>
@@ -6744,7 +6684,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="466" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>104</v>
       </c>
@@ -6755,7 +6695,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="467" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>127</v>
       </c>
@@ -6766,7 +6706,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="468" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>127</v>
       </c>
@@ -6777,7 +6717,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="469" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>127</v>
       </c>
@@ -6788,7 +6728,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="470"